--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41377,13 +41377,13 @@
         <v>-0.02946816111180972</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1084833265175437</v>
+        <v>0.1084833265175429</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002095078499053615</v>
+        <v>0.002095078499053618</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2731943305570402</v>
+        <v>0.2731943305570398</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41530,25 +41530,25 @@
         <v>0.04824898247695586</v>
       </c>
       <c r="AI255" t="n">
-        <v>7.163128638666562</v>
+        <v>7.163128638666564</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.02412869970171805</v>
+        <v>-0.02412869970171982</v>
       </c>
       <c r="AK255" t="n">
-        <v>7.169685517636701</v>
+        <v>7.169685517636702</v>
       </c>
       <c r="AL255" t="n">
-        <v>-0.03068557867185717</v>
+        <v>-0.03068557867185806</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.1070568455331707</v>
+        <v>0.107056845533171</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002204315292537711</v>
+        <v>0.002204315292537673</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2729110366374826</v>
+        <v>0.2729110366374832</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41695,10 +41695,10 @@
         <v>0.04139578206851535</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.159965220045755</v>
+        <v>7.159965220045757</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.01856535966367456</v>
+        <v>-0.01856535966367723</v>
       </c>
       <c r="AK256" t="n">
         <v>7.165514191511657</v>
@@ -41707,13 +41707,13 @@
         <v>-0.02411433112957706</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.1050285904128648</v>
+        <v>0.1050285904128647</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002321116913413366</v>
+        <v>0.002321116913413412</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2720155547682577</v>
+        <v>0.2720155547682573</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41860,10 +41860,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.150419484347115</v>
+        <v>7.150419484347116</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.00901962396503464</v>
+        <v>-0.009019623965035528</v>
       </c>
       <c r="AK257" t="n">
         <v>7.161074530187645</v>
@@ -41872,13 +41872,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.102938554978808</v>
+        <v>0.1029385549788083</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002436328878122375</v>
+        <v>0.002436328878122382</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2711996176877889</v>
+        <v>0.2711996176877891</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42025,10 +42025,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI258" t="n">
-        <v>7.14851145777603</v>
+        <v>7.148511457776028</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-0.01601128611465263</v>
+        <v>-0.01601128611465086</v>
       </c>
       <c r="AK258" t="n">
         <v>7.150963414761942</v>
@@ -42037,13 +42037,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.1011329645838857</v>
+        <v>0.1011329645838851</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.002517185580011383</v>
+        <v>0.002517185580011447</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2709113683260674</v>
+        <v>0.2709113683260677</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42202,13 +42202,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.09870181295186436</v>
+        <v>0.09870181295186471</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.002644711580562605</v>
+        <v>0.002644711580562537</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2704892730019285</v>
+        <v>0.2704892730019304</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42355,10 +42355,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI260" t="n">
-        <v>7.153772633426657</v>
+        <v>7.153772633426659</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-0.03287247931288739</v>
+        <v>-0.03287247931288917</v>
       </c>
       <c r="AK260" t="n">
         <v>7.154757231824306</v>
@@ -42367,13 +42367,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.09555831842873888</v>
+        <v>0.09555831842873846</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.002822832879878049</v>
+        <v>0.002822832879878071</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2697410008595938</v>
+        <v>0.2697410008595936</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42520,10 +42520,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.153331199414497</v>
+        <v>7.153331199414496</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.0326313169071728</v>
+        <v>-0.03263131690717191</v>
       </c>
       <c r="AK261" t="n">
         <v>7.15450652143491</v>
@@ -42532,13 +42532,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.09188440665249918</v>
+        <v>0.0918844066524992</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003041971996730116</v>
+        <v>0.003041971996730133</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2698098046976254</v>
+        <v>0.2698098046976256</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42685,10 +42685,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI262" t="n">
-        <v>7.15694314831959</v>
+        <v>7.156943148319592</v>
       </c>
       <c r="AJ262" t="n">
-        <v>-0.0385430514262799</v>
+        <v>-0.03854305142628167</v>
       </c>
       <c r="AK262" t="n">
         <v>7.154505434137821</v>
@@ -42697,13 +42697,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.08748497753913362</v>
+        <v>0.08748497753913406</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.003298336925509857</v>
+        <v>0.003298336925509862</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2682008942988222</v>
+        <v>0.2682008942988235</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42862,13 +42862,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM263" t="n">
-        <v>0.08245870840593096</v>
+        <v>0.0824587084059305</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.003602928090795422</v>
+        <v>0.003602928090795432</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2685806390401518</v>
+        <v>0.2685806390401517</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43030,10 +43030,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.003819541738581439</v>
+        <v>0.003819541738581442</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.2696768907787754</v>
+        <v>0.2696768907787764</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43180,10 +43180,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.154685377655176</v>
+        <v>7.154685377655177</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.04048526245131878</v>
+        <v>-0.04048526245131967</v>
       </c>
       <c r="AK265" t="n">
         <v>7.15808570026938</v>
@@ -43192,13 +43192,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.07200163454913533</v>
+        <v>0.07200163454913491</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.004193740708391577</v>
+        <v>0.004193740708391541</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.2701165988147326</v>
+        <v>0.270116598814735</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43345,10 +43345,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI266" t="n">
-        <v>7.158449213455078</v>
+        <v>7.158449213455076</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-0.05514911885058549</v>
+        <v>-0.05514911885058371</v>
       </c>
       <c r="AK266" t="n">
         <v>7.157644979270017</v>
@@ -43357,13 +43357,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.06676111471939436</v>
+        <v>0.06676111471939408</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.004505219337594384</v>
+        <v>0.00450521933759436</v>
       </c>
       <c r="AO266" t="n">
-        <v>0.2733976337163387</v>
+        <v>0.2733976337163381</v>
       </c>
       <c r="AP266" t="n">
         <v/>
@@ -43510,10 +43510,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.160761769069201</v>
+        <v>7.160761769069204</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04786198879576364</v>
+        <v>-0.04786198879576631</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159146249199162</v>
@@ -43522,10 +43522,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.06148465881746766</v>
+        <v>0.06148465881746725</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.004852471327681566</v>
+        <v>0.004852471327681615</v>
       </c>
       <c r="AO267" t="n">
         <v>0.2778048766368325</v>
@@ -43675,10 +43675,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI268" t="n">
-        <v>7.162478122158094</v>
+        <v>7.162478122158095</v>
       </c>
       <c r="AJ268" t="n">
-        <v>-0.04957834188465693</v>
+        <v>-0.04957834188465782</v>
       </c>
       <c r="AK268" t="n">
         <v>7.159578986975002</v>
@@ -43687,13 +43687,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.05582594297075712</v>
+        <v>0.05582594297075769</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.005234102211236467</v>
+        <v>0.005234102211236422</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.2824480243750598</v>
+        <v>0.282448024375059</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43852,13 +43852,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.04949165986049463</v>
+        <v>0.04949165986049534</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.005677665039252918</v>
+        <v>0.005677665039252891</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.2878618994559794</v>
+        <v>0.2878618994559775</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -44017,13 +44017,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.04287777011073606</v>
+        <v>0.04287777011073584</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.006155260602669625</v>
+        <v>0.006155260602669632</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.2948468705933236</v>
+        <v>0.2948468705933219</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44170,10 +44170,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.173971773133423</v>
+        <v>7.173971773133425</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.04247200582995614</v>
+        <v>-0.04247200582995792</v>
       </c>
       <c r="AK271" t="n">
         <v>7.159255388854645</v>
@@ -44182,13 +44182,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.03486942009661778</v>
+        <v>0.0348694200966178</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.006728155724408201</v>
+        <v>0.006728155724408227</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3044998756423967</v>
+        <v>0.304499875642397</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44335,25 +44335,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.172030417300565</v>
+        <v>7.172030417300567</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.03823038754592645</v>
+        <v>-0.03823038754592822</v>
       </c>
       <c r="AK272" t="n">
-        <v>7.167062070913352</v>
+        <v>7.167062070913353</v>
       </c>
       <c r="AL272" t="n">
-        <v>-0.03326204115871345</v>
+        <v>-0.03326204115871434</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.03279550096037874</v>
+        <v>0.03279550096037902</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.006903991232239758</v>
+        <v>0.006903991232239788</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3170366335916608</v>
+        <v>0.3170366335916601</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44500,10 +44500,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.171236182927454</v>
+        <v>7.171236182927453</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.0384360806935673</v>
+        <v>-0.03843608069356641</v>
       </c>
       <c r="AK273" t="n">
         <v>7.16747443083108</v>
@@ -44512,13 +44512,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.02972414459983913</v>
+        <v>0.02972414459983895</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.007158147882859</v>
+        <v>0.007158147882858998</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3270754385893863</v>
+        <v>0.3270754385893867</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44665,10 +44665,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI274" t="n">
-        <v>7.170425137628194</v>
+        <v>7.170425137628191</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-0.0510251132141315</v>
+        <v>-0.05102511321412884</v>
       </c>
       <c r="AK274" t="n">
         <v>7.168373097443463</v>
@@ -44677,13 +44677,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.02657019411530295</v>
+        <v>0.02657019411530269</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.007420436972250398</v>
+        <v>0.007420436972250415</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3357224795973281</v>
+        <v>0.3357224795973284</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44842,13 +44842,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.02366886174665165</v>
+        <v>0.02366886174665103</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.007679120311627231</v>
+        <v>0.007679120311627263</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.345021958194194</v>
+        <v>0.3450219581941938</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -44995,10 +44995,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI276" t="n">
-        <v>7.172249622131823</v>
+        <v>7.172249622131827</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-0.05324966409349319</v>
+        <v>-0.05324966409349674</v>
       </c>
       <c r="AK276" t="n">
         <v>7.167365057101177</v>
@@ -45007,13 +45007,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01956653131084189</v>
+        <v>0.01956653131084185</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008034860291676519</v>
+        <v>0.008034860291676559</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.3572033251592186</v>
+        <v>0.3572033251592189</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45160,10 +45160,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.171656420777023</v>
+        <v>7.171656420777024</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.0526564627386934</v>
+        <v>-0.05265646273869429</v>
       </c>
       <c r="AK277" t="n">
         <v>7.167567681415887</v>
@@ -45172,13 +45172,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM277" t="n">
-        <v>0.0163839608889081</v>
+        <v>0.01638396088890769</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.008326212487477898</v>
+        <v>0.008326212487477964</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.3674516177552964</v>
+        <v>0.3674516177552961</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45325,10 +45325,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI278" t="n">
-        <v>7.175289829564746</v>
+        <v>7.175289829564748</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-0.05628987152641596</v>
+        <v>-0.05628987152641773</v>
       </c>
       <c r="AK278" t="n">
         <v>7.167553154788029</v>
@@ -45337,13 +45337,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.01351198449095179</v>
+        <v>0.01351198449095157</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.008601682347582911</v>
+        <v>0.008601682347582891</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.375864684661753</v>
+        <v>0.3758646846617525</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45496,19 +45496,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK279" t="n">
-        <v>7.167460814777641</v>
+        <v>7.16746081477764</v>
       </c>
       <c r="AL279" t="n">
-        <v>-0.048460856739311</v>
+        <v>-0.04846085673931011</v>
       </c>
       <c r="AM279" t="n">
-        <v>0.01196199498966377</v>
+        <v>0.01196199498966369</v>
       </c>
       <c r="AN279" t="n">
-        <v>0.008797062853284078</v>
+        <v>0.008797062853284063</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.3847384959530228</v>
+        <v>0.3847384959530242</v>
       </c>
       <c r="AP279" t="n">
         <v/>
@@ -45816,10 +45816,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI281" t="n">
-        <v>7.189678003526526</v>
+        <v>7.189678003526525</v>
       </c>
       <c r="AJ281" t="n">
-        <v>-0.07117777082999321</v>
+        <v>-0.07117777082999144</v>
       </c>
       <c r="AK281" t="n">
         <v/>
@@ -45828,13 +45828,13 @@
         <v/>
       </c>
       <c r="AM281" t="n">
-        <v>0.007307555239791735</v>
+        <v>0.007307555239791734</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009236289154790363</v>
+        <v>0.009236289154790337</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4010397173569483</v>
+        <v>0.401039717356949</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45981,10 +45981,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI282" t="n">
-        <v>7.183919177237466</v>
+        <v>7.183919177237467</v>
       </c>
       <c r="AJ282" t="n">
-        <v>-0.056419120017007</v>
+        <v>-0.05641912001700788</v>
       </c>
       <c r="AK282" t="n">
         <v>7.168706858585229</v>
@@ -45993,13 +45993,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.006573598200531427</v>
+        <v>0.006573598200530942</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009378157495070007</v>
+        <v>0.009378157495070056</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4093166892046876</v>
+        <v>0.4093166892046883</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46158,13 +46158,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.00571969992866044</v>
+        <v>0.005719699928660468</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009535855797507651</v>
+        <v>0.009535855797507643</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4189456552735351</v>
+        <v>0.4189456552735356</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46311,10 +46311,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI284" t="n">
-        <v>7.183803634757355</v>
+        <v>7.183803634757356</v>
       </c>
       <c r="AJ284" t="n">
-        <v>-0.08380373012478692</v>
+        <v>-0.08380373012478781</v>
       </c>
       <c r="AK284" t="n">
         <v>7.157754776965645</v>
@@ -46323,13 +46323,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.007205793377055721</v>
+        <v>0.007205793377056199</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.00954184705868257</v>
+        <v>0.009541847058682544</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4265135453780416</v>
+        <v>0.4265135453780396</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46482,19 +46482,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK285" t="n">
-        <v>7.153578345933643</v>
+        <v>7.153578345933642</v>
       </c>
       <c r="AL285" t="n">
-        <v>-0.01517826811381884</v>
+        <v>-0.01517826811381795</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.009937300636551421</v>
+        <v>0.009937300636551308</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009475108253955637</v>
+        <v>0.00947510825395563</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.4359288044119891</v>
+        <v>0.4359288044119884</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46641,10 +46641,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI286" t="n">
-        <v>7.175374323571332</v>
+        <v>7.175374323571331</v>
       </c>
       <c r="AJ286" t="n">
-        <v>-0.04917412444413483</v>
+        <v>-0.04917412444413394</v>
       </c>
       <c r="AK286" t="n">
         <v>7.155226204999164</v>
@@ -46653,13 +46653,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01039951522374727</v>
+        <v>0.01039951522374721</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009534227083684297</v>
+        <v>0.009534227083684284</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4462248692464653</v>
+        <v>0.446224869246465</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46818,13 +46818,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.01174445052819296</v>
+        <v>0.01174445052819259</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009539024405591111</v>
+        <v>0.009539024405591096</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4561706550234662</v>
+        <v>0.4561706550234678</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46971,10 +46971,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI288" t="n">
-        <v>7.176295466764673</v>
+        <v>7.176295466764674</v>
       </c>
       <c r="AJ288" t="n">
-        <v>-0.04989547286818841</v>
+        <v>-0.04989547286818929</v>
       </c>
       <c r="AK288" t="n">
         <v>7.150954883812801</v>
@@ -46983,13 +46983,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.01399948938427885</v>
+        <v>0.01399948938427905</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009474826008246765</v>
+        <v>0.009474826008246758</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.4654004237248376</v>
+        <v>0.4654004237248369</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47148,13 +47148,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM289" t="n">
-        <v>0.01676993900799728</v>
+        <v>0.01676993900799729</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.00937702887797469</v>
+        <v>0.009377028877974699</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.4767009396389351</v>
+        <v>0.476700939638935</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47316,10 +47316,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.009204864903404482</v>
+        <v>0.009204864903404497</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.4883841032893032</v>
+        <v>0.4883841032893044</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47478,13 +47478,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.02435543352765317</v>
+        <v>0.02435543352765289</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.00904582198402234</v>
+        <v>0.009045821984022376</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.4990078266507749</v>
+        <v>0.4990078266507766</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47631,10 +47631,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI292" t="n">
-        <v>7.175210595491394</v>
+        <v>7.175210595491395</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.04951059854315165</v>
+        <v>-0.04951059854315254</v>
       </c>
       <c r="AK292" t="n">
         <v>7.151444380572274</v>
@@ -47643,13 +47643,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.02840267381959008</v>
+        <v>0.02840267381959001</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008843610540066056</v>
+        <v>0.008843610540066053</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5123725312709417</v>
+        <v>0.5123725312709416</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47799,7 +47799,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.05177635201935082</v>
+        <v>-0.05177635201934994</v>
       </c>
       <c r="AK293" t="n">
         <v>7.151307469847429</v>
@@ -47808,13 +47808,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.03189518855892809</v>
+        <v>0.03189518855892823</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008740250954211236</v>
+        <v>0.008740250954211215</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.5303980242931252</v>
+        <v>0.5303980242931245</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47961,10 +47961,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI294" t="n">
-        <v>7.172173616645314</v>
+        <v>7.172173616645312</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.06197368836162287</v>
+        <v>-0.06197368836162021</v>
       </c>
       <c r="AK294" t="n">
         <v>7.152170779642037</v>
@@ -47973,13 +47973,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM294" t="n">
-        <v>0.03448417181877479</v>
+        <v>0.03448417181877508</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008638296330047519</v>
+        <v>0.008638296330047493</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5364004192446541</v>
+        <v>0.536400419244653</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48129,7 +48129,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.08262387272163618</v>
+        <v>-0.08262387272163529</v>
       </c>
       <c r="AK295" t="n">
         <v>7.155242422656618</v>
@@ -48141,10 +48141,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008527848481957647</v>
+        <v>0.008527848481957645</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5479838817473681</v>
+        <v>0.5479838817473677</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48291,10 +48291,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.184188525998638</v>
+        <v>7.18418852599864</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.08518854888682181</v>
+        <v>-0.08518854888682359</v>
       </c>
       <c r="AK296" t="n">
         <v>7.174067278312125</v>
@@ -48303,13 +48303,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.03996026841105382</v>
+        <v>0.03996026841105445</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008497979041970699</v>
+        <v>0.008497979041970659</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.553499551641869</v>
+        <v>0.5534995516418705</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48456,10 +48456,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI297" t="n">
-        <v>7.185513015749274</v>
+        <v>7.185513015749276</v>
       </c>
       <c r="AJ297" t="n">
-        <v>-0.07571315384131516</v>
+        <v>-0.07571315384131694</v>
       </c>
       <c r="AK297" t="n">
         <v>7.175957423377739</v>
@@ -48468,13 +48468,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04233079818885083</v>
+        <v>0.04233079818885077</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008432709457890224</v>
+        <v>0.008432709457890229</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5557951014363788</v>
+        <v>0.5557951014363787</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48627,19 +48627,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK298" t="n">
-        <v>7.174765662541792</v>
+        <v>7.174765662541793</v>
       </c>
       <c r="AL298" t="n">
-        <v>-0.05786569534818842</v>
+        <v>-0.05786569534818931</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04394124299371556</v>
+        <v>0.04394124299371591</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008396387260434506</v>
+        <v>0.008396387260434499</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5565519909812453</v>
+        <v>0.5565519909812464</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48786,10 +48786,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI299" t="n">
-        <v>7.18593291662286</v>
+        <v>7.185932916622859</v>
       </c>
       <c r="AJ299" t="n">
-        <v>-0.01413278005669749</v>
+        <v>-0.0141327800566966</v>
       </c>
       <c r="AK299" t="n">
         <v>7.172730869790855</v>
@@ -48798,13 +48798,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04590755972499803</v>
+        <v>0.04590755972499789</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008346613473328291</v>
+        <v>0.008346613473328282</v>
       </c>
       <c r="AO299" t="n">
-        <v>0.5588443644440755</v>
+        <v>0.5588443644440741</v>
       </c>
       <c r="AP299" t="n">
         <v/>
@@ -48951,10 +48951,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI300" t="n">
-        <v>7.187602005018014</v>
+        <v>7.187602005018013</v>
       </c>
       <c r="AJ300" t="n">
-        <v>-0.0581020927560516</v>
+        <v>-0.05810209275604983</v>
       </c>
       <c r="AK300" t="n">
         <v>7.168923754586179</v>
@@ -48963,10 +48963,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.04658552832149689</v>
+        <v>0.04658552832149703</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008354655440128426</v>
+        <v>0.008354655440128402</v>
       </c>
       <c r="AO300" t="n">
         <v>0.5613325805619827</v>
@@ -49128,13 +49128,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.04820692510781883</v>
+        <v>0.04820692510781933</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008303818071592054</v>
+        <v>0.008303818071592001</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5626464255878516</v>
+        <v>0.5626464255878519</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49293,13 +49293,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.04983084886774771</v>
+        <v>0.04983084886774743</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008251024544031682</v>
+        <v>0.008251024544031704</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5641340630354323</v>
+        <v>0.5641340630354328</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49458,13 +49458,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05170461329917048</v>
+        <v>0.05170461329917111</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008192726391276836</v>
+        <v>0.008192726391276807</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5658195968244545</v>
+        <v>0.5658195968244528</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49623,13 +49623,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05348369580043772</v>
+        <v>0.05348369580043773</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008143044151838252</v>
+        <v>0.008143044151838245</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5671346874885956</v>
+        <v>0.5671346874885959</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49776,10 +49776,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.175179910580593</v>
+        <v>7.175179910580594</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.05588002196975328</v>
+        <v>-0.05588002196975417</v>
       </c>
       <c r="AK305" t="n">
         <v>7.165699812335961</v>
@@ -49788,13 +49788,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.0552098256436935</v>
+        <v>0.05520982564369371</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008124788470663643</v>
+        <v>0.008124788470663676</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5701242576280905</v>
+        <v>0.5701242576280907</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49941,10 +49941,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.173581841712229</v>
+        <v>7.173581841712227</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.05428195310138939</v>
+        <v>-0.05428195310138761</v>
       </c>
       <c r="AK306" t="n">
         <v>7.162626578418298</v>
@@ -49953,13 +49953,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05644890839995281</v>
+        <v>0.05644890839995315</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.008105230252153447</v>
+        <v>0.008105230252153435</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.5713754740215494</v>
+        <v>0.5713754740215509</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50106,10 +50106,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.176011726611838</v>
+        <v>7.176011726611837</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.06401173805592997</v>
+        <v>-0.06401173805592908</v>
       </c>
       <c r="AK307" t="n">
         <v>7.165542054185019</v>
@@ -50118,13 +50118,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.05727663218544039</v>
+        <v>0.05727663218544052</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.008124035226526509</v>
+        <v>0.00812403522652648</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5730004147442582</v>
+        <v>0.573000414744258</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50271,10 +50271,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.176983405221908</v>
+        <v>7.17698340522191</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.07778363334080485</v>
+        <v>-0.07778363334080662</v>
       </c>
       <c r="AK308" t="n">
         <v>7.170209849598846</v>
@@ -50283,13 +50283,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.05825580143844532</v>
+        <v>0.05825580143844533</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.008106527117828759</v>
+        <v>0.008106527117828777</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5728585525731367</v>
+        <v>0.5728585525731363</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50436,10 +50436,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.174841035863563</v>
+        <v>7.174841035863564</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.06734095956961816</v>
+        <v>-0.06734095956961905</v>
       </c>
       <c r="AK309" t="n">
         <v>7.166925629020364</v>
@@ -50448,13 +50448,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM309" t="n">
-        <v>0.05980113395910441</v>
+        <v>0.05980113395910436</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.008056914781095341</v>
+        <v>0.008056914781095353</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5723268395754482</v>
+        <v>0.5723268395754473</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50601,10 +50601,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.179777800337526</v>
+        <v>7.179777800337525</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.07227772404358035</v>
+        <v>-0.07227772404357946</v>
       </c>
       <c r="AK310" t="n">
         <v>7.163704513322672</v>
@@ -50616,10 +50616,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.008007544934860184</v>
+        <v>0.008007544934860181</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.5724055344141876</v>
+        <v>0.5724055344141883</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50766,10 +50766,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.176651545551677</v>
+        <v>7.176651545551679</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.06915146925773197</v>
+        <v>-0.06915146925773374</v>
       </c>
       <c r="AK311" t="n">
         <v>7.163430147298699</v>
@@ -50778,13 +50778,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06321929365038026</v>
+        <v>0.06321929365037962</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007927773212025837</v>
+        <v>0.007927773212025854</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5724635828813827</v>
+        <v>0.572463582881384</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50931,10 +50931,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI312" t="n">
-        <v>7.173279688539582</v>
+        <v>7.173279688539583</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.06577961224563644</v>
+        <v>-0.06577961224563733</v>
       </c>
       <c r="AK312" t="n">
         <v>7.158871783064204</v>
@@ -50943,13 +50943,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.0652304825929222</v>
+        <v>0.06523048259292186</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007809540836127932</v>
+        <v>0.007809540836127948</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.571009056129113</v>
+        <v>0.5710090561291132</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51096,10 +51096,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI313" t="n">
-        <v>7.168542018724479</v>
+        <v>7.168542018724481</v>
       </c>
       <c r="AJ313" t="n">
-        <v>-0.06194221098522146</v>
+        <v>-0.06194221098522323</v>
       </c>
       <c r="AK313" t="n">
         <v>7.152618309751275</v>
@@ -51108,13 +51108,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.06741194340959927</v>
+        <v>0.067411943409599</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007660511838810949</v>
+        <v>0.007660511838810988</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5694124450603408</v>
+        <v>0.5694124450603424</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51261,10 +51261,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI314" t="n">
-        <v>7.161829635752617</v>
+        <v>7.161829635752616</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.0596296044720992</v>
+        <v>-0.05962960447209831</v>
       </c>
       <c r="AK314" t="n">
         <v>7.144956229005203</v>
@@ -51273,16 +51273,16 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.06977835201573281</v>
+        <v>0.06977835201573312</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.007516908058882097</v>
+        <v>0.007516908058882096</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5690369646398684</v>
+        <v>0.5690369646398685</v>
       </c>
       <c r="AP314" t="n">
-        <v>-0.4405932303089651</v>
+        <v>-0.4405932303088999</v>
       </c>
       <c r="AQ314" t="n">
         <v>17.5</v>
@@ -51429,7 +51429,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ315" t="n">
-        <v>-0.07699331565738188</v>
+        <v>-0.07699331565738099</v>
       </c>
       <c r="AK315" t="n">
         <v>7.140422114543136</v>
@@ -51438,16 +51438,16 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.07195366789421676</v>
+        <v>0.07195366789421653</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.007394117938767422</v>
+        <v>0.007394117938767417</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.5693040973288199</v>
+        <v>0.5693040973288186</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.401609825776634</v>
+        <v>-1.401609825776575</v>
       </c>
       <c r="AQ315" t="n">
         <v>5.737704918032787</v>
@@ -51603,16 +51603,16 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.07456301989532414</v>
+        <v>0.07456301989532385</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.007241314760731996</v>
+        <v>0.007241314760732032</v>
       </c>
       <c r="AO316" t="n">
         <v>0.5685877661607006</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.764925667104294</v>
+        <v>-1.764925667104289</v>
       </c>
       <c r="AQ316" t="n">
         <v>3.225806451612903</v>
@@ -51768,16 +51768,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.07747971887849607</v>
+        <v>0.07747971887849656</v>
       </c>
       <c r="AN317" t="n">
-        <v>0.007090143655538702</v>
+        <v>0.0070901436555387</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5681709745664091</v>
+        <v>0.5681709745664083</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.732708967932799</v>
+        <v>-1.732708967932794</v>
       </c>
       <c r="AQ317" t="n">
         <v>4.761904761904762</v>
@@ -51921,10 +51921,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.165084051386047</v>
+        <v>7.165084051386049</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.08998410631768738</v>
+        <v>-0.08998410631768916</v>
       </c>
       <c r="AK318" t="n">
         <v>7.14582045097363</v>
@@ -51933,16 +51933,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08000072584212836</v>
+        <v>0.08000072584212846</v>
       </c>
       <c r="AN318" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5684087510734968</v>
+        <v>0.5684087510734981</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.933309554770118</v>
+        <v>-1.933309554770203</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.34375</v>
@@ -52086,10 +52086,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.161419741275553</v>
+        <v>7.161419741275552</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.08971964514518227</v>
+        <v>-0.08971964514518138</v>
       </c>
       <c r="AK319" t="n">
         <v>7.155707108847959</v>
@@ -52098,16 +52098,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08204996863507528</v>
+        <v>0.08204996863507508</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006919462921967468</v>
+        <v>0.006919462921967476</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5672869954461461</v>
+        <v>0.5672869954461468</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.85197372206685</v>
+        <v>-1.851973722066798</v>
       </c>
       <c r="AQ319" t="n">
         <v>2.307692307692308</v>
@@ -52251,10 +52251,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.155488092579303</v>
+        <v>7.155488092579304</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.08548792091792645</v>
+        <v>-0.08548792091792734</v>
       </c>
       <c r="AK320" t="n">
         <v>7.150451326287159</v>
@@ -52263,16 +52263,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.08469403553214211</v>
+        <v>0.08469403553214168</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006815201188096372</v>
+        <v>0.006815201188096393</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5663505631396781</v>
+        <v>0.5663505631396779</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.585123774138113</v>
+        <v>-1.58512377413815</v>
       </c>
       <c r="AQ320" t="n">
         <v>3.787878787878788</v>
@@ -52416,10 +52416,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.15883281736398</v>
+        <v>7.158832817363979</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.09523275404000575</v>
+        <v>-0.09523275404000398</v>
       </c>
       <c r="AK321" t="n">
         <v>7.147115644271845</v>
@@ -52428,16 +52428,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.08699523504893142</v>
+        <v>0.08699523504893081</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006735083295172689</v>
+        <v>0.006735083295172709</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5654743012892984</v>
+        <v>0.5654743012892969</v>
       </c>
       <c r="AP321" t="n">
-        <v>-2.010469305142959</v>
+        <v>-2.010469305142868</v>
       </c>
       <c r="AQ321" t="n">
         <v>1.492537313432836</v>
@@ -52581,10 +52581,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.161703459649029</v>
+        <v>7.161703459649028</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.09030329409116788</v>
+        <v>-0.090303294091167</v>
       </c>
       <c r="AK322" t="n">
         <v>7.152131804583207</v>
@@ -52593,16 +52593,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.08901512474159586</v>
+        <v>0.08901512474159551</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006668288608758129</v>
+        <v>0.006668288608758136</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5631673144521655</v>
+        <v>0.5631673144521659</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.708641496112943</v>
+        <v>-1.7086414961129</v>
       </c>
       <c r="AQ322" t="n">
         <v>2.205882352941176</v>
@@ -52746,10 +52746,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.162535384813327</v>
+        <v>7.162535384813326</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.09293527952768255</v>
+        <v>-0.09293527952768166</v>
       </c>
       <c r="AK323" t="n">
         <v>7.157753883768605</v>
@@ -52758,16 +52758,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09116436352661936</v>
+        <v>0.09116436352661951</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006624805625172246</v>
+        <v>0.006624805625172231</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5612585549312785</v>
+        <v>0.5612585549312774</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.783048493172593</v>
+        <v>-1.783048493172553</v>
       </c>
       <c r="AQ323" t="n">
         <v>2.898550724637681</v>
@@ -52911,10 +52911,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.166818450294681</v>
+        <v>7.166818450294679</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.09581835111255188</v>
+        <v>-0.0958183511125501</v>
       </c>
       <c r="AK324" t="n">
         <v>7.158620349112049</v>
@@ -52923,16 +52923,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.09320704864741212</v>
+        <v>0.09320704864741254</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006594358041710186</v>
+        <v>0.006594358041710158</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5590514368572459</v>
+        <v>0.5590514368572466</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.86170589090406</v>
+        <v>-1.861705890903985</v>
       </c>
       <c r="AQ324" t="n">
         <v>1.428571428571429</v>
@@ -53076,10 +53076,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.157691007010208</v>
+        <v>7.157691007010206</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.09439087425874337</v>
+        <v>-0.0943908742587416</v>
       </c>
       <c r="AK325" t="n">
         <v>7.164942158928604</v>
@@ -53088,16 +53088,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.09491020692123982</v>
+        <v>0.09491020692123933</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006562900445417306</v>
+        <v>0.006562900445417311</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5551825155208129</v>
+        <v>0.5551825155208145</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.740893009303131</v>
+        <v>-1.740893009303061</v>
       </c>
       <c r="AQ325" t="n">
         <v>2.816901408450704</v>
@@ -53241,10 +53241,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI326" t="n">
-        <v>7.15177642643162</v>
+        <v>7.151776426431621</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.08777629673191267</v>
+        <v>-0.08777629673191356</v>
       </c>
       <c r="AK326" t="n">
         <v>7.154764404811184</v>
@@ -53253,16 +53253,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.0970468105051025</v>
+        <v>0.097046810505102</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006523984583215632</v>
+        <v>0.006523984583215639</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5522992358254815</v>
+        <v>0.5522992358254805</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.397254909158938</v>
+        <v>-1.397254909158988</v>
       </c>
       <c r="AQ326" t="n">
         <v>6.25</v>
@@ -53406,10 +53406,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI327" t="n">
-        <v>7.150992404319682</v>
+        <v>7.15099240431968</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.09309245238486774</v>
+        <v>-0.09309245238486596</v>
       </c>
       <c r="AK327" t="n">
         <v>7.150261540163492</v>
@@ -53418,16 +53418,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.09904197982498671</v>
+        <v>0.09904197982498698</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006505848878330779</v>
+        <v>0.006505848878330736</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5500699492277157</v>
+        <v>0.5500699492277152</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.60660796274169</v>
+        <v>-1.606607962741622</v>
       </c>
       <c r="AQ327" t="n">
         <v>4.10958904109589</v>
@@ -53571,10 +53571,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI328" t="n">
-        <v>7.147140093605207</v>
+        <v>7.147140093605204</v>
       </c>
       <c r="AJ328" t="n">
-        <v>-0.09314019278733543</v>
+        <v>-0.09314019278733277</v>
       </c>
       <c r="AK328" t="n">
         <v>7.148879230661717</v>
@@ -53583,16 +53583,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1013300516539142</v>
+        <v>0.1013300516539148</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006479631055951091</v>
+        <v>0.006479631055951007</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5478993564899672</v>
+        <v>0.5478993564899665</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.5704701060782</v>
+        <v>-1.570470106078097</v>
       </c>
       <c r="AQ328" t="n">
         <v>3.378378378378378</v>
@@ -53742,22 +53742,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK329" t="n">
-        <v>7.145816711184185</v>
+        <v>7.145816711184184</v>
       </c>
       <c r="AL329" t="n">
-        <v>-0.09881677984873605</v>
+        <v>-0.09881677984873516</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1033273874042092</v>
+        <v>0.1033273874042088</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006468712737497656</v>
+        <v>0.006468712737497662</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5455500876237913</v>
+        <v>0.5455500876237902</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.644458314609671</v>
+        <v>-1.644458314609691</v>
       </c>
       <c r="AQ329" t="n">
         <v>2</v>
@@ -53904,7 +53904,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.102826205226771</v>
+        <v>-0.1028262052267701</v>
       </c>
       <c r="AK330" t="n">
         <v>7.139092738717567</v>
@@ -53913,16 +53913,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.1056457020972505</v>
+        <v>0.1056457020972507</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006435041090934217</v>
+        <v>0.006435041090934165</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5433399026839674</v>
+        <v>0.5433399026839665</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.908944663479643</v>
+        <v>-1.908944663479627</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.631578947368421</v>
@@ -54069,7 +54069,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ331" t="n">
-        <v>-0.09909609661495811</v>
+        <v>-0.099096096614959</v>
       </c>
       <c r="AK331" t="n">
         <v>7.140479586010682</v>
@@ -54078,16 +54078,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1076802390191602</v>
+        <v>0.10768023901916</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006405465077205527</v>
+        <v>0.006405465077205547</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5402459241219618</v>
+        <v>0.5402459241219614</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.697400237615708</v>
+        <v>-1.697400237615767</v>
       </c>
       <c r="AQ331" t="n">
         <v>2.597402597402597</v>
@@ -54231,10 +54231,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI332" t="n">
-        <v>7.145743344370558</v>
+        <v>7.145743344370562</v>
       </c>
       <c r="AJ332" t="n">
-        <v>-0.1052431803385758</v>
+        <v>-0.1052431803385794</v>
       </c>
       <c r="AK332" t="n">
         <v>7.136632587022158</v>
@@ -54243,16 +54243,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1100130126862084</v>
+        <v>0.1100130126862077</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.00636655476599019</v>
+        <v>0.006366554765990282</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5375708073661639</v>
+        <v>0.5375708073661647</v>
       </c>
       <c r="AP332" t="n">
-        <v>-1.908750947691146</v>
+        <v>-1.908750947691312</v>
       </c>
       <c r="AQ332" t="n">
         <v>2.564102564102564</v>
@@ -54408,16 +54408,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1122475627674581</v>
+        <v>0.1122475627674583</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.00633726551246258</v>
+        <v>0.006337265512462553</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5341613739773232</v>
+        <v>0.5341613739773245</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.583166329559655</v>
+        <v>-1.583166329559663</v>
       </c>
       <c r="AQ333" t="n">
         <v>3.164556962025316</v>
@@ -54561,10 +54561,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI334" t="n">
-        <v>7.14251973303301</v>
+        <v>7.142519733033009</v>
       </c>
       <c r="AJ334" t="n">
-        <v>-0.1016195026252955</v>
+        <v>-0.1016195026252946</v>
       </c>
       <c r="AK334" t="n">
         <v>7.135172643569136</v>
@@ -54573,16 +54573,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.114650916606818</v>
+        <v>0.1146509166068179</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006337163869517234</v>
+        <v>0.006337163869517243</v>
       </c>
       <c r="AO334" t="n">
-        <v>0.5319767312874311</v>
+        <v>0.5319767312874306</v>
       </c>
       <c r="AP334" t="n">
-        <v>-1.672372608149172</v>
+        <v>-1.672372608149145</v>
       </c>
       <c r="AQ334" t="n">
         <v>2.5</v>
@@ -54738,16 +54738,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.1171965158426948</v>
+        <v>0.1171965158426952</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.00636765350379247</v>
+        <v>0.006367653503792481</v>
       </c>
       <c r="AO335" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP335" t="n">
-        <v>-2.112865586535191</v>
+        <v>-2.112865586535205</v>
       </c>
       <c r="AQ335" t="n">
         <v>1.234567901234568</v>
@@ -54891,10 +54891,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.140851085964112</v>
+        <v>7.140851085964109</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1128512080344244</v>
+        <v>-0.1128512080344217</v>
       </c>
       <c r="AK336" t="n">
         <v>7.142783913375006</v>
@@ -54903,16 +54903,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM336" t="n">
-        <v>0.1192272052402563</v>
+        <v>0.119227205240256</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.00638313303870985</v>
+        <v>0.006383133038709798</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5243060286247104</v>
+        <v>0.5243060286247103</v>
       </c>
       <c r="AP336" t="n">
-        <v>-2.008653898053848</v>
+        <v>-2.00865389805376</v>
       </c>
       <c r="AQ336" t="n">
         <v>2.439024390243902</v>
@@ -55056,10 +55056,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.139245392969565</v>
+        <v>7.139245392969567</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.1112455150398777</v>
+        <v>-0.1112455150398795</v>
       </c>
       <c r="AK337" t="n">
         <v>7.141836927013541</v>
@@ -55068,16 +55068,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1211746327267792</v>
+        <v>0.1211746327267789</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006404909068509461</v>
+        <v>0.006404909068509476</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.518531819719905</v>
+        <v>0.5185318197199045</v>
       </c>
       <c r="AP337" t="n">
-        <v>-1.888782075973597</v>
+        <v>-1.888782075973682</v>
       </c>
       <c r="AQ337" t="n">
         <v>3.614457831325301</v>
@@ -55221,10 +55221,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI338" t="n">
-        <v>7.136520216281902</v>
+        <v>7.136520216281903</v>
       </c>
       <c r="AJ338" t="n">
-        <v>-0.1085203383522142</v>
+        <v>-0.108520338352216</v>
       </c>
       <c r="AK338" t="n">
         <v>7.13958125183462</v>
@@ -55233,16 +55233,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM338" t="n">
-        <v>0.1228335954516143</v>
+        <v>0.1228335954516147</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006430223802628476</v>
+        <v>0.006430223802628449</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.5122974965428486</v>
+        <v>0.5122974965428477</v>
       </c>
       <c r="AP338" t="n">
-        <v>-1.736494972713559</v>
+        <v>-1.736494972713637</v>
       </c>
       <c r="AQ338" t="n">
         <v>4.761904761904762</v>
@@ -55401,13 +55401,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006430805642792618</v>
+        <v>0.006430805642792636</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.5056597011855207</v>
+        <v>0.5056597011855208</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.470659774605421</v>
+        <v>-2.470659774605434</v>
       </c>
       <c r="AQ339" t="n">
         <v>1.176470588235294</v>
@@ -55551,10 +55551,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.13656285793475</v>
+        <v>7.136562857934749</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.1404629090516929</v>
+        <v>-0.140462909051692</v>
       </c>
       <c r="AK340" t="n">
         <v>7.132705938528055</v>
@@ -55566,13 +55566,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006419568115912051</v>
+        <v>0.006419568115912044</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.4979995576252233</v>
+        <v>0.4979995576252224</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.727207985371653</v>
+        <v>-2.727207985371637</v>
       </c>
       <c r="AQ340" t="n">
         <v>1.162790697674419</v>
@@ -55716,10 +55716,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.135435320996254</v>
+        <v>7.135435320996258</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1393353721131971</v>
+        <v>-0.1393353721132016</v>
       </c>
       <c r="AK341" t="n">
         <v>7.134470034900207</v>
@@ -55728,16 +55728,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1290155516631951</v>
+        <v>0.1290155516631957</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006423940675024553</v>
+        <v>0.006423940675024581</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4894561560517011</v>
+        <v>0.489456156051701</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.565086807497373</v>
+        <v>-2.565086807497531</v>
       </c>
       <c r="AQ341" t="n">
         <v>2.873563218390804</v>
@@ -55881,10 +55881,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI342" t="n">
-        <v>7.135221482968312</v>
+        <v>7.135221482968309</v>
       </c>
       <c r="AJ342" t="n">
-        <v>-0.1391215340852554</v>
+        <v>-0.1391215340852527</v>
       </c>
       <c r="AK342" t="n">
         <v>7.133435115388912</v>
@@ -55893,16 +55893,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1313692321875792</v>
+        <v>0.1313692321875789</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006422605647444502</v>
+        <v>0.006422605647444513</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4811392039904442</v>
+        <v>0.4811392039904447</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.452561988903891</v>
+        <v>-2.452561988903807</v>
       </c>
       <c r="AQ342" t="n">
         <v>3.977272727272728</v>
@@ -56046,10 +56046,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI343" t="n">
-        <v>7.129120131622732</v>
+        <v>7.129120131622726</v>
       </c>
       <c r="AJ343" t="n">
-        <v>-0.1360199653019309</v>
+        <v>-0.1360199653019256</v>
       </c>
       <c r="AK343" t="n">
         <v>7.132510325395203</v>
@@ -56058,16 +56058,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1334873867685108</v>
+        <v>0.1334873867685099</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006388619079873553</v>
+        <v>0.006388619079873509</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4724960612931048</v>
+        <v>0.4724960612931043</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.263088388410211</v>
+        <v>-2.263088388410052</v>
       </c>
       <c r="AQ343" t="n">
         <v>5.056179775280899</v>
@@ -56223,16 +56223,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1357975915367741</v>
+        <v>0.1357975915367747</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.006324213907675122</v>
+        <v>0.006324213907675097</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4647750649852558</v>
+        <v>0.4647750649852552</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.339494277788859</v>
+        <v>-2.339494277788878</v>
       </c>
       <c r="AQ344" t="n">
         <v>2.777777777777778</v>
@@ -56376,10 +56376,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI345" t="n">
-        <v>7.122818285283532</v>
+        <v>7.122818285283529</v>
       </c>
       <c r="AJ345" t="n">
-        <v>-0.1394184172720578</v>
+        <v>-0.1394184172720543</v>
       </c>
       <c r="AK345" t="n">
         <v>7.123271418608565</v>
@@ -56388,16 +56388,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1386638579210689</v>
+        <v>0.1386638579210687</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.006222091828703747</v>
+        <v>0.006222091828703702</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4565264017486775</v>
+        <v>0.4565264017486783</v>
       </c>
       <c r="AP345" t="n">
-        <v>-2.212855822565248</v>
+        <v>-2.212855822565158</v>
       </c>
       <c r="AQ345" t="n">
         <v>3.846153846153847</v>
@@ -56553,16 +56553,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM346" t="n">
-        <v>0.1423176752089981</v>
+        <v>0.1423176752089984</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.006093783709292289</v>
+        <v>0.006093783709292283</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4497199830569214</v>
+        <v>0.4497199830569224</v>
       </c>
       <c r="AP346" t="n">
-        <v>-1.839621473354138</v>
+        <v>-1.839621473354158</v>
       </c>
       <c r="AQ346" t="n">
         <v>8.695652173913043</v>
@@ -56706,10 +56706,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.13316040486909</v>
+        <v>7.133160404869088</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1496604010543923</v>
+        <v>-0.1496604010543905</v>
       </c>
       <c r="AK347" t="n">
         <v>7.117219286120759</v>
@@ -56721,13 +56721,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005984113522022499</v>
+        <v>0.005984113522022494</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4438783751010228</v>
+        <v>0.4438783751010233</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.393245268221441</v>
+        <v>-2.393245268221414</v>
       </c>
       <c r="AQ347" t="n">
         <v>7.526881720430107</v>
@@ -56871,10 +56871,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.129653220712091</v>
+        <v>7.12965322071209</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.152453189431573</v>
+        <v>-0.1524531894315722</v>
       </c>
       <c r="AK348" t="n">
         <v>7.126254605494273</v>
@@ -56883,16 +56883,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1503893187551739</v>
+        <v>0.1503893187551748</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005963146506628762</v>
+        <v>0.005963146506628741</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.441201873624737</v>
+        <v>0.4412018736247373</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.388213882432258</v>
+        <v>-2.388213882432259</v>
       </c>
       <c r="AQ348" t="n">
         <v>7.446808510638299</v>
@@ -57036,10 +57036,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.128380415829729</v>
+        <v>7.128380415829728</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1552802304354417</v>
+        <v>-0.1552802304354408</v>
       </c>
       <c r="AK349" t="n">
         <v>7.124321202568002</v>
@@ -57048,16 +57048,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1546287435667593</v>
+        <v>0.1546287435667592</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.005975981199024824</v>
+        <v>0.005975981199024843</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.43858274446866</v>
+        <v>0.4385827444686599</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.383472938167509</v>
+        <v>-2.383472938167511</v>
       </c>
       <c r="AQ349" t="n">
         <v>7.36842105263158</v>
@@ -57201,10 +57201,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI350" t="n">
-        <v>7.124429161493114</v>
+        <v>7.124429161493117</v>
       </c>
       <c r="AJ350" t="n">
-        <v>-0.1469291996400868</v>
+        <v>-0.1469291996400894</v>
       </c>
       <c r="AK350" t="n">
         <v>7.121152072356459</v>
@@ -57213,16 +57213,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1587808126513008</v>
+        <v>0.1587808126513012</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.005899221619931436</v>
+        <v>0.00589922161993145</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.4336499747757655</v>
+        <v>0.4336499747757657</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.079767923589147</v>
+        <v>-2.079767923589242</v>
       </c>
       <c r="AQ350" t="n">
         <v>15.625</v>
@@ -57378,16 +57378,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1636493008978486</v>
+        <v>0.1636493008978488</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.005897856672615022</v>
+        <v>0.005897856672615054</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4343048343988722</v>
+        <v>0.434304834398872</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.389525538660926</v>
+        <v>-2.389525538660947</v>
       </c>
       <c r="AQ351" t="n">
         <v>13.4020618556701</v>
@@ -57531,10 +57531,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.141397967314151</v>
+        <v>7.141397967314147</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1753978872055084</v>
+        <v>-0.1753978872055049</v>
       </c>
       <c r="AK352" t="n">
         <v>7.12802266215534</v>
@@ -57543,16 +57543,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1676675897666616</v>
+        <v>0.1676675897666615</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.005952601612807589</v>
+        <v>0.005952601612807557</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4322693842687804</v>
+        <v>0.4322693842687806</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.675191840286052</v>
+        <v>-2.675191840285986</v>
       </c>
       <c r="AQ352" t="n">
         <v>12.24489795918367</v>
@@ -57696,10 +57696,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.140412492855501</v>
+        <v>7.140412492855504</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.1723124219021317</v>
+        <v>-0.1723124219021352</v>
       </c>
       <c r="AK353" t="n">
         <v>7.137738577466652</v>
@@ -57708,16 +57708,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.1710383543493662</v>
+        <v>0.1710383543493657</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.00606844425683546</v>
+        <v>0.006068444256835448</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4285062718639572</v>
+        <v>0.4285062718639565</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.494973402314836</v>
+        <v>-2.494973402314948</v>
       </c>
       <c r="AQ353" t="n">
         <v>19.19191919191919</v>
@@ -57861,10 +57861,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.138020503721584</v>
+        <v>7.138020503721587</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1699204327682153</v>
+        <v>-0.169920432768218</v>
       </c>
       <c r="AK354" t="n">
         <v>7.13663078035759</v>
@@ -57873,16 +57873,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1761956824342154</v>
+        <v>0.176195682434215</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.006402952059750703</v>
+        <v>0.006402952059750722</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4374093872433956</v>
+        <v>0.4374093872433962</v>
       </c>
       <c r="AP354" t="n">
-        <v>-2.351019822312645</v>
+        <v>-2.351019822312725</v>
       </c>
       <c r="AQ354" t="n">
         <v>19</v>
@@ -58026,28 +58026,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI355" t="n">
-        <v>7.136830620687383</v>
+        <v>7.136830620687384</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1769307183436331</v>
+        <v>-0.1769307183436339</v>
       </c>
       <c r="AK355" t="n">
-        <v>7.140049017840021</v>
+        <v>7.14004901784002</v>
       </c>
       <c r="AL355" t="n">
-        <v>-0.1801491154962713</v>
+        <v>-0.1801491154962704</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1796308914905974</v>
+        <v>0.1796308914905975</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.006948414844703805</v>
+        <v>0.006948414844703821</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4458727441769483</v>
+        <v>0.4458727441769479</v>
       </c>
       <c r="AP355" t="n">
-        <v>-2.440918439429997</v>
+        <v>-2.440918439430029</v>
       </c>
       <c r="AQ355" t="n">
         <v>17.32673267326733</v>
@@ -58187,10 +58187,10 @@
         <v/>
       </c>
       <c r="AI356" t="n">
-        <v>7.13363857926656</v>
+        <v>7.133638579266565</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1699387616090897</v>
+        <v>-0.1699387616090942</v>
       </c>
       <c r="AK356" t="n">
         <v>7.13798584867198</v>
@@ -58199,16 +58199,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1829391475229935</v>
+        <v>0.1829391475229931</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.00760204732154433</v>
+        <v>0.007602047321544403</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4545618931940826</v>
+        <v>0.4545618931940824</v>
       </c>
       <c r="AP356" t="n">
-        <v>-2.200405813749797</v>
+        <v>-2.200405813749908</v>
       </c>
       <c r="AQ356" t="n">
         <v>26.96078431372549</v>
@@ -58352,10 +58352,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI357" t="n">
-        <v>7.126409468908567</v>
+        <v>7.12640946890857</v>
       </c>
       <c r="AJ357" t="n">
-        <v>-0.1538094856932348</v>
+        <v>-0.1538094856932375</v>
       </c>
       <c r="AK357" t="n">
         <v>7.138565167526504</v>
@@ -58364,16 +58364,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1834764543657157</v>
+        <v>0.1834764543657148</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.007712839302340297</v>
+        <v>0.007712839302340374</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4511257152112024</v>
+        <v>0.4511257152112026</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.769646277064464</v>
+        <v>-1.769646277064527</v>
       </c>
       <c r="AQ357" t="n">
         <v>22.02075004759185</v>
@@ -58517,10 +58517,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI358" t="n">
-        <v>7.110999512759042</v>
+        <v>7.110999512759045</v>
       </c>
       <c r="AJ358" t="n">
-        <v>-0.1383995295437099</v>
+        <v>-0.1383995295437126</v>
       </c>
       <c r="AK358" t="n">
         <v>7.137040595974374</v>
@@ -58529,16 +58529,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.1869739626316108</v>
+        <v>0.1869739626316104</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.008354609519984808</v>
+        <v>0.00835460951998479</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4618871834350127</v>
+        <v>0.4618871834350119</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.377633656933842</v>
+        <v>-1.377633656933903</v>
       </c>
       <c r="AQ358" t="n">
         <v>16.42550410754294</v>
@@ -58694,16 +58694,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.1901371272406383</v>
+        <v>0.1901371272406391</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.008787529863310259</v>
+        <v>0.008787529863310189</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4631528842621208</v>
+        <v>0.4631528842621211</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.413967751523646</v>
+        <v>-1.413967751523643</v>
       </c>
       <c r="AQ359" t="n">
         <v>10.03663003663004</v>
@@ -58847,10 +58847,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI360" t="n">
-        <v>7.102293381264122</v>
+        <v>7.10229338126412</v>
       </c>
       <c r="AJ360" t="n">
-        <v>-0.1477931828998642</v>
+        <v>-0.1477931828998624</v>
       </c>
       <c r="AK360" t="n">
         <v>7.113436809075056</v>
@@ -58859,16 +58859,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.193945683545753</v>
+        <v>0.1939456835457532</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.009306466714917755</v>
+        <v>0.009306466714917722</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4650211967660295</v>
+        <v>0.4650211967660294</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.556195774880501</v>
+        <v>-1.556195774880458</v>
       </c>
       <c r="AQ360" t="n">
         <v>10.90296495956873</v>
@@ -59024,16 +59024,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.1968971496416338</v>
+        <v>0.1968971496416331</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.009915270508004639</v>
+        <v>0.009915270508004642</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4658112293095935</v>
+        <v>0.4658112293095933</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.332466214895519</v>
+        <v>-1.332466214895518</v>
       </c>
       <c r="AQ361" t="n">
         <v>11.24140363251631</v>
@@ -59189,16 +59189,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.200157477381068</v>
+        <v>0.2001574773810679</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01045224758824685</v>
+        <v>0.01045224758824684</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4652001227613058</v>
+        <v>0.4652001227613064</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.593977891557415</v>
+        <v>-1.593977891557414</v>
       </c>
       <c r="AQ362" t="n">
         <v>5.096919349255798</v>
@@ -59342,10 +59342,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI363" t="n">
-        <v>7.112155432918444</v>
+        <v>7.112155432918446</v>
       </c>
       <c r="AJ363" t="n">
-        <v>-0.1611552192953969</v>
+        <v>-0.1611552192953987</v>
       </c>
       <c r="AK363" t="n">
         <v>7.115439870473561</v>
@@ -59354,16 +59354,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2059164257597547</v>
+        <v>0.2059164257597553</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.0109580623600705</v>
+        <v>0.01095806236007055</v>
       </c>
       <c r="AO363" t="n">
-        <v>0.4647071558511972</v>
+        <v>0.4647071558511969</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.789779639197566</v>
+        <v>-1.789779639197605</v>
       </c>
       <c r="AQ363" t="n">
         <v>6.455997281685355</v>
@@ -59519,16 +59519,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2103846028094625</v>
+        <v>0.2103846028094628</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01138655624224671</v>
+        <v>0.01138655624224677</v>
       </c>
       <c r="AO364" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.817649544165025</v>
+        <v>-1.817649544165022</v>
       </c>
       <c r="AQ364" t="n">
         <v>10.98415346121768</v>
@@ -59672,10 +59672,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI365" t="n">
-        <v>7.110775793344654</v>
+        <v>7.110775793344653</v>
       </c>
       <c r="AJ365" t="n">
-        <v>-0.1730759985753672</v>
+        <v>-0.1730759985753663</v>
       </c>
       <c r="AK365" t="n">
         <v>7.127056499711662</v>
@@ -59684,16 +59684,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2137349114935566</v>
+        <v>0.2137349114935569</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.0118427752189066</v>
+        <v>0.01184277521890661</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4573024605378192</v>
+        <v>0.4573024605378193</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.982092372266673</v>
+        <v>-1.982092372266651</v>
       </c>
       <c r="AQ365" t="n">
         <v>12.26044226044226</v>
@@ -59849,16 +59849,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2192999169256231</v>
+        <v>0.2192999169256238</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01242692746354283</v>
+        <v>0.01242692746354282</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4593518446085587</v>
+        <v>0.4593518446085588</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.541667257522197</v>
+        <v>-1.541667257522195</v>
       </c>
       <c r="AQ366" t="n">
         <v>13.91972329472329</v>
@@ -60002,28 +60002,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.095070446253632</v>
+        <v>7.095070446253633</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1572705156811223</v>
+        <v>-0.1572705156811232</v>
       </c>
       <c r="AK367" t="n">
-        <v>7.099084322920754</v>
+        <v>7.099084322920755</v>
       </c>
       <c r="AL367" t="n">
-        <v>-0.1612843923482439</v>
+        <v>-0.1612843923482448</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2273791016644665</v>
+        <v>0.2273791016644669</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01301934706840001</v>
+        <v>0.01301934706839999</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4655241261491888</v>
+        <v>0.4655241261491886</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.574345528037874</v>
+        <v>-1.574345528037892</v>
       </c>
       <c r="AQ367" t="n">
         <v>12.01406447534766</v>
@@ -60167,10 +60167,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.077412848446856</v>
+        <v>7.077412848446851</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.138612990353594</v>
+        <v>-0.1386129903535895</v>
       </c>
       <c r="AK368" t="n">
         <v>7.107752072150756</v>
@@ -60179,16 +60179,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2346680713248287</v>
+        <v>0.2346680713248289</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01366280940279221</v>
+        <v>0.01366280940279216</v>
       </c>
       <c r="AO368" t="n">
-        <v>0.4682122340216205</v>
+        <v>0.4682122340216202</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.144790164634194</v>
+        <v>-1.144790164634094</v>
       </c>
       <c r="AQ368" t="n">
         <v>19.36811054184133</v>
@@ -60332,10 +60332,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.067855559671529</v>
+        <v>7.067855559671527</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1458556283360801</v>
+        <v>-0.1458556283360775</v>
       </c>
       <c r="AK369" t="n">
         <v>7.100856094477853</v>
@@ -60344,16 +60344,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2404731763378833</v>
+        <v>0.2404731763378842</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01427110593278805</v>
+        <v>0.01427110593278799</v>
       </c>
       <c r="AO369" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.291445978779306</v>
+        <v>-1.291445978779248</v>
       </c>
       <c r="AQ369" t="n">
         <v>18.78718535469108</v>
@@ -60497,10 +60497,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.081794385763168</v>
+        <v>7.081794385763164</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1711942003688813</v>
+        <v>-0.1711942003688769</v>
       </c>
       <c r="AK370" t="n">
         <v>7.090764621929079</v>
@@ -60509,16 +60509,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2453259423721924</v>
+        <v>0.2453259423721931</v>
       </c>
       <c r="AN370" t="n">
-        <v>0.01502424352484376</v>
+        <v>0.01502424352484369</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4756424387980304</v>
+        <v>0.4756424387980298</v>
       </c>
       <c r="AP370" t="n">
-        <v>-1.821236982629602</v>
+        <v>-1.821236982629511</v>
       </c>
       <c r="AQ370" t="n">
         <v>15.19865067466267</v>
@@ -60662,10 +60662,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.068234493406101</v>
+        <v>7.068234493406102</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1557345887735329</v>
+        <v>-0.1557345887735337</v>
       </c>
       <c r="AK371" t="n">
         <v>7.110983013755962</v>
@@ -60674,16 +60674,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2481172514763511</v>
+        <v>0.2481172514763508</v>
       </c>
       <c r="AN371" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.4781214750573156</v>
+        <v>0.4781214750573159</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.46017834906476</v>
+        <v>-1.460178349064784</v>
       </c>
       <c r="AQ371" t="n">
         <v>18.92130857648099</v>
@@ -60827,28 +60827,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.04701169343388</v>
+        <v>7.047011693433886</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.1469114622632253</v>
+        <v>-0.1469114622632315</v>
       </c>
       <c r="AK372" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1936362268489633</v>
+        <v>-0.1936362268489642</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2517176519946887</v>
+        <v>0.2517176519946896</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01672959897123727</v>
+        <v>0.01672959897123732</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.4820447952807055</v>
+        <v>0.482044795280705</v>
       </c>
       <c r="AP372" t="n">
-        <v>-1.252621156666045</v>
+        <v>-1.252621156666182</v>
       </c>
       <c r="AQ372" t="n">
         <v>18.30001448645517</v>
@@ -60992,28 +60992,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.043635211714486</v>
+        <v>7.043635211714482</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1356352193438806</v>
+        <v>-0.135635219343877</v>
       </c>
       <c r="AK373" t="n">
-        <v>7.069112439760901</v>
+        <v>7.069112439760902</v>
       </c>
       <c r="AL373" t="n">
-        <v>-0.1611124473902956</v>
+        <v>-0.1611124473902965</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2568291528619769</v>
+        <v>0.2568291528619773</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.0175878422274923</v>
+        <v>0.01758784222749221</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.488825658962754</v>
+        <v>0.4888256589627545</v>
       </c>
       <c r="AP373" t="n">
-        <v>-0.9972661263734258</v>
+        <v>-0.9972661263733498</v>
       </c>
       <c r="AQ373" t="n">
         <v>23.6113089303518</v>
@@ -61157,10 +61157,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.04532069676962</v>
+        <v>7.045320696769622</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1373207043990146</v>
+        <v>-0.1373207043990163</v>
       </c>
       <c r="AK374" t="n">
         <v>7.067486653848666</v>
@@ -61169,16 +61169,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2611441025487396</v>
+        <v>0.2611441025487395</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.01863884916361523</v>
+        <v>0.01863884916361525</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.4958891106408189</v>
+        <v>0.4958891106408185</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.025289911488955</v>
+        <v>-1.025289911488995</v>
       </c>
       <c r="AQ374" t="n">
         <v>21.31652661064426</v>
@@ -61322,10 +61322,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI375" t="n">
-        <v>7.052957186540212</v>
+        <v>7.052957186540217</v>
       </c>
       <c r="AJ375" t="n">
-        <v>-0.1449571941696064</v>
+        <v>-0.1449571941696117</v>
       </c>
       <c r="AK375" t="n">
         <v>7.066060765041626</v>
@@ -61334,16 +61334,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM375" t="n">
-        <v>0.2646928033319788</v>
+        <v>0.2646928033319798</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.0196144718499898</v>
+        <v>0.01961447184998982</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.4990325267638065</v>
+        <v>0.4990325267638059</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.180573654908609</v>
+        <v>-1.180573654908724</v>
       </c>
       <c r="AQ375" t="n">
         <v>18.67079889807162</v>
@@ -61487,28 +61487,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.055218091951103</v>
+        <v>7.055218091951101</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1472180995804973</v>
+        <v>-0.1472180995804955</v>
       </c>
       <c r="AK376" t="n">
-        <v>7.06464674575351</v>
+        <v>7.064646745753511</v>
       </c>
       <c r="AL376" t="n">
-        <v>-0.1566467533829048</v>
+        <v>-0.1566467533829057</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2692457951306194</v>
+        <v>0.2692457951306195</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02045122459205891</v>
+        <v>0.02045122459205889</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5009265659871951</v>
+        <v>0.5009265659871953</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.217381411470217</v>
+        <v>-1.217381411470178</v>
       </c>
       <c r="AQ376" t="n">
         <v>17.70085354288037</v>
@@ -61652,10 +61652,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI377" t="n">
-        <v>7.050463258619345</v>
+        <v>7.050463258619342</v>
       </c>
       <c r="AJ377" t="n">
-        <v>-0.1423631304455171</v>
+        <v>-0.1423631304455135</v>
       </c>
       <c r="AK377" t="n">
         <v>7.063274589921972</v>
@@ -61664,16 +61664,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM377" t="n">
-        <v>0.2738618637550991</v>
+        <v>0.2738618637550985</v>
       </c>
       <c r="AN377" t="n">
-        <v>0.02103732430364855</v>
+        <v>0.02103732430364852</v>
       </c>
       <c r="AO377" t="n">
-        <v>0.5007948901071723</v>
+        <v>0.5007948901071727</v>
       </c>
       <c r="AP377" t="n">
-        <v>-1.101457435093542</v>
+        <v>-1.101457435093465</v>
       </c>
       <c r="AQ377" t="n">
         <v>22.04784752765561</v>
@@ -61990,16 +61990,16 @@
         <v/>
       </c>
       <c r="AM379" t="n">
-        <v>0.2803441195876753</v>
+        <v>0.280344119587675</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02230845224183688</v>
+        <v>0.02230845224183686</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5036776407221312</v>
+        <v>0.5036776407221306</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.253596032660393</v>
+        <v>-1.253596032660394</v>
       </c>
       <c r="AQ379" t="n">
         <v>24.19354838709677</v>
@@ -62143,10 +62143,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.056824809597052</v>
+        <v>7.056824809597053</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.1737247767906558</v>
+        <v>-0.1737247767906567</v>
       </c>
       <c r="AK380" t="n">
         <v>7.071238163852278</v>
@@ -62155,16 +62155,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2841407798055452</v>
+        <v>0.2841407798055449</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02276542233315985</v>
+        <v>0.02276542233315987</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5036956996297983</v>
+        <v>0.5036956996297977</v>
       </c>
       <c r="AP380" t="n">
-        <v>-1.741339932678327</v>
+        <v>-1.741339932678348</v>
       </c>
       <c r="AQ380" t="n">
         <v>21.2</v>
@@ -62308,10 +62308,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.047265922594908</v>
+        <v>7.04726592259491</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.178065692950133</v>
+        <v>-0.1780656929501347</v>
       </c>
       <c r="AK381" t="n">
         <v>7.075283303194255</v>
@@ -62320,16 +62320,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.2869603504542598</v>
+        <v>0.2869603504542605</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02324367830537833</v>
+        <v>0.02324367830537832</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.5029697249741724</v>
+        <v>0.5029697249741727</v>
       </c>
       <c r="AP381" t="n">
-        <v>-1.803528001978095</v>
+        <v>-1.803528001978133</v>
       </c>
       <c r="AQ381" t="n">
         <v>10.31746031746032</v>
@@ -62473,10 +62473,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.030237372659579</v>
+        <v>7.030237372659574</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.1893374283541593</v>
+        <v>-0.189337428354154</v>
       </c>
       <c r="AK382" t="n">
         <v>7.061088020066238</v>
@@ -62485,16 +62485,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.2909556153842324</v>
+        <v>0.2909556153842325</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02343150180192457</v>
+        <v>0.02343150180192449</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.5011874977636526</v>
+        <v>0.501187497763653</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.003260963431223</v>
+        <v>-2.003260963431115</v>
       </c>
       <c r="AQ382" t="n">
         <v>2.362204724409449</v>
@@ -62638,10 +62638,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.074556523891907</v>
+        <v>7.074556523891909</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2166563812222293</v>
+        <v>-0.2166563812222311</v>
       </c>
       <c r="AK383" t="n">
         <v>7.045371831199247</v>
@@ -62650,16 +62650,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.2963660759601009</v>
+        <v>0.2963660759601011</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02388105320115906</v>
+        <v>0.02388105320115907</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.5011837436137511</v>
+        <v>0.5011837436137521</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.504656154321755</v>
+        <v>-2.504656154321796</v>
       </c>
       <c r="AQ383" t="n">
         <v>14.453125</v>
@@ -62803,10 +62803,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI384" t="n">
-        <v>7.103552248295403</v>
+        <v>7.103552248295395</v>
       </c>
       <c r="AJ384" t="n">
-        <v>-0.2215522788129807</v>
+        <v>-0.2215522788129736</v>
       </c>
       <c r="AK384" t="n">
         <v>7.078406423284397</v>
@@ -62815,16 +62815,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.2998407912997099</v>
+        <v>0.29984079129971</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02427773372157407</v>
+        <v>0.02427773372157399</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.4964684575356701</v>
+        <v>0.4964684575356704</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.529447296146643</v>
+        <v>-2.529447296146512</v>
       </c>
       <c r="AQ384" t="n">
         <v>18.99224806201551</v>
@@ -62980,16 +62980,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3035220749319821</v>
+        <v>0.3035220749319825</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02465824743687013</v>
+        <v>0.02465824743687012</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4899948718309223</v>
+        <v>0.4899948718309226</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.242027341128819</v>
+        <v>-2.242027341128829</v>
       </c>
       <c r="AQ385" t="n">
         <v>22.69230769230769</v>
@@ -63133,10 +63133,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.127779594400253</v>
+        <v>7.12777959440025</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2307797584322353</v>
+        <v>-0.2307797584322326</v>
       </c>
       <c r="AK386" t="n">
         <v>7.110202206771168</v>
@@ -63145,16 +63145,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3056770963992276</v>
+        <v>0.3056770963992281</v>
       </c>
       <c r="AN386" t="n">
-        <v>0.02512392944114575</v>
+        <v>0.02512392944114572</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.48360047858094</v>
+        <v>0.4836004785809395</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.575931200243936</v>
+        <v>-2.575931200243899</v>
       </c>
       <c r="AQ386" t="n">
         <v>22.13740458015267</v>
@@ -63298,28 +63298,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.117424820782308</v>
+        <v>7.117424820782309</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.2204249848142901</v>
+        <v>-0.2204249848142918</v>
       </c>
       <c r="AK387" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL387" t="n">
-        <v>-0.21822100705125</v>
+        <v>-0.2182210070512509</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3083414575758079</v>
+        <v>0.3083414575758074</v>
       </c>
       <c r="AN387" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.4749824439402989</v>
+        <v>0.474982443940299</v>
       </c>
       <c r="AP387" t="n">
-        <v>-2.316485060974883</v>
+        <v>-2.316485060974927</v>
       </c>
       <c r="AQ387" t="n">
         <v>24.62121212121212</v>
@@ -63463,10 +63463,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.116315246651979</v>
+        <v>7.116315246651977</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.2198151360257583</v>
+        <v>-0.2198151360257565</v>
       </c>
       <c r="AK388" t="n">
         <v>7.112470209890858</v>
@@ -63475,16 +63475,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3094443575020188</v>
+        <v>0.3094443575020182</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.02578750722031873</v>
+        <v>0.0257875072203187</v>
       </c>
       <c r="AO388" t="n">
-        <v>0.467103914503924</v>
+        <v>0.4671039145039241</v>
       </c>
       <c r="AP388" t="n">
-        <v>-2.251366387607492</v>
+        <v>-2.25136638760747</v>
       </c>
       <c r="AQ388" t="n">
         <v>24.43609022556391</v>
@@ -63628,28 +63628,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.109165799046382</v>
+        <v>7.109165799046384</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.1981660241135206</v>
+        <v>-0.1981660241135224</v>
       </c>
       <c r="AK389" t="n">
-        <v>7.105086649080123</v>
+        <v>7.105086649080124</v>
       </c>
       <c r="AL389" t="n">
-        <v>-0.1940868741472617</v>
+        <v>-0.1940868741472626</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3112159059696449</v>
+        <v>0.3112159059696454</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02619128791084347</v>
+        <v>0.02619128791084346</v>
       </c>
       <c r="AO389" t="n">
-        <v>0.4597800393113443</v>
+        <v>0.4597800393113445</v>
       </c>
       <c r="AP389" t="n">
-        <v>-1.814601966012038</v>
+        <v>-1.81460196601208</v>
       </c>
       <c r="AQ389" t="n">
         <v>25.74626865671642</v>
@@ -63793,10 +63793,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.14047665869759</v>
+        <v>7.140476658697598</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.2639765289978833</v>
+        <v>-0.2639765289978913</v>
       </c>
       <c r="AK390" t="n">
         <v>7.107009848336411</v>
@@ -63805,16 +63805,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3120213667410841</v>
+        <v>0.3120213667410843</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02660872919284651</v>
+        <v>0.02660872919284657</v>
       </c>
       <c r="AO390" t="n">
-        <v>0.4527828726277021</v>
+        <v>0.4527828726277016</v>
       </c>
       <c r="AP390" t="n">
-        <v>-2.929905508633069</v>
+        <v>-2.929905508633215</v>
       </c>
       <c r="AQ390" t="n">
         <v>18.51851851851852</v>
@@ -63958,10 +63958,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI391" t="n">
-        <v>7.192104266103096</v>
+        <v>7.192104266103097</v>
       </c>
       <c r="AJ391" t="n">
-        <v>-0.3266042928059765</v>
+        <v>-0.3266042928059782</v>
       </c>
       <c r="AK391" t="n">
         <v>7.130667004235951</v>
@@ -63970,16 +63970,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3119580514589062</v>
+        <v>0.3119580514589064</v>
       </c>
       <c r="AN391" t="n">
-        <v>0.02723917591229311</v>
+        <v>0.02723917591229313</v>
       </c>
       <c r="AO391" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.820789712855619</v>
+        <v>-3.820789712855648</v>
       </c>
       <c r="AQ391" t="n">
         <v>21.32352941176471</v>
@@ -64135,7 +64135,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.3060770546706496</v>
+        <v>0.3060770546706492</v>
       </c>
       <c r="AN392" t="n">
         <v>0.02737088803905663</v>
@@ -64288,10 +64288,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.164105908482372</v>
+        <v>7.16410590848237</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.2680058642318839</v>
+        <v>-0.2680058642318812</v>
       </c>
       <c r="AK393" t="n">
         <v>7.162206823443969</v>
@@ -64300,16 +64300,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.3021518080029217</v>
+        <v>0.3021518080029227</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02724691784252936</v>
+        <v>0.02724691784252931</v>
       </c>
       <c r="AO393" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP393" t="n">
-        <v>-2.578588976687523</v>
+        <v>-2.578588976687483</v>
       </c>
       <c r="AQ393" t="n">
         <v>23.18840579710145</v>
@@ -64453,10 +64453,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.165713254747862</v>
+        <v>7.165713254747866</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.2102131288628524</v>
+        <v>-0.2102131288628559</v>
       </c>
       <c r="AK394" t="n">
         <v>7.141021818380439</v>
@@ -64465,16 +64465,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.3004913268435102</v>
+        <v>0.3004913268435098</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02739193077523432</v>
+        <v>0.02739193077523433</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3752726470948199</v>
+        <v>0.3752726470948202</v>
       </c>
       <c r="AP394" t="n">
-        <v>-1.634045789661968</v>
+        <v>-1.634045789662024</v>
       </c>
       <c r="AQ394" t="n">
         <v>29.85611510791367</v>
@@ -64618,10 +64618,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.208249532027231</v>
+        <v>7.208249532027229</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.321949445052133</v>
+        <v>-0.3219494450521312</v>
       </c>
       <c r="AK395" t="n">
         <v>7.146296571548195</v>
@@ -64630,16 +64630,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2982197220770058</v>
+        <v>0.2982197220770054</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02742417953210373</v>
+        <v>0.02742417953210363</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.3625782951332475</v>
+        <v>0.3625782951332472</v>
       </c>
       <c r="AP395" t="n">
-        <v>-3.260996506849911</v>
+        <v>-3.260996506849887</v>
       </c>
       <c r="AQ395" t="n">
         <v>24.64285714285714</v>
@@ -64783,28 +64783,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.193412187855726</v>
+        <v>7.193412187855718</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3208121092729623</v>
+        <v>-0.3208121092729543</v>
       </c>
       <c r="AK396" t="n">
-        <v>7.176497065376473</v>
+        <v>7.176497065376474</v>
       </c>
       <c r="AL396" t="n">
-        <v>-0.3038969867937098</v>
+        <v>-0.3038969867937107</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2910761841041086</v>
+        <v>0.2910761841041076</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02685747952387156</v>
+        <v>0.02685747952387152</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.3370674577034442</v>
+        <v>0.3370674577034428</v>
       </c>
       <c r="AP396" t="n">
-        <v>-3.117150734278383</v>
+        <v>-3.117150734278276</v>
       </c>
       <c r="AQ396" t="n">
         <v>25.53191489361702</v>
@@ -64948,10 +64948,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.227115602342041</v>
+        <v>7.227115602342048</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3273157785810543</v>
+        <v>-0.3273157785810614</v>
       </c>
       <c r="AK397" t="n">
         <v>7.185469892270627</v>
@@ -64960,16 +64960,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.281226998760588</v>
+        <v>0.2812269987605887</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.0269718053742217</v>
+        <v>0.02697180537422167</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.3136210223326474</v>
+        <v>0.3136210223326478</v>
       </c>
       <c r="AP397" t="n">
-        <v>-3.090982180858172</v>
+        <v>-3.090982180858276</v>
       </c>
       <c r="AQ397" t="n">
         <v>26.40845070422535</v>
@@ -65113,10 +65113,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.187163192389367</v>
+        <v>7.187163192389372</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.3014629665592885</v>
+        <v>-0.3014629665592938</v>
       </c>
       <c r="AK398" t="n">
         <v>7.208338760609084</v>
@@ -65125,16 +65125,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2681836981576121</v>
+        <v>0.2681836981576122</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02658698789673927</v>
+        <v>0.02658698789673936</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.2859081509452629</v>
+        <v>0.285908150945263</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.642799587348761</v>
+        <v>-2.642799587348834</v>
       </c>
       <c r="AQ398" t="n">
         <v>27.27272727272727</v>
@@ -65278,10 +65278,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.214951953115579</v>
+        <v>7.214951953115591</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.3349518386746606</v>
+        <v>-0.334951838674673</v>
       </c>
       <c r="AK399" t="n">
         <v>7.186200492654655</v>
@@ -65290,16 +65290,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2591628297636748</v>
+        <v>0.2591628297636744</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.02587977479594331</v>
+        <v>0.02587977479594339</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.2661082014924122</v>
+        <v>0.266108201492412</v>
       </c>
       <c r="AP399" t="n">
-        <v>-3.001867292174275</v>
+        <v>-3.00186729217443</v>
       </c>
       <c r="AQ399" t="n">
         <v>26.73611111111111</v>
@@ -65443,10 +65443,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI400" t="n">
-        <v>7.197430004066453</v>
+        <v>7.197430004066455</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.3056300773086402</v>
+        <v>-0.305630077308642</v>
       </c>
       <c r="AK400" t="n">
         <v>7.201835396295348</v>
@@ -65455,16 +65455,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2466333883508324</v>
+        <v>0.2466333883508319</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.02476543449503272</v>
+        <v>0.0247654344950328</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.2401258754735008</v>
+        <v>0.2401258754735003</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.534507398102835</v>
+        <v>-2.534507398102846</v>
       </c>
       <c r="AQ400" t="n">
         <v>25.51724137931034</v>
@@ -65611,25 +65611,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.3291230670577878</v>
+        <v>-0.3291230670577869</v>
       </c>
       <c r="AK401" t="n">
-        <v>7.179650721554483</v>
+        <v>7.179650721554484</v>
       </c>
       <c r="AL401" t="n">
-        <v>-0.2786506986662998</v>
+        <v>-0.2786506986663007</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.2377807761788565</v>
+        <v>0.2377807761788571</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.02334020127887796</v>
+        <v>0.02334020127887793</v>
       </c>
       <c r="AO401" t="n">
-        <v>0.2171758918683913</v>
+        <v>0.2171758918683914</v>
       </c>
       <c r="AP401" t="n">
-        <v>-2.76248223845191</v>
+        <v>-2.762482238451886</v>
       </c>
       <c r="AQ401" t="n">
         <v>26.02739726027397</v>
@@ -65773,10 +65773,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.208528037732954</v>
+        <v>7.20852803773295</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.2978281933726024</v>
+        <v>-0.2978281933725988</v>
       </c>
       <c r="AK402" t="n">
         <v>7.206616000051887</v>
@@ -65785,16 +65785,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.2255544515066683</v>
+        <v>0.2255544515066686</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.0206724522626572</v>
+        <v>0.0206724522626571</v>
       </c>
       <c r="AO402" t="n">
-        <v>0.1898019966940708</v>
+        <v>0.1898019966940717</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.302865963394901</v>
+        <v>-2.302865963394848</v>
       </c>
       <c r="AQ402" t="n">
         <v>15.98639455782313</v>
@@ -65938,10 +65938,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.198803092238432</v>
+        <v>7.19880309223843</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2872029793233928</v>
+        <v>-0.287202979323391</v>
       </c>
       <c r="AK403" t="n">
         <v>7.18051307481679</v>
@@ -65950,16 +65950,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.2150441262650616</v>
+        <v>0.2150441262650612</v>
       </c>
       <c r="AN403" t="n">
-        <v>0.0177489551638892</v>
+        <v>0.01774895516388914</v>
       </c>
       <c r="AO403" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP403" t="n">
-        <v>-2.125372134371282</v>
+        <v>-2.125372134371253</v>
       </c>
       <c r="AQ403" t="n">
         <v>14.52702702702703</v>
@@ -66103,10 +66103,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.172424239411002</v>
+        <v>7.172424239411004</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2608241264959634</v>
+        <v>-0.2608241264959652</v>
       </c>
       <c r="AK404" t="n">
         <v>7.16705299197773</v>
@@ -66115,16 +66115,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.2054336514894463</v>
+        <v>0.205433651489446</v>
       </c>
       <c r="AN404" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO404" t="n">
-        <v>0.1417286033373033</v>
+        <v>0.1417286033373026</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.765505948615028</v>
+        <v>-1.765505948615044</v>
       </c>
       <c r="AQ404" t="n">
         <v>18.45637583892617</v>
@@ -66268,10 +66268,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.163756390646673</v>
+        <v>7.163756390646672</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2695565424716238</v>
+        <v>-0.2695565424716229</v>
       </c>
       <c r="AK405" t="n">
         <v>7.153532751444382</v>
@@ -66280,16 +66280,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1941661953581056</v>
+        <v>0.1941661953581061</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.01312004055850015</v>
+        <v>0.01312004055850013</v>
       </c>
       <c r="AO405" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP405" t="n">
-        <v>-1.847646922476733</v>
+        <v>-1.847646922476716</v>
       </c>
       <c r="AQ405" t="n">
         <v>24.66666666666667</v>
@@ -66433,10 +66433,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.158063699621736</v>
+        <v>7.158063699621738</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.2875636118836988</v>
+        <v>-0.2875636118837006</v>
       </c>
       <c r="AK406" t="n">
         <v>7.150669702211316</v>
@@ -66445,16 +66445,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.183949493726688</v>
+        <v>0.1839494937266881</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.01194074338472802</v>
+        <v>0.01194074338472806</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.110754980517583</v>
+        <v>0.1107549805175829</v>
       </c>
       <c r="AP406" t="n">
-        <v>-2.036901689708342</v>
+        <v>-2.036901689708357</v>
       </c>
       <c r="AQ406" t="n">
         <v>12.91390728476821</v>
@@ -66598,10 +66598,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.157435208014565</v>
+        <v>7.157435208014563</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2723353201666647</v>
+        <v>-0.272335320166663</v>
       </c>
       <c r="AK407" t="n">
         <v>7.140926852093823</v>
@@ -66610,16 +66610,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1753430411611928</v>
+        <v>0.1753430411611933</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.009717654232020439</v>
+        <v>0.00971765423202034</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.09620195025422784</v>
+        <v>0.09620195025422695</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.822067618268836</v>
+        <v>-1.822067618268809</v>
       </c>
       <c r="AQ407" t="n">
         <v>20.72368421052632</v>
@@ -66763,10 +66763,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.15038681134007</v>
+        <v>7.150386811340072</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2679867754819156</v>
+        <v>-0.2679867754819174</v>
       </c>
       <c r="AK408" t="n">
         <v>7.142886401315924</v>
@@ -66775,16 +66775,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1664838398737869</v>
+        <v>0.1664838398737872</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.008089376136153925</v>
+        <v>0.008089376136153875</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.08489626886092971</v>
+        <v>0.0848962688609296</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.745105232570966</v>
+        <v>-1.745105232570982</v>
       </c>
       <c r="AQ408" t="n">
         <v>20.26143790849673</v>
@@ -66928,10 +66928,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.137094841694642</v>
+        <v>7.137094841694645</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2547949416397106</v>
+        <v>-0.2547949416397133</v>
       </c>
       <c r="AK409" t="n">
         <v>7.137840883333127</v>
@@ -66940,16 +66940,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1571907956492617</v>
+        <v>0.1571907956492611</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.006581947594647856</v>
+        <v>0.006581947594647974</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.07412699588694738</v>
+        <v>0.07412699588694804</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.566475044001832</v>
+        <v>-1.566475044001858</v>
       </c>
       <c r="AQ409" t="n">
         <v>20.45454545454545</v>
@@ -67093,10 +67093,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.1233912344352</v>
+        <v>7.123391234435203</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2666912908927195</v>
+        <v>-0.2666912908927221</v>
       </c>
       <c r="AK410" t="n">
         <v>7.12862724785568</v>
@@ -67105,16 +67105,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM410" t="n">
-        <v>0.1487097707294973</v>
+        <v>0.1487097707294961</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005441006961990058</v>
+        <v>0.005441006961990014</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.06531270865715666</v>
+        <v>0.06531270865715677</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.689235476196365</v>
+        <v>-1.68923547619639</v>
       </c>
       <c r="AQ410" t="n">
         <v>14.19354838709677</v>
@@ -67258,10 +67258,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.116007318552882</v>
+        <v>7.11600731855288</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2873072529400895</v>
+        <v>-0.2873072529400869</v>
       </c>
       <c r="AK411" t="n">
         <v>7.118961040191934</v>
@@ -67270,16 +67270,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM411" t="n">
-        <v>0.1409513724492179</v>
+        <v>0.1409513724492178</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005644373135176906</v>
+        <v>0.005644373135176822</v>
       </c>
       <c r="AO411" t="n">
-        <v>0.0598657761353214</v>
+        <v>0.05986577613532174</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.90848602634981</v>
+        <v>-1.908486026349772</v>
       </c>
       <c r="AQ411" t="n">
         <v>9.935897435897436</v>
@@ -67423,10 +67423,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI412" t="n">
-        <v>7.11526245458776</v>
+        <v>7.115262454587763</v>
       </c>
       <c r="AJ412" t="n">
-        <v>-0.2838625369852208</v>
+        <v>-0.2838625369852235</v>
       </c>
       <c r="AK412" t="n">
         <v>7.113208458946866</v>
@@ -67438,13 +67438,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005618445165739529</v>
+        <v>0.005618445165739616</v>
       </c>
       <c r="AO412" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.840960329226772</v>
+        <v>-1.840960329226796</v>
       </c>
       <c r="AQ412" t="n">
         <v>8.598726114649681</v>
@@ -67600,16 +67600,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM413" t="n">
-        <v>0.1248427026608145</v>
+        <v>0.1248427026608149</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005050876420738303</v>
+        <v>0.005050876420738246</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.04692762159457986</v>
+        <v>0.04692762159458042</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.755949528666207</v>
+        <v>-1.755949528666201</v>
       </c>
       <c r="AQ413" t="n">
         <v>13.60759493670886</v>
@@ -67753,10 +67753,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.100218718661558</v>
+        <v>7.100218718661557</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2699188643829933</v>
+        <v>-0.2699188643829924</v>
       </c>
       <c r="AK414" t="n">
         <v>7.105971078464224</v>
@@ -67768,13 +67768,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.00520957018071537</v>
+        <v>0.005209570180715356</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.04219701739313308</v>
+        <v>0.0421970173931332</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.633946744033963</v>
+        <v>-1.633946744033946</v>
       </c>
       <c r="AQ414" t="n">
         <v>14.77987421383648</v>
@@ -67918,10 +67918,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI415" t="n">
-        <v>7.097935875054439</v>
+        <v>7.097935875054437</v>
       </c>
       <c r="AJ415" t="n">
-        <v>-0.2822358208857381</v>
+        <v>-0.2822358208857363</v>
       </c>
       <c r="AK415" t="n">
         <v>7.101361129315627</v>
@@ -67930,16 +67930,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.1117472247487876</v>
+        <v>0.1117472247487875</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005385102682029925</v>
+        <v>0.005385102682029907</v>
       </c>
       <c r="AO415" t="n">
-        <v>0.03866992220359033</v>
+        <v>0.03866992220359</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.755252893295981</v>
+        <v>-1.755252893295954</v>
       </c>
       <c r="AQ415" t="n">
         <v>13.75</v>
@@ -68083,10 +68083,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI416" t="n">
-        <v>7.097978821692021</v>
+        <v>7.097978821692022</v>
       </c>
       <c r="AJ416" t="n">
-        <v>-0.2799789819093057</v>
+        <v>-0.2799789819093075</v>
       </c>
       <c r="AK416" t="n">
         <v>7.099648834314064</v>
@@ -68095,16 +68095,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.1065475925362025</v>
+        <v>0.1065475925362033</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.005956926407441003</v>
+        <v>0.005956926407440957</v>
       </c>
       <c r="AO416" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.707781371906486</v>
+        <v>-1.7077813719065</v>
       </c>
       <c r="AQ416" t="n">
         <v>13.66459627329192</v>
@@ -68260,16 +68260,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.1013724682419976</v>
+        <v>0.1013724682419977</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.006126167203105847</v>
+        <v>0.006126167203105798</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.03348722035246277</v>
+        <v>0.03348722035246332</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.545702361153165</v>
+        <v>-1.545702361153159</v>
       </c>
       <c r="AQ417" t="n">
         <v>22.22222222222222</v>
@@ -68413,10 +68413,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI418" t="n">
-        <v>7.087097940453343</v>
+        <v>7.087097940453345</v>
       </c>
       <c r="AJ418" t="n">
-        <v>-0.2700980281913798</v>
+        <v>-0.2700980281913825</v>
       </c>
       <c r="AK418" t="n">
         <v>7.090805518999606</v>
@@ -68425,16 +68425,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.09919462776856289</v>
+        <v>0.09919462776856321</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.006113943880485968</v>
+        <v>0.006113943880485972</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.03204155062895098</v>
+        <v>0.03204155062895153</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.560217818508615</v>
+        <v>-1.560217818508639</v>
       </c>
       <c r="AQ418" t="n">
         <v>17.17791411042945</v>
@@ -68590,16 +68590,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.09750750254701511</v>
+        <v>0.097507502547015</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.005510714664730422</v>
+        <v>0.005510714664730507</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.03001455024934274</v>
+        <v>0.03001455024934374</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.618797990886851</v>
+        <v>-1.618797990886845</v>
       </c>
       <c r="AQ419" t="n">
         <v>14.02439024390244</v>
@@ -68755,16 +68755,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.09380549503386949</v>
+        <v>0.09380549503386901</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.004784904607979855</v>
+        <v>0.004784904607979881</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.02699383492044827</v>
+        <v>0.02699383492044782</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.576016406515585</v>
+        <v>-1.576016406515579</v>
       </c>
       <c r="AQ420" t="n">
         <v>17.57575757575758</v>
@@ -68908,10 +68908,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.097145375663948</v>
+        <v>7.097145375663951</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.2729452223131181</v>
+        <v>-0.2729452223131208</v>
       </c>
       <c r="AK421" t="n">
         <v>7.093828611034739</v>
@@ -68920,16 +68920,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.08945254406056392</v>
+        <v>0.08945254406056438</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.004001520125414807</v>
+        <v>0.004001520125414798</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.02385555423225172</v>
+        <v>0.02385555423225116</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.541997667984746</v>
+        <v>-1.54199766798477</v>
       </c>
       <c r="AQ421" t="n">
         <v>21.68674698795181</v>
@@ -69073,10 +69073,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.088227962421954</v>
+        <v>7.088227962421951</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2622277487989066</v>
+        <v>-0.262227748798904</v>
       </c>
       <c r="AK422" t="n">
         <v>7.092951699003613</v>
@@ -69085,16 +69085,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.07912491692886864</v>
+        <v>0.07912491692886899</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.003813743757049957</v>
+        <v>0.003813743757049903</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.01902803623666371</v>
+        <v>0.01902803623666316</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.408148123344101</v>
+        <v>-1.408148123344065</v>
       </c>
       <c r="AQ422" t="n">
         <v>34.4311377245509</v>
@@ -69238,10 +69238,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.082675656384675</v>
+        <v>7.082675656384673</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2467758265201727</v>
+        <v>-0.2467758265201709</v>
       </c>
       <c r="AK423" t="n">
         <v>7.085940899278786</v>
@@ -69250,16 +69250,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.07019093860911679</v>
+        <v>0.07019093860911668</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.003788844982403293</v>
+        <v>0.003788844982403339</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.0153072785246503</v>
+        <v>0.01530727852465064</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.224883418791533</v>
+        <v>-1.224883418791509</v>
       </c>
       <c r="AQ423" t="n">
         <v>32.44047619047619</v>
@@ -69403,10 +69403,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.082585232341569</v>
+        <v>7.082585232341567</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2597850728872233</v>
+        <v>-0.2597850728872215</v>
       </c>
       <c r="AK424" t="n">
         <v>7.080231185021037</v>
@@ -69415,16 +69415,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.06072301451314636</v>
+        <v>0.0607230145131474</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.003218097337044184</v>
+        <v>0.003218097337044118</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.01127031184523331</v>
+        <v>0.01127031184523342</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.359556645403171</v>
+        <v>-1.359556645403147</v>
       </c>
       <c r="AQ424" t="n">
         <v>32.54437869822485</v>
@@ -69568,10 +69568,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI425" t="n">
-        <v>7.082752176397554</v>
+        <v>7.082752176397555</v>
       </c>
       <c r="AJ425" t="n">
-        <v>-0.2453522168333455</v>
+        <v>-0.2453522168333464</v>
       </c>
       <c r="AK425" t="n">
         <v>7.078545045220129</v>
@@ -69580,16 +69580,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.04987769893955601</v>
+        <v>0.04987769893955558</v>
       </c>
       <c r="AN425" t="n">
-        <v>0.002647769861786034</v>
+        <v>0.002647769861786137</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.007555907385723093</v>
+        <v>0.00755590738572276</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.18912402869255</v>
+        <v>-1.189124028692556</v>
       </c>
       <c r="AQ425" t="n">
         <v>34.11764705882352</v>
@@ -69733,10 +69733,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI426" t="n">
-        <v>7.073418742129173</v>
+        <v>7.073418742129174</v>
       </c>
       <c r="AJ426" t="n">
-        <v>-0.2359186467617418</v>
+        <v>-0.2359186467617427</v>
       </c>
       <c r="AK426" t="n">
         <v>7.075576762908686</v>
@@ -69745,16 +69745,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM426" t="n">
-        <v>0.03723342047483347</v>
+        <v>0.03723342047483359</v>
       </c>
       <c r="AN426" t="n">
-        <v>0.0007434096776329864</v>
+        <v>0.0007434096776329363</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.003691827899840794</v>
+        <v>0.003691827899839573</v>
       </c>
       <c r="AP426" t="n">
-        <v>-1.076578522273149</v>
+        <v>-1.076578522273155</v>
       </c>
       <c r="AQ426" t="n">
         <v>36.54970760233918</v>
@@ -69910,16 +69910,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM427" t="n">
-        <v>0.02391394499985489</v>
+        <v>0.02391394499985428</v>
       </c>
       <c r="AN427" t="n">
-        <v>0.0004638728584110585</v>
+        <v>0.0004638728584110997</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.001504277651263042</v>
+        <v>0.00150427765126282</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.116075578135648</v>
+        <v>-1.116075578135644</v>
       </c>
       <c r="AQ427" t="n">
         <v>34.30232558139535</v>
@@ -70063,10 +70063,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI428" t="n">
-        <v>7.06117555197594</v>
+        <v>7.061175551975939</v>
       </c>
       <c r="AJ428" t="n">
-        <v>-0.2336756854903443</v>
+        <v>-0.2336756854903435</v>
       </c>
       <c r="AK428" t="n">
         <v>7.061105294515807</v>
@@ -70075,16 +70075,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM428" t="n">
-        <v>0.01023096587809607</v>
+        <v>0.01023096587809661</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.0001641525470544615</v>
+        <v>-0.0001641525470544823</v>
       </c>
       <c r="AO428" t="n">
-        <v>0.000253092979595082</v>
+        <v>0.0002530929795961923</v>
       </c>
       <c r="AP428" t="n">
-        <v>-1.037865720030718</v>
+        <v>-1.037865720030704</v>
       </c>
       <c r="AQ428" t="n">
         <v>39.30635838150289</v>
@@ -70240,16 +70240,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.001349940557734529</v>
+        <v>-0.001349940557734956</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.001242569541730301</v>
+        <v>-0.001242569541730382</v>
       </c>
       <c r="AO429" t="n">
-        <v>9.828375502973774e-05</v>
+        <v>9.828375502929365e-05</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.9421931502147847</v>
+        <v>-0.9421931502147813</v>
       </c>
       <c r="AQ429" t="n">
         <v>39.6551724137931</v>
@@ -70393,10 +70393,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.051845784111937</v>
+        <v>7.051845784111939</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.22174572460266</v>
+        <v>-0.2217457246026617</v>
       </c>
       <c r="AK430" t="n">
         <v>7.04924004450221</v>
@@ -70405,16 +70405,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.0124592779456514</v>
+        <v>-0.01245927794565087</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.002690846636687166</v>
+        <v>-0.002690846636687106</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.000914944322433886</v>
+        <v>0.0009149443224345521</v>
       </c>
       <c r="AP430" t="n">
-        <v>-0.8946168972865196</v>
+        <v>-0.8946168972865359</v>
       </c>
       <c r="AQ430" t="n">
         <v>36.57142857142857</v>
@@ -70558,10 +70558,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.044932512363692</v>
+        <v>7.044932512363691</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2339326420633991</v>
+        <v>-0.2339326420633983</v>
       </c>
       <c r="AK431" t="n">
         <v>7.044607485549974</v>
@@ -70570,16 +70570,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.0235197471891116</v>
+        <v>-0.02351974718911197</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003286981705062081</v>
+        <v>-0.003286981705062079</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.002235402288773058</v>
+        <v>0.002235402288773947</v>
       </c>
       <c r="AP431" t="n">
-        <v>-1.025034800695901</v>
+        <v>-1.025034800695888</v>
       </c>
       <c r="AQ431" t="n">
         <v>34.65909090909091</v>
@@ -70723,10 +70723,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.04138072456642</v>
+        <v>7.041380724566422</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2399805399350727</v>
+        <v>-0.2399805399350745</v>
       </c>
       <c r="AK432" t="n">
         <v>7.036677431055121</v>
@@ -70735,16 +70735,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.03604973348542571</v>
+        <v>-0.03604973348542533</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003896888881646666</v>
+        <v>-0.003896888881646653</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.004508577134016423</v>
+        <v>0.004508577134016534</v>
       </c>
       <c r="AP432" t="n">
-        <v>-1.085983877862673</v>
+        <v>-1.085983877862689</v>
       </c>
       <c r="AQ432" t="n">
         <v>27.40112994350282</v>
@@ -70888,10 +70888,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI433" t="n">
-        <v>7.031781164871438</v>
+        <v>7.031781164871437</v>
       </c>
       <c r="AJ433" t="n">
-        <v>-0.2312812487947777</v>
+        <v>-0.2312812487947769</v>
       </c>
       <c r="AK433" t="n">
         <v>7.031531243279009</v>
@@ -70900,16 +70900,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.04964211158845258</v>
+        <v>-0.0496421115884523</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.003622848094475877</v>
+        <v>-0.003622848094475932</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.007358432861333086</v>
+        <v>0.007358432861332531</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.983178989495507</v>
+        <v>-0.9831789894954935</v>
       </c>
       <c r="AQ433" t="n">
         <v>34.83146067415731</v>
@@ -71065,16 +71065,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.06336633742876532</v>
+        <v>-0.06336633742876464</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.003832222031667326</v>
+        <v>-0.00383222203166729</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.01139353356262962</v>
+        <v>0.0113935335626284</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.9132686155557176</v>
+        <v>-0.9132686155557141</v>
       </c>
       <c r="AQ434" t="n">
         <v>35.47486033519553</v>
@@ -71218,10 +71218,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI435" t="n">
-        <v>7.012358254068221</v>
+        <v>7.012358254068223</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.2203584371736902</v>
+        <v>-0.220358437173692</v>
       </c>
       <c r="AK435" t="n">
         <v>7.010266108789461</v>
@@ -71230,16 +71230,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.07815930192347212</v>
+        <v>-0.07815930192347351</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.003730201847889384</v>
+        <v>-0.0037302018478894</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.01669360800688602</v>
+        <v>0.01669360800688513</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.8521135061576661</v>
+        <v>-0.8521135061576827</v>
       </c>
       <c r="AQ435" t="n">
         <v>34.72222222222222</v>
@@ -71383,10 +71383,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI436" t="n">
-        <v>7.001516536947591</v>
+        <v>7.001516536947593</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.2107164423430987</v>
+        <v>-0.2107164423431005</v>
       </c>
       <c r="AK436" t="n">
         <v>7.003692382618654</v>
@@ -71395,16 +71395,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.09225745624393285</v>
+        <v>-0.09225745624393369</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.003729646461095566</v>
+        <v>-0.003729646461095512</v>
       </c>
       <c r="AO436" t="n">
-        <v>0.02283737241168682</v>
+        <v>0.02283737241168637</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.7409128144376621</v>
+        <v>-0.7409128144376789</v>
       </c>
       <c r="AQ436" t="n">
         <v>39.22651933701658</v>
@@ -71548,10 +71548,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.982853032266831</v>
+        <v>6.98285303226683</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1977530490514985</v>
+        <v>-0.1977530490514976</v>
       </c>
       <c r="AK437" t="n">
         <v>6.994908837140057</v>
@@ -71560,16 +71560,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1040956648961739</v>
+        <v>-0.1040956648961724</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.004775368000139281</v>
+        <v>-0.004775368000139335</v>
       </c>
       <c r="AO437" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.5932977716256395</v>
+        <v>-0.5932977716256262</v>
       </c>
       <c r="AQ437" t="n">
         <v>40.38461538461539</v>
@@ -71713,10 +71713,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI438" t="n">
-        <v>6.976537964100195</v>
+        <v>6.976537964100197</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1673381540721186</v>
+        <v>-0.1673381540721204</v>
       </c>
       <c r="AK438" t="n">
         <v>6.976048621620001</v>
@@ -71725,16 +71725,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.1171809788132892</v>
+        <v>-0.1171809788132883</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.006568629287185491</v>
+        <v>-0.006568629287185546</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.03914952746580436</v>
+        <v>0.03914952746580425</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.2508070992156945</v>
+        <v>-0.2508070992157119</v>
       </c>
       <c r="AQ438" t="n">
         <v>48.08743169398907</v>
@@ -71881,7 +71881,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ439" t="n">
-        <v>-0.1582257113591092</v>
+        <v>-0.1582257113591101</v>
       </c>
       <c r="AK439" t="n">
         <v>6.970728111892008</v>
@@ -71890,16 +71890,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM439" t="n">
-        <v>-0.127636816539943</v>
+        <v>-0.127636816539944</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.00745101973257774</v>
+        <v>-0.007451019732577668</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.04750067483060572</v>
+        <v>0.04750067483060583</v>
       </c>
       <c r="AP439" t="n">
-        <v>-0.14773902465238</v>
+        <v>-0.1477390246523876</v>
       </c>
       <c r="AQ439" t="n">
         <v>49.18478260869566</v>
@@ -72058,13 +72058,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.008628156625160163</v>
+        <v>-0.008628156625160088</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.05751510742764121</v>
+        <v>0.05751510742764043</v>
       </c>
       <c r="AP440" t="n">
-        <v>-0.03659458102661073</v>
+        <v>-0.03659458102660845</v>
       </c>
       <c r="AQ440" t="n">
         <v>51.35135135135135</v>
@@ -72208,10 +72208,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.950644730799363</v>
+        <v>6.950644730799358</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1501448147227027</v>
+        <v>-0.1501448147226974</v>
       </c>
       <c r="AK441" t="n">
         <v>6.959853578800648</v>
@@ -72220,16 +72220,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1469566450661556</v>
+        <v>-0.1469566450661546</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.009026348114251901</v>
+        <v>-0.009026348114251986</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.06603756167960351</v>
+        <v>0.06603756167960417</v>
       </c>
       <c r="AP441" t="n">
-        <v>-0.05626100341237209</v>
+        <v>-0.05626100341230957</v>
       </c>
       <c r="AQ441" t="n">
         <v>49.19354838709678</v>
@@ -72373,28 +72373,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.934622414140152</v>
+        <v>6.934622414140156</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1321226430219875</v>
+        <v>-0.1321226430219919</v>
       </c>
       <c r="AK442" t="n">
-        <v>6.947114416435721</v>
+        <v>6.94711441643572</v>
       </c>
       <c r="AL442" t="n">
-        <v>-0.1446146453175565</v>
+        <v>-0.1446146453175556</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1568781652619921</v>
+        <v>-0.1568781652619925</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.01004287133747513</v>
+        <v>-0.010042871337475</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.07699206242755419</v>
+        <v>0.07699206242755485</v>
       </c>
       <c r="AP442" t="n">
-        <v>0.1480195792193899</v>
+        <v>0.1480195792193409</v>
       </c>
       <c r="AQ442" t="n">
         <v>58.28877005347594</v>
@@ -72538,10 +72538,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.928042396530073</v>
+        <v>6.928042396530076</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.133542522415083</v>
+        <v>-0.1335425224150857</v>
       </c>
       <c r="AK443" t="n">
         <v>6.933186989735641</v>
@@ -72550,16 +72550,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.1650917115670582</v>
+        <v>-0.1650917115670576</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01061494647532512</v>
+        <v>-0.0106149464753251</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.08732871254562202</v>
+        <v>0.08732871254562191</v>
       </c>
       <c r="AP443" t="n">
-        <v>0.1314955391289917</v>
+        <v>0.1314955391289633</v>
       </c>
       <c r="AQ443" t="n">
         <v>55.0531914893617</v>
@@ -72703,10 +72703,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.941461393298106</v>
+        <v>6.941461393298105</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1469615191831153</v>
+        <v>-0.1469615191831144</v>
       </c>
       <c r="AK444" t="n">
         <v>6.925995477801935</v>
@@ -72715,16 +72715,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.1745447047691478</v>
+        <v>-0.1745447047691483</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01108963812755724</v>
+        <v>-0.01108963812755723</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.09935205695041927</v>
+        <v>0.09935205695041804</v>
       </c>
       <c r="AP444" t="n">
-        <v>-0.02165722024127693</v>
+        <v>-0.02165722024126449</v>
       </c>
       <c r="AQ444" t="n">
         <v>48.67724867724867</v>
@@ -72868,10 +72868,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.933232103976423</v>
+        <v>6.93323210397643</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.147232329043562</v>
+        <v>-0.1472323290435682</v>
       </c>
       <c r="AK445" t="n">
         <v>6.938996539173566</v>
@@ -72880,16 +72880,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM445" t="n">
-        <v>-0.1853013335308053</v>
+        <v>-0.1853013335308036</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01193987645426136</v>
+        <v>-0.01193987645426134</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.1123648810347067</v>
+        <v>0.1123648810347069</v>
       </c>
       <c r="AP445" t="n">
-        <v>-0.02469248456278582</v>
+        <v>-0.02469248456285458</v>
       </c>
       <c r="AQ445" t="n">
         <v>44.47368421052632</v>
@@ -73033,10 +73033,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.928429644379658</v>
+        <v>6.928429644379657</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1496296336985061</v>
+        <v>-0.1496296336985043</v>
       </c>
       <c r="AK446" t="n">
         <v>6.93160690101155</v>
@@ -73048,13 +73048,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01257308415669775</v>
+        <v>-0.01257308415669778</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1258578984724115</v>
+        <v>0.125857898472412</v>
       </c>
       <c r="AP446" t="n">
-        <v>-0.05207285656414852</v>
+        <v>-0.05207285656412575</v>
       </c>
       <c r="AQ446" t="n">
         <v>44.76439790575916</v>
@@ -73198,10 +73198,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.925068850639512</v>
+        <v>6.925068850639515</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1455688430101176</v>
+        <v>-0.1455688430101203</v>
       </c>
       <c r="AK447" t="n">
         <v>6.924763510572069</v>
@@ -73210,16 +73210,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2060805417157789</v>
+        <v>-0.2060805417157788</v>
       </c>
       <c r="AN447" t="n">
-        <v>-0.01318646791849928</v>
+        <v>-0.01318646791849926</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1396251026736647</v>
+        <v>0.1396251026736655</v>
       </c>
       <c r="AP447" t="n">
-        <v>-0.00532539912611095</v>
+        <v>-0.005325399126139124</v>
       </c>
       <c r="AQ447" t="n">
         <v>48.4375</v>
@@ -73363,10 +73363,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.900929863197373</v>
+        <v>6.900929863197374</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1347297975845798</v>
+        <v>-0.1347297975845807</v>
       </c>
       <c r="AK448" t="n">
         <v>6.921049732547429</v>
@@ -73375,16 +73375,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM448" t="n">
-        <v>-0.2151279705591481</v>
+        <v>-0.2151279705591488</v>
       </c>
       <c r="AN448" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1518365696223549</v>
+        <v>0.1518365696223548</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.1194301167255552</v>
+        <v>0.1194301167255473</v>
       </c>
       <c r="AQ448" t="n">
         <v>49.48186528497409</v>
@@ -73528,10 +73528,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.89521901018146</v>
+        <v>6.895219010181459</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.1302191436958644</v>
+        <v>-0.1302191436958635</v>
       </c>
       <c r="AK449" t="n">
         <v>6.89978353884127</v>
@@ -73543,13 +73543,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01278923357027006</v>
+        <v>-0.01278923357027009</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.1644177475946105</v>
+        <v>0.1644177475946104</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.1711578920391523</v>
+        <v>0.1711578920391648</v>
       </c>
       <c r="AQ449" t="n">
         <v>47.16494845360825</v>
@@ -73693,10 +73693,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.87951223984858</v>
+        <v>6.879512239848579</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.1173123611559532</v>
+        <v>-0.1173123611559523</v>
       </c>
       <c r="AK450" t="n">
         <v>6.893260360395011</v>
@@ -73705,16 +73705,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.233692768734328</v>
+        <v>-0.233692768734329</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01245257184765156</v>
+        <v>-0.01245257184765153</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.1791295233320875</v>
+        <v>0.179129523332087</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.3199422777651673</v>
+        <v>0.3199422777651793</v>
       </c>
       <c r="AQ450" t="n">
         <v>50.51282051282051</v>
@@ -73858,10 +73858,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI451" t="n">
-        <v>6.882426232260437</v>
+        <v>6.882426232260446</v>
       </c>
       <c r="AJ451" t="n">
-        <v>-0.1132263840853884</v>
+        <v>-0.1132263840853973</v>
       </c>
       <c r="AK451" t="n">
         <v>6.880758546638964</v>
@@ -73870,16 +73870,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2433281856134888</v>
+        <v>-0.2433281856134891</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01202813951384067</v>
+        <v>-0.01202813951384066</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.1944608722019407</v>
+        <v>0.1944608722019401</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.3663796020963871</v>
+        <v>0.3663796020962863</v>
       </c>
       <c r="AQ451" t="n">
         <v>52.04081632653062</v>
@@ -74035,16 +74035,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.25202644278106</v>
+        <v>-0.2520264427810588</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01246671652825434</v>
+        <v>-0.01246671652825437</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2101991144027905</v>
+        <v>0.2101991144027906</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.9316471322250883</v>
+        <v>0.9316471322250902</v>
       </c>
       <c r="AQ452" t="n">
         <v>64.72081218274111</v>
@@ -74188,10 +74188,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.841963898035326</v>
+        <v>6.841963898035317</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.07646382937077512</v>
+        <v>-0.07646382937076623</v>
       </c>
       <c r="AK453" t="n">
         <v>6.844785316397215</v>
@@ -74200,16 +74200,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.2592973891940566</v>
+        <v>-0.2592973891940562</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01305068899435077</v>
+        <v>-0.01305068899435097</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2277185089957524</v>
+        <v>0.2277185089957531</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7869542060736205</v>
+        <v>0.7869542060737252</v>
       </c>
       <c r="AQ453" t="n">
         <v>58.08080808080808</v>
@@ -74353,28 +74353,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.845644916883079</v>
+        <v>6.845644916883085</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.08014484821852808</v>
+        <v>-0.08014484821853429</v>
       </c>
       <c r="AK454" t="n">
-        <v>6.849407886968132</v>
+        <v>6.849407886968131</v>
       </c>
       <c r="AL454" t="n">
-        <v>-0.08390781830358129</v>
+        <v>-0.08390781830358041</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2668003223256254</v>
+        <v>-0.2668003223256257</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.0136798902005495</v>
+        <v>-0.01367989020054944</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.2456601220977566</v>
+        <v>0.2456601220977563</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.7411156361323163</v>
+        <v>0.7411156361322451</v>
       </c>
       <c r="AQ454" t="n">
         <v>57.78894472361809</v>
@@ -74518,10 +74518,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.842084108625038</v>
+        <v>6.842084108625032</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.06958407047806503</v>
+        <v>-0.0695840704780597</v>
       </c>
       <c r="AK455" t="n">
         <v>6.852702018840203</v>
@@ -74530,16 +74530,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.273543646731814</v>
+        <v>-0.2735436467318143</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01403412282467991</v>
+        <v>-0.01403412282467997</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.261983510217226</v>
+        <v>0.2619835102172253</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.8606851556422036</v>
+        <v>0.8606851556422667</v>
       </c>
       <c r="AQ455" t="n">
         <v>63</v>
@@ -74683,10 +74683,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.863831060847785</v>
+        <v>6.863831060847773</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.09133102270081217</v>
+        <v>-0.09133102270080062</v>
       </c>
       <c r="AK456" t="n">
         <v>6.850973969550408</v>
@@ -74695,16 +74695,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM456" t="n">
-        <v>-0.2787367835501617</v>
+        <v>-0.2787367835501612</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.01406387644726588</v>
+        <v>-0.01406387644726603</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.2758112468611976</v>
+        <v>0.2758112468611987</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.6044845987545961</v>
+        <v>0.6044845987547318</v>
       </c>
       <c r="AQ456" t="n">
         <v>61.94029850746269</v>
@@ -74848,10 +74848,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI457" t="n">
-        <v>6.853037915615573</v>
+        <v>6.853037915615571</v>
       </c>
       <c r="AJ457" t="n">
-        <v>-0.07753809490634467</v>
+        <v>-0.07753809490634289</v>
       </c>
       <c r="AK457" t="n">
         <v>6.873527983489108</v>
@@ -74863,13 +74863,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN457" t="n">
-        <v>-0.01379017718565697</v>
+        <v>-0.013790177185657</v>
       </c>
       <c r="AO457" t="n">
-        <v>0.2854425463774817</v>
+        <v>0.285442546377481</v>
       </c>
       <c r="AP457" t="n">
-        <v>0.762927807513867</v>
+        <v>0.7629278075138878</v>
       </c>
       <c r="AQ457" t="n">
         <v>68.06930693069307</v>
@@ -75025,7 +75025,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.2865252693972545</v>
+        <v>-0.2865252693972544</v>
       </c>
       <c r="AN458" t="n">
         <v>-0.01327380582108439</v>
@@ -75034,7 +75034,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP458" t="n">
-        <v>0.5648982895268598</v>
+        <v>0.5648982895268601</v>
       </c>
       <c r="AQ458" t="n">
         <v>61.33004926108374</v>
@@ -75178,10 +75178,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.860047631936787</v>
+        <v>6.860047631936786</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.1030476624543653</v>
+        <v>-0.1030476624543644</v>
       </c>
       <c r="AK459" t="n">
         <v>6.865985861260643</v>
@@ -75190,16 +75190,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.2905223093479492</v>
+        <v>-0.290522309347949</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.01240158194086378</v>
+        <v>-0.01240158194086383</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3024992257449914</v>
+        <v>0.3024992257449916</v>
       </c>
       <c r="AP459" t="n">
-        <v>0.4606483756803518</v>
+        <v>0.4606483756803628</v>
       </c>
       <c r="AQ459" t="n">
         <v>57.59803921568628</v>
@@ -75343,10 +75343,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.801980414635016</v>
+        <v>6.801980414635013</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.04478065038330659</v>
+        <v>-0.04478065038330392</v>
       </c>
       <c r="AK460" t="n">
         <v>6.863576603094304</v>
@@ -75355,16 +75355,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.2950697019949104</v>
+        <v>-0.2950697019949103</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.01161053315968381</v>
+        <v>-0.0116105331596838</v>
       </c>
       <c r="AO460" t="n">
-        <v>0.3113800696686918</v>
+        <v>0.3113800696686924</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.139401850244913</v>
+        <v>1.139401850244943</v>
       </c>
       <c r="AQ460" t="n">
         <v>78.53658536585365</v>
@@ -75508,10 +75508,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.789283666813422</v>
+        <v>6.789283666813423</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.03208390256171256</v>
+        <v>-0.03208390256171434</v>
       </c>
       <c r="AK461" t="n">
         <v>6.809671190627447</v>
@@ -75520,16 +75520,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.2987092362344108</v>
+        <v>-0.2987092362344105</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.01030385953714808</v>
+        <v>-0.01030385953714813</v>
       </c>
       <c r="AO461" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.280307854289602</v>
+        <v>1.280307854289579</v>
       </c>
       <c r="AQ461" t="n">
         <v>81.55339805825244</v>
@@ -75673,10 +75673,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.789252537988933</v>
+        <v>6.789252537988938</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.0206525509589035</v>
+        <v>-0.02065255095890883</v>
       </c>
       <c r="AK462" t="n">
         <v>6.802840448144932</v>
@@ -75685,16 +75685,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3027504956929284</v>
+        <v>-0.3027504956929287</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.008812786025409641</v>
+        <v>-0.00881278602540958</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.3322271170679635</v>
+        <v>0.332227117067963</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.404215965965194</v>
+        <v>1.404215965965131</v>
       </c>
       <c r="AQ462" t="n">
         <v>82.60869565217391</v>
@@ -75838,10 +75838,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.774001672255932</v>
+        <v>6.774001672255927</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.005401685225902675</v>
+        <v>-0.005401685225897346</v>
       </c>
       <c r="AK463" t="n">
         <v>6.800260207803535</v>
@@ -75850,16 +75850,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3068099364477367</v>
+        <v>-0.3068099364477369</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.007070247176567688</v>
+        <v>-0.007070247176567734</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3427146952658534</v>
+        <v>0.3427146952658529</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.56945400069665</v>
+        <v>1.569454000696709</v>
       </c>
       <c r="AQ463" t="n">
         <v>83.41346153846153</v>
@@ -76003,10 +76003,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.802628307046303</v>
+        <v>6.802628307046305</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.02812841385782594</v>
+        <v>-0.0281284138578286</v>
       </c>
       <c r="AK464" t="n">
         <v>6.781970485204615</v>
@@ -76015,16 +76015,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3121566752204101</v>
+        <v>-0.3121566752204096</v>
       </c>
       <c r="AN464" t="n">
-        <v>-0.005102880740085154</v>
+        <v>-0.005102880740085192</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.3560731605465757</v>
+        <v>0.3560731605465752</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.29601405563901</v>
+        <v>1.296014055638977</v>
       </c>
       <c r="AQ464" t="n">
         <v>79.42583732057417</v>
@@ -76168,28 +76168,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.815944895083632</v>
+        <v>6.815944895083629</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.02594493323060476</v>
+        <v>-0.0259449332306021</v>
       </c>
       <c r="AK465" t="n">
-        <v>6.809638458820508</v>
+        <v>6.809638458820509</v>
       </c>
       <c r="AL465" t="n">
-        <v>-0.01963849696748099</v>
+        <v>-0.01963849696748188</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3181413841564619</v>
+        <v>-0.3181413841564625</v>
       </c>
       <c r="AN465" t="n">
-        <v>-0.003317316385138562</v>
+        <v>-0.003317316385138602</v>
       </c>
       <c r="AO465" t="n">
-        <v>0.3690689225934922</v>
+        <v>0.3690689225934927</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.312827614648325</v>
+        <v>1.312827614648354</v>
       </c>
       <c r="AQ465" t="n">
         <v>81.19047619047619</v>
@@ -76333,10 +76333,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.821941449304753</v>
+        <v>6.821941449304759</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.03194148745172587</v>
+        <v>-0.0319414874517312</v>
       </c>
       <c r="AK466" t="n">
         <v>6.819973703544699</v>
@@ -76345,16 +76345,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3244228225822198</v>
+        <v>-0.3244228225822193</v>
       </c>
       <c r="AN466" t="n">
-        <v>-0.001700148658338742</v>
+        <v>-0.001700148658338674</v>
       </c>
       <c r="AO466" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.235661012584574</v>
+        <v>1.235661012584512</v>
       </c>
       <c r="AQ466" t="n">
         <v>77.96208530805687</v>
@@ -76498,10 +76498,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.826413262727749</v>
+        <v>6.826413262727742</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.03641330087472205</v>
+        <v>-0.03641330087471495</v>
       </c>
       <c r="AK467" t="n">
         <v>6.822087900644207</v>
@@ -76510,16 +76510,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3308797299382495</v>
+        <v>-0.3308797299382499</v>
       </c>
       <c r="AN467" t="n">
-        <v>-7.481797733213274e-05</v>
+        <v>-7.481797733216444e-05</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.396078871041881</v>
+        <v>0.3960788710418811</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.177071213951572</v>
+        <v>1.177071213951652</v>
       </c>
       <c r="AQ467" t="n">
         <v>78.5377358490566</v>
@@ -76663,10 +76663,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.81265664767955</v>
+        <v>6.812656647679548</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.01465678882334931</v>
+        <v>-0.01465678882334664</v>
       </c>
       <c r="AK468" t="n">
         <v>6.823881638371397</v>
@@ -76675,16 +76675,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3363418922753058</v>
+        <v>-0.3363418922753055</v>
       </c>
       <c r="AN468" t="n">
-        <v>0.001379920606120097</v>
+        <v>0.001379920606120022</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4081029523904167</v>
+        <v>0.4081029523904164</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.419204189894323</v>
+        <v>1.419204189894351</v>
       </c>
       <c r="AQ468" t="n">
         <v>83.09859154929578</v>
@@ -76828,10 +76828,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI469" t="n">
-        <v>6.802797817425505</v>
+        <v>6.802797817425507</v>
       </c>
       <c r="AJ469" t="n">
-        <v>-0.009197735028044107</v>
+        <v>-0.009197735028045884</v>
       </c>
       <c r="AK469" t="n">
         <v>6.808320681191073</v>
@@ -76840,16 +76840,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3410659803634682</v>
+        <v>-0.3410659803634685</v>
       </c>
       <c r="AN469" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4198133218741357</v>
+        <v>0.4198133218741356</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.471334908821365</v>
+        <v>1.471334908821341</v>
       </c>
       <c r="AQ469" t="n">
         <v>83.17757009345794</v>
@@ -76999,22 +76999,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK470" t="n">
-        <v>6.795980661778266</v>
+        <v>6.795980661778267</v>
       </c>
       <c r="AL470" t="n">
-        <v>-0.002380579380805159</v>
+        <v>-0.002380579380806047</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3461577281601509</v>
+        <v>-0.3461577281601511</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.00428288788357468</v>
+        <v>0.004282887883574671</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4328049372030969</v>
+        <v>0.4328049372030962</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.532704943923479</v>
+        <v>1.532704943923476</v>
       </c>
       <c r="AQ470" t="n">
         <v>84.41860465116279</v>
@@ -77158,10 +77158,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.800189882196236</v>
+        <v>6.800189882196235</v>
       </c>
       <c r="AJ471" t="n">
-        <v>-0.005989938653755189</v>
+        <v>-0.005989938653754301</v>
       </c>
       <c r="AK471" t="n">
         <v>6.78726841810145</v>
@@ -77170,16 +77170,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3502903933401418</v>
+        <v>-0.3502903933401412</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.005405808652032067</v>
+        <v>0.005405808652032051</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4450018361960534</v>
+        <v>0.4450018361960529</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.485189478864205</v>
+        <v>1.485189478864212</v>
       </c>
       <c r="AQ471" t="n">
         <v>83.33333333333334</v>
@@ -77323,10 +77323,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.797972083642554</v>
+        <v>6.79797208364255</v>
       </c>
       <c r="AJ472" t="n">
-        <v>-0.009372115686010929</v>
+        <v>-0.009372115686007376</v>
       </c>
       <c r="AK472" t="n">
         <v>6.791305278184372</v>
@@ -77335,16 +77335,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM472" t="n">
-        <v>-0.3548656112706071</v>
+        <v>-0.3548656112706069</v>
       </c>
       <c r="AN472" t="n">
-        <v>0.006091291211178139</v>
+        <v>0.006091291211178074</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4593697101544705</v>
+        <v>0.4593697101544711</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.436147929377155</v>
+        <v>1.436147929377192</v>
       </c>
       <c r="AQ472" t="n">
         <v>82.02764976958525</v>
@@ -77488,10 +77488,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.800452644405178</v>
+        <v>6.800452644405181</v>
       </c>
       <c r="AJ473" t="n">
-        <v>-0.01185267644863508</v>
+        <v>-0.01185267644863774</v>
       </c>
       <c r="AK473" t="n">
         <v>6.789098969069376</v>
@@ -77506,10 +77506,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.4721687943484545</v>
+        <v>0.4721687943484544</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.398187361022255</v>
+        <v>1.398187361022222</v>
       </c>
       <c r="AQ473" t="n">
         <v>78.89908256880734</v>
@@ -77653,10 +77653,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.778720347685814</v>
+        <v>6.778720347685821</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.01707986135959594</v>
+        <v>0.01707986135958883</v>
       </c>
       <c r="AK474" t="n">
         <v>6.790465135395929</v>
@@ -77665,16 +77665,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3625273381377933</v>
+        <v>-0.3625273381377937</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.007343464385960585</v>
+        <v>0.007343464385960674</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.4863203622043382</v>
+        <v>0.4863203622043377</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.712749797966303</v>
+        <v>1.71274979796622</v>
       </c>
       <c r="AQ474" t="n">
         <v>84.01826484018265</v>
@@ -77818,10 +77818,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.769755998762545</v>
+        <v>6.769755998762547</v>
       </c>
       <c r="AJ475" t="n">
-        <v>0.02364381202847099</v>
+        <v>0.02364381202846833</v>
       </c>
       <c r="AK475" t="n">
         <v>6.767889899932765</v>
@@ -77830,16 +77830,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3660007866474813</v>
+        <v>-0.3660007866474812</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.008260137822954145</v>
+        <v>0.00826013782295415</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.4997690914082401</v>
+        <v>0.4997690914082398</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.770409513214951</v>
+        <v>1.770409513214919</v>
       </c>
       <c r="AQ475" t="n">
         <v>84.77272727272728</v>
@@ -77983,10 +77983,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.789177604754244</v>
+        <v>6.789177604754239</v>
       </c>
       <c r="AJ476" t="n">
-        <v>0.01332216636391959</v>
+        <v>0.01332216636392491</v>
       </c>
       <c r="AK476" t="n">
         <v>6.759766754404358</v>
@@ -77995,16 +77995,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3700034659576351</v>
+        <v>-0.3700034659576358</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.009871715534546958</v>
+        <v>0.00987171553454691</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5120623436103324</v>
+        <v>0.5120623436103316</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.639833830313563</v>
+        <v>1.63983383031362</v>
       </c>
       <c r="AQ476" t="n">
         <v>84.84162895927602</v>
@@ -78148,10 +78148,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI477" t="n">
-        <v>6.774331376960425</v>
+        <v>6.774331376960423</v>
       </c>
       <c r="AJ477" t="n">
-        <v>0.01776857573732915</v>
+        <v>0.01776857573733093</v>
       </c>
       <c r="AK477" t="n">
         <v>6.777856240868369</v>
@@ -78160,16 +78160,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3750442390024147</v>
+        <v>-0.3750442390024145</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01196068662558781</v>
+        <v>0.01196068662558775</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.5238651846176463</v>
+        <v>0.5238651846176465</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.675321848806344</v>
+        <v>1.67532184880636</v>
       </c>
       <c r="AQ477" t="n">
         <v>84.00900900900902</v>
@@ -78325,16 +78325,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3816350905604307</v>
+        <v>-0.3816350905604304</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01460798460929556</v>
+        <v>0.01460798460929558</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5379583104732891</v>
+        <v>0.537958310473289</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.621777678682498</v>
+        <v>1.621777678682495</v>
       </c>
       <c r="AQ478" t="n">
         <v>84.52914798206278</v>
@@ -78478,10 +78478,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.789815280543245</v>
+        <v>6.789815280543246</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.01031527291385093</v>
+        <v>-0.01031527291385181</v>
       </c>
       <c r="AK479" t="n">
         <v>6.744939020214936</v>
@@ -78490,16 +78490,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.3872393091179339</v>
+        <v>-0.3872393091179336</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01685992867552231</v>
+        <v>0.01685992867552227</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5511317941481415</v>
+        <v>0.5511317941481411</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.339566442594212</v>
+        <v>1.3395664425942</v>
       </c>
       <c r="AQ479" t="n">
         <v>82.14285714285714</v>
@@ -78643,10 +78643,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.801295181477309</v>
+        <v>6.801295181477315</v>
       </c>
       <c r="AJ480" t="n">
-        <v>-0.0312952005507956</v>
+        <v>-0.03129520055080093</v>
       </c>
       <c r="AK480" t="n">
         <v>6.772636231606738</v>
@@ -78655,16 +78655,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3930200198603389</v>
+        <v>-0.393020019860339</v>
       </c>
       <c r="AN480" t="n">
-        <v>0.01873686412955481</v>
+        <v>0.01873686412955489</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.5644439393662187</v>
+        <v>0.5644439393662184</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.100144262686309</v>
+        <v>1.100144262686249</v>
       </c>
       <c r="AQ480" t="n">
         <v>76.44444444444446</v>
@@ -78808,10 +78808,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.791632066062364</v>
+        <v>6.791632066062363</v>
       </c>
       <c r="AJ481" t="n">
-        <v>-0.02343214540806748</v>
+        <v>-0.0234321454080666</v>
       </c>
       <c r="AK481" t="n">
         <v>6.788619247652995</v>
@@ -78820,16 +78820,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3966294116439323</v>
+        <v>-0.3966294116439325</v>
       </c>
       <c r="AN481" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.5769744719733717</v>
+        <v>0.576974471973372</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.181475994909424</v>
+        <v>1.181475994909433</v>
       </c>
       <c r="AQ481" t="n">
         <v>74.3362831858407</v>
@@ -78973,10 +78973,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.779898505875918</v>
+        <v>6.779898505875916</v>
       </c>
       <c r="AJ482" t="n">
-        <v>-0.00739846772894559</v>
+        <v>-0.007398467728943814</v>
       </c>
       <c r="AK482" t="n">
         <v>6.776305653888958</v>
@@ -78985,16 +78985,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3980313152890724</v>
+        <v>-0.3980313152890726</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.0193312470422838</v>
+        <v>0.01933124704228378</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.5877384296086161</v>
+        <v>0.5877384296086169</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.351537097819748</v>
+        <v>1.351537097819766</v>
       </c>
       <c r="AQ482" t="n">
         <v>76.21145374449338</v>
@@ -79138,10 +79138,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.771360892616116</v>
+        <v>6.771360892616113</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.001139145530856922</v>
+        <v>0.001139145530859587</v>
       </c>
       <c r="AK483" t="n">
         <v>6.76492936370744</v>
@@ -79150,16 +79150,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.3979537985659302</v>
+        <v>-0.3979537985659305</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01835844536093246</v>
+        <v>0.0183584453609324</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6001791687136286</v>
+        <v>0.6001791687136281</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.436676488237739</v>
+        <v>1.436676488237766</v>
       </c>
       <c r="AQ483" t="n">
         <v>77.19298245614036</v>
@@ -79303,10 +79303,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.751667781721842</v>
+        <v>6.751667781721844</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.02083225642513042</v>
+        <v>0.02083225642512865</v>
       </c>
       <c r="AK484" t="n">
         <v>6.753855191419989</v>
@@ -79315,16 +79315,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3975762425746347</v>
+        <v>-0.3975762425746344</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01731206726614282</v>
+        <v>0.01731206726614276</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6129676701055397</v>
+        <v>0.6129676701055393</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.6416363802477</v>
+        <v>1.641636380247678</v>
       </c>
       <c r="AQ484" t="n">
         <v>82.53275109170306</v>
@@ -79468,10 +79468,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.72973866986929</v>
+        <v>6.729738669869288</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.0358615345984834</v>
+        <v>0.03586153459848518</v>
       </c>
       <c r="AK485" t="n">
         <v>6.736226026398153</v>
@@ -79480,16 +79480,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.3964908591695858</v>
+        <v>-0.3964908591695859</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01740130648959375</v>
+        <v>0.01740130648959376</v>
       </c>
       <c r="AO485" t="n">
-        <v>0.6198907013195265</v>
+        <v>0.6198907013195262</v>
       </c>
       <c r="AP485" t="n">
-        <v>1.791030923987134</v>
+        <v>1.79103092398715</v>
       </c>
       <c r="AQ485" t="n">
         <v>80</v>
@@ -79633,10 +79633,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.713320364291505</v>
+        <v>6.713320364291503</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.05917967385546774</v>
+        <v>0.05917967385546952</v>
       </c>
       <c r="AK486" t="n">
         <v>6.717723214958548</v>
@@ -79645,16 +79645,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM486" t="n">
-        <v>-0.3947605344816719</v>
+        <v>-0.394760534481672</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.01742962324324019</v>
+        <v>0.01742962324324016</v>
       </c>
       <c r="AO486" t="n">
-        <v>0.6272835381163618</v>
+        <v>0.6272835381163622</v>
       </c>
       <c r="AP486" t="n">
-        <v>2.024609944078435</v>
+        <v>2.02460994407845</v>
       </c>
       <c r="AQ486" t="n">
         <v>86.7965367965368</v>
@@ -79798,10 +79798,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.731179671396997</v>
+        <v>6.731179671396989</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.04132036674997597</v>
+        <v>0.04132036674998396</v>
       </c>
       <c r="AK487" t="n">
         <v>6.699415101064979</v>
@@ -79813,13 +79813,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.0176659673264611</v>
+        <v>0.01766596732646103</v>
       </c>
       <c r="AO487" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.812586682659161</v>
+        <v>1.812586682659243</v>
       </c>
       <c r="AQ487" t="n">
         <v>86.20689655172413</v>
@@ -79963,10 +79963,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.740946959621005</v>
+        <v>6.740946959621007</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.03085308157772548</v>
+        <v>0.03085308157772371</v>
       </c>
       <c r="AK488" t="n">
         <v>6.714685154719483</v>
@@ -79975,16 +79975,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.392942339423851</v>
+        <v>-0.3929423394238508</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.0184207037809263</v>
+        <v>0.01842070378092631</v>
       </c>
       <c r="AO488" t="n">
-        <v>0.6403745111659787</v>
+        <v>0.640374511165978</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.684785401375887</v>
+        <v>1.684785401375863</v>
       </c>
       <c r="AQ488" t="n">
         <v>84.12017167381974</v>
@@ -80128,10 +80128,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.758957757771704</v>
+        <v>6.7589577577717</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.006742105662134179</v>
+        <v>0.006742105662137732</v>
       </c>
       <c r="AK489" t="n">
         <v>6.722064699270507</v>
@@ -80140,16 +80140,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.3931401656438955</v>
+        <v>-0.3931401656438959</v>
       </c>
       <c r="AN489" t="n">
-        <v>0.01902711841846487</v>
+        <v>0.01902711841846483</v>
       </c>
       <c r="AO489" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.414712695882782</v>
+        <v>1.414712695882816</v>
       </c>
       <c r="AQ489" t="n">
         <v>79.91452991452991</v>
@@ -80293,10 +80293,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI490" t="n">
-        <v>6.763209774497788</v>
+        <v>6.763209774497792</v>
       </c>
       <c r="AJ490" t="n">
-        <v>0.007790133949477251</v>
+        <v>0.007790133949473699</v>
       </c>
       <c r="AK490" t="n">
         <v>6.739235851443908</v>
@@ -80305,16 +80305,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3951733572725246</v>
+        <v>-0.3951733572725242</v>
       </c>
       <c r="AN490" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6590798145480942</v>
+        <v>0.6590798145480943</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.416860716206502</v>
+        <v>1.41686071620646</v>
       </c>
       <c r="AQ490" t="n">
         <v>80.21276595744681</v>
@@ -80470,16 +80470,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.396000186332361</v>
+        <v>-0.3960001863323608</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02043272610569401</v>
+        <v>0.02043272610569408</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.6685846444009627</v>
+        <v>0.6685846444009622</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.599280092475877</v>
+        <v>1.599280092475873</v>
       </c>
       <c r="AQ491" t="n">
         <v>80.72033898305085</v>
@@ -80623,10 +80623,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.714622134232888</v>
+        <v>6.714622134232894</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.04037798020802974</v>
+        <v>0.04037798020802441</v>
       </c>
       <c r="AK492" t="n">
         <v>6.746779913842831</v>
@@ -80635,16 +80635,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM492" t="n">
-        <v>-0.3967409053619114</v>
+        <v>-0.396740905361911</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.02120763540003743</v>
+        <v>0.02120763540003751</v>
       </c>
       <c r="AO492" t="n">
-        <v>0.6777865296786978</v>
+        <v>0.6777865296786982</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.740194523547725</v>
+        <v>1.740194523547664</v>
       </c>
       <c r="AQ492" t="n">
         <v>83.33333333333334</v>
@@ -80788,28 +80788,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.73157005939442</v>
+        <v>6.731570059394423</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.01932973232310964</v>
+        <v>0.01932973232310609</v>
       </c>
       <c r="AK493" t="n">
-        <v>6.728823425344639</v>
+        <v>6.728823425344638</v>
       </c>
       <c r="AL493" t="n">
-        <v>0.02207636637289045</v>
+        <v>0.02207636637289134</v>
       </c>
       <c r="AM493" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02200829621703764</v>
+        <v>0.0220082962170377</v>
       </c>
       <c r="AO493" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.504731032544678</v>
+        <v>1.504731032544637</v>
       </c>
       <c r="AQ493" t="n">
         <v>78.78151260504201</v>
@@ -80953,10 +80953,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.748064561399863</v>
+        <v>6.748064561399866</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.00423522421415079</v>
+        <v>0.004235224214148126</v>
       </c>
       <c r="AK494" t="n">
         <v>6.740096815166266</v>
@@ -80965,16 +80965,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.3976889317784196</v>
+        <v>-0.3976889317784199</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02268190844878653</v>
+        <v>0.02268190844878654</v>
       </c>
       <c r="AO494" t="n">
-        <v>0.6953567146475526</v>
+        <v>0.6953567146475523</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.33593563729877</v>
+        <v>1.33593563729874</v>
       </c>
       <c r="AQ494" t="n">
         <v>73.84937238493724</v>
@@ -81118,10 +81118,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.747226278872151</v>
+        <v>6.747226278872152</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.005973775296550521</v>
+        <v>0.005973775296548745</v>
       </c>
       <c r="AK495" t="n">
         <v>6.755554272205931</v>
@@ -81130,16 +81130,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.400351527586135</v>
+        <v>-0.4003515275861345</v>
       </c>
       <c r="AN495" t="n">
-        <v>0.02398656672240616</v>
+        <v>0.02398656672240618</v>
       </c>
       <c r="AO495" t="n">
-        <v>0.7067969646460924</v>
+        <v>0.7067969646460921</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.346470010405875</v>
+        <v>1.346470010405854</v>
       </c>
       <c r="AQ495" t="n">
         <v>73.54166666666667</v>
@@ -81283,10 +81283,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.724989986752573</v>
+        <v>6.724989986752571</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.02471008267491737</v>
+        <v>0.02471008267491914</v>
       </c>
       <c r="AK496" t="n">
         <v>6.75925064743029</v>
@@ -81295,7 +81295,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4017887258056131</v>
+        <v>-0.4017887258056133</v>
       </c>
       <c r="AN496" t="n">
         <v>0.02482212216928553</v>
@@ -81304,7 +81304,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.534738827052756</v>
+        <v>1.534738827052774</v>
       </c>
       <c r="AQ496" t="n">
         <v>76.97095435684648</v>
@@ -81448,28 +81448,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.738231277482303</v>
+        <v>6.738231277482312</v>
       </c>
       <c r="AJ497" t="n">
-        <v>0.01056852339049996</v>
+        <v>0.01056852339049108</v>
       </c>
       <c r="AK497" t="n">
-        <v>6.734775445902896</v>
+        <v>6.734775445902895</v>
       </c>
       <c r="AL497" t="n">
-        <v>0.01402435496990684</v>
+        <v>0.01402435496990773</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.402229404255429</v>
+        <v>-0.4022294042554291</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02545790195722734</v>
+        <v>0.02545790195722747</v>
       </c>
       <c r="AO497" t="n">
-        <v>0.7273309315128232</v>
+        <v>0.7273309315128231</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.376586915245278</v>
+        <v>1.376586915245184</v>
       </c>
       <c r="AQ497" t="n">
         <v>74.3801652892562</v>
@@ -81613,10 +81613,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.718201282169575</v>
+        <v>6.718201282169581</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.02919852480674301</v>
+        <v>0.02919852480673768</v>
       </c>
       <c r="AK498" t="n">
         <v>6.753996132599221</v>
@@ -81625,16 +81625,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4027953816469059</v>
+        <v>-0.4027953816469058</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02608258444417639</v>
+        <v>0.02608258444417638</v>
       </c>
       <c r="AO498" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.562402624386304</v>
+        <v>1.562402624386248</v>
       </c>
       <c r="AQ498" t="n">
         <v>78.18930041152262</v>
@@ -81778,10 +81778,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI499" t="n">
-        <v>6.730898772467415</v>
+        <v>6.730898772467414</v>
       </c>
       <c r="AJ499" t="n">
-        <v>0.01650103450890317</v>
+        <v>0.01650103450890406</v>
       </c>
       <c r="AK499" t="n">
         <v>6.732394407262716</v>
@@ -81790,16 +81790,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.402509900769414</v>
+        <v>-0.4025099007694142</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02634377330607648</v>
+        <v>0.02634377330607651</v>
       </c>
       <c r="AO499" t="n">
-        <v>0.7465615195282662</v>
+        <v>0.746561519528266</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.419661467469243</v>
+        <v>1.419661467469252</v>
       </c>
       <c r="AQ499" t="n">
         <v>78.68852459016394</v>
@@ -81955,16 +81955,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4034224290251453</v>
+        <v>-0.4034224290251451</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02736182786837866</v>
+        <v>0.02736182786837871</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.7551898634710656</v>
+        <v>0.755189863471066</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.285527143558826</v>
+        <v>1.285527143558827</v>
       </c>
       <c r="AQ500" t="n">
         <v>76.73469387755102</v>
@@ -82108,10 +82108,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.75570846679488</v>
+        <v>6.755708466794879</v>
       </c>
       <c r="AJ501" t="n">
-        <v>-0.01240850570479246</v>
+        <v>-0.01240850570479068</v>
       </c>
       <c r="AK501" t="n">
         <v>6.746865899087779</v>
@@ -82120,16 +82120,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.4037073020769305</v>
+        <v>-0.4037073020769307</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02778289906564353</v>
+        <v>0.02778289906564352</v>
       </c>
       <c r="AO501" t="n">
-        <v>0.7638221248099444</v>
+        <v>0.7638221248099442</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.103708249481985</v>
+        <v>1.103708249482004</v>
       </c>
       <c r="AQ501" t="n">
         <v>79.47154471544715</v>
@@ -82273,10 +82273,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI502" t="n">
-        <v>6.73601646973097</v>
+        <v>6.73601646973098</v>
       </c>
       <c r="AJ502" t="n">
-        <v>0.006783766017321113</v>
+        <v>0.006783766017311343</v>
       </c>
       <c r="AK502" t="n">
         <v>6.761018647414997</v>
@@ -82285,16 +82285,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM502" t="n">
-        <v>-0.4035108188951355</v>
+        <v>-0.403510818895136</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02805871830419202</v>
+        <v>0.02805871830419215</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.298142681594773</v>
+        <v>1.298142681594672</v>
       </c>
       <c r="AQ502" t="n">
         <v>83.19838056680162</v>
@@ -82453,13 +82453,13 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02827333203020884</v>
+        <v>0.02827333203020888</v>
       </c>
       <c r="AO503" t="n">
         <v>0.7726830480787004</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.383694782072954</v>
+        <v>1.383694782072955</v>
       </c>
       <c r="AQ503" t="n">
         <v>83.66935483870968</v>
@@ -82603,10 +82603,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.725806144687716</v>
+        <v>6.725806144687715</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.01409396746438318</v>
+        <v>0.01409396746438496</v>
       </c>
       <c r="AK504" t="n">
         <v>6.744478107428201</v>
@@ -82615,16 +82615,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.4027900432658339</v>
+        <v>-0.4027900432658338</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.0289145361322863</v>
+        <v>0.02891453613228628</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7784357006627718</v>
+        <v>0.7784357006627721</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.358780907702631</v>
+        <v>1.358780907702651</v>
       </c>
       <c r="AQ504" t="n">
         <v>83.13253012048193</v>
@@ -82768,10 +82768,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.700854569500285</v>
+        <v>6.700854569500288</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.04174539464156091</v>
+        <v>0.04174539464155735</v>
       </c>
       <c r="AK505" t="n">
         <v>6.743301592583855</v>
@@ -82780,16 +82780,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.4027426974585472</v>
+        <v>-0.402742697458547</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.0295556803648227</v>
+        <v>0.02955568036482276</v>
       </c>
       <c r="AO505" t="n">
-        <v>0.7839391318357879</v>
+        <v>0.7839391318357882</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.635541400731539</v>
+        <v>1.635541400731503</v>
       </c>
       <c r="AQ505" t="n">
         <v>88</v>
@@ -82933,10 +82933,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.705597066237454</v>
+        <v>6.705597066237452</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.02390275065707748</v>
+        <v>0.02390275065707925</v>
       </c>
       <c r="AK506" t="n">
         <v>6.74285285202661</v>
@@ -82945,16 +82945,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM506" t="n">
-        <v>-0.4015885003200582</v>
+        <v>-0.401588500320058</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.02985284499018428</v>
+        <v>0.02985284499018426</v>
       </c>
       <c r="AO506" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.443037887227141</v>
+        <v>1.443037887227161</v>
       </c>
       <c r="AQ506" t="n">
         <v>84.8</v>
@@ -83098,28 +83098,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.686024746022948</v>
+        <v>6.686024746022946</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.03647510138916132</v>
+        <v>0.0364751013891631</v>
       </c>
       <c r="AK507" t="n">
-        <v>6.744526329542679</v>
+        <v>6.744526329542678</v>
       </c>
       <c r="AL507" t="n">
-        <v>-0.02202648213056957</v>
+        <v>-0.02202648213056868</v>
       </c>
       <c r="AM507" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.02995529076246446</v>
+        <v>0.02995529076246445</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.7933293013213371</v>
+        <v>0.7933293013213367</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.566099953457549</v>
+        <v>1.566099953457567</v>
       </c>
       <c r="AQ507" t="n">
         <v>84.2</v>
@@ -83263,10 +83263,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.689653251437547</v>
+        <v>6.689653251437546</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.03134694311201347</v>
+        <v>0.03134694311201436</v>
       </c>
       <c r="AK508" t="n">
         <v>6.730402461316146</v>
@@ -83275,16 +83275,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3993041981056886</v>
+        <v>-0.3993041981056888</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03010093147709737</v>
+        <v>0.03010093147709741</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.7985853639949436</v>
+        <v>0.7985853639949437</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.507036858820233</v>
+        <v>1.507036858820243</v>
       </c>
       <c r="AQ508" t="n">
         <v>85</v>
@@ -83428,10 +83428,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.716786041117424</v>
+        <v>6.716786041117415</v>
       </c>
       <c r="AJ509" t="n">
-        <v>0.005113945149665788</v>
+        <v>0.00511394514967467</v>
       </c>
       <c r="AK509" t="n">
         <v>6.728106442363027</v>
@@ -83440,16 +83440,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM509" t="n">
-        <v>-0.3976134529492094</v>
+        <v>-0.3976134529492091</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03006044259180338</v>
+        <v>0.03006044259180324</v>
       </c>
       <c r="AO509" t="n">
-        <v>0.8026437279892848</v>
+        <v>0.8026437279892851</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.234777974751887</v>
+        <v>1.234777974751978</v>
       </c>
       <c r="AQ509" t="n">
         <v>81.59999999999999</v>
@@ -83593,10 +83593,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.72193279551444</v>
+        <v>6.721932795514441</v>
       </c>
       <c r="AJ510" t="n">
-        <v>-0.001632597913121536</v>
+        <v>-0.001632597913122424</v>
       </c>
       <c r="AK510" t="n">
         <v>6.752314636061016</v>
@@ -83608,13 +83608,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03043336917902487</v>
+        <v>0.03043336917902489</v>
       </c>
       <c r="AO510" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.163823515923099</v>
+        <v>1.163823515923089</v>
       </c>
       <c r="AQ510" t="n">
         <v>82.19999999999999</v>
@@ -83758,28 +83758,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.718669003366529</v>
+        <v>6.718669003366535</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.003830844045580761</v>
+        <v>0.003830844045574544</v>
       </c>
       <c r="AK511" t="n">
-        <v>6.750203856204786</v>
+        <v>6.750203856204787</v>
       </c>
       <c r="AL511" t="n">
-        <v>-0.02770400879267676</v>
+        <v>-0.02770400879267765</v>
       </c>
       <c r="AM511" t="n">
-        <v>-0.3969152632178359</v>
+        <v>-0.3969152632178358</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03100517332816427</v>
+        <v>0.03100517332816438</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8091236362457366</v>
+        <v>0.8091236362457368</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.217453571381111</v>
+        <v>1.217453571381047</v>
       </c>
       <c r="AQ511" t="n">
         <v>82.80000000000001</v>
@@ -83923,10 +83923,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.680190080689519</v>
+        <v>6.680190080689523</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.04230976672259068</v>
+        <v>0.04230976672258624</v>
       </c>
       <c r="AK512" t="n">
         <v>6.74780904069481</v>
@@ -83935,16 +83935,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM512" t="n">
-        <v>-0.3964565291282773</v>
+        <v>-0.3964565291282772</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03139664408873165</v>
+        <v>0.03139664408873172</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8123541153569371</v>
+        <v>0.8123541153569376</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.60449324842414</v>
+        <v>1.604493248424094</v>
       </c>
       <c r="AQ512" t="n">
         <v>89.8</v>
@@ -84088,10 +84088,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.671580974366949</v>
+        <v>6.671580974366952</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.05441885778637179</v>
+        <v>0.05441885778636824</v>
       </c>
       <c r="AK513" t="n">
         <v>6.701878095437348</v>
@@ -84103,13 +84103,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.03163116863423025</v>
+        <v>0.03163116863423027</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8147568654710426</v>
+        <v>0.8147568654710424</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.717274375116493</v>
+        <v>1.717274375116458</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.2</v>
@@ -84253,28 +84253,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI514" t="n">
-        <v>6.656216276126093</v>
+        <v>6.656216276126097</v>
       </c>
       <c r="AJ514" t="n">
-        <v>0.06978355602722708</v>
+        <v>0.06978355602722353</v>
       </c>
       <c r="AK514" t="n">
-        <v>6.701765808189925</v>
+        <v>6.701765808189924</v>
       </c>
       <c r="AL514" t="n">
-        <v>0.02423402396339558</v>
+        <v>0.02423402396339647</v>
       </c>
       <c r="AM514" t="n">
-        <v>-0.3932426568003567</v>
+        <v>-0.3932426568003564</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.03191273276172183</v>
+        <v>0.0319127327617218</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8170879052811416</v>
+        <v>0.8170879052811413</v>
       </c>
       <c r="AP514" t="n">
-        <v>1.858889534485378</v>
+        <v>1.858889534485343</v>
       </c>
       <c r="AQ514" t="n">
         <v>90.59999999999999</v>
@@ -84424,22 +84424,22 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK515" t="n">
-        <v>6.682658801267994</v>
+        <v>6.682658801267993</v>
       </c>
       <c r="AL515" t="n">
-        <v>0.03754126053010154</v>
+        <v>0.03754126053010243</v>
       </c>
       <c r="AM515" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN515" t="n">
-        <v>0.03225018457163047</v>
+        <v>0.03225018457163042</v>
       </c>
       <c r="AO515" t="n">
-        <v>0.8195353634242113</v>
+        <v>0.8195353634242114</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.818117584748586</v>
+        <v>1.818117584748587</v>
       </c>
       <c r="AQ515" t="n">
         <v>90.2</v>
@@ -84583,10 +84583,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.654231073451242</v>
+        <v>6.654231073451243</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.06476878921965668</v>
+        <v>0.06476878921965579</v>
       </c>
       <c r="AK516" t="n">
         <v>6.682840937292736</v>
@@ -84595,16 +84595,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM516" t="n">
-        <v>-0.3894836768645476</v>
+        <v>-0.3894836768645471</v>
       </c>
       <c r="AN516" t="n">
-        <v>0.03277193700354209</v>
+        <v>0.03277193700354208</v>
       </c>
       <c r="AO516" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.781104797300574</v>
+        <v>1.781104797300566</v>
       </c>
       <c r="AQ516" t="n">
         <v>90.2</v>
@@ -84748,10 +84748,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.650937329061552</v>
+        <v>6.650937329061554</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.06806253360934633</v>
+        <v>0.06806253360934456</v>
       </c>
       <c r="AK517" t="n">
         <v>6.698821600583909</v>
@@ -84760,16 +84760,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.3885003849593203</v>
+        <v>-0.3885003849593205</v>
       </c>
       <c r="AN517" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8264954348925952</v>
+        <v>0.8264954348925954</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.799874833536366</v>
+        <v>1.79987483353635</v>
       </c>
       <c r="AQ517" t="n">
         <v>91</v>
@@ -84913,10 +84913,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI518" t="n">
-        <v>6.651733245487366</v>
+        <v>6.651733245487365</v>
       </c>
       <c r="AJ518" t="n">
-        <v>0.05906692541107184</v>
+        <v>0.05906692541107272</v>
       </c>
       <c r="AK518" t="n">
         <v>6.69208631505748</v>
@@ -84925,16 +84925,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM518" t="n">
-        <v>-0.3869746098498528</v>
+        <v>-0.3869746098498524</v>
       </c>
       <c r="AN518" t="n">
-        <v>0.03441888977522091</v>
+        <v>0.0344188897752209</v>
       </c>
       <c r="AO518" t="n">
-        <v>0.8294137131605726</v>
+        <v>0.8294137131605728</v>
       </c>
       <c r="AP518" t="n">
-        <v>1.696616308981445</v>
+        <v>1.696616308981455</v>
       </c>
       <c r="AQ518" t="n">
         <v>90.40000000000001</v>
@@ -85078,10 +85078,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.632036771677475</v>
+        <v>6.632036771677474</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.07876339922096243</v>
+        <v>0.07876339922096331</v>
       </c>
       <c r="AK519" t="n">
         <v>6.692627206904497</v>
@@ -85099,7 +85099,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP519" t="n">
-        <v>1.875440190456845</v>
+        <v>1.875440190456855</v>
       </c>
       <c r="AQ519" t="n">
         <v>91</v>
@@ -85243,10 +85243,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI520" t="n">
-        <v>6.617259294346145</v>
+        <v>6.617259294346139</v>
       </c>
       <c r="AJ520" t="n">
-        <v>0.09324046914262496</v>
+        <v>0.09324046914263029</v>
       </c>
       <c r="AK520" t="n">
         <v>6.685306332307247</v>
@@ -85258,13 +85258,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03459091746240425</v>
+        <v>0.03459091746240417</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8328314813119078</v>
+        <v>0.8328314813119074</v>
       </c>
       <c r="AP520" t="n">
-        <v>1.998006000856694</v>
+        <v>1.998006000856746</v>
       </c>
       <c r="AQ520" t="n">
         <v>91</v>
@@ -85420,13 +85420,13 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM521" t="n">
-        <v>-0.3791985032227784</v>
+        <v>-0.379198503222778</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03468237364461172</v>
+        <v>0.03468237364461174</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8349203610870052</v>
+        <v>0.8349203610870053</v>
       </c>
       <c r="AP521" t="n">
         <v>2.317228225252931</v>
@@ -85588,10 +85588,10 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.0343742787852416</v>
+        <v>0.03437427878524163</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8337972329517072</v>
+        <v>0.8337972329517069</v>
       </c>
       <c r="AP522" t="n">
         <v>2.426255822246374</v>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41377,13 +41377,13 @@
         <v>-0.02946816111180972</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1084833265175429</v>
+        <v>0.1084833265175437</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002095078499053618</v>
+        <v>0.002095078499053615</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2731943305570398</v>
+        <v>0.2731943305570402</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41530,25 +41530,25 @@
         <v>0.04824898247695586</v>
       </c>
       <c r="AI255" t="n">
-        <v>7.163128638666564</v>
+        <v>7.163128638666562</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.02412869970171982</v>
+        <v>-0.02412869970171805</v>
       </c>
       <c r="AK255" t="n">
-        <v>7.169685517636702</v>
+        <v>7.169685517636701</v>
       </c>
       <c r="AL255" t="n">
-        <v>-0.03068557867185806</v>
+        <v>-0.03068557867185717</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.107056845533171</v>
+        <v>0.1070568455331707</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002204315292537673</v>
+        <v>0.002204315292537711</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2729110366374832</v>
+        <v>0.2729110366374826</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41695,10 +41695,10 @@
         <v>0.04139578206851535</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.159965220045757</v>
+        <v>7.159965220045755</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.01856535966367723</v>
+        <v>-0.01856535966367456</v>
       </c>
       <c r="AK256" t="n">
         <v>7.165514191511657</v>
@@ -41707,13 +41707,13 @@
         <v>-0.02411433112957706</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.1050285904128647</v>
+        <v>0.1050285904128648</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002321116913413412</v>
+        <v>0.002321116913413366</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2720155547682573</v>
+        <v>0.2720155547682577</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41860,10 +41860,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.150419484347116</v>
+        <v>7.150419484347115</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.009019623965035528</v>
+        <v>-0.00901962396503464</v>
       </c>
       <c r="AK257" t="n">
         <v>7.161074530187645</v>
@@ -41872,13 +41872,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.1029385549788083</v>
+        <v>0.102938554978808</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002436328878122382</v>
+        <v>0.002436328878122375</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2711996176877891</v>
+        <v>0.2711996176877889</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42025,10 +42025,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI258" t="n">
-        <v>7.148511457776028</v>
+        <v>7.14851145777603</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-0.01601128611465086</v>
+        <v>-0.01601128611465263</v>
       </c>
       <c r="AK258" t="n">
         <v>7.150963414761942</v>
@@ -42037,13 +42037,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.1011329645838851</v>
+        <v>0.1011329645838857</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.002517185580011447</v>
+        <v>0.002517185580011383</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2709113683260677</v>
+        <v>0.2709113683260674</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42202,13 +42202,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.09870181295186471</v>
+        <v>0.09870181295186436</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.002644711580562537</v>
+        <v>0.002644711580562605</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2704892730019304</v>
+        <v>0.2704892730019285</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42355,10 +42355,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI260" t="n">
-        <v>7.153772633426659</v>
+        <v>7.153772633426657</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-0.03287247931288917</v>
+        <v>-0.03287247931288739</v>
       </c>
       <c r="AK260" t="n">
         <v>7.154757231824306</v>
@@ -42367,13 +42367,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.09555831842873846</v>
+        <v>0.09555831842873888</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.002822832879878071</v>
+        <v>0.002822832879878049</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2697410008595936</v>
+        <v>0.2697410008595938</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42520,10 +42520,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.153331199414496</v>
+        <v>7.153331199414497</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.03263131690717191</v>
+        <v>-0.0326313169071728</v>
       </c>
       <c r="AK261" t="n">
         <v>7.15450652143491</v>
@@ -42532,13 +42532,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.0918844066524992</v>
+        <v>0.09188440665249918</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003041971996730133</v>
+        <v>0.003041971996730116</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2698098046976256</v>
+        <v>0.2698098046976254</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42685,10 +42685,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI262" t="n">
-        <v>7.156943148319592</v>
+        <v>7.15694314831959</v>
       </c>
       <c r="AJ262" t="n">
-        <v>-0.03854305142628167</v>
+        <v>-0.0385430514262799</v>
       </c>
       <c r="AK262" t="n">
         <v>7.154505434137821</v>
@@ -42697,13 +42697,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.08748497753913406</v>
+        <v>0.08748497753913362</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.003298336925509862</v>
+        <v>0.003298336925509857</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2682008942988235</v>
+        <v>0.2682008942988222</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42862,13 +42862,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM263" t="n">
-        <v>0.0824587084059305</v>
+        <v>0.08245870840593096</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.003602928090795432</v>
+        <v>0.003602928090795422</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2685806390401517</v>
+        <v>0.2685806390401518</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43030,10 +43030,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.003819541738581442</v>
+        <v>0.003819541738581439</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.2696768907787764</v>
+        <v>0.2696768907787754</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43180,10 +43180,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.154685377655177</v>
+        <v>7.154685377655176</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.04048526245131967</v>
+        <v>-0.04048526245131878</v>
       </c>
       <c r="AK265" t="n">
         <v>7.15808570026938</v>
@@ -43192,13 +43192,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.07200163454913491</v>
+        <v>0.07200163454913533</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.004193740708391541</v>
+        <v>0.004193740708391577</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.270116598814735</v>
+        <v>0.2701165988147326</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43345,10 +43345,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI266" t="n">
-        <v>7.158449213455076</v>
+        <v>7.158449213455078</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-0.05514911885058371</v>
+        <v>-0.05514911885058549</v>
       </c>
       <c r="AK266" t="n">
         <v>7.157644979270017</v>
@@ -43357,13 +43357,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.06676111471939408</v>
+        <v>0.06676111471939436</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.00450521933759436</v>
+        <v>0.004505219337594384</v>
       </c>
       <c r="AO266" t="n">
-        <v>0.2733976337163381</v>
+        <v>0.2733976337163387</v>
       </c>
       <c r="AP266" t="n">
         <v/>
@@ -43510,10 +43510,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.160761769069204</v>
+        <v>7.160761769069201</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04786198879576631</v>
+        <v>-0.04786198879576364</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159146249199162</v>
@@ -43522,10 +43522,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.06148465881746725</v>
+        <v>0.06148465881746766</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.004852471327681615</v>
+        <v>0.004852471327681566</v>
       </c>
       <c r="AO267" t="n">
         <v>0.2778048766368325</v>
@@ -43675,10 +43675,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI268" t="n">
-        <v>7.162478122158095</v>
+        <v>7.162478122158094</v>
       </c>
       <c r="AJ268" t="n">
-        <v>-0.04957834188465782</v>
+        <v>-0.04957834188465693</v>
       </c>
       <c r="AK268" t="n">
         <v>7.159578986975002</v>
@@ -43687,13 +43687,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.05582594297075769</v>
+        <v>0.05582594297075712</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.005234102211236422</v>
+        <v>0.005234102211236467</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.282448024375059</v>
+        <v>0.2824480243750598</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43852,13 +43852,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.04949165986049534</v>
+        <v>0.04949165986049463</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.005677665039252891</v>
+        <v>0.005677665039252918</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.2878618994559775</v>
+        <v>0.2878618994559794</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -44017,13 +44017,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.04287777011073584</v>
+        <v>0.04287777011073606</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.006155260602669632</v>
+        <v>0.006155260602669625</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.2948468705933219</v>
+        <v>0.2948468705933236</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44170,10 +44170,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.173971773133425</v>
+        <v>7.173971773133423</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.04247200582995792</v>
+        <v>-0.04247200582995614</v>
       </c>
       <c r="AK271" t="n">
         <v>7.159255388854645</v>
@@ -44182,13 +44182,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.0348694200966178</v>
+        <v>0.03486942009661778</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.006728155724408227</v>
+        <v>0.006728155724408201</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.304499875642397</v>
+        <v>0.3044998756423967</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44335,25 +44335,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.172030417300567</v>
+        <v>7.172030417300565</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.03823038754592822</v>
+        <v>-0.03823038754592645</v>
       </c>
       <c r="AK272" t="n">
-        <v>7.167062070913353</v>
+        <v>7.167062070913352</v>
       </c>
       <c r="AL272" t="n">
-        <v>-0.03326204115871434</v>
+        <v>-0.03326204115871345</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.03279550096037902</v>
+        <v>0.03279550096037874</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.006903991232239788</v>
+        <v>0.006903991232239758</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3170366335916601</v>
+        <v>0.3170366335916608</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44500,10 +44500,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.171236182927453</v>
+        <v>7.171236182927454</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.03843608069356641</v>
+        <v>-0.0384360806935673</v>
       </c>
       <c r="AK273" t="n">
         <v>7.16747443083108</v>
@@ -44512,13 +44512,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.02972414459983895</v>
+        <v>0.02972414459983913</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.007158147882858998</v>
+        <v>0.007158147882859</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3270754385893867</v>
+        <v>0.3270754385893863</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44665,10 +44665,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI274" t="n">
-        <v>7.170425137628191</v>
+        <v>7.170425137628194</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-0.05102511321412884</v>
+        <v>-0.0510251132141315</v>
       </c>
       <c r="AK274" t="n">
         <v>7.168373097443463</v>
@@ -44677,13 +44677,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.02657019411530269</v>
+        <v>0.02657019411530295</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.007420436972250415</v>
+        <v>0.007420436972250398</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3357224795973284</v>
+        <v>0.3357224795973281</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44842,13 +44842,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.02366886174665103</v>
+        <v>0.02366886174665165</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.007679120311627263</v>
+        <v>0.007679120311627231</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3450219581941938</v>
+        <v>0.345021958194194</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -44995,10 +44995,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI276" t="n">
-        <v>7.172249622131827</v>
+        <v>7.172249622131823</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-0.05324966409349674</v>
+        <v>-0.05324966409349319</v>
       </c>
       <c r="AK276" t="n">
         <v>7.167365057101177</v>
@@ -45007,13 +45007,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01956653131084185</v>
+        <v>0.01956653131084189</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008034860291676559</v>
+        <v>0.008034860291676519</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.3572033251592189</v>
+        <v>0.3572033251592186</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45160,10 +45160,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.171656420777024</v>
+        <v>7.171656420777023</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.05265646273869429</v>
+        <v>-0.0526564627386934</v>
       </c>
       <c r="AK277" t="n">
         <v>7.167567681415887</v>
@@ -45172,13 +45172,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM277" t="n">
-        <v>0.01638396088890769</v>
+        <v>0.0163839608889081</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.008326212487477964</v>
+        <v>0.008326212487477898</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.3674516177552961</v>
+        <v>0.3674516177552964</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45325,10 +45325,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI278" t="n">
-        <v>7.175289829564748</v>
+        <v>7.175289829564746</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-0.05628987152641773</v>
+        <v>-0.05628987152641596</v>
       </c>
       <c r="AK278" t="n">
         <v>7.167553154788029</v>
@@ -45337,13 +45337,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.01351198449095157</v>
+        <v>0.01351198449095179</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.008601682347582891</v>
+        <v>0.008601682347582911</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.3758646846617525</v>
+        <v>0.375864684661753</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45496,19 +45496,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK279" t="n">
-        <v>7.16746081477764</v>
+        <v>7.167460814777641</v>
       </c>
       <c r="AL279" t="n">
-        <v>-0.04846085673931011</v>
+        <v>-0.048460856739311</v>
       </c>
       <c r="AM279" t="n">
-        <v>0.01196199498966369</v>
+        <v>0.01196199498966377</v>
       </c>
       <c r="AN279" t="n">
-        <v>0.008797062853284063</v>
+        <v>0.008797062853284078</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.3847384959530242</v>
+        <v>0.3847384959530228</v>
       </c>
       <c r="AP279" t="n">
         <v/>
@@ -45816,10 +45816,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI281" t="n">
-        <v>7.189678003526525</v>
+        <v>7.189678003526526</v>
       </c>
       <c r="AJ281" t="n">
-        <v>-0.07117777082999144</v>
+        <v>-0.07117777082999321</v>
       </c>
       <c r="AK281" t="n">
         <v/>
@@ -45828,13 +45828,13 @@
         <v/>
       </c>
       <c r="AM281" t="n">
-        <v>0.007307555239791734</v>
+        <v>0.007307555239791735</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009236289154790337</v>
+        <v>0.009236289154790363</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.401039717356949</v>
+        <v>0.4010397173569483</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45981,10 +45981,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI282" t="n">
-        <v>7.183919177237467</v>
+        <v>7.183919177237466</v>
       </c>
       <c r="AJ282" t="n">
-        <v>-0.05641912001700788</v>
+        <v>-0.056419120017007</v>
       </c>
       <c r="AK282" t="n">
         <v>7.168706858585229</v>
@@ -45993,13 +45993,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.006573598200530942</v>
+        <v>0.006573598200531427</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009378157495070056</v>
+        <v>0.009378157495070007</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4093166892046883</v>
+        <v>0.4093166892046876</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46158,13 +46158,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.005719699928660468</v>
+        <v>0.00571969992866044</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009535855797507643</v>
+        <v>0.009535855797507651</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4189456552735356</v>
+        <v>0.4189456552735351</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46311,10 +46311,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI284" t="n">
-        <v>7.183803634757356</v>
+        <v>7.183803634757355</v>
       </c>
       <c r="AJ284" t="n">
-        <v>-0.08380373012478781</v>
+        <v>-0.08380373012478692</v>
       </c>
       <c r="AK284" t="n">
         <v>7.157754776965645</v>
@@ -46323,13 +46323,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.007205793377056199</v>
+        <v>0.007205793377055721</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.009541847058682544</v>
+        <v>0.00954184705868257</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4265135453780396</v>
+        <v>0.4265135453780416</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46482,19 +46482,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK285" t="n">
-        <v>7.153578345933642</v>
+        <v>7.153578345933643</v>
       </c>
       <c r="AL285" t="n">
-        <v>-0.01517826811381795</v>
+        <v>-0.01517826811381884</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.009937300636551308</v>
+        <v>0.009937300636551421</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.00947510825395563</v>
+        <v>0.009475108253955637</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.4359288044119884</v>
+        <v>0.4359288044119891</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46641,10 +46641,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI286" t="n">
-        <v>7.175374323571331</v>
+        <v>7.175374323571332</v>
       </c>
       <c r="AJ286" t="n">
-        <v>-0.04917412444413394</v>
+        <v>-0.04917412444413483</v>
       </c>
       <c r="AK286" t="n">
         <v>7.155226204999164</v>
@@ -46653,13 +46653,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01039951522374721</v>
+        <v>0.01039951522374727</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009534227083684284</v>
+        <v>0.009534227083684297</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.446224869246465</v>
+        <v>0.4462248692464653</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46818,13 +46818,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.01174445052819259</v>
+        <v>0.01174445052819296</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009539024405591096</v>
+        <v>0.009539024405591111</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4561706550234678</v>
+        <v>0.4561706550234662</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46971,10 +46971,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI288" t="n">
-        <v>7.176295466764674</v>
+        <v>7.176295466764673</v>
       </c>
       <c r="AJ288" t="n">
-        <v>-0.04989547286818929</v>
+        <v>-0.04989547286818841</v>
       </c>
       <c r="AK288" t="n">
         <v>7.150954883812801</v>
@@ -46983,13 +46983,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.01399948938427905</v>
+        <v>0.01399948938427885</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009474826008246758</v>
+        <v>0.009474826008246765</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.4654004237248369</v>
+        <v>0.4654004237248376</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47148,13 +47148,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM289" t="n">
-        <v>0.01676993900799729</v>
+        <v>0.01676993900799728</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.009377028877974699</v>
+        <v>0.00937702887797469</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.476700939638935</v>
+        <v>0.4767009396389351</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47316,10 +47316,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.009204864903404497</v>
+        <v>0.009204864903404482</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.4883841032893044</v>
+        <v>0.4883841032893032</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47478,13 +47478,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.02435543352765289</v>
+        <v>0.02435543352765317</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.009045821984022376</v>
+        <v>0.00904582198402234</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.4990078266507766</v>
+        <v>0.4990078266507749</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47631,10 +47631,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI292" t="n">
-        <v>7.175210595491395</v>
+        <v>7.175210595491394</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.04951059854315254</v>
+        <v>-0.04951059854315165</v>
       </c>
       <c r="AK292" t="n">
         <v>7.151444380572274</v>
@@ -47643,13 +47643,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.02840267381959001</v>
+        <v>0.02840267381959008</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008843610540066053</v>
+        <v>0.008843610540066056</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5123725312709416</v>
+        <v>0.5123725312709417</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47799,7 +47799,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.05177635201934994</v>
+        <v>-0.05177635201935082</v>
       </c>
       <c r="AK293" t="n">
         <v>7.151307469847429</v>
@@ -47808,13 +47808,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.03189518855892823</v>
+        <v>0.03189518855892809</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008740250954211215</v>
+        <v>0.008740250954211236</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.5303980242931245</v>
+        <v>0.5303980242931252</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47961,10 +47961,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI294" t="n">
-        <v>7.172173616645312</v>
+        <v>7.172173616645314</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.06197368836162021</v>
+        <v>-0.06197368836162287</v>
       </c>
       <c r="AK294" t="n">
         <v>7.152170779642037</v>
@@ -47973,13 +47973,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM294" t="n">
-        <v>0.03448417181877508</v>
+        <v>0.03448417181877479</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008638296330047493</v>
+        <v>0.008638296330047519</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.536400419244653</v>
+        <v>0.5364004192446541</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48129,7 +48129,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.08262387272163529</v>
+        <v>-0.08262387272163618</v>
       </c>
       <c r="AK295" t="n">
         <v>7.155242422656618</v>
@@ -48141,10 +48141,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008527848481957645</v>
+        <v>0.008527848481957647</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5479838817473677</v>
+        <v>0.5479838817473681</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48291,10 +48291,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.18418852599864</v>
+        <v>7.184188525998638</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.08518854888682359</v>
+        <v>-0.08518854888682181</v>
       </c>
       <c r="AK296" t="n">
         <v>7.174067278312125</v>
@@ -48303,13 +48303,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.03996026841105445</v>
+        <v>0.03996026841105382</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008497979041970659</v>
+        <v>0.008497979041970699</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.5534995516418705</v>
+        <v>0.553499551641869</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48456,10 +48456,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI297" t="n">
-        <v>7.185513015749276</v>
+        <v>7.185513015749274</v>
       </c>
       <c r="AJ297" t="n">
-        <v>-0.07571315384131694</v>
+        <v>-0.07571315384131516</v>
       </c>
       <c r="AK297" t="n">
         <v>7.175957423377739</v>
@@ -48468,13 +48468,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04233079818885077</v>
+        <v>0.04233079818885083</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008432709457890229</v>
+        <v>0.008432709457890224</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5557951014363787</v>
+        <v>0.5557951014363788</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48627,19 +48627,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK298" t="n">
-        <v>7.174765662541793</v>
+        <v>7.174765662541792</v>
       </c>
       <c r="AL298" t="n">
-        <v>-0.05786569534818931</v>
+        <v>-0.05786569534818842</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04394124299371591</v>
+        <v>0.04394124299371556</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008396387260434499</v>
+        <v>0.008396387260434506</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5565519909812464</v>
+        <v>0.5565519909812453</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48786,10 +48786,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI299" t="n">
-        <v>7.185932916622859</v>
+        <v>7.18593291662286</v>
       </c>
       <c r="AJ299" t="n">
-        <v>-0.0141327800566966</v>
+        <v>-0.01413278005669749</v>
       </c>
       <c r="AK299" t="n">
         <v>7.172730869790855</v>
@@ -48798,13 +48798,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04590755972499789</v>
+        <v>0.04590755972499803</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008346613473328282</v>
+        <v>0.008346613473328291</v>
       </c>
       <c r="AO299" t="n">
-        <v>0.5588443644440741</v>
+        <v>0.5588443644440755</v>
       </c>
       <c r="AP299" t="n">
         <v/>
@@ -48951,10 +48951,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI300" t="n">
-        <v>7.187602005018013</v>
+        <v>7.187602005018014</v>
       </c>
       <c r="AJ300" t="n">
-        <v>-0.05810209275604983</v>
+        <v>-0.0581020927560516</v>
       </c>
       <c r="AK300" t="n">
         <v>7.168923754586179</v>
@@ -48963,10 +48963,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.04658552832149703</v>
+        <v>0.04658552832149689</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008354655440128402</v>
+        <v>0.008354655440128426</v>
       </c>
       <c r="AO300" t="n">
         <v>0.5613325805619827</v>
@@ -49128,13 +49128,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.04820692510781933</v>
+        <v>0.04820692510781883</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008303818071592001</v>
+        <v>0.008303818071592054</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5626464255878519</v>
+        <v>0.5626464255878516</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49293,13 +49293,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.04983084886774743</v>
+        <v>0.04983084886774771</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008251024544031704</v>
+        <v>0.008251024544031682</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5641340630354328</v>
+        <v>0.5641340630354323</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49458,13 +49458,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05170461329917111</v>
+        <v>0.05170461329917048</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008192726391276807</v>
+        <v>0.008192726391276836</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5658195968244528</v>
+        <v>0.5658195968244545</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49623,13 +49623,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05348369580043773</v>
+        <v>0.05348369580043772</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008143044151838245</v>
+        <v>0.008143044151838252</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5671346874885959</v>
+        <v>0.5671346874885956</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49776,10 +49776,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.175179910580594</v>
+        <v>7.175179910580593</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.05588002196975417</v>
+        <v>-0.05588002196975328</v>
       </c>
       <c r="AK305" t="n">
         <v>7.165699812335961</v>
@@ -49788,13 +49788,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05520982564369371</v>
+        <v>0.0552098256436935</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008124788470663676</v>
+        <v>0.008124788470663643</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5701242576280907</v>
+        <v>0.5701242576280905</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49941,10 +49941,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.173581841712227</v>
+        <v>7.173581841712229</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.05428195310138761</v>
+        <v>-0.05428195310138939</v>
       </c>
       <c r="AK306" t="n">
         <v>7.162626578418298</v>
@@ -49953,13 +49953,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05644890839995315</v>
+        <v>0.05644890839995281</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.008105230252153435</v>
+        <v>0.008105230252153447</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.5713754740215509</v>
+        <v>0.5713754740215494</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50106,10 +50106,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.176011726611837</v>
+        <v>7.176011726611838</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.06401173805592908</v>
+        <v>-0.06401173805592997</v>
       </c>
       <c r="AK307" t="n">
         <v>7.165542054185019</v>
@@ -50118,13 +50118,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.05727663218544052</v>
+        <v>0.05727663218544039</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.00812403522652648</v>
+        <v>0.008124035226526509</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.573000414744258</v>
+        <v>0.5730004147442582</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50271,10 +50271,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.17698340522191</v>
+        <v>7.176983405221908</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.07778363334080662</v>
+        <v>-0.07778363334080485</v>
       </c>
       <c r="AK308" t="n">
         <v>7.170209849598846</v>
@@ -50283,13 +50283,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.05825580143844533</v>
+        <v>0.05825580143844532</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.008106527117828777</v>
+        <v>0.008106527117828759</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5728585525731363</v>
+        <v>0.5728585525731367</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50436,10 +50436,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.174841035863564</v>
+        <v>7.174841035863563</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.06734095956961905</v>
+        <v>-0.06734095956961816</v>
       </c>
       <c r="AK309" t="n">
         <v>7.166925629020364</v>
@@ -50448,13 +50448,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM309" t="n">
-        <v>0.05980113395910436</v>
+        <v>0.05980113395910441</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.008056914781095353</v>
+        <v>0.008056914781095341</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5723268395754473</v>
+        <v>0.5723268395754482</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50601,10 +50601,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.179777800337525</v>
+        <v>7.179777800337526</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.07227772404357946</v>
+        <v>-0.07227772404358035</v>
       </c>
       <c r="AK310" t="n">
         <v>7.163704513322672</v>
@@ -50616,10 +50616,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.008007544934860181</v>
+        <v>0.008007544934860184</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.5724055344141883</v>
+        <v>0.5724055344141876</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50766,10 +50766,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.176651545551679</v>
+        <v>7.176651545551677</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.06915146925773374</v>
+        <v>-0.06915146925773197</v>
       </c>
       <c r="AK311" t="n">
         <v>7.163430147298699</v>
@@ -50778,13 +50778,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06321929365037962</v>
+        <v>0.06321929365038026</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007927773212025854</v>
+        <v>0.007927773212025837</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.572463582881384</v>
+        <v>0.5724635828813827</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50931,10 +50931,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI312" t="n">
-        <v>7.173279688539583</v>
+        <v>7.173279688539582</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.06577961224563733</v>
+        <v>-0.06577961224563644</v>
       </c>
       <c r="AK312" t="n">
         <v>7.158871783064204</v>
@@ -50943,13 +50943,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.06523048259292186</v>
+        <v>0.0652304825929222</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007809540836127948</v>
+        <v>0.007809540836127932</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.5710090561291132</v>
+        <v>0.571009056129113</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51096,10 +51096,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI313" t="n">
-        <v>7.168542018724481</v>
+        <v>7.168542018724479</v>
       </c>
       <c r="AJ313" t="n">
-        <v>-0.06194221098522323</v>
+        <v>-0.06194221098522146</v>
       </c>
       <c r="AK313" t="n">
         <v>7.152618309751275</v>
@@ -51108,13 +51108,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.067411943409599</v>
+        <v>0.06741194340959927</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007660511838810988</v>
+        <v>0.007660511838810949</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5694124450603424</v>
+        <v>0.5694124450603408</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51261,10 +51261,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI314" t="n">
-        <v>7.161829635752616</v>
+        <v>7.161829635752617</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.05962960447209831</v>
+        <v>-0.0596296044720992</v>
       </c>
       <c r="AK314" t="n">
         <v>7.144956229005203</v>
@@ -51273,16 +51273,16 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.06977835201573312</v>
+        <v>0.06977835201573281</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.007516908058882096</v>
+        <v>0.007516908058882097</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5690369646398685</v>
+        <v>0.5690369646398684</v>
       </c>
       <c r="AP314" t="n">
-        <v>-0.4405932303088999</v>
+        <v>-0.4405932303089651</v>
       </c>
       <c r="AQ314" t="n">
         <v>17.5</v>
@@ -51429,7 +51429,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ315" t="n">
-        <v>-0.07699331565738099</v>
+        <v>-0.07699331565738188</v>
       </c>
       <c r="AK315" t="n">
         <v>7.140422114543136</v>
@@ -51438,16 +51438,16 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.07195366789421653</v>
+        <v>0.07195366789421676</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.007394117938767417</v>
+        <v>0.007394117938767422</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.5693040973288186</v>
+        <v>0.5693040973288199</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.401609825776575</v>
+        <v>-1.401609825776634</v>
       </c>
       <c r="AQ315" t="n">
         <v>5.737704918032787</v>
@@ -51603,16 +51603,16 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.07456301989532385</v>
+        <v>0.07456301989532414</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.007241314760732032</v>
+        <v>0.007241314760731996</v>
       </c>
       <c r="AO316" t="n">
         <v>0.5685877661607006</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.764925667104289</v>
+        <v>-1.764925667104294</v>
       </c>
       <c r="AQ316" t="n">
         <v>3.225806451612903</v>
@@ -51768,16 +51768,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.07747971887849656</v>
+        <v>0.07747971887849607</v>
       </c>
       <c r="AN317" t="n">
-        <v>0.0070901436555387</v>
+        <v>0.007090143655538702</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5681709745664083</v>
+        <v>0.5681709745664091</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.732708967932794</v>
+        <v>-1.732708967932799</v>
       </c>
       <c r="AQ317" t="n">
         <v>4.761904761904762</v>
@@ -51921,10 +51921,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.165084051386049</v>
+        <v>7.165084051386047</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.08998410631768916</v>
+        <v>-0.08998410631768738</v>
       </c>
       <c r="AK318" t="n">
         <v>7.14582045097363</v>
@@ -51933,16 +51933,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08000072584212846</v>
+        <v>0.08000072584212836</v>
       </c>
       <c r="AN318" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5684087510734981</v>
+        <v>0.5684087510734968</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.933309554770203</v>
+        <v>-1.933309554770118</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.34375</v>
@@ -52086,10 +52086,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.161419741275552</v>
+        <v>7.161419741275553</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.08971964514518138</v>
+        <v>-0.08971964514518227</v>
       </c>
       <c r="AK319" t="n">
         <v>7.155707108847959</v>
@@ -52098,16 +52098,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08204996863507508</v>
+        <v>0.08204996863507528</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006919462921967476</v>
+        <v>0.006919462921967468</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5672869954461468</v>
+        <v>0.5672869954461461</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.851973722066798</v>
+        <v>-1.85197372206685</v>
       </c>
       <c r="AQ319" t="n">
         <v>2.307692307692308</v>
@@ -52251,10 +52251,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.155488092579304</v>
+        <v>7.155488092579303</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.08548792091792734</v>
+        <v>-0.08548792091792645</v>
       </c>
       <c r="AK320" t="n">
         <v>7.150451326287159</v>
@@ -52263,16 +52263,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.08469403553214168</v>
+        <v>0.08469403553214211</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006815201188096393</v>
+        <v>0.006815201188096372</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5663505631396779</v>
+        <v>0.5663505631396781</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.58512377413815</v>
+        <v>-1.585123774138113</v>
       </c>
       <c r="AQ320" t="n">
         <v>3.787878787878788</v>
@@ -52416,10 +52416,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.158832817363979</v>
+        <v>7.15883281736398</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.09523275404000398</v>
+        <v>-0.09523275404000575</v>
       </c>
       <c r="AK321" t="n">
         <v>7.147115644271845</v>
@@ -52428,16 +52428,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.08699523504893081</v>
+        <v>0.08699523504893142</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006735083295172709</v>
+        <v>0.006735083295172689</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5654743012892969</v>
+        <v>0.5654743012892984</v>
       </c>
       <c r="AP321" t="n">
-        <v>-2.010469305142868</v>
+        <v>-2.010469305142959</v>
       </c>
       <c r="AQ321" t="n">
         <v>1.492537313432836</v>
@@ -52581,10 +52581,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.161703459649028</v>
+        <v>7.161703459649029</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.090303294091167</v>
+        <v>-0.09030329409116788</v>
       </c>
       <c r="AK322" t="n">
         <v>7.152131804583207</v>
@@ -52593,16 +52593,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.08901512474159551</v>
+        <v>0.08901512474159586</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006668288608758136</v>
+        <v>0.006668288608758129</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5631673144521659</v>
+        <v>0.5631673144521655</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.7086414961129</v>
+        <v>-1.708641496112943</v>
       </c>
       <c r="AQ322" t="n">
         <v>2.205882352941176</v>
@@ -52746,10 +52746,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.162535384813326</v>
+        <v>7.162535384813327</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.09293527952768166</v>
+        <v>-0.09293527952768255</v>
       </c>
       <c r="AK323" t="n">
         <v>7.157753883768605</v>
@@ -52758,16 +52758,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09116436352661951</v>
+        <v>0.09116436352661936</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006624805625172231</v>
+        <v>0.006624805625172246</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5612585549312774</v>
+        <v>0.5612585549312785</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.783048493172553</v>
+        <v>-1.783048493172593</v>
       </c>
       <c r="AQ323" t="n">
         <v>2.898550724637681</v>
@@ -52911,10 +52911,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.166818450294679</v>
+        <v>7.166818450294681</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.0958183511125501</v>
+        <v>-0.09581835111255188</v>
       </c>
       <c r="AK324" t="n">
         <v>7.158620349112049</v>
@@ -52923,16 +52923,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.09320704864741254</v>
+        <v>0.09320704864741212</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006594358041710158</v>
+        <v>0.006594358041710186</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5590514368572466</v>
+        <v>0.5590514368572459</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.861705890903985</v>
+        <v>-1.86170589090406</v>
       </c>
       <c r="AQ324" t="n">
         <v>1.428571428571429</v>
@@ -53076,10 +53076,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.157691007010206</v>
+        <v>7.157691007010208</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.0943908742587416</v>
+        <v>-0.09439087425874337</v>
       </c>
       <c r="AK325" t="n">
         <v>7.164942158928604</v>
@@ -53088,16 +53088,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.09491020692123933</v>
+        <v>0.09491020692123982</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006562900445417311</v>
+        <v>0.006562900445417306</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5551825155208145</v>
+        <v>0.5551825155208129</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.740893009303061</v>
+        <v>-1.740893009303131</v>
       </c>
       <c r="AQ325" t="n">
         <v>2.816901408450704</v>
@@ -53241,10 +53241,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI326" t="n">
-        <v>7.151776426431621</v>
+        <v>7.15177642643162</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.08777629673191356</v>
+        <v>-0.08777629673191267</v>
       </c>
       <c r="AK326" t="n">
         <v>7.154764404811184</v>
@@ -53253,16 +53253,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.097046810505102</v>
+        <v>0.0970468105051025</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006523984583215639</v>
+        <v>0.006523984583215632</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5522992358254805</v>
+        <v>0.5522992358254815</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.397254909158988</v>
+        <v>-1.397254909158938</v>
       </c>
       <c r="AQ326" t="n">
         <v>6.25</v>
@@ -53406,10 +53406,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI327" t="n">
-        <v>7.15099240431968</v>
+        <v>7.150992404319682</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.09309245238486596</v>
+        <v>-0.09309245238486774</v>
       </c>
       <c r="AK327" t="n">
         <v>7.150261540163492</v>
@@ -53418,16 +53418,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.09904197982498698</v>
+        <v>0.09904197982498671</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006505848878330736</v>
+        <v>0.006505848878330779</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5500699492277152</v>
+        <v>0.5500699492277157</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.606607962741622</v>
+        <v>-1.60660796274169</v>
       </c>
       <c r="AQ327" t="n">
         <v>4.10958904109589</v>
@@ -53571,10 +53571,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI328" t="n">
-        <v>7.147140093605204</v>
+        <v>7.147140093605207</v>
       </c>
       <c r="AJ328" t="n">
-        <v>-0.09314019278733277</v>
+        <v>-0.09314019278733543</v>
       </c>
       <c r="AK328" t="n">
         <v>7.148879230661717</v>
@@ -53583,16 +53583,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1013300516539148</v>
+        <v>0.1013300516539142</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006479631055951007</v>
+        <v>0.006479631055951091</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5478993564899665</v>
+        <v>0.5478993564899672</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.570470106078097</v>
+        <v>-1.5704701060782</v>
       </c>
       <c r="AQ328" t="n">
         <v>3.378378378378378</v>
@@ -53742,22 +53742,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK329" t="n">
-        <v>7.145816711184184</v>
+        <v>7.145816711184185</v>
       </c>
       <c r="AL329" t="n">
-        <v>-0.09881677984873516</v>
+        <v>-0.09881677984873605</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1033273874042088</v>
+        <v>0.1033273874042092</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006468712737497662</v>
+        <v>0.006468712737497656</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5455500876237902</v>
+        <v>0.5455500876237913</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.644458314609691</v>
+        <v>-1.644458314609671</v>
       </c>
       <c r="AQ329" t="n">
         <v>2</v>
@@ -53904,7 +53904,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.1028262052267701</v>
+        <v>-0.102826205226771</v>
       </c>
       <c r="AK330" t="n">
         <v>7.139092738717567</v>
@@ -53913,16 +53913,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.1056457020972507</v>
+        <v>0.1056457020972505</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006435041090934165</v>
+        <v>0.006435041090934217</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5433399026839665</v>
+        <v>0.5433399026839674</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.908944663479627</v>
+        <v>-1.908944663479643</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.631578947368421</v>
@@ -54069,7 +54069,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ331" t="n">
-        <v>-0.099096096614959</v>
+        <v>-0.09909609661495811</v>
       </c>
       <c r="AK331" t="n">
         <v>7.140479586010682</v>
@@ -54078,16 +54078,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.10768023901916</v>
+        <v>0.1076802390191602</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006405465077205547</v>
+        <v>0.006405465077205527</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5402459241219614</v>
+        <v>0.5402459241219618</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.697400237615767</v>
+        <v>-1.697400237615708</v>
       </c>
       <c r="AQ331" t="n">
         <v>2.597402597402597</v>
@@ -54231,10 +54231,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI332" t="n">
-        <v>7.145743344370562</v>
+        <v>7.145743344370558</v>
       </c>
       <c r="AJ332" t="n">
-        <v>-0.1052431803385794</v>
+        <v>-0.1052431803385758</v>
       </c>
       <c r="AK332" t="n">
         <v>7.136632587022158</v>
@@ -54243,16 +54243,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1100130126862077</v>
+        <v>0.1100130126862084</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006366554765990282</v>
+        <v>0.00636655476599019</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5375708073661647</v>
+        <v>0.5375708073661639</v>
       </c>
       <c r="AP332" t="n">
-        <v>-1.908750947691312</v>
+        <v>-1.908750947691146</v>
       </c>
       <c r="AQ332" t="n">
         <v>2.564102564102564</v>
@@ -54408,16 +54408,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1122475627674583</v>
+        <v>0.1122475627674581</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006337265512462553</v>
+        <v>0.00633726551246258</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5341613739773245</v>
+        <v>0.5341613739773232</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.583166329559663</v>
+        <v>-1.583166329559655</v>
       </c>
       <c r="AQ333" t="n">
         <v>3.164556962025316</v>
@@ -54561,10 +54561,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI334" t="n">
-        <v>7.142519733033009</v>
+        <v>7.14251973303301</v>
       </c>
       <c r="AJ334" t="n">
-        <v>-0.1016195026252946</v>
+        <v>-0.1016195026252955</v>
       </c>
       <c r="AK334" t="n">
         <v>7.135172643569136</v>
@@ -54573,16 +54573,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1146509166068179</v>
+        <v>0.114650916606818</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006337163869517243</v>
+        <v>0.006337163869517234</v>
       </c>
       <c r="AO334" t="n">
-        <v>0.5319767312874306</v>
+        <v>0.5319767312874311</v>
       </c>
       <c r="AP334" t="n">
-        <v>-1.672372608149145</v>
+        <v>-1.672372608149172</v>
       </c>
       <c r="AQ334" t="n">
         <v>2.5</v>
@@ -54738,16 +54738,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.1171965158426952</v>
+        <v>0.1171965158426948</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006367653503792481</v>
+        <v>0.00636765350379247</v>
       </c>
       <c r="AO335" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP335" t="n">
-        <v>-2.112865586535205</v>
+        <v>-2.112865586535191</v>
       </c>
       <c r="AQ335" t="n">
         <v>1.234567901234568</v>
@@ -54891,10 +54891,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.140851085964109</v>
+        <v>7.140851085964112</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1128512080344217</v>
+        <v>-0.1128512080344244</v>
       </c>
       <c r="AK336" t="n">
         <v>7.142783913375006</v>
@@ -54903,16 +54903,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM336" t="n">
-        <v>0.119227205240256</v>
+        <v>0.1192272052402563</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006383133038709798</v>
+        <v>0.00638313303870985</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5243060286247103</v>
+        <v>0.5243060286247104</v>
       </c>
       <c r="AP336" t="n">
-        <v>-2.00865389805376</v>
+        <v>-2.008653898053848</v>
       </c>
       <c r="AQ336" t="n">
         <v>2.439024390243902</v>
@@ -55056,10 +55056,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.139245392969567</v>
+        <v>7.139245392969565</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.1112455150398795</v>
+        <v>-0.1112455150398777</v>
       </c>
       <c r="AK337" t="n">
         <v>7.141836927013541</v>
@@ -55068,16 +55068,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1211746327267789</v>
+        <v>0.1211746327267792</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006404909068509476</v>
+        <v>0.006404909068509461</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.5185318197199045</v>
+        <v>0.518531819719905</v>
       </c>
       <c r="AP337" t="n">
-        <v>-1.888782075973682</v>
+        <v>-1.888782075973597</v>
       </c>
       <c r="AQ337" t="n">
         <v>3.614457831325301</v>
@@ -55221,10 +55221,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI338" t="n">
-        <v>7.136520216281903</v>
+        <v>7.136520216281902</v>
       </c>
       <c r="AJ338" t="n">
-        <v>-0.108520338352216</v>
+        <v>-0.1085203383522142</v>
       </c>
       <c r="AK338" t="n">
         <v>7.13958125183462</v>
@@ -55233,16 +55233,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM338" t="n">
-        <v>0.1228335954516147</v>
+        <v>0.1228335954516143</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006430223802628449</v>
+        <v>0.006430223802628476</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.5122974965428477</v>
+        <v>0.5122974965428486</v>
       </c>
       <c r="AP338" t="n">
-        <v>-1.736494972713637</v>
+        <v>-1.736494972713559</v>
       </c>
       <c r="AQ338" t="n">
         <v>4.761904761904762</v>
@@ -55401,13 +55401,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006430805642792636</v>
+        <v>0.006430805642792618</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.5056597011855208</v>
+        <v>0.5056597011855207</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.470659774605434</v>
+        <v>-2.470659774605421</v>
       </c>
       <c r="AQ339" t="n">
         <v>1.176470588235294</v>
@@ -55551,10 +55551,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.136562857934749</v>
+        <v>7.13656285793475</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.140462909051692</v>
+        <v>-0.1404629090516929</v>
       </c>
       <c r="AK340" t="n">
         <v>7.132705938528055</v>
@@ -55566,13 +55566,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006419568115912044</v>
+        <v>0.006419568115912051</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.4979995576252224</v>
+        <v>0.4979995576252233</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.727207985371637</v>
+        <v>-2.727207985371653</v>
       </c>
       <c r="AQ340" t="n">
         <v>1.162790697674419</v>
@@ -55716,10 +55716,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.135435320996258</v>
+        <v>7.135435320996254</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1393353721132016</v>
+        <v>-0.1393353721131971</v>
       </c>
       <c r="AK341" t="n">
         <v>7.134470034900207</v>
@@ -55728,16 +55728,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1290155516631957</v>
+        <v>0.1290155516631951</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006423940675024581</v>
+        <v>0.006423940675024553</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.489456156051701</v>
+        <v>0.4894561560517011</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.565086807497531</v>
+        <v>-2.565086807497373</v>
       </c>
       <c r="AQ341" t="n">
         <v>2.873563218390804</v>
@@ -55881,10 +55881,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI342" t="n">
-        <v>7.135221482968309</v>
+        <v>7.135221482968312</v>
       </c>
       <c r="AJ342" t="n">
-        <v>-0.1391215340852527</v>
+        <v>-0.1391215340852554</v>
       </c>
       <c r="AK342" t="n">
         <v>7.133435115388912</v>
@@ -55893,16 +55893,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1313692321875789</v>
+        <v>0.1313692321875792</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006422605647444513</v>
+        <v>0.006422605647444502</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4811392039904447</v>
+        <v>0.4811392039904442</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.452561988903807</v>
+        <v>-2.452561988903891</v>
       </c>
       <c r="AQ342" t="n">
         <v>3.977272727272728</v>
@@ -56046,10 +56046,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI343" t="n">
-        <v>7.129120131622726</v>
+        <v>7.129120131622732</v>
       </c>
       <c r="AJ343" t="n">
-        <v>-0.1360199653019256</v>
+        <v>-0.1360199653019309</v>
       </c>
       <c r="AK343" t="n">
         <v>7.132510325395203</v>
@@ -56058,16 +56058,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1334873867685099</v>
+        <v>0.1334873867685108</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006388619079873509</v>
+        <v>0.006388619079873553</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4724960612931043</v>
+        <v>0.4724960612931048</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.263088388410052</v>
+        <v>-2.263088388410211</v>
       </c>
       <c r="AQ343" t="n">
         <v>5.056179775280899</v>
@@ -56223,16 +56223,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1357975915367747</v>
+        <v>0.1357975915367741</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.006324213907675097</v>
+        <v>0.006324213907675122</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4647750649852552</v>
+        <v>0.4647750649852558</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.339494277788878</v>
+        <v>-2.339494277788859</v>
       </c>
       <c r="AQ344" t="n">
         <v>2.777777777777778</v>
@@ -56376,10 +56376,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI345" t="n">
-        <v>7.122818285283529</v>
+        <v>7.122818285283532</v>
       </c>
       <c r="AJ345" t="n">
-        <v>-0.1394184172720543</v>
+        <v>-0.1394184172720578</v>
       </c>
       <c r="AK345" t="n">
         <v>7.123271418608565</v>
@@ -56388,16 +56388,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1386638579210687</v>
+        <v>0.1386638579210689</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.006222091828703702</v>
+        <v>0.006222091828703747</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4565264017486783</v>
+        <v>0.4565264017486775</v>
       </c>
       <c r="AP345" t="n">
-        <v>-2.212855822565158</v>
+        <v>-2.212855822565248</v>
       </c>
       <c r="AQ345" t="n">
         <v>3.846153846153847</v>
@@ -56553,16 +56553,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM346" t="n">
-        <v>0.1423176752089984</v>
+        <v>0.1423176752089981</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.006093783709292283</v>
+        <v>0.006093783709292289</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4497199830569224</v>
+        <v>0.4497199830569214</v>
       </c>
       <c r="AP346" t="n">
-        <v>-1.839621473354158</v>
+        <v>-1.839621473354138</v>
       </c>
       <c r="AQ346" t="n">
         <v>8.695652173913043</v>
@@ -56706,10 +56706,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.133160404869088</v>
+        <v>7.13316040486909</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1496604010543905</v>
+        <v>-0.1496604010543923</v>
       </c>
       <c r="AK347" t="n">
         <v>7.117219286120759</v>
@@ -56721,13 +56721,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005984113522022494</v>
+        <v>0.005984113522022499</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4438783751010233</v>
+        <v>0.4438783751010228</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.393245268221414</v>
+        <v>-2.393245268221441</v>
       </c>
       <c r="AQ347" t="n">
         <v>7.526881720430107</v>
@@ -56871,10 +56871,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.12965322071209</v>
+        <v>7.129653220712091</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1524531894315722</v>
+        <v>-0.152453189431573</v>
       </c>
       <c r="AK348" t="n">
         <v>7.126254605494273</v>
@@ -56883,16 +56883,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1503893187551748</v>
+        <v>0.1503893187551739</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005963146506628741</v>
+        <v>0.005963146506628762</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4412018736247373</v>
+        <v>0.441201873624737</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.388213882432259</v>
+        <v>-2.388213882432258</v>
       </c>
       <c r="AQ348" t="n">
         <v>7.446808510638299</v>
@@ -57036,10 +57036,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.128380415829728</v>
+        <v>7.128380415829729</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1552802304354408</v>
+        <v>-0.1552802304354417</v>
       </c>
       <c r="AK349" t="n">
         <v>7.124321202568002</v>
@@ -57048,16 +57048,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1546287435667592</v>
+        <v>0.1546287435667593</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.005975981199024843</v>
+        <v>0.005975981199024824</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4385827444686599</v>
+        <v>0.43858274446866</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.383472938167511</v>
+        <v>-2.383472938167509</v>
       </c>
       <c r="AQ349" t="n">
         <v>7.36842105263158</v>
@@ -57201,10 +57201,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI350" t="n">
-        <v>7.124429161493117</v>
+        <v>7.124429161493114</v>
       </c>
       <c r="AJ350" t="n">
-        <v>-0.1469291996400894</v>
+        <v>-0.1469291996400868</v>
       </c>
       <c r="AK350" t="n">
         <v>7.121152072356459</v>
@@ -57213,16 +57213,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1587808126513012</v>
+        <v>0.1587808126513008</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.00589922161993145</v>
+        <v>0.005899221619931436</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.4336499747757657</v>
+        <v>0.4336499747757655</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.079767923589242</v>
+        <v>-2.079767923589147</v>
       </c>
       <c r="AQ350" t="n">
         <v>15.625</v>
@@ -57378,16 +57378,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1636493008978488</v>
+        <v>0.1636493008978486</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.005897856672615054</v>
+        <v>0.005897856672615022</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.434304834398872</v>
+        <v>0.4343048343988722</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.389525538660947</v>
+        <v>-2.389525538660926</v>
       </c>
       <c r="AQ351" t="n">
         <v>13.4020618556701</v>
@@ -57531,10 +57531,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.141397967314147</v>
+        <v>7.141397967314151</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1753978872055049</v>
+        <v>-0.1753978872055084</v>
       </c>
       <c r="AK352" t="n">
         <v>7.12802266215534</v>
@@ -57543,16 +57543,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1676675897666615</v>
+        <v>0.1676675897666616</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.005952601612807557</v>
+        <v>0.005952601612807589</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4322693842687806</v>
+        <v>0.4322693842687804</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.675191840285986</v>
+        <v>-2.675191840286052</v>
       </c>
       <c r="AQ352" t="n">
         <v>12.24489795918367</v>
@@ -57696,10 +57696,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.140412492855504</v>
+        <v>7.140412492855501</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.1723124219021352</v>
+        <v>-0.1723124219021317</v>
       </c>
       <c r="AK353" t="n">
         <v>7.137738577466652</v>
@@ -57708,16 +57708,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.1710383543493657</v>
+        <v>0.1710383543493662</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.006068444256835448</v>
+        <v>0.00606844425683546</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4285062718639565</v>
+        <v>0.4285062718639572</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.494973402314948</v>
+        <v>-2.494973402314836</v>
       </c>
       <c r="AQ353" t="n">
         <v>19.19191919191919</v>
@@ -57861,10 +57861,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.138020503721587</v>
+        <v>7.138020503721584</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.169920432768218</v>
+        <v>-0.1699204327682153</v>
       </c>
       <c r="AK354" t="n">
         <v>7.13663078035759</v>
@@ -57873,16 +57873,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.176195682434215</v>
+        <v>0.1761956824342154</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.006402952059750722</v>
+        <v>0.006402952059750703</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4374093872433962</v>
+        <v>0.4374093872433956</v>
       </c>
       <c r="AP354" t="n">
-        <v>-2.351019822312725</v>
+        <v>-2.351019822312645</v>
       </c>
       <c r="AQ354" t="n">
         <v>19</v>
@@ -58026,28 +58026,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI355" t="n">
-        <v>7.136830620687384</v>
+        <v>7.136830620687383</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1769307183436339</v>
+        <v>-0.1769307183436331</v>
       </c>
       <c r="AK355" t="n">
-        <v>7.14004901784002</v>
+        <v>7.140049017840021</v>
       </c>
       <c r="AL355" t="n">
-        <v>-0.1801491154962704</v>
+        <v>-0.1801491154962713</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1796308914905975</v>
+        <v>0.1796308914905974</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.006948414844703821</v>
+        <v>0.006948414844703805</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4458727441769479</v>
+        <v>0.4458727441769483</v>
       </c>
       <c r="AP355" t="n">
-        <v>-2.440918439430029</v>
+        <v>-2.440918439429997</v>
       </c>
       <c r="AQ355" t="n">
         <v>17.32673267326733</v>
@@ -58187,10 +58187,10 @@
         <v/>
       </c>
       <c r="AI356" t="n">
-        <v>7.133638579266565</v>
+        <v>7.13363857926656</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1699387616090942</v>
+        <v>-0.1699387616090897</v>
       </c>
       <c r="AK356" t="n">
         <v>7.13798584867198</v>
@@ -58199,16 +58199,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1829391475229931</v>
+        <v>0.1829391475229935</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.007602047321544403</v>
+        <v>0.00760204732154433</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4545618931940824</v>
+        <v>0.4545618931940826</v>
       </c>
       <c r="AP356" t="n">
-        <v>-2.200405813749908</v>
+        <v>-2.200405813749797</v>
       </c>
       <c r="AQ356" t="n">
         <v>26.96078431372549</v>
@@ -58352,10 +58352,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI357" t="n">
-        <v>7.12640946890857</v>
+        <v>7.126409468908567</v>
       </c>
       <c r="AJ357" t="n">
-        <v>-0.1538094856932375</v>
+        <v>-0.1538094856932348</v>
       </c>
       <c r="AK357" t="n">
         <v>7.138565167526504</v>
@@ -58364,16 +58364,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1834764543657148</v>
+        <v>0.1834764543657157</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.007712839302340374</v>
+        <v>0.007712839302340297</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4511257152112026</v>
+        <v>0.4511257152112024</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.769646277064527</v>
+        <v>-1.769646277064464</v>
       </c>
       <c r="AQ357" t="n">
         <v>22.02075004759185</v>
@@ -58517,10 +58517,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI358" t="n">
-        <v>7.110999512759045</v>
+        <v>7.110999512759042</v>
       </c>
       <c r="AJ358" t="n">
-        <v>-0.1383995295437126</v>
+        <v>-0.1383995295437099</v>
       </c>
       <c r="AK358" t="n">
         <v>7.137040595974374</v>
@@ -58529,16 +58529,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.1869739626316104</v>
+        <v>0.1869739626316108</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.00835460951998479</v>
+        <v>0.008354609519984808</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4618871834350119</v>
+        <v>0.4618871834350127</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.377633656933903</v>
+        <v>-1.377633656933842</v>
       </c>
       <c r="AQ358" t="n">
         <v>16.42550410754294</v>
@@ -58694,16 +58694,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.1901371272406391</v>
+        <v>0.1901371272406383</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.008787529863310189</v>
+        <v>0.008787529863310259</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4631528842621211</v>
+        <v>0.4631528842621208</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.413967751523643</v>
+        <v>-1.413967751523646</v>
       </c>
       <c r="AQ359" t="n">
         <v>10.03663003663004</v>
@@ -58847,10 +58847,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI360" t="n">
-        <v>7.10229338126412</v>
+        <v>7.102293381264122</v>
       </c>
       <c r="AJ360" t="n">
-        <v>-0.1477931828998624</v>
+        <v>-0.1477931828998642</v>
       </c>
       <c r="AK360" t="n">
         <v>7.113436809075056</v>
@@ -58859,16 +58859,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.1939456835457532</v>
+        <v>0.193945683545753</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.009306466714917722</v>
+        <v>0.009306466714917755</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4650211967660294</v>
+        <v>0.4650211967660295</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.556195774880458</v>
+        <v>-1.556195774880501</v>
       </c>
       <c r="AQ360" t="n">
         <v>10.90296495956873</v>
@@ -59024,16 +59024,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.1968971496416331</v>
+        <v>0.1968971496416338</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.009915270508004642</v>
+        <v>0.009915270508004639</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4658112293095933</v>
+        <v>0.4658112293095935</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.332466214895518</v>
+        <v>-1.332466214895519</v>
       </c>
       <c r="AQ361" t="n">
         <v>11.24140363251631</v>
@@ -59189,16 +59189,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2001574773810679</v>
+        <v>0.200157477381068</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01045224758824684</v>
+        <v>0.01045224758824685</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4652001227613064</v>
+        <v>0.4652001227613058</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.593977891557414</v>
+        <v>-1.593977891557415</v>
       </c>
       <c r="AQ362" t="n">
         <v>5.096919349255798</v>
@@ -59342,10 +59342,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI363" t="n">
-        <v>7.112155432918446</v>
+        <v>7.112155432918444</v>
       </c>
       <c r="AJ363" t="n">
-        <v>-0.1611552192953987</v>
+        <v>-0.1611552192953969</v>
       </c>
       <c r="AK363" t="n">
         <v>7.115439870473561</v>
@@ -59354,16 +59354,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2059164257597553</v>
+        <v>0.2059164257597547</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01095806236007055</v>
+        <v>0.0109580623600705</v>
       </c>
       <c r="AO363" t="n">
-        <v>0.4647071558511969</v>
+        <v>0.4647071558511972</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.789779639197605</v>
+        <v>-1.789779639197566</v>
       </c>
       <c r="AQ363" t="n">
         <v>6.455997281685355</v>
@@ -59519,16 +59519,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2103846028094628</v>
+        <v>0.2103846028094625</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01138655624224677</v>
+        <v>0.01138655624224671</v>
       </c>
       <c r="AO364" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.817649544165022</v>
+        <v>-1.817649544165025</v>
       </c>
       <c r="AQ364" t="n">
         <v>10.98415346121768</v>
@@ -59672,10 +59672,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI365" t="n">
-        <v>7.110775793344653</v>
+        <v>7.110775793344654</v>
       </c>
       <c r="AJ365" t="n">
-        <v>-0.1730759985753663</v>
+        <v>-0.1730759985753672</v>
       </c>
       <c r="AK365" t="n">
         <v>7.127056499711662</v>
@@ -59684,16 +59684,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2137349114935569</v>
+        <v>0.2137349114935566</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01184277521890661</v>
+        <v>0.0118427752189066</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4573024605378193</v>
+        <v>0.4573024605378192</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.982092372266651</v>
+        <v>-1.982092372266673</v>
       </c>
       <c r="AQ365" t="n">
         <v>12.26044226044226</v>
@@ -59849,16 +59849,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2192999169256238</v>
+        <v>0.2192999169256231</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01242692746354282</v>
+        <v>0.01242692746354283</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4593518446085588</v>
+        <v>0.4593518446085587</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.541667257522195</v>
+        <v>-1.541667257522197</v>
       </c>
       <c r="AQ366" t="n">
         <v>13.91972329472329</v>
@@ -60002,28 +60002,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.095070446253633</v>
+        <v>7.095070446253632</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1572705156811232</v>
+        <v>-0.1572705156811223</v>
       </c>
       <c r="AK367" t="n">
-        <v>7.099084322920755</v>
+        <v>7.099084322920754</v>
       </c>
       <c r="AL367" t="n">
-        <v>-0.1612843923482448</v>
+        <v>-0.1612843923482439</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2273791016644669</v>
+        <v>0.2273791016644665</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01301934706839999</v>
+        <v>0.01301934706840001</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4655241261491886</v>
+        <v>0.4655241261491888</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.574345528037892</v>
+        <v>-1.574345528037874</v>
       </c>
       <c r="AQ367" t="n">
         <v>12.01406447534766</v>
@@ -60167,10 +60167,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.077412848446851</v>
+        <v>7.077412848446856</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1386129903535895</v>
+        <v>-0.138612990353594</v>
       </c>
       <c r="AK368" t="n">
         <v>7.107752072150756</v>
@@ -60179,16 +60179,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2346680713248289</v>
+        <v>0.2346680713248287</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01366280940279216</v>
+        <v>0.01366280940279221</v>
       </c>
       <c r="AO368" t="n">
-        <v>0.4682122340216202</v>
+        <v>0.4682122340216205</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.144790164634094</v>
+        <v>-1.144790164634194</v>
       </c>
       <c r="AQ368" t="n">
         <v>19.36811054184133</v>
@@ -60332,10 +60332,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.067855559671527</v>
+        <v>7.067855559671529</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1458556283360775</v>
+        <v>-0.1458556283360801</v>
       </c>
       <c r="AK369" t="n">
         <v>7.100856094477853</v>
@@ -60344,16 +60344,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2404731763378842</v>
+        <v>0.2404731763378833</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01427110593278799</v>
+        <v>0.01427110593278805</v>
       </c>
       <c r="AO369" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.291445978779248</v>
+        <v>-1.291445978779306</v>
       </c>
       <c r="AQ369" t="n">
         <v>18.78718535469108</v>
@@ -60497,10 +60497,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.081794385763164</v>
+        <v>7.081794385763168</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1711942003688769</v>
+        <v>-0.1711942003688813</v>
       </c>
       <c r="AK370" t="n">
         <v>7.090764621929079</v>
@@ -60509,16 +60509,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2453259423721931</v>
+        <v>0.2453259423721924</v>
       </c>
       <c r="AN370" t="n">
-        <v>0.01502424352484369</v>
+        <v>0.01502424352484376</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4756424387980298</v>
+        <v>0.4756424387980304</v>
       </c>
       <c r="AP370" t="n">
-        <v>-1.821236982629511</v>
+        <v>-1.821236982629602</v>
       </c>
       <c r="AQ370" t="n">
         <v>15.19865067466267</v>
@@ -60662,10 +60662,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.068234493406102</v>
+        <v>7.068234493406101</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1557345887735337</v>
+        <v>-0.1557345887735329</v>
       </c>
       <c r="AK371" t="n">
         <v>7.110983013755962</v>
@@ -60674,16 +60674,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2481172514763508</v>
+        <v>0.2481172514763511</v>
       </c>
       <c r="AN371" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.4781214750573159</v>
+        <v>0.4781214750573156</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.460178349064784</v>
+        <v>-1.46017834906476</v>
       </c>
       <c r="AQ371" t="n">
         <v>18.92130857648099</v>
@@ -60827,28 +60827,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.047011693433886</v>
+        <v>7.04701169343388</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.1469114622632315</v>
+        <v>-0.1469114622632253</v>
       </c>
       <c r="AK372" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1936362268489642</v>
+        <v>-0.1936362268489633</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2517176519946896</v>
+        <v>0.2517176519946887</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01672959897123732</v>
+        <v>0.01672959897123727</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.482044795280705</v>
+        <v>0.4820447952807055</v>
       </c>
       <c r="AP372" t="n">
-        <v>-1.252621156666182</v>
+        <v>-1.252621156666045</v>
       </c>
       <c r="AQ372" t="n">
         <v>18.30001448645517</v>
@@ -60992,28 +60992,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.043635211714482</v>
+        <v>7.043635211714486</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.135635219343877</v>
+        <v>-0.1356352193438806</v>
       </c>
       <c r="AK373" t="n">
-        <v>7.069112439760902</v>
+        <v>7.069112439760901</v>
       </c>
       <c r="AL373" t="n">
-        <v>-0.1611124473902965</v>
+        <v>-0.1611124473902956</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2568291528619773</v>
+        <v>0.2568291528619769</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.01758784222749221</v>
+        <v>0.0175878422274923</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.4888256589627545</v>
+        <v>0.488825658962754</v>
       </c>
       <c r="AP373" t="n">
-        <v>-0.9972661263733498</v>
+        <v>-0.9972661263734258</v>
       </c>
       <c r="AQ373" t="n">
         <v>23.6113089303518</v>
@@ -61157,10 +61157,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.045320696769622</v>
+        <v>7.04532069676962</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1373207043990163</v>
+        <v>-0.1373207043990146</v>
       </c>
       <c r="AK374" t="n">
         <v>7.067486653848666</v>
@@ -61169,16 +61169,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2611441025487395</v>
+        <v>0.2611441025487396</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.01863884916361525</v>
+        <v>0.01863884916361523</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.4958891106408185</v>
+        <v>0.4958891106408189</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.025289911488995</v>
+        <v>-1.025289911488955</v>
       </c>
       <c r="AQ374" t="n">
         <v>21.31652661064426</v>
@@ -61322,10 +61322,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI375" t="n">
-        <v>7.052957186540217</v>
+        <v>7.052957186540212</v>
       </c>
       <c r="AJ375" t="n">
-        <v>-0.1449571941696117</v>
+        <v>-0.1449571941696064</v>
       </c>
       <c r="AK375" t="n">
         <v>7.066060765041626</v>
@@ -61334,16 +61334,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM375" t="n">
-        <v>0.2646928033319798</v>
+        <v>0.2646928033319788</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.01961447184998982</v>
+        <v>0.0196144718499898</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.4990325267638059</v>
+        <v>0.4990325267638065</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.180573654908724</v>
+        <v>-1.180573654908609</v>
       </c>
       <c r="AQ375" t="n">
         <v>18.67079889807162</v>
@@ -61487,28 +61487,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.055218091951101</v>
+        <v>7.055218091951103</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1472180995804955</v>
+        <v>-0.1472180995804973</v>
       </c>
       <c r="AK376" t="n">
-        <v>7.064646745753511</v>
+        <v>7.06464674575351</v>
       </c>
       <c r="AL376" t="n">
-        <v>-0.1566467533829057</v>
+        <v>-0.1566467533829048</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2692457951306195</v>
+        <v>0.2692457951306194</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02045122459205889</v>
+        <v>0.02045122459205891</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5009265659871953</v>
+        <v>0.5009265659871951</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.217381411470178</v>
+        <v>-1.217381411470217</v>
       </c>
       <c r="AQ376" t="n">
         <v>17.70085354288037</v>
@@ -61652,10 +61652,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI377" t="n">
-        <v>7.050463258619342</v>
+        <v>7.050463258619345</v>
       </c>
       <c r="AJ377" t="n">
-        <v>-0.1423631304455135</v>
+        <v>-0.1423631304455171</v>
       </c>
       <c r="AK377" t="n">
         <v>7.063274589921972</v>
@@ -61664,16 +61664,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM377" t="n">
-        <v>0.2738618637550985</v>
+        <v>0.2738618637550991</v>
       </c>
       <c r="AN377" t="n">
-        <v>0.02103732430364852</v>
+        <v>0.02103732430364855</v>
       </c>
       <c r="AO377" t="n">
-        <v>0.5007948901071727</v>
+        <v>0.5007948901071723</v>
       </c>
       <c r="AP377" t="n">
-        <v>-1.101457435093465</v>
+        <v>-1.101457435093542</v>
       </c>
       <c r="AQ377" t="n">
         <v>22.04784752765561</v>
@@ -61990,16 +61990,16 @@
         <v/>
       </c>
       <c r="AM379" t="n">
-        <v>0.280344119587675</v>
+        <v>0.2803441195876753</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02230845224183686</v>
+        <v>0.02230845224183688</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5036776407221306</v>
+        <v>0.5036776407221312</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.253596032660394</v>
+        <v>-1.253596032660393</v>
       </c>
       <c r="AQ379" t="n">
         <v>24.19354838709677</v>
@@ -62143,10 +62143,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.056824809597053</v>
+        <v>7.056824809597052</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.1737247767906567</v>
+        <v>-0.1737247767906558</v>
       </c>
       <c r="AK380" t="n">
         <v>7.071238163852278</v>
@@ -62155,16 +62155,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2841407798055449</v>
+        <v>0.2841407798055452</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02276542233315987</v>
+        <v>0.02276542233315985</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5036956996297977</v>
+        <v>0.5036956996297983</v>
       </c>
       <c r="AP380" t="n">
-        <v>-1.741339932678348</v>
+        <v>-1.741339932678327</v>
       </c>
       <c r="AQ380" t="n">
         <v>21.2</v>
@@ -62308,10 +62308,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.04726592259491</v>
+        <v>7.047265922594908</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.1780656929501347</v>
+        <v>-0.178065692950133</v>
       </c>
       <c r="AK381" t="n">
         <v>7.075283303194255</v>
@@ -62320,16 +62320,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.2869603504542605</v>
+        <v>0.2869603504542598</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02324367830537832</v>
+        <v>0.02324367830537833</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.5029697249741727</v>
+        <v>0.5029697249741724</v>
       </c>
       <c r="AP381" t="n">
-        <v>-1.803528001978133</v>
+        <v>-1.803528001978095</v>
       </c>
       <c r="AQ381" t="n">
         <v>10.31746031746032</v>
@@ -62473,10 +62473,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.030237372659574</v>
+        <v>7.030237372659579</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.189337428354154</v>
+        <v>-0.1893374283541593</v>
       </c>
       <c r="AK382" t="n">
         <v>7.061088020066238</v>
@@ -62485,16 +62485,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.2909556153842325</v>
+        <v>0.2909556153842324</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02343150180192449</v>
+        <v>0.02343150180192457</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.501187497763653</v>
+        <v>0.5011874977636526</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.003260963431115</v>
+        <v>-2.003260963431223</v>
       </c>
       <c r="AQ382" t="n">
         <v>2.362204724409449</v>
@@ -62638,10 +62638,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.074556523891909</v>
+        <v>7.074556523891907</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2166563812222311</v>
+        <v>-0.2166563812222293</v>
       </c>
       <c r="AK383" t="n">
         <v>7.045371831199247</v>
@@ -62650,16 +62650,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.2963660759601011</v>
+        <v>0.2963660759601009</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02388105320115907</v>
+        <v>0.02388105320115906</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.5011837436137521</v>
+        <v>0.5011837436137511</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.504656154321796</v>
+        <v>-2.504656154321755</v>
       </c>
       <c r="AQ383" t="n">
         <v>14.453125</v>
@@ -62803,10 +62803,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI384" t="n">
-        <v>7.103552248295395</v>
+        <v>7.103552248295403</v>
       </c>
       <c r="AJ384" t="n">
-        <v>-0.2215522788129736</v>
+        <v>-0.2215522788129807</v>
       </c>
       <c r="AK384" t="n">
         <v>7.078406423284397</v>
@@ -62815,16 +62815,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.29984079129971</v>
+        <v>0.2998407912997099</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02427773372157399</v>
+        <v>0.02427773372157407</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.4964684575356704</v>
+        <v>0.4964684575356701</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.529447296146512</v>
+        <v>-2.529447296146643</v>
       </c>
       <c r="AQ384" t="n">
         <v>18.99224806201551</v>
@@ -62980,16 +62980,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3035220749319825</v>
+        <v>0.3035220749319821</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02465824743687012</v>
+        <v>0.02465824743687013</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4899948718309226</v>
+        <v>0.4899948718309223</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.242027341128829</v>
+        <v>-2.242027341128819</v>
       </c>
       <c r="AQ385" t="n">
         <v>22.69230769230769</v>
@@ -63133,10 +63133,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.12777959440025</v>
+        <v>7.127779594400253</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2307797584322326</v>
+        <v>-0.2307797584322353</v>
       </c>
       <c r="AK386" t="n">
         <v>7.110202206771168</v>
@@ -63145,16 +63145,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3056770963992281</v>
+        <v>0.3056770963992276</v>
       </c>
       <c r="AN386" t="n">
-        <v>0.02512392944114572</v>
+        <v>0.02512392944114575</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.4836004785809395</v>
+        <v>0.48360047858094</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.575931200243899</v>
+        <v>-2.575931200243936</v>
       </c>
       <c r="AQ386" t="n">
         <v>22.13740458015267</v>
@@ -63298,28 +63298,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.117424820782309</v>
+        <v>7.117424820782308</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.2204249848142918</v>
+        <v>-0.2204249848142901</v>
       </c>
       <c r="AK387" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL387" t="n">
-        <v>-0.2182210070512509</v>
+        <v>-0.21822100705125</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3083414575758074</v>
+        <v>0.3083414575758079</v>
       </c>
       <c r="AN387" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.474982443940299</v>
+        <v>0.4749824439402989</v>
       </c>
       <c r="AP387" t="n">
-        <v>-2.316485060974927</v>
+        <v>-2.316485060974883</v>
       </c>
       <c r="AQ387" t="n">
         <v>24.62121212121212</v>
@@ -63463,10 +63463,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.116315246651977</v>
+        <v>7.116315246651979</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.2198151360257565</v>
+        <v>-0.2198151360257583</v>
       </c>
       <c r="AK388" t="n">
         <v>7.112470209890858</v>
@@ -63475,16 +63475,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3094443575020182</v>
+        <v>0.3094443575020188</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.0257875072203187</v>
+        <v>0.02578750722031873</v>
       </c>
       <c r="AO388" t="n">
-        <v>0.4671039145039241</v>
+        <v>0.467103914503924</v>
       </c>
       <c r="AP388" t="n">
-        <v>-2.25136638760747</v>
+        <v>-2.251366387607492</v>
       </c>
       <c r="AQ388" t="n">
         <v>24.43609022556391</v>
@@ -63628,28 +63628,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.109165799046384</v>
+        <v>7.109165799046382</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.1981660241135224</v>
+        <v>-0.1981660241135206</v>
       </c>
       <c r="AK389" t="n">
-        <v>7.105086649080124</v>
+        <v>7.105086649080123</v>
       </c>
       <c r="AL389" t="n">
-        <v>-0.1940868741472626</v>
+        <v>-0.1940868741472617</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3112159059696454</v>
+        <v>0.3112159059696449</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02619128791084346</v>
+        <v>0.02619128791084347</v>
       </c>
       <c r="AO389" t="n">
-        <v>0.4597800393113445</v>
+        <v>0.4597800393113443</v>
       </c>
       <c r="AP389" t="n">
-        <v>-1.81460196601208</v>
+        <v>-1.814601966012038</v>
       </c>
       <c r="AQ389" t="n">
         <v>25.74626865671642</v>
@@ -63793,10 +63793,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.140476658697598</v>
+        <v>7.14047665869759</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.2639765289978913</v>
+        <v>-0.2639765289978833</v>
       </c>
       <c r="AK390" t="n">
         <v>7.107009848336411</v>
@@ -63805,16 +63805,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3120213667410843</v>
+        <v>0.3120213667410841</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02660872919284657</v>
+        <v>0.02660872919284651</v>
       </c>
       <c r="AO390" t="n">
-        <v>0.4527828726277016</v>
+        <v>0.4527828726277021</v>
       </c>
       <c r="AP390" t="n">
-        <v>-2.929905508633215</v>
+        <v>-2.929905508633069</v>
       </c>
       <c r="AQ390" t="n">
         <v>18.51851851851852</v>
@@ -63958,10 +63958,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI391" t="n">
-        <v>7.192104266103097</v>
+        <v>7.192104266103096</v>
       </c>
       <c r="AJ391" t="n">
-        <v>-0.3266042928059782</v>
+        <v>-0.3266042928059765</v>
       </c>
       <c r="AK391" t="n">
         <v>7.130667004235951</v>
@@ -63970,16 +63970,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3119580514589064</v>
+        <v>0.3119580514589062</v>
       </c>
       <c r="AN391" t="n">
-        <v>0.02723917591229313</v>
+        <v>0.02723917591229311</v>
       </c>
       <c r="AO391" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.820789712855648</v>
+        <v>-3.820789712855619</v>
       </c>
       <c r="AQ391" t="n">
         <v>21.32352941176471</v>
@@ -64135,7 +64135,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.3060770546706492</v>
+        <v>0.3060770546706496</v>
       </c>
       <c r="AN392" t="n">
         <v>0.02737088803905663</v>
@@ -64288,10 +64288,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.16410590848237</v>
+        <v>7.164105908482372</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.2680058642318812</v>
+        <v>-0.2680058642318839</v>
       </c>
       <c r="AK393" t="n">
         <v>7.162206823443969</v>
@@ -64300,16 +64300,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.3021518080029227</v>
+        <v>0.3021518080029217</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02724691784252931</v>
+        <v>0.02724691784252936</v>
       </c>
       <c r="AO393" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP393" t="n">
-        <v>-2.578588976687483</v>
+        <v>-2.578588976687523</v>
       </c>
       <c r="AQ393" t="n">
         <v>23.18840579710145</v>
@@ -64453,10 +64453,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.165713254747866</v>
+        <v>7.165713254747862</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.2102131288628559</v>
+        <v>-0.2102131288628524</v>
       </c>
       <c r="AK394" t="n">
         <v>7.141021818380439</v>
@@ -64465,16 +64465,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.3004913268435098</v>
+        <v>0.3004913268435102</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02739193077523433</v>
+        <v>0.02739193077523432</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3752726470948202</v>
+        <v>0.3752726470948199</v>
       </c>
       <c r="AP394" t="n">
-        <v>-1.634045789662024</v>
+        <v>-1.634045789661968</v>
       </c>
       <c r="AQ394" t="n">
         <v>29.85611510791367</v>
@@ -64618,10 +64618,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.208249532027229</v>
+        <v>7.208249532027231</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3219494450521312</v>
+        <v>-0.321949445052133</v>
       </c>
       <c r="AK395" t="n">
         <v>7.146296571548195</v>
@@ -64630,16 +64630,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2982197220770054</v>
+        <v>0.2982197220770058</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02742417953210363</v>
+        <v>0.02742417953210373</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.3625782951332472</v>
+        <v>0.3625782951332475</v>
       </c>
       <c r="AP395" t="n">
-        <v>-3.260996506849887</v>
+        <v>-3.260996506849911</v>
       </c>
       <c r="AQ395" t="n">
         <v>24.64285714285714</v>
@@ -64783,28 +64783,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.193412187855718</v>
+        <v>7.193412187855726</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3208121092729543</v>
+        <v>-0.3208121092729623</v>
       </c>
       <c r="AK396" t="n">
-        <v>7.176497065376474</v>
+        <v>7.176497065376473</v>
       </c>
       <c r="AL396" t="n">
-        <v>-0.3038969867937107</v>
+        <v>-0.3038969867937098</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2910761841041076</v>
+        <v>0.2910761841041086</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02685747952387152</v>
+        <v>0.02685747952387156</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.3370674577034428</v>
+        <v>0.3370674577034442</v>
       </c>
       <c r="AP396" t="n">
-        <v>-3.117150734278276</v>
+        <v>-3.117150734278383</v>
       </c>
       <c r="AQ396" t="n">
         <v>25.53191489361702</v>
@@ -64948,10 +64948,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.227115602342048</v>
+        <v>7.227115602342041</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3273157785810614</v>
+        <v>-0.3273157785810543</v>
       </c>
       <c r="AK397" t="n">
         <v>7.185469892270627</v>
@@ -64960,16 +64960,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2812269987605887</v>
+        <v>0.281226998760588</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02697180537422167</v>
+        <v>0.0269718053742217</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.3136210223326478</v>
+        <v>0.3136210223326474</v>
       </c>
       <c r="AP397" t="n">
-        <v>-3.090982180858276</v>
+        <v>-3.090982180858172</v>
       </c>
       <c r="AQ397" t="n">
         <v>26.40845070422535</v>
@@ -65113,10 +65113,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.187163192389372</v>
+        <v>7.187163192389367</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.3014629665592938</v>
+        <v>-0.3014629665592885</v>
       </c>
       <c r="AK398" t="n">
         <v>7.208338760609084</v>
@@ -65125,16 +65125,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2681836981576122</v>
+        <v>0.2681836981576121</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02658698789673936</v>
+        <v>0.02658698789673927</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.285908150945263</v>
+        <v>0.2859081509452629</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.642799587348834</v>
+        <v>-2.642799587348761</v>
       </c>
       <c r="AQ398" t="n">
         <v>27.27272727272727</v>
@@ -65278,10 +65278,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.214951953115591</v>
+        <v>7.214951953115579</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.334951838674673</v>
+        <v>-0.3349518386746606</v>
       </c>
       <c r="AK399" t="n">
         <v>7.186200492654655</v>
@@ -65290,16 +65290,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2591628297636744</v>
+        <v>0.2591628297636748</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.02587977479594339</v>
+        <v>0.02587977479594331</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.266108201492412</v>
+        <v>0.2661082014924122</v>
       </c>
       <c r="AP399" t="n">
-        <v>-3.00186729217443</v>
+        <v>-3.001867292174275</v>
       </c>
       <c r="AQ399" t="n">
         <v>26.73611111111111</v>
@@ -65443,10 +65443,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI400" t="n">
-        <v>7.197430004066455</v>
+        <v>7.197430004066453</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.305630077308642</v>
+        <v>-0.3056300773086402</v>
       </c>
       <c r="AK400" t="n">
         <v>7.201835396295348</v>
@@ -65455,16 +65455,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2466333883508319</v>
+        <v>0.2466333883508324</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.0247654344950328</v>
+        <v>0.02476543449503272</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.2401258754735003</v>
+        <v>0.2401258754735008</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.534507398102846</v>
+        <v>-2.534507398102835</v>
       </c>
       <c r="AQ400" t="n">
         <v>25.51724137931034</v>
@@ -65611,25 +65611,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.3291230670577869</v>
+        <v>-0.3291230670577878</v>
       </c>
       <c r="AK401" t="n">
-        <v>7.179650721554484</v>
+        <v>7.179650721554483</v>
       </c>
       <c r="AL401" t="n">
-        <v>-0.2786506986663007</v>
+        <v>-0.2786506986662998</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.2377807761788571</v>
+        <v>0.2377807761788565</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.02334020127887793</v>
+        <v>0.02334020127887796</v>
       </c>
       <c r="AO401" t="n">
-        <v>0.2171758918683914</v>
+        <v>0.2171758918683913</v>
       </c>
       <c r="AP401" t="n">
-        <v>-2.762482238451886</v>
+        <v>-2.76248223845191</v>
       </c>
       <c r="AQ401" t="n">
         <v>26.02739726027397</v>
@@ -65773,10 +65773,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.20852803773295</v>
+        <v>7.208528037732954</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.2978281933725988</v>
+        <v>-0.2978281933726024</v>
       </c>
       <c r="AK402" t="n">
         <v>7.206616000051887</v>
@@ -65785,16 +65785,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.2255544515066686</v>
+        <v>0.2255544515066683</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.0206724522626571</v>
+        <v>0.0206724522626572</v>
       </c>
       <c r="AO402" t="n">
-        <v>0.1898019966940717</v>
+        <v>0.1898019966940708</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.302865963394848</v>
+        <v>-2.302865963394901</v>
       </c>
       <c r="AQ402" t="n">
         <v>15.98639455782313</v>
@@ -65938,10 +65938,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.19880309223843</v>
+        <v>7.198803092238432</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.287202979323391</v>
+        <v>-0.2872029793233928</v>
       </c>
       <c r="AK403" t="n">
         <v>7.18051307481679</v>
@@ -65950,16 +65950,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.2150441262650612</v>
+        <v>0.2150441262650616</v>
       </c>
       <c r="AN403" t="n">
-        <v>0.01774895516388914</v>
+        <v>0.0177489551638892</v>
       </c>
       <c r="AO403" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP403" t="n">
-        <v>-2.125372134371253</v>
+        <v>-2.125372134371282</v>
       </c>
       <c r="AQ403" t="n">
         <v>14.52702702702703</v>
@@ -66103,10 +66103,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.172424239411004</v>
+        <v>7.172424239411002</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2608241264959652</v>
+        <v>-0.2608241264959634</v>
       </c>
       <c r="AK404" t="n">
         <v>7.16705299197773</v>
@@ -66115,16 +66115,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.205433651489446</v>
+        <v>0.2054336514894463</v>
       </c>
       <c r="AN404" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO404" t="n">
-        <v>0.1417286033373026</v>
+        <v>0.1417286033373033</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.765505948615044</v>
+        <v>-1.765505948615028</v>
       </c>
       <c r="AQ404" t="n">
         <v>18.45637583892617</v>
@@ -66268,10 +66268,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.163756390646672</v>
+        <v>7.163756390646673</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2695565424716229</v>
+        <v>-0.2695565424716238</v>
       </c>
       <c r="AK405" t="n">
         <v>7.153532751444382</v>
@@ -66280,16 +66280,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1941661953581061</v>
+        <v>0.1941661953581056</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.01312004055850013</v>
+        <v>0.01312004055850015</v>
       </c>
       <c r="AO405" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP405" t="n">
-        <v>-1.847646922476716</v>
+        <v>-1.847646922476733</v>
       </c>
       <c r="AQ405" t="n">
         <v>24.66666666666667</v>
@@ -66433,10 +66433,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.158063699621738</v>
+        <v>7.158063699621736</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.2875636118837006</v>
+        <v>-0.2875636118836988</v>
       </c>
       <c r="AK406" t="n">
         <v>7.150669702211316</v>
@@ -66445,16 +66445,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1839494937266881</v>
+        <v>0.183949493726688</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.01194074338472806</v>
+        <v>0.01194074338472802</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.1107549805175829</v>
+        <v>0.110754980517583</v>
       </c>
       <c r="AP406" t="n">
-        <v>-2.036901689708357</v>
+        <v>-2.036901689708342</v>
       </c>
       <c r="AQ406" t="n">
         <v>12.91390728476821</v>
@@ -66598,10 +66598,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.157435208014563</v>
+        <v>7.157435208014565</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.272335320166663</v>
+        <v>-0.2723353201666647</v>
       </c>
       <c r="AK407" t="n">
         <v>7.140926852093823</v>
@@ -66610,16 +66610,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1753430411611933</v>
+        <v>0.1753430411611928</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.00971765423202034</v>
+        <v>0.009717654232020439</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.09620195025422695</v>
+        <v>0.09620195025422784</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.822067618268809</v>
+        <v>-1.822067618268836</v>
       </c>
       <c r="AQ407" t="n">
         <v>20.72368421052632</v>
@@ -66763,10 +66763,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.150386811340072</v>
+        <v>7.15038681134007</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2679867754819174</v>
+        <v>-0.2679867754819156</v>
       </c>
       <c r="AK408" t="n">
         <v>7.142886401315924</v>
@@ -66775,16 +66775,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1664838398737872</v>
+        <v>0.1664838398737869</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.008089376136153875</v>
+        <v>0.008089376136153925</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.0848962688609296</v>
+        <v>0.08489626886092971</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.745105232570982</v>
+        <v>-1.745105232570966</v>
       </c>
       <c r="AQ408" t="n">
         <v>20.26143790849673</v>
@@ -66928,10 +66928,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.137094841694645</v>
+        <v>7.137094841694642</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2547949416397133</v>
+        <v>-0.2547949416397106</v>
       </c>
       <c r="AK409" t="n">
         <v>7.137840883333127</v>
@@ -66940,16 +66940,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1571907956492611</v>
+        <v>0.1571907956492617</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.006581947594647974</v>
+        <v>0.006581947594647856</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.07412699588694804</v>
+        <v>0.07412699588694738</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.566475044001858</v>
+        <v>-1.566475044001832</v>
       </c>
       <c r="AQ409" t="n">
         <v>20.45454545454545</v>
@@ -67093,10 +67093,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.123391234435203</v>
+        <v>7.1233912344352</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2666912908927221</v>
+        <v>-0.2666912908927195</v>
       </c>
       <c r="AK410" t="n">
         <v>7.12862724785568</v>
@@ -67105,16 +67105,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM410" t="n">
-        <v>0.1487097707294961</v>
+        <v>0.1487097707294973</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005441006961990014</v>
+        <v>0.005441006961990058</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.06531270865715677</v>
+        <v>0.06531270865715666</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.68923547619639</v>
+        <v>-1.689235476196365</v>
       </c>
       <c r="AQ410" t="n">
         <v>14.19354838709677</v>
@@ -67258,10 +67258,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.11600731855288</v>
+        <v>7.116007318552882</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2873072529400869</v>
+        <v>-0.2873072529400895</v>
       </c>
       <c r="AK411" t="n">
         <v>7.118961040191934</v>
@@ -67270,16 +67270,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM411" t="n">
-        <v>0.1409513724492178</v>
+        <v>0.1409513724492179</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005644373135176822</v>
+        <v>0.005644373135176906</v>
       </c>
       <c r="AO411" t="n">
-        <v>0.05986577613532174</v>
+        <v>0.0598657761353214</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.908486026349772</v>
+        <v>-1.90848602634981</v>
       </c>
       <c r="AQ411" t="n">
         <v>9.935897435897436</v>
@@ -67423,10 +67423,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI412" t="n">
-        <v>7.115262454587763</v>
+        <v>7.11526245458776</v>
       </c>
       <c r="AJ412" t="n">
-        <v>-0.2838625369852235</v>
+        <v>-0.2838625369852208</v>
       </c>
       <c r="AK412" t="n">
         <v>7.113208458946866</v>
@@ -67438,13 +67438,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005618445165739616</v>
+        <v>0.005618445165739529</v>
       </c>
       <c r="AO412" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.840960329226796</v>
+        <v>-1.840960329226772</v>
       </c>
       <c r="AQ412" t="n">
         <v>8.598726114649681</v>
@@ -67600,16 +67600,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM413" t="n">
-        <v>0.1248427026608149</v>
+        <v>0.1248427026608145</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005050876420738246</v>
+        <v>0.005050876420738303</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.04692762159458042</v>
+        <v>0.04692762159457986</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.755949528666201</v>
+        <v>-1.755949528666207</v>
       </c>
       <c r="AQ413" t="n">
         <v>13.60759493670886</v>
@@ -67753,10 +67753,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.100218718661557</v>
+        <v>7.100218718661558</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2699188643829924</v>
+        <v>-0.2699188643829933</v>
       </c>
       <c r="AK414" t="n">
         <v>7.105971078464224</v>
@@ -67768,13 +67768,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.005209570180715356</v>
+        <v>0.00520957018071537</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.0421970173931332</v>
+        <v>0.04219701739313308</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.633946744033946</v>
+        <v>-1.633946744033963</v>
       </c>
       <c r="AQ414" t="n">
         <v>14.77987421383648</v>
@@ -67918,10 +67918,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI415" t="n">
-        <v>7.097935875054437</v>
+        <v>7.097935875054439</v>
       </c>
       <c r="AJ415" t="n">
-        <v>-0.2822358208857363</v>
+        <v>-0.2822358208857381</v>
       </c>
       <c r="AK415" t="n">
         <v>7.101361129315627</v>
@@ -67930,16 +67930,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.1117472247487875</v>
+        <v>0.1117472247487876</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005385102682029907</v>
+        <v>0.005385102682029925</v>
       </c>
       <c r="AO415" t="n">
-        <v>0.03866992220359</v>
+        <v>0.03866992220359033</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.755252893295954</v>
+        <v>-1.755252893295981</v>
       </c>
       <c r="AQ415" t="n">
         <v>13.75</v>
@@ -68083,10 +68083,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI416" t="n">
-        <v>7.097978821692022</v>
+        <v>7.097978821692021</v>
       </c>
       <c r="AJ416" t="n">
-        <v>-0.2799789819093075</v>
+        <v>-0.2799789819093057</v>
       </c>
       <c r="AK416" t="n">
         <v>7.099648834314064</v>
@@ -68095,16 +68095,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.1065475925362033</v>
+        <v>0.1065475925362025</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.005956926407440957</v>
+        <v>0.005956926407441003</v>
       </c>
       <c r="AO416" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.7077813719065</v>
+        <v>-1.707781371906486</v>
       </c>
       <c r="AQ416" t="n">
         <v>13.66459627329192</v>
@@ -68260,16 +68260,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.1013724682419977</v>
+        <v>0.1013724682419976</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.006126167203105798</v>
+        <v>0.006126167203105847</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.03348722035246332</v>
+        <v>0.03348722035246277</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.545702361153159</v>
+        <v>-1.545702361153165</v>
       </c>
       <c r="AQ417" t="n">
         <v>22.22222222222222</v>
@@ -68413,10 +68413,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI418" t="n">
-        <v>7.087097940453345</v>
+        <v>7.087097940453343</v>
       </c>
       <c r="AJ418" t="n">
-        <v>-0.2700980281913825</v>
+        <v>-0.2700980281913798</v>
       </c>
       <c r="AK418" t="n">
         <v>7.090805518999606</v>
@@ -68425,16 +68425,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.09919462776856321</v>
+        <v>0.09919462776856289</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.006113943880485972</v>
+        <v>0.006113943880485968</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.03204155062895153</v>
+        <v>0.03204155062895098</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.560217818508639</v>
+        <v>-1.560217818508615</v>
       </c>
       <c r="AQ418" t="n">
         <v>17.17791411042945</v>
@@ -68590,16 +68590,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.097507502547015</v>
+        <v>0.09750750254701511</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.005510714664730507</v>
+        <v>0.005510714664730422</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.03001455024934374</v>
+        <v>0.03001455024934274</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.618797990886845</v>
+        <v>-1.618797990886851</v>
       </c>
       <c r="AQ419" t="n">
         <v>14.02439024390244</v>
@@ -68755,16 +68755,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.09380549503386901</v>
+        <v>0.09380549503386949</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.004784904607979881</v>
+        <v>0.004784904607979855</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.02699383492044782</v>
+        <v>0.02699383492044827</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.576016406515579</v>
+        <v>-1.576016406515585</v>
       </c>
       <c r="AQ420" t="n">
         <v>17.57575757575758</v>
@@ -68908,10 +68908,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.097145375663951</v>
+        <v>7.097145375663948</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.2729452223131208</v>
+        <v>-0.2729452223131181</v>
       </c>
       <c r="AK421" t="n">
         <v>7.093828611034739</v>
@@ -68920,16 +68920,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.08945254406056438</v>
+        <v>0.08945254406056392</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.004001520125414798</v>
+        <v>0.004001520125414807</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.02385555423225116</v>
+        <v>0.02385555423225172</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.54199766798477</v>
+        <v>-1.541997667984746</v>
       </c>
       <c r="AQ421" t="n">
         <v>21.68674698795181</v>
@@ -69073,10 +69073,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.088227962421951</v>
+        <v>7.088227962421954</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.262227748798904</v>
+        <v>-0.2622277487989066</v>
       </c>
       <c r="AK422" t="n">
         <v>7.092951699003613</v>
@@ -69085,16 +69085,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.07912491692886899</v>
+        <v>0.07912491692886864</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.003813743757049903</v>
+        <v>0.003813743757049957</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.01902803623666316</v>
+        <v>0.01902803623666371</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.408148123344065</v>
+        <v>-1.408148123344101</v>
       </c>
       <c r="AQ422" t="n">
         <v>34.4311377245509</v>
@@ -69238,10 +69238,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.082675656384673</v>
+        <v>7.082675656384675</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2467758265201709</v>
+        <v>-0.2467758265201727</v>
       </c>
       <c r="AK423" t="n">
         <v>7.085940899278786</v>
@@ -69250,16 +69250,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.07019093860911668</v>
+        <v>0.07019093860911679</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.003788844982403339</v>
+        <v>0.003788844982403293</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.01530727852465064</v>
+        <v>0.0153072785246503</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.224883418791509</v>
+        <v>-1.224883418791533</v>
       </c>
       <c r="AQ423" t="n">
         <v>32.44047619047619</v>
@@ -69403,10 +69403,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.082585232341567</v>
+        <v>7.082585232341569</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2597850728872215</v>
+        <v>-0.2597850728872233</v>
       </c>
       <c r="AK424" t="n">
         <v>7.080231185021037</v>
@@ -69415,16 +69415,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.0607230145131474</v>
+        <v>0.06072301451314636</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.003218097337044118</v>
+        <v>0.003218097337044184</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.01127031184523342</v>
+        <v>0.01127031184523331</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.359556645403147</v>
+        <v>-1.359556645403171</v>
       </c>
       <c r="AQ424" t="n">
         <v>32.54437869822485</v>
@@ -69568,10 +69568,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI425" t="n">
-        <v>7.082752176397555</v>
+        <v>7.082752176397554</v>
       </c>
       <c r="AJ425" t="n">
-        <v>-0.2453522168333464</v>
+        <v>-0.2453522168333455</v>
       </c>
       <c r="AK425" t="n">
         <v>7.078545045220129</v>
@@ -69580,16 +69580,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.04987769893955558</v>
+        <v>0.04987769893955601</v>
       </c>
       <c r="AN425" t="n">
-        <v>0.002647769861786137</v>
+        <v>0.002647769861786034</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.00755590738572276</v>
+        <v>0.007555907385723093</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.189124028692556</v>
+        <v>-1.18912402869255</v>
       </c>
       <c r="AQ425" t="n">
         <v>34.11764705882352</v>
@@ -69733,10 +69733,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI426" t="n">
-        <v>7.073418742129174</v>
+        <v>7.073418742129173</v>
       </c>
       <c r="AJ426" t="n">
-        <v>-0.2359186467617427</v>
+        <v>-0.2359186467617418</v>
       </c>
       <c r="AK426" t="n">
         <v>7.075576762908686</v>
@@ -69745,16 +69745,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM426" t="n">
-        <v>0.03723342047483359</v>
+        <v>0.03723342047483347</v>
       </c>
       <c r="AN426" t="n">
-        <v>0.0007434096776329363</v>
+        <v>0.0007434096776329864</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.003691827899839573</v>
+        <v>0.003691827899840794</v>
       </c>
       <c r="AP426" t="n">
-        <v>-1.076578522273155</v>
+        <v>-1.076578522273149</v>
       </c>
       <c r="AQ426" t="n">
         <v>36.54970760233918</v>
@@ -69910,16 +69910,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM427" t="n">
-        <v>0.02391394499985428</v>
+        <v>0.02391394499985489</v>
       </c>
       <c r="AN427" t="n">
-        <v>0.0004638728584110997</v>
+        <v>0.0004638728584110585</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.00150427765126282</v>
+        <v>0.001504277651263042</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.116075578135644</v>
+        <v>-1.116075578135648</v>
       </c>
       <c r="AQ427" t="n">
         <v>34.30232558139535</v>
@@ -70063,10 +70063,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI428" t="n">
-        <v>7.061175551975939</v>
+        <v>7.06117555197594</v>
       </c>
       <c r="AJ428" t="n">
-        <v>-0.2336756854903435</v>
+        <v>-0.2336756854903443</v>
       </c>
       <c r="AK428" t="n">
         <v>7.061105294515807</v>
@@ -70075,16 +70075,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM428" t="n">
-        <v>0.01023096587809661</v>
+        <v>0.01023096587809607</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.0001641525470544823</v>
+        <v>-0.0001641525470544615</v>
       </c>
       <c r="AO428" t="n">
-        <v>0.0002530929795961923</v>
+        <v>0.000253092979595082</v>
       </c>
       <c r="AP428" t="n">
-        <v>-1.037865720030704</v>
+        <v>-1.037865720030718</v>
       </c>
       <c r="AQ428" t="n">
         <v>39.30635838150289</v>
@@ -70240,16 +70240,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.001349940557734956</v>
+        <v>-0.001349940557734529</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.001242569541730382</v>
+        <v>-0.001242569541730301</v>
       </c>
       <c r="AO429" t="n">
-        <v>9.828375502929365e-05</v>
+        <v>9.828375502973774e-05</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.9421931502147813</v>
+        <v>-0.9421931502147847</v>
       </c>
       <c r="AQ429" t="n">
         <v>39.6551724137931</v>
@@ -70393,10 +70393,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.051845784111939</v>
+        <v>7.051845784111937</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.2217457246026617</v>
+        <v>-0.22174572460266</v>
       </c>
       <c r="AK430" t="n">
         <v>7.04924004450221</v>
@@ -70405,16 +70405,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.01245927794565087</v>
+        <v>-0.0124592779456514</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.002690846636687106</v>
+        <v>-0.002690846636687166</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.0009149443224345521</v>
+        <v>0.000914944322433886</v>
       </c>
       <c r="AP430" t="n">
-        <v>-0.8946168972865359</v>
+        <v>-0.8946168972865196</v>
       </c>
       <c r="AQ430" t="n">
         <v>36.57142857142857</v>
@@ -70558,10 +70558,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.044932512363691</v>
+        <v>7.044932512363692</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2339326420633983</v>
+        <v>-0.2339326420633991</v>
       </c>
       <c r="AK431" t="n">
         <v>7.044607485549974</v>
@@ -70570,16 +70570,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.02351974718911197</v>
+        <v>-0.0235197471891116</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003286981705062079</v>
+        <v>-0.003286981705062081</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.002235402288773947</v>
+        <v>0.002235402288773058</v>
       </c>
       <c r="AP431" t="n">
-        <v>-1.025034800695888</v>
+        <v>-1.025034800695901</v>
       </c>
       <c r="AQ431" t="n">
         <v>34.65909090909091</v>
@@ -70723,10 +70723,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.041380724566422</v>
+        <v>7.04138072456642</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2399805399350745</v>
+        <v>-0.2399805399350727</v>
       </c>
       <c r="AK432" t="n">
         <v>7.036677431055121</v>
@@ -70735,16 +70735,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.03604973348542533</v>
+        <v>-0.03604973348542571</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003896888881646653</v>
+        <v>-0.003896888881646666</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.004508577134016534</v>
+        <v>0.004508577134016423</v>
       </c>
       <c r="AP432" t="n">
-        <v>-1.085983877862689</v>
+        <v>-1.085983877862673</v>
       </c>
       <c r="AQ432" t="n">
         <v>27.40112994350282</v>
@@ -70888,10 +70888,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI433" t="n">
-        <v>7.031781164871437</v>
+        <v>7.031781164871438</v>
       </c>
       <c r="AJ433" t="n">
-        <v>-0.2312812487947769</v>
+        <v>-0.2312812487947777</v>
       </c>
       <c r="AK433" t="n">
         <v>7.031531243279009</v>
@@ -70900,16 +70900,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.0496421115884523</v>
+        <v>-0.04964211158845258</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.003622848094475932</v>
+        <v>-0.003622848094475877</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.007358432861332531</v>
+        <v>0.007358432861333086</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.9831789894954935</v>
+        <v>-0.983178989495507</v>
       </c>
       <c r="AQ433" t="n">
         <v>34.83146067415731</v>
@@ -71065,16 +71065,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.06336633742876464</v>
+        <v>-0.06336633742876532</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.00383222203166729</v>
+        <v>-0.003832222031667326</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.0113935335626284</v>
+        <v>0.01139353356262962</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.9132686155557141</v>
+        <v>-0.9132686155557176</v>
       </c>
       <c r="AQ434" t="n">
         <v>35.47486033519553</v>
@@ -71218,10 +71218,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI435" t="n">
-        <v>7.012358254068223</v>
+        <v>7.012358254068221</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.220358437173692</v>
+        <v>-0.2203584371736902</v>
       </c>
       <c r="AK435" t="n">
         <v>7.010266108789461</v>
@@ -71230,16 +71230,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.07815930192347351</v>
+        <v>-0.07815930192347212</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.0037302018478894</v>
+        <v>-0.003730201847889384</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.01669360800688513</v>
+        <v>0.01669360800688602</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.8521135061576827</v>
+        <v>-0.8521135061576661</v>
       </c>
       <c r="AQ435" t="n">
         <v>34.72222222222222</v>
@@ -71383,10 +71383,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI436" t="n">
-        <v>7.001516536947593</v>
+        <v>7.001516536947591</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.2107164423431005</v>
+        <v>-0.2107164423430987</v>
       </c>
       <c r="AK436" t="n">
         <v>7.003692382618654</v>
@@ -71395,16 +71395,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.09225745624393369</v>
+        <v>-0.09225745624393285</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.003729646461095512</v>
+        <v>-0.003729646461095566</v>
       </c>
       <c r="AO436" t="n">
-        <v>0.02283737241168637</v>
+        <v>0.02283737241168682</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.7409128144376789</v>
+        <v>-0.7409128144376621</v>
       </c>
       <c r="AQ436" t="n">
         <v>39.22651933701658</v>
@@ -71548,10 +71548,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.98285303226683</v>
+        <v>6.982853032266831</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1977530490514976</v>
+        <v>-0.1977530490514985</v>
       </c>
       <c r="AK437" t="n">
         <v>6.994908837140057</v>
@@ -71560,16 +71560,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1040956648961724</v>
+        <v>-0.1040956648961739</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.004775368000139335</v>
+        <v>-0.004775368000139281</v>
       </c>
       <c r="AO437" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.5932977716256262</v>
+        <v>-0.5932977716256395</v>
       </c>
       <c r="AQ437" t="n">
         <v>40.38461538461539</v>
@@ -71713,10 +71713,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI438" t="n">
-        <v>6.976537964100197</v>
+        <v>6.976537964100195</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1673381540721204</v>
+        <v>-0.1673381540721186</v>
       </c>
       <c r="AK438" t="n">
         <v>6.976048621620001</v>
@@ -71725,16 +71725,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.1171809788132883</v>
+        <v>-0.1171809788132892</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.006568629287185546</v>
+        <v>-0.006568629287185491</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.03914952746580425</v>
+        <v>0.03914952746580436</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.2508070992157119</v>
+        <v>-0.2508070992156945</v>
       </c>
       <c r="AQ438" t="n">
         <v>48.08743169398907</v>
@@ -71881,7 +71881,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ439" t="n">
-        <v>-0.1582257113591101</v>
+        <v>-0.1582257113591092</v>
       </c>
       <c r="AK439" t="n">
         <v>6.970728111892008</v>
@@ -71890,16 +71890,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM439" t="n">
-        <v>-0.127636816539944</v>
+        <v>-0.127636816539943</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.007451019732577668</v>
+        <v>-0.00745101973257774</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.04750067483060583</v>
+        <v>0.04750067483060572</v>
       </c>
       <c r="AP439" t="n">
-        <v>-0.1477390246523876</v>
+        <v>-0.14773902465238</v>
       </c>
       <c r="AQ439" t="n">
         <v>49.18478260869566</v>
@@ -72058,13 +72058,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.008628156625160088</v>
+        <v>-0.008628156625160163</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.05751510742764043</v>
+        <v>0.05751510742764121</v>
       </c>
       <c r="AP440" t="n">
-        <v>-0.03659458102660845</v>
+        <v>-0.03659458102661073</v>
       </c>
       <c r="AQ440" t="n">
         <v>51.35135135135135</v>
@@ -72208,10 +72208,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.950644730799358</v>
+        <v>6.950644730799363</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1501448147226974</v>
+        <v>-0.1501448147227027</v>
       </c>
       <c r="AK441" t="n">
         <v>6.959853578800648</v>
@@ -72220,16 +72220,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1469566450661546</v>
+        <v>-0.1469566450661556</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.009026348114251986</v>
+        <v>-0.009026348114251901</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.06603756167960417</v>
+        <v>0.06603756167960351</v>
       </c>
       <c r="AP441" t="n">
-        <v>-0.05626100341230957</v>
+        <v>-0.05626100341237209</v>
       </c>
       <c r="AQ441" t="n">
         <v>49.19354838709678</v>
@@ -72373,28 +72373,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.934622414140156</v>
+        <v>6.934622414140152</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1321226430219919</v>
+        <v>-0.1321226430219875</v>
       </c>
       <c r="AK442" t="n">
-        <v>6.94711441643572</v>
+        <v>6.947114416435721</v>
       </c>
       <c r="AL442" t="n">
-        <v>-0.1446146453175556</v>
+        <v>-0.1446146453175565</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1568781652619925</v>
+        <v>-0.1568781652619921</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.010042871337475</v>
+        <v>-0.01004287133747513</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.07699206242755485</v>
+        <v>0.07699206242755419</v>
       </c>
       <c r="AP442" t="n">
-        <v>0.1480195792193409</v>
+        <v>0.1480195792193899</v>
       </c>
       <c r="AQ442" t="n">
         <v>58.28877005347594</v>
@@ -72538,10 +72538,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.928042396530076</v>
+        <v>6.928042396530073</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1335425224150857</v>
+        <v>-0.133542522415083</v>
       </c>
       <c r="AK443" t="n">
         <v>6.933186989735641</v>
@@ -72550,16 +72550,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.1650917115670576</v>
+        <v>-0.1650917115670582</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.0106149464753251</v>
+        <v>-0.01061494647532512</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.08732871254562191</v>
+        <v>0.08732871254562202</v>
       </c>
       <c r="AP443" t="n">
-        <v>0.1314955391289633</v>
+        <v>0.1314955391289917</v>
       </c>
       <c r="AQ443" t="n">
         <v>55.0531914893617</v>
@@ -72703,10 +72703,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.941461393298105</v>
+        <v>6.941461393298106</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1469615191831144</v>
+        <v>-0.1469615191831153</v>
       </c>
       <c r="AK444" t="n">
         <v>6.925995477801935</v>
@@ -72715,16 +72715,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.1745447047691483</v>
+        <v>-0.1745447047691478</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01108963812755723</v>
+        <v>-0.01108963812755724</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.09935205695041804</v>
+        <v>0.09935205695041927</v>
       </c>
       <c r="AP444" t="n">
-        <v>-0.02165722024126449</v>
+        <v>-0.02165722024127693</v>
       </c>
       <c r="AQ444" t="n">
         <v>48.67724867724867</v>
@@ -72868,10 +72868,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.93323210397643</v>
+        <v>6.933232103976423</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1472323290435682</v>
+        <v>-0.147232329043562</v>
       </c>
       <c r="AK445" t="n">
         <v>6.938996539173566</v>
@@ -72880,16 +72880,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM445" t="n">
-        <v>-0.1853013335308036</v>
+        <v>-0.1853013335308053</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01193987645426134</v>
+        <v>-0.01193987645426136</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.1123648810347069</v>
+        <v>0.1123648810347067</v>
       </c>
       <c r="AP445" t="n">
-        <v>-0.02469248456285458</v>
+        <v>-0.02469248456278582</v>
       </c>
       <c r="AQ445" t="n">
         <v>44.47368421052632</v>
@@ -73033,10 +73033,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.928429644379657</v>
+        <v>6.928429644379658</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1496296336985043</v>
+        <v>-0.1496296336985061</v>
       </c>
       <c r="AK446" t="n">
         <v>6.93160690101155</v>
@@ -73048,13 +73048,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01257308415669778</v>
+        <v>-0.01257308415669775</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.125857898472412</v>
+        <v>0.1258578984724115</v>
       </c>
       <c r="AP446" t="n">
-        <v>-0.05207285656412575</v>
+        <v>-0.05207285656414852</v>
       </c>
       <c r="AQ446" t="n">
         <v>44.76439790575916</v>
@@ -73198,10 +73198,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.925068850639515</v>
+        <v>6.925068850639512</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1455688430101203</v>
+        <v>-0.1455688430101176</v>
       </c>
       <c r="AK447" t="n">
         <v>6.924763510572069</v>
@@ -73210,16 +73210,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2060805417157788</v>
+        <v>-0.2060805417157789</v>
       </c>
       <c r="AN447" t="n">
-        <v>-0.01318646791849926</v>
+        <v>-0.01318646791849928</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1396251026736655</v>
+        <v>0.1396251026736647</v>
       </c>
       <c r="AP447" t="n">
-        <v>-0.005325399126139124</v>
+        <v>-0.00532539912611095</v>
       </c>
       <c r="AQ447" t="n">
         <v>48.4375</v>
@@ -73363,10 +73363,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.900929863197374</v>
+        <v>6.900929863197373</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1347297975845807</v>
+        <v>-0.1347297975845798</v>
       </c>
       <c r="AK448" t="n">
         <v>6.921049732547429</v>
@@ -73375,16 +73375,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM448" t="n">
-        <v>-0.2151279705591488</v>
+        <v>-0.2151279705591481</v>
       </c>
       <c r="AN448" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1518365696223548</v>
+        <v>0.1518365696223549</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.1194301167255473</v>
+        <v>0.1194301167255552</v>
       </c>
       <c r="AQ448" t="n">
         <v>49.48186528497409</v>
@@ -73528,10 +73528,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.895219010181459</v>
+        <v>6.89521901018146</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.1302191436958635</v>
+        <v>-0.1302191436958644</v>
       </c>
       <c r="AK449" t="n">
         <v>6.89978353884127</v>
@@ -73543,13 +73543,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01278923357027009</v>
+        <v>-0.01278923357027006</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.1644177475946104</v>
+        <v>0.1644177475946105</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.1711578920391648</v>
+        <v>0.1711578920391523</v>
       </c>
       <c r="AQ449" t="n">
         <v>47.16494845360825</v>
@@ -73693,10 +73693,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.879512239848579</v>
+        <v>6.87951223984858</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.1173123611559523</v>
+        <v>-0.1173123611559532</v>
       </c>
       <c r="AK450" t="n">
         <v>6.893260360395011</v>
@@ -73705,16 +73705,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.233692768734329</v>
+        <v>-0.233692768734328</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01245257184765153</v>
+        <v>-0.01245257184765156</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.179129523332087</v>
+        <v>0.1791295233320875</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.3199422777651793</v>
+        <v>0.3199422777651673</v>
       </c>
       <c r="AQ450" t="n">
         <v>50.51282051282051</v>
@@ -73858,10 +73858,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI451" t="n">
-        <v>6.882426232260446</v>
+        <v>6.882426232260437</v>
       </c>
       <c r="AJ451" t="n">
-        <v>-0.1132263840853973</v>
+        <v>-0.1132263840853884</v>
       </c>
       <c r="AK451" t="n">
         <v>6.880758546638964</v>
@@ -73870,16 +73870,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2433281856134891</v>
+        <v>-0.2433281856134888</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01202813951384066</v>
+        <v>-0.01202813951384067</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.1944608722019401</v>
+        <v>0.1944608722019407</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.3663796020962863</v>
+        <v>0.3663796020963871</v>
       </c>
       <c r="AQ451" t="n">
         <v>52.04081632653062</v>
@@ -74035,16 +74035,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2520264427810588</v>
+        <v>-0.25202644278106</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01246671652825437</v>
+        <v>-0.01246671652825434</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2101991144027906</v>
+        <v>0.2101991144027905</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.9316471322250902</v>
+        <v>0.9316471322250883</v>
       </c>
       <c r="AQ452" t="n">
         <v>64.72081218274111</v>
@@ -74188,10 +74188,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.841963898035317</v>
+        <v>6.841963898035326</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.07646382937076623</v>
+        <v>-0.07646382937077512</v>
       </c>
       <c r="AK453" t="n">
         <v>6.844785316397215</v>
@@ -74200,16 +74200,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.2592973891940562</v>
+        <v>-0.2592973891940566</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01305068899435097</v>
+        <v>-0.01305068899435077</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2277185089957531</v>
+        <v>0.2277185089957524</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7869542060737252</v>
+        <v>0.7869542060736205</v>
       </c>
       <c r="AQ453" t="n">
         <v>58.08080808080808</v>
@@ -74353,28 +74353,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.845644916883085</v>
+        <v>6.845644916883079</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.08014484821853429</v>
+        <v>-0.08014484821852808</v>
       </c>
       <c r="AK454" t="n">
-        <v>6.849407886968131</v>
+        <v>6.849407886968132</v>
       </c>
       <c r="AL454" t="n">
-        <v>-0.08390781830358041</v>
+        <v>-0.08390781830358129</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2668003223256257</v>
+        <v>-0.2668003223256254</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.01367989020054944</v>
+        <v>-0.0136798902005495</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.2456601220977563</v>
+        <v>0.2456601220977566</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.7411156361322451</v>
+        <v>0.7411156361323163</v>
       </c>
       <c r="AQ454" t="n">
         <v>57.78894472361809</v>
@@ -74518,10 +74518,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.842084108625032</v>
+        <v>6.842084108625038</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.0695840704780597</v>
+        <v>-0.06958407047806503</v>
       </c>
       <c r="AK455" t="n">
         <v>6.852702018840203</v>
@@ -74530,16 +74530,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.2735436467318143</v>
+        <v>-0.273543646731814</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01403412282467997</v>
+        <v>-0.01403412282467991</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.2619835102172253</v>
+        <v>0.261983510217226</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.8606851556422667</v>
+        <v>0.8606851556422036</v>
       </c>
       <c r="AQ455" t="n">
         <v>63</v>
@@ -74683,10 +74683,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.863831060847773</v>
+        <v>6.863831060847785</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.09133102270080062</v>
+        <v>-0.09133102270081217</v>
       </c>
       <c r="AK456" t="n">
         <v>6.850973969550408</v>
@@ -74695,16 +74695,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM456" t="n">
-        <v>-0.2787367835501612</v>
+        <v>-0.2787367835501617</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.01406387644726603</v>
+        <v>-0.01406387644726588</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.2758112468611987</v>
+        <v>0.2758112468611976</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.6044845987547318</v>
+        <v>0.6044845987545961</v>
       </c>
       <c r="AQ456" t="n">
         <v>61.94029850746269</v>
@@ -74848,10 +74848,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI457" t="n">
-        <v>6.853037915615571</v>
+        <v>6.853037915615573</v>
       </c>
       <c r="AJ457" t="n">
-        <v>-0.07753809490634289</v>
+        <v>-0.07753809490634467</v>
       </c>
       <c r="AK457" t="n">
         <v>6.873527983489108</v>
@@ -74863,13 +74863,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN457" t="n">
-        <v>-0.013790177185657</v>
+        <v>-0.01379017718565697</v>
       </c>
       <c r="AO457" t="n">
-        <v>0.285442546377481</v>
+        <v>0.2854425463774817</v>
       </c>
       <c r="AP457" t="n">
-        <v>0.7629278075138878</v>
+        <v>0.762927807513867</v>
       </c>
       <c r="AQ457" t="n">
         <v>68.06930693069307</v>
@@ -75025,7 +75025,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.2865252693972544</v>
+        <v>-0.2865252693972545</v>
       </c>
       <c r="AN458" t="n">
         <v>-0.01327380582108439</v>
@@ -75034,7 +75034,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP458" t="n">
-        <v>0.5648982895268601</v>
+        <v>0.5648982895268598</v>
       </c>
       <c r="AQ458" t="n">
         <v>61.33004926108374</v>
@@ -75178,10 +75178,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.860047631936786</v>
+        <v>6.860047631936787</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.1030476624543644</v>
+        <v>-0.1030476624543653</v>
       </c>
       <c r="AK459" t="n">
         <v>6.865985861260643</v>
@@ -75190,16 +75190,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.290522309347949</v>
+        <v>-0.2905223093479492</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.01240158194086383</v>
+        <v>-0.01240158194086378</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3024992257449916</v>
+        <v>0.3024992257449914</v>
       </c>
       <c r="AP459" t="n">
-        <v>0.4606483756803628</v>
+        <v>0.4606483756803518</v>
       </c>
       <c r="AQ459" t="n">
         <v>57.59803921568628</v>
@@ -75343,10 +75343,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.801980414635013</v>
+        <v>6.801980414635016</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.04478065038330392</v>
+        <v>-0.04478065038330659</v>
       </c>
       <c r="AK460" t="n">
         <v>6.863576603094304</v>
@@ -75355,16 +75355,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.2950697019949103</v>
+        <v>-0.2950697019949104</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.0116105331596838</v>
+        <v>-0.01161053315968381</v>
       </c>
       <c r="AO460" t="n">
-        <v>0.3113800696686924</v>
+        <v>0.3113800696686918</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.139401850244943</v>
+        <v>1.139401850244913</v>
       </c>
       <c r="AQ460" t="n">
         <v>78.53658536585365</v>
@@ -75508,10 +75508,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.789283666813423</v>
+        <v>6.789283666813422</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.03208390256171434</v>
+        <v>-0.03208390256171256</v>
       </c>
       <c r="AK461" t="n">
         <v>6.809671190627447</v>
@@ -75520,16 +75520,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.2987092362344105</v>
+        <v>-0.2987092362344108</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.01030385953714813</v>
+        <v>-0.01030385953714808</v>
       </c>
       <c r="AO461" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.280307854289579</v>
+        <v>1.280307854289602</v>
       </c>
       <c r="AQ461" t="n">
         <v>81.55339805825244</v>
@@ -75673,10 +75673,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.789252537988938</v>
+        <v>6.789252537988933</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.02065255095890883</v>
+        <v>-0.0206525509589035</v>
       </c>
       <c r="AK462" t="n">
         <v>6.802840448144932</v>
@@ -75685,16 +75685,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3027504956929287</v>
+        <v>-0.3027504956929284</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.00881278602540958</v>
+        <v>-0.008812786025409641</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.332227117067963</v>
+        <v>0.3322271170679635</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.404215965965131</v>
+        <v>1.404215965965194</v>
       </c>
       <c r="AQ462" t="n">
         <v>82.60869565217391</v>
@@ -75838,10 +75838,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.774001672255927</v>
+        <v>6.774001672255932</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.005401685225897346</v>
+        <v>-0.005401685225902675</v>
       </c>
       <c r="AK463" t="n">
         <v>6.800260207803535</v>
@@ -75850,16 +75850,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3068099364477369</v>
+        <v>-0.3068099364477367</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.007070247176567734</v>
+        <v>-0.007070247176567688</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3427146952658529</v>
+        <v>0.3427146952658534</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.569454000696709</v>
+        <v>1.56945400069665</v>
       </c>
       <c r="AQ463" t="n">
         <v>83.41346153846153</v>
@@ -76003,10 +76003,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.802628307046305</v>
+        <v>6.802628307046303</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.0281284138578286</v>
+        <v>-0.02812841385782594</v>
       </c>
       <c r="AK464" t="n">
         <v>6.781970485204615</v>
@@ -76015,16 +76015,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3121566752204096</v>
+        <v>-0.3121566752204101</v>
       </c>
       <c r="AN464" t="n">
-        <v>-0.005102880740085192</v>
+        <v>-0.005102880740085154</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.3560731605465752</v>
+        <v>0.3560731605465757</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.296014055638977</v>
+        <v>1.29601405563901</v>
       </c>
       <c r="AQ464" t="n">
         <v>79.42583732057417</v>
@@ -76168,28 +76168,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.815944895083629</v>
+        <v>6.815944895083632</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.0259449332306021</v>
+        <v>-0.02594493323060476</v>
       </c>
       <c r="AK465" t="n">
-        <v>6.809638458820509</v>
+        <v>6.809638458820508</v>
       </c>
       <c r="AL465" t="n">
-        <v>-0.01963849696748188</v>
+        <v>-0.01963849696748099</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3181413841564625</v>
+        <v>-0.3181413841564619</v>
       </c>
       <c r="AN465" t="n">
-        <v>-0.003317316385138602</v>
+        <v>-0.003317316385138562</v>
       </c>
       <c r="AO465" t="n">
-        <v>0.3690689225934927</v>
+        <v>0.3690689225934922</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.312827614648354</v>
+        <v>1.312827614648325</v>
       </c>
       <c r="AQ465" t="n">
         <v>81.19047619047619</v>
@@ -76333,10 +76333,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.821941449304759</v>
+        <v>6.821941449304753</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.0319414874517312</v>
+        <v>-0.03194148745172587</v>
       </c>
       <c r="AK466" t="n">
         <v>6.819973703544699</v>
@@ -76345,16 +76345,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3244228225822193</v>
+        <v>-0.3244228225822198</v>
       </c>
       <c r="AN466" t="n">
-        <v>-0.001700148658338674</v>
+        <v>-0.001700148658338742</v>
       </c>
       <c r="AO466" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.235661012584512</v>
+        <v>1.235661012584574</v>
       </c>
       <c r="AQ466" t="n">
         <v>77.96208530805687</v>
@@ -76498,10 +76498,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.826413262727742</v>
+        <v>6.826413262727749</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.03641330087471495</v>
+        <v>-0.03641330087472205</v>
       </c>
       <c r="AK467" t="n">
         <v>6.822087900644207</v>
@@ -76510,16 +76510,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3308797299382499</v>
+        <v>-0.3308797299382495</v>
       </c>
       <c r="AN467" t="n">
-        <v>-7.481797733216444e-05</v>
+        <v>-7.481797733213274e-05</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.3960788710418811</v>
+        <v>0.396078871041881</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.177071213951652</v>
+        <v>1.177071213951572</v>
       </c>
       <c r="AQ467" t="n">
         <v>78.5377358490566</v>
@@ -76663,10 +76663,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.812656647679548</v>
+        <v>6.81265664767955</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.01465678882334664</v>
+        <v>-0.01465678882334931</v>
       </c>
       <c r="AK468" t="n">
         <v>6.823881638371397</v>
@@ -76675,16 +76675,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3363418922753055</v>
+        <v>-0.3363418922753058</v>
       </c>
       <c r="AN468" t="n">
-        <v>0.001379920606120022</v>
+        <v>0.001379920606120097</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4081029523904164</v>
+        <v>0.4081029523904167</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.419204189894351</v>
+        <v>1.419204189894323</v>
       </c>
       <c r="AQ468" t="n">
         <v>83.09859154929578</v>
@@ -76828,10 +76828,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI469" t="n">
-        <v>6.802797817425507</v>
+        <v>6.802797817425505</v>
       </c>
       <c r="AJ469" t="n">
-        <v>-0.009197735028045884</v>
+        <v>-0.009197735028044107</v>
       </c>
       <c r="AK469" t="n">
         <v>6.808320681191073</v>
@@ -76840,16 +76840,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3410659803634685</v>
+        <v>-0.3410659803634682</v>
       </c>
       <c r="AN469" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4198133218741356</v>
+        <v>0.4198133218741357</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.471334908821341</v>
+        <v>1.471334908821365</v>
       </c>
       <c r="AQ469" t="n">
         <v>83.17757009345794</v>
@@ -76999,22 +76999,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK470" t="n">
-        <v>6.795980661778267</v>
+        <v>6.795980661778266</v>
       </c>
       <c r="AL470" t="n">
-        <v>-0.002380579380806047</v>
+        <v>-0.002380579380805159</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3461577281601511</v>
+        <v>-0.3461577281601509</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.004282887883574671</v>
+        <v>0.00428288788357468</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4328049372030962</v>
+        <v>0.4328049372030969</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.532704943923476</v>
+        <v>1.532704943923479</v>
       </c>
       <c r="AQ470" t="n">
         <v>84.41860465116279</v>
@@ -77158,10 +77158,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.800189882196235</v>
+        <v>6.800189882196236</v>
       </c>
       <c r="AJ471" t="n">
-        <v>-0.005989938653754301</v>
+        <v>-0.005989938653755189</v>
       </c>
       <c r="AK471" t="n">
         <v>6.78726841810145</v>
@@ -77170,16 +77170,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3502903933401412</v>
+        <v>-0.3502903933401418</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.005405808652032051</v>
+        <v>0.005405808652032067</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4450018361960529</v>
+        <v>0.4450018361960534</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.485189478864212</v>
+        <v>1.485189478864205</v>
       </c>
       <c r="AQ471" t="n">
         <v>83.33333333333334</v>
@@ -77323,10 +77323,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.79797208364255</v>
+        <v>6.797972083642554</v>
       </c>
       <c r="AJ472" t="n">
-        <v>-0.009372115686007376</v>
+        <v>-0.009372115686010929</v>
       </c>
       <c r="AK472" t="n">
         <v>6.791305278184372</v>
@@ -77335,16 +77335,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM472" t="n">
-        <v>-0.3548656112706069</v>
+        <v>-0.3548656112706071</v>
       </c>
       <c r="AN472" t="n">
-        <v>0.006091291211178074</v>
+        <v>0.006091291211178139</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4593697101544711</v>
+        <v>0.4593697101544705</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.436147929377192</v>
+        <v>1.436147929377155</v>
       </c>
       <c r="AQ472" t="n">
         <v>82.02764976958525</v>
@@ -77488,10 +77488,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.800452644405181</v>
+        <v>6.800452644405178</v>
       </c>
       <c r="AJ473" t="n">
-        <v>-0.01185267644863774</v>
+        <v>-0.01185267644863508</v>
       </c>
       <c r="AK473" t="n">
         <v>6.789098969069376</v>
@@ -77506,10 +77506,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.4721687943484544</v>
+        <v>0.4721687943484545</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.398187361022222</v>
+        <v>1.398187361022255</v>
       </c>
       <c r="AQ473" t="n">
         <v>78.89908256880734</v>
@@ -77653,10 +77653,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.778720347685821</v>
+        <v>6.778720347685814</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.01707986135958883</v>
+        <v>0.01707986135959594</v>
       </c>
       <c r="AK474" t="n">
         <v>6.790465135395929</v>
@@ -77665,16 +77665,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3625273381377937</v>
+        <v>-0.3625273381377933</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.007343464385960674</v>
+        <v>0.007343464385960585</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.4863203622043377</v>
+        <v>0.4863203622043382</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.71274979796622</v>
+        <v>1.712749797966303</v>
       </c>
       <c r="AQ474" t="n">
         <v>84.01826484018265</v>
@@ -77818,10 +77818,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.769755998762547</v>
+        <v>6.769755998762545</v>
       </c>
       <c r="AJ475" t="n">
-        <v>0.02364381202846833</v>
+        <v>0.02364381202847099</v>
       </c>
       <c r="AK475" t="n">
         <v>6.767889899932765</v>
@@ -77830,16 +77830,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3660007866474812</v>
+        <v>-0.3660007866474813</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.00826013782295415</v>
+        <v>0.008260137822954145</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.4997690914082398</v>
+        <v>0.4997690914082401</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.770409513214919</v>
+        <v>1.770409513214951</v>
       </c>
       <c r="AQ475" t="n">
         <v>84.77272727272728</v>
@@ -77983,10 +77983,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.789177604754239</v>
+        <v>6.789177604754244</v>
       </c>
       <c r="AJ476" t="n">
-        <v>0.01332216636392491</v>
+        <v>0.01332216636391959</v>
       </c>
       <c r="AK476" t="n">
         <v>6.759766754404358</v>
@@ -77995,16 +77995,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3700034659576358</v>
+        <v>-0.3700034659576351</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.00987171553454691</v>
+        <v>0.009871715534546958</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5120623436103316</v>
+        <v>0.5120623436103324</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.63983383031362</v>
+        <v>1.639833830313563</v>
       </c>
       <c r="AQ476" t="n">
         <v>84.84162895927602</v>
@@ -78148,10 +78148,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI477" t="n">
-        <v>6.774331376960423</v>
+        <v>6.774331376960425</v>
       </c>
       <c r="AJ477" t="n">
-        <v>0.01776857573733093</v>
+        <v>0.01776857573732915</v>
       </c>
       <c r="AK477" t="n">
         <v>6.777856240868369</v>
@@ -78160,16 +78160,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3750442390024145</v>
+        <v>-0.3750442390024147</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01196068662558775</v>
+        <v>0.01196068662558781</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.5238651846176465</v>
+        <v>0.5238651846176463</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.67532184880636</v>
+        <v>1.675321848806344</v>
       </c>
       <c r="AQ477" t="n">
         <v>84.00900900900902</v>
@@ -78325,16 +78325,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3816350905604304</v>
+        <v>-0.3816350905604307</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01460798460929558</v>
+        <v>0.01460798460929556</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.537958310473289</v>
+        <v>0.5379583104732891</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.621777678682495</v>
+        <v>1.621777678682498</v>
       </c>
       <c r="AQ478" t="n">
         <v>84.52914798206278</v>
@@ -78478,10 +78478,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.789815280543246</v>
+        <v>6.789815280543245</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.01031527291385181</v>
+        <v>-0.01031527291385093</v>
       </c>
       <c r="AK479" t="n">
         <v>6.744939020214936</v>
@@ -78490,16 +78490,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.3872393091179336</v>
+        <v>-0.3872393091179339</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01685992867552227</v>
+        <v>0.01685992867552231</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5511317941481411</v>
+        <v>0.5511317941481415</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.3395664425942</v>
+        <v>1.339566442594212</v>
       </c>
       <c r="AQ479" t="n">
         <v>82.14285714285714</v>
@@ -78643,10 +78643,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.801295181477315</v>
+        <v>6.801295181477309</v>
       </c>
       <c r="AJ480" t="n">
-        <v>-0.03129520055080093</v>
+        <v>-0.0312952005507956</v>
       </c>
       <c r="AK480" t="n">
         <v>6.772636231606738</v>
@@ -78655,16 +78655,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.393020019860339</v>
+        <v>-0.3930200198603389</v>
       </c>
       <c r="AN480" t="n">
-        <v>0.01873686412955489</v>
+        <v>0.01873686412955481</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.5644439393662184</v>
+        <v>0.5644439393662187</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.100144262686249</v>
+        <v>1.100144262686309</v>
       </c>
       <c r="AQ480" t="n">
         <v>76.44444444444446</v>
@@ -78808,10 +78808,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.791632066062363</v>
+        <v>6.791632066062364</v>
       </c>
       <c r="AJ481" t="n">
-        <v>-0.0234321454080666</v>
+        <v>-0.02343214540806748</v>
       </c>
       <c r="AK481" t="n">
         <v>6.788619247652995</v>
@@ -78820,16 +78820,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3966294116439325</v>
+        <v>-0.3966294116439323</v>
       </c>
       <c r="AN481" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.576974471973372</v>
+        <v>0.5769744719733717</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.181475994909433</v>
+        <v>1.181475994909424</v>
       </c>
       <c r="AQ481" t="n">
         <v>74.3362831858407</v>
@@ -78973,10 +78973,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.779898505875916</v>
+        <v>6.779898505875918</v>
       </c>
       <c r="AJ482" t="n">
-        <v>-0.007398467728943814</v>
+        <v>-0.00739846772894559</v>
       </c>
       <c r="AK482" t="n">
         <v>6.776305653888958</v>
@@ -78985,16 +78985,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3980313152890726</v>
+        <v>-0.3980313152890724</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.01933124704228378</v>
+        <v>0.0193312470422838</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.5877384296086169</v>
+        <v>0.5877384296086161</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.351537097819766</v>
+        <v>1.351537097819748</v>
       </c>
       <c r="AQ482" t="n">
         <v>76.21145374449338</v>
@@ -79138,10 +79138,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.771360892616113</v>
+        <v>6.771360892616116</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.001139145530859587</v>
+        <v>0.001139145530856922</v>
       </c>
       <c r="AK483" t="n">
         <v>6.76492936370744</v>
@@ -79150,16 +79150,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.3979537985659305</v>
+        <v>-0.3979537985659302</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.0183584453609324</v>
+        <v>0.01835844536093246</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6001791687136281</v>
+        <v>0.6001791687136286</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.436676488237766</v>
+        <v>1.436676488237739</v>
       </c>
       <c r="AQ483" t="n">
         <v>77.19298245614036</v>
@@ -79303,10 +79303,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.751667781721844</v>
+        <v>6.751667781721842</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.02083225642512865</v>
+        <v>0.02083225642513042</v>
       </c>
       <c r="AK484" t="n">
         <v>6.753855191419989</v>
@@ -79315,16 +79315,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3975762425746344</v>
+        <v>-0.3975762425746347</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01731206726614276</v>
+        <v>0.01731206726614282</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6129676701055393</v>
+        <v>0.6129676701055397</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.641636380247678</v>
+        <v>1.6416363802477</v>
       </c>
       <c r="AQ484" t="n">
         <v>82.53275109170306</v>
@@ -79468,10 +79468,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.729738669869288</v>
+        <v>6.72973866986929</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.03586153459848518</v>
+        <v>0.0358615345984834</v>
       </c>
       <c r="AK485" t="n">
         <v>6.736226026398153</v>
@@ -79480,16 +79480,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.3964908591695859</v>
+        <v>-0.3964908591695858</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01740130648959376</v>
+        <v>0.01740130648959375</v>
       </c>
       <c r="AO485" t="n">
-        <v>0.6198907013195262</v>
+        <v>0.6198907013195265</v>
       </c>
       <c r="AP485" t="n">
-        <v>1.79103092398715</v>
+        <v>1.791030923987134</v>
       </c>
       <c r="AQ485" t="n">
         <v>80</v>
@@ -79633,10 +79633,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.713320364291503</v>
+        <v>6.713320364291505</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.05917967385546952</v>
+        <v>0.05917967385546774</v>
       </c>
       <c r="AK486" t="n">
         <v>6.717723214958548</v>
@@ -79645,16 +79645,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM486" t="n">
-        <v>-0.394760534481672</v>
+        <v>-0.3947605344816719</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.01742962324324016</v>
+        <v>0.01742962324324019</v>
       </c>
       <c r="AO486" t="n">
-        <v>0.6272835381163622</v>
+        <v>0.6272835381163618</v>
       </c>
       <c r="AP486" t="n">
-        <v>2.02460994407845</v>
+        <v>2.024609944078435</v>
       </c>
       <c r="AQ486" t="n">
         <v>86.7965367965368</v>
@@ -79798,10 +79798,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.731179671396989</v>
+        <v>6.731179671396997</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.04132036674998396</v>
+        <v>0.04132036674997597</v>
       </c>
       <c r="AK487" t="n">
         <v>6.699415101064979</v>
@@ -79813,13 +79813,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.01766596732646103</v>
+        <v>0.0176659673264611</v>
       </c>
       <c r="AO487" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.812586682659243</v>
+        <v>1.812586682659161</v>
       </c>
       <c r="AQ487" t="n">
         <v>86.20689655172413</v>
@@ -79963,10 +79963,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.740946959621007</v>
+        <v>6.740946959621005</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.03085308157772371</v>
+        <v>0.03085308157772548</v>
       </c>
       <c r="AK488" t="n">
         <v>6.714685154719483</v>
@@ -79975,16 +79975,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3929423394238508</v>
+        <v>-0.392942339423851</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.01842070378092631</v>
+        <v>0.0184207037809263</v>
       </c>
       <c r="AO488" t="n">
-        <v>0.640374511165978</v>
+        <v>0.6403745111659787</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.684785401375863</v>
+        <v>1.684785401375887</v>
       </c>
       <c r="AQ488" t="n">
         <v>84.12017167381974</v>
@@ -80128,10 +80128,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.7589577577717</v>
+        <v>6.758957757771704</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.006742105662137732</v>
+        <v>0.006742105662134179</v>
       </c>
       <c r="AK489" t="n">
         <v>6.722064699270507</v>
@@ -80140,16 +80140,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.3931401656438959</v>
+        <v>-0.3931401656438955</v>
       </c>
       <c r="AN489" t="n">
-        <v>0.01902711841846483</v>
+        <v>0.01902711841846487</v>
       </c>
       <c r="AO489" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.414712695882816</v>
+        <v>1.414712695882782</v>
       </c>
       <c r="AQ489" t="n">
         <v>79.91452991452991</v>
@@ -80293,10 +80293,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI490" t="n">
-        <v>6.763209774497792</v>
+        <v>6.763209774497788</v>
       </c>
       <c r="AJ490" t="n">
-        <v>0.007790133949473699</v>
+        <v>0.007790133949477251</v>
       </c>
       <c r="AK490" t="n">
         <v>6.739235851443908</v>
@@ -80305,16 +80305,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3951733572725242</v>
+        <v>-0.3951733572725246</v>
       </c>
       <c r="AN490" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6590798145480943</v>
+        <v>0.6590798145480942</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.41686071620646</v>
+        <v>1.416860716206502</v>
       </c>
       <c r="AQ490" t="n">
         <v>80.21276595744681</v>
@@ -80470,16 +80470,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.3960001863323608</v>
+        <v>-0.396000186332361</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02043272610569408</v>
+        <v>0.02043272610569401</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.6685846444009622</v>
+        <v>0.6685846444009627</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.599280092475873</v>
+        <v>1.599280092475877</v>
       </c>
       <c r="AQ491" t="n">
         <v>80.72033898305085</v>
@@ -80623,10 +80623,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.714622134232894</v>
+        <v>6.714622134232888</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.04037798020802441</v>
+        <v>0.04037798020802974</v>
       </c>
       <c r="AK492" t="n">
         <v>6.746779913842831</v>
@@ -80635,16 +80635,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM492" t="n">
-        <v>-0.396740905361911</v>
+        <v>-0.3967409053619114</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.02120763540003751</v>
+        <v>0.02120763540003743</v>
       </c>
       <c r="AO492" t="n">
-        <v>0.6777865296786982</v>
+        <v>0.6777865296786978</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.740194523547664</v>
+        <v>1.740194523547725</v>
       </c>
       <c r="AQ492" t="n">
         <v>83.33333333333334</v>
@@ -80788,28 +80788,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.731570059394423</v>
+        <v>6.73157005939442</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.01932973232310609</v>
+        <v>0.01932973232310964</v>
       </c>
       <c r="AK493" t="n">
-        <v>6.728823425344638</v>
+        <v>6.728823425344639</v>
       </c>
       <c r="AL493" t="n">
-        <v>0.02207636637289134</v>
+        <v>0.02207636637289045</v>
       </c>
       <c r="AM493" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.0220082962170377</v>
+        <v>0.02200829621703764</v>
       </c>
       <c r="AO493" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.504731032544637</v>
+        <v>1.504731032544678</v>
       </c>
       <c r="AQ493" t="n">
         <v>78.78151260504201</v>
@@ -80953,10 +80953,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.748064561399866</v>
+        <v>6.748064561399863</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.004235224214148126</v>
+        <v>0.00423522421415079</v>
       </c>
       <c r="AK494" t="n">
         <v>6.740096815166266</v>
@@ -80965,16 +80965,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.3976889317784199</v>
+        <v>-0.3976889317784196</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02268190844878654</v>
+        <v>0.02268190844878653</v>
       </c>
       <c r="AO494" t="n">
-        <v>0.6953567146475523</v>
+        <v>0.6953567146475526</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.33593563729874</v>
+        <v>1.33593563729877</v>
       </c>
       <c r="AQ494" t="n">
         <v>73.84937238493724</v>
@@ -81118,10 +81118,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.747226278872152</v>
+        <v>6.747226278872151</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.005973775296548745</v>
+        <v>0.005973775296550521</v>
       </c>
       <c r="AK495" t="n">
         <v>6.755554272205931</v>
@@ -81130,16 +81130,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.4003515275861345</v>
+        <v>-0.400351527586135</v>
       </c>
       <c r="AN495" t="n">
-        <v>0.02398656672240618</v>
+        <v>0.02398656672240616</v>
       </c>
       <c r="AO495" t="n">
-        <v>0.7067969646460921</v>
+        <v>0.7067969646460924</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.346470010405854</v>
+        <v>1.346470010405875</v>
       </c>
       <c r="AQ495" t="n">
         <v>73.54166666666667</v>
@@ -81283,10 +81283,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.724989986752571</v>
+        <v>6.724989986752573</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.02471008267491914</v>
+        <v>0.02471008267491737</v>
       </c>
       <c r="AK496" t="n">
         <v>6.75925064743029</v>
@@ -81295,7 +81295,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4017887258056133</v>
+        <v>-0.4017887258056131</v>
       </c>
       <c r="AN496" t="n">
         <v>0.02482212216928553</v>
@@ -81304,7 +81304,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.534738827052774</v>
+        <v>1.534738827052756</v>
       </c>
       <c r="AQ496" t="n">
         <v>76.97095435684648</v>
@@ -81448,28 +81448,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.738231277482312</v>
+        <v>6.738231277482303</v>
       </c>
       <c r="AJ497" t="n">
-        <v>0.01056852339049108</v>
+        <v>0.01056852339049996</v>
       </c>
       <c r="AK497" t="n">
-        <v>6.734775445902895</v>
+        <v>6.734775445902896</v>
       </c>
       <c r="AL497" t="n">
-        <v>0.01402435496990773</v>
+        <v>0.01402435496990684</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4022294042554291</v>
+        <v>-0.402229404255429</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02545790195722747</v>
+        <v>0.02545790195722734</v>
       </c>
       <c r="AO497" t="n">
-        <v>0.7273309315128231</v>
+        <v>0.7273309315128232</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.376586915245184</v>
+        <v>1.376586915245278</v>
       </c>
       <c r="AQ497" t="n">
         <v>74.3801652892562</v>
@@ -81613,10 +81613,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.718201282169581</v>
+        <v>6.718201282169575</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.02919852480673768</v>
+        <v>0.02919852480674301</v>
       </c>
       <c r="AK498" t="n">
         <v>6.753996132599221</v>
@@ -81625,16 +81625,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4027953816469058</v>
+        <v>-0.4027953816469059</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02608258444417638</v>
+        <v>0.02608258444417639</v>
       </c>
       <c r="AO498" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.562402624386248</v>
+        <v>1.562402624386304</v>
       </c>
       <c r="AQ498" t="n">
         <v>78.18930041152262</v>
@@ -81778,10 +81778,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI499" t="n">
-        <v>6.730898772467414</v>
+        <v>6.730898772467415</v>
       </c>
       <c r="AJ499" t="n">
-        <v>0.01650103450890406</v>
+        <v>0.01650103450890317</v>
       </c>
       <c r="AK499" t="n">
         <v>6.732394407262716</v>
@@ -81790,16 +81790,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.4025099007694142</v>
+        <v>-0.402509900769414</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02634377330607651</v>
+        <v>0.02634377330607648</v>
       </c>
       <c r="AO499" t="n">
-        <v>0.746561519528266</v>
+        <v>0.7465615195282662</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.419661467469252</v>
+        <v>1.419661467469243</v>
       </c>
       <c r="AQ499" t="n">
         <v>78.68852459016394</v>
@@ -81955,16 +81955,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4034224290251451</v>
+        <v>-0.4034224290251453</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02736182786837871</v>
+        <v>0.02736182786837866</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.755189863471066</v>
+        <v>0.7551898634710656</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.285527143558827</v>
+        <v>1.285527143558826</v>
       </c>
       <c r="AQ500" t="n">
         <v>76.73469387755102</v>
@@ -82108,10 +82108,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.755708466794879</v>
+        <v>6.75570846679488</v>
       </c>
       <c r="AJ501" t="n">
-        <v>-0.01240850570479068</v>
+        <v>-0.01240850570479246</v>
       </c>
       <c r="AK501" t="n">
         <v>6.746865899087779</v>
@@ -82120,16 +82120,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.4037073020769307</v>
+        <v>-0.4037073020769305</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02778289906564352</v>
+        <v>0.02778289906564353</v>
       </c>
       <c r="AO501" t="n">
-        <v>0.7638221248099442</v>
+        <v>0.7638221248099444</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.103708249482004</v>
+        <v>1.103708249481985</v>
       </c>
       <c r="AQ501" t="n">
         <v>79.47154471544715</v>
@@ -82273,10 +82273,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI502" t="n">
-        <v>6.73601646973098</v>
+        <v>6.73601646973097</v>
       </c>
       <c r="AJ502" t="n">
-        <v>0.006783766017311343</v>
+        <v>0.006783766017321113</v>
       </c>
       <c r="AK502" t="n">
         <v>6.761018647414997</v>
@@ -82285,16 +82285,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM502" t="n">
-        <v>-0.403510818895136</v>
+        <v>-0.4035108188951355</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02805871830419215</v>
+        <v>0.02805871830419202</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.298142681594672</v>
+        <v>1.298142681594773</v>
       </c>
       <c r="AQ502" t="n">
         <v>83.19838056680162</v>
@@ -82453,13 +82453,13 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02827333203020888</v>
+        <v>0.02827333203020884</v>
       </c>
       <c r="AO503" t="n">
         <v>0.7726830480787004</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.383694782072955</v>
+        <v>1.383694782072954</v>
       </c>
       <c r="AQ503" t="n">
         <v>83.66935483870968</v>
@@ -82603,10 +82603,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.725806144687715</v>
+        <v>6.725806144687716</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.01409396746438496</v>
+        <v>0.01409396746438318</v>
       </c>
       <c r="AK504" t="n">
         <v>6.744478107428201</v>
@@ -82615,16 +82615,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.4027900432658338</v>
+        <v>-0.4027900432658339</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.02891453613228628</v>
+        <v>0.0289145361322863</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7784357006627721</v>
+        <v>0.7784357006627718</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.358780907702651</v>
+        <v>1.358780907702631</v>
       </c>
       <c r="AQ504" t="n">
         <v>83.13253012048193</v>
@@ -82768,10 +82768,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.700854569500288</v>
+        <v>6.700854569500285</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.04174539464155735</v>
+        <v>0.04174539464156091</v>
       </c>
       <c r="AK505" t="n">
         <v>6.743301592583855</v>
@@ -82780,16 +82780,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.402742697458547</v>
+        <v>-0.4027426974585472</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.02955568036482276</v>
+        <v>0.0295556803648227</v>
       </c>
       <c r="AO505" t="n">
-        <v>0.7839391318357882</v>
+        <v>0.7839391318357879</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.635541400731503</v>
+        <v>1.635541400731539</v>
       </c>
       <c r="AQ505" t="n">
         <v>88</v>
@@ -82933,10 +82933,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.705597066237452</v>
+        <v>6.705597066237454</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.02390275065707925</v>
+        <v>0.02390275065707748</v>
       </c>
       <c r="AK506" t="n">
         <v>6.74285285202661</v>
@@ -82945,16 +82945,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM506" t="n">
-        <v>-0.401588500320058</v>
+        <v>-0.4015885003200582</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.02985284499018426</v>
+        <v>0.02985284499018428</v>
       </c>
       <c r="AO506" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.443037887227161</v>
+        <v>1.443037887227141</v>
       </c>
       <c r="AQ506" t="n">
         <v>84.8</v>
@@ -83098,28 +83098,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.686024746022946</v>
+        <v>6.686024746022948</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.0364751013891631</v>
+        <v>0.03647510138916132</v>
       </c>
       <c r="AK507" t="n">
-        <v>6.744526329542678</v>
+        <v>6.744526329542679</v>
       </c>
       <c r="AL507" t="n">
-        <v>-0.02202648213056868</v>
+        <v>-0.02202648213056957</v>
       </c>
       <c r="AM507" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.02995529076246445</v>
+        <v>0.02995529076246446</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.7933293013213367</v>
+        <v>0.7933293013213371</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.566099953457567</v>
+        <v>1.566099953457549</v>
       </c>
       <c r="AQ507" t="n">
         <v>84.2</v>
@@ -83263,10 +83263,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.689653251437546</v>
+        <v>6.689653251437547</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.03134694311201436</v>
+        <v>0.03134694311201347</v>
       </c>
       <c r="AK508" t="n">
         <v>6.730402461316146</v>
@@ -83275,16 +83275,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3993041981056888</v>
+        <v>-0.3993041981056886</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03010093147709741</v>
+        <v>0.03010093147709737</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.7985853639949437</v>
+        <v>0.7985853639949436</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.507036858820243</v>
+        <v>1.507036858820233</v>
       </c>
       <c r="AQ508" t="n">
         <v>85</v>
@@ -83428,10 +83428,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.716786041117415</v>
+        <v>6.716786041117424</v>
       </c>
       <c r="AJ509" t="n">
-        <v>0.00511394514967467</v>
+        <v>0.005113945149665788</v>
       </c>
       <c r="AK509" t="n">
         <v>6.728106442363027</v>
@@ -83440,16 +83440,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM509" t="n">
-        <v>-0.3976134529492091</v>
+        <v>-0.3976134529492094</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03006044259180324</v>
+        <v>0.03006044259180338</v>
       </c>
       <c r="AO509" t="n">
-        <v>0.8026437279892851</v>
+        <v>0.8026437279892848</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.234777974751978</v>
+        <v>1.234777974751887</v>
       </c>
       <c r="AQ509" t="n">
         <v>81.59999999999999</v>
@@ -83593,10 +83593,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.721932795514441</v>
+        <v>6.72193279551444</v>
       </c>
       <c r="AJ510" t="n">
-        <v>-0.001632597913122424</v>
+        <v>-0.001632597913121536</v>
       </c>
       <c r="AK510" t="n">
         <v>6.752314636061016</v>
@@ -83608,13 +83608,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03043336917902489</v>
+        <v>0.03043336917902487</v>
       </c>
       <c r="AO510" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.163823515923089</v>
+        <v>1.163823515923099</v>
       </c>
       <c r="AQ510" t="n">
         <v>82.19999999999999</v>
@@ -83758,28 +83758,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.718669003366535</v>
+        <v>6.718669003366529</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.003830844045574544</v>
+        <v>0.003830844045580761</v>
       </c>
       <c r="AK511" t="n">
-        <v>6.750203856204787</v>
+        <v>6.750203856204786</v>
       </c>
       <c r="AL511" t="n">
-        <v>-0.02770400879267765</v>
+        <v>-0.02770400879267676</v>
       </c>
       <c r="AM511" t="n">
-        <v>-0.3969152632178358</v>
+        <v>-0.3969152632178359</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03100517332816438</v>
+        <v>0.03100517332816427</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8091236362457368</v>
+        <v>0.8091236362457366</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.217453571381047</v>
+        <v>1.217453571381111</v>
       </c>
       <c r="AQ511" t="n">
         <v>82.80000000000001</v>
@@ -83923,10 +83923,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.680190080689523</v>
+        <v>6.680190080689519</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.04230976672258624</v>
+        <v>0.04230976672259068</v>
       </c>
       <c r="AK512" t="n">
         <v>6.74780904069481</v>
@@ -83935,16 +83935,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM512" t="n">
-        <v>-0.3964565291282772</v>
+        <v>-0.3964565291282773</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03139664408873172</v>
+        <v>0.03139664408873165</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8123541153569376</v>
+        <v>0.8123541153569371</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.604493248424094</v>
+        <v>1.60449324842414</v>
       </c>
       <c r="AQ512" t="n">
         <v>89.8</v>
@@ -84088,10 +84088,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.671580974366952</v>
+        <v>6.671580974366949</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.05441885778636824</v>
+        <v>0.05441885778637179</v>
       </c>
       <c r="AK513" t="n">
         <v>6.701878095437348</v>
@@ -84103,13 +84103,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.03163116863423027</v>
+        <v>0.03163116863423025</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8147568654710424</v>
+        <v>0.8147568654710426</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.717274375116458</v>
+        <v>1.717274375116493</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.2</v>
@@ -84253,28 +84253,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI514" t="n">
-        <v>6.656216276126097</v>
+        <v>6.656216276126093</v>
       </c>
       <c r="AJ514" t="n">
-        <v>0.06978355602722353</v>
+        <v>0.06978355602722708</v>
       </c>
       <c r="AK514" t="n">
-        <v>6.701765808189924</v>
+        <v>6.701765808189925</v>
       </c>
       <c r="AL514" t="n">
-        <v>0.02423402396339647</v>
+        <v>0.02423402396339558</v>
       </c>
       <c r="AM514" t="n">
-        <v>-0.3932426568003564</v>
+        <v>-0.3932426568003567</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.0319127327617218</v>
+        <v>0.03191273276172183</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8170879052811413</v>
+        <v>0.8170879052811416</v>
       </c>
       <c r="AP514" t="n">
-        <v>1.858889534485343</v>
+        <v>1.858889534485378</v>
       </c>
       <c r="AQ514" t="n">
         <v>90.59999999999999</v>
@@ -84424,22 +84424,22 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK515" t="n">
-        <v>6.682658801267993</v>
+        <v>6.682658801267994</v>
       </c>
       <c r="AL515" t="n">
-        <v>0.03754126053010243</v>
+        <v>0.03754126053010154</v>
       </c>
       <c r="AM515" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN515" t="n">
-        <v>0.03225018457163042</v>
+        <v>0.03225018457163047</v>
       </c>
       <c r="AO515" t="n">
-        <v>0.8195353634242114</v>
+        <v>0.8195353634242113</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.818117584748587</v>
+        <v>1.818117584748586</v>
       </c>
       <c r="AQ515" t="n">
         <v>90.2</v>
@@ -84583,10 +84583,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.654231073451243</v>
+        <v>6.654231073451242</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.06476878921965579</v>
+        <v>0.06476878921965668</v>
       </c>
       <c r="AK516" t="n">
         <v>6.682840937292736</v>
@@ -84595,16 +84595,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM516" t="n">
-        <v>-0.3894836768645471</v>
+        <v>-0.3894836768645476</v>
       </c>
       <c r="AN516" t="n">
-        <v>0.03277193700354208</v>
+        <v>0.03277193700354209</v>
       </c>
       <c r="AO516" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.781104797300566</v>
+        <v>1.781104797300574</v>
       </c>
       <c r="AQ516" t="n">
         <v>90.2</v>
@@ -84748,10 +84748,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.650937329061554</v>
+        <v>6.650937329061552</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.06806253360934456</v>
+        <v>0.06806253360934633</v>
       </c>
       <c r="AK517" t="n">
         <v>6.698821600583909</v>
@@ -84760,16 +84760,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.3885003849593205</v>
+        <v>-0.3885003849593203</v>
       </c>
       <c r="AN517" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8264954348925954</v>
+        <v>0.8264954348925952</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.79987483353635</v>
+        <v>1.799874833536366</v>
       </c>
       <c r="AQ517" t="n">
         <v>91</v>
@@ -84913,10 +84913,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI518" t="n">
-        <v>6.651733245487365</v>
+        <v>6.651733245487366</v>
       </c>
       <c r="AJ518" t="n">
-        <v>0.05906692541107272</v>
+        <v>0.05906692541107184</v>
       </c>
       <c r="AK518" t="n">
         <v>6.69208631505748</v>
@@ -84925,16 +84925,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM518" t="n">
-        <v>-0.3869746098498524</v>
+        <v>-0.3869746098498528</v>
       </c>
       <c r="AN518" t="n">
-        <v>0.0344188897752209</v>
+        <v>0.03441888977522091</v>
       </c>
       <c r="AO518" t="n">
-        <v>0.8294137131605728</v>
+        <v>0.8294137131605726</v>
       </c>
       <c r="AP518" t="n">
-        <v>1.696616308981455</v>
+        <v>1.696616308981445</v>
       </c>
       <c r="AQ518" t="n">
         <v>90.40000000000001</v>
@@ -85078,10 +85078,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.632036771677474</v>
+        <v>6.632036771677475</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.07876339922096331</v>
+        <v>0.07876339922096243</v>
       </c>
       <c r="AK519" t="n">
         <v>6.692627206904497</v>
@@ -85099,7 +85099,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP519" t="n">
-        <v>1.875440190456855</v>
+        <v>1.875440190456845</v>
       </c>
       <c r="AQ519" t="n">
         <v>91</v>
@@ -85243,10 +85243,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI520" t="n">
-        <v>6.617259294346139</v>
+        <v>6.617259294346145</v>
       </c>
       <c r="AJ520" t="n">
-        <v>0.09324046914263029</v>
+        <v>0.09324046914262496</v>
       </c>
       <c r="AK520" t="n">
         <v>6.685306332307247</v>
@@ -85258,13 +85258,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03459091746240417</v>
+        <v>0.03459091746240425</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8328314813119074</v>
+        <v>0.8328314813119078</v>
       </c>
       <c r="AP520" t="n">
-        <v>1.998006000856746</v>
+        <v>1.998006000856694</v>
       </c>
       <c r="AQ520" t="n">
         <v>91</v>
@@ -85420,13 +85420,13 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM521" t="n">
-        <v>-0.379198503222778</v>
+        <v>-0.3791985032227784</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03468237364461174</v>
+        <v>0.03468237364461172</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8349203610870053</v>
+        <v>0.8349203610870052</v>
       </c>
       <c r="AP521" t="n">
         <v>2.317228225252931</v>
@@ -85588,10 +85588,10 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03437427878524163</v>
+        <v>0.0343742787852416</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8337972329517069</v>
+        <v>0.8337972329517072</v>
       </c>
       <c r="AP522" t="n">
         <v>2.426255822246374</v>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -85347,13 +85347,13 @@
         <v>1.48</v>
       </c>
       <c r="R521" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="S521" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="T521" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U521" t="n">
         <v>-3.357531583688344</v>
@@ -85365,10 +85365,10 @@
         <v>-1.603017957351371</v>
       </c>
       <c r="X521" t="n">
-        <v>1.128372874073991</v>
+        <v>1.197250761503854</v>
       </c>
       <c r="Y521" t="n">
-        <v>38.95582329317269</v>
+        <v>39.3574297188755</v>
       </c>
       <c r="Z521" t="inlineStr">
         <is>
@@ -85391,7 +85391,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="AF521" t="n">
-        <v>0.9462528740739939</v>
+        <v>1.015130761503857</v>
       </c>
       <c r="AG521" t="n">
         <v>6.931259412128282</v>
@@ -85464,25 +85464,25 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>4.63</v>
+        <v>4.65</v>
       </c>
       <c r="C522" t="n">
         <v>1.2436</v>
       </c>
       <c r="D522" t="n">
-        <v>3.3834</v>
+        <v>3.406400000000001</v>
       </c>
       <c r="E522" t="n">
-        <v>6.706099987030029</v>
+        <v>6.708000183105469</v>
       </c>
       <c r="F522" t="n">
-        <v>6.709149837493896</v>
+        <v>6.706120014190674</v>
       </c>
       <c r="G522" t="n">
         <v>6.6977</v>
       </c>
       <c r="H522" t="n">
-        <v>0.003049850463867188</v>
+        <v>-0.001880168914794922</v>
       </c>
       <c r="I522" t="n">
         <v>99.12000274658203</v>
@@ -85491,49 +85491,49 @@
         <v>0</v>
       </c>
       <c r="K522" t="n">
-        <v>3.3834</v>
+        <v>3.406400000000001</v>
       </c>
       <c r="L522" t="n">
-        <v>3.09854</v>
+        <v>3.09969</v>
       </c>
       <c r="M522" t="n">
-        <v>2.99448</v>
+        <v>2.994863333333333</v>
       </c>
       <c r="N522" t="n">
-        <v>2.837971666666667</v>
+        <v>2.838163333333333</v>
       </c>
       <c r="O522" t="n">
-        <v>99.80000000000001</v>
+        <v>100</v>
       </c>
       <c r="P522" t="n">
-        <v>99.9001996007984</v>
+        <v>100</v>
       </c>
       <c r="Q522" t="n">
         <v>1.48</v>
       </c>
       <c r="R522" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="S522" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="T522" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U522" t="n">
-        <v>-3.770936241008185</v>
+        <v>-3.701891751410343</v>
       </c>
       <c r="V522" t="n">
         <v>6.5096</v>
       </c>
       <c r="W522" t="n">
-        <v>-2.930167868210609</v>
+        <v>-2.957665141470223</v>
       </c>
       <c r="X522" t="n">
-        <v>-0.255579052970023</v>
+        <v>-0.2163235751241555</v>
       </c>
       <c r="Y522" t="n">
-        <v>7.630522088353414</v>
+        <v>8.835341365461847</v>
       </c>
       <c r="Z522" t="inlineStr">
         <is>
@@ -85556,25 +85556,25 @@
         <v>1.984126984126984</v>
       </c>
       <c r="AF522" t="n">
-        <v>-0.4376990529700198</v>
+        <v>-0.3984435751241522</v>
       </c>
       <c r="AG522" t="n">
-        <v>6.95898274179919</v>
+        <v>6.956323088568441</v>
       </c>
       <c r="AH522" t="n">
-        <v>-0.2528827547691606</v>
+        <v>-0.2483229054629721</v>
       </c>
       <c r="AI522" t="n">
-        <v>6.567838465599584</v>
+        <v>6.559361964677803</v>
       </c>
       <c r="AJ522" t="n">
-        <v>0.1382615214304455</v>
+        <v>0.1486382184276662</v>
       </c>
       <c r="AK522" t="n">
         <v>6.617345065810827</v>
       </c>
       <c r="AL522" t="n">
-        <v>0.08875492121920203</v>
+        <v>0.09065511729464149</v>
       </c>
       <c r="AM522" t="n">
         <v>-0.3685435183382903</v>
@@ -85586,13 +85586,13 @@
         <v>0.8313650598704547</v>
       </c>
       <c r="AP522" t="n">
-        <v>2.341940497809787</v>
+        <v>2.437784108534264</v>
       </c>
       <c r="AQ522" t="n">
-        <v>91.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AR522" t="n">
-        <v>-0.005416740220768371</v>
+        <v>-0.005419845950007125</v>
       </c>
       <c r="AS522" t="n">
         <v>6.7778000831604</v>
@@ -85616,10 +85616,10 @@
         <v>3.125</v>
       </c>
       <c r="AZ522" t="n">
-        <v>63.50375</v>
+        <v>63.69374999999999</v>
       </c>
       <c r="BA522" t="n">
-        <v>63.55028270541696</v>
+        <v>63.58828270541697</v>
       </c>
     </row>
   </sheetData>
@@ -85846,7 +85846,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -85861,7 +85861,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -85881,12 +85881,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -85896,12 +85896,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -85936,7 +85936,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -85946,7 +85946,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -85971,7 +85971,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41361,10 +41361,10 @@
         <v/>
       </c>
       <c r="AI254" t="n">
-        <v>7.164454424594246</v>
+        <v>7.164454424594245</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.02545448562940233</v>
+        <v>-0.02545448562940145</v>
       </c>
       <c r="AK254" t="n">
         <v>7.171026992419335</v>
@@ -41373,13 +41373,13 @@
         <v>-0.03202705345449175</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1023969939185646</v>
+        <v>0.1023969939185656</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002417390403537972</v>
+        <v>0.002417390403537929</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2665217851726001</v>
+        <v>0.2665217851725994</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41522,10 +41522,10 @@
         <v/>
       </c>
       <c r="AI255" t="n">
-        <v>7.160742529934239</v>
+        <v>7.16074252993424</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.01934266955215858</v>
+        <v>-0.01934266955216035</v>
       </c>
       <c r="AK255" t="n">
         <v>7.166224790710233</v>
@@ -41534,13 +41534,13 @@
         <v>-0.02482493032815292</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.1026368091542314</v>
+        <v>0.1026368091542317</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002433131908989014</v>
+        <v>0.002433131908989026</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2688740668038477</v>
+        <v>0.2688740668038501</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41687,10 +41687,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.150419484347116</v>
+        <v>7.150419484347115</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.009019623965035528</v>
+        <v>-0.00901962396503464</v>
       </c>
       <c r="AK256" t="n">
         <v>7.161074530187645</v>
@@ -41699,13 +41699,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.1029385549788083</v>
+        <v>0.102938554978808</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002436328878122382</v>
+        <v>0.002436328878122375</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2711996176877891</v>
+        <v>0.2711996176877889</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41852,10 +41852,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.148511457776028</v>
+        <v>7.14851145777603</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.01601128611465086</v>
+        <v>-0.01601128611465263</v>
       </c>
       <c r="AK257" t="n">
         <v>7.150963414761942</v>
@@ -41864,13 +41864,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.1011329645838851</v>
+        <v>0.1011329645838857</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002517185580011447</v>
+        <v>0.002517185580011383</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2709113683260677</v>
+        <v>0.2709113683260674</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42029,13 +42029,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.09870181295186471</v>
+        <v>0.09870181295186436</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.002644711580562537</v>
+        <v>0.002644711580562605</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2704892730019304</v>
+        <v>0.2704892730019285</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42182,10 +42182,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI259" t="n">
-        <v>7.153772633426659</v>
+        <v>7.153772633426657</v>
       </c>
       <c r="AJ259" t="n">
-        <v>-0.03287247931288917</v>
+        <v>-0.03287247931288739</v>
       </c>
       <c r="AK259" t="n">
         <v>7.154757231824306</v>
@@ -42194,13 +42194,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.09555831842873846</v>
+        <v>0.09555831842873888</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.002822832879878071</v>
+        <v>0.002822832879878049</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2697410008595936</v>
+        <v>0.2697410008595938</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42347,10 +42347,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI260" t="n">
-        <v>7.153331199414496</v>
+        <v>7.153331199414497</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-0.03263131690717191</v>
+        <v>-0.0326313169071728</v>
       </c>
       <c r="AK260" t="n">
         <v>7.15450652143491</v>
@@ -42359,13 +42359,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.0918844066524992</v>
+        <v>0.09188440665249918</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003041971996730133</v>
+        <v>0.003041971996730116</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2698098046976256</v>
+        <v>0.2698098046976254</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42512,10 +42512,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.156943148319592</v>
+        <v>7.15694314831959</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.03854305142628167</v>
+        <v>-0.0385430514262799</v>
       </c>
       <c r="AK261" t="n">
         <v>7.154505434137821</v>
@@ -42524,13 +42524,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.08748497753913406</v>
+        <v>0.08748497753913362</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003298336925509862</v>
+        <v>0.003298336925509857</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2682008942988235</v>
+        <v>0.2682008942988222</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42689,13 +42689,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.0824587084059305</v>
+        <v>0.08245870840593096</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.003602928090795432</v>
+        <v>0.003602928090795422</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2685806390401517</v>
+        <v>0.2685806390401518</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42857,10 +42857,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.003819541738581442</v>
+        <v>0.003819541738581439</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2696768907787764</v>
+        <v>0.2696768907787754</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43007,10 +43007,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.154685377655177</v>
+        <v>7.154685377655176</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.04048526245131967</v>
+        <v>-0.04048526245131878</v>
       </c>
       <c r="AK264" t="n">
         <v>7.15808570026938</v>
@@ -43019,13 +43019,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.07200163454913491</v>
+        <v>0.07200163454913533</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.004193740708391541</v>
+        <v>0.004193740708391577</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.270116598814735</v>
+        <v>0.2701165988147326</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43172,10 +43172,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.158449213455076</v>
+        <v>7.158449213455078</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.05514911885058371</v>
+        <v>-0.05514911885058549</v>
       </c>
       <c r="AK265" t="n">
         <v>7.157644979270017</v>
@@ -43184,13 +43184,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.06676111471939408</v>
+        <v>0.06676111471939436</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.00450521933759436</v>
+        <v>0.004505219337594384</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.2733976337163381</v>
+        <v>0.2733976337163387</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43337,10 +43337,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI266" t="n">
-        <v>7.160761769069204</v>
+        <v>7.160761769069201</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-0.04786198879576631</v>
+        <v>-0.04786198879576364</v>
       </c>
       <c r="AK266" t="n">
         <v>7.159146249199162</v>
@@ -43349,10 +43349,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.06148465881746725</v>
+        <v>0.06148465881746766</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.004852471327681615</v>
+        <v>0.004852471327681566</v>
       </c>
       <c r="AO266" t="n">
         <v>0.2778048766368325</v>
@@ -43502,10 +43502,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.162478122158095</v>
+        <v>7.162478122158094</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04957834188465782</v>
+        <v>-0.04957834188465693</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159578986975002</v>
@@ -43514,13 +43514,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.05582594297075769</v>
+        <v>0.05582594297075712</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.005234102211236422</v>
+        <v>0.005234102211236467</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.282448024375059</v>
+        <v>0.2824480243750598</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43679,13 +43679,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.04949165986049534</v>
+        <v>0.04949165986049463</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.005677665039252891</v>
+        <v>0.005677665039252918</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.2878618994559775</v>
+        <v>0.2878618994559794</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43844,13 +43844,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.04287777011073584</v>
+        <v>0.04287777011073606</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.006155260602669632</v>
+        <v>0.006155260602669625</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.2948468705933219</v>
+        <v>0.2948468705933236</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -43997,10 +43997,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.173971773133425</v>
+        <v>7.173971773133423</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.04247200582995792</v>
+        <v>-0.04247200582995614</v>
       </c>
       <c r="AK270" t="n">
         <v>7.159255388854645</v>
@@ -44009,13 +44009,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.0348694200966178</v>
+        <v>0.03486942009661778</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.006728155724408227</v>
+        <v>0.006728155724408201</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.304499875642397</v>
+        <v>0.3044998756423967</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44162,25 +44162,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.172030417300567</v>
+        <v>7.172030417300565</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.03823038754592822</v>
+        <v>-0.03823038754592645</v>
       </c>
       <c r="AK271" t="n">
-        <v>7.167062070913353</v>
+        <v>7.167062070913352</v>
       </c>
       <c r="AL271" t="n">
-        <v>-0.03326204115871434</v>
+        <v>-0.03326204115871345</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.03279550096037902</v>
+        <v>0.03279550096037874</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.006903991232239788</v>
+        <v>0.006903991232239758</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3170366335916601</v>
+        <v>0.3170366335916608</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44327,10 +44327,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.171236182927453</v>
+        <v>7.171236182927454</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.03843608069356641</v>
+        <v>-0.0384360806935673</v>
       </c>
       <c r="AK272" t="n">
         <v>7.16747443083108</v>
@@ -44339,13 +44339,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.02972414459983895</v>
+        <v>0.02972414459983913</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.007158147882858998</v>
+        <v>0.007158147882859</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3270754385893867</v>
+        <v>0.3270754385893863</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44492,10 +44492,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.170425137628191</v>
+        <v>7.170425137628194</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.05102511321412884</v>
+        <v>-0.0510251132141315</v>
       </c>
       <c r="AK273" t="n">
         <v>7.168373097443463</v>
@@ -44504,13 +44504,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.02657019411530269</v>
+        <v>0.02657019411530295</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.007420436972250415</v>
+        <v>0.007420436972250398</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3357224795973284</v>
+        <v>0.3357224795973281</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44669,13 +44669,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.02366886174665103</v>
+        <v>0.02366886174665165</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.007679120311627263</v>
+        <v>0.007679120311627231</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3450219581941938</v>
+        <v>0.345021958194194</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44822,10 +44822,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI275" t="n">
-        <v>7.172249622131827</v>
+        <v>7.172249622131823</v>
       </c>
       <c r="AJ275" t="n">
-        <v>-0.05324966409349674</v>
+        <v>-0.05324966409349319</v>
       </c>
       <c r="AK275" t="n">
         <v>7.167365057101177</v>
@@ -44834,13 +44834,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.01956653131084185</v>
+        <v>0.01956653131084189</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008034860291676559</v>
+        <v>0.008034860291676519</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3572033251592189</v>
+        <v>0.3572033251592186</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -44987,10 +44987,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI276" t="n">
-        <v>7.171656420777024</v>
+        <v>7.171656420777023</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-0.05265646273869429</v>
+        <v>-0.0526564627386934</v>
       </c>
       <c r="AK276" t="n">
         <v>7.167567681415887</v>
@@ -44999,13 +44999,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01638396088890769</v>
+        <v>0.0163839608889081</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008326212487477964</v>
+        <v>0.008326212487477898</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.3674516177552961</v>
+        <v>0.3674516177552964</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45152,10 +45152,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.175289829564748</v>
+        <v>7.175289829564746</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.05628987152641773</v>
+        <v>-0.05628987152641596</v>
       </c>
       <c r="AK277" t="n">
         <v>7.167553154788029</v>
@@ -45164,13 +45164,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM277" t="n">
-        <v>0.01351198449095157</v>
+        <v>0.01351198449095179</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.008601682347582891</v>
+        <v>0.008601682347582911</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.3758646846617525</v>
+        <v>0.375864684661753</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45323,19 +45323,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK278" t="n">
-        <v>7.16746081477764</v>
+        <v>7.167460814777641</v>
       </c>
       <c r="AL278" t="n">
-        <v>-0.04846085673931011</v>
+        <v>-0.048460856739311</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.01196199498966369</v>
+        <v>0.01196199498966377</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.008797062853284063</v>
+        <v>0.008797062853284078</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.3847384959530242</v>
+        <v>0.3847384959530228</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45643,10 +45643,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI280" t="n">
-        <v>7.189678003526525</v>
+        <v>7.189678003526526</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-0.07117777082999144</v>
+        <v>-0.07117777082999321</v>
       </c>
       <c r="AK280" t="n">
         <v/>
@@ -45655,13 +45655,13 @@
         <v/>
       </c>
       <c r="AM280" t="n">
-        <v>0.007307555239791734</v>
+        <v>0.007307555239791735</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.009236289154790337</v>
+        <v>0.009236289154790363</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.401039717356949</v>
+        <v>0.4010397173569483</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45808,10 +45808,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI281" t="n">
-        <v>7.183919177237467</v>
+        <v>7.183919177237466</v>
       </c>
       <c r="AJ281" t="n">
-        <v>-0.05641912001700788</v>
+        <v>-0.056419120017007</v>
       </c>
       <c r="AK281" t="n">
         <v>7.168706858585229</v>
@@ -45820,13 +45820,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.006573598200530942</v>
+        <v>0.006573598200531427</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009378157495070056</v>
+        <v>0.009378157495070007</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4093166892046883</v>
+        <v>0.4093166892046876</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45985,13 +45985,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.005719699928660468</v>
+        <v>0.00571969992866044</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009535855797507643</v>
+        <v>0.009535855797507651</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4189456552735356</v>
+        <v>0.4189456552735351</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46138,10 +46138,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI283" t="n">
-        <v>7.183803634757356</v>
+        <v>7.183803634757355</v>
       </c>
       <c r="AJ283" t="n">
-        <v>-0.08380373012478781</v>
+        <v>-0.08380373012478692</v>
       </c>
       <c r="AK283" t="n">
         <v>7.157754776965645</v>
@@ -46150,13 +46150,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.007205793377056199</v>
+        <v>0.007205793377055721</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009541847058682544</v>
+        <v>0.00954184705868257</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4265135453780396</v>
+        <v>0.4265135453780416</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46309,19 +46309,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK284" t="n">
-        <v>7.153578345933642</v>
+        <v>7.153578345933643</v>
       </c>
       <c r="AL284" t="n">
-        <v>-0.01517826811381795</v>
+        <v>-0.01517826811381884</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.009937300636551308</v>
+        <v>0.009937300636551421</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.00947510825395563</v>
+        <v>0.009475108253955637</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4359288044119884</v>
+        <v>0.4359288044119891</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46468,10 +46468,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI285" t="n">
-        <v>7.175374323571331</v>
+        <v>7.175374323571332</v>
       </c>
       <c r="AJ285" t="n">
-        <v>-0.04917412444413394</v>
+        <v>-0.04917412444413483</v>
       </c>
       <c r="AK285" t="n">
         <v>7.155226204999164</v>
@@ -46480,13 +46480,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01039951522374721</v>
+        <v>0.01039951522374727</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009534227083684284</v>
+        <v>0.009534227083684297</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.446224869246465</v>
+        <v>0.4462248692464653</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46645,13 +46645,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01174445052819259</v>
+        <v>0.01174445052819296</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009539024405591096</v>
+        <v>0.009539024405591111</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4561706550234678</v>
+        <v>0.4561706550234662</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46798,10 +46798,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI287" t="n">
-        <v>7.176295466764674</v>
+        <v>7.176295466764673</v>
       </c>
       <c r="AJ287" t="n">
-        <v>-0.04989547286818929</v>
+        <v>-0.04989547286818841</v>
       </c>
       <c r="AK287" t="n">
         <v>7.150954883812801</v>
@@ -46810,13 +46810,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.01399948938427905</v>
+        <v>0.01399948938427885</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009474826008246758</v>
+        <v>0.009474826008246765</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4654004237248369</v>
+        <v>0.4654004237248376</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46975,13 +46975,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.01676993900799729</v>
+        <v>0.01676993900799728</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009377028877974699</v>
+        <v>0.00937702887797469</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.476700939638935</v>
+        <v>0.4767009396389351</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47143,10 +47143,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.009204864903404497</v>
+        <v>0.009204864903404482</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.4883841032893044</v>
+        <v>0.4883841032893032</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47305,13 +47305,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.02435543352765289</v>
+        <v>0.02435543352765317</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.009045821984022376</v>
+        <v>0.00904582198402234</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.4990078266507766</v>
+        <v>0.4990078266507749</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47458,10 +47458,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI291" t="n">
-        <v>7.175210595491395</v>
+        <v>7.175210595491394</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.04951059854315254</v>
+        <v>-0.04951059854315165</v>
       </c>
       <c r="AK291" t="n">
         <v>7.151444380572274</v>
@@ -47470,13 +47470,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.02840267381959001</v>
+        <v>0.02840267381959008</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008843610540066053</v>
+        <v>0.008843610540066056</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.5123725312709416</v>
+        <v>0.5123725312709417</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47626,7 +47626,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.05177635201934994</v>
+        <v>-0.05177635201935082</v>
       </c>
       <c r="AK292" t="n">
         <v>7.151307469847429</v>
@@ -47635,13 +47635,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.03189518855892823</v>
+        <v>0.03189518855892809</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008740250954211215</v>
+        <v>0.008740250954211236</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5303980242931245</v>
+        <v>0.5303980242931252</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47788,10 +47788,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI293" t="n">
-        <v>7.172173616645312</v>
+        <v>7.172173616645314</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.06197368836162021</v>
+        <v>-0.06197368836162287</v>
       </c>
       <c r="AK293" t="n">
         <v>7.152170779642037</v>
@@ -47800,13 +47800,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.03448417181877508</v>
+        <v>0.03448417181877479</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008638296330047493</v>
+        <v>0.008638296330047519</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.536400419244653</v>
+        <v>0.5364004192446541</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47956,7 +47956,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.08262387272163529</v>
+        <v>-0.08262387272163618</v>
       </c>
       <c r="AK294" t="n">
         <v>7.155242422656618</v>
@@ -47968,10 +47968,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008527848481957645</v>
+        <v>0.008527848481957647</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5479838817473677</v>
+        <v>0.5479838817473681</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48118,10 +48118,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI295" t="n">
-        <v>7.18418852599864</v>
+        <v>7.184188525998638</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.08518854888682359</v>
+        <v>-0.08518854888682181</v>
       </c>
       <c r="AK295" t="n">
         <v>7.174067278312125</v>
@@ -48130,13 +48130,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.03996026841105445</v>
+        <v>0.03996026841105382</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008497979041970659</v>
+        <v>0.008497979041970699</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5534995516418705</v>
+        <v>0.553499551641869</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48283,10 +48283,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.185513015749276</v>
+        <v>7.185513015749274</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.07571315384131694</v>
+        <v>-0.07571315384131516</v>
       </c>
       <c r="AK296" t="n">
         <v>7.175957423377739</v>
@@ -48295,13 +48295,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04233079818885077</v>
+        <v>0.04233079818885083</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008432709457890229</v>
+        <v>0.008432709457890224</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.5557951014363787</v>
+        <v>0.5557951014363788</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48454,19 +48454,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK297" t="n">
-        <v>7.174765662541793</v>
+        <v>7.174765662541792</v>
       </c>
       <c r="AL297" t="n">
-        <v>-0.05786569534818931</v>
+        <v>-0.05786569534818842</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04394124299371591</v>
+        <v>0.04394124299371556</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008396387260434499</v>
+        <v>0.008396387260434506</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5565519909812464</v>
+        <v>0.5565519909812453</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48613,10 +48613,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI298" t="n">
-        <v>7.185932916622859</v>
+        <v>7.18593291662286</v>
       </c>
       <c r="AJ298" t="n">
-        <v>-0.0141327800566966</v>
+        <v>-0.01413278005669749</v>
       </c>
       <c r="AK298" t="n">
         <v>7.172730869790855</v>
@@ -48625,13 +48625,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04590755972499789</v>
+        <v>0.04590755972499803</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008346613473328282</v>
+        <v>0.008346613473328291</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5588443644440741</v>
+        <v>0.5588443644440755</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48778,10 +48778,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI299" t="n">
-        <v>7.187602005018013</v>
+        <v>7.187602005018014</v>
       </c>
       <c r="AJ299" t="n">
-        <v>-0.05810209275604983</v>
+        <v>-0.0581020927560516</v>
       </c>
       <c r="AK299" t="n">
         <v>7.168923754586179</v>
@@ -48790,10 +48790,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04658552832149703</v>
+        <v>0.04658552832149689</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008354655440128402</v>
+        <v>0.008354655440128426</v>
       </c>
       <c r="AO299" t="n">
         <v>0.5613325805619827</v>
@@ -48955,13 +48955,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.04820692510781933</v>
+        <v>0.04820692510781883</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008303818071592001</v>
+        <v>0.008303818071592054</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5626464255878519</v>
+        <v>0.5626464255878516</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49120,13 +49120,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.04983084886774743</v>
+        <v>0.04983084886774771</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008251024544031704</v>
+        <v>0.008251024544031682</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5641340630354328</v>
+        <v>0.5641340630354323</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49285,13 +49285,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05170461329917111</v>
+        <v>0.05170461329917048</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008192726391276807</v>
+        <v>0.008192726391276836</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5658195968244528</v>
+        <v>0.5658195968244545</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49450,13 +49450,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05348369580043773</v>
+        <v>0.05348369580043772</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008143044151838245</v>
+        <v>0.008143044151838252</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5671346874885959</v>
+        <v>0.5671346874885956</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49603,10 +49603,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.175179910580594</v>
+        <v>7.175179910580593</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.05588002196975417</v>
+        <v>-0.05588002196975328</v>
       </c>
       <c r="AK304" t="n">
         <v>7.165699812335961</v>
@@ -49615,13 +49615,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05520982564369371</v>
+        <v>0.0552098256436935</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008124788470663676</v>
+        <v>0.008124788470663643</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5701242576280907</v>
+        <v>0.5701242576280905</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49768,10 +49768,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.173581841712227</v>
+        <v>7.173581841712229</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.05428195310138761</v>
+        <v>-0.05428195310138939</v>
       </c>
       <c r="AK305" t="n">
         <v>7.162626578418298</v>
@@ -49780,13 +49780,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05644890839995315</v>
+        <v>0.05644890839995281</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008105230252153435</v>
+        <v>0.008105230252153447</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5713754740215509</v>
+        <v>0.5713754740215494</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49933,10 +49933,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.176011726611837</v>
+        <v>7.176011726611838</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.06401173805592908</v>
+        <v>-0.06401173805592997</v>
       </c>
       <c r="AK306" t="n">
         <v>7.165542054185019</v>
@@ -49945,13 +49945,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05727663218544052</v>
+        <v>0.05727663218544039</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.00812403522652648</v>
+        <v>0.008124035226526509</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.573000414744258</v>
+        <v>0.5730004147442582</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50098,10 +50098,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.17698340522191</v>
+        <v>7.176983405221908</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.07778363334080662</v>
+        <v>-0.07778363334080485</v>
       </c>
       <c r="AK307" t="n">
         <v>7.170209849598846</v>
@@ -50110,13 +50110,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.05825580143844533</v>
+        <v>0.05825580143844532</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.008106527117828777</v>
+        <v>0.008106527117828759</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5728585525731363</v>
+        <v>0.5728585525731367</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50263,10 +50263,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.174841035863564</v>
+        <v>7.174841035863563</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.06734095956961905</v>
+        <v>-0.06734095956961816</v>
       </c>
       <c r="AK308" t="n">
         <v>7.166925629020364</v>
@@ -50275,13 +50275,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.05980113395910436</v>
+        <v>0.05980113395910441</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.008056914781095353</v>
+        <v>0.008056914781095341</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5723268395754473</v>
+        <v>0.5723268395754482</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50428,10 +50428,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.179777800337525</v>
+        <v>7.179777800337526</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.07227772404357946</v>
+        <v>-0.07227772404358035</v>
       </c>
       <c r="AK309" t="n">
         <v>7.163704513322672</v>
@@ -50443,10 +50443,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.008007544934860181</v>
+        <v>0.008007544934860184</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5724055344141883</v>
+        <v>0.5724055344141876</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50593,10 +50593,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.176651545551679</v>
+        <v>7.176651545551677</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.06915146925773374</v>
+        <v>-0.06915146925773197</v>
       </c>
       <c r="AK310" t="n">
         <v>7.163430147298699</v>
@@ -50605,13 +50605,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.06321929365037962</v>
+        <v>0.06321929365038026</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007927773212025854</v>
+        <v>0.007927773212025837</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.572463582881384</v>
+        <v>0.5724635828813827</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50758,10 +50758,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.173279688539583</v>
+        <v>7.173279688539582</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.06577961224563733</v>
+        <v>-0.06577961224563644</v>
       </c>
       <c r="AK311" t="n">
         <v>7.158871783064204</v>
@@ -50770,13 +50770,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06523048259292186</v>
+        <v>0.0652304825929222</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007809540836127948</v>
+        <v>0.007809540836127932</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5710090561291132</v>
+        <v>0.571009056129113</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50923,10 +50923,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI312" t="n">
-        <v>7.168542018724481</v>
+        <v>7.168542018724479</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.06194221098522323</v>
+        <v>-0.06194221098522146</v>
       </c>
       <c r="AK312" t="n">
         <v>7.152618309751275</v>
@@ -50935,13 +50935,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.067411943409599</v>
+        <v>0.06741194340959927</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007660511838810988</v>
+        <v>0.007660511838810949</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.5694124450603424</v>
+        <v>0.5694124450603408</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51088,10 +51088,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI313" t="n">
-        <v>7.161829635752616</v>
+        <v>7.161829635752617</v>
       </c>
       <c r="AJ313" t="n">
-        <v>-0.05962960447209831</v>
+        <v>-0.0596296044720992</v>
       </c>
       <c r="AK313" t="n">
         <v>7.144956229005203</v>
@@ -51100,13 +51100,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.06977835201573312</v>
+        <v>0.06977835201573281</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007516908058882096</v>
+        <v>0.007516908058882097</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5690369646398685</v>
+        <v>0.5690369646398684</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51256,7 +51256,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.07699331565738099</v>
+        <v>-0.07699331565738188</v>
       </c>
       <c r="AK314" t="n">
         <v>7.140422114543136</v>
@@ -51265,16 +51265,16 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.07195366789421653</v>
+        <v>0.07195366789421676</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.007394117938767417</v>
+        <v>0.007394117938767422</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5693040973288186</v>
+        <v>0.5693040973288199</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.387214816667044</v>
+        <v>-1.387214816667113</v>
       </c>
       <c r="AQ314" t="n">
         <v>5.862068965517241</v>
@@ -51430,16 +51430,16 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.07456301989532385</v>
+        <v>0.07456301989532414</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.007241314760732032</v>
+        <v>0.007241314760731996</v>
       </c>
       <c r="AO315" t="n">
         <v>0.5685877661607006</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.751355156100289</v>
+        <v>-1.751355156100307</v>
       </c>
       <c r="AQ315" t="n">
         <v>3.306474020561267</v>
@@ -51595,16 +51595,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.07747971887849656</v>
+        <v>0.07747971887849607</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.0070901436555387</v>
+        <v>0.007090143655538702</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5681709745664083</v>
+        <v>0.5681709745664091</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.719358275118384</v>
+        <v>-1.7193582751184</v>
       </c>
       <c r="AQ316" t="n">
         <v>4.919354838709678</v>
@@ -51748,10 +51748,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.165084051386049</v>
+        <v>7.165084051386047</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.08998410631768916</v>
+        <v>-0.08998410631768738</v>
       </c>
       <c r="AK317" t="n">
         <v>7.14582045097363</v>
@@ -51760,16 +51760,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08000072584212846</v>
+        <v>0.08000072584212836</v>
       </c>
       <c r="AN317" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5684087510734981</v>
+        <v>0.5684087510734968</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.920512463066454</v>
+        <v>-1.920512463066381</v>
       </c>
       <c r="AQ317" t="n">
         <v>2.432995055945876</v>
@@ -51913,10 +51913,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.161419741275552</v>
+        <v>7.161419741275553</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.08971964514518138</v>
+        <v>-0.08971964514518227</v>
       </c>
       <c r="AK318" t="n">
         <v>7.155707108847959</v>
@@ -51925,16 +51925,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08204996863507508</v>
+        <v>0.08204996863507528</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006919462921967476</v>
+        <v>0.006919462921967468</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5672869954461468</v>
+        <v>0.5672869954461461</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.839265028040945</v>
+        <v>-1.83926502804101</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.368951612903226</v>
@@ -52078,10 +52078,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.155488092579304</v>
+        <v>7.155488092579303</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.08548792091792734</v>
+        <v>-0.08548792091792645</v>
       </c>
       <c r="AK319" t="n">
         <v>7.150451326287159</v>
@@ -52090,16 +52090,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08469403553214168</v>
+        <v>0.08469403553214211</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006815201188096393</v>
+        <v>0.006815201188096372</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5663505631396779</v>
+        <v>0.5663505631396781</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.572203541131127</v>
+        <v>-1.572203541131099</v>
       </c>
       <c r="AQ319" t="n">
         <v>3.870573870573871</v>
@@ -52243,10 +52243,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.158832817363979</v>
+        <v>7.15883281736398</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.09523275404000398</v>
+        <v>-0.09523275404000575</v>
       </c>
       <c r="AK320" t="n">
         <v>7.147115644271845</v>
@@ -52255,16 +52255,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.08699523504893081</v>
+        <v>0.08699523504893142</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006735083295172709</v>
+        <v>0.006735083295172689</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5654743012892969</v>
+        <v>0.5654743012892984</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.998545444594283</v>
+        <v>-1.998545444594386</v>
       </c>
       <c r="AQ320" t="n">
         <v>1.538825757575758</v>
@@ -52408,10 +52408,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.161703459649028</v>
+        <v>7.161703459649029</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.090303294091167</v>
+        <v>-0.09030329409116788</v>
       </c>
       <c r="AK321" t="n">
         <v>7.152131804583207</v>
@@ -52420,16 +52420,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.08901512474159551</v>
+        <v>0.08901512474159586</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006668288608758136</v>
+        <v>0.006668288608758129</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5631673144521659</v>
+        <v>0.5631673144521655</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.696375567991948</v>
+        <v>-1.696375567992</v>
       </c>
       <c r="AQ321" t="n">
         <v>2.261768082663605</v>
@@ -52573,10 +52573,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.162535384813326</v>
+        <v>7.162535384813327</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.09293527952768166</v>
+        <v>-0.09293527952768255</v>
       </c>
       <c r="AK322" t="n">
         <v>7.157753883768605</v>
@@ -52585,16 +52585,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.09116436352661951</v>
+        <v>0.09116436352661936</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006624805625172231</v>
+        <v>0.006624805625172246</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5612585549312774</v>
+        <v>0.5612585549312785</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.77116632357484</v>
+        <v>-1.771166323574888</v>
       </c>
       <c r="AQ322" t="n">
         <v>2.985739750445632</v>
@@ -52738,10 +52738,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.166818450294679</v>
+        <v>7.166818450294681</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.0958183511125501</v>
+        <v>-0.09581835111255188</v>
       </c>
       <c r="AK323" t="n">
         <v>7.158620349112049</v>
@@ -52750,16 +52750,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09320704864741254</v>
+        <v>0.09320704864741212</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006594358041710158</v>
+        <v>0.006594358041710186</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5590514368572466</v>
+        <v>0.5590514368572459</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.85019582999533</v>
+        <v>-1.850195829995415</v>
       </c>
       <c r="AQ323" t="n">
         <v>1.470906337875838</v>
@@ -52903,10 +52903,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.157691007010206</v>
+        <v>7.157691007010208</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.0943908742587416</v>
+        <v>-0.09439087425874337</v>
       </c>
       <c r="AK324" t="n">
         <v>7.164942158928604</v>
@@ -52915,16 +52915,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.09491020692123933</v>
+        <v>0.09491020692123982</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006562900445417311</v>
+        <v>0.006562900445417306</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5551825155208145</v>
+        <v>0.5551825155208129</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.729349174402516</v>
+        <v>-1.729349174402595</v>
       </c>
       <c r="AQ324" t="n">
         <v>2.878151260504202</v>
@@ -53068,10 +53068,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.151776426431621</v>
+        <v>7.15177642643162</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.08777629673191356</v>
+        <v>-0.08777629673191267</v>
       </c>
       <c r="AK325" t="n">
         <v>7.154764404811184</v>
@@ -53080,16 +53080,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.097046810505102</v>
+        <v>0.0970468105051025</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006523984583215639</v>
+        <v>0.006523984583215632</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5522992358254805</v>
+        <v>0.5522992358254815</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.385185049809918</v>
+        <v>-1.385185049809873</v>
       </c>
       <c r="AQ325" t="n">
         <v>6.358440498060829</v>
@@ -53233,10 +53233,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI326" t="n">
-        <v>7.15099240431968</v>
+        <v>7.150992404319682</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.09309245238486596</v>
+        <v>-0.09309245238486774</v>
       </c>
       <c r="AK326" t="n">
         <v>7.150261540163492</v>
@@ -53245,16 +53245,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.09904197982498698</v>
+        <v>0.09904197982498671</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006505848878330736</v>
+        <v>0.006505848878330779</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5500699492277152</v>
+        <v>0.5500699492277157</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.595274724905276</v>
+        <v>-1.595274724905352</v>
       </c>
       <c r="AQ326" t="n">
         <v>4.206349206349207</v>
@@ -53398,10 +53398,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI327" t="n">
-        <v>7.147140093605204</v>
+        <v>7.147140093605207</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.09314019278733277</v>
+        <v>-0.09314019278733543</v>
       </c>
       <c r="AK327" t="n">
         <v>7.148879230661717</v>
@@ -53410,16 +53410,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.1013300516539148</v>
+        <v>0.1013300516539142</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006479631055951007</v>
+        <v>0.006479631055951091</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5478993564899665</v>
+        <v>0.5478993564899672</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.559279185803214</v>
+        <v>-1.559279185803325</v>
       </c>
       <c r="AQ327" t="n">
         <v>3.443951379509936</v>
@@ -53569,22 +53569,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK328" t="n">
-        <v>7.145816711184184</v>
+        <v>7.145816711184185</v>
       </c>
       <c r="AL328" t="n">
-        <v>-0.09881677984873516</v>
+        <v>-0.09881677984873605</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1033273874042088</v>
+        <v>0.1033273874042092</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006468712737497662</v>
+        <v>0.006468712737497656</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5455500876237902</v>
+        <v>0.5455500876237913</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.633678780047227</v>
+        <v>-1.633678780047215</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.045795795795796</v>
@@ -53731,7 +53731,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ329" t="n">
-        <v>-0.1028262052267701</v>
+        <v>-0.102826205226771</v>
       </c>
       <c r="AK329" t="n">
         <v>7.139092738717567</v>
@@ -53740,16 +53740,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1056457020972507</v>
+        <v>0.1056457020972505</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006435041090934165</v>
+        <v>0.006435041090934217</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5433399026839665</v>
+        <v>0.5433399026839674</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.899027440937709</v>
+        <v>-1.899027440937733</v>
       </c>
       <c r="AQ329" t="n">
         <v>2.721461187214611</v>
@@ -53896,7 +53896,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.099096096614959</v>
+        <v>-0.09909609661495811</v>
       </c>
       <c r="AK330" t="n">
         <v>7.140479586010682</v>
@@ -53905,16 +53905,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.10768023901916</v>
+        <v>0.1076802390191602</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006405465077205547</v>
+        <v>0.006405465077205527</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5402459241219614</v>
+        <v>0.5402459241219618</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.687116422037569</v>
+        <v>-1.687116422037517</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.667140825035561</v>
@@ -54058,10 +54058,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI331" t="n">
-        <v>7.145743344370562</v>
+        <v>7.145743344370558</v>
       </c>
       <c r="AJ331" t="n">
-        <v>-0.1052431803385794</v>
+        <v>-0.1052431803385758</v>
       </c>
       <c r="AK331" t="n">
         <v>7.136632587022158</v>
@@ -54070,16 +54070,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1100130126862077</v>
+        <v>0.1100130126862084</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006366554765990282</v>
+        <v>0.00636655476599019</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5375708073661647</v>
+        <v>0.5375708073661639</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.899194629591059</v>
+        <v>-1.8991946295909</v>
       </c>
       <c r="AQ331" t="n">
         <v>2.649350649350649</v>
@@ -54235,16 +54235,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1122475627674583</v>
+        <v>0.1122475627674581</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006337265512462553</v>
+        <v>0.00633726551246258</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5341613739773245</v>
+        <v>0.5341613739773232</v>
       </c>
       <c r="AP332" t="n">
-        <v>-1.572918871746104</v>
+        <v>-1.572918871746101</v>
       </c>
       <c r="AQ332" t="n">
         <v>3.221997300944669</v>
@@ -54388,10 +54388,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI333" t="n">
-        <v>7.142519733033009</v>
+        <v>7.14251973303301</v>
       </c>
       <c r="AJ333" t="n">
-        <v>-0.1016195026252946</v>
+        <v>-0.1016195026252955</v>
       </c>
       <c r="AK333" t="n">
         <v>7.135172643569136</v>
@@ -54400,16 +54400,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1146509166068179</v>
+        <v>0.114650916606818</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006337163869517243</v>
+        <v>0.006337163869517234</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5319767312874306</v>
+        <v>0.5319767312874311</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.662569740270745</v>
+        <v>-1.662569740270778</v>
       </c>
       <c r="AQ333" t="n">
         <v>2.548084826565839</v>
@@ -54565,16 +54565,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1171965158426952</v>
+        <v>0.1171965158426948</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006367653503792481</v>
+        <v>0.00636765350379247</v>
       </c>
       <c r="AO334" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP334" t="n">
-        <v>-2.104390790930698</v>
+        <v>-2.104390790930691</v>
       </c>
       <c r="AQ334" t="n">
         <v>1.266025641025641</v>
@@ -54718,10 +54718,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI335" t="n">
-        <v>7.140851085964109</v>
+        <v>7.140851085964112</v>
       </c>
       <c r="AJ335" t="n">
-        <v>-0.1128512080344217</v>
+        <v>-0.1128512080344244</v>
       </c>
       <c r="AK335" t="n">
         <v>7.142783913375006</v>
@@ -54730,16 +54730,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.119227205240256</v>
+        <v>0.1192272052402563</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006383133038709798</v>
+        <v>0.00638313303870985</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.5243060286247103</v>
+        <v>0.5243060286247104</v>
       </c>
       <c r="AP335" t="n">
-        <v>-1.999980781016792</v>
+        <v>-1.999980781016887</v>
       </c>
       <c r="AQ335" t="n">
         <v>2.500390686044694</v>
@@ -54883,10 +54883,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.139245392969567</v>
+        <v>7.139245392969565</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1112455150398795</v>
+        <v>-0.1112455150398777</v>
       </c>
       <c r="AK336" t="n">
         <v>7.141836927013541</v>
@@ -54895,16 +54895,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM336" t="n">
-        <v>0.1211746327267789</v>
+        <v>0.1211746327267792</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006404909068509476</v>
+        <v>0.006404909068509461</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5185318197199045</v>
+        <v>0.518531819719905</v>
       </c>
       <c r="AP336" t="n">
-        <v>-1.879907772594156</v>
+        <v>-1.879907772594078</v>
       </c>
       <c r="AQ336" t="n">
         <v>3.704268292682927</v>
@@ -55048,10 +55048,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.136520216281903</v>
+        <v>7.136520216281902</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.108520338352216</v>
+        <v>-0.1085203383522142</v>
       </c>
       <c r="AK337" t="n">
         <v>7.13958125183462</v>
@@ -55060,16 +55060,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1228335954516147</v>
+        <v>0.1228335954516143</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006430223802628449</v>
+        <v>0.006430223802628476</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.5122974965428477</v>
+        <v>0.5122974965428486</v>
       </c>
       <c r="AP337" t="n">
-        <v>-1.727357918499389</v>
+        <v>-1.727357918499316</v>
       </c>
       <c r="AQ337" t="n">
         <v>4.878774356686003</v>
@@ -55228,13 +55228,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006430805642792636</v>
+        <v>0.006430805642792618</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.5056597011855208</v>
+        <v>0.5056597011855207</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.463446639918009</v>
+        <v>-2.463446639918004</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.204994192799071</v>
@@ -55378,10 +55378,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.136562857934749</v>
+        <v>7.13656285793475</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.140462909051692</v>
+        <v>-0.1404629090516929</v>
       </c>
       <c r="AK339" t="n">
         <v>7.132705938528055</v>
@@ -55393,13 +55393,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006419568115912044</v>
+        <v>0.006419568115912051</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4979995576252224</v>
+        <v>0.4979995576252233</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.720289042953629</v>
+        <v>-2.720289042953653</v>
       </c>
       <c r="AQ339" t="n">
         <v>1.190644932671864</v>
@@ -55543,10 +55543,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.135435320996258</v>
+        <v>7.135435320996254</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.1393353721132016</v>
+        <v>-0.1393353721131971</v>
       </c>
       <c r="AK340" t="n">
         <v>7.134470034900207</v>
@@ -55555,16 +55555,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1290155516631957</v>
+        <v>0.1290155516631951</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006423940675024581</v>
+        <v>0.006423940675024553</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.489456156051701</v>
+        <v>0.4894561560517011</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.557572429280606</v>
+        <v>-2.557572429280455</v>
       </c>
       <c r="AQ340" t="n">
         <v>2.948504983388704</v>
@@ -55708,10 +55708,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.135221482968309</v>
+        <v>7.135221482968312</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1391215340852527</v>
+        <v>-0.1391215340852554</v>
       </c>
       <c r="AK341" t="n">
         <v>7.133435115388912</v>
@@ -55720,16 +55720,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1313692321875789</v>
+        <v>0.1313692321875792</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006422605647444513</v>
+        <v>0.006422605647444502</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4811392039904447</v>
+        <v>0.4811392039904442</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.444696267851527</v>
+        <v>-2.444696267851617</v>
       </c>
       <c r="AQ341" t="n">
         <v>4.077079107505071</v>
@@ -55873,10 +55873,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI342" t="n">
-        <v>7.129120131622726</v>
+        <v>7.129120131622732</v>
       </c>
       <c r="AJ342" t="n">
-        <v>-0.1360199653019256</v>
+        <v>-0.1360199653019309</v>
       </c>
       <c r="AK342" t="n">
         <v>7.132510325395203</v>
@@ -55885,16 +55885,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1334873867685099</v>
+        <v>0.1334873867685108</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006388619079873509</v>
+        <v>0.006388619079873553</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4724960612931043</v>
+        <v>0.4724960612931048</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.254840378259555</v>
+        <v>-2.254840378259721</v>
       </c>
       <c r="AQ342" t="n">
         <v>5.17970401691332</v>
@@ -56050,16 +56050,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1357975915367747</v>
+        <v>0.1357975915367741</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006324213907675097</v>
+        <v>0.006324213907675122</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4647750649852552</v>
+        <v>0.4647750649852558</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.331385793786239</v>
+        <v>-2.331385793786226</v>
       </c>
       <c r="AQ343" t="n">
         <v>2.860648327521632</v>
@@ -56203,10 +56203,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI344" t="n">
-        <v>7.122818285283529</v>
+        <v>7.122818285283532</v>
       </c>
       <c r="AJ344" t="n">
-        <v>-0.1394184172720543</v>
+        <v>-0.1394184172720578</v>
       </c>
       <c r="AK344" t="n">
         <v>7.123271418608565</v>
@@ -56215,16 +56215,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1386638579210687</v>
+        <v>0.1386638579210689</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.006222091828703702</v>
+        <v>0.006222091828703747</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4565264017486783</v>
+        <v>0.4565264017486775</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.204545221728734</v>
+        <v>-2.204545221728828</v>
       </c>
       <c r="AQ344" t="n">
         <v>3.939393939393939</v>
@@ -56380,16 +56380,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1423176752089984</v>
+        <v>0.1423176752089981</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.006093783709292283</v>
+        <v>0.006093783709292289</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4497199830569224</v>
+        <v>0.4497199830569214</v>
       </c>
       <c r="AP345" t="n">
-        <v>-1.830741702885553</v>
+        <v>-1.830741702885538</v>
       </c>
       <c r="AQ345" t="n">
         <v>8.889986418076306</v>
@@ -56533,10 +56533,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.133160404869088</v>
+        <v>7.13316040486909</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.1496604010543905</v>
+        <v>-0.1496604010543923</v>
       </c>
       <c r="AK346" t="n">
         <v>7.117219286120759</v>
@@ -56548,13 +56548,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.005984113522022494</v>
+        <v>0.005984113522022499</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4438783751010233</v>
+        <v>0.4438783751010228</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.385403684195726</v>
+        <v>-2.385403684195758</v>
       </c>
       <c r="AQ346" t="n">
         <v>7.765700483091787</v>
@@ -56698,10 +56698,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.12965322071209</v>
+        <v>7.129653220712091</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1524531894315722</v>
+        <v>-0.152453189431573</v>
       </c>
       <c r="AK347" t="n">
         <v>7.126254605494273</v>
@@ -56710,16 +56710,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1503893187551748</v>
+        <v>0.1503893187551739</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005963146506628741</v>
+        <v>0.005963146506628762</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4412018736247373</v>
+        <v>0.441201873624737</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.380336796004049</v>
+        <v>-2.380336796004052</v>
       </c>
       <c r="AQ347" t="n">
         <v>7.680491551459293</v>
@@ -56863,10 +56863,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.128380415829728</v>
+        <v>7.128380415829729</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1552802304354408</v>
+        <v>-0.1552802304354417</v>
       </c>
       <c r="AK348" t="n">
         <v>7.124321202568002</v>
@@ -56875,16 +56875,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1546287435667592</v>
+        <v>0.1546287435667593</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005975981199024843</v>
+        <v>0.005975981199024824</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4385827444686599</v>
+        <v>0.43858274446866</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.375569581173715</v>
+        <v>-2.375569581173716</v>
       </c>
       <c r="AQ348" t="n">
         <v>7.597132284921368</v>
@@ -57028,10 +57028,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.124429161493117</v>
+        <v>7.124429161493114</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1469291996400894</v>
+        <v>-0.1469291996400868</v>
       </c>
       <c r="AK349" t="n">
         <v>7.121152072356459</v>
@@ -57040,16 +57040,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1587808126513012</v>
+        <v>0.1587808126513008</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.00589922161993145</v>
+        <v>0.005899221619931436</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4336499747757657</v>
+        <v>0.4336499747757655</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.071444053426131</v>
+        <v>-2.071444053426039</v>
       </c>
       <c r="AQ349" t="n">
         <v>16.08375778155065</v>
@@ -57205,16 +57205,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1636493008978488</v>
+        <v>0.1636493008978486</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.005897856672615054</v>
+        <v>0.005897856672615022</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.434304834398872</v>
+        <v>0.4343048343988722</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.381707053311504</v>
+        <v>-2.381707053311488</v>
       </c>
       <c r="AQ350" t="n">
         <v>13.81870567375887</v>
@@ -57358,10 +57358,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.141397967314147</v>
+        <v>7.141397967314151</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.1753978872055049</v>
+        <v>-0.1753978872055084</v>
       </c>
       <c r="AK351" t="n">
         <v>7.12802266215534</v>
@@ -57370,16 +57370,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1676675897666615</v>
+        <v>0.1676675897666616</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.005952601612807557</v>
+        <v>0.005952601612807589</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4322693842687806</v>
+        <v>0.4322693842687804</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.667671235283137</v>
+        <v>-2.667671235283208</v>
       </c>
       <c r="AQ351" t="n">
         <v>12.62072707542051</v>
@@ -57523,10 +57523,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.140412492855504</v>
+        <v>7.140412492855501</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1723124219021352</v>
+        <v>-0.1723124219021317</v>
       </c>
       <c r="AK352" t="n">
         <v>7.137738577466652</v>
@@ -57535,16 +57535,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1710383543493657</v>
+        <v>0.1710383543493662</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.006068444256835448</v>
+        <v>0.00606844425683546</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4285062718639565</v>
+        <v>0.4285062718639572</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.487142522607826</v>
+        <v>-2.487142522607719</v>
       </c>
       <c r="AQ352" t="n">
         <v>19.77040816326531</v>
@@ -57688,10 +57688,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.138020503721587</v>
+        <v>7.138020503721584</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.169920432768218</v>
+        <v>-0.1699204327682153</v>
       </c>
       <c r="AK353" t="n">
         <v>7.13663078035759</v>
@@ -57700,16 +57700,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.176195682434215</v>
+        <v>0.1761956824342154</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.006402952059750722</v>
+        <v>0.006402952059750703</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4374093872433962</v>
+        <v>0.4374093872433956</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.343009734619097</v>
+        <v>-2.343009734619021</v>
       </c>
       <c r="AQ353" t="n">
         <v>19.55638862855358</v>
@@ -57853,28 +57853,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.136830620687384</v>
+        <v>7.136830620687383</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1769307183436339</v>
+        <v>-0.1769307183436331</v>
       </c>
       <c r="AK354" t="n">
-        <v>7.14004901784002</v>
+        <v>7.140049017840021</v>
       </c>
       <c r="AL354" t="n">
-        <v>-0.1801491154962704</v>
+        <v>-0.1801491154962713</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1796308914905975</v>
+        <v>0.1796308914905974</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.006948414844703821</v>
+        <v>0.006948414844703805</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4458727441769479</v>
+        <v>0.4458727441769483</v>
       </c>
       <c r="AP354" t="n">
-        <v>-2.433015356127483</v>
+        <v>-2.433015356127453</v>
       </c>
       <c r="AQ354" t="n">
         <v>17.8469387755102</v>
@@ -58014,10 +58014,10 @@
         <v/>
       </c>
       <c r="AI355" t="n">
-        <v>7.133638579266565</v>
+        <v>7.13363857926656</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1699387616090942</v>
+        <v>-0.1699387616090897</v>
       </c>
       <c r="AK355" t="n">
         <v>7.13798584867198</v>
@@ -58026,16 +58026,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1829391475229931</v>
+        <v>0.1829391475229935</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.007602047321544403</v>
+        <v>0.00760204732154433</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4545618931940824</v>
+        <v>0.4545618931940826</v>
       </c>
       <c r="AP355" t="n">
-        <v>-2.192268299666791</v>
+        <v>-2.192268299666683</v>
       </c>
       <c r="AQ355" t="n">
         <v>26.98019801980198</v>
@@ -58179,10 +58179,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI356" t="n">
-        <v>7.12640946890857</v>
+        <v>7.126409468908567</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1538094856932375</v>
+        <v>-0.1538094856932348</v>
       </c>
       <c r="AK356" t="n">
         <v>7.138565167526504</v>
@@ -58191,16 +58191,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1834764543657148</v>
+        <v>0.1834764543657157</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.007712839302340374</v>
+        <v>0.007712839302340297</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4511257152112026</v>
+        <v>0.4511257152112024</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.761104492054283</v>
+        <v>-1.761104492054221</v>
       </c>
       <c r="AQ356" t="n">
         <v>22.60843731431967</v>
@@ -58344,10 +58344,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI357" t="n">
-        <v>7.110999512759045</v>
+        <v>7.110999512759042</v>
       </c>
       <c r="AJ357" t="n">
-        <v>-0.1383995295437126</v>
+        <v>-0.1383995295437099</v>
       </c>
       <c r="AK357" t="n">
         <v>7.137040595974374</v>
@@ -58356,16 +58356,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1869739626316104</v>
+        <v>0.1869739626316108</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.00835460951998479</v>
+        <v>0.008354609519984808</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4618871834350119</v>
+        <v>0.4618871834350127</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.368717051122944</v>
+        <v>-1.368717051122884</v>
       </c>
       <c r="AQ357" t="n">
         <v>16.75242718446602</v>
@@ -58521,16 +58521,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.1901371272406391</v>
+        <v>0.1901371272406383</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.008787529863310189</v>
+        <v>0.008787529863310259</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4631528842621211</v>
+        <v>0.4631528842621208</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.405229583753368</v>
+        <v>-1.405229583753373</v>
       </c>
       <c r="AQ358" t="n">
         <v>10.21039603960396</v>
@@ -58674,10 +58674,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI359" t="n">
-        <v>7.10229338126412</v>
+        <v>7.102293381264122</v>
       </c>
       <c r="AJ359" t="n">
-        <v>-0.1477931828998624</v>
+        <v>-0.1477931828998642</v>
       </c>
       <c r="AK359" t="n">
         <v>7.113436809075056</v>
@@ -58686,16 +58686,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.1939456835457532</v>
+        <v>0.193945683545753</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.009306466714917722</v>
+        <v>0.009306466714917755</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4650211967660294</v>
+        <v>0.4650211967660295</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.547790886058297</v>
+        <v>-1.547790886058342</v>
       </c>
       <c r="AQ359" t="n">
         <v>11.12044817927171</v>
@@ -58851,16 +58851,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.1968971496416331</v>
+        <v>0.1968971496416338</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.009915270508004642</v>
+        <v>0.009915270508004639</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4658112293095933</v>
+        <v>0.4658112293095935</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.323847614466191</v>
+        <v>-1.323847614466194</v>
       </c>
       <c r="AQ360" t="n">
         <v>11.40318739695915</v>
@@ -59016,16 +59016,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2001574773810679</v>
+        <v>0.200157477381068</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.01045224758824684</v>
+        <v>0.01045224758824685</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4652001227613064</v>
+        <v>0.4652001227613058</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.585894032713987</v>
+        <v>-1.58589403271399</v>
       </c>
       <c r="AQ361" t="n">
         <v>5.153666427030913</v>
@@ -59169,10 +59169,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI362" t="n">
-        <v>7.112155432918446</v>
+        <v>7.112155432918444</v>
       </c>
       <c r="AJ362" t="n">
-        <v>-0.1611552192953987</v>
+        <v>-0.1611552192953969</v>
       </c>
       <c r="AK362" t="n">
         <v>7.115439870473561</v>
@@ -59181,16 +59181,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2059164257597553</v>
+        <v>0.2059164257597547</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01095806236007055</v>
+        <v>0.0109580623600705</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4647071558511969</v>
+        <v>0.4647071558511972</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.78212565773126</v>
+        <v>-1.782125657731223</v>
       </c>
       <c r="AQ362" t="n">
         <v>6.587301587301587</v>
@@ -59346,16 +59346,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2103846028094628</v>
+        <v>0.2103846028094625</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01138655624224677</v>
+        <v>0.01138655624224671</v>
       </c>
       <c r="AO363" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.810148439959766</v>
+        <v>-1.81014843995977</v>
       </c>
       <c r="AQ363" t="n">
         <v>11.2428596157175</v>
@@ -59499,10 +59499,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI364" t="n">
-        <v>7.110775793344653</v>
+        <v>7.110775793344654</v>
       </c>
       <c r="AJ364" t="n">
-        <v>-0.1730759985753663</v>
+        <v>-0.1730759985753672</v>
       </c>
       <c r="AK364" t="n">
         <v>7.127056499711662</v>
@@ -59511,16 +59511,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2137349114935569</v>
+        <v>0.2137349114935566</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01184277521890661</v>
+        <v>0.0118427752189066</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4573024605378193</v>
+        <v>0.4573024605378192</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.974952691681103</v>
+        <v>-1.974952691681126</v>
       </c>
       <c r="AQ364" t="n">
         <v>12.5785896346644</v>
@@ -59676,16 +59676,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2192999169256238</v>
+        <v>0.2192999169256231</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01242692746354282</v>
+        <v>0.01242692746354283</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4593518446085588</v>
+        <v>0.4593518446085587</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.53389908426528</v>
+        <v>-1.533899084265283</v>
       </c>
       <c r="AQ365" t="n">
         <v>14.21421421421421</v>
@@ -59829,28 +59829,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.095070446253633</v>
+        <v>7.095070446253632</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.1572705156811232</v>
+        <v>-0.1572705156811223</v>
       </c>
       <c r="AK366" t="n">
-        <v>7.099084322920755</v>
+        <v>7.099084322920754</v>
       </c>
       <c r="AL366" t="n">
-        <v>-0.1612843923482448</v>
+        <v>-0.1612843923482439</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2273791016644669</v>
+        <v>0.2273791016644665</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01301934706839999</v>
+        <v>0.01301934706840001</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4655241261491886</v>
+        <v>0.4655241261491888</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.566746911622516</v>
+        <v>-1.5667469116225</v>
       </c>
       <c r="AQ366" t="n">
         <v>12.26245085190039</v>
@@ -59994,10 +59994,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.077412848446851</v>
+        <v>7.077412848446856</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1386129903535895</v>
+        <v>-0.138612990353594</v>
       </c>
       <c r="AK367" t="n">
         <v>7.107752072150756</v>
@@ -60006,16 +60006,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2346680713248289</v>
+        <v>0.2346680713248287</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01366280940279216</v>
+        <v>0.01366280940279221</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4682122340216202</v>
+        <v>0.4682122340216205</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.136522825763405</v>
+        <v>-1.136522825763505</v>
       </c>
       <c r="AQ367" t="n">
         <v>19.68624296057924</v>
@@ -60159,10 +60159,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.067855559671527</v>
+        <v>7.067855559671529</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1458556283360775</v>
+        <v>-0.1458556283360801</v>
       </c>
       <c r="AK368" t="n">
         <v>7.100856094477853</v>
@@ -60171,16 +60171,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2404731763378842</v>
+        <v>0.2404731763378833</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01427110593278799</v>
+        <v>0.01427110593278805</v>
       </c>
       <c r="AO368" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.28355700537033</v>
+        <v>-1.283557005370389</v>
       </c>
       <c r="AQ368" t="n">
         <v>19.14414414414414</v>
@@ -60324,10 +60324,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.081794385763164</v>
+        <v>7.081794385763168</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1711942003688769</v>
+        <v>-0.1711942003688813</v>
       </c>
       <c r="AK369" t="n">
         <v>7.090764621929079</v>
@@ -60336,16 +60336,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2453259423721931</v>
+        <v>0.2453259423721924</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01502424352484369</v>
+        <v>0.01502424352484376</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.4756424387980298</v>
+        <v>0.4756424387980304</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.814459861875897</v>
+        <v>-1.814459861875991</v>
       </c>
       <c r="AQ369" t="n">
         <v>15.5667701863354</v>
@@ -60489,10 +60489,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.068234493406102</v>
+        <v>7.068234493406101</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1557345887735337</v>
+        <v>-0.1557345887735329</v>
       </c>
       <c r="AK370" t="n">
         <v>7.110983013755962</v>
@@ -60501,16 +60501,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2481172514763508</v>
+        <v>0.2481172514763511</v>
       </c>
       <c r="AN370" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4781214750573159</v>
+        <v>0.4781214750573156</v>
       </c>
       <c r="AP370" t="n">
-        <v>-1.452804883187617</v>
+        <v>-1.452804883187595</v>
       </c>
       <c r="AQ370" t="n">
         <v>19.33170582850168</v>
@@ -60654,28 +60654,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.047011693433886</v>
+        <v>7.04701169343388</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1469114622632315</v>
+        <v>-0.1469114622632253</v>
       </c>
       <c r="AK371" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL371" t="n">
-        <v>-0.1936362268489642</v>
+        <v>-0.1936362268489633</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2517176519946896</v>
+        <v>0.2517176519946887</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.01672959897123732</v>
+        <v>0.01672959897123727</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.482044795280705</v>
+        <v>0.4820447952807055</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.244932890532577</v>
+        <v>-1.244932890532441</v>
       </c>
       <c r="AQ371" t="n">
         <v>18.62348178137652</v>
@@ -60819,28 +60819,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.043635211714482</v>
+        <v>7.043635211714486</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.135635219343877</v>
+        <v>-0.1356352193438806</v>
       </c>
       <c r="AK372" t="n">
-        <v>7.069112439760902</v>
+        <v>7.069112439760901</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1611124473902965</v>
+        <v>-0.1611124473902956</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2568291528619773</v>
+        <v>0.2568291528619769</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01758784222749221</v>
+        <v>0.0175878422274923</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.4888256589627545</v>
+        <v>0.488825658962754</v>
       </c>
       <c r="AP372" t="n">
-        <v>-0.9891368860718699</v>
+        <v>-0.9891368860719471</v>
       </c>
       <c r="AQ372" t="n">
         <v>23.98305084745763</v>
@@ -60984,10 +60984,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.045320696769622</v>
+        <v>7.04532069676962</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1373207043990163</v>
+        <v>-0.1373207043990146</v>
       </c>
       <c r="AK373" t="n">
         <v>7.067486653848666</v>
@@ -60996,16 +60996,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2611441025487395</v>
+        <v>0.2611441025487396</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.01863884916361525</v>
+        <v>0.01863884916361523</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.4958891106408185</v>
+        <v>0.4958891106408189</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.017305448193841</v>
+        <v>-1.017305448193802</v>
       </c>
       <c r="AQ373" t="n">
         <v>21.6350333236743</v>
@@ -61149,10 +61149,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.052957186540217</v>
+        <v>7.052957186540212</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1449571941696117</v>
+        <v>-0.1449571941696064</v>
       </c>
       <c r="AK374" t="n">
         <v>7.066060765041626</v>
@@ -61161,16 +61161,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2646928033319798</v>
+        <v>0.2646928033319788</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.01961447184998982</v>
+        <v>0.0196144718499898</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.4990325267638059</v>
+        <v>0.4990325267638065</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.17302240203794</v>
+        <v>-1.173022402037825</v>
       </c>
       <c r="AQ374" t="n">
         <v>18.98504273504274</v>
@@ -61314,28 +61314,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI375" t="n">
-        <v>7.055218091951101</v>
+        <v>7.055218091951103</v>
       </c>
       <c r="AJ375" t="n">
-        <v>-0.1472180995804955</v>
+        <v>-0.1472180995804973</v>
       </c>
       <c r="AK375" t="n">
-        <v>7.064646745753511</v>
+        <v>7.06464674575351</v>
       </c>
       <c r="AL375" t="n">
-        <v>-0.1566467533829057</v>
+        <v>-0.1566467533829048</v>
       </c>
       <c r="AM375" t="n">
-        <v>0.2692457951306195</v>
+        <v>0.2692457951306194</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.02045122459205889</v>
+        <v>0.02045122459205891</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.5009265659871953</v>
+        <v>0.5009265659871951</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.210005799573701</v>
+        <v>-1.210005799573742</v>
       </c>
       <c r="AQ375" t="n">
         <v>18.01022552178176</v>
@@ -61479,10 +61479,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.050463258619342</v>
+        <v>7.050463258619345</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1423631304455135</v>
+        <v>-0.1423631304455171</v>
       </c>
       <c r="AK376" t="n">
         <v>7.063274589921972</v>
@@ -61491,16 +61491,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2738618637550985</v>
+        <v>0.2738618637550991</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02103732430364852</v>
+        <v>0.02103732430364855</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5007948901071727</v>
+        <v>0.5007948901071723</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.093899743579132</v>
+        <v>-1.09389974357921</v>
       </c>
       <c r="AQ376" t="n">
         <v>22.43077558892409</v>
@@ -61817,13 +61817,13 @@
         <v/>
       </c>
       <c r="AM378" t="n">
-        <v>0.280344119587675</v>
+        <v>0.2803441195876753</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02230845224183686</v>
+        <v>0.02230845224183688</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.5036776407221306</v>
+        <v>0.5036776407221312</v>
       </c>
       <c r="AP378" t="n">
         <v>-1.246491204623905</v>
@@ -61970,10 +61970,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.056824809597053</v>
+        <v>7.056824809597052</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.1737247767906567</v>
+        <v>-0.1737247767906558</v>
       </c>
       <c r="AK379" t="n">
         <v>7.071238163852278</v>
@@ -61982,16 +61982,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2841407798055449</v>
+        <v>0.2841407798055452</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02276542233315987</v>
+        <v>0.02276542233315985</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5036956996297977</v>
+        <v>0.5036956996297983</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.735499502858073</v>
+        <v>-1.735499502858054</v>
       </c>
       <c r="AQ379" t="n">
         <v>21.70148069804337</v>
@@ -62135,10 +62135,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.04726592259491</v>
+        <v>7.047265922594908</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.1780656929501347</v>
+        <v>-0.178065692950133</v>
       </c>
       <c r="AK380" t="n">
         <v>7.075283303194255</v>
@@ -62147,16 +62147,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2869603504542605</v>
+        <v>0.2869603504542598</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02324367830537832</v>
+        <v>0.02324367830537833</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5029697249741727</v>
+        <v>0.5029697249741724</v>
       </c>
       <c r="AP380" t="n">
-        <v>-1.797910715459853</v>
+        <v>-1.797910715459816</v>
       </c>
       <c r="AQ380" t="n">
         <v>10.56260162601626</v>
@@ -62300,10 +62300,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.030237372659574</v>
+        <v>7.030237372659579</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.189337428354154</v>
+        <v>-0.1893374283541593</v>
       </c>
       <c r="AK381" t="n">
         <v>7.061088020066238</v>
@@ -62312,16 +62312,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.2909556153842325</v>
+        <v>0.2909556153842324</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02343150180192449</v>
+        <v>0.02343150180192457</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.501187497763653</v>
+        <v>0.5011874977636526</v>
       </c>
       <c r="AP381" t="n">
-        <v>-1.998175164150586</v>
+        <v>-1.998175164150696</v>
       </c>
       <c r="AQ381" t="n">
         <v>2.412954429083461</v>
@@ -62465,10 +62465,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.074556523891909</v>
+        <v>7.074556523891907</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.2166563812222311</v>
+        <v>-0.2166563812222293</v>
       </c>
       <c r="AK382" t="n">
         <v>7.045371831199247</v>
@@ -62477,16 +62477,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.2963660759601011</v>
+        <v>0.2963660759601009</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02388105320115907</v>
+        <v>0.02388105320115906</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.5011837436137521</v>
+        <v>0.5011837436137511</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.500689639035226</v>
+        <v>-2.500689639035188</v>
       </c>
       <c r="AQ382" t="n">
         <v>14.79370078740157</v>
@@ -62630,10 +62630,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.103552248295395</v>
+        <v>7.103552248295403</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2215522788129736</v>
+        <v>-0.2215522788129807</v>
       </c>
       <c r="AK383" t="n">
         <v>7.078406423284397</v>
@@ -62642,16 +62642,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.29984079129971</v>
+        <v>0.2998407912997099</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02427773372157399</v>
+        <v>0.02427773372157407</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.4964684575356704</v>
+        <v>0.4964684575356701</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.525433235757391</v>
+        <v>-2.525433235757525</v>
       </c>
       <c r="AQ383" t="n">
         <v>19.43824404761905</v>
@@ -62807,16 +62807,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3035220749319825</v>
+        <v>0.3035220749319821</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02465824743687012</v>
+        <v>0.02465824743687013</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.4899948718309226</v>
+        <v>0.4899948718309223</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.237361550577034</v>
+        <v>-2.237361550577025</v>
       </c>
       <c r="AQ384" t="n">
         <v>23.21003479216261</v>
@@ -62960,10 +62960,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.12777959440025</v>
+        <v>7.127779594400253</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.2307797584322326</v>
+        <v>-0.2307797584322353</v>
       </c>
       <c r="AK385" t="n">
         <v>7.110202206771168</v>
@@ -62972,16 +62972,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3056770963992281</v>
+        <v>0.3056770963992276</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02512392944114572</v>
+        <v>0.02512392944114575</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4836004785809395</v>
+        <v>0.48360047858094</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.571887198688558</v>
+        <v>-2.571887198688598</v>
       </c>
       <c r="AQ385" t="n">
         <v>22.65024038461538</v>
@@ -63125,28 +63125,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.117424820782309</v>
+        <v>7.117424820782308</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2204249848142918</v>
+        <v>-0.2204249848142901</v>
       </c>
       <c r="AK386" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL386" t="n">
-        <v>-0.2182210070512509</v>
+        <v>-0.21822100705125</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3083414575758074</v>
+        <v>0.3083414575758079</v>
       </c>
       <c r="AN386" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.474982443940299</v>
+        <v>0.4749824439402989</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.311874447286236</v>
+        <v>-2.311874447286193</v>
       </c>
       <c r="AQ386" t="n">
         <v>25.17604591987692</v>
@@ -63290,10 +63290,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.116315246651977</v>
+        <v>7.116315246651979</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.2198151360257565</v>
+        <v>-0.2198151360257583</v>
       </c>
       <c r="AK387" t="n">
         <v>7.112470209890858</v>
@@ -63302,16 +63302,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3094443575020182</v>
+        <v>0.3094443575020188</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.0257875072203187</v>
+        <v>0.02578750722031873</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.4671039145039241</v>
+        <v>0.467103914503924</v>
       </c>
       <c r="AP387" t="n">
-        <v>-2.246620026390865</v>
+        <v>-2.246620026390889</v>
       </c>
       <c r="AQ387" t="n">
         <v>24.97668997668998</v>
@@ -63455,28 +63455,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.109165799046384</v>
+        <v>7.109165799046382</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.1981660241135224</v>
+        <v>-0.1981660241135206</v>
       </c>
       <c r="AK388" t="n">
-        <v>7.105086649080124</v>
+        <v>7.105086649080123</v>
       </c>
       <c r="AL388" t="n">
-        <v>-0.1940868741472626</v>
+        <v>-0.1940868741472617</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3112159059696454</v>
+        <v>0.3112159059696449</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.02619128791084346</v>
+        <v>0.02619128791084347</v>
       </c>
       <c r="AO388" t="n">
-        <v>0.4597800393113445</v>
+        <v>0.4597800393113443</v>
       </c>
       <c r="AP388" t="n">
-        <v>-1.809041966473271</v>
+        <v>-1.809041966473231</v>
       </c>
       <c r="AQ388" t="n">
         <v>26.295701084773</v>
@@ -63620,10 +63620,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.140476658697598</v>
+        <v>7.14047665869759</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.2639765289978913</v>
+        <v>-0.2639765289978833</v>
       </c>
       <c r="AK389" t="n">
         <v>7.107009848336411</v>
@@ -63632,16 +63632,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3120213667410843</v>
+        <v>0.3120213667410841</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02660872919284657</v>
+        <v>0.02660872919284651</v>
       </c>
       <c r="AO389" t="n">
-        <v>0.4527828726277016</v>
+        <v>0.4527828726277021</v>
       </c>
       <c r="AP389" t="n">
-        <v>-2.92634131629074</v>
+        <v>-2.926341316290596</v>
       </c>
       <c r="AQ389" t="n">
         <v>18.93374038896427</v>
@@ -63785,10 +63785,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.192104266103097</v>
+        <v>7.192104266103096</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.3266042928059782</v>
+        <v>-0.3266042928059765</v>
       </c>
       <c r="AK390" t="n">
         <v>7.130667004235951</v>
@@ -63797,16 +63797,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3119580514589064</v>
+        <v>0.3119580514589062</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02723917591229313</v>
+        <v>0.02723917591229311</v>
       </c>
       <c r="AO390" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP390" t="n">
-        <v>-3.817928756740285</v>
+        <v>-3.817928756740258</v>
       </c>
       <c r="AQ390" t="n">
         <v>21.7989417989418</v>
@@ -63962,7 +63962,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3060770546706492</v>
+        <v>0.3060770546706496</v>
       </c>
       <c r="AN391" t="n">
         <v>0.02737088803905663</v>
@@ -63971,7 +63971,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.687217725798318</v>
+        <v>-3.687217725798322</v>
       </c>
       <c r="AQ391" t="n">
         <v>19.39749780509219</v>
@@ -64115,10 +64115,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.16410590848237</v>
+        <v>7.164105908482372</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.2680058642318812</v>
+        <v>-0.2680058642318839</v>
       </c>
       <c r="AK392" t="n">
         <v>7.162206823443969</v>
@@ -64127,16 +64127,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.3021518080029227</v>
+        <v>0.3021518080029217</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02724691784252931</v>
+        <v>0.02724691784252936</v>
       </c>
       <c r="AO392" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP392" t="n">
-        <v>-2.573346866416288</v>
+        <v>-2.573346866416331</v>
       </c>
       <c r="AQ392" t="n">
         <v>23.6874831035415</v>
@@ -64280,10 +64280,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.165713254747866</v>
+        <v>7.165713254747862</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.2102131288628559</v>
+        <v>-0.2102131288628524</v>
       </c>
       <c r="AK393" t="n">
         <v>7.141021818380439</v>
@@ -64292,16 +64292,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.3004913268435098</v>
+        <v>0.3004913268435102</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02739193077523433</v>
+        <v>0.02739193077523432</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3752726470948202</v>
+        <v>0.3752726470948199</v>
       </c>
       <c r="AP393" t="n">
-        <v>-1.627744531597144</v>
+        <v>-1.627744531597089</v>
       </c>
       <c r="AQ393" t="n">
         <v>30.46142369991475</v>
@@ -64445,10 +64445,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.208249532027229</v>
+        <v>7.208249532027231</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3219494450521312</v>
+        <v>-0.321949445052133</v>
       </c>
       <c r="AK394" t="n">
         <v>7.146296571548195</v>
@@ -64457,16 +64457,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2982197220770054</v>
+        <v>0.2982197220770058</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02742417953210363</v>
+        <v>0.02742417953210373</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3625782951332472</v>
+        <v>0.3625782951332475</v>
       </c>
       <c r="AP394" t="n">
-        <v>-3.256367936666931</v>
+        <v>-3.256367936666958</v>
       </c>
       <c r="AQ394" t="n">
         <v>25.16672793152339</v>
@@ -64610,28 +64610,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.193412187855718</v>
+        <v>7.193412187855726</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3208121092729543</v>
+        <v>-0.3208121092729623</v>
       </c>
       <c r="AK395" t="n">
-        <v>7.176497065376474</v>
+        <v>7.176497065376473</v>
       </c>
       <c r="AL395" t="n">
-        <v>-0.3038969867937107</v>
+        <v>-0.3038969867937098</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2910761841041076</v>
+        <v>0.2910761841041086</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02685747952387152</v>
+        <v>0.02685747952387156</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.3370674577034428</v>
+        <v>0.3370674577034442</v>
       </c>
       <c r="AP395" t="n">
-        <v>-3.112137549565402</v>
+        <v>-3.112137549565511</v>
       </c>
       <c r="AQ395" t="n">
         <v>26.06625258799172</v>
@@ -64775,10 +64775,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.227115602342048</v>
+        <v>7.227115602342041</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3273157785810614</v>
+        <v>-0.3273157785810543</v>
       </c>
       <c r="AK396" t="n">
         <v>7.185469892270627</v>
@@ -64787,16 +64787,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2812269987605887</v>
+        <v>0.281226998760588</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02697180537422167</v>
+        <v>0.0269718053742217</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.3136210223326478</v>
+        <v>0.3136210223326474</v>
       </c>
       <c r="AP396" t="n">
-        <v>-3.08574377662453</v>
+        <v>-3.085743776624427</v>
       </c>
       <c r="AQ396" t="n">
         <v>26.96821266391142</v>
@@ -64940,10 +64940,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.187163192389372</v>
+        <v>7.187163192389367</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3014629665592938</v>
+        <v>-0.3014629665592885</v>
       </c>
       <c r="AK397" t="n">
         <v>7.208338760609084</v>
@@ -64952,16 +64952,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2681836981576122</v>
+        <v>0.2681836981576121</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02658698789673936</v>
+        <v>0.02658698789673927</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.285908150945263</v>
+        <v>0.2859081509452629</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.637149998460412</v>
+        <v>-2.63714999846034</v>
       </c>
       <c r="AQ397" t="n">
         <v>27.82696177062374</v>
@@ -65105,10 +65105,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.214951953115591</v>
+        <v>7.214951953115579</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.334951838674673</v>
+        <v>-0.3349518386746606</v>
       </c>
       <c r="AK398" t="n">
         <v>7.186200492654655</v>
@@ -65117,16 +65117,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2591628297636744</v>
+        <v>0.2591628297636748</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02587977479594339</v>
+        <v>0.02587977479594331</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.266108201492412</v>
+        <v>0.2661082014924122</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.99635759486535</v>
+        <v>-2.996357594865196</v>
       </c>
       <c r="AQ398" t="n">
         <v>27.30000495957943</v>
@@ -65270,10 +65270,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.197430004066455</v>
+        <v>7.197430004066453</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.305630077308642</v>
+        <v>-0.3056300773086402</v>
       </c>
       <c r="AK399" t="n">
         <v>7.201835396295348</v>
@@ -65282,16 +65282,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2466333883508319</v>
+        <v>0.2466333883508324</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.0247654344950328</v>
+        <v>0.02476543449503272</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.2401258754735003</v>
+        <v>0.2401258754735008</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.528667553133092</v>
+        <v>-2.528667553133083</v>
       </c>
       <c r="AQ399" t="n">
         <v>26.02210485133021</v>
@@ -65438,25 +65438,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.3291230670577869</v>
+        <v>-0.3291230670577878</v>
       </c>
       <c r="AK400" t="n">
-        <v>7.179650721554484</v>
+        <v>7.179650721554483</v>
       </c>
       <c r="AL400" t="n">
-        <v>-0.2786506986663007</v>
+        <v>-0.2786506986662998</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2377807761788571</v>
+        <v>0.2377807761788565</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.02334020127887793</v>
+        <v>0.02334020127887796</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.2171758918683914</v>
+        <v>0.2171758918683913</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.756739116666435</v>
+        <v>-2.75673911666646</v>
       </c>
       <c r="AQ400" t="n">
         <v>26.55895828309622</v>
@@ -65600,10 +65600,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.20852803773295</v>
+        <v>7.208528037732954</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2978281933725988</v>
+        <v>-0.2978281933726024</v>
       </c>
       <c r="AK401" t="n">
         <v>7.206616000051887</v>
@@ -65612,16 +65612,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.2255544515066686</v>
+        <v>0.2255544515066683</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.0206724522626571</v>
+        <v>0.0206724522626572</v>
       </c>
       <c r="AO401" t="n">
-        <v>0.1898019966940717</v>
+        <v>0.1898019966940708</v>
       </c>
       <c r="AP401" t="n">
-        <v>-2.296876954307927</v>
+        <v>-2.296876954307982</v>
       </c>
       <c r="AQ401" t="n">
         <v>16.2718797564688</v>
@@ -65765,10 +65765,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.19880309223843</v>
+        <v>7.198803092238432</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.287202979323391</v>
+        <v>-0.2872029793233928</v>
       </c>
       <c r="AK402" t="n">
         <v>7.18051307481679</v>
@@ -65777,16 +65777,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.2150441262650612</v>
+        <v>0.2150441262650616</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.01774895516388914</v>
+        <v>0.0177489551638892</v>
       </c>
       <c r="AO402" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.119327753717743</v>
+        <v>-2.119327753717773</v>
       </c>
       <c r="AQ402" t="n">
         <v>14.77597935726015</v>
@@ -65930,10 +65930,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.172424239411004</v>
+        <v>7.172424239411002</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2608241264959652</v>
+        <v>-0.2608241264959634</v>
       </c>
       <c r="AK403" t="n">
         <v>7.16705299197773</v>
@@ -65942,16 +65942,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.205433651489446</v>
+        <v>0.2054336514894463</v>
       </c>
       <c r="AN403" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO403" t="n">
-        <v>0.1417286033373026</v>
+        <v>0.1417286033373033</v>
       </c>
       <c r="AP403" t="n">
-        <v>-1.759310618264857</v>
+        <v>-1.759310618264842</v>
       </c>
       <c r="AQ403" t="n">
         <v>18.77082562014069</v>
@@ -66095,10 +66095,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.163756390646672</v>
+        <v>7.163756390646673</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2695565424716229</v>
+        <v>-0.2695565424716238</v>
       </c>
       <c r="AK404" t="n">
         <v>7.153532751444382</v>
@@ -66107,16 +66107,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.1941661953581061</v>
+        <v>0.1941661953581056</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.01312004055850013</v>
+        <v>0.01312004055850015</v>
       </c>
       <c r="AO404" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.841567079186516</v>
+        <v>-1.841567079186534</v>
       </c>
       <c r="AQ404" t="n">
         <v>25.11528101173355</v>
@@ -66260,10 +66260,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.158063699621738</v>
+        <v>7.158063699621736</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2875636118837006</v>
+        <v>-0.2875636118836988</v>
       </c>
       <c r="AK405" t="n">
         <v>7.150669702211316</v>
@@ -66272,16 +66272,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1839494937266881</v>
+        <v>0.183949493726688</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.01194074338472806</v>
+        <v>0.01194074338472802</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.1107549805175829</v>
+        <v>0.110754980517583</v>
       </c>
       <c r="AP405" t="n">
-        <v>-2.03099915444689</v>
+        <v>-2.030999154446876</v>
       </c>
       <c r="AQ405" t="n">
         <v>13.12612612612613</v>
@@ -66425,10 +66425,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.157435208014563</v>
+        <v>7.157435208014565</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.272335320166663</v>
+        <v>-0.2723353201666647</v>
       </c>
       <c r="AK406" t="n">
         <v>7.140926852093823</v>
@@ -66437,16 +66437,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1753430411611933</v>
+        <v>0.1753430411611928</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.00971765423202034</v>
+        <v>0.009717654232020439</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.09620195025422695</v>
+        <v>0.09620195025422784</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.816085835102861</v>
+        <v>-1.816085835102889</v>
       </c>
       <c r="AQ406" t="n">
         <v>21.08315925152229</v>
@@ -66590,10 +66590,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.150386811340072</v>
+        <v>7.15038681134007</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2679867754819174</v>
+        <v>-0.2679867754819156</v>
       </c>
       <c r="AK407" t="n">
         <v>7.142886401315924</v>
@@ -66602,16 +66602,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1664838398737872</v>
+        <v>0.1664838398737869</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.008089376136153875</v>
+        <v>0.008089376136153925</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.0848962688609296</v>
+        <v>0.08489626886092971</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.739134136482415</v>
+        <v>-1.7391341364824</v>
       </c>
       <c r="AQ407" t="n">
         <v>20.59649122807017</v>
@@ -66755,10 +66755,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.137094841694645</v>
+        <v>7.137094841694642</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2547949416397133</v>
+        <v>-0.2547949416397106</v>
       </c>
       <c r="AK408" t="n">
         <v>7.137840883333127</v>
@@ -66767,16 +66767,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1571907956492611</v>
+        <v>0.1571907956492617</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.006581947594647974</v>
+        <v>0.006581947594647856</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.07412699588694804</v>
+        <v>0.07412699588694738</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.560440892271773</v>
+        <v>-1.560440892271748</v>
       </c>
       <c r="AQ408" t="n">
         <v>20.77868675063845</v>
@@ -66920,10 +66920,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.123391234435203</v>
+        <v>7.1233912344352</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2666912908927221</v>
+        <v>-0.2666912908927195</v>
       </c>
       <c r="AK409" t="n">
         <v>7.12862724785568</v>
@@ -66932,16 +66932,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1487097707294961</v>
+        <v>0.1487097707294973</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005441006961990014</v>
+        <v>0.005441006961990058</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.06531270865715677</v>
+        <v>0.06531270865715666</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.683353509644539</v>
+        <v>-1.683353509644515</v>
       </c>
       <c r="AQ409" t="n">
         <v>14.40105946684894</v>
@@ -67085,10 +67085,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.11600731855288</v>
+        <v>7.116007318552882</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2873072529400869</v>
+        <v>-0.2873072529400895</v>
       </c>
       <c r="AK410" t="n">
         <v>7.118961040191934</v>
@@ -67097,16 +67097,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM410" t="n">
-        <v>0.1409513724492178</v>
+        <v>0.1409513724492179</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005644373135176822</v>
+        <v>0.005644373135176906</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.05986577613532174</v>
+        <v>0.0598657761353214</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.902826462226918</v>
+        <v>-1.902826462226957</v>
       </c>
       <c r="AQ410" t="n">
         <v>10.08011806873287</v>
@@ -67250,10 +67250,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.115262454587763</v>
+        <v>7.11526245458776</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2838625369852235</v>
+        <v>-0.2838625369852208</v>
       </c>
       <c r="AK411" t="n">
         <v>7.113208458946866</v>
@@ -67265,13 +67265,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005618445165739616</v>
+        <v>0.005618445165739529</v>
       </c>
       <c r="AO411" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.835305502148032</v>
+        <v>-1.835305502148007</v>
       </c>
       <c r="AQ411" t="n">
         <v>8.707958707958708</v>
@@ -67427,16 +67427,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM412" t="n">
-        <v>0.1248427026608149</v>
+        <v>0.1248427026608145</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005050876420738246</v>
+        <v>0.005050876420738303</v>
       </c>
       <c r="AO412" t="n">
-        <v>0.04692762159458042</v>
+        <v>0.04692762159457986</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.750285662434824</v>
+        <v>-1.750285662434831</v>
       </c>
       <c r="AQ412" t="n">
         <v>13.8093281282104</v>
@@ -67580,10 +67580,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI413" t="n">
-        <v>7.100218718661557</v>
+        <v>7.100218718661558</v>
       </c>
       <c r="AJ413" t="n">
-        <v>-0.2699188643829924</v>
+        <v>-0.2699188643829933</v>
       </c>
       <c r="AK413" t="n">
         <v>7.105971078464224</v>
@@ -67595,13 +67595,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005209570180715356</v>
+        <v>0.00520957018071537</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.0421970173931332</v>
+        <v>0.04219701739313308</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.628242528710586</v>
+        <v>-1.628242528710603</v>
       </c>
       <c r="AQ413" t="n">
         <v>14.99513145082765</v>
@@ -67745,10 +67745,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.097935875054437</v>
+        <v>7.097935875054439</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2822358208857363</v>
+        <v>-0.2822358208857381</v>
       </c>
       <c r="AK414" t="n">
         <v>7.101361129315627</v>
@@ -67757,16 +67757,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.1117472247487875</v>
+        <v>0.1117472247487876</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.005385102682029907</v>
+        <v>0.005385102682029925</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.03866992220359</v>
+        <v>0.03866992220359033</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.749707041474974</v>
+        <v>-1.749707041475001</v>
       </c>
       <c r="AQ414" t="n">
         <v>13.95264992188439</v>
@@ -67910,10 +67910,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI415" t="n">
-        <v>7.097978821692022</v>
+        <v>7.097978821692021</v>
       </c>
       <c r="AJ415" t="n">
-        <v>-0.2799789819093075</v>
+        <v>-0.2799789819093057</v>
       </c>
       <c r="AK415" t="n">
         <v>7.099648834314064</v>
@@ -67922,16 +67922,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.1065475925362033</v>
+        <v>0.1065475925362025</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005956926407440957</v>
+        <v>0.005956926407441003</v>
       </c>
       <c r="AO415" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.702251341870201</v>
+        <v>-1.702251341870187</v>
       </c>
       <c r="AQ415" t="n">
         <v>13.86075949367089</v>
@@ -68087,16 +68087,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.1013724682419977</v>
+        <v>0.1013724682419976</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.006126167203105798</v>
+        <v>0.006126167203105847</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.03348722035246332</v>
+        <v>0.03348722035246277</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.540086272869379</v>
+        <v>-1.540086272869385</v>
       </c>
       <c r="AQ416" t="n">
         <v>22.55166217430368</v>
@@ -68240,10 +68240,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI417" t="n">
-        <v>7.087097940453345</v>
+        <v>7.087097940453343</v>
       </c>
       <c r="AJ417" t="n">
-        <v>-0.2700980281913825</v>
+        <v>-0.2700980281913798</v>
       </c>
       <c r="AK417" t="n">
         <v>7.090805518999606</v>
@@ -68252,16 +68252,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.09919462776856321</v>
+        <v>0.09919462776856289</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.006113943880485972</v>
+        <v>0.006113943880485968</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.03204155062895153</v>
+        <v>0.03204155062895098</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.554670831775283</v>
+        <v>-1.554670831775259</v>
       </c>
       <c r="AQ417" t="n">
         <v>17.4266975308642</v>
@@ -68417,16 +68417,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.097507502547015</v>
+        <v>0.09750750254701511</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.005510714664730507</v>
+        <v>0.005510714664730422</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.03001455024934374</v>
+        <v>0.03001455024934274</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.613360789246392</v>
+        <v>-1.613360789246399</v>
       </c>
       <c r="AQ418" t="n">
         <v>14.21712456655108</v>
@@ -68582,16 +68582,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.09380549503386901</v>
+        <v>0.09380549503386949</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.004784904607979881</v>
+        <v>0.004784904607979855</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.02699383492044782</v>
+        <v>0.02699383492044827</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.570592769098327</v>
+        <v>-1.570592769098333</v>
       </c>
       <c r="AQ419" t="n">
         <v>17.8297199638663</v>
@@ -68735,10 +68735,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.097145375663951</v>
+        <v>7.097145375663948</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2729452223131208</v>
+        <v>-0.2729452223131181</v>
       </c>
       <c r="AK420" t="n">
         <v>7.093828611034739</v>
@@ -68747,16 +68747,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.08945254406056438</v>
+        <v>0.08945254406056392</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.004001520125414798</v>
+        <v>0.004001520125414807</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.02385555423225116</v>
+        <v>0.02385555423225172</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.536594443203972</v>
+        <v>-1.536594443203949</v>
       </c>
       <c r="AQ420" t="n">
         <v>22.01152630600483</v>
@@ -68900,10 +68900,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.088227962421951</v>
+        <v>7.088227962421954</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.262227748798904</v>
+        <v>-0.2622277487989066</v>
       </c>
       <c r="AK421" t="n">
         <v>7.092951699003613</v>
@@ -68912,16 +68912,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.07912491692886899</v>
+        <v>0.07912491692886864</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.003813743757049903</v>
+        <v>0.003813743757049957</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.01902803623666316</v>
+        <v>0.01902803623666371</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.402662234957516</v>
+        <v>-1.402662234957552</v>
       </c>
       <c r="AQ421" t="n">
         <v>34.95077872465472</v>
@@ -69065,10 +69065,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.082675656384673</v>
+        <v>7.082675656384675</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2467758265201709</v>
+        <v>-0.2467758265201727</v>
       </c>
       <c r="AK422" t="n">
         <v>7.085940899278786</v>
@@ -69077,16 +69077,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.07019093860911668</v>
+        <v>0.07019093860911679</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.003788844982403339</v>
+        <v>0.003788844982403293</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.01530727852465064</v>
+        <v>0.0153072785246503</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.219255624926024</v>
+        <v>-1.219255624926049</v>
       </c>
       <c r="AQ422" t="n">
         <v>32.91054255126112</v>
@@ -69230,10 +69230,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.082585232341567</v>
+        <v>7.082585232341569</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2597850728872215</v>
+        <v>-0.2597850728872233</v>
       </c>
       <c r="AK423" t="n">
         <v>7.080231185021037</v>
@@ -69242,16 +69242,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.0607230145131474</v>
+        <v>0.06072301451314636</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.003218097337044118</v>
+        <v>0.003218097337044184</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.01127031184523342</v>
+        <v>0.01127031184523331</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.354123018284604</v>
+        <v>-1.354123018284628</v>
       </c>
       <c r="AQ423" t="n">
         <v>33.01778542742398</v>
@@ -69395,10 +69395,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.082752176397555</v>
+        <v>7.082752176397554</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2453522168333464</v>
+        <v>-0.2453522168333455</v>
       </c>
       <c r="AK424" t="n">
         <v>7.078545045220129</v>
@@ -69407,16 +69407,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.04987769893955558</v>
+        <v>0.04987769893955601</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.002647769861786137</v>
+        <v>0.002647769861786034</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.00755590738572276</v>
+        <v>0.007555907385723093</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.183549452314946</v>
+        <v>-1.183549452314941</v>
       </c>
       <c r="AQ424" t="n">
         <v>34.60652659178685</v>
@@ -69560,10 +69560,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI425" t="n">
-        <v>7.073418742129174</v>
+        <v>7.073418742129173</v>
       </c>
       <c r="AJ425" t="n">
-        <v>-0.2359186467617427</v>
+        <v>-0.2359186467617418</v>
       </c>
       <c r="AK425" t="n">
         <v>7.075576762908686</v>
@@ -69572,16 +69572,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.03723342047483359</v>
+        <v>0.03723342047483347</v>
       </c>
       <c r="AN425" t="n">
-        <v>0.0007434096776329363</v>
+        <v>0.0007434096776329864</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.003691827899839573</v>
+        <v>0.003691827899840794</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.070919300606854</v>
+        <v>-1.070919300606848</v>
       </c>
       <c r="AQ425" t="n">
         <v>37.07633053221289</v>
@@ -69737,16 +69737,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM426" t="n">
-        <v>0.02391394499985428</v>
+        <v>0.02391394499985489</v>
       </c>
       <c r="AN426" t="n">
-        <v>0.0004638728584110997</v>
+        <v>0.0004638728584110585</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.00150427765126282</v>
+        <v>0.001504277651263042</v>
       </c>
       <c r="AP426" t="n">
-        <v>-1.11050563204875</v>
+        <v>-1.110505632048755</v>
       </c>
       <c r="AQ426" t="n">
         <v>34.78667081905948</v>
@@ -69890,10 +69890,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI427" t="n">
-        <v>7.061175551975939</v>
+        <v>7.06117555197594</v>
       </c>
       <c r="AJ427" t="n">
-        <v>-0.2336756854903435</v>
+        <v>-0.2336756854903443</v>
       </c>
       <c r="AK427" t="n">
         <v>7.061105294515807</v>
@@ -69902,16 +69902,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM427" t="n">
-        <v>0.01023096587809661</v>
+        <v>0.01023096587809607</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.0001641525470544823</v>
+        <v>-0.0001641525470544615</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.0002530929795961923</v>
+        <v>0.000253092979595082</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.032242914660647</v>
+        <v>-1.032242914660661</v>
       </c>
       <c r="AQ427" t="n">
         <v>39.87004103967168</v>
@@ -70067,16 +70067,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.001349940557734956</v>
+        <v>-0.001349940557734529</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.001242569541730382</v>
+        <v>-0.001242569541730301</v>
       </c>
       <c r="AO428" t="n">
-        <v>9.828375502929365e-05</v>
+        <v>9.828375502973774e-05</v>
       </c>
       <c r="AP428" t="n">
-        <v>-0.9364901210219889</v>
+        <v>-0.9364901210219928</v>
       </c>
       <c r="AQ428" t="n">
         <v>40.21566440185241</v>
@@ -70220,10 +70220,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.051845784111939</v>
+        <v>7.051845784111937</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2217457246026617</v>
+        <v>-0.22174572460266</v>
       </c>
       <c r="AK429" t="n">
         <v>7.04924004450221</v>
@@ -70232,16 +70232,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.01245927794565087</v>
+        <v>-0.0124592779456514</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.002690846636687106</v>
+        <v>-0.002690846636687166</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.0009149443224345521</v>
+        <v>0.000914944322433886</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.8888893481318413</v>
+        <v>-0.8888893481318249</v>
       </c>
       <c r="AQ429" t="n">
         <v>37.07230686982091</v>
@@ -70385,10 +70385,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.044932512363691</v>
+        <v>7.044932512363692</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.2339326420633983</v>
+        <v>-0.2339326420633991</v>
       </c>
       <c r="AK430" t="n">
         <v>7.044607485549974</v>
@@ -70397,16 +70397,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.02351974718911197</v>
+        <v>-0.0235197471891116</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.003286981705062079</v>
+        <v>-0.003286981705062081</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.002235402288773947</v>
+        <v>0.002235402288773058</v>
       </c>
       <c r="AP430" t="n">
-        <v>-1.019515488213925</v>
+        <v>-1.019515488213939</v>
       </c>
       <c r="AQ430" t="n">
         <v>35.1345995045417</v>
@@ -70550,10 +70550,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.041380724566422</v>
+        <v>7.04138072456642</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2399805399350745</v>
+        <v>-0.2399805399350727</v>
       </c>
       <c r="AK431" t="n">
         <v>7.036677431055121</v>
@@ -70562,16 +70562,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.03604973348542533</v>
+        <v>-0.03604973348542571</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003896888881646653</v>
+        <v>-0.003896888881646666</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.004508577134016534</v>
+        <v>0.004508577134016423</v>
       </c>
       <c r="AP431" t="n">
-        <v>-1.080586188982384</v>
+        <v>-1.080586188982368</v>
       </c>
       <c r="AQ431" t="n">
         <v>27.75274294670847</v>
@@ -70715,10 +70715,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.031781164871437</v>
+        <v>7.031781164871438</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2312812487947769</v>
+        <v>-0.2312812487947777</v>
       </c>
       <c r="AK432" t="n">
         <v>7.031531243279009</v>
@@ -70727,16 +70727,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.0496421115884523</v>
+        <v>-0.04964211158845258</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003622848094475932</v>
+        <v>-0.003622848094475877</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.007358432861332531</v>
+        <v>0.007358432861333086</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.9776792404870553</v>
+        <v>-0.9776792404870693</v>
       </c>
       <c r="AQ432" t="n">
         <v>35.29620661824052</v>
@@ -70892,16 +70892,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.06336633742876464</v>
+        <v>-0.06336633742876532</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.00383222203166729</v>
+        <v>-0.003832222031667326</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.0113935335626284</v>
+        <v>0.01139353356262962</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.9077068786391019</v>
+        <v>-0.9077068786391058</v>
       </c>
       <c r="AQ433" t="n">
         <v>35.93909601634321</v>
@@ -71045,10 +71045,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI434" t="n">
-        <v>7.012358254068223</v>
+        <v>7.012358254068221</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.220358437173692</v>
+        <v>-0.2203584371736902</v>
       </c>
       <c r="AK434" t="n">
         <v>7.010266108789461</v>
@@ -71057,16 +71057,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.07815930192347351</v>
+        <v>-0.07815930192347212</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.0037302018478894</v>
+        <v>-0.003730201847889384</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.01669360800688513</v>
+        <v>0.01669360800688602</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.8464978886523586</v>
+        <v>-0.8464978886523424</v>
       </c>
       <c r="AQ434" t="n">
         <v>35.15923365842881</v>
@@ -71210,10 +71210,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI435" t="n">
-        <v>7.001516536947593</v>
+        <v>7.001516536947591</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.2107164423431005</v>
+        <v>-0.2107164423430987</v>
       </c>
       <c r="AK435" t="n">
         <v>7.003692382618654</v>
@@ -71222,16 +71222,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.09225745624393369</v>
+        <v>-0.09225745624393285</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.003729646461095512</v>
+        <v>-0.003729646461095566</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.02283737241168637</v>
+        <v>0.02283737241168682</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.7351651051066752</v>
+        <v>-0.7351651051066588</v>
       </c>
       <c r="AQ435" t="n">
         <v>39.72846441947566</v>
@@ -71375,10 +71375,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI436" t="n">
-        <v>6.98285303226683</v>
+        <v>6.982853032266831</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.1977530490514976</v>
+        <v>-0.1977530490514985</v>
       </c>
       <c r="AK436" t="n">
         <v>6.994908837140057</v>
@@ -71387,16 +71387,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.1040956648961724</v>
+        <v>-0.1040956648961739</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.004775368000139335</v>
+        <v>-0.004775368000139281</v>
       </c>
       <c r="AO436" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.5873560645130924</v>
+        <v>-0.5873560645131055</v>
       </c>
       <c r="AQ436" t="n">
         <v>40.89169418809222</v>
@@ -71540,10 +71540,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.976537964100197</v>
+        <v>6.976537964100195</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1673381540721204</v>
+        <v>-0.1673381540721186</v>
       </c>
       <c r="AK437" t="n">
         <v>6.976048621620001</v>
@@ -71552,16 +71552,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1171809788132883</v>
+        <v>-0.1171809788132892</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.006568629287185546</v>
+        <v>-0.006568629287185491</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.03914952746580425</v>
+        <v>0.03914952746580436</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.244365528744401</v>
+        <v>-0.2443655287443834</v>
       </c>
       <c r="AQ437" t="n">
         <v>48.68742368742369</v>
@@ -71708,7 +71708,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1582257113591101</v>
+        <v>-0.1582257113591092</v>
       </c>
       <c r="AK438" t="n">
         <v>6.970728111892008</v>
@@ -71717,16 +71717,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.127636816539944</v>
+        <v>-0.127636816539943</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.007451019732577668</v>
+        <v>-0.00745101973257774</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.04750067483060583</v>
+        <v>0.04750067483060572</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.1411566897223107</v>
+        <v>-0.1411566897223032</v>
       </c>
       <c r="AQ438" t="n">
         <v>49.78866648552365</v>
@@ -71885,13 +71885,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.008628156625160088</v>
+        <v>-0.008628156625160163</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.05751510742764043</v>
+        <v>0.05751510742764121</v>
       </c>
       <c r="AP439" t="n">
-        <v>-0.02985731997459472</v>
+        <v>-0.02985731997459668</v>
       </c>
       <c r="AQ439" t="n">
         <v>51.95891065456283</v>
@@ -72035,10 +72035,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.950644730799358</v>
+        <v>6.950644730799363</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1501448147226974</v>
+        <v>-0.1501448147227027</v>
       </c>
       <c r="AK440" t="n">
         <v>6.959853578800648</v>
@@ -72047,16 +72047,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1469566450661546</v>
+        <v>-0.1469566450661556</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.009026348114251986</v>
+        <v>-0.009026348114251901</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.06603756167960417</v>
+        <v>0.06603756167960351</v>
       </c>
       <c r="AP440" t="n">
-        <v>-0.04957227832841285</v>
+        <v>-0.04957227832847518</v>
       </c>
       <c r="AQ440" t="n">
         <v>49.76960567124502</v>
@@ -72200,28 +72200,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.934622414140156</v>
+        <v>6.934622414140152</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1321226430219919</v>
+        <v>-0.1321226430219875</v>
       </c>
       <c r="AK441" t="n">
-        <v>6.94711441643572</v>
+        <v>6.947114416435721</v>
       </c>
       <c r="AL441" t="n">
-        <v>-0.1446146453175556</v>
+        <v>-0.1446146453175565</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1568781652619925</v>
+        <v>-0.1568781652619921</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.010042871337475</v>
+        <v>-0.01004287133747513</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.07699206242755485</v>
+        <v>0.07699206242755419</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.1550111672272632</v>
+        <v>0.1550111672273127</v>
       </c>
       <c r="AQ441" t="n">
         <v>58.94401589527817</v>
@@ -72365,10 +72365,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.928042396530076</v>
+        <v>6.928042396530073</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1335425224150857</v>
+        <v>-0.133542522415083</v>
       </c>
       <c r="AK442" t="n">
         <v>6.933186989735641</v>
@@ -72377,16 +72377,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1650917115670576</v>
+        <v>-0.1650917115670582</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.0106149464753251</v>
+        <v>-0.01061494647532512</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.08732871254562191</v>
+        <v>0.08732871254562202</v>
       </c>
       <c r="AP442" t="n">
-        <v>0.1384398386498393</v>
+        <v>0.1384398386498683</v>
       </c>
       <c r="AQ442" t="n">
         <v>55.65399624223154</v>
@@ -72530,10 +72530,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.941461393298105</v>
+        <v>6.941461393298106</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1469615191831144</v>
+        <v>-0.1469615191831153</v>
       </c>
       <c r="AK443" t="n">
         <v>6.925995477801935</v>
@@ -72542,16 +72542,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.1745447047691483</v>
+        <v>-0.1745447047691478</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01108963812755723</v>
+        <v>-0.01108963812755724</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.09935205695041804</v>
+        <v>0.09935205695041927</v>
       </c>
       <c r="AP443" t="n">
-        <v>-0.01497644213845123</v>
+        <v>-0.01497644213846336</v>
       </c>
       <c r="AQ443" t="n">
         <v>49.22214596202242</v>
@@ -72695,10 +72695,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.93323210397643</v>
+        <v>6.933232103976423</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1472323290435682</v>
+        <v>-0.147232329043562</v>
       </c>
       <c r="AK444" t="n">
         <v>6.938996539173566</v>
@@ -72707,16 +72707,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.1853013335308036</v>
+        <v>-0.1853013335308053</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01193987645426134</v>
+        <v>-0.01193987645426136</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1123648810347069</v>
+        <v>0.1123648810347067</v>
       </c>
       <c r="AP444" t="n">
-        <v>-0.01803400433169996</v>
+        <v>-0.01803400433163076</v>
       </c>
       <c r="AQ444" t="n">
         <v>44.95232436408907</v>
@@ -72860,10 +72860,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.928429644379657</v>
+        <v>6.928429644379658</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1496296336985043</v>
+        <v>-0.1496296336985061</v>
       </c>
       <c r="AK445" t="n">
         <v>6.93160690101155</v>
@@ -72875,13 +72875,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01257308415669778</v>
+        <v>-0.01257308415669775</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.125857898472412</v>
+        <v>0.1258578984724115</v>
       </c>
       <c r="AP445" t="n">
-        <v>-0.04547613693365601</v>
+        <v>-0.04547613693367852</v>
       </c>
       <c r="AQ445" t="n">
         <v>45.25195968645016</v>
@@ -73025,10 +73025,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.925068850639515</v>
+        <v>6.925068850639512</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1455688430101203</v>
+        <v>-0.1455688430101176</v>
       </c>
       <c r="AK446" t="n">
         <v>6.924763510572069</v>
@@ -73037,16 +73037,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM446" t="n">
-        <v>-0.2060805417157788</v>
+        <v>-0.2060805417157789</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01318646791849926</v>
+        <v>-0.01318646791849928</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1396251026736655</v>
+        <v>0.1396251026736647</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.001331178123722838</v>
+        <v>0.001331178123751393</v>
       </c>
       <c r="AQ446" t="n">
         <v>48.95703482090916</v>
@@ -73190,10 +73190,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.900929863197374</v>
+        <v>6.900929863197373</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1347297975845807</v>
+        <v>-0.1347297975845798</v>
       </c>
       <c r="AK447" t="n">
         <v>6.921049732547429</v>
@@ -73202,16 +73202,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2151279705591488</v>
+        <v>-0.2151279705591481</v>
       </c>
       <c r="AN447" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1518365696223548</v>
+        <v>0.1518365696223549</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.1262747588338355</v>
+        <v>0.1262747588338435</v>
       </c>
       <c r="AQ447" t="n">
         <v>49.97532894736842</v>
@@ -73355,10 +73355,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.895219010181459</v>
+        <v>6.89521901018146</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1302191436958635</v>
+        <v>-0.1302191436958644</v>
       </c>
       <c r="AK448" t="n">
         <v>6.89978353884127</v>
@@ -73370,13 +73370,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01278923357027009</v>
+        <v>-0.01278923357027006</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1644177475946104</v>
+        <v>0.1644177475946105</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.1780680365315467</v>
+        <v>0.1780680365315346</v>
       </c>
       <c r="AQ448" t="n">
         <v>47.61278246480211</v>
@@ -73520,10 +73520,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.879512239848579</v>
+        <v>6.87951223984858</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.1173123611559523</v>
+        <v>-0.1173123611559532</v>
       </c>
       <c r="AK449" t="n">
         <v>6.893260360395011</v>
@@ -73532,16 +73532,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.233692768734329</v>
+        <v>-0.233692768734328</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01245257184765153</v>
+        <v>-0.01245257184765156</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.179129523332087</v>
+        <v>0.1791295233320875</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.3270752588397787</v>
+        <v>0.3270752588397669</v>
       </c>
       <c r="AQ449" t="n">
         <v>51.00408075601375</v>
@@ -73685,10 +73685,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.882426232260446</v>
+        <v>6.882426232260437</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.1132263840853973</v>
+        <v>-0.1132263840853884</v>
       </c>
       <c r="AK450" t="n">
         <v>6.880758546638964</v>
@@ -73697,16 +73697,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.2433281856134891</v>
+        <v>-0.2433281856134888</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01202813951384066</v>
+        <v>-0.01202813951384067</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.1944608722019401</v>
+        <v>0.1944608722019407</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.3735609578737231</v>
+        <v>0.3735609578738251</v>
       </c>
       <c r="AQ450" t="n">
         <v>52.54948850803774</v>
@@ -73862,16 +73862,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2520264427810588</v>
+        <v>-0.25202644278106</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01246671652825437</v>
+        <v>-0.01246671652825434</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.2101991144027906</v>
+        <v>0.2101991144027905</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.9396869993792598</v>
+        <v>0.939686999379259</v>
       </c>
       <c r="AQ451" t="n">
         <v>65.32979171049863</v>
@@ -74015,10 +74015,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.841963898035317</v>
+        <v>6.841963898035326</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.07646382937076623</v>
+        <v>-0.07646382937077512</v>
       </c>
       <c r="AK452" t="n">
         <v>6.844785316397215</v>
@@ -74027,16 +74027,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2592973891940562</v>
+        <v>-0.2592973891940566</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01305068899435097</v>
+        <v>-0.01305068899435077</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2277185089957531</v>
+        <v>0.2277185089957524</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.7946882605952149</v>
+        <v>0.794688260595111</v>
       </c>
       <c r="AQ452" t="n">
         <v>58.60471170115841</v>
@@ -74180,28 +74180,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.845644916883085</v>
+        <v>6.845644916883079</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.08014484821853429</v>
+        <v>-0.08014484821852808</v>
       </c>
       <c r="AK453" t="n">
-        <v>6.849407886968131</v>
+        <v>6.849407886968132</v>
       </c>
       <c r="AL453" t="n">
-        <v>-0.08390781830358041</v>
+        <v>-0.08390781830358129</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.2668003223256257</v>
+        <v>-0.2668003223256254</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01367989020054944</v>
+        <v>-0.0136798902005495</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2456601220977563</v>
+        <v>0.2456601220977566</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7487140043297179</v>
+        <v>0.7487140043297899</v>
       </c>
       <c r="AQ453" t="n">
         <v>58.31271902700475</v>
@@ -74345,10 +74345,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.842084108625032</v>
+        <v>6.842084108625038</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.0695840704780597</v>
+        <v>-0.06958407047806503</v>
       </c>
       <c r="AK454" t="n">
         <v>6.852702018840203</v>
@@ -74357,16 +74357,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2735436467318143</v>
+        <v>-0.273543646731814</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.01403412282467997</v>
+        <v>-0.01403412282467991</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.2619835102172253</v>
+        <v>0.261983510217226</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.8683972750773455</v>
+        <v>0.8683972750772836</v>
       </c>
       <c r="AQ454" t="n">
         <v>63.58441955972757</v>
@@ -74510,10 +74510,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.863831060847773</v>
+        <v>6.863831060847785</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.09133102270080062</v>
+        <v>-0.09133102270081217</v>
       </c>
       <c r="AK455" t="n">
         <v>6.850973969550408</v>
@@ -74522,16 +74522,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.2787367835501612</v>
+        <v>-0.2787367835501617</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01406387644726603</v>
+        <v>-0.01406387644726588</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.2758112468611987</v>
+        <v>0.2758112468611976</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.6117510238643564</v>
+        <v>0.6117510238642219</v>
       </c>
       <c r="AQ455" t="n">
         <v>62.5530303030303</v>
@@ -74675,10 +74675,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.853037915615571</v>
+        <v>6.853037915615573</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.07753809490634289</v>
+        <v>-0.07753809490634467</v>
       </c>
       <c r="AK456" t="n">
         <v>6.873527983489108</v>
@@ -74690,13 +74690,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.013790177185657</v>
+        <v>-0.01379017718565697</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.285442546377481</v>
+        <v>0.2854425463774817</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.7703772441622895</v>
+        <v>0.7703772441622695</v>
       </c>
       <c r="AQ456" t="n">
         <v>68.73796844921122</v>
@@ -74852,7 +74852,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2865252693972544</v>
+        <v>-0.2865252693972545</v>
       </c>
       <c r="AN457" t="n">
         <v>-0.01327380582108439</v>
@@ -74861,7 +74861,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP457" t="n">
-        <v>0.5720048978375456</v>
+        <v>0.5720048978375459</v>
       </c>
       <c r="AQ457" t="n">
         <v>61.93811881188119</v>
@@ -75005,10 +75005,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.860047631936786</v>
+        <v>6.860047631936787</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.1030476624543644</v>
+        <v>-0.1030476624543653</v>
       </c>
       <c r="AK458" t="n">
         <v>6.865985861260643</v>
@@ -75017,16 +75017,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.290522309347949</v>
+        <v>-0.2905223093479492</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.01240158194086383</v>
+        <v>-0.01240158194086378</v>
       </c>
       <c r="AO458" t="n">
-        <v>0.3024992257449916</v>
+        <v>0.3024992257449914</v>
       </c>
       <c r="AP458" t="n">
-        <v>0.4675645678050873</v>
+        <v>0.4675645678050772</v>
       </c>
       <c r="AQ458" t="n">
         <v>58.16851702080729</v>
@@ -75170,10 +75170,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.801980414635013</v>
+        <v>6.801980414635016</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.04478065038330392</v>
+        <v>-0.04478065038330659</v>
       </c>
       <c r="AK459" t="n">
         <v>6.863576603094304</v>
@@ -75182,16 +75182,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.2950697019949103</v>
+        <v>-0.2950697019949104</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.0116105331596838</v>
+        <v>-0.01161053315968381</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3113800696686924</v>
+        <v>0.3113800696686918</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.14722151151879</v>
+        <v>1.147221511518761</v>
       </c>
       <c r="AQ459" t="n">
         <v>79.24917491749174</v>
@@ -75335,10 +75335,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.789283666813423</v>
+        <v>6.789283666813422</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.03208390256171434</v>
+        <v>-0.03208390256171256</v>
       </c>
       <c r="AK460" t="n">
         <v>6.809671190627447</v>
@@ -75347,16 +75347,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.2987092362344105</v>
+        <v>-0.2987092362344108</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.01030385953714813</v>
+        <v>-0.01030385953714808</v>
       </c>
       <c r="AO460" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.28818749803842</v>
+        <v>1.288187498038444</v>
       </c>
       <c r="AQ460" t="n">
         <v>82.03652529136127</v>
@@ -75500,10 +75500,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.789252537988938</v>
+        <v>6.789252537988933</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.02065255095890883</v>
+        <v>-0.0206525509589035</v>
       </c>
       <c r="AK461" t="n">
         <v>6.802840448144932</v>
@@ -75512,16 +75512,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3027504956929287</v>
+        <v>-0.3027504956929284</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.00881278602540958</v>
+        <v>-0.008812786025409641</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.332227117067963</v>
+        <v>0.3322271170679635</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.412097260525123</v>
+        <v>1.412097260525188</v>
       </c>
       <c r="AQ461" t="n">
         <v>83.09775366457262</v>
@@ -75665,10 +75665,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.774001672255927</v>
+        <v>6.774001672255932</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.005401685225897346</v>
+        <v>-0.005401685225902675</v>
       </c>
       <c r="AK462" t="n">
         <v>6.800260207803535</v>
@@ -75677,16 +75677,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3068099364477369</v>
+        <v>-0.3068099364477367</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.007070247176567734</v>
+        <v>-0.007070247176567688</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.3427146952658529</v>
+        <v>0.3427146952658534</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.577343453912065</v>
+        <v>1.577343453912008</v>
       </c>
       <c r="AQ462" t="n">
         <v>83.90243902439025</v>
@@ -75830,10 +75830,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.802628307046305</v>
+        <v>6.802628307046303</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.0281284138578286</v>
+        <v>-0.02812841385782594</v>
       </c>
       <c r="AK463" t="n">
         <v>6.781970485204615</v>
@@ -75842,16 +75842,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3121566752204096</v>
+        <v>-0.3121566752204101</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.005102880740085192</v>
+        <v>-0.005102880740085154</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3560731605465752</v>
+        <v>0.3560731605465757</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.303420740488044</v>
+        <v>1.303420740488078</v>
       </c>
       <c r="AQ463" t="n">
         <v>79.87303958177745</v>
@@ -75995,28 +75995,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.815944895083629</v>
+        <v>6.815944895083632</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.0259449332306021</v>
+        <v>-0.02594493323060476</v>
       </c>
       <c r="AK464" t="n">
-        <v>6.809638458820509</v>
+        <v>6.809638458820508</v>
       </c>
       <c r="AL464" t="n">
-        <v>-0.01963849696748188</v>
+        <v>-0.01963849696748099</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3181413841564625</v>
+        <v>-0.3181413841564619</v>
       </c>
       <c r="AN464" t="n">
-        <v>-0.003317316385138602</v>
+        <v>-0.003317316385138562</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.3690689225934927</v>
+        <v>0.3690689225934922</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.320112988335384</v>
+        <v>1.320112988335356</v>
       </c>
       <c r="AQ464" t="n">
         <v>81.66100362896702</v>
@@ -76160,10 +76160,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.821941449304759</v>
+        <v>6.821941449304753</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.0319414874517312</v>
+        <v>-0.03194148745172587</v>
       </c>
       <c r="AK465" t="n">
         <v>6.819973703544699</v>
@@ -76172,16 +76172,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3244228225822193</v>
+        <v>-0.3244228225822198</v>
       </c>
       <c r="AN465" t="n">
-        <v>-0.001700148658338674</v>
+        <v>-0.001700148658338742</v>
       </c>
       <c r="AO465" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.242734811900659</v>
+        <v>1.242734811900723</v>
       </c>
       <c r="AQ465" t="n">
         <v>78.39056776556777</v>
@@ -76325,10 +76325,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.826413262727742</v>
+        <v>6.826413262727749</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.03641330087471495</v>
+        <v>-0.03641330087472205</v>
       </c>
       <c r="AK466" t="n">
         <v>6.822087900644207</v>
@@ -76337,16 +76337,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3308797299382499</v>
+        <v>-0.3308797299382495</v>
       </c>
       <c r="AN466" t="n">
-        <v>-7.481797733216444e-05</v>
+        <v>-7.481797733213274e-05</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.3960788710418811</v>
+        <v>0.396078871041881</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.18397024508706</v>
+        <v>1.183970245086981</v>
       </c>
       <c r="AQ466" t="n">
         <v>78.98365042291209</v>
@@ -76490,10 +76490,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.812656647679548</v>
+        <v>6.81265664767955</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.01465678882334664</v>
+        <v>-0.01465678882334931</v>
       </c>
       <c r="AK467" t="n">
         <v>6.823881638371397</v>
@@ -76502,16 +76502,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3363418922753055</v>
+        <v>-0.3363418922753058</v>
       </c>
       <c r="AN467" t="n">
-        <v>0.001379920606120022</v>
+        <v>0.001379920606120097</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4081029523904164</v>
+        <v>0.4081029523904167</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.426200199707695</v>
+        <v>1.426200199707669</v>
       </c>
       <c r="AQ467" t="n">
         <v>83.57816711590297</v>
@@ -76655,10 +76655,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.802797817425507</v>
+        <v>6.802797817425505</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.009197735028045884</v>
+        <v>-0.009197735028044107</v>
       </c>
       <c r="AK468" t="n">
         <v>6.808320681191073</v>
@@ -76667,16 +76667,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3410659803634685</v>
+        <v>-0.3410659803634682</v>
       </c>
       <c r="AN468" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4198133218741356</v>
+        <v>0.4198133218741357</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.478216789207188</v>
+        <v>1.478216789207213</v>
       </c>
       <c r="AQ468" t="n">
         <v>83.65373918074005</v>
@@ -76826,22 +76826,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK469" t="n">
-        <v>6.795980661778267</v>
+        <v>6.795980661778266</v>
       </c>
       <c r="AL469" t="n">
-        <v>-0.002380579380806047</v>
+        <v>-0.002380579380805159</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3461577281601511</v>
+        <v>-0.3461577281601509</v>
       </c>
       <c r="AN469" t="n">
-        <v>0.004282887883574671</v>
+        <v>0.00428288788357468</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4328049372030962</v>
+        <v>0.4328049372030969</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.539467082609258</v>
+        <v>1.539467082609263</v>
       </c>
       <c r="AQ469" t="n">
         <v>84.90566037735849</v>
@@ -76985,10 +76985,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.800189882196235</v>
+        <v>6.800189882196236</v>
       </c>
       <c r="AJ470" t="n">
-        <v>-0.005989938653754301</v>
+        <v>-0.005989938653755189</v>
       </c>
       <c r="AK470" t="n">
         <v>6.78726841810145</v>
@@ -76997,16 +76997,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3502903933401412</v>
+        <v>-0.3502903933401418</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.005405808652032051</v>
+        <v>0.005405808652032067</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4450018361960529</v>
+        <v>0.4450018361960534</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.491748497297388</v>
+        <v>1.491748497297383</v>
       </c>
       <c r="AQ470" t="n">
         <v>83.80718419041381</v>
@@ -77150,10 +77150,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.79797208364255</v>
+        <v>6.797972083642554</v>
       </c>
       <c r="AJ471" t="n">
-        <v>-0.009372115686007376</v>
+        <v>-0.009372115686010929</v>
       </c>
       <c r="AK471" t="n">
         <v>6.791305278184372</v>
@@ -77162,16 +77162,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3548656112706069</v>
+        <v>-0.3548656112706071</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.006091291211178074</v>
+        <v>0.006091291211178139</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4593697101544711</v>
+        <v>0.4593697101544705</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.442519142421117</v>
+        <v>1.442519142421081</v>
       </c>
       <c r="AQ471" t="n">
         <v>82.48745240567671</v>
@@ -77315,10 +77315,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.800452644405181</v>
+        <v>6.800452644405178</v>
       </c>
       <c r="AJ472" t="n">
-        <v>-0.01185267644863774</v>
+        <v>-0.01185267644863508</v>
       </c>
       <c r="AK472" t="n">
         <v>6.789098969069376</v>
@@ -77333,10 +77333,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4721687943484544</v>
+        <v>0.4721687943484545</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.404392199013741</v>
+        <v>1.404392199013776</v>
       </c>
       <c r="AQ472" t="n">
         <v>79.31518593934199</v>
@@ -77480,10 +77480,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.778720347685821</v>
+        <v>6.778720347685814</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.01707986135958883</v>
+        <v>0.01707986135959594</v>
       </c>
       <c r="AK473" t="n">
         <v>6.790465135395929</v>
@@ -77492,16 +77492,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3625273381377937</v>
+        <v>-0.3625273381377933</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.007343464385960674</v>
+        <v>0.007343464385960585</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.4863203622043377</v>
+        <v>0.4863203622043382</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.718967726687749</v>
+        <v>1.718967726687834</v>
       </c>
       <c r="AQ473" t="n">
         <v>84.49074074074073</v>
@@ -77645,10 +77645,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.769755998762547</v>
+        <v>6.769755998762545</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.02364381202846833</v>
+        <v>0.02364381202847099</v>
       </c>
       <c r="AK474" t="n">
         <v>6.767889899932765</v>
@@ -77657,16 +77657,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3660007866474812</v>
+        <v>-0.3660007866474813</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.00826013782295415</v>
+        <v>0.008260137822954145</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.4997690914082398</v>
+        <v>0.4997690914082401</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.776447733059097</v>
+        <v>1.776447733059131</v>
       </c>
       <c r="AQ474" t="n">
         <v>85.25345622119815</v>
@@ -77810,10 +77810,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.789177604754239</v>
+        <v>6.789177604754244</v>
       </c>
       <c r="AJ475" t="n">
-        <v>0.01332216636392491</v>
+        <v>0.01332216636391959</v>
       </c>
       <c r="AK475" t="n">
         <v>6.759766754404358</v>
@@ -77822,16 +77822,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3700034659576358</v>
+        <v>-0.3700034659576351</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.00987171553454691</v>
+        <v>0.009871715534546958</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.5120623436103316</v>
+        <v>0.5120623436103324</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.645621086027352</v>
+        <v>1.645621086027296</v>
       </c>
       <c r="AQ475" t="n">
         <v>85.32527105921602</v>
@@ -77975,10 +77975,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.774331376960423</v>
+        <v>6.774331376960425</v>
       </c>
       <c r="AJ476" t="n">
-        <v>0.01776857573733093</v>
+        <v>0.01776857573732915</v>
       </c>
       <c r="AK476" t="n">
         <v>6.777856240868369</v>
@@ -77987,16 +77987,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3750442390024145</v>
+        <v>-0.3750442390024147</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01196068662558775</v>
+        <v>0.01196068662558781</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5238651846176465</v>
+        <v>0.5238651846176463</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.680943449342473</v>
+        <v>1.680943449342458</v>
       </c>
       <c r="AQ476" t="n">
         <v>84.47695200314055</v>
@@ -78152,16 +78152,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3816350905604304</v>
+        <v>-0.3816350905604307</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01460798460929558</v>
+        <v>0.01460798460929556</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.537958310473289</v>
+        <v>0.5379583104732891</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.627209299316994</v>
+        <v>1.627209299316998</v>
       </c>
       <c r="AQ477" t="n">
         <v>85.00614250614251</v>
@@ -78305,10 +78305,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.789815280543246</v>
+        <v>6.789815280543245</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.01031527291385181</v>
+        <v>-0.01031527291385093</v>
       </c>
       <c r="AK478" t="n">
         <v>6.744939020214936</v>
@@ -78317,16 +78317,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3872393091179336</v>
+        <v>-0.3872393091179339</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01685992867552227</v>
+        <v>0.01685992867552231</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5511317941481411</v>
+        <v>0.5511317941481415</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.344782590346758</v>
+        <v>1.344782590346771</v>
       </c>
       <c r="AQ478" t="n">
         <v>82.60150559016293</v>
@@ -78470,10 +78470,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.801295181477315</v>
+        <v>6.801295181477309</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.03129520055080093</v>
+        <v>-0.0312952005507956</v>
       </c>
       <c r="AK479" t="n">
         <v>6.772636231606738</v>
@@ -78482,16 +78482,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.393020019860339</v>
+        <v>-0.3930200198603389</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01873686412955489</v>
+        <v>0.01873686412955481</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5644439393662184</v>
+        <v>0.5644439393662187</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.10520581121148</v>
+        <v>1.105205811211542</v>
       </c>
       <c r="AQ479" t="n">
         <v>76.84604247104247</v>
@@ -78635,10 +78635,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.791632066062363</v>
+        <v>6.791632066062364</v>
       </c>
       <c r="AJ480" t="n">
-        <v>-0.0234321454080666</v>
+        <v>-0.02343214540806748</v>
       </c>
       <c r="AK480" t="n">
         <v>6.788619247652995</v>
@@ -78647,16 +78647,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3966294116439325</v>
+        <v>-0.3966294116439323</v>
       </c>
       <c r="AN480" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.576974471973372</v>
+        <v>0.5769744719733717</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.186476859823366</v>
+        <v>1.186476859823359</v>
       </c>
       <c r="AQ480" t="n">
         <v>74.69955156950672</v>
@@ -78800,10 +78800,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.779898505875916</v>
+        <v>6.779898505875918</v>
       </c>
       <c r="AJ481" t="n">
-        <v>-0.007398467728943814</v>
+        <v>-0.00739846772894559</v>
       </c>
       <c r="AK481" t="n">
         <v>6.776305653888958</v>
@@ -78812,16 +78812,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3980313152890726</v>
+        <v>-0.3980313152890724</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01933124704228378</v>
+        <v>0.0193312470422838</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.5877384296086169</v>
+        <v>0.5877384296086161</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.356475842636204</v>
+        <v>1.356475842636188</v>
       </c>
       <c r="AQ481" t="n">
         <v>76.57830278128949</v>
@@ -78965,10 +78965,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.771360892616113</v>
+        <v>6.771360892616116</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.001139145530859587</v>
+        <v>0.001139145530856922</v>
       </c>
       <c r="AK482" t="n">
         <v>6.76492936370744</v>
@@ -78977,16 +78977,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3979537985659305</v>
+        <v>-0.3979537985659302</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.0183584453609324</v>
+        <v>0.01835844536093246</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6001791687136281</v>
+        <v>0.6001791687136286</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.441515297066416</v>
+        <v>1.44151529706639</v>
       </c>
       <c r="AQ482" t="n">
         <v>77.56534508076359</v>
@@ -79130,10 +79130,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.751667781721844</v>
+        <v>6.751667781721842</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.02083225642512865</v>
+        <v>0.02083225642513042</v>
       </c>
       <c r="AK483" t="n">
         <v>6.753855191419989</v>
@@ -79142,16 +79142,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.3975762425746344</v>
+        <v>-0.3975762425746347</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01731206726614276</v>
+        <v>0.01731206726614282</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6129676701055393</v>
+        <v>0.6129676701055397</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.646360276993232</v>
+        <v>1.646360276993257</v>
       </c>
       <c r="AQ483" t="n">
         <v>82.96654246235056</v>
@@ -79295,10 +79295,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.729738669869288</v>
+        <v>6.72973866986929</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.03586153459848518</v>
+        <v>0.0358615345984834</v>
       </c>
       <c r="AK484" t="n">
         <v>6.736226026398153</v>
@@ -79307,16 +79307,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3964908591695859</v>
+        <v>-0.3964908591695858</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01740130648959376</v>
+        <v>0.01740130648959375</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6198907013195262</v>
+        <v>0.6198907013195265</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.795594927274907</v>
+        <v>1.795594927274892</v>
       </c>
       <c r="AQ484" t="n">
         <v>80.39647577092511</v>
@@ -79460,10 +79460,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.713320364291503</v>
+        <v>6.713320364291505</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.05917967385546952</v>
+        <v>0.05917967385546774</v>
       </c>
       <c r="AK485" t="n">
         <v>6.717723214958548</v>
@@ -79472,16 +79472,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.394760534481672</v>
+        <v>-0.3947605344816719</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01742962324324016</v>
+        <v>0.01742962324324019</v>
       </c>
       <c r="AO485" t="n">
-        <v>0.6272835381163622</v>
+        <v>0.6272835381163618</v>
       </c>
       <c r="AP485" t="n">
-        <v>2.028963267389809</v>
+        <v>2.028963267389796</v>
       </c>
       <c r="AQ485" t="n">
         <v>87.28070175438597</v>
@@ -79625,10 +79625,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.731179671396989</v>
+        <v>6.731179671396997</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.04132036674998396</v>
+        <v>0.04132036674997597</v>
       </c>
       <c r="AK486" t="n">
         <v>6.699415101064979</v>
@@ -79640,13 +79640,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.01766596732646103</v>
+        <v>0.0176659673264611</v>
       </c>
       <c r="AO486" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.816762279753399</v>
+        <v>1.816762279753319</v>
       </c>
       <c r="AQ486" t="n">
         <v>86.68311310232708</v>
@@ -79790,10 +79790,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.740946959621007</v>
+        <v>6.740946959621005</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.03085308157772371</v>
+        <v>0.03085308157772548</v>
       </c>
       <c r="AK487" t="n">
         <v>6.714685154719483</v>
@@ -79802,16 +79802,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.3929423394238508</v>
+        <v>-0.392942339423851</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.01842070378092631</v>
+        <v>0.0184207037809263</v>
       </c>
       <c r="AO487" t="n">
-        <v>0.640374511165978</v>
+        <v>0.6403745111659787</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.688819755019156</v>
+        <v>1.688819755019181</v>
       </c>
       <c r="AQ487" t="n">
         <v>84.57083958020989</v>
@@ -79955,10 +79955,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.7589577577717</v>
+        <v>6.758957757771704</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.006742105662137732</v>
+        <v>0.006742105662134179</v>
       </c>
       <c r="AK488" t="n">
         <v>6.722064699270507</v>
@@ -79967,16 +79967,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3931401656438959</v>
+        <v>-0.3931401656438955</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.01902711841846483</v>
+        <v>0.01902711841846487</v>
       </c>
       <c r="AO488" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.41867091232492</v>
+        <v>1.418670912324887</v>
       </c>
       <c r="AQ488" t="n">
         <v>80.32160972075135</v>
@@ -80120,10 +80120,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.763209774497792</v>
+        <v>6.763209774497788</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.007790133949473699</v>
+        <v>0.007790133949477251</v>
       </c>
       <c r="AK489" t="n">
         <v>6.739235851443908</v>
@@ -80132,16 +80132,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.3951733572725242</v>
+        <v>-0.3951733572725246</v>
       </c>
       <c r="AN489" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO489" t="n">
-        <v>0.6590798145480943</v>
+        <v>0.6590798145480942</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.420718764998806</v>
+        <v>1.420718764998849</v>
       </c>
       <c r="AQ489" t="n">
         <v>80.62186855290304</v>
@@ -80297,16 +80297,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3960001863323608</v>
+        <v>-0.396000186332361</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.02043272610569408</v>
+        <v>0.02043272610569401</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6685846444009622</v>
+        <v>0.6685846444009627</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.602984141316341</v>
+        <v>1.602984141316347</v>
       </c>
       <c r="AQ490" t="n">
         <v>81.12318509725139</v>
@@ -80450,10 +80450,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.714622134232894</v>
+        <v>6.714622134232888</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.04037798020802441</v>
+        <v>0.04037798020802974</v>
       </c>
       <c r="AK491" t="n">
         <v>6.746779913842831</v>
@@ -80462,16 +80462,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.396740905361911</v>
+        <v>-0.3967409053619114</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02120763540003751</v>
+        <v>0.02120763540003743</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.6777865296786982</v>
+        <v>0.6777865296786978</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.743725177744846</v>
+        <v>1.743725177744909</v>
       </c>
       <c r="AQ491" t="n">
         <v>83.76430537447487</v>
@@ -80615,28 +80615,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.731570059394423</v>
+        <v>6.73157005939442</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.01932973232310609</v>
+        <v>0.01932973232310964</v>
       </c>
       <c r="AK492" t="n">
-        <v>6.728823425344638</v>
+        <v>6.728823425344639</v>
       </c>
       <c r="AL492" t="n">
-        <v>0.02207636637289134</v>
+        <v>0.02207636637289045</v>
       </c>
       <c r="AM492" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.0220082962170377</v>
+        <v>0.02200829621703764</v>
       </c>
       <c r="AO492" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.508214089918481</v>
+        <v>1.508214089918522</v>
       </c>
       <c r="AQ492" t="n">
         <v>79.16330011670706</v>
@@ -80780,10 +80780,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.748064561399866</v>
+        <v>6.748064561399863</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.004235224214148126</v>
+        <v>0.00423522421415079</v>
       </c>
       <c r="AK493" t="n">
         <v>6.740096815166266</v>
@@ -80792,16 +80792,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.3976889317784199</v>
+        <v>-0.3976889317784196</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02268190844878654</v>
+        <v>0.02268190844878653</v>
       </c>
       <c r="AO493" t="n">
-        <v>0.6953567146475523</v>
+        <v>0.6953567146475526</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.339383633714908</v>
+        <v>1.339383633714939</v>
       </c>
       <c r="AQ493" t="n">
         <v>74.17924797037459</v>
@@ -80945,10 +80945,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.747226278872152</v>
+        <v>6.747226278872151</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.005973775296548745</v>
+        <v>0.005973775296550521</v>
       </c>
       <c r="AK494" t="n">
         <v>6.755554272205931</v>
@@ -80957,16 +80957,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4003515275861345</v>
+        <v>-0.400351527586135</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02398656672240618</v>
+        <v>0.02398656672240616</v>
       </c>
       <c r="AO494" t="n">
-        <v>0.7067969646460921</v>
+        <v>0.7067969646460924</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.34983246065289</v>
+        <v>1.349832460652912</v>
       </c>
       <c r="AQ494" t="n">
         <v>73.86614409547516</v>
@@ -81110,10 +81110,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.724989986752571</v>
+        <v>6.724989986752573</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.02471008267491914</v>
+        <v>0.02471008267491737</v>
       </c>
       <c r="AK495" t="n">
         <v>6.75925064743029</v>
@@ -81122,7 +81122,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.4017887258056133</v>
+        <v>-0.4017887258056131</v>
       </c>
       <c r="AN495" t="n">
         <v>0.02482212216928553</v>
@@ -81131,7 +81131,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.537934200391007</v>
+        <v>1.537934200390992</v>
       </c>
       <c r="AQ495" t="n">
         <v>77.32142857142857</v>
@@ -81275,28 +81275,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.738231277482312</v>
+        <v>6.738231277482303</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.01056852339049108</v>
+        <v>0.01056852339049996</v>
       </c>
       <c r="AK496" t="n">
-        <v>6.734775445902895</v>
+        <v>6.734775445902896</v>
       </c>
       <c r="AL496" t="n">
-        <v>0.01402435496990773</v>
+        <v>0.01402435496990684</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4022294042554291</v>
+        <v>-0.402229404255429</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02545790195722747</v>
+        <v>0.02545790195722734</v>
       </c>
       <c r="AO496" t="n">
-        <v>0.7273309315128231</v>
+        <v>0.7273309315128232</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.379757628265576</v>
+        <v>1.379757628265672</v>
       </c>
       <c r="AQ496" t="n">
         <v>74.71049844615358</v>
@@ -81440,10 +81440,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.718201282169581</v>
+        <v>6.718201282169575</v>
       </c>
       <c r="AJ497" t="n">
-        <v>0.02919852480673768</v>
+        <v>0.02919852480674301</v>
       </c>
       <c r="AK497" t="n">
         <v>6.753996132599221</v>
@@ -81452,16 +81452,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4027953816469058</v>
+        <v>-0.4027953816469059</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02608258444417638</v>
+        <v>0.02608258444417639</v>
       </c>
       <c r="AO497" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.565396263588755</v>
+        <v>1.565396263588813</v>
       </c>
       <c r="AQ497" t="n">
         <v>78.55027548209367</v>
@@ -81605,10 +81605,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.730898772467414</v>
+        <v>6.730898772467415</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.01650103450890406</v>
+        <v>0.01650103450890317</v>
       </c>
       <c r="AK498" t="n">
         <v>6.732394407262716</v>
@@ -81617,16 +81617,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4025099007694142</v>
+        <v>-0.402509900769414</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02634377330607651</v>
+        <v>0.02634377330607648</v>
       </c>
       <c r="AO498" t="n">
-        <v>0.746561519528266</v>
+        <v>0.7465615195282662</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.422631365509687</v>
+        <v>1.422631365509679</v>
       </c>
       <c r="AQ498" t="n">
         <v>79.06784146987005</v>
@@ -81782,16 +81782,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.4034224290251451</v>
+        <v>-0.4034224290251453</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02736182786837871</v>
+        <v>0.02736182786837866</v>
       </c>
       <c r="AO499" t="n">
-        <v>0.755189863471066</v>
+        <v>0.7551898634710656</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.28848874127045</v>
+        <v>1.288488741270451</v>
       </c>
       <c r="AQ499" t="n">
         <v>77.09998645170032</v>
@@ -81935,10 +81935,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI500" t="n">
-        <v>6.755708466794879</v>
+        <v>6.75570846679488</v>
       </c>
       <c r="AJ500" t="n">
-        <v>-0.01240850570479068</v>
+        <v>-0.01240850570479246</v>
       </c>
       <c r="AK500" t="n">
         <v>6.746865899087779</v>
@@ -81947,16 +81947,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4037073020769307</v>
+        <v>-0.4037073020769305</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02778289906564352</v>
+        <v>0.02778289906564353</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.7638221248099442</v>
+        <v>0.7638221248099444</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.106704203783623</v>
+        <v>1.106704203783605</v>
       </c>
       <c r="AQ500" t="n">
         <v>79.88914084152179</v>
@@ -82100,10 +82100,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.73601646973098</v>
+        <v>6.73601646973097</v>
       </c>
       <c r="AJ501" t="n">
-        <v>0.006783766017311343</v>
+        <v>0.006783766017321113</v>
       </c>
       <c r="AK501" t="n">
         <v>6.761018647414997</v>
@@ -82112,16 +82112,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.403510818895136</v>
+        <v>-0.4035108188951355</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02805871830419215</v>
+        <v>0.02805871830419202</v>
       </c>
       <c r="AO501" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.300975206946079</v>
+        <v>1.300975206946182</v>
       </c>
       <c r="AQ501" t="n">
         <v>83.63654538184727</v>
@@ -82280,13 +82280,13 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02827333203020888</v>
+        <v>0.02827333203020884</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7726830480787004</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.386408072754962</v>
+        <v>1.386408072754963</v>
       </c>
       <c r="AQ502" t="n">
         <v>84.10476741303809</v>
@@ -82430,10 +82430,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.725806144687715</v>
+        <v>6.725806144687716</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.01409396746438496</v>
+        <v>0.01409396746438318</v>
       </c>
       <c r="AK503" t="n">
         <v>6.744478107428201</v>
@@ -82442,16 +82442,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM503" t="n">
-        <v>-0.4027900432658338</v>
+        <v>-0.4027900432658339</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02891453613228628</v>
+        <v>0.0289145361322863</v>
       </c>
       <c r="AO503" t="n">
-        <v>0.7784357006627721</v>
+        <v>0.7784357006627718</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.361435739620025</v>
+        <v>1.361435739620007</v>
       </c>
       <c r="AQ503" t="n">
         <v>83.56281143456596</v>
@@ -82595,10 +82595,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.700854569500288</v>
+        <v>6.700854569500285</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.04174539464155735</v>
+        <v>0.04174539464156091</v>
       </c>
       <c r="AK504" t="n">
         <v>6.743301592583855</v>
@@ -82607,16 +82607,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.402742697458547</v>
+        <v>-0.4027426974585472</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.02955568036482276</v>
+        <v>0.0295556803648227</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7839391318357882</v>
+        <v>0.7839391318357879</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.637941562843737</v>
+        <v>1.637941562843773</v>
       </c>
       <c r="AQ504" t="n">
         <v>88.46316439848462</v>
@@ -82760,10 +82760,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.705597066237452</v>
+        <v>6.705597066237454</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.02390275065707925</v>
+        <v>0.02390275065707748</v>
       </c>
       <c r="AK505" t="n">
         <v>6.74285285202661</v>
@@ -82772,16 +82772,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.401588500320058</v>
+        <v>-0.4015885003200582</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.02985284499018426</v>
+        <v>0.02985284499018428</v>
       </c>
       <c r="AO505" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.44324674128027</v>
+        <v>1.443246741280252</v>
       </c>
       <c r="AQ505" t="n">
         <v>85.09516129032258</v>
@@ -82925,28 +82925,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.686024746022946</v>
+        <v>6.686024746022948</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.0364751013891631</v>
+        <v>0.03647510138916132</v>
       </c>
       <c r="AK506" t="n">
-        <v>6.744526329542678</v>
+        <v>6.744526329542679</v>
       </c>
       <c r="AL506" t="n">
-        <v>-0.02202648213056868</v>
+        <v>-0.02202648213056957</v>
       </c>
       <c r="AM506" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.02995529076246445</v>
+        <v>0.02995529076246446</v>
       </c>
       <c r="AO506" t="n">
-        <v>0.7933293013213367</v>
+        <v>0.7933293013213371</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.566182359822747</v>
+        <v>1.566182359822729</v>
       </c>
       <c r="AQ506" t="n">
         <v>84.34056224899598</v>
@@ -83090,10 +83090,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.689653251437546</v>
+        <v>6.689653251437547</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.03134694311201436</v>
+        <v>0.03134694311201347</v>
       </c>
       <c r="AK507" t="n">
         <v>6.730402461316146</v>
@@ -83102,16 +83102,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM507" t="n">
-        <v>-0.3993041981056888</v>
+        <v>-0.3993041981056886</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03010093147709741</v>
+        <v>0.03010093147709737</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.7985853639949437</v>
+        <v>0.7985853639949436</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.507036858820242</v>
+        <v>1.507036858820234</v>
       </c>
       <c r="AQ507" t="n">
         <v>85</v>
@@ -83255,10 +83255,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.716786041117415</v>
+        <v>6.716786041117424</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.00511394514967467</v>
+        <v>0.005113945149665788</v>
       </c>
       <c r="AK508" t="n">
         <v>6.728106442363027</v>
@@ -83267,16 +83267,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3976134529492091</v>
+        <v>-0.3976134529492094</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03006044259180324</v>
+        <v>0.03006044259180338</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.8026437279892851</v>
+        <v>0.8026437279892848</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.234777974751978</v>
+        <v>1.234777974751887</v>
       </c>
       <c r="AQ508" t="n">
         <v>81.59999999999999</v>
@@ -83420,10 +83420,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.721932795514441</v>
+        <v>6.72193279551444</v>
       </c>
       <c r="AJ509" t="n">
-        <v>-0.001632597913122424</v>
+        <v>-0.001632597913121536</v>
       </c>
       <c r="AK509" t="n">
         <v>6.752314636061016</v>
@@ -83435,13 +83435,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03043336917902489</v>
+        <v>0.03043336917902487</v>
       </c>
       <c r="AO509" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.163823515923089</v>
+        <v>1.163823515923099</v>
       </c>
       <c r="AQ509" t="n">
         <v>82.19999999999999</v>
@@ -83585,28 +83585,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.718669003366535</v>
+        <v>6.718669003366529</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.003830844045574544</v>
+        <v>0.003830844045580761</v>
       </c>
       <c r="AK510" t="n">
-        <v>6.750203856204787</v>
+        <v>6.750203856204786</v>
       </c>
       <c r="AL510" t="n">
-        <v>-0.02770400879267765</v>
+        <v>-0.02770400879267676</v>
       </c>
       <c r="AM510" t="n">
-        <v>-0.3969152632178358</v>
+        <v>-0.3969152632178359</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03100517332816438</v>
+        <v>0.03100517332816427</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8091236362457368</v>
+        <v>0.8091236362457366</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.217453571381047</v>
+        <v>1.217453571381112</v>
       </c>
       <c r="AQ510" t="n">
         <v>82.80000000000001</v>
@@ -83750,10 +83750,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.680190080689523</v>
+        <v>6.680190080689519</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.04230976672258624</v>
+        <v>0.04230976672259068</v>
       </c>
       <c r="AK511" t="n">
         <v>6.74780904069481</v>
@@ -83762,16 +83762,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM511" t="n">
-        <v>-0.3964565291282772</v>
+        <v>-0.3964565291282773</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03139664408873172</v>
+        <v>0.03139664408873165</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8123541153569376</v>
+        <v>0.8123541153569371</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.604493248424094</v>
+        <v>1.604493248424141</v>
       </c>
       <c r="AQ511" t="n">
         <v>89.8</v>
@@ -83915,10 +83915,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.671580974366952</v>
+        <v>6.671580974366949</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.05441885778636824</v>
+        <v>0.05441885778637179</v>
       </c>
       <c r="AK512" t="n">
         <v>6.701878095437348</v>
@@ -83930,13 +83930,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03163116863423027</v>
+        <v>0.03163116863423025</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8147568654710424</v>
+        <v>0.8147568654710426</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.717274375116457</v>
+        <v>1.717274375116494</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.2</v>
@@ -84080,28 +84080,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.656216276126097</v>
+        <v>6.656216276126093</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.06978355602722353</v>
+        <v>0.06978355602722708</v>
       </c>
       <c r="AK513" t="n">
-        <v>6.701765808189924</v>
+        <v>6.701765808189925</v>
       </c>
       <c r="AL513" t="n">
-        <v>0.02423402396339647</v>
+        <v>0.02423402396339558</v>
       </c>
       <c r="AM513" t="n">
-        <v>-0.3932426568003564</v>
+        <v>-0.3932426568003567</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.0319127327617218</v>
+        <v>0.03191273276172183</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8170879052811413</v>
+        <v>0.8170879052811416</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.858889534485343</v>
+        <v>1.858889534485379</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.59999999999999</v>
@@ -84251,19 +84251,19 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK514" t="n">
-        <v>6.682658801267993</v>
+        <v>6.682658801267994</v>
       </c>
       <c r="AL514" t="n">
-        <v>0.03754126053010243</v>
+        <v>0.03754126053010154</v>
       </c>
       <c r="AM514" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.03225018457163042</v>
+        <v>0.03225018457163047</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8195353634242114</v>
+        <v>0.8195353634242113</v>
       </c>
       <c r="AP514" t="n">
         <v>1.818117584748586</v>
@@ -84410,10 +84410,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.654231073451243</v>
+        <v>6.654231073451242</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.06476878921965579</v>
+        <v>0.06476878921965668</v>
       </c>
       <c r="AK515" t="n">
         <v>6.682840937292736</v>
@@ -84422,16 +84422,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM515" t="n">
-        <v>-0.3894836768645471</v>
+        <v>-0.3894836768645476</v>
       </c>
       <c r="AN515" t="n">
-        <v>0.03277193700354208</v>
+        <v>0.03277193700354209</v>
       </c>
       <c r="AO515" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.781104797300566</v>
+        <v>1.781104797300575</v>
       </c>
       <c r="AQ515" t="n">
         <v>90.2</v>
@@ -84575,10 +84575,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.650937329061554</v>
+        <v>6.650937329061552</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.06806253360934456</v>
+        <v>0.06806253360934633</v>
       </c>
       <c r="AK516" t="n">
         <v>6.698821600583909</v>
@@ -84587,16 +84587,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM516" t="n">
-        <v>-0.3885003849593205</v>
+        <v>-0.3885003849593203</v>
       </c>
       <c r="AN516" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO516" t="n">
-        <v>0.8264954348925954</v>
+        <v>0.8264954348925952</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.79987483353635</v>
+        <v>1.799874833536367</v>
       </c>
       <c r="AQ516" t="n">
         <v>91</v>
@@ -84740,10 +84740,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.651733245487365</v>
+        <v>6.651733245487366</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.05906692541107272</v>
+        <v>0.05906692541107184</v>
       </c>
       <c r="AK517" t="n">
         <v>6.69208631505748</v>
@@ -84752,16 +84752,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.3869746098498524</v>
+        <v>-0.3869746098498528</v>
       </c>
       <c r="AN517" t="n">
-        <v>0.0344188897752209</v>
+        <v>0.03441888977522091</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8294137131605728</v>
+        <v>0.8294137131605726</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.696616308981454</v>
+        <v>1.696616308981445</v>
       </c>
       <c r="AQ517" t="n">
         <v>90.40000000000001</v>
@@ -84905,10 +84905,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI518" t="n">
-        <v>6.632036771677474</v>
+        <v>6.632036771677475</v>
       </c>
       <c r="AJ518" t="n">
-        <v>0.07876339922096331</v>
+        <v>0.07876339922096243</v>
       </c>
       <c r="AK518" t="n">
         <v>6.692627206904497</v>
@@ -84926,7 +84926,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP518" t="n">
-        <v>1.875440190456854</v>
+        <v>1.875440190456846</v>
       </c>
       <c r="AQ518" t="n">
         <v>91</v>
@@ -85070,10 +85070,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.617259294346139</v>
+        <v>6.617259294346145</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.09324046914263029</v>
+        <v>0.09324046914262496</v>
       </c>
       <c r="AK519" t="n">
         <v>6.685306332307247</v>
@@ -85085,13 +85085,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03459091746240417</v>
+        <v>0.03459091746240425</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8328314813119074</v>
+        <v>0.8328314813119078</v>
       </c>
       <c r="AP519" t="n">
-        <v>1.998006000856745</v>
+        <v>1.998006000856694</v>
       </c>
       <c r="AQ519" t="n">
         <v>91</v>
@@ -85247,16 +85247,16 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM520" t="n">
-        <v>-0.379198503222778</v>
+        <v>-0.3791985032227784</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03468237364461174</v>
+        <v>0.03468237364461172</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8349203610870053</v>
+        <v>0.8349203610870052</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.31722822525293</v>
+        <v>2.317228225252932</v>
       </c>
       <c r="AQ520" t="n">
         <v>93</v>
@@ -85415,13 +85415,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03437427878524163</v>
+        <v>0.0343742787852416</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8337972329517069</v>
+        <v>0.8337972329517072</v>
       </c>
       <c r="AP521" t="n">
-        <v>2.426255822246373</v>
+        <v>2.426255822246376</v>
       </c>
       <c r="AQ521" t="n">
         <v>93.40000000000001</v>
@@ -85476,13 +85476,13 @@
         <v>6.708000183105469</v>
       </c>
       <c r="F522" t="n">
-        <v>6.706120014190674</v>
+        <v>6.708040237426758</v>
       </c>
       <c r="G522" t="n">
         <v>6.6977</v>
       </c>
       <c r="H522" t="n">
-        <v>-0.001880168914794922</v>
+        <v>4.00543212890625e-05</v>
       </c>
       <c r="I522" t="n">
         <v>99.12000274658203</v>
@@ -85568,7 +85568,7 @@
         <v>6.559361964677803</v>
       </c>
       <c r="AJ522" t="n">
-        <v>0.1486382184276662</v>
+        <v>0.1486382184276653</v>
       </c>
       <c r="AK522" t="n">
         <v>6.617345065810827</v>
@@ -85577,16 +85577,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM522" t="n">
-        <v>-0.3685435183382903</v>
+        <v>-0.3685435183382902</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03361173230743109</v>
+        <v>0.03361173230743112</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8313650598704547</v>
+        <v>0.8313650598704546</v>
       </c>
       <c r="AP522" t="n">
-        <v>2.437784108534264</v>
+        <v>2.437784108534258</v>
       </c>
       <c r="AQ522" t="n">
         <v>92</v>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41361,10 +41361,10 @@
         <v/>
       </c>
       <c r="AI254" t="n">
-        <v>7.164454424594246</v>
+        <v>7.164454424594245</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.02545448562940233</v>
+        <v>-0.02545448562940145</v>
       </c>
       <c r="AK254" t="n">
         <v>7.171026992419335</v>
@@ -41373,13 +41373,13 @@
         <v>-0.03202705345449175</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1023969939185646</v>
+        <v>0.1023969939185656</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002417390403537972</v>
+        <v>0.002417390403537929</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2665217851726001</v>
+        <v>0.2665217851725994</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41522,10 +41522,10 @@
         <v/>
       </c>
       <c r="AI255" t="n">
-        <v>7.160742529934239</v>
+        <v>7.16074252993424</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.01934266955215858</v>
+        <v>-0.01934266955216035</v>
       </c>
       <c r="AK255" t="n">
         <v>7.166224790710233</v>
@@ -41534,13 +41534,13 @@
         <v>-0.02482493032815292</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.1026368091542314</v>
+        <v>0.1026368091542317</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002433131908989014</v>
+        <v>0.002433131908989026</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2688740668038477</v>
+        <v>0.2688740668038501</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41687,10 +41687,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.150419484347116</v>
+        <v>7.150419484347115</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.009019623965035528</v>
+        <v>-0.00901962396503464</v>
       </c>
       <c r="AK256" t="n">
         <v>7.161074530187645</v>
@@ -41699,13 +41699,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.1029385549788083</v>
+        <v>0.102938554978808</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002436328878122382</v>
+        <v>0.002436328878122375</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2711996176877891</v>
+        <v>0.2711996176877889</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41852,10 +41852,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.148511457776028</v>
+        <v>7.14851145777603</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.01601128611465086</v>
+        <v>-0.01601128611465263</v>
       </c>
       <c r="AK257" t="n">
         <v>7.150963414761942</v>
@@ -41864,13 +41864,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.1011329645838851</v>
+        <v>0.1011329645838857</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002517185580011447</v>
+        <v>0.002517185580011383</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2709113683260677</v>
+        <v>0.2709113683260674</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42029,13 +42029,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.09870181295186471</v>
+        <v>0.09870181295186436</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.002644711580562537</v>
+        <v>0.002644711580562605</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2704892730019304</v>
+        <v>0.2704892730019285</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42182,10 +42182,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI259" t="n">
-        <v>7.153772633426659</v>
+        <v>7.153772633426657</v>
       </c>
       <c r="AJ259" t="n">
-        <v>-0.03287247931288917</v>
+        <v>-0.03287247931288739</v>
       </c>
       <c r="AK259" t="n">
         <v>7.154757231824306</v>
@@ -42194,13 +42194,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.09555831842873846</v>
+        <v>0.09555831842873888</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.002822832879878071</v>
+        <v>0.002822832879878049</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2697410008595936</v>
+        <v>0.2697410008595938</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42347,10 +42347,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI260" t="n">
-        <v>7.153331199414496</v>
+        <v>7.153331199414497</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-0.03263131690717191</v>
+        <v>-0.0326313169071728</v>
       </c>
       <c r="AK260" t="n">
         <v>7.15450652143491</v>
@@ -42359,13 +42359,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.0918844066524992</v>
+        <v>0.09188440665249918</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003041971996730133</v>
+        <v>0.003041971996730116</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2698098046976256</v>
+        <v>0.2698098046976254</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42512,10 +42512,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.156943148319592</v>
+        <v>7.15694314831959</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.03854305142628167</v>
+        <v>-0.0385430514262799</v>
       </c>
       <c r="AK261" t="n">
         <v>7.154505434137821</v>
@@ -42524,13 +42524,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.08748497753913406</v>
+        <v>0.08748497753913362</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003298336925509862</v>
+        <v>0.003298336925509857</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2682008942988235</v>
+        <v>0.2682008942988222</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42689,13 +42689,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.0824587084059305</v>
+        <v>0.08245870840593096</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.003602928090795432</v>
+        <v>0.003602928090795422</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2685806390401517</v>
+        <v>0.2685806390401518</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42857,10 +42857,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.003819541738581442</v>
+        <v>0.003819541738581439</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2696768907787764</v>
+        <v>0.2696768907787754</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43007,10 +43007,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.154685377655177</v>
+        <v>7.154685377655176</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.04048526245131967</v>
+        <v>-0.04048526245131878</v>
       </c>
       <c r="AK264" t="n">
         <v>7.15808570026938</v>
@@ -43019,13 +43019,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.07200163454913491</v>
+        <v>0.07200163454913533</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.004193740708391541</v>
+        <v>0.004193740708391577</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.270116598814735</v>
+        <v>0.2701165988147326</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43172,10 +43172,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.158449213455076</v>
+        <v>7.158449213455078</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.05514911885058371</v>
+        <v>-0.05514911885058549</v>
       </c>
       <c r="AK265" t="n">
         <v>7.157644979270017</v>
@@ -43184,13 +43184,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.06676111471939408</v>
+        <v>0.06676111471939436</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.00450521933759436</v>
+        <v>0.004505219337594384</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.2733976337163381</v>
+        <v>0.2733976337163387</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43337,10 +43337,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI266" t="n">
-        <v>7.160761769069204</v>
+        <v>7.160761769069201</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-0.04786198879576631</v>
+        <v>-0.04786198879576364</v>
       </c>
       <c r="AK266" t="n">
         <v>7.159146249199162</v>
@@ -43349,10 +43349,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.06148465881746725</v>
+        <v>0.06148465881746766</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.004852471327681615</v>
+        <v>0.004852471327681566</v>
       </c>
       <c r="AO266" t="n">
         <v>0.2778048766368325</v>
@@ -43502,10 +43502,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.162478122158095</v>
+        <v>7.162478122158094</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04957834188465782</v>
+        <v>-0.04957834188465693</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159578986975002</v>
@@ -43514,13 +43514,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.05582594297075769</v>
+        <v>0.05582594297075712</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.005234102211236422</v>
+        <v>0.005234102211236467</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.282448024375059</v>
+        <v>0.2824480243750598</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43679,13 +43679,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.04949165986049534</v>
+        <v>0.04949165986049463</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.005677665039252891</v>
+        <v>0.005677665039252918</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.2878618994559775</v>
+        <v>0.2878618994559794</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43844,13 +43844,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.04287777011073584</v>
+        <v>0.04287777011073606</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.006155260602669632</v>
+        <v>0.006155260602669625</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.2948468705933219</v>
+        <v>0.2948468705933236</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -43997,10 +43997,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.173971773133425</v>
+        <v>7.173971773133423</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.04247200582995792</v>
+        <v>-0.04247200582995614</v>
       </c>
       <c r="AK270" t="n">
         <v>7.159255388854645</v>
@@ -44009,13 +44009,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.0348694200966178</v>
+        <v>0.03486942009661778</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.006728155724408227</v>
+        <v>0.006728155724408201</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.304499875642397</v>
+        <v>0.3044998756423967</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44162,25 +44162,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.172030417300567</v>
+        <v>7.172030417300565</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.03823038754592822</v>
+        <v>-0.03823038754592645</v>
       </c>
       <c r="AK271" t="n">
-        <v>7.167062070913353</v>
+        <v>7.167062070913352</v>
       </c>
       <c r="AL271" t="n">
-        <v>-0.03326204115871434</v>
+        <v>-0.03326204115871345</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.03279550096037902</v>
+        <v>0.03279550096037874</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.006903991232239788</v>
+        <v>0.006903991232239758</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3170366335916601</v>
+        <v>0.3170366335916608</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44327,10 +44327,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.171236182927453</v>
+        <v>7.171236182927454</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.03843608069356641</v>
+        <v>-0.0384360806935673</v>
       </c>
       <c r="AK272" t="n">
         <v>7.16747443083108</v>
@@ -44339,13 +44339,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.02972414459983895</v>
+        <v>0.02972414459983913</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.007158147882858998</v>
+        <v>0.007158147882859</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3270754385893867</v>
+        <v>0.3270754385893863</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44492,10 +44492,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.170425137628191</v>
+        <v>7.170425137628194</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.05102511321412884</v>
+        <v>-0.0510251132141315</v>
       </c>
       <c r="AK273" t="n">
         <v>7.168373097443463</v>
@@ -44504,13 +44504,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.02657019411530269</v>
+        <v>0.02657019411530295</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.007420436972250415</v>
+        <v>0.007420436972250398</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3357224795973284</v>
+        <v>0.3357224795973281</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44669,13 +44669,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.02366886174665103</v>
+        <v>0.02366886174665165</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.007679120311627263</v>
+        <v>0.007679120311627231</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3450219581941938</v>
+        <v>0.345021958194194</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44822,10 +44822,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI275" t="n">
-        <v>7.172249622131827</v>
+        <v>7.172249622131823</v>
       </c>
       <c r="AJ275" t="n">
-        <v>-0.05324966409349674</v>
+        <v>-0.05324966409349319</v>
       </c>
       <c r="AK275" t="n">
         <v>7.167365057101177</v>
@@ -44834,13 +44834,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.01956653131084185</v>
+        <v>0.01956653131084189</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008034860291676559</v>
+        <v>0.008034860291676519</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3572033251592189</v>
+        <v>0.3572033251592186</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -44987,10 +44987,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI276" t="n">
-        <v>7.171656420777024</v>
+        <v>7.171656420777023</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-0.05265646273869429</v>
+        <v>-0.0526564627386934</v>
       </c>
       <c r="AK276" t="n">
         <v>7.167567681415887</v>
@@ -44999,13 +44999,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01638396088890769</v>
+        <v>0.0163839608889081</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008326212487477964</v>
+        <v>0.008326212487477898</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.3674516177552961</v>
+        <v>0.3674516177552964</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45152,10 +45152,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.175289829564748</v>
+        <v>7.175289829564746</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.05628987152641773</v>
+        <v>-0.05628987152641596</v>
       </c>
       <c r="AK277" t="n">
         <v>7.167553154788029</v>
@@ -45164,13 +45164,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM277" t="n">
-        <v>0.01351198449095157</v>
+        <v>0.01351198449095179</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.008601682347582891</v>
+        <v>0.008601682347582911</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.3758646846617525</v>
+        <v>0.375864684661753</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45323,19 +45323,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK278" t="n">
-        <v>7.16746081477764</v>
+        <v>7.167460814777641</v>
       </c>
       <c r="AL278" t="n">
-        <v>-0.04846085673931011</v>
+        <v>-0.048460856739311</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.01196199498966369</v>
+        <v>0.01196199498966377</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.008797062853284063</v>
+        <v>0.008797062853284078</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.3847384959530242</v>
+        <v>0.3847384959530228</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45643,10 +45643,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI280" t="n">
-        <v>7.189678003526525</v>
+        <v>7.189678003526526</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-0.07117777082999144</v>
+        <v>-0.07117777082999321</v>
       </c>
       <c r="AK280" t="n">
         <v/>
@@ -45655,13 +45655,13 @@
         <v/>
       </c>
       <c r="AM280" t="n">
-        <v>0.007307555239791734</v>
+        <v>0.007307555239791735</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.009236289154790337</v>
+        <v>0.009236289154790363</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.401039717356949</v>
+        <v>0.4010397173569483</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45808,10 +45808,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI281" t="n">
-        <v>7.183919177237467</v>
+        <v>7.183919177237466</v>
       </c>
       <c r="AJ281" t="n">
-        <v>-0.05641912001700788</v>
+        <v>-0.056419120017007</v>
       </c>
       <c r="AK281" t="n">
         <v>7.168706858585229</v>
@@ -45820,13 +45820,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.006573598200530942</v>
+        <v>0.006573598200531427</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009378157495070056</v>
+        <v>0.009378157495070007</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4093166892046883</v>
+        <v>0.4093166892046876</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45985,13 +45985,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.005719699928660468</v>
+        <v>0.00571969992866044</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009535855797507643</v>
+        <v>0.009535855797507651</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4189456552735356</v>
+        <v>0.4189456552735351</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46138,10 +46138,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI283" t="n">
-        <v>7.183803634757356</v>
+        <v>7.183803634757355</v>
       </c>
       <c r="AJ283" t="n">
-        <v>-0.08380373012478781</v>
+        <v>-0.08380373012478692</v>
       </c>
       <c r="AK283" t="n">
         <v>7.157754776965645</v>
@@ -46150,13 +46150,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.007205793377056199</v>
+        <v>0.007205793377055721</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009541847058682544</v>
+        <v>0.00954184705868257</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4265135453780396</v>
+        <v>0.4265135453780416</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46309,19 +46309,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK284" t="n">
-        <v>7.153578345933642</v>
+        <v>7.153578345933643</v>
       </c>
       <c r="AL284" t="n">
-        <v>-0.01517826811381795</v>
+        <v>-0.01517826811381884</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.009937300636551308</v>
+        <v>0.009937300636551421</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.00947510825395563</v>
+        <v>0.009475108253955637</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4359288044119884</v>
+        <v>0.4359288044119891</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46468,10 +46468,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI285" t="n">
-        <v>7.175374323571331</v>
+        <v>7.175374323571332</v>
       </c>
       <c r="AJ285" t="n">
-        <v>-0.04917412444413394</v>
+        <v>-0.04917412444413483</v>
       </c>
       <c r="AK285" t="n">
         <v>7.155226204999164</v>
@@ -46480,13 +46480,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01039951522374721</v>
+        <v>0.01039951522374727</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009534227083684284</v>
+        <v>0.009534227083684297</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.446224869246465</v>
+        <v>0.4462248692464653</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46645,13 +46645,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01174445052819259</v>
+        <v>0.01174445052819296</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009539024405591096</v>
+        <v>0.009539024405591111</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4561706550234678</v>
+        <v>0.4561706550234662</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46798,10 +46798,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI287" t="n">
-        <v>7.176295466764674</v>
+        <v>7.176295466764673</v>
       </c>
       <c r="AJ287" t="n">
-        <v>-0.04989547286818929</v>
+        <v>-0.04989547286818841</v>
       </c>
       <c r="AK287" t="n">
         <v>7.150954883812801</v>
@@ -46810,13 +46810,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.01399948938427905</v>
+        <v>0.01399948938427885</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009474826008246758</v>
+        <v>0.009474826008246765</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4654004237248369</v>
+        <v>0.4654004237248376</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46975,13 +46975,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.01676993900799729</v>
+        <v>0.01676993900799728</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009377028877974699</v>
+        <v>0.00937702887797469</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.476700939638935</v>
+        <v>0.4767009396389351</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47143,10 +47143,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.009204864903404497</v>
+        <v>0.009204864903404482</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.4883841032893044</v>
+        <v>0.4883841032893032</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47305,13 +47305,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.02435543352765289</v>
+        <v>0.02435543352765317</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.009045821984022376</v>
+        <v>0.00904582198402234</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.4990078266507766</v>
+        <v>0.4990078266507749</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47458,10 +47458,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI291" t="n">
-        <v>7.175210595491395</v>
+        <v>7.175210595491394</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.04951059854315254</v>
+        <v>-0.04951059854315165</v>
       </c>
       <c r="AK291" t="n">
         <v>7.151444380572274</v>
@@ -47470,13 +47470,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.02840267381959001</v>
+        <v>0.02840267381959008</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008843610540066053</v>
+        <v>0.008843610540066056</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.5123725312709416</v>
+        <v>0.5123725312709417</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47626,7 +47626,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.05177635201934994</v>
+        <v>-0.05177635201935082</v>
       </c>
       <c r="AK292" t="n">
         <v>7.151307469847429</v>
@@ -47635,13 +47635,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.03189518855892823</v>
+        <v>0.03189518855892809</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008740250954211215</v>
+        <v>0.008740250954211236</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5303980242931245</v>
+        <v>0.5303980242931252</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47788,10 +47788,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI293" t="n">
-        <v>7.172173616645312</v>
+        <v>7.172173616645314</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.06197368836162021</v>
+        <v>-0.06197368836162287</v>
       </c>
       <c r="AK293" t="n">
         <v>7.152170779642037</v>
@@ -47800,13 +47800,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.03448417181877508</v>
+        <v>0.03448417181877479</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008638296330047493</v>
+        <v>0.008638296330047519</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.536400419244653</v>
+        <v>0.5364004192446541</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47956,7 +47956,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.08262387272163529</v>
+        <v>-0.08262387272163618</v>
       </c>
       <c r="AK294" t="n">
         <v>7.155242422656618</v>
@@ -47968,10 +47968,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008527848481957645</v>
+        <v>0.008527848481957647</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5479838817473677</v>
+        <v>0.5479838817473681</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48118,10 +48118,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI295" t="n">
-        <v>7.18418852599864</v>
+        <v>7.184188525998638</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.08518854888682359</v>
+        <v>-0.08518854888682181</v>
       </c>
       <c r="AK295" t="n">
         <v>7.174067278312125</v>
@@ -48130,13 +48130,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.03996026841105445</v>
+        <v>0.03996026841105382</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008497979041970659</v>
+        <v>0.008497979041970699</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5534995516418705</v>
+        <v>0.553499551641869</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48283,10 +48283,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.185513015749276</v>
+        <v>7.185513015749274</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.07571315384131694</v>
+        <v>-0.07571315384131516</v>
       </c>
       <c r="AK296" t="n">
         <v>7.175957423377739</v>
@@ -48295,13 +48295,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04233079818885077</v>
+        <v>0.04233079818885083</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008432709457890229</v>
+        <v>0.008432709457890224</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.5557951014363787</v>
+        <v>0.5557951014363788</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48454,19 +48454,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK297" t="n">
-        <v>7.174765662541793</v>
+        <v>7.174765662541792</v>
       </c>
       <c r="AL297" t="n">
-        <v>-0.05786569534818931</v>
+        <v>-0.05786569534818842</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04394124299371591</v>
+        <v>0.04394124299371556</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008396387260434499</v>
+        <v>0.008396387260434506</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5565519909812464</v>
+        <v>0.5565519909812453</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48613,10 +48613,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI298" t="n">
-        <v>7.185932916622859</v>
+        <v>7.18593291662286</v>
       </c>
       <c r="AJ298" t="n">
-        <v>-0.0141327800566966</v>
+        <v>-0.01413278005669749</v>
       </c>
       <c r="AK298" t="n">
         <v>7.172730869790855</v>
@@ -48625,13 +48625,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04590755972499789</v>
+        <v>0.04590755972499803</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008346613473328282</v>
+        <v>0.008346613473328291</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5588443644440741</v>
+        <v>0.5588443644440755</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48778,10 +48778,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI299" t="n">
-        <v>7.187602005018013</v>
+        <v>7.187602005018014</v>
       </c>
       <c r="AJ299" t="n">
-        <v>-0.05810209275604983</v>
+        <v>-0.0581020927560516</v>
       </c>
       <c r="AK299" t="n">
         <v>7.168923754586179</v>
@@ -48790,10 +48790,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04658552832149703</v>
+        <v>0.04658552832149689</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008354655440128402</v>
+        <v>0.008354655440128426</v>
       </c>
       <c r="AO299" t="n">
         <v>0.5613325805619827</v>
@@ -48955,13 +48955,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.04820692510781933</v>
+        <v>0.04820692510781883</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008303818071592001</v>
+        <v>0.008303818071592054</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5626464255878519</v>
+        <v>0.5626464255878516</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49120,13 +49120,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.04983084886774743</v>
+        <v>0.04983084886774771</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008251024544031704</v>
+        <v>0.008251024544031682</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5641340630354328</v>
+        <v>0.5641340630354323</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49285,13 +49285,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05170461329917111</v>
+        <v>0.05170461329917048</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008192726391276807</v>
+        <v>0.008192726391276836</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5658195968244528</v>
+        <v>0.5658195968244545</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49450,13 +49450,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05348369580043773</v>
+        <v>0.05348369580043772</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008143044151838245</v>
+        <v>0.008143044151838252</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5671346874885959</v>
+        <v>0.5671346874885956</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49603,10 +49603,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.175179910580594</v>
+        <v>7.175179910580593</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.05588002196975417</v>
+        <v>-0.05588002196975328</v>
       </c>
       <c r="AK304" t="n">
         <v>7.165699812335961</v>
@@ -49615,13 +49615,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05520982564369371</v>
+        <v>0.0552098256436935</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008124788470663676</v>
+        <v>0.008124788470663643</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5701242576280907</v>
+        <v>0.5701242576280905</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49768,10 +49768,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.173581841712227</v>
+        <v>7.173581841712229</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.05428195310138761</v>
+        <v>-0.05428195310138939</v>
       </c>
       <c r="AK305" t="n">
         <v>7.162626578418298</v>
@@ -49780,13 +49780,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05644890839995315</v>
+        <v>0.05644890839995281</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008105230252153435</v>
+        <v>0.008105230252153447</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5713754740215509</v>
+        <v>0.5713754740215494</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49933,10 +49933,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.176011726611837</v>
+        <v>7.176011726611838</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.06401173805592908</v>
+        <v>-0.06401173805592997</v>
       </c>
       <c r="AK306" t="n">
         <v>7.165542054185019</v>
@@ -49945,13 +49945,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05727663218544052</v>
+        <v>0.05727663218544039</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.00812403522652648</v>
+        <v>0.008124035226526509</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.573000414744258</v>
+        <v>0.5730004147442582</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50098,10 +50098,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.17698340522191</v>
+        <v>7.176983405221908</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.07778363334080662</v>
+        <v>-0.07778363334080485</v>
       </c>
       <c r="AK307" t="n">
         <v>7.170209849598846</v>
@@ -50110,13 +50110,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.05825580143844533</v>
+        <v>0.05825580143844532</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.008106527117828777</v>
+        <v>0.008106527117828759</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5728585525731363</v>
+        <v>0.5728585525731367</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50263,10 +50263,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.174841035863564</v>
+        <v>7.174841035863563</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.06734095956961905</v>
+        <v>-0.06734095956961816</v>
       </c>
       <c r="AK308" t="n">
         <v>7.166925629020364</v>
@@ -50275,13 +50275,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.05980113395910436</v>
+        <v>0.05980113395910441</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.008056914781095353</v>
+        <v>0.008056914781095341</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5723268395754473</v>
+        <v>0.5723268395754482</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50428,10 +50428,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.179777800337525</v>
+        <v>7.179777800337526</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.07227772404357946</v>
+        <v>-0.07227772404358035</v>
       </c>
       <c r="AK309" t="n">
         <v>7.163704513322672</v>
@@ -50443,10 +50443,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.008007544934860181</v>
+        <v>0.008007544934860184</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5724055344141883</v>
+        <v>0.5724055344141876</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50593,10 +50593,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.176651545551679</v>
+        <v>7.176651545551677</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.06915146925773374</v>
+        <v>-0.06915146925773197</v>
       </c>
       <c r="AK310" t="n">
         <v>7.163430147298699</v>
@@ -50605,13 +50605,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.06321929365037962</v>
+        <v>0.06321929365038026</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007927773212025854</v>
+        <v>0.007927773212025837</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.572463582881384</v>
+        <v>0.5724635828813827</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50758,10 +50758,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.173279688539583</v>
+        <v>7.173279688539582</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.06577961224563733</v>
+        <v>-0.06577961224563644</v>
       </c>
       <c r="AK311" t="n">
         <v>7.158871783064204</v>
@@ -50770,13 +50770,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06523048259292186</v>
+        <v>0.0652304825929222</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007809540836127948</v>
+        <v>0.007809540836127932</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5710090561291132</v>
+        <v>0.571009056129113</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50923,10 +50923,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI312" t="n">
-        <v>7.168542018724481</v>
+        <v>7.168542018724479</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.06194221098522323</v>
+        <v>-0.06194221098522146</v>
       </c>
       <c r="AK312" t="n">
         <v>7.152618309751275</v>
@@ -50935,13 +50935,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.067411943409599</v>
+        <v>0.06741194340959927</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007660511838810988</v>
+        <v>0.007660511838810949</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.5694124450603424</v>
+        <v>0.5694124450603408</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51088,10 +51088,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI313" t="n">
-        <v>7.161829635752616</v>
+        <v>7.161829635752617</v>
       </c>
       <c r="AJ313" t="n">
-        <v>-0.05962960447209831</v>
+        <v>-0.0596296044720992</v>
       </c>
       <c r="AK313" t="n">
         <v>7.144956229005203</v>
@@ -51100,13 +51100,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.06977835201573312</v>
+        <v>0.06977835201573281</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007516908058882096</v>
+        <v>0.007516908058882097</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5690369646398685</v>
+        <v>0.5690369646398684</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51256,7 +51256,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.07699331565738099</v>
+        <v>-0.07699331565738188</v>
       </c>
       <c r="AK314" t="n">
         <v>7.140422114543136</v>
@@ -51265,16 +51265,16 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.07195366789421653</v>
+        <v>0.07195366789421676</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.007394117938767417</v>
+        <v>0.007394117938767422</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5693040973288186</v>
+        <v>0.5693040973288199</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.387214816667044</v>
+        <v>-1.387214816667113</v>
       </c>
       <c r="AQ314" t="n">
         <v>5.862068965517241</v>
@@ -51430,16 +51430,16 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.07456301989532385</v>
+        <v>0.07456301989532414</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.007241314760732032</v>
+        <v>0.007241314760731996</v>
       </c>
       <c r="AO315" t="n">
         <v>0.5685877661607006</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.751355156100289</v>
+        <v>-1.751355156100307</v>
       </c>
       <c r="AQ315" t="n">
         <v>3.306474020561267</v>
@@ -51595,16 +51595,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.07747971887849656</v>
+        <v>0.07747971887849607</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.0070901436555387</v>
+        <v>0.007090143655538702</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5681709745664083</v>
+        <v>0.5681709745664091</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.719358275118384</v>
+        <v>-1.7193582751184</v>
       </c>
       <c r="AQ316" t="n">
         <v>4.919354838709678</v>
@@ -51748,10 +51748,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.165084051386049</v>
+        <v>7.165084051386047</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.08998410631768916</v>
+        <v>-0.08998410631768738</v>
       </c>
       <c r="AK317" t="n">
         <v>7.14582045097363</v>
@@ -51760,16 +51760,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08000072584212846</v>
+        <v>0.08000072584212836</v>
       </c>
       <c r="AN317" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5684087510734981</v>
+        <v>0.5684087510734968</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.920512463066454</v>
+        <v>-1.920512463066381</v>
       </c>
       <c r="AQ317" t="n">
         <v>2.432995055945876</v>
@@ -51913,10 +51913,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.161419741275552</v>
+        <v>7.161419741275553</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.08971964514518138</v>
+        <v>-0.08971964514518227</v>
       </c>
       <c r="AK318" t="n">
         <v>7.155707108847959</v>
@@ -51925,16 +51925,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08204996863507508</v>
+        <v>0.08204996863507528</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006919462921967476</v>
+        <v>0.006919462921967468</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5672869954461468</v>
+        <v>0.5672869954461461</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.839265028040945</v>
+        <v>-1.83926502804101</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.368951612903226</v>
@@ -52078,10 +52078,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.155488092579304</v>
+        <v>7.155488092579303</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.08548792091792734</v>
+        <v>-0.08548792091792645</v>
       </c>
       <c r="AK319" t="n">
         <v>7.150451326287159</v>
@@ -52090,16 +52090,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08469403553214168</v>
+        <v>0.08469403553214211</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006815201188096393</v>
+        <v>0.006815201188096372</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5663505631396779</v>
+        <v>0.5663505631396781</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.572203541131127</v>
+        <v>-1.572203541131099</v>
       </c>
       <c r="AQ319" t="n">
         <v>3.870573870573871</v>
@@ -52243,10 +52243,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.158832817363979</v>
+        <v>7.15883281736398</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.09523275404000398</v>
+        <v>-0.09523275404000575</v>
       </c>
       <c r="AK320" t="n">
         <v>7.147115644271845</v>
@@ -52255,16 +52255,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.08699523504893081</v>
+        <v>0.08699523504893142</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006735083295172709</v>
+        <v>0.006735083295172689</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5654743012892969</v>
+        <v>0.5654743012892984</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.998545444594283</v>
+        <v>-1.998545444594386</v>
       </c>
       <c r="AQ320" t="n">
         <v>1.538825757575758</v>
@@ -52408,10 +52408,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.161703459649028</v>
+        <v>7.161703459649029</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.090303294091167</v>
+        <v>-0.09030329409116788</v>
       </c>
       <c r="AK321" t="n">
         <v>7.152131804583207</v>
@@ -52420,16 +52420,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.08901512474159551</v>
+        <v>0.08901512474159586</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006668288608758136</v>
+        <v>0.006668288608758129</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5631673144521659</v>
+        <v>0.5631673144521655</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.696375567991948</v>
+        <v>-1.696375567992</v>
       </c>
       <c r="AQ321" t="n">
         <v>2.261768082663605</v>
@@ -52573,10 +52573,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.162535384813326</v>
+        <v>7.162535384813327</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.09293527952768166</v>
+        <v>-0.09293527952768255</v>
       </c>
       <c r="AK322" t="n">
         <v>7.157753883768605</v>
@@ -52585,16 +52585,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.09116436352661951</v>
+        <v>0.09116436352661936</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006624805625172231</v>
+        <v>0.006624805625172246</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5612585549312774</v>
+        <v>0.5612585549312785</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.77116632357484</v>
+        <v>-1.771166323574888</v>
       </c>
       <c r="AQ322" t="n">
         <v>2.985739750445632</v>
@@ -52738,10 +52738,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.166818450294679</v>
+        <v>7.166818450294681</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.0958183511125501</v>
+        <v>-0.09581835111255188</v>
       </c>
       <c r="AK323" t="n">
         <v>7.158620349112049</v>
@@ -52750,16 +52750,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09320704864741254</v>
+        <v>0.09320704864741212</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006594358041710158</v>
+        <v>0.006594358041710186</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5590514368572466</v>
+        <v>0.5590514368572459</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.85019582999533</v>
+        <v>-1.850195829995415</v>
       </c>
       <c r="AQ323" t="n">
         <v>1.470906337875838</v>
@@ -52903,10 +52903,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.157691007010206</v>
+        <v>7.157691007010208</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.0943908742587416</v>
+        <v>-0.09439087425874337</v>
       </c>
       <c r="AK324" t="n">
         <v>7.164942158928604</v>
@@ -52915,16 +52915,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.09491020692123933</v>
+        <v>0.09491020692123982</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006562900445417311</v>
+        <v>0.006562900445417306</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5551825155208145</v>
+        <v>0.5551825155208129</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.729349174402516</v>
+        <v>-1.729349174402595</v>
       </c>
       <c r="AQ324" t="n">
         <v>2.878151260504202</v>
@@ -53068,10 +53068,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.151776426431621</v>
+        <v>7.15177642643162</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.08777629673191356</v>
+        <v>-0.08777629673191267</v>
       </c>
       <c r="AK325" t="n">
         <v>7.154764404811184</v>
@@ -53080,16 +53080,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.097046810505102</v>
+        <v>0.0970468105051025</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006523984583215639</v>
+        <v>0.006523984583215632</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5522992358254805</v>
+        <v>0.5522992358254815</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.385185049809918</v>
+        <v>-1.385185049809873</v>
       </c>
       <c r="AQ325" t="n">
         <v>6.358440498060829</v>
@@ -53233,10 +53233,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI326" t="n">
-        <v>7.15099240431968</v>
+        <v>7.150992404319682</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.09309245238486596</v>
+        <v>-0.09309245238486774</v>
       </c>
       <c r="AK326" t="n">
         <v>7.150261540163492</v>
@@ -53245,16 +53245,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.09904197982498698</v>
+        <v>0.09904197982498671</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006505848878330736</v>
+        <v>0.006505848878330779</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5500699492277152</v>
+        <v>0.5500699492277157</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.595274724905276</v>
+        <v>-1.595274724905352</v>
       </c>
       <c r="AQ326" t="n">
         <v>4.206349206349207</v>
@@ -53398,10 +53398,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI327" t="n">
-        <v>7.147140093605204</v>
+        <v>7.147140093605207</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.09314019278733277</v>
+        <v>-0.09314019278733543</v>
       </c>
       <c r="AK327" t="n">
         <v>7.148879230661717</v>
@@ -53410,16 +53410,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.1013300516539148</v>
+        <v>0.1013300516539142</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006479631055951007</v>
+        <v>0.006479631055951091</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5478993564899665</v>
+        <v>0.5478993564899672</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.559279185803214</v>
+        <v>-1.559279185803325</v>
       </c>
       <c r="AQ327" t="n">
         <v>3.443951379509936</v>
@@ -53569,22 +53569,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK328" t="n">
-        <v>7.145816711184184</v>
+        <v>7.145816711184185</v>
       </c>
       <c r="AL328" t="n">
-        <v>-0.09881677984873516</v>
+        <v>-0.09881677984873605</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1033273874042088</v>
+        <v>0.1033273874042092</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006468712737497662</v>
+        <v>0.006468712737497656</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5455500876237902</v>
+        <v>0.5455500876237913</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.633678780047227</v>
+        <v>-1.633678780047215</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.045795795795796</v>
@@ -53731,7 +53731,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ329" t="n">
-        <v>-0.1028262052267701</v>
+        <v>-0.102826205226771</v>
       </c>
       <c r="AK329" t="n">
         <v>7.139092738717567</v>
@@ -53740,16 +53740,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1056457020972507</v>
+        <v>0.1056457020972505</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006435041090934165</v>
+        <v>0.006435041090934217</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5433399026839665</v>
+        <v>0.5433399026839674</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.899027440937709</v>
+        <v>-1.899027440937733</v>
       </c>
       <c r="AQ329" t="n">
         <v>2.721461187214611</v>
@@ -53896,7 +53896,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.099096096614959</v>
+        <v>-0.09909609661495811</v>
       </c>
       <c r="AK330" t="n">
         <v>7.140479586010682</v>
@@ -53905,16 +53905,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.10768023901916</v>
+        <v>0.1076802390191602</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006405465077205547</v>
+        <v>0.006405465077205527</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5402459241219614</v>
+        <v>0.5402459241219618</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.687116422037569</v>
+        <v>-1.687116422037517</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.667140825035561</v>
@@ -54058,10 +54058,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI331" t="n">
-        <v>7.145743344370562</v>
+        <v>7.145743344370558</v>
       </c>
       <c r="AJ331" t="n">
-        <v>-0.1052431803385794</v>
+        <v>-0.1052431803385758</v>
       </c>
       <c r="AK331" t="n">
         <v>7.136632587022158</v>
@@ -54070,16 +54070,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1100130126862077</v>
+        <v>0.1100130126862084</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006366554765990282</v>
+        <v>0.00636655476599019</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5375708073661647</v>
+        <v>0.5375708073661639</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.899194629591059</v>
+        <v>-1.8991946295909</v>
       </c>
       <c r="AQ331" t="n">
         <v>2.649350649350649</v>
@@ -54235,16 +54235,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1122475627674583</v>
+        <v>0.1122475627674581</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006337265512462553</v>
+        <v>0.00633726551246258</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5341613739773245</v>
+        <v>0.5341613739773232</v>
       </c>
       <c r="AP332" t="n">
-        <v>-1.572918871746104</v>
+        <v>-1.572918871746101</v>
       </c>
       <c r="AQ332" t="n">
         <v>3.221997300944669</v>
@@ -54388,10 +54388,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI333" t="n">
-        <v>7.142519733033009</v>
+        <v>7.14251973303301</v>
       </c>
       <c r="AJ333" t="n">
-        <v>-0.1016195026252946</v>
+        <v>-0.1016195026252955</v>
       </c>
       <c r="AK333" t="n">
         <v>7.135172643569136</v>
@@ -54400,16 +54400,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1146509166068179</v>
+        <v>0.114650916606818</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006337163869517243</v>
+        <v>0.006337163869517234</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5319767312874306</v>
+        <v>0.5319767312874311</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.662569740270745</v>
+        <v>-1.662569740270778</v>
       </c>
       <c r="AQ333" t="n">
         <v>2.548084826565839</v>
@@ -54565,16 +54565,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1171965158426952</v>
+        <v>0.1171965158426948</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006367653503792481</v>
+        <v>0.00636765350379247</v>
       </c>
       <c r="AO334" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP334" t="n">
-        <v>-2.104390790930698</v>
+        <v>-2.104390790930691</v>
       </c>
       <c r="AQ334" t="n">
         <v>1.266025641025641</v>
@@ -54718,10 +54718,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI335" t="n">
-        <v>7.140851085964109</v>
+        <v>7.140851085964112</v>
       </c>
       <c r="AJ335" t="n">
-        <v>-0.1128512080344217</v>
+        <v>-0.1128512080344244</v>
       </c>
       <c r="AK335" t="n">
         <v>7.142783913375006</v>
@@ -54730,16 +54730,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.119227205240256</v>
+        <v>0.1192272052402563</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006383133038709798</v>
+        <v>0.00638313303870985</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.5243060286247103</v>
+        <v>0.5243060286247104</v>
       </c>
       <c r="AP335" t="n">
-        <v>-1.999980781016792</v>
+        <v>-1.999980781016887</v>
       </c>
       <c r="AQ335" t="n">
         <v>2.500390686044694</v>
@@ -54883,10 +54883,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.139245392969567</v>
+        <v>7.139245392969565</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1112455150398795</v>
+        <v>-0.1112455150398777</v>
       </c>
       <c r="AK336" t="n">
         <v>7.141836927013541</v>
@@ -54895,16 +54895,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM336" t="n">
-        <v>0.1211746327267789</v>
+        <v>0.1211746327267792</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006404909068509476</v>
+        <v>0.006404909068509461</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5185318197199045</v>
+        <v>0.518531819719905</v>
       </c>
       <c r="AP336" t="n">
-        <v>-1.879907772594156</v>
+        <v>-1.879907772594078</v>
       </c>
       <c r="AQ336" t="n">
         <v>3.704268292682927</v>
@@ -55048,10 +55048,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.136520216281903</v>
+        <v>7.136520216281902</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.108520338352216</v>
+        <v>-0.1085203383522142</v>
       </c>
       <c r="AK337" t="n">
         <v>7.13958125183462</v>
@@ -55060,16 +55060,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1228335954516147</v>
+        <v>0.1228335954516143</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006430223802628449</v>
+        <v>0.006430223802628476</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.5122974965428477</v>
+        <v>0.5122974965428486</v>
       </c>
       <c r="AP337" t="n">
-        <v>-1.727357918499389</v>
+        <v>-1.727357918499316</v>
       </c>
       <c r="AQ337" t="n">
         <v>4.878774356686003</v>
@@ -55228,13 +55228,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006430805642792636</v>
+        <v>0.006430805642792618</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.5056597011855208</v>
+        <v>0.5056597011855207</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.463446639918009</v>
+        <v>-2.463446639918004</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.204994192799071</v>
@@ -55378,10 +55378,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.136562857934749</v>
+        <v>7.13656285793475</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.140462909051692</v>
+        <v>-0.1404629090516929</v>
       </c>
       <c r="AK339" t="n">
         <v>7.132705938528055</v>
@@ -55393,13 +55393,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006419568115912044</v>
+        <v>0.006419568115912051</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4979995576252224</v>
+        <v>0.4979995576252233</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.720289042953629</v>
+        <v>-2.720289042953653</v>
       </c>
       <c r="AQ339" t="n">
         <v>1.190644932671864</v>
@@ -55543,10 +55543,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.135435320996258</v>
+        <v>7.135435320996254</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.1393353721132016</v>
+        <v>-0.1393353721131971</v>
       </c>
       <c r="AK340" t="n">
         <v>7.134470034900207</v>
@@ -55555,16 +55555,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1290155516631957</v>
+        <v>0.1290155516631951</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006423940675024581</v>
+        <v>0.006423940675024553</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.489456156051701</v>
+        <v>0.4894561560517011</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.557572429280606</v>
+        <v>-2.557572429280455</v>
       </c>
       <c r="AQ340" t="n">
         <v>2.948504983388704</v>
@@ -55708,10 +55708,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.135221482968309</v>
+        <v>7.135221482968312</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1391215340852527</v>
+        <v>-0.1391215340852554</v>
       </c>
       <c r="AK341" t="n">
         <v>7.133435115388912</v>
@@ -55720,16 +55720,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1313692321875789</v>
+        <v>0.1313692321875792</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006422605647444513</v>
+        <v>0.006422605647444502</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4811392039904447</v>
+        <v>0.4811392039904442</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.444696267851527</v>
+        <v>-2.444696267851617</v>
       </c>
       <c r="AQ341" t="n">
         <v>4.077079107505071</v>
@@ -55873,10 +55873,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI342" t="n">
-        <v>7.129120131622726</v>
+        <v>7.129120131622732</v>
       </c>
       <c r="AJ342" t="n">
-        <v>-0.1360199653019256</v>
+        <v>-0.1360199653019309</v>
       </c>
       <c r="AK342" t="n">
         <v>7.132510325395203</v>
@@ -55885,16 +55885,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1334873867685099</v>
+        <v>0.1334873867685108</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006388619079873509</v>
+        <v>0.006388619079873553</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4724960612931043</v>
+        <v>0.4724960612931048</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.254840378259555</v>
+        <v>-2.254840378259721</v>
       </c>
       <c r="AQ342" t="n">
         <v>5.17970401691332</v>
@@ -56050,16 +56050,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1357975915367747</v>
+        <v>0.1357975915367741</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006324213907675097</v>
+        <v>0.006324213907675122</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4647750649852552</v>
+        <v>0.4647750649852558</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.331385793786239</v>
+        <v>-2.331385793786226</v>
       </c>
       <c r="AQ343" t="n">
         <v>2.860648327521632</v>
@@ -56203,10 +56203,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI344" t="n">
-        <v>7.122818285283529</v>
+        <v>7.122818285283532</v>
       </c>
       <c r="AJ344" t="n">
-        <v>-0.1394184172720543</v>
+        <v>-0.1394184172720578</v>
       </c>
       <c r="AK344" t="n">
         <v>7.123271418608565</v>
@@ -56215,16 +56215,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1386638579210687</v>
+        <v>0.1386638579210689</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.006222091828703702</v>
+        <v>0.006222091828703747</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4565264017486783</v>
+        <v>0.4565264017486775</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.204545221728734</v>
+        <v>-2.204545221728828</v>
       </c>
       <c r="AQ344" t="n">
         <v>3.939393939393939</v>
@@ -56380,16 +56380,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1423176752089984</v>
+        <v>0.1423176752089981</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.006093783709292283</v>
+        <v>0.006093783709292289</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4497199830569224</v>
+        <v>0.4497199830569214</v>
       </c>
       <c r="AP345" t="n">
-        <v>-1.830741702885553</v>
+        <v>-1.830741702885538</v>
       </c>
       <c r="AQ345" t="n">
         <v>8.889986418076306</v>
@@ -56533,10 +56533,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.133160404869088</v>
+        <v>7.13316040486909</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.1496604010543905</v>
+        <v>-0.1496604010543923</v>
       </c>
       <c r="AK346" t="n">
         <v>7.117219286120759</v>
@@ -56548,13 +56548,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.005984113522022494</v>
+        <v>0.005984113522022499</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4438783751010233</v>
+        <v>0.4438783751010228</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.385403684195726</v>
+        <v>-2.385403684195758</v>
       </c>
       <c r="AQ346" t="n">
         <v>7.765700483091787</v>
@@ -56698,10 +56698,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.12965322071209</v>
+        <v>7.129653220712091</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1524531894315722</v>
+        <v>-0.152453189431573</v>
       </c>
       <c r="AK347" t="n">
         <v>7.126254605494273</v>
@@ -56710,16 +56710,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1503893187551748</v>
+        <v>0.1503893187551739</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005963146506628741</v>
+        <v>0.005963146506628762</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4412018736247373</v>
+        <v>0.441201873624737</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.380336796004049</v>
+        <v>-2.380336796004052</v>
       </c>
       <c r="AQ347" t="n">
         <v>7.680491551459293</v>
@@ -56863,10 +56863,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.128380415829728</v>
+        <v>7.128380415829729</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1552802304354408</v>
+        <v>-0.1552802304354417</v>
       </c>
       <c r="AK348" t="n">
         <v>7.124321202568002</v>
@@ -56875,16 +56875,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1546287435667592</v>
+        <v>0.1546287435667593</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005975981199024843</v>
+        <v>0.005975981199024824</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4385827444686599</v>
+        <v>0.43858274446866</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.375569581173715</v>
+        <v>-2.375569581173716</v>
       </c>
       <c r="AQ348" t="n">
         <v>7.597132284921368</v>
@@ -57028,10 +57028,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.124429161493117</v>
+        <v>7.124429161493114</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1469291996400894</v>
+        <v>-0.1469291996400868</v>
       </c>
       <c r="AK349" t="n">
         <v>7.121152072356459</v>
@@ -57040,16 +57040,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1587808126513012</v>
+        <v>0.1587808126513008</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.00589922161993145</v>
+        <v>0.005899221619931436</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4336499747757657</v>
+        <v>0.4336499747757655</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.071444053426131</v>
+        <v>-2.071444053426039</v>
       </c>
       <c r="AQ349" t="n">
         <v>16.08375778155065</v>
@@ -57205,16 +57205,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1636493008978488</v>
+        <v>0.1636493008978486</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.005897856672615054</v>
+        <v>0.005897856672615022</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.434304834398872</v>
+        <v>0.4343048343988722</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.381707053311504</v>
+        <v>-2.381707053311488</v>
       </c>
       <c r="AQ350" t="n">
         <v>13.81870567375887</v>
@@ -57358,10 +57358,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.141397967314147</v>
+        <v>7.141397967314151</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.1753978872055049</v>
+        <v>-0.1753978872055084</v>
       </c>
       <c r="AK351" t="n">
         <v>7.12802266215534</v>
@@ -57370,16 +57370,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1676675897666615</v>
+        <v>0.1676675897666616</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.005952601612807557</v>
+        <v>0.005952601612807589</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4322693842687806</v>
+        <v>0.4322693842687804</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.667671235283137</v>
+        <v>-2.667671235283208</v>
       </c>
       <c r="AQ351" t="n">
         <v>12.62072707542051</v>
@@ -57523,10 +57523,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.140412492855504</v>
+        <v>7.140412492855501</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1723124219021352</v>
+        <v>-0.1723124219021317</v>
       </c>
       <c r="AK352" t="n">
         <v>7.137738577466652</v>
@@ -57535,16 +57535,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1710383543493657</v>
+        <v>0.1710383543493662</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.006068444256835448</v>
+        <v>0.00606844425683546</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4285062718639565</v>
+        <v>0.4285062718639572</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.487142522607826</v>
+        <v>-2.487142522607719</v>
       </c>
       <c r="AQ352" t="n">
         <v>19.77040816326531</v>
@@ -57688,10 +57688,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.138020503721587</v>
+        <v>7.138020503721584</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.169920432768218</v>
+        <v>-0.1699204327682153</v>
       </c>
       <c r="AK353" t="n">
         <v>7.13663078035759</v>
@@ -57700,16 +57700,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.176195682434215</v>
+        <v>0.1761956824342154</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.006402952059750722</v>
+        <v>0.006402952059750703</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4374093872433962</v>
+        <v>0.4374093872433956</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.343009734619097</v>
+        <v>-2.343009734619021</v>
       </c>
       <c r="AQ353" t="n">
         <v>19.55638862855358</v>
@@ -57853,28 +57853,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.136830620687384</v>
+        <v>7.136830620687383</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1769307183436339</v>
+        <v>-0.1769307183436331</v>
       </c>
       <c r="AK354" t="n">
-        <v>7.14004901784002</v>
+        <v>7.140049017840021</v>
       </c>
       <c r="AL354" t="n">
-        <v>-0.1801491154962704</v>
+        <v>-0.1801491154962713</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1796308914905975</v>
+        <v>0.1796308914905974</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.006948414844703821</v>
+        <v>0.006948414844703805</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4458727441769479</v>
+        <v>0.4458727441769483</v>
       </c>
       <c r="AP354" t="n">
-        <v>-2.433015356127483</v>
+        <v>-2.433015356127453</v>
       </c>
       <c r="AQ354" t="n">
         <v>17.8469387755102</v>
@@ -58014,10 +58014,10 @@
         <v/>
       </c>
       <c r="AI355" t="n">
-        <v>7.133638579266565</v>
+        <v>7.13363857926656</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1699387616090942</v>
+        <v>-0.1699387616090897</v>
       </c>
       <c r="AK355" t="n">
         <v>7.13798584867198</v>
@@ -58026,16 +58026,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1829391475229931</v>
+        <v>0.1829391475229935</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.007602047321544403</v>
+        <v>0.00760204732154433</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4545618931940824</v>
+        <v>0.4545618931940826</v>
       </c>
       <c r="AP355" t="n">
-        <v>-2.192268299666791</v>
+        <v>-2.192268299666683</v>
       </c>
       <c r="AQ355" t="n">
         <v>26.98019801980198</v>
@@ -58179,10 +58179,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI356" t="n">
-        <v>7.12640946890857</v>
+        <v>7.126409468908567</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1538094856932375</v>
+        <v>-0.1538094856932348</v>
       </c>
       <c r="AK356" t="n">
         <v>7.138565167526504</v>
@@ -58191,16 +58191,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1834764543657148</v>
+        <v>0.1834764543657157</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.007712839302340374</v>
+        <v>0.007712839302340297</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4511257152112026</v>
+        <v>0.4511257152112024</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.761104492054283</v>
+        <v>-1.761104492054221</v>
       </c>
       <c r="AQ356" t="n">
         <v>22.60843731431967</v>
@@ -58344,10 +58344,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI357" t="n">
-        <v>7.110999512759045</v>
+        <v>7.110999512759042</v>
       </c>
       <c r="AJ357" t="n">
-        <v>-0.1383995295437126</v>
+        <v>-0.1383995295437099</v>
       </c>
       <c r="AK357" t="n">
         <v>7.137040595974374</v>
@@ -58356,16 +58356,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1869739626316104</v>
+        <v>0.1869739626316108</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.00835460951998479</v>
+        <v>0.008354609519984808</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4618871834350119</v>
+        <v>0.4618871834350127</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.368717051122944</v>
+        <v>-1.368717051122884</v>
       </c>
       <c r="AQ357" t="n">
         <v>16.75242718446602</v>
@@ -58521,16 +58521,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.1901371272406391</v>
+        <v>0.1901371272406383</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.008787529863310189</v>
+        <v>0.008787529863310259</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4631528842621211</v>
+        <v>0.4631528842621208</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.405229583753368</v>
+        <v>-1.405229583753373</v>
       </c>
       <c r="AQ358" t="n">
         <v>10.21039603960396</v>
@@ -58674,10 +58674,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI359" t="n">
-        <v>7.10229338126412</v>
+        <v>7.102293381264122</v>
       </c>
       <c r="AJ359" t="n">
-        <v>-0.1477931828998624</v>
+        <v>-0.1477931828998642</v>
       </c>
       <c r="AK359" t="n">
         <v>7.113436809075056</v>
@@ -58686,16 +58686,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.1939456835457532</v>
+        <v>0.193945683545753</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.009306466714917722</v>
+        <v>0.009306466714917755</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4650211967660294</v>
+        <v>0.4650211967660295</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.547790886058297</v>
+        <v>-1.547790886058342</v>
       </c>
       <c r="AQ359" t="n">
         <v>11.12044817927171</v>
@@ -58851,16 +58851,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.1968971496416331</v>
+        <v>0.1968971496416338</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.009915270508004642</v>
+        <v>0.009915270508004639</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4658112293095933</v>
+        <v>0.4658112293095935</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.323847614466191</v>
+        <v>-1.323847614466194</v>
       </c>
       <c r="AQ360" t="n">
         <v>11.40318739695915</v>
@@ -59016,16 +59016,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2001574773810679</v>
+        <v>0.200157477381068</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.01045224758824684</v>
+        <v>0.01045224758824685</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4652001227613064</v>
+        <v>0.4652001227613058</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.585894032713987</v>
+        <v>-1.58589403271399</v>
       </c>
       <c r="AQ361" t="n">
         <v>5.153666427030913</v>
@@ -59169,10 +59169,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI362" t="n">
-        <v>7.112155432918446</v>
+        <v>7.112155432918444</v>
       </c>
       <c r="AJ362" t="n">
-        <v>-0.1611552192953987</v>
+        <v>-0.1611552192953969</v>
       </c>
       <c r="AK362" t="n">
         <v>7.115439870473561</v>
@@ -59181,16 +59181,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2059164257597553</v>
+        <v>0.2059164257597547</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01095806236007055</v>
+        <v>0.0109580623600705</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4647071558511969</v>
+        <v>0.4647071558511972</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.78212565773126</v>
+        <v>-1.782125657731223</v>
       </c>
       <c r="AQ362" t="n">
         <v>6.587301587301587</v>
@@ -59346,16 +59346,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2103846028094628</v>
+        <v>0.2103846028094625</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01138655624224677</v>
+        <v>0.01138655624224671</v>
       </c>
       <c r="AO363" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.810148439959766</v>
+        <v>-1.81014843995977</v>
       </c>
       <c r="AQ363" t="n">
         <v>11.2428596157175</v>
@@ -59499,10 +59499,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI364" t="n">
-        <v>7.110775793344653</v>
+        <v>7.110775793344654</v>
       </c>
       <c r="AJ364" t="n">
-        <v>-0.1730759985753663</v>
+        <v>-0.1730759985753672</v>
       </c>
       <c r="AK364" t="n">
         <v>7.127056499711662</v>
@@ -59511,16 +59511,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2137349114935569</v>
+        <v>0.2137349114935566</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01184277521890661</v>
+        <v>0.0118427752189066</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4573024605378193</v>
+        <v>0.4573024605378192</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.974952691681103</v>
+        <v>-1.974952691681126</v>
       </c>
       <c r="AQ364" t="n">
         <v>12.5785896346644</v>
@@ -59676,16 +59676,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2192999169256238</v>
+        <v>0.2192999169256231</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01242692746354282</v>
+        <v>0.01242692746354283</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4593518446085588</v>
+        <v>0.4593518446085587</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.53389908426528</v>
+        <v>-1.533899084265283</v>
       </c>
       <c r="AQ365" t="n">
         <v>14.21421421421421</v>
@@ -59829,28 +59829,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.095070446253633</v>
+        <v>7.095070446253632</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.1572705156811232</v>
+        <v>-0.1572705156811223</v>
       </c>
       <c r="AK366" t="n">
-        <v>7.099084322920755</v>
+        <v>7.099084322920754</v>
       </c>
       <c r="AL366" t="n">
-        <v>-0.1612843923482448</v>
+        <v>-0.1612843923482439</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2273791016644669</v>
+        <v>0.2273791016644665</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01301934706839999</v>
+        <v>0.01301934706840001</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4655241261491886</v>
+        <v>0.4655241261491888</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.566746911622516</v>
+        <v>-1.5667469116225</v>
       </c>
       <c r="AQ366" t="n">
         <v>12.26245085190039</v>
@@ -59994,10 +59994,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.077412848446851</v>
+        <v>7.077412848446856</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1386129903535895</v>
+        <v>-0.138612990353594</v>
       </c>
       <c r="AK367" t="n">
         <v>7.107752072150756</v>
@@ -60006,16 +60006,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2346680713248289</v>
+        <v>0.2346680713248287</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01366280940279216</v>
+        <v>0.01366280940279221</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4682122340216202</v>
+        <v>0.4682122340216205</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.136522825763405</v>
+        <v>-1.136522825763505</v>
       </c>
       <c r="AQ367" t="n">
         <v>19.68624296057924</v>
@@ -60159,10 +60159,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.067855559671527</v>
+        <v>7.067855559671529</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1458556283360775</v>
+        <v>-0.1458556283360801</v>
       </c>
       <c r="AK368" t="n">
         <v>7.100856094477853</v>
@@ -60171,16 +60171,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2404731763378842</v>
+        <v>0.2404731763378833</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01427110593278799</v>
+        <v>0.01427110593278805</v>
       </c>
       <c r="AO368" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.28355700537033</v>
+        <v>-1.283557005370389</v>
       </c>
       <c r="AQ368" t="n">
         <v>19.14414414414414</v>
@@ -60324,10 +60324,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.081794385763164</v>
+        <v>7.081794385763168</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1711942003688769</v>
+        <v>-0.1711942003688813</v>
       </c>
       <c r="AK369" t="n">
         <v>7.090764621929079</v>
@@ -60336,16 +60336,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2453259423721931</v>
+        <v>0.2453259423721924</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01502424352484369</v>
+        <v>0.01502424352484376</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.4756424387980298</v>
+        <v>0.4756424387980304</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.814459861875897</v>
+        <v>-1.814459861875991</v>
       </c>
       <c r="AQ369" t="n">
         <v>15.5667701863354</v>
@@ -60489,10 +60489,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.068234493406102</v>
+        <v>7.068234493406101</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1557345887735337</v>
+        <v>-0.1557345887735329</v>
       </c>
       <c r="AK370" t="n">
         <v>7.110983013755962</v>
@@ -60501,16 +60501,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2481172514763508</v>
+        <v>0.2481172514763511</v>
       </c>
       <c r="AN370" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4781214750573159</v>
+        <v>0.4781214750573156</v>
       </c>
       <c r="AP370" t="n">
-        <v>-1.452804883187617</v>
+        <v>-1.452804883187595</v>
       </c>
       <c r="AQ370" t="n">
         <v>19.33170582850168</v>
@@ -60654,28 +60654,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.047011693433886</v>
+        <v>7.04701169343388</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1469114622632315</v>
+        <v>-0.1469114622632253</v>
       </c>
       <c r="AK371" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL371" t="n">
-        <v>-0.1936362268489642</v>
+        <v>-0.1936362268489633</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2517176519946896</v>
+        <v>0.2517176519946887</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.01672959897123732</v>
+        <v>0.01672959897123727</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.482044795280705</v>
+        <v>0.4820447952807055</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.244932890532577</v>
+        <v>-1.244932890532441</v>
       </c>
       <c r="AQ371" t="n">
         <v>18.62348178137652</v>
@@ -60819,28 +60819,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.043635211714482</v>
+        <v>7.043635211714486</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.135635219343877</v>
+        <v>-0.1356352193438806</v>
       </c>
       <c r="AK372" t="n">
-        <v>7.069112439760902</v>
+        <v>7.069112439760901</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1611124473902965</v>
+        <v>-0.1611124473902956</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2568291528619773</v>
+        <v>0.2568291528619769</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01758784222749221</v>
+        <v>0.0175878422274923</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.4888256589627545</v>
+        <v>0.488825658962754</v>
       </c>
       <c r="AP372" t="n">
-        <v>-0.9891368860718699</v>
+        <v>-0.9891368860719471</v>
       </c>
       <c r="AQ372" t="n">
         <v>23.98305084745763</v>
@@ -60984,10 +60984,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.045320696769622</v>
+        <v>7.04532069676962</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1373207043990163</v>
+        <v>-0.1373207043990146</v>
       </c>
       <c r="AK373" t="n">
         <v>7.067486653848666</v>
@@ -60996,16 +60996,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2611441025487395</v>
+        <v>0.2611441025487396</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.01863884916361525</v>
+        <v>0.01863884916361523</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.4958891106408185</v>
+        <v>0.4958891106408189</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.017305448193841</v>
+        <v>-1.017305448193802</v>
       </c>
       <c r="AQ373" t="n">
         <v>21.6350333236743</v>
@@ -61149,10 +61149,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.052957186540217</v>
+        <v>7.052957186540212</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1449571941696117</v>
+        <v>-0.1449571941696064</v>
       </c>
       <c r="AK374" t="n">
         <v>7.066060765041626</v>
@@ -61161,16 +61161,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2646928033319798</v>
+        <v>0.2646928033319788</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.01961447184998982</v>
+        <v>0.0196144718499898</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.4990325267638059</v>
+        <v>0.4990325267638065</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.17302240203794</v>
+        <v>-1.173022402037825</v>
       </c>
       <c r="AQ374" t="n">
         <v>18.98504273504274</v>
@@ -61314,28 +61314,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI375" t="n">
-        <v>7.055218091951101</v>
+        <v>7.055218091951103</v>
       </c>
       <c r="AJ375" t="n">
-        <v>-0.1472180995804955</v>
+        <v>-0.1472180995804973</v>
       </c>
       <c r="AK375" t="n">
-        <v>7.064646745753511</v>
+        <v>7.06464674575351</v>
       </c>
       <c r="AL375" t="n">
-        <v>-0.1566467533829057</v>
+        <v>-0.1566467533829048</v>
       </c>
       <c r="AM375" t="n">
-        <v>0.2692457951306195</v>
+        <v>0.2692457951306194</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.02045122459205889</v>
+        <v>0.02045122459205891</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.5009265659871953</v>
+        <v>0.5009265659871951</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.210005799573701</v>
+        <v>-1.210005799573742</v>
       </c>
       <c r="AQ375" t="n">
         <v>18.01022552178176</v>
@@ -61479,10 +61479,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.050463258619342</v>
+        <v>7.050463258619345</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1423631304455135</v>
+        <v>-0.1423631304455171</v>
       </c>
       <c r="AK376" t="n">
         <v>7.063274589921972</v>
@@ -61491,16 +61491,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2738618637550985</v>
+        <v>0.2738618637550991</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02103732430364852</v>
+        <v>0.02103732430364855</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5007948901071727</v>
+        <v>0.5007948901071723</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.093899743579132</v>
+        <v>-1.09389974357921</v>
       </c>
       <c r="AQ376" t="n">
         <v>22.43077558892409</v>
@@ -61817,13 +61817,13 @@
         <v/>
       </c>
       <c r="AM378" t="n">
-        <v>0.280344119587675</v>
+        <v>0.2803441195876753</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02230845224183686</v>
+        <v>0.02230845224183688</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.5036776407221306</v>
+        <v>0.5036776407221312</v>
       </c>
       <c r="AP378" t="n">
         <v>-1.246491204623905</v>
@@ -61970,10 +61970,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.056824809597053</v>
+        <v>7.056824809597052</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.1737247767906567</v>
+        <v>-0.1737247767906558</v>
       </c>
       <c r="AK379" t="n">
         <v>7.071238163852278</v>
@@ -61982,16 +61982,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2841407798055449</v>
+        <v>0.2841407798055452</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02276542233315987</v>
+        <v>0.02276542233315985</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5036956996297977</v>
+        <v>0.5036956996297983</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.735499502858073</v>
+        <v>-1.735499502858054</v>
       </c>
       <c r="AQ379" t="n">
         <v>21.70148069804337</v>
@@ -62135,10 +62135,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.04726592259491</v>
+        <v>7.047265922594908</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.1780656929501347</v>
+        <v>-0.178065692950133</v>
       </c>
       <c r="AK380" t="n">
         <v>7.075283303194255</v>
@@ -62147,16 +62147,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2869603504542605</v>
+        <v>0.2869603504542598</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02324367830537832</v>
+        <v>0.02324367830537833</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5029697249741727</v>
+        <v>0.5029697249741724</v>
       </c>
       <c r="AP380" t="n">
-        <v>-1.797910715459853</v>
+        <v>-1.797910715459816</v>
       </c>
       <c r="AQ380" t="n">
         <v>10.56260162601626</v>
@@ -62300,10 +62300,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.030237372659574</v>
+        <v>7.030237372659579</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.189337428354154</v>
+        <v>-0.1893374283541593</v>
       </c>
       <c r="AK381" t="n">
         <v>7.061088020066238</v>
@@ -62312,16 +62312,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.2909556153842325</v>
+        <v>0.2909556153842324</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02343150180192449</v>
+        <v>0.02343150180192457</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.501187497763653</v>
+        <v>0.5011874977636526</v>
       </c>
       <c r="AP381" t="n">
-        <v>-1.998175164150586</v>
+        <v>-1.998175164150696</v>
       </c>
       <c r="AQ381" t="n">
         <v>2.412954429083461</v>
@@ -62465,10 +62465,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.074556523891909</v>
+        <v>7.074556523891907</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.2166563812222311</v>
+        <v>-0.2166563812222293</v>
       </c>
       <c r="AK382" t="n">
         <v>7.045371831199247</v>
@@ -62477,16 +62477,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.2963660759601011</v>
+        <v>0.2963660759601009</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02388105320115907</v>
+        <v>0.02388105320115906</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.5011837436137521</v>
+        <v>0.5011837436137511</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.500689639035226</v>
+        <v>-2.500689639035188</v>
       </c>
       <c r="AQ382" t="n">
         <v>14.79370078740157</v>
@@ -62630,10 +62630,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.103552248295395</v>
+        <v>7.103552248295403</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2215522788129736</v>
+        <v>-0.2215522788129807</v>
       </c>
       <c r="AK383" t="n">
         <v>7.078406423284397</v>
@@ -62642,16 +62642,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.29984079129971</v>
+        <v>0.2998407912997099</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02427773372157399</v>
+        <v>0.02427773372157407</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.4964684575356704</v>
+        <v>0.4964684575356701</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.525433235757391</v>
+        <v>-2.525433235757525</v>
       </c>
       <c r="AQ383" t="n">
         <v>19.43824404761905</v>
@@ -62807,16 +62807,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3035220749319825</v>
+        <v>0.3035220749319821</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02465824743687012</v>
+        <v>0.02465824743687013</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.4899948718309226</v>
+        <v>0.4899948718309223</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.237361550577034</v>
+        <v>-2.237361550577025</v>
       </c>
       <c r="AQ384" t="n">
         <v>23.21003479216261</v>
@@ -62960,10 +62960,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.12777959440025</v>
+        <v>7.127779594400253</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.2307797584322326</v>
+        <v>-0.2307797584322353</v>
       </c>
       <c r="AK385" t="n">
         <v>7.110202206771168</v>
@@ -62972,16 +62972,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3056770963992281</v>
+        <v>0.3056770963992276</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02512392944114572</v>
+        <v>0.02512392944114575</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4836004785809395</v>
+        <v>0.48360047858094</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.571887198688558</v>
+        <v>-2.571887198688598</v>
       </c>
       <c r="AQ385" t="n">
         <v>22.65024038461538</v>
@@ -63125,28 +63125,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.117424820782309</v>
+        <v>7.117424820782308</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2204249848142918</v>
+        <v>-0.2204249848142901</v>
       </c>
       <c r="AK386" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL386" t="n">
-        <v>-0.2182210070512509</v>
+        <v>-0.21822100705125</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3083414575758074</v>
+        <v>0.3083414575758079</v>
       </c>
       <c r="AN386" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.474982443940299</v>
+        <v>0.4749824439402989</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.311874447286236</v>
+        <v>-2.311874447286193</v>
       </c>
       <c r="AQ386" t="n">
         <v>25.17604591987692</v>
@@ -63290,10 +63290,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.116315246651977</v>
+        <v>7.116315246651979</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.2198151360257565</v>
+        <v>-0.2198151360257583</v>
       </c>
       <c r="AK387" t="n">
         <v>7.112470209890858</v>
@@ -63302,16 +63302,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3094443575020182</v>
+        <v>0.3094443575020188</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.0257875072203187</v>
+        <v>0.02578750722031873</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.4671039145039241</v>
+        <v>0.467103914503924</v>
       </c>
       <c r="AP387" t="n">
-        <v>-2.246620026390865</v>
+        <v>-2.246620026390889</v>
       </c>
       <c r="AQ387" t="n">
         <v>24.97668997668998</v>
@@ -63455,28 +63455,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.109165799046384</v>
+        <v>7.109165799046382</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.1981660241135224</v>
+        <v>-0.1981660241135206</v>
       </c>
       <c r="AK388" t="n">
-        <v>7.105086649080124</v>
+        <v>7.105086649080123</v>
       </c>
       <c r="AL388" t="n">
-        <v>-0.1940868741472626</v>
+        <v>-0.1940868741472617</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3112159059696454</v>
+        <v>0.3112159059696449</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.02619128791084346</v>
+        <v>0.02619128791084347</v>
       </c>
       <c r="AO388" t="n">
-        <v>0.4597800393113445</v>
+        <v>0.4597800393113443</v>
       </c>
       <c r="AP388" t="n">
-        <v>-1.809041966473271</v>
+        <v>-1.809041966473231</v>
       </c>
       <c r="AQ388" t="n">
         <v>26.295701084773</v>
@@ -63620,10 +63620,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.140476658697598</v>
+        <v>7.14047665869759</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.2639765289978913</v>
+        <v>-0.2639765289978833</v>
       </c>
       <c r="AK389" t="n">
         <v>7.107009848336411</v>
@@ -63632,16 +63632,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3120213667410843</v>
+        <v>0.3120213667410841</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02660872919284657</v>
+        <v>0.02660872919284651</v>
       </c>
       <c r="AO389" t="n">
-        <v>0.4527828726277016</v>
+        <v>0.4527828726277021</v>
       </c>
       <c r="AP389" t="n">
-        <v>-2.92634131629074</v>
+        <v>-2.926341316290596</v>
       </c>
       <c r="AQ389" t="n">
         <v>18.93374038896427</v>
@@ -63785,10 +63785,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.192104266103097</v>
+        <v>7.192104266103096</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.3266042928059782</v>
+        <v>-0.3266042928059765</v>
       </c>
       <c r="AK390" t="n">
         <v>7.130667004235951</v>
@@ -63797,16 +63797,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3119580514589064</v>
+        <v>0.3119580514589062</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02723917591229313</v>
+        <v>0.02723917591229311</v>
       </c>
       <c r="AO390" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP390" t="n">
-        <v>-3.817928756740285</v>
+        <v>-3.817928756740258</v>
       </c>
       <c r="AQ390" t="n">
         <v>21.7989417989418</v>
@@ -63962,7 +63962,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3060770546706492</v>
+        <v>0.3060770546706496</v>
       </c>
       <c r="AN391" t="n">
         <v>0.02737088803905663</v>
@@ -63971,7 +63971,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.687217725798318</v>
+        <v>-3.687217725798322</v>
       </c>
       <c r="AQ391" t="n">
         <v>19.39749780509219</v>
@@ -64115,10 +64115,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.16410590848237</v>
+        <v>7.164105908482372</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.2680058642318812</v>
+        <v>-0.2680058642318839</v>
       </c>
       <c r="AK392" t="n">
         <v>7.162206823443969</v>
@@ -64127,16 +64127,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.3021518080029227</v>
+        <v>0.3021518080029217</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02724691784252931</v>
+        <v>0.02724691784252936</v>
       </c>
       <c r="AO392" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP392" t="n">
-        <v>-2.573346866416288</v>
+        <v>-2.573346866416331</v>
       </c>
       <c r="AQ392" t="n">
         <v>23.6874831035415</v>
@@ -64280,10 +64280,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.165713254747866</v>
+        <v>7.165713254747862</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.2102131288628559</v>
+        <v>-0.2102131288628524</v>
       </c>
       <c r="AK393" t="n">
         <v>7.141021818380439</v>
@@ -64292,16 +64292,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.3004913268435098</v>
+        <v>0.3004913268435102</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02739193077523433</v>
+        <v>0.02739193077523432</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3752726470948202</v>
+        <v>0.3752726470948199</v>
       </c>
       <c r="AP393" t="n">
-        <v>-1.627744531597144</v>
+        <v>-1.627744531597089</v>
       </c>
       <c r="AQ393" t="n">
         <v>30.46142369991475</v>
@@ -64445,10 +64445,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.208249532027229</v>
+        <v>7.208249532027231</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3219494450521312</v>
+        <v>-0.321949445052133</v>
       </c>
       <c r="AK394" t="n">
         <v>7.146296571548195</v>
@@ -64457,16 +64457,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2982197220770054</v>
+        <v>0.2982197220770058</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02742417953210363</v>
+        <v>0.02742417953210373</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3625782951332472</v>
+        <v>0.3625782951332475</v>
       </c>
       <c r="AP394" t="n">
-        <v>-3.256367936666931</v>
+        <v>-3.256367936666958</v>
       </c>
       <c r="AQ394" t="n">
         <v>25.16672793152339</v>
@@ -64610,28 +64610,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.193412187855718</v>
+        <v>7.193412187855726</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3208121092729543</v>
+        <v>-0.3208121092729623</v>
       </c>
       <c r="AK395" t="n">
-        <v>7.176497065376474</v>
+        <v>7.176497065376473</v>
       </c>
       <c r="AL395" t="n">
-        <v>-0.3038969867937107</v>
+        <v>-0.3038969867937098</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2910761841041076</v>
+        <v>0.2910761841041086</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02685747952387152</v>
+        <v>0.02685747952387156</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.3370674577034428</v>
+        <v>0.3370674577034442</v>
       </c>
       <c r="AP395" t="n">
-        <v>-3.112137549565402</v>
+        <v>-3.112137549565511</v>
       </c>
       <c r="AQ395" t="n">
         <v>26.06625258799172</v>
@@ -64775,10 +64775,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.227115602342048</v>
+        <v>7.227115602342041</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3273157785810614</v>
+        <v>-0.3273157785810543</v>
       </c>
       <c r="AK396" t="n">
         <v>7.185469892270627</v>
@@ -64787,16 +64787,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2812269987605887</v>
+        <v>0.281226998760588</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02697180537422167</v>
+        <v>0.0269718053742217</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.3136210223326478</v>
+        <v>0.3136210223326474</v>
       </c>
       <c r="AP396" t="n">
-        <v>-3.08574377662453</v>
+        <v>-3.085743776624427</v>
       </c>
       <c r="AQ396" t="n">
         <v>26.96821266391142</v>
@@ -64940,10 +64940,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.187163192389372</v>
+        <v>7.187163192389367</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3014629665592938</v>
+        <v>-0.3014629665592885</v>
       </c>
       <c r="AK397" t="n">
         <v>7.208338760609084</v>
@@ -64952,16 +64952,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2681836981576122</v>
+        <v>0.2681836981576121</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02658698789673936</v>
+        <v>0.02658698789673927</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.285908150945263</v>
+        <v>0.2859081509452629</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.637149998460412</v>
+        <v>-2.63714999846034</v>
       </c>
       <c r="AQ397" t="n">
         <v>27.82696177062374</v>
@@ -65105,10 +65105,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.214951953115591</v>
+        <v>7.214951953115579</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.334951838674673</v>
+        <v>-0.3349518386746606</v>
       </c>
       <c r="AK398" t="n">
         <v>7.186200492654655</v>
@@ -65117,16 +65117,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2591628297636744</v>
+        <v>0.2591628297636748</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02587977479594339</v>
+        <v>0.02587977479594331</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.266108201492412</v>
+        <v>0.2661082014924122</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.99635759486535</v>
+        <v>-2.996357594865196</v>
       </c>
       <c r="AQ398" t="n">
         <v>27.30000495957943</v>
@@ -65270,10 +65270,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.197430004066455</v>
+        <v>7.197430004066453</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.305630077308642</v>
+        <v>-0.3056300773086402</v>
       </c>
       <c r="AK399" t="n">
         <v>7.201835396295348</v>
@@ -65282,16 +65282,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2466333883508319</v>
+        <v>0.2466333883508324</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.0247654344950328</v>
+        <v>0.02476543449503272</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.2401258754735003</v>
+        <v>0.2401258754735008</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.528667553133092</v>
+        <v>-2.528667553133083</v>
       </c>
       <c r="AQ399" t="n">
         <v>26.02210485133021</v>
@@ -65438,25 +65438,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.3291230670577869</v>
+        <v>-0.3291230670577878</v>
       </c>
       <c r="AK400" t="n">
-        <v>7.179650721554484</v>
+        <v>7.179650721554483</v>
       </c>
       <c r="AL400" t="n">
-        <v>-0.2786506986663007</v>
+        <v>-0.2786506986662998</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2377807761788571</v>
+        <v>0.2377807761788565</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.02334020127887793</v>
+        <v>0.02334020127887796</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.2171758918683914</v>
+        <v>0.2171758918683913</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.756739116666435</v>
+        <v>-2.75673911666646</v>
       </c>
       <c r="AQ400" t="n">
         <v>26.55895828309622</v>
@@ -65600,10 +65600,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.20852803773295</v>
+        <v>7.208528037732954</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2978281933725988</v>
+        <v>-0.2978281933726024</v>
       </c>
       <c r="AK401" t="n">
         <v>7.206616000051887</v>
@@ -65612,16 +65612,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.2255544515066686</v>
+        <v>0.2255544515066683</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.0206724522626571</v>
+        <v>0.0206724522626572</v>
       </c>
       <c r="AO401" t="n">
-        <v>0.1898019966940717</v>
+        <v>0.1898019966940708</v>
       </c>
       <c r="AP401" t="n">
-        <v>-2.296876954307927</v>
+        <v>-2.296876954307982</v>
       </c>
       <c r="AQ401" t="n">
         <v>16.2718797564688</v>
@@ -65765,10 +65765,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.19880309223843</v>
+        <v>7.198803092238432</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.287202979323391</v>
+        <v>-0.2872029793233928</v>
       </c>
       <c r="AK402" t="n">
         <v>7.18051307481679</v>
@@ -65777,16 +65777,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.2150441262650612</v>
+        <v>0.2150441262650616</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.01774895516388914</v>
+        <v>0.0177489551638892</v>
       </c>
       <c r="AO402" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.119327753717743</v>
+        <v>-2.119327753717773</v>
       </c>
       <c r="AQ402" t="n">
         <v>14.77597935726015</v>
@@ -65930,10 +65930,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.172424239411004</v>
+        <v>7.172424239411002</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2608241264959652</v>
+        <v>-0.2608241264959634</v>
       </c>
       <c r="AK403" t="n">
         <v>7.16705299197773</v>
@@ -65942,16 +65942,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.205433651489446</v>
+        <v>0.2054336514894463</v>
       </c>
       <c r="AN403" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO403" t="n">
-        <v>0.1417286033373026</v>
+        <v>0.1417286033373033</v>
       </c>
       <c r="AP403" t="n">
-        <v>-1.759310618264857</v>
+        <v>-1.759310618264842</v>
       </c>
       <c r="AQ403" t="n">
         <v>18.77082562014069</v>
@@ -66095,10 +66095,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.163756390646672</v>
+        <v>7.163756390646673</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2695565424716229</v>
+        <v>-0.2695565424716238</v>
       </c>
       <c r="AK404" t="n">
         <v>7.153532751444382</v>
@@ -66107,16 +66107,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.1941661953581061</v>
+        <v>0.1941661953581056</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.01312004055850013</v>
+        <v>0.01312004055850015</v>
       </c>
       <c r="AO404" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.841567079186516</v>
+        <v>-1.841567079186534</v>
       </c>
       <c r="AQ404" t="n">
         <v>25.11528101173355</v>
@@ -66260,10 +66260,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.158063699621738</v>
+        <v>7.158063699621736</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2875636118837006</v>
+        <v>-0.2875636118836988</v>
       </c>
       <c r="AK405" t="n">
         <v>7.150669702211316</v>
@@ -66272,16 +66272,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1839494937266881</v>
+        <v>0.183949493726688</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.01194074338472806</v>
+        <v>0.01194074338472802</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.1107549805175829</v>
+        <v>0.110754980517583</v>
       </c>
       <c r="AP405" t="n">
-        <v>-2.03099915444689</v>
+        <v>-2.030999154446876</v>
       </c>
       <c r="AQ405" t="n">
         <v>13.12612612612613</v>
@@ -66425,10 +66425,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.157435208014563</v>
+        <v>7.157435208014565</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.272335320166663</v>
+        <v>-0.2723353201666647</v>
       </c>
       <c r="AK406" t="n">
         <v>7.140926852093823</v>
@@ -66437,16 +66437,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1753430411611933</v>
+        <v>0.1753430411611928</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.00971765423202034</v>
+        <v>0.009717654232020439</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.09620195025422695</v>
+        <v>0.09620195025422784</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.816085835102861</v>
+        <v>-1.816085835102889</v>
       </c>
       <c r="AQ406" t="n">
         <v>21.08315925152229</v>
@@ -66590,10 +66590,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.150386811340072</v>
+        <v>7.15038681134007</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2679867754819174</v>
+        <v>-0.2679867754819156</v>
       </c>
       <c r="AK407" t="n">
         <v>7.142886401315924</v>
@@ -66602,16 +66602,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1664838398737872</v>
+        <v>0.1664838398737869</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.008089376136153875</v>
+        <v>0.008089376136153925</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.0848962688609296</v>
+        <v>0.08489626886092971</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.739134136482415</v>
+        <v>-1.7391341364824</v>
       </c>
       <c r="AQ407" t="n">
         <v>20.59649122807017</v>
@@ -66755,10 +66755,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.137094841694645</v>
+        <v>7.137094841694642</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2547949416397133</v>
+        <v>-0.2547949416397106</v>
       </c>
       <c r="AK408" t="n">
         <v>7.137840883333127</v>
@@ -66767,16 +66767,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1571907956492611</v>
+        <v>0.1571907956492617</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.006581947594647974</v>
+        <v>0.006581947594647856</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.07412699588694804</v>
+        <v>0.07412699588694738</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.560440892271773</v>
+        <v>-1.560440892271748</v>
       </c>
       <c r="AQ408" t="n">
         <v>20.77868675063845</v>
@@ -66920,10 +66920,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.123391234435203</v>
+        <v>7.1233912344352</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2666912908927221</v>
+        <v>-0.2666912908927195</v>
       </c>
       <c r="AK409" t="n">
         <v>7.12862724785568</v>
@@ -66932,16 +66932,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1487097707294961</v>
+        <v>0.1487097707294973</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005441006961990014</v>
+        <v>0.005441006961990058</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.06531270865715677</v>
+        <v>0.06531270865715666</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.683353509644539</v>
+        <v>-1.683353509644515</v>
       </c>
       <c r="AQ409" t="n">
         <v>14.40105946684894</v>
@@ -67085,10 +67085,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.11600731855288</v>
+        <v>7.116007318552882</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2873072529400869</v>
+        <v>-0.2873072529400895</v>
       </c>
       <c r="AK410" t="n">
         <v>7.118961040191934</v>
@@ -67097,16 +67097,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM410" t="n">
-        <v>0.1409513724492178</v>
+        <v>0.1409513724492179</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005644373135176822</v>
+        <v>0.005644373135176906</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.05986577613532174</v>
+        <v>0.0598657761353214</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.902826462226918</v>
+        <v>-1.902826462226957</v>
       </c>
       <c r="AQ410" t="n">
         <v>10.08011806873287</v>
@@ -67250,10 +67250,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.115262454587763</v>
+        <v>7.11526245458776</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2838625369852235</v>
+        <v>-0.2838625369852208</v>
       </c>
       <c r="AK411" t="n">
         <v>7.113208458946866</v>
@@ -67265,13 +67265,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005618445165739616</v>
+        <v>0.005618445165739529</v>
       </c>
       <c r="AO411" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.835305502148032</v>
+        <v>-1.835305502148007</v>
       </c>
       <c r="AQ411" t="n">
         <v>8.707958707958708</v>
@@ -67427,16 +67427,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM412" t="n">
-        <v>0.1248427026608149</v>
+        <v>0.1248427026608145</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005050876420738246</v>
+        <v>0.005050876420738303</v>
       </c>
       <c r="AO412" t="n">
-        <v>0.04692762159458042</v>
+        <v>0.04692762159457986</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.750285662434824</v>
+        <v>-1.750285662434831</v>
       </c>
       <c r="AQ412" t="n">
         <v>13.8093281282104</v>
@@ -67580,10 +67580,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI413" t="n">
-        <v>7.100218718661557</v>
+        <v>7.100218718661558</v>
       </c>
       <c r="AJ413" t="n">
-        <v>-0.2699188643829924</v>
+        <v>-0.2699188643829933</v>
       </c>
       <c r="AK413" t="n">
         <v>7.105971078464224</v>
@@ -67595,13 +67595,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005209570180715356</v>
+        <v>0.00520957018071537</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.0421970173931332</v>
+        <v>0.04219701739313308</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.628242528710586</v>
+        <v>-1.628242528710603</v>
       </c>
       <c r="AQ413" t="n">
         <v>14.99513145082765</v>
@@ -67745,10 +67745,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.097935875054437</v>
+        <v>7.097935875054439</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2822358208857363</v>
+        <v>-0.2822358208857381</v>
       </c>
       <c r="AK414" t="n">
         <v>7.101361129315627</v>
@@ -67757,16 +67757,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.1117472247487875</v>
+        <v>0.1117472247487876</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.005385102682029907</v>
+        <v>0.005385102682029925</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.03866992220359</v>
+        <v>0.03866992220359033</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.749707041474974</v>
+        <v>-1.749707041475001</v>
       </c>
       <c r="AQ414" t="n">
         <v>13.95264992188439</v>
@@ -67910,10 +67910,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI415" t="n">
-        <v>7.097978821692022</v>
+        <v>7.097978821692021</v>
       </c>
       <c r="AJ415" t="n">
-        <v>-0.2799789819093075</v>
+        <v>-0.2799789819093057</v>
       </c>
       <c r="AK415" t="n">
         <v>7.099648834314064</v>
@@ -67922,16 +67922,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.1065475925362033</v>
+        <v>0.1065475925362025</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005956926407440957</v>
+        <v>0.005956926407441003</v>
       </c>
       <c r="AO415" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.702251341870201</v>
+        <v>-1.702251341870187</v>
       </c>
       <c r="AQ415" t="n">
         <v>13.86075949367089</v>
@@ -68087,16 +68087,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.1013724682419977</v>
+        <v>0.1013724682419976</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.006126167203105798</v>
+        <v>0.006126167203105847</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.03348722035246332</v>
+        <v>0.03348722035246277</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.540086272869379</v>
+        <v>-1.540086272869385</v>
       </c>
       <c r="AQ416" t="n">
         <v>22.55166217430368</v>
@@ -68240,10 +68240,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI417" t="n">
-        <v>7.087097940453345</v>
+        <v>7.087097940453343</v>
       </c>
       <c r="AJ417" t="n">
-        <v>-0.2700980281913825</v>
+        <v>-0.2700980281913798</v>
       </c>
       <c r="AK417" t="n">
         <v>7.090805518999606</v>
@@ -68252,16 +68252,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.09919462776856321</v>
+        <v>0.09919462776856289</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.006113943880485972</v>
+        <v>0.006113943880485968</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.03204155062895153</v>
+        <v>0.03204155062895098</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.554670831775283</v>
+        <v>-1.554670831775259</v>
       </c>
       <c r="AQ417" t="n">
         <v>17.4266975308642</v>
@@ -68417,16 +68417,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.097507502547015</v>
+        <v>0.09750750254701511</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.005510714664730507</v>
+        <v>0.005510714664730422</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.03001455024934374</v>
+        <v>0.03001455024934274</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.613360789246392</v>
+        <v>-1.613360789246399</v>
       </c>
       <c r="AQ418" t="n">
         <v>14.21712456655108</v>
@@ -68582,16 +68582,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.09380549503386901</v>
+        <v>0.09380549503386949</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.004784904607979881</v>
+        <v>0.004784904607979855</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.02699383492044782</v>
+        <v>0.02699383492044827</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.570592769098327</v>
+        <v>-1.570592769098333</v>
       </c>
       <c r="AQ419" t="n">
         <v>17.8297199638663</v>
@@ -68735,10 +68735,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.097145375663951</v>
+        <v>7.097145375663948</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2729452223131208</v>
+        <v>-0.2729452223131181</v>
       </c>
       <c r="AK420" t="n">
         <v>7.093828611034739</v>
@@ -68747,16 +68747,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.08945254406056438</v>
+        <v>0.08945254406056392</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.004001520125414798</v>
+        <v>0.004001520125414807</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.02385555423225116</v>
+        <v>0.02385555423225172</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.536594443203972</v>
+        <v>-1.536594443203949</v>
       </c>
       <c r="AQ420" t="n">
         <v>22.01152630600483</v>
@@ -68900,10 +68900,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.088227962421951</v>
+        <v>7.088227962421954</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.262227748798904</v>
+        <v>-0.2622277487989066</v>
       </c>
       <c r="AK421" t="n">
         <v>7.092951699003613</v>
@@ -68912,16 +68912,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.07912491692886899</v>
+        <v>0.07912491692886864</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.003813743757049903</v>
+        <v>0.003813743757049957</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.01902803623666316</v>
+        <v>0.01902803623666371</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.402662234957516</v>
+        <v>-1.402662234957552</v>
       </c>
       <c r="AQ421" t="n">
         <v>34.95077872465472</v>
@@ -69065,10 +69065,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.082675656384673</v>
+        <v>7.082675656384675</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2467758265201709</v>
+        <v>-0.2467758265201727</v>
       </c>
       <c r="AK422" t="n">
         <v>7.085940899278786</v>
@@ -69077,16 +69077,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.07019093860911668</v>
+        <v>0.07019093860911679</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.003788844982403339</v>
+        <v>0.003788844982403293</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.01530727852465064</v>
+        <v>0.0153072785246503</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.219255624926024</v>
+        <v>-1.219255624926049</v>
       </c>
       <c r="AQ422" t="n">
         <v>32.91054255126112</v>
@@ -69230,10 +69230,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.082585232341567</v>
+        <v>7.082585232341569</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2597850728872215</v>
+        <v>-0.2597850728872233</v>
       </c>
       <c r="AK423" t="n">
         <v>7.080231185021037</v>
@@ -69242,16 +69242,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.0607230145131474</v>
+        <v>0.06072301451314636</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.003218097337044118</v>
+        <v>0.003218097337044184</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.01127031184523342</v>
+        <v>0.01127031184523331</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.354123018284604</v>
+        <v>-1.354123018284628</v>
       </c>
       <c r="AQ423" t="n">
         <v>33.01778542742398</v>
@@ -69395,10 +69395,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.082752176397555</v>
+        <v>7.082752176397554</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2453522168333464</v>
+        <v>-0.2453522168333455</v>
       </c>
       <c r="AK424" t="n">
         <v>7.078545045220129</v>
@@ -69407,16 +69407,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.04987769893955558</v>
+        <v>0.04987769893955601</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.002647769861786137</v>
+        <v>0.002647769861786034</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.00755590738572276</v>
+        <v>0.007555907385723093</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.183549452314946</v>
+        <v>-1.183549452314941</v>
       </c>
       <c r="AQ424" t="n">
         <v>34.60652659178685</v>
@@ -69560,10 +69560,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI425" t="n">
-        <v>7.073418742129174</v>
+        <v>7.073418742129173</v>
       </c>
       <c r="AJ425" t="n">
-        <v>-0.2359186467617427</v>
+        <v>-0.2359186467617418</v>
       </c>
       <c r="AK425" t="n">
         <v>7.075576762908686</v>
@@ -69572,16 +69572,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.03723342047483359</v>
+        <v>0.03723342047483347</v>
       </c>
       <c r="AN425" t="n">
-        <v>0.0007434096776329363</v>
+        <v>0.0007434096776329864</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.003691827899839573</v>
+        <v>0.003691827899840794</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.070919300606854</v>
+        <v>-1.070919300606848</v>
       </c>
       <c r="AQ425" t="n">
         <v>37.07633053221289</v>
@@ -69737,16 +69737,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM426" t="n">
-        <v>0.02391394499985428</v>
+        <v>0.02391394499985489</v>
       </c>
       <c r="AN426" t="n">
-        <v>0.0004638728584110997</v>
+        <v>0.0004638728584110585</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.00150427765126282</v>
+        <v>0.001504277651263042</v>
       </c>
       <c r="AP426" t="n">
-        <v>-1.11050563204875</v>
+        <v>-1.110505632048755</v>
       </c>
       <c r="AQ426" t="n">
         <v>34.78667081905948</v>
@@ -69890,10 +69890,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI427" t="n">
-        <v>7.061175551975939</v>
+        <v>7.06117555197594</v>
       </c>
       <c r="AJ427" t="n">
-        <v>-0.2336756854903435</v>
+        <v>-0.2336756854903443</v>
       </c>
       <c r="AK427" t="n">
         <v>7.061105294515807</v>
@@ -69902,16 +69902,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM427" t="n">
-        <v>0.01023096587809661</v>
+        <v>0.01023096587809607</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.0001641525470544823</v>
+        <v>-0.0001641525470544615</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.0002530929795961923</v>
+        <v>0.000253092979595082</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.032242914660647</v>
+        <v>-1.032242914660661</v>
       </c>
       <c r="AQ427" t="n">
         <v>39.87004103967168</v>
@@ -70067,16 +70067,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.001349940557734956</v>
+        <v>-0.001349940557734529</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.001242569541730382</v>
+        <v>-0.001242569541730301</v>
       </c>
       <c r="AO428" t="n">
-        <v>9.828375502929365e-05</v>
+        <v>9.828375502973774e-05</v>
       </c>
       <c r="AP428" t="n">
-        <v>-0.9364901210219889</v>
+        <v>-0.9364901210219928</v>
       </c>
       <c r="AQ428" t="n">
         <v>40.21566440185241</v>
@@ -70220,10 +70220,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.051845784111939</v>
+        <v>7.051845784111937</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2217457246026617</v>
+        <v>-0.22174572460266</v>
       </c>
       <c r="AK429" t="n">
         <v>7.04924004450221</v>
@@ -70232,16 +70232,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.01245927794565087</v>
+        <v>-0.0124592779456514</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.002690846636687106</v>
+        <v>-0.002690846636687166</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.0009149443224345521</v>
+        <v>0.000914944322433886</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.8888893481318413</v>
+        <v>-0.8888893481318249</v>
       </c>
       <c r="AQ429" t="n">
         <v>37.07230686982091</v>
@@ -70385,10 +70385,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.044932512363691</v>
+        <v>7.044932512363692</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.2339326420633983</v>
+        <v>-0.2339326420633991</v>
       </c>
       <c r="AK430" t="n">
         <v>7.044607485549974</v>
@@ -70397,16 +70397,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.02351974718911197</v>
+        <v>-0.0235197471891116</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.003286981705062079</v>
+        <v>-0.003286981705062081</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.002235402288773947</v>
+        <v>0.002235402288773058</v>
       </c>
       <c r="AP430" t="n">
-        <v>-1.019515488213925</v>
+        <v>-1.019515488213939</v>
       </c>
       <c r="AQ430" t="n">
         <v>35.1345995045417</v>
@@ -70550,10 +70550,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.041380724566422</v>
+        <v>7.04138072456642</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2399805399350745</v>
+        <v>-0.2399805399350727</v>
       </c>
       <c r="AK431" t="n">
         <v>7.036677431055121</v>
@@ -70562,16 +70562,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.03604973348542533</v>
+        <v>-0.03604973348542571</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003896888881646653</v>
+        <v>-0.003896888881646666</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.004508577134016534</v>
+        <v>0.004508577134016423</v>
       </c>
       <c r="AP431" t="n">
-        <v>-1.080586188982384</v>
+        <v>-1.080586188982368</v>
       </c>
       <c r="AQ431" t="n">
         <v>27.75274294670847</v>
@@ -70715,10 +70715,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.031781164871437</v>
+        <v>7.031781164871438</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2312812487947769</v>
+        <v>-0.2312812487947777</v>
       </c>
       <c r="AK432" t="n">
         <v>7.031531243279009</v>
@@ -70727,16 +70727,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.0496421115884523</v>
+        <v>-0.04964211158845258</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003622848094475932</v>
+        <v>-0.003622848094475877</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.007358432861332531</v>
+        <v>0.007358432861333086</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.9776792404870553</v>
+        <v>-0.9776792404870693</v>
       </c>
       <c r="AQ432" t="n">
         <v>35.29620661824052</v>
@@ -70892,16 +70892,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.06336633742876464</v>
+        <v>-0.06336633742876532</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.00383222203166729</v>
+        <v>-0.003832222031667326</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.0113935335626284</v>
+        <v>0.01139353356262962</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.9077068786391019</v>
+        <v>-0.9077068786391058</v>
       </c>
       <c r="AQ433" t="n">
         <v>35.93909601634321</v>
@@ -71045,10 +71045,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI434" t="n">
-        <v>7.012358254068223</v>
+        <v>7.012358254068221</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.220358437173692</v>
+        <v>-0.2203584371736902</v>
       </c>
       <c r="AK434" t="n">
         <v>7.010266108789461</v>
@@ -71057,16 +71057,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.07815930192347351</v>
+        <v>-0.07815930192347212</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.0037302018478894</v>
+        <v>-0.003730201847889384</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.01669360800688513</v>
+        <v>0.01669360800688602</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.8464978886523586</v>
+        <v>-0.8464978886523424</v>
       </c>
       <c r="AQ434" t="n">
         <v>35.15923365842881</v>
@@ -71210,10 +71210,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI435" t="n">
-        <v>7.001516536947593</v>
+        <v>7.001516536947591</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.2107164423431005</v>
+        <v>-0.2107164423430987</v>
       </c>
       <c r="AK435" t="n">
         <v>7.003692382618654</v>
@@ -71222,16 +71222,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.09225745624393369</v>
+        <v>-0.09225745624393285</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.003729646461095512</v>
+        <v>-0.003729646461095566</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.02283737241168637</v>
+        <v>0.02283737241168682</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.7351651051066752</v>
+        <v>-0.7351651051066588</v>
       </c>
       <c r="AQ435" t="n">
         <v>39.72846441947566</v>
@@ -71375,10 +71375,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI436" t="n">
-        <v>6.98285303226683</v>
+        <v>6.982853032266831</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.1977530490514976</v>
+        <v>-0.1977530490514985</v>
       </c>
       <c r="AK436" t="n">
         <v>6.994908837140057</v>
@@ -71387,16 +71387,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.1040956648961724</v>
+        <v>-0.1040956648961739</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.004775368000139335</v>
+        <v>-0.004775368000139281</v>
       </c>
       <c r="AO436" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.5873560645130924</v>
+        <v>-0.5873560645131055</v>
       </c>
       <c r="AQ436" t="n">
         <v>40.89169418809222</v>
@@ -71540,10 +71540,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.976537964100197</v>
+        <v>6.976537964100195</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1673381540721204</v>
+        <v>-0.1673381540721186</v>
       </c>
       <c r="AK437" t="n">
         <v>6.976048621620001</v>
@@ -71552,16 +71552,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1171809788132883</v>
+        <v>-0.1171809788132892</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.006568629287185546</v>
+        <v>-0.006568629287185491</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.03914952746580425</v>
+        <v>0.03914952746580436</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.244365528744401</v>
+        <v>-0.2443655287443834</v>
       </c>
       <c r="AQ437" t="n">
         <v>48.68742368742369</v>
@@ -71708,7 +71708,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1582257113591101</v>
+        <v>-0.1582257113591092</v>
       </c>
       <c r="AK438" t="n">
         <v>6.970728111892008</v>
@@ -71717,16 +71717,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.127636816539944</v>
+        <v>-0.127636816539943</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.007451019732577668</v>
+        <v>-0.00745101973257774</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.04750067483060583</v>
+        <v>0.04750067483060572</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.1411566897223107</v>
+        <v>-0.1411566897223032</v>
       </c>
       <c r="AQ438" t="n">
         <v>49.78866648552365</v>
@@ -71885,13 +71885,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.008628156625160088</v>
+        <v>-0.008628156625160163</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.05751510742764043</v>
+        <v>0.05751510742764121</v>
       </c>
       <c r="AP439" t="n">
-        <v>-0.02985731997459472</v>
+        <v>-0.02985731997459668</v>
       </c>
       <c r="AQ439" t="n">
         <v>51.95891065456283</v>
@@ -72035,10 +72035,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.950644730799358</v>
+        <v>6.950644730799363</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1501448147226974</v>
+        <v>-0.1501448147227027</v>
       </c>
       <c r="AK440" t="n">
         <v>6.959853578800648</v>
@@ -72047,16 +72047,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1469566450661546</v>
+        <v>-0.1469566450661556</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.009026348114251986</v>
+        <v>-0.009026348114251901</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.06603756167960417</v>
+        <v>0.06603756167960351</v>
       </c>
       <c r="AP440" t="n">
-        <v>-0.04957227832841285</v>
+        <v>-0.04957227832847518</v>
       </c>
       <c r="AQ440" t="n">
         <v>49.76960567124502</v>
@@ -72200,28 +72200,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.934622414140156</v>
+        <v>6.934622414140152</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1321226430219919</v>
+        <v>-0.1321226430219875</v>
       </c>
       <c r="AK441" t="n">
-        <v>6.94711441643572</v>
+        <v>6.947114416435721</v>
       </c>
       <c r="AL441" t="n">
-        <v>-0.1446146453175556</v>
+        <v>-0.1446146453175565</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1568781652619925</v>
+        <v>-0.1568781652619921</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.010042871337475</v>
+        <v>-0.01004287133747513</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.07699206242755485</v>
+        <v>0.07699206242755419</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.1550111672272632</v>
+        <v>0.1550111672273127</v>
       </c>
       <c r="AQ441" t="n">
         <v>58.94401589527817</v>
@@ -72365,10 +72365,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.928042396530076</v>
+        <v>6.928042396530073</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1335425224150857</v>
+        <v>-0.133542522415083</v>
       </c>
       <c r="AK442" t="n">
         <v>6.933186989735641</v>
@@ -72377,16 +72377,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1650917115670576</v>
+        <v>-0.1650917115670582</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.0106149464753251</v>
+        <v>-0.01061494647532512</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.08732871254562191</v>
+        <v>0.08732871254562202</v>
       </c>
       <c r="AP442" t="n">
-        <v>0.1384398386498393</v>
+        <v>0.1384398386498683</v>
       </c>
       <c r="AQ442" t="n">
         <v>55.65399624223154</v>
@@ -72530,10 +72530,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.941461393298105</v>
+        <v>6.941461393298106</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1469615191831144</v>
+        <v>-0.1469615191831153</v>
       </c>
       <c r="AK443" t="n">
         <v>6.925995477801935</v>
@@ -72542,16 +72542,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.1745447047691483</v>
+        <v>-0.1745447047691478</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01108963812755723</v>
+        <v>-0.01108963812755724</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.09935205695041804</v>
+        <v>0.09935205695041927</v>
       </c>
       <c r="AP443" t="n">
-        <v>-0.01497644213845123</v>
+        <v>-0.01497644213846336</v>
       </c>
       <c r="AQ443" t="n">
         <v>49.22214596202242</v>
@@ -72695,10 +72695,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.93323210397643</v>
+        <v>6.933232103976423</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1472323290435682</v>
+        <v>-0.147232329043562</v>
       </c>
       <c r="AK444" t="n">
         <v>6.938996539173566</v>
@@ -72707,16 +72707,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.1853013335308036</v>
+        <v>-0.1853013335308053</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01193987645426134</v>
+        <v>-0.01193987645426136</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1123648810347069</v>
+        <v>0.1123648810347067</v>
       </c>
       <c r="AP444" t="n">
-        <v>-0.01803400433169996</v>
+        <v>-0.01803400433163076</v>
       </c>
       <c r="AQ444" t="n">
         <v>44.95232436408907</v>
@@ -72860,10 +72860,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.928429644379657</v>
+        <v>6.928429644379658</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1496296336985043</v>
+        <v>-0.1496296336985061</v>
       </c>
       <c r="AK445" t="n">
         <v>6.93160690101155</v>
@@ -72875,13 +72875,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01257308415669778</v>
+        <v>-0.01257308415669775</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.125857898472412</v>
+        <v>0.1258578984724115</v>
       </c>
       <c r="AP445" t="n">
-        <v>-0.04547613693365601</v>
+        <v>-0.04547613693367852</v>
       </c>
       <c r="AQ445" t="n">
         <v>45.25195968645016</v>
@@ -73025,10 +73025,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.925068850639515</v>
+        <v>6.925068850639512</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1455688430101203</v>
+        <v>-0.1455688430101176</v>
       </c>
       <c r="AK446" t="n">
         <v>6.924763510572069</v>
@@ -73037,16 +73037,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM446" t="n">
-        <v>-0.2060805417157788</v>
+        <v>-0.2060805417157789</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01318646791849926</v>
+        <v>-0.01318646791849928</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1396251026736655</v>
+        <v>0.1396251026736647</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.001331178123722838</v>
+        <v>0.001331178123751393</v>
       </c>
       <c r="AQ446" t="n">
         <v>48.95703482090916</v>
@@ -73190,10 +73190,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.900929863197374</v>
+        <v>6.900929863197373</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1347297975845807</v>
+        <v>-0.1347297975845798</v>
       </c>
       <c r="AK447" t="n">
         <v>6.921049732547429</v>
@@ -73202,16 +73202,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2151279705591488</v>
+        <v>-0.2151279705591481</v>
       </c>
       <c r="AN447" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1518365696223548</v>
+        <v>0.1518365696223549</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.1262747588338355</v>
+        <v>0.1262747588338435</v>
       </c>
       <c r="AQ447" t="n">
         <v>49.97532894736842</v>
@@ -73355,10 +73355,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.895219010181459</v>
+        <v>6.89521901018146</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1302191436958635</v>
+        <v>-0.1302191436958644</v>
       </c>
       <c r="AK448" t="n">
         <v>6.89978353884127</v>
@@ -73370,13 +73370,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01278923357027009</v>
+        <v>-0.01278923357027006</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1644177475946104</v>
+        <v>0.1644177475946105</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.1780680365315467</v>
+        <v>0.1780680365315346</v>
       </c>
       <c r="AQ448" t="n">
         <v>47.61278246480211</v>
@@ -73520,10 +73520,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.879512239848579</v>
+        <v>6.87951223984858</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.1173123611559523</v>
+        <v>-0.1173123611559532</v>
       </c>
       <c r="AK449" t="n">
         <v>6.893260360395011</v>
@@ -73532,16 +73532,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.233692768734329</v>
+        <v>-0.233692768734328</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01245257184765153</v>
+        <v>-0.01245257184765156</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.179129523332087</v>
+        <v>0.1791295233320875</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.3270752588397787</v>
+        <v>0.3270752588397669</v>
       </c>
       <c r="AQ449" t="n">
         <v>51.00408075601375</v>
@@ -73685,10 +73685,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.882426232260446</v>
+        <v>6.882426232260437</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.1132263840853973</v>
+        <v>-0.1132263840853884</v>
       </c>
       <c r="AK450" t="n">
         <v>6.880758546638964</v>
@@ -73697,16 +73697,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.2433281856134891</v>
+        <v>-0.2433281856134888</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01202813951384066</v>
+        <v>-0.01202813951384067</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.1944608722019401</v>
+        <v>0.1944608722019407</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.3735609578737231</v>
+        <v>0.3735609578738251</v>
       </c>
       <c r="AQ450" t="n">
         <v>52.54948850803774</v>
@@ -73862,16 +73862,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2520264427810588</v>
+        <v>-0.25202644278106</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01246671652825437</v>
+        <v>-0.01246671652825434</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.2101991144027906</v>
+        <v>0.2101991144027905</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.9396869993792598</v>
+        <v>0.939686999379259</v>
       </c>
       <c r="AQ451" t="n">
         <v>65.32979171049863</v>
@@ -74015,10 +74015,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.841963898035317</v>
+        <v>6.841963898035326</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.07646382937076623</v>
+        <v>-0.07646382937077512</v>
       </c>
       <c r="AK452" t="n">
         <v>6.844785316397215</v>
@@ -74027,16 +74027,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2592973891940562</v>
+        <v>-0.2592973891940566</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01305068899435097</v>
+        <v>-0.01305068899435077</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2277185089957531</v>
+        <v>0.2277185089957524</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.7946882605952149</v>
+        <v>0.794688260595111</v>
       </c>
       <c r="AQ452" t="n">
         <v>58.60471170115841</v>
@@ -74180,28 +74180,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.845644916883085</v>
+        <v>6.845644916883079</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.08014484821853429</v>
+        <v>-0.08014484821852808</v>
       </c>
       <c r="AK453" t="n">
-        <v>6.849407886968131</v>
+        <v>6.849407886968132</v>
       </c>
       <c r="AL453" t="n">
-        <v>-0.08390781830358041</v>
+        <v>-0.08390781830358129</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.2668003223256257</v>
+        <v>-0.2668003223256254</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01367989020054944</v>
+        <v>-0.0136798902005495</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2456601220977563</v>
+        <v>0.2456601220977566</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7487140043297179</v>
+        <v>0.7487140043297899</v>
       </c>
       <c r="AQ453" t="n">
         <v>58.31271902700475</v>
@@ -74345,10 +74345,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.842084108625032</v>
+        <v>6.842084108625038</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.0695840704780597</v>
+        <v>-0.06958407047806503</v>
       </c>
       <c r="AK454" t="n">
         <v>6.852702018840203</v>
@@ -74357,16 +74357,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2735436467318143</v>
+        <v>-0.273543646731814</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.01403412282467997</v>
+        <v>-0.01403412282467991</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.2619835102172253</v>
+        <v>0.261983510217226</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.8683972750773455</v>
+        <v>0.8683972750772836</v>
       </c>
       <c r="AQ454" t="n">
         <v>63.58441955972757</v>
@@ -74510,10 +74510,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.863831060847773</v>
+        <v>6.863831060847785</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.09133102270080062</v>
+        <v>-0.09133102270081217</v>
       </c>
       <c r="AK455" t="n">
         <v>6.850973969550408</v>
@@ -74522,16 +74522,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.2787367835501612</v>
+        <v>-0.2787367835501617</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01406387644726603</v>
+        <v>-0.01406387644726588</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.2758112468611987</v>
+        <v>0.2758112468611976</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.6117510238643564</v>
+        <v>0.6117510238642219</v>
       </c>
       <c r="AQ455" t="n">
         <v>62.5530303030303</v>
@@ -74675,10 +74675,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.853037915615571</v>
+        <v>6.853037915615573</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.07753809490634289</v>
+        <v>-0.07753809490634467</v>
       </c>
       <c r="AK456" t="n">
         <v>6.873527983489108</v>
@@ -74690,13 +74690,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.013790177185657</v>
+        <v>-0.01379017718565697</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.285442546377481</v>
+        <v>0.2854425463774817</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.7703772441622895</v>
+        <v>0.7703772441622695</v>
       </c>
       <c r="AQ456" t="n">
         <v>68.73796844921122</v>
@@ -74852,7 +74852,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2865252693972544</v>
+        <v>-0.2865252693972545</v>
       </c>
       <c r="AN457" t="n">
         <v>-0.01327380582108439</v>
@@ -74861,7 +74861,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP457" t="n">
-        <v>0.5720048978375456</v>
+        <v>0.5720048978375459</v>
       </c>
       <c r="AQ457" t="n">
         <v>61.93811881188119</v>
@@ -75005,10 +75005,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.860047631936786</v>
+        <v>6.860047631936787</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.1030476624543644</v>
+        <v>-0.1030476624543653</v>
       </c>
       <c r="AK458" t="n">
         <v>6.865985861260643</v>
@@ -75017,16 +75017,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.290522309347949</v>
+        <v>-0.2905223093479492</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.01240158194086383</v>
+        <v>-0.01240158194086378</v>
       </c>
       <c r="AO458" t="n">
-        <v>0.3024992257449916</v>
+        <v>0.3024992257449914</v>
       </c>
       <c r="AP458" t="n">
-        <v>0.4675645678050873</v>
+        <v>0.4675645678050772</v>
       </c>
       <c r="AQ458" t="n">
         <v>58.16851702080729</v>
@@ -75170,10 +75170,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.801980414635013</v>
+        <v>6.801980414635016</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.04478065038330392</v>
+        <v>-0.04478065038330659</v>
       </c>
       <c r="AK459" t="n">
         <v>6.863576603094304</v>
@@ -75182,16 +75182,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.2950697019949103</v>
+        <v>-0.2950697019949104</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.0116105331596838</v>
+        <v>-0.01161053315968381</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3113800696686924</v>
+        <v>0.3113800696686918</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.14722151151879</v>
+        <v>1.147221511518761</v>
       </c>
       <c r="AQ459" t="n">
         <v>79.24917491749174</v>
@@ -75335,10 +75335,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.789283666813423</v>
+        <v>6.789283666813422</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.03208390256171434</v>
+        <v>-0.03208390256171256</v>
       </c>
       <c r="AK460" t="n">
         <v>6.809671190627447</v>
@@ -75347,16 +75347,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.2987092362344105</v>
+        <v>-0.2987092362344108</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.01030385953714813</v>
+        <v>-0.01030385953714808</v>
       </c>
       <c r="AO460" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.28818749803842</v>
+        <v>1.288187498038444</v>
       </c>
       <c r="AQ460" t="n">
         <v>82.03652529136127</v>
@@ -75500,10 +75500,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.789252537988938</v>
+        <v>6.789252537988933</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.02065255095890883</v>
+        <v>-0.0206525509589035</v>
       </c>
       <c r="AK461" t="n">
         <v>6.802840448144932</v>
@@ -75512,16 +75512,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3027504956929287</v>
+        <v>-0.3027504956929284</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.00881278602540958</v>
+        <v>-0.008812786025409641</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.332227117067963</v>
+        <v>0.3322271170679635</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.412097260525123</v>
+        <v>1.412097260525188</v>
       </c>
       <c r="AQ461" t="n">
         <v>83.09775366457262</v>
@@ -75665,10 +75665,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.774001672255927</v>
+        <v>6.774001672255932</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.005401685225897346</v>
+        <v>-0.005401685225902675</v>
       </c>
       <c r="AK462" t="n">
         <v>6.800260207803535</v>
@@ -75677,16 +75677,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3068099364477369</v>
+        <v>-0.3068099364477367</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.007070247176567734</v>
+        <v>-0.007070247176567688</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.3427146952658529</v>
+        <v>0.3427146952658534</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.577343453912065</v>
+        <v>1.577343453912008</v>
       </c>
       <c r="AQ462" t="n">
         <v>83.90243902439025</v>
@@ -75830,10 +75830,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.802628307046305</v>
+        <v>6.802628307046303</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.0281284138578286</v>
+        <v>-0.02812841385782594</v>
       </c>
       <c r="AK463" t="n">
         <v>6.781970485204615</v>
@@ -75842,16 +75842,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3121566752204096</v>
+        <v>-0.3121566752204101</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.005102880740085192</v>
+        <v>-0.005102880740085154</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3560731605465752</v>
+        <v>0.3560731605465757</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.303420740488044</v>
+        <v>1.303420740488078</v>
       </c>
       <c r="AQ463" t="n">
         <v>79.87303958177745</v>
@@ -75995,28 +75995,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.815944895083629</v>
+        <v>6.815944895083632</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.0259449332306021</v>
+        <v>-0.02594493323060476</v>
       </c>
       <c r="AK464" t="n">
-        <v>6.809638458820509</v>
+        <v>6.809638458820508</v>
       </c>
       <c r="AL464" t="n">
-        <v>-0.01963849696748188</v>
+        <v>-0.01963849696748099</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3181413841564625</v>
+        <v>-0.3181413841564619</v>
       </c>
       <c r="AN464" t="n">
-        <v>-0.003317316385138602</v>
+        <v>-0.003317316385138562</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.3690689225934927</v>
+        <v>0.3690689225934922</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.320112988335384</v>
+        <v>1.320112988335356</v>
       </c>
       <c r="AQ464" t="n">
         <v>81.66100362896702</v>
@@ -76160,10 +76160,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.821941449304759</v>
+        <v>6.821941449304753</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.0319414874517312</v>
+        <v>-0.03194148745172587</v>
       </c>
       <c r="AK465" t="n">
         <v>6.819973703544699</v>
@@ -76172,16 +76172,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3244228225822193</v>
+        <v>-0.3244228225822198</v>
       </c>
       <c r="AN465" t="n">
-        <v>-0.001700148658338674</v>
+        <v>-0.001700148658338742</v>
       </c>
       <c r="AO465" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.242734811900659</v>
+        <v>1.242734811900723</v>
       </c>
       <c r="AQ465" t="n">
         <v>78.39056776556777</v>
@@ -76325,10 +76325,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.826413262727742</v>
+        <v>6.826413262727749</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.03641330087471495</v>
+        <v>-0.03641330087472205</v>
       </c>
       <c r="AK466" t="n">
         <v>6.822087900644207</v>
@@ -76337,16 +76337,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3308797299382499</v>
+        <v>-0.3308797299382495</v>
       </c>
       <c r="AN466" t="n">
-        <v>-7.481797733216444e-05</v>
+        <v>-7.481797733213274e-05</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.3960788710418811</v>
+        <v>0.396078871041881</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.18397024508706</v>
+        <v>1.183970245086981</v>
       </c>
       <c r="AQ466" t="n">
         <v>78.98365042291209</v>
@@ -76490,10 +76490,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.812656647679548</v>
+        <v>6.81265664767955</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.01465678882334664</v>
+        <v>-0.01465678882334931</v>
       </c>
       <c r="AK467" t="n">
         <v>6.823881638371397</v>
@@ -76502,16 +76502,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3363418922753055</v>
+        <v>-0.3363418922753058</v>
       </c>
       <c r="AN467" t="n">
-        <v>0.001379920606120022</v>
+        <v>0.001379920606120097</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4081029523904164</v>
+        <v>0.4081029523904167</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.426200199707695</v>
+        <v>1.426200199707669</v>
       </c>
       <c r="AQ467" t="n">
         <v>83.57816711590297</v>
@@ -76655,10 +76655,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.802797817425507</v>
+        <v>6.802797817425505</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.009197735028045884</v>
+        <v>-0.009197735028044107</v>
       </c>
       <c r="AK468" t="n">
         <v>6.808320681191073</v>
@@ -76667,16 +76667,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3410659803634685</v>
+        <v>-0.3410659803634682</v>
       </c>
       <c r="AN468" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4198133218741356</v>
+        <v>0.4198133218741357</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.478216789207188</v>
+        <v>1.478216789207213</v>
       </c>
       <c r="AQ468" t="n">
         <v>83.65373918074005</v>
@@ -76826,22 +76826,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK469" t="n">
-        <v>6.795980661778267</v>
+        <v>6.795980661778266</v>
       </c>
       <c r="AL469" t="n">
-        <v>-0.002380579380806047</v>
+        <v>-0.002380579380805159</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3461577281601511</v>
+        <v>-0.3461577281601509</v>
       </c>
       <c r="AN469" t="n">
-        <v>0.004282887883574671</v>
+        <v>0.00428288788357468</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4328049372030962</v>
+        <v>0.4328049372030969</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.539467082609258</v>
+        <v>1.539467082609263</v>
       </c>
       <c r="AQ469" t="n">
         <v>84.90566037735849</v>
@@ -76985,10 +76985,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.800189882196235</v>
+        <v>6.800189882196236</v>
       </c>
       <c r="AJ470" t="n">
-        <v>-0.005989938653754301</v>
+        <v>-0.005989938653755189</v>
       </c>
       <c r="AK470" t="n">
         <v>6.78726841810145</v>
@@ -76997,16 +76997,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3502903933401412</v>
+        <v>-0.3502903933401418</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.005405808652032051</v>
+        <v>0.005405808652032067</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4450018361960529</v>
+        <v>0.4450018361960534</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.491748497297388</v>
+        <v>1.491748497297383</v>
       </c>
       <c r="AQ470" t="n">
         <v>83.80718419041381</v>
@@ -77150,10 +77150,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.79797208364255</v>
+        <v>6.797972083642554</v>
       </c>
       <c r="AJ471" t="n">
-        <v>-0.009372115686007376</v>
+        <v>-0.009372115686010929</v>
       </c>
       <c r="AK471" t="n">
         <v>6.791305278184372</v>
@@ -77162,16 +77162,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3548656112706069</v>
+        <v>-0.3548656112706071</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.006091291211178074</v>
+        <v>0.006091291211178139</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4593697101544711</v>
+        <v>0.4593697101544705</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.442519142421117</v>
+        <v>1.442519142421081</v>
       </c>
       <c r="AQ471" t="n">
         <v>82.48745240567671</v>
@@ -77315,10 +77315,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.800452644405181</v>
+        <v>6.800452644405178</v>
       </c>
       <c r="AJ472" t="n">
-        <v>-0.01185267644863774</v>
+        <v>-0.01185267644863508</v>
       </c>
       <c r="AK472" t="n">
         <v>6.789098969069376</v>
@@ -77333,10 +77333,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4721687943484544</v>
+        <v>0.4721687943484545</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.404392199013741</v>
+        <v>1.404392199013776</v>
       </c>
       <c r="AQ472" t="n">
         <v>79.31518593934199</v>
@@ -77480,10 +77480,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.778720347685821</v>
+        <v>6.778720347685814</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.01707986135958883</v>
+        <v>0.01707986135959594</v>
       </c>
       <c r="AK473" t="n">
         <v>6.790465135395929</v>
@@ -77492,16 +77492,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3625273381377937</v>
+        <v>-0.3625273381377933</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.007343464385960674</v>
+        <v>0.007343464385960585</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.4863203622043377</v>
+        <v>0.4863203622043382</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.718967726687749</v>
+        <v>1.718967726687834</v>
       </c>
       <c r="AQ473" t="n">
         <v>84.49074074074073</v>
@@ -77645,10 +77645,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.769755998762547</v>
+        <v>6.769755998762545</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.02364381202846833</v>
+        <v>0.02364381202847099</v>
       </c>
       <c r="AK474" t="n">
         <v>6.767889899932765</v>
@@ -77657,16 +77657,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3660007866474812</v>
+        <v>-0.3660007866474813</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.00826013782295415</v>
+        <v>0.008260137822954145</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.4997690914082398</v>
+        <v>0.4997690914082401</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.776447733059097</v>
+        <v>1.776447733059131</v>
       </c>
       <c r="AQ474" t="n">
         <v>85.25345622119815</v>
@@ -77810,10 +77810,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.789177604754239</v>
+        <v>6.789177604754244</v>
       </c>
       <c r="AJ475" t="n">
-        <v>0.01332216636392491</v>
+        <v>0.01332216636391959</v>
       </c>
       <c r="AK475" t="n">
         <v>6.759766754404358</v>
@@ -77822,16 +77822,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3700034659576358</v>
+        <v>-0.3700034659576351</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.00987171553454691</v>
+        <v>0.009871715534546958</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.5120623436103316</v>
+        <v>0.5120623436103324</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.645621086027352</v>
+        <v>1.645621086027296</v>
       </c>
       <c r="AQ475" t="n">
         <v>85.32527105921602</v>
@@ -77975,10 +77975,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.774331376960423</v>
+        <v>6.774331376960425</v>
       </c>
       <c r="AJ476" t="n">
-        <v>0.01776857573733093</v>
+        <v>0.01776857573732915</v>
       </c>
       <c r="AK476" t="n">
         <v>6.777856240868369</v>
@@ -77987,16 +77987,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3750442390024145</v>
+        <v>-0.3750442390024147</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01196068662558775</v>
+        <v>0.01196068662558781</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5238651846176465</v>
+        <v>0.5238651846176463</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.680943449342473</v>
+        <v>1.680943449342458</v>
       </c>
       <c r="AQ476" t="n">
         <v>84.47695200314055</v>
@@ -78152,16 +78152,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3816350905604304</v>
+        <v>-0.3816350905604307</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01460798460929558</v>
+        <v>0.01460798460929556</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.537958310473289</v>
+        <v>0.5379583104732891</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.627209299316994</v>
+        <v>1.627209299316998</v>
       </c>
       <c r="AQ477" t="n">
         <v>85.00614250614251</v>
@@ -78305,10 +78305,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.789815280543246</v>
+        <v>6.789815280543245</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.01031527291385181</v>
+        <v>-0.01031527291385093</v>
       </c>
       <c r="AK478" t="n">
         <v>6.744939020214936</v>
@@ -78317,16 +78317,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3872393091179336</v>
+        <v>-0.3872393091179339</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01685992867552227</v>
+        <v>0.01685992867552231</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5511317941481411</v>
+        <v>0.5511317941481415</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.344782590346758</v>
+        <v>1.344782590346771</v>
       </c>
       <c r="AQ478" t="n">
         <v>82.60150559016293</v>
@@ -78470,10 +78470,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.801295181477315</v>
+        <v>6.801295181477309</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.03129520055080093</v>
+        <v>-0.0312952005507956</v>
       </c>
       <c r="AK479" t="n">
         <v>6.772636231606738</v>
@@ -78482,16 +78482,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.393020019860339</v>
+        <v>-0.3930200198603389</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01873686412955489</v>
+        <v>0.01873686412955481</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5644439393662184</v>
+        <v>0.5644439393662187</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.10520581121148</v>
+        <v>1.105205811211542</v>
       </c>
       <c r="AQ479" t="n">
         <v>76.84604247104247</v>
@@ -78635,10 +78635,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.791632066062363</v>
+        <v>6.791632066062364</v>
       </c>
       <c r="AJ480" t="n">
-        <v>-0.0234321454080666</v>
+        <v>-0.02343214540806748</v>
       </c>
       <c r="AK480" t="n">
         <v>6.788619247652995</v>
@@ -78647,16 +78647,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3966294116439325</v>
+        <v>-0.3966294116439323</v>
       </c>
       <c r="AN480" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.576974471973372</v>
+        <v>0.5769744719733717</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.186476859823366</v>
+        <v>1.186476859823359</v>
       </c>
       <c r="AQ480" t="n">
         <v>74.69955156950672</v>
@@ -78800,10 +78800,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.779898505875916</v>
+        <v>6.779898505875918</v>
       </c>
       <c r="AJ481" t="n">
-        <v>-0.007398467728943814</v>
+        <v>-0.00739846772894559</v>
       </c>
       <c r="AK481" t="n">
         <v>6.776305653888958</v>
@@ -78812,16 +78812,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3980313152890726</v>
+        <v>-0.3980313152890724</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01933124704228378</v>
+        <v>0.0193312470422838</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.5877384296086169</v>
+        <v>0.5877384296086161</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.356475842636204</v>
+        <v>1.356475842636188</v>
       </c>
       <c r="AQ481" t="n">
         <v>76.57830278128949</v>
@@ -78965,10 +78965,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.771360892616113</v>
+        <v>6.771360892616116</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.001139145530859587</v>
+        <v>0.001139145530856922</v>
       </c>
       <c r="AK482" t="n">
         <v>6.76492936370744</v>
@@ -78977,16 +78977,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3979537985659305</v>
+        <v>-0.3979537985659302</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.0183584453609324</v>
+        <v>0.01835844536093246</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6001791687136281</v>
+        <v>0.6001791687136286</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.441515297066416</v>
+        <v>1.44151529706639</v>
       </c>
       <c r="AQ482" t="n">
         <v>77.56534508076359</v>
@@ -79130,10 +79130,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.751667781721844</v>
+        <v>6.751667781721842</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.02083225642512865</v>
+        <v>0.02083225642513042</v>
       </c>
       <c r="AK483" t="n">
         <v>6.753855191419989</v>
@@ -79142,16 +79142,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.3975762425746344</v>
+        <v>-0.3975762425746347</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01731206726614276</v>
+        <v>0.01731206726614282</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6129676701055393</v>
+        <v>0.6129676701055397</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.646360276993232</v>
+        <v>1.646360276993257</v>
       </c>
       <c r="AQ483" t="n">
         <v>82.96654246235056</v>
@@ -79295,10 +79295,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.729738669869288</v>
+        <v>6.72973866986929</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.03586153459848518</v>
+        <v>0.0358615345984834</v>
       </c>
       <c r="AK484" t="n">
         <v>6.736226026398153</v>
@@ -79307,16 +79307,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3964908591695859</v>
+        <v>-0.3964908591695858</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01740130648959376</v>
+        <v>0.01740130648959375</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6198907013195262</v>
+        <v>0.6198907013195265</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.795594927274907</v>
+        <v>1.795594927274892</v>
       </c>
       <c r="AQ484" t="n">
         <v>80.39647577092511</v>
@@ -79460,10 +79460,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.713320364291503</v>
+        <v>6.713320364291505</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.05917967385546952</v>
+        <v>0.05917967385546774</v>
       </c>
       <c r="AK485" t="n">
         <v>6.717723214958548</v>
@@ -79472,16 +79472,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.394760534481672</v>
+        <v>-0.3947605344816719</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01742962324324016</v>
+        <v>0.01742962324324019</v>
       </c>
       <c r="AO485" t="n">
-        <v>0.6272835381163622</v>
+        <v>0.6272835381163618</v>
       </c>
       <c r="AP485" t="n">
-        <v>2.028963267389809</v>
+        <v>2.028963267389796</v>
       </c>
       <c r="AQ485" t="n">
         <v>87.28070175438597</v>
@@ -79625,10 +79625,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.731179671396989</v>
+        <v>6.731179671396997</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.04132036674998396</v>
+        <v>0.04132036674997597</v>
       </c>
       <c r="AK486" t="n">
         <v>6.699415101064979</v>
@@ -79640,13 +79640,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.01766596732646103</v>
+        <v>0.0176659673264611</v>
       </c>
       <c r="AO486" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.816762279753399</v>
+        <v>1.816762279753319</v>
       </c>
       <c r="AQ486" t="n">
         <v>86.68311310232708</v>
@@ -79790,10 +79790,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.740946959621007</v>
+        <v>6.740946959621005</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.03085308157772371</v>
+        <v>0.03085308157772548</v>
       </c>
       <c r="AK487" t="n">
         <v>6.714685154719483</v>
@@ -79802,16 +79802,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.3929423394238508</v>
+        <v>-0.392942339423851</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.01842070378092631</v>
+        <v>0.0184207037809263</v>
       </c>
       <c r="AO487" t="n">
-        <v>0.640374511165978</v>
+        <v>0.6403745111659787</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.688819755019156</v>
+        <v>1.688819755019181</v>
       </c>
       <c r="AQ487" t="n">
         <v>84.57083958020989</v>
@@ -79955,10 +79955,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.7589577577717</v>
+        <v>6.758957757771704</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.006742105662137732</v>
+        <v>0.006742105662134179</v>
       </c>
       <c r="AK488" t="n">
         <v>6.722064699270507</v>
@@ -79967,16 +79967,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3931401656438959</v>
+        <v>-0.3931401656438955</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.01902711841846483</v>
+        <v>0.01902711841846487</v>
       </c>
       <c r="AO488" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.41867091232492</v>
+        <v>1.418670912324887</v>
       </c>
       <c r="AQ488" t="n">
         <v>80.32160972075135</v>
@@ -80120,10 +80120,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.763209774497792</v>
+        <v>6.763209774497788</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.007790133949473699</v>
+        <v>0.007790133949477251</v>
       </c>
       <c r="AK489" t="n">
         <v>6.739235851443908</v>
@@ -80132,16 +80132,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.3951733572725242</v>
+        <v>-0.3951733572725246</v>
       </c>
       <c r="AN489" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO489" t="n">
-        <v>0.6590798145480943</v>
+        <v>0.6590798145480942</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.420718764998806</v>
+        <v>1.420718764998849</v>
       </c>
       <c r="AQ489" t="n">
         <v>80.62186855290304</v>
@@ -80297,16 +80297,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3960001863323608</v>
+        <v>-0.396000186332361</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.02043272610569408</v>
+        <v>0.02043272610569401</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6685846444009622</v>
+        <v>0.6685846444009627</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.602984141316341</v>
+        <v>1.602984141316347</v>
       </c>
       <c r="AQ490" t="n">
         <v>81.12318509725139</v>
@@ -80450,10 +80450,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.714622134232894</v>
+        <v>6.714622134232888</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.04037798020802441</v>
+        <v>0.04037798020802974</v>
       </c>
       <c r="AK491" t="n">
         <v>6.746779913842831</v>
@@ -80462,16 +80462,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.396740905361911</v>
+        <v>-0.3967409053619114</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02120763540003751</v>
+        <v>0.02120763540003743</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.6777865296786982</v>
+        <v>0.6777865296786978</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.743725177744846</v>
+        <v>1.743725177744909</v>
       </c>
       <c r="AQ491" t="n">
         <v>83.76430537447487</v>
@@ -80615,28 +80615,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.731570059394423</v>
+        <v>6.73157005939442</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.01932973232310609</v>
+        <v>0.01932973232310964</v>
       </c>
       <c r="AK492" t="n">
-        <v>6.728823425344638</v>
+        <v>6.728823425344639</v>
       </c>
       <c r="AL492" t="n">
-        <v>0.02207636637289134</v>
+        <v>0.02207636637289045</v>
       </c>
       <c r="AM492" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.0220082962170377</v>
+        <v>0.02200829621703764</v>
       </c>
       <c r="AO492" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.508214089918481</v>
+        <v>1.508214089918522</v>
       </c>
       <c r="AQ492" t="n">
         <v>79.16330011670706</v>
@@ -80780,10 +80780,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.748064561399866</v>
+        <v>6.748064561399863</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.004235224214148126</v>
+        <v>0.00423522421415079</v>
       </c>
       <c r="AK493" t="n">
         <v>6.740096815166266</v>
@@ -80792,16 +80792,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.3976889317784199</v>
+        <v>-0.3976889317784196</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02268190844878654</v>
+        <v>0.02268190844878653</v>
       </c>
       <c r="AO493" t="n">
-        <v>0.6953567146475523</v>
+        <v>0.6953567146475526</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.339383633714908</v>
+        <v>1.339383633714939</v>
       </c>
       <c r="AQ493" t="n">
         <v>74.17924797037459</v>
@@ -80945,10 +80945,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.747226278872152</v>
+        <v>6.747226278872151</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.005973775296548745</v>
+        <v>0.005973775296550521</v>
       </c>
       <c r="AK494" t="n">
         <v>6.755554272205931</v>
@@ -80957,16 +80957,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4003515275861345</v>
+        <v>-0.400351527586135</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02398656672240618</v>
+        <v>0.02398656672240616</v>
       </c>
       <c r="AO494" t="n">
-        <v>0.7067969646460921</v>
+        <v>0.7067969646460924</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.34983246065289</v>
+        <v>1.349832460652912</v>
       </c>
       <c r="AQ494" t="n">
         <v>73.86614409547516</v>
@@ -81110,10 +81110,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.724989986752571</v>
+        <v>6.724989986752573</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.02471008267491914</v>
+        <v>0.02471008267491737</v>
       </c>
       <c r="AK495" t="n">
         <v>6.75925064743029</v>
@@ -81122,7 +81122,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.4017887258056133</v>
+        <v>-0.4017887258056131</v>
       </c>
       <c r="AN495" t="n">
         <v>0.02482212216928553</v>
@@ -81131,7 +81131,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.537934200391007</v>
+        <v>1.537934200390992</v>
       </c>
       <c r="AQ495" t="n">
         <v>77.32142857142857</v>
@@ -81275,28 +81275,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.738231277482312</v>
+        <v>6.738231277482303</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.01056852339049108</v>
+        <v>0.01056852339049996</v>
       </c>
       <c r="AK496" t="n">
-        <v>6.734775445902895</v>
+        <v>6.734775445902896</v>
       </c>
       <c r="AL496" t="n">
-        <v>0.01402435496990773</v>
+        <v>0.01402435496990684</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4022294042554291</v>
+        <v>-0.402229404255429</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02545790195722747</v>
+        <v>0.02545790195722734</v>
       </c>
       <c r="AO496" t="n">
-        <v>0.7273309315128231</v>
+        <v>0.7273309315128232</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.379757628265576</v>
+        <v>1.379757628265672</v>
       </c>
       <c r="AQ496" t="n">
         <v>74.71049844615358</v>
@@ -81440,10 +81440,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.718201282169581</v>
+        <v>6.718201282169575</v>
       </c>
       <c r="AJ497" t="n">
-        <v>0.02919852480673768</v>
+        <v>0.02919852480674301</v>
       </c>
       <c r="AK497" t="n">
         <v>6.753996132599221</v>
@@ -81452,16 +81452,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4027953816469058</v>
+        <v>-0.4027953816469059</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02608258444417638</v>
+        <v>0.02608258444417639</v>
       </c>
       <c r="AO497" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.565396263588755</v>
+        <v>1.565396263588813</v>
       </c>
       <c r="AQ497" t="n">
         <v>78.55027548209367</v>
@@ -81605,10 +81605,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.730898772467414</v>
+        <v>6.730898772467415</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.01650103450890406</v>
+        <v>0.01650103450890317</v>
       </c>
       <c r="AK498" t="n">
         <v>6.732394407262716</v>
@@ -81617,16 +81617,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4025099007694142</v>
+        <v>-0.402509900769414</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02634377330607651</v>
+        <v>0.02634377330607648</v>
       </c>
       <c r="AO498" t="n">
-        <v>0.746561519528266</v>
+        <v>0.7465615195282662</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.422631365509687</v>
+        <v>1.422631365509679</v>
       </c>
       <c r="AQ498" t="n">
         <v>79.06784146987005</v>
@@ -81782,16 +81782,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.4034224290251451</v>
+        <v>-0.4034224290251453</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02736182786837871</v>
+        <v>0.02736182786837866</v>
       </c>
       <c r="AO499" t="n">
-        <v>0.755189863471066</v>
+        <v>0.7551898634710656</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.28848874127045</v>
+        <v>1.288488741270451</v>
       </c>
       <c r="AQ499" t="n">
         <v>77.09998645170032</v>
@@ -81935,10 +81935,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI500" t="n">
-        <v>6.755708466794879</v>
+        <v>6.75570846679488</v>
       </c>
       <c r="AJ500" t="n">
-        <v>-0.01240850570479068</v>
+        <v>-0.01240850570479246</v>
       </c>
       <c r="AK500" t="n">
         <v>6.746865899087779</v>
@@ -81947,16 +81947,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4037073020769307</v>
+        <v>-0.4037073020769305</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02778289906564352</v>
+        <v>0.02778289906564353</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.7638221248099442</v>
+        <v>0.7638221248099444</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.106704203783623</v>
+        <v>1.106704203783605</v>
       </c>
       <c r="AQ500" t="n">
         <v>79.88914084152179</v>
@@ -82100,10 +82100,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.73601646973098</v>
+        <v>6.73601646973097</v>
       </c>
       <c r="AJ501" t="n">
-        <v>0.006783766017311343</v>
+        <v>0.006783766017321113</v>
       </c>
       <c r="AK501" t="n">
         <v>6.761018647414997</v>
@@ -82112,16 +82112,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.403510818895136</v>
+        <v>-0.4035108188951355</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02805871830419215</v>
+        <v>0.02805871830419202</v>
       </c>
       <c r="AO501" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.300975206946079</v>
+        <v>1.300975206946182</v>
       </c>
       <c r="AQ501" t="n">
         <v>83.63654538184727</v>
@@ -82280,13 +82280,13 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02827333203020888</v>
+        <v>0.02827333203020884</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7726830480787004</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.386408072754962</v>
+        <v>1.386408072754963</v>
       </c>
       <c r="AQ502" t="n">
         <v>84.10476741303809</v>
@@ -82430,10 +82430,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.725806144687715</v>
+        <v>6.725806144687716</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.01409396746438496</v>
+        <v>0.01409396746438318</v>
       </c>
       <c r="AK503" t="n">
         <v>6.744478107428201</v>
@@ -82442,16 +82442,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM503" t="n">
-        <v>-0.4027900432658338</v>
+        <v>-0.4027900432658339</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02891453613228628</v>
+        <v>0.0289145361322863</v>
       </c>
       <c r="AO503" t="n">
-        <v>0.7784357006627721</v>
+        <v>0.7784357006627718</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.361435739620025</v>
+        <v>1.361435739620007</v>
       </c>
       <c r="AQ503" t="n">
         <v>83.56281143456596</v>
@@ -82595,10 +82595,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.700854569500288</v>
+        <v>6.700854569500285</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.04174539464155735</v>
+        <v>0.04174539464156091</v>
       </c>
       <c r="AK504" t="n">
         <v>6.743301592583855</v>
@@ -82607,16 +82607,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.402742697458547</v>
+        <v>-0.4027426974585472</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.02955568036482276</v>
+        <v>0.0295556803648227</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7839391318357882</v>
+        <v>0.7839391318357879</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.637941562843737</v>
+        <v>1.637941562843773</v>
       </c>
       <c r="AQ504" t="n">
         <v>88.46316439848462</v>
@@ -82760,10 +82760,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.705597066237452</v>
+        <v>6.705597066237454</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.02390275065707925</v>
+        <v>0.02390275065707748</v>
       </c>
       <c r="AK505" t="n">
         <v>6.74285285202661</v>
@@ -82772,16 +82772,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.401588500320058</v>
+        <v>-0.4015885003200582</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.02985284499018426</v>
+        <v>0.02985284499018428</v>
       </c>
       <c r="AO505" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.44324674128027</v>
+        <v>1.443246741280252</v>
       </c>
       <c r="AQ505" t="n">
         <v>85.09516129032258</v>
@@ -82925,28 +82925,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.686024746022946</v>
+        <v>6.686024746022948</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.0364751013891631</v>
+        <v>0.03647510138916132</v>
       </c>
       <c r="AK506" t="n">
-        <v>6.744526329542678</v>
+        <v>6.744526329542679</v>
       </c>
       <c r="AL506" t="n">
-        <v>-0.02202648213056868</v>
+        <v>-0.02202648213056957</v>
       </c>
       <c r="AM506" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.02995529076246445</v>
+        <v>0.02995529076246446</v>
       </c>
       <c r="AO506" t="n">
-        <v>0.7933293013213367</v>
+        <v>0.7933293013213371</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.566182359822747</v>
+        <v>1.566182359822729</v>
       </c>
       <c r="AQ506" t="n">
         <v>84.34056224899598</v>
@@ -83090,10 +83090,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.689653251437546</v>
+        <v>6.689653251437547</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.03134694311201436</v>
+        <v>0.03134694311201347</v>
       </c>
       <c r="AK507" t="n">
         <v>6.730402461316146</v>
@@ -83102,16 +83102,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM507" t="n">
-        <v>-0.3993041981056888</v>
+        <v>-0.3993041981056886</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03010093147709741</v>
+        <v>0.03010093147709737</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.7985853639949437</v>
+        <v>0.7985853639949436</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.507036858820242</v>
+        <v>1.507036858820234</v>
       </c>
       <c r="AQ507" t="n">
         <v>85</v>
@@ -83255,10 +83255,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.716786041117415</v>
+        <v>6.716786041117424</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.00511394514967467</v>
+        <v>0.005113945149665788</v>
       </c>
       <c r="AK508" t="n">
         <v>6.728106442363027</v>
@@ -83267,16 +83267,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3976134529492091</v>
+        <v>-0.3976134529492094</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03006044259180324</v>
+        <v>0.03006044259180338</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.8026437279892851</v>
+        <v>0.8026437279892848</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.234777974751978</v>
+        <v>1.234777974751887</v>
       </c>
       <c r="AQ508" t="n">
         <v>81.59999999999999</v>
@@ -83420,10 +83420,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.721932795514441</v>
+        <v>6.72193279551444</v>
       </c>
       <c r="AJ509" t="n">
-        <v>-0.001632597913122424</v>
+        <v>-0.001632597913121536</v>
       </c>
       <c r="AK509" t="n">
         <v>6.752314636061016</v>
@@ -83435,13 +83435,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03043336917902489</v>
+        <v>0.03043336917902487</v>
       </c>
       <c r="AO509" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.163823515923089</v>
+        <v>1.163823515923099</v>
       </c>
       <c r="AQ509" t="n">
         <v>82.19999999999999</v>
@@ -83585,28 +83585,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.718669003366535</v>
+        <v>6.718669003366529</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.003830844045574544</v>
+        <v>0.003830844045580761</v>
       </c>
       <c r="AK510" t="n">
-        <v>6.750203856204787</v>
+        <v>6.750203856204786</v>
       </c>
       <c r="AL510" t="n">
-        <v>-0.02770400879267765</v>
+        <v>-0.02770400879267676</v>
       </c>
       <c r="AM510" t="n">
-        <v>-0.3969152632178358</v>
+        <v>-0.3969152632178359</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03100517332816438</v>
+        <v>0.03100517332816427</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8091236362457368</v>
+        <v>0.8091236362457366</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.217453571381047</v>
+        <v>1.217453571381112</v>
       </c>
       <c r="AQ510" t="n">
         <v>82.80000000000001</v>
@@ -83750,10 +83750,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.680190080689523</v>
+        <v>6.680190080689519</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.04230976672258624</v>
+        <v>0.04230976672259068</v>
       </c>
       <c r="AK511" t="n">
         <v>6.74780904069481</v>
@@ -83762,16 +83762,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM511" t="n">
-        <v>-0.3964565291282772</v>
+        <v>-0.3964565291282773</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03139664408873172</v>
+        <v>0.03139664408873165</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8123541153569376</v>
+        <v>0.8123541153569371</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.604493248424094</v>
+        <v>1.604493248424141</v>
       </c>
       <c r="AQ511" t="n">
         <v>89.8</v>
@@ -83915,10 +83915,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.671580974366952</v>
+        <v>6.671580974366949</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.05441885778636824</v>
+        <v>0.05441885778637179</v>
       </c>
       <c r="AK512" t="n">
         <v>6.701878095437348</v>
@@ -83930,13 +83930,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03163116863423027</v>
+        <v>0.03163116863423025</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8147568654710424</v>
+        <v>0.8147568654710426</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.717274375116457</v>
+        <v>1.717274375116494</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.2</v>
@@ -84080,28 +84080,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.656216276126097</v>
+        <v>6.656216276126093</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.06978355602722353</v>
+        <v>0.06978355602722708</v>
       </c>
       <c r="AK513" t="n">
-        <v>6.701765808189924</v>
+        <v>6.701765808189925</v>
       </c>
       <c r="AL513" t="n">
-        <v>0.02423402396339647</v>
+        <v>0.02423402396339558</v>
       </c>
       <c r="AM513" t="n">
-        <v>-0.3932426568003564</v>
+        <v>-0.3932426568003567</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.0319127327617218</v>
+        <v>0.03191273276172183</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8170879052811413</v>
+        <v>0.8170879052811416</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.858889534485343</v>
+        <v>1.858889534485379</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.59999999999999</v>
@@ -84251,19 +84251,19 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK514" t="n">
-        <v>6.682658801267993</v>
+        <v>6.682658801267994</v>
       </c>
       <c r="AL514" t="n">
-        <v>0.03754126053010243</v>
+        <v>0.03754126053010154</v>
       </c>
       <c r="AM514" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.03225018457163042</v>
+        <v>0.03225018457163047</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8195353634242114</v>
+        <v>0.8195353634242113</v>
       </c>
       <c r="AP514" t="n">
         <v>1.818117584748586</v>
@@ -84410,10 +84410,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.654231073451243</v>
+        <v>6.654231073451242</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.06476878921965579</v>
+        <v>0.06476878921965668</v>
       </c>
       <c r="AK515" t="n">
         <v>6.682840937292736</v>
@@ -84422,16 +84422,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM515" t="n">
-        <v>-0.3894836768645471</v>
+        <v>-0.3894836768645476</v>
       </c>
       <c r="AN515" t="n">
-        <v>0.03277193700354208</v>
+        <v>0.03277193700354209</v>
       </c>
       <c r="AO515" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.781104797300566</v>
+        <v>1.781104797300575</v>
       </c>
       <c r="AQ515" t="n">
         <v>90.2</v>
@@ -84575,10 +84575,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.650937329061554</v>
+        <v>6.650937329061552</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.06806253360934456</v>
+        <v>0.06806253360934633</v>
       </c>
       <c r="AK516" t="n">
         <v>6.698821600583909</v>
@@ -84587,16 +84587,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM516" t="n">
-        <v>-0.3885003849593205</v>
+        <v>-0.3885003849593203</v>
       </c>
       <c r="AN516" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO516" t="n">
-        <v>0.8264954348925954</v>
+        <v>0.8264954348925952</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.79987483353635</v>
+        <v>1.799874833536367</v>
       </c>
       <c r="AQ516" t="n">
         <v>91</v>
@@ -84740,10 +84740,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.651733245487365</v>
+        <v>6.651733245487366</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.05906692541107272</v>
+        <v>0.05906692541107184</v>
       </c>
       <c r="AK517" t="n">
         <v>6.69208631505748</v>
@@ -84752,16 +84752,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.3869746098498524</v>
+        <v>-0.3869746098498528</v>
       </c>
       <c r="AN517" t="n">
-        <v>0.0344188897752209</v>
+        <v>0.03441888977522091</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8294137131605728</v>
+        <v>0.8294137131605726</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.696616308981454</v>
+        <v>1.696616308981445</v>
       </c>
       <c r="AQ517" t="n">
         <v>90.40000000000001</v>
@@ -84905,10 +84905,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI518" t="n">
-        <v>6.632036771677474</v>
+        <v>6.632036771677475</v>
       </c>
       <c r="AJ518" t="n">
-        <v>0.07876339922096331</v>
+        <v>0.07876339922096243</v>
       </c>
       <c r="AK518" t="n">
         <v>6.692627206904497</v>
@@ -84926,7 +84926,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP518" t="n">
-        <v>1.875440190456854</v>
+        <v>1.875440190456846</v>
       </c>
       <c r="AQ518" t="n">
         <v>91</v>
@@ -85070,10 +85070,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.617259294346139</v>
+        <v>6.617259294346145</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.09324046914263029</v>
+        <v>0.09324046914262496</v>
       </c>
       <c r="AK519" t="n">
         <v>6.685306332307247</v>
@@ -85085,13 +85085,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03459091746240417</v>
+        <v>0.03459091746240425</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8328314813119074</v>
+        <v>0.8328314813119078</v>
       </c>
       <c r="AP519" t="n">
-        <v>1.998006000856745</v>
+        <v>1.998006000856694</v>
       </c>
       <c r="AQ519" t="n">
         <v>91</v>
@@ -85247,16 +85247,16 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM520" t="n">
-        <v>-0.379198503222778</v>
+        <v>-0.3791985032227784</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03468237364461174</v>
+        <v>0.03468237364461172</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8349203610870053</v>
+        <v>0.8349203610870052</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.31722822525293</v>
+        <v>2.317228225252932</v>
       </c>
       <c r="AQ520" t="n">
         <v>93</v>
@@ -85415,13 +85415,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03437427878524163</v>
+        <v>0.0343742787852416</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8337972329517069</v>
+        <v>0.8337972329517072</v>
       </c>
       <c r="AP521" t="n">
-        <v>2.426255822246373</v>
+        <v>2.426255822246376</v>
       </c>
       <c r="AQ521" t="n">
         <v>93.40000000000001</v>
@@ -85512,13 +85512,13 @@
         <v>1.48</v>
       </c>
       <c r="R522" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="S522" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="T522" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U522" t="n">
         <v>-3.701891751410343</v>
@@ -85530,7 +85530,7 @@
         <v>-1.630891176493998</v>
       </c>
       <c r="X522" t="n">
-        <v>1.16816505732853</v>
+        <v>1.187838879093239</v>
       </c>
       <c r="Y522" t="n">
         <v>38.95582329317269</v>
@@ -85556,7 +85556,7 @@
         <v>1.587301587301587</v>
       </c>
       <c r="AF522" t="n">
-        <v>0.9869550573285313</v>
+        <v>1.006628879093241</v>
       </c>
       <c r="AG522" t="n">
         <v>6.956323088568441</v>
@@ -85565,10 +85565,10 @@
         <v>-0.2483229054629721</v>
       </c>
       <c r="AI522" t="n">
-        <v>6.570789830572489</v>
+        <v>6.57078983057249</v>
       </c>
       <c r="AJ522" t="n">
-        <v>0.1372103525329802</v>
+        <v>0.1372103525329784</v>
       </c>
       <c r="AK522" t="n">
         <v>6.617345065810827</v>
@@ -85577,16 +85577,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM522" t="n">
-        <v>-0.3685435183382903</v>
+        <v>-0.3685435183382902</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03361173230743109</v>
+        <v>0.03361173230743112</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8313650598704547</v>
+        <v>0.8313650598704546</v>
       </c>
       <c r="AP522" t="n">
-        <v>2.332216400368044</v>
+        <v>2.33221640036803</v>
       </c>
       <c r="AQ522" t="n">
         <v>91.8</v>
@@ -85629,25 +85629,25 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="C523" t="n">
         <v>1.2439</v>
       </c>
       <c r="D523" t="n">
-        <v>3.406400000000001</v>
+        <v>3.4261</v>
       </c>
       <c r="E523" t="n">
-        <v>6.708000183105469</v>
+        <v>6.708199977874756</v>
       </c>
       <c r="F523" t="n">
-        <v>6.711699962615967</v>
+        <v>6.711750030517578</v>
       </c>
       <c r="G523" t="n">
         <v>6.6997</v>
       </c>
       <c r="H523" t="n">
-        <v>0.003699779510498047</v>
+        <v>0.003550052642822266</v>
       </c>
       <c r="I523" t="n">
         <v>99.45999908447266</v>
@@ -85656,49 +85656,49 @@
         <v>0</v>
       </c>
       <c r="K523" t="n">
-        <v>3.406400000000001</v>
+        <v>3.4261</v>
       </c>
       <c r="L523" t="n">
-        <v>3.12182</v>
+        <v>3.122805</v>
       </c>
       <c r="M523" t="n">
-        <v>3.003365000000001</v>
+        <v>3.003693333333334</v>
       </c>
       <c r="N523" t="n">
-        <v>2.845588333333333</v>
+        <v>2.8457525</v>
       </c>
       <c r="O523" t="n">
-        <v>99.80000000000001</v>
+        <v>100</v>
       </c>
       <c r="P523" t="n">
-        <v>99.9001996007984</v>
+        <v>100</v>
       </c>
       <c r="Q523" t="n">
         <v>1.48</v>
       </c>
       <c r="R523" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="S523" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="T523" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U523" t="n">
-        <v>-3.733512061191609</v>
+        <v>-3.69078534719845</v>
       </c>
       <c r="V523" t="n">
         <v>6.5135</v>
       </c>
       <c r="W523" t="n">
-        <v>-2.899525608173514</v>
+        <v>-2.902417616006125</v>
       </c>
       <c r="X523" t="n">
-        <v>-0.1556549721290379</v>
+        <v>-0.1392532658255785</v>
       </c>
       <c r="Y523" t="n">
-        <v>10.44176706827309</v>
+        <v>11.24497991967871</v>
       </c>
       <c r="Z523" t="inlineStr">
         <is>
@@ -85721,43 +85721,43 @@
         <v>1.785714285714286</v>
       </c>
       <c r="AF523" t="n">
-        <v>-0.3368649721290362</v>
+        <v>-0.3204632658255768</v>
       </c>
       <c r="AG523" t="n">
-        <v>6.958444179006467</v>
+        <v>6.955785239718927</v>
       </c>
       <c r="AH523" t="n">
-        <v>-0.2504439959009979</v>
+        <v>-0.2475852618441712</v>
       </c>
       <c r="AI523" t="n">
-        <v>6.575891804535481</v>
+        <v>6.568743061970067</v>
       </c>
       <c r="AJ523" t="n">
-        <v>0.1321083785699875</v>
+        <v>0.139456915904689</v>
       </c>
       <c r="AK523" t="n">
         <v>6.613295682645951</v>
       </c>
       <c r="AL523" t="n">
-        <v>0.0947045004595175</v>
+        <v>0.09490429522880461</v>
       </c>
       <c r="AM523" t="n">
-        <v>-0.362880333269974</v>
+        <v>-0.3628803332699742</v>
       </c>
       <c r="AN523" t="n">
-        <v>0.0328662017206236</v>
+        <v>0.03286620172062364</v>
       </c>
       <c r="AO523" t="n">
-        <v>0.82993355238613</v>
+        <v>0.8299335523861298</v>
       </c>
       <c r="AP523" t="n">
-        <v>2.25582252405286</v>
+        <v>2.323204012475562</v>
       </c>
       <c r="AQ523" t="n">
-        <v>91.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AR523" t="n">
-        <v>-0.003816550942697882</v>
+        <v>-0.00381722595136601</v>
       </c>
       <c r="AS523" t="n">
         <v>6.7778000831604</v>
@@ -85781,10 +85781,10 @@
         <v>7.216494845360824</v>
       </c>
       <c r="AZ523" t="n">
-        <v>64.93577319587628</v>
+        <v>65.12577319587628</v>
       </c>
       <c r="BA523" t="n">
-        <v>64.02735038807049</v>
+        <v>64.06535038807048</v>
       </c>
     </row>
   </sheetData>
@@ -86011,7 +86011,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -86026,7 +86026,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -86046,12 +86046,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -86061,12 +86061,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -86101,7 +86101,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -86111,7 +86111,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -86136,7 +86136,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA523"/>
+  <dimension ref="A1:BA524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41361,10 +41361,10 @@
         <v/>
       </c>
       <c r="AI254" t="n">
-        <v>7.164454424594246</v>
+        <v>7.164454424594245</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.02545448562940233</v>
+        <v>-0.02545448562940145</v>
       </c>
       <c r="AK254" t="n">
         <v>7.171026992419335</v>
@@ -41373,13 +41373,13 @@
         <v>-0.03202705345449175</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1023969939185646</v>
+        <v>0.1023969939185656</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002417390403537972</v>
+        <v>0.002417390403537929</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2665217851726001</v>
+        <v>0.2665217851725994</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41522,10 +41522,10 @@
         <v/>
       </c>
       <c r="AI255" t="n">
-        <v>7.160742529934239</v>
+        <v>7.16074252993424</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.01934266955215858</v>
+        <v>-0.01934266955216035</v>
       </c>
       <c r="AK255" t="n">
         <v>7.166224790710233</v>
@@ -41534,13 +41534,13 @@
         <v>-0.02482493032815292</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.1026368091542314</v>
+        <v>0.1026368091542317</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002433131908989014</v>
+        <v>0.002433131908989026</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2688740668038477</v>
+        <v>0.2688740668038501</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41687,10 +41687,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.150419484347116</v>
+        <v>7.150419484347115</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.009019623965035528</v>
+        <v>-0.00901962396503464</v>
       </c>
       <c r="AK256" t="n">
         <v>7.161074530187645</v>
@@ -41699,13 +41699,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.1029385549788083</v>
+        <v>0.102938554978808</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002436328878122382</v>
+        <v>0.002436328878122375</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2711996176877891</v>
+        <v>0.2711996176877889</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41852,10 +41852,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.148511457776028</v>
+        <v>7.14851145777603</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.01601128611465086</v>
+        <v>-0.01601128611465263</v>
       </c>
       <c r="AK257" t="n">
         <v>7.150963414761942</v>
@@ -41864,13 +41864,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.1011329645838851</v>
+        <v>0.1011329645838857</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002517185580011447</v>
+        <v>0.002517185580011383</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2709113683260677</v>
+        <v>0.2709113683260674</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42029,13 +42029,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.09870181295186471</v>
+        <v>0.09870181295186436</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.002644711580562537</v>
+        <v>0.002644711580562605</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2704892730019304</v>
+        <v>0.2704892730019285</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42182,10 +42182,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI259" t="n">
-        <v>7.153772633426659</v>
+        <v>7.153772633426657</v>
       </c>
       <c r="AJ259" t="n">
-        <v>-0.03287247931288917</v>
+        <v>-0.03287247931288739</v>
       </c>
       <c r="AK259" t="n">
         <v>7.154757231824306</v>
@@ -42194,13 +42194,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.09555831842873846</v>
+        <v>0.09555831842873888</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.002822832879878071</v>
+        <v>0.002822832879878049</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2697410008595936</v>
+        <v>0.2697410008595938</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42347,10 +42347,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI260" t="n">
-        <v>7.153331199414496</v>
+        <v>7.153331199414497</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-0.03263131690717191</v>
+        <v>-0.0326313169071728</v>
       </c>
       <c r="AK260" t="n">
         <v>7.15450652143491</v>
@@ -42359,13 +42359,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.0918844066524992</v>
+        <v>0.09188440665249918</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003041971996730133</v>
+        <v>0.003041971996730116</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2698098046976256</v>
+        <v>0.2698098046976254</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42512,10 +42512,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.156943148319592</v>
+        <v>7.15694314831959</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.03854305142628167</v>
+        <v>-0.0385430514262799</v>
       </c>
       <c r="AK261" t="n">
         <v>7.154505434137821</v>
@@ -42524,13 +42524,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.08748497753913406</v>
+        <v>0.08748497753913362</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003298336925509862</v>
+        <v>0.003298336925509857</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2682008942988235</v>
+        <v>0.2682008942988222</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42689,13 +42689,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.0824587084059305</v>
+        <v>0.08245870840593096</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.003602928090795432</v>
+        <v>0.003602928090795422</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2685806390401517</v>
+        <v>0.2685806390401518</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42857,10 +42857,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.003819541738581442</v>
+        <v>0.003819541738581439</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2696768907787764</v>
+        <v>0.2696768907787754</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43007,10 +43007,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.154685377655177</v>
+        <v>7.154685377655176</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.04048526245131967</v>
+        <v>-0.04048526245131878</v>
       </c>
       <c r="AK264" t="n">
         <v>7.15808570026938</v>
@@ -43019,13 +43019,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.07200163454913491</v>
+        <v>0.07200163454913533</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.004193740708391541</v>
+        <v>0.004193740708391577</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.270116598814735</v>
+        <v>0.2701165988147326</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43172,10 +43172,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.158449213455076</v>
+        <v>7.158449213455078</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.05514911885058371</v>
+        <v>-0.05514911885058549</v>
       </c>
       <c r="AK265" t="n">
         <v>7.157644979270017</v>
@@ -43184,13 +43184,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.06676111471939408</v>
+        <v>0.06676111471939436</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.00450521933759436</v>
+        <v>0.004505219337594384</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.2733976337163381</v>
+        <v>0.2733976337163387</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43337,10 +43337,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI266" t="n">
-        <v>7.160761769069204</v>
+        <v>7.160761769069201</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-0.04786198879576631</v>
+        <v>-0.04786198879576364</v>
       </c>
       <c r="AK266" t="n">
         <v>7.159146249199162</v>
@@ -43349,10 +43349,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.06148465881746725</v>
+        <v>0.06148465881746766</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.004852471327681615</v>
+        <v>0.004852471327681566</v>
       </c>
       <c r="AO266" t="n">
         <v>0.2778048766368325</v>
@@ -43502,10 +43502,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.162478122158095</v>
+        <v>7.162478122158094</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04957834188465782</v>
+        <v>-0.04957834188465693</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159578986975002</v>
@@ -43514,13 +43514,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.05582594297075769</v>
+        <v>0.05582594297075712</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.005234102211236422</v>
+        <v>0.005234102211236467</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.282448024375059</v>
+        <v>0.2824480243750598</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43679,13 +43679,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.04949165986049534</v>
+        <v>0.04949165986049463</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.005677665039252891</v>
+        <v>0.005677665039252918</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.2878618994559775</v>
+        <v>0.2878618994559794</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43844,13 +43844,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.04287777011073584</v>
+        <v>0.04287777011073606</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.006155260602669632</v>
+        <v>0.006155260602669625</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.2948468705933219</v>
+        <v>0.2948468705933236</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -43997,10 +43997,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.173971773133425</v>
+        <v>7.173971773133423</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.04247200582995792</v>
+        <v>-0.04247200582995614</v>
       </c>
       <c r="AK270" t="n">
         <v>7.159255388854645</v>
@@ -44009,13 +44009,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.0348694200966178</v>
+        <v>0.03486942009661778</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.006728155724408227</v>
+        <v>0.006728155724408201</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.304499875642397</v>
+        <v>0.3044998756423967</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44162,25 +44162,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.172030417300567</v>
+        <v>7.172030417300565</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.03823038754592822</v>
+        <v>-0.03823038754592645</v>
       </c>
       <c r="AK271" t="n">
-        <v>7.167062070913353</v>
+        <v>7.167062070913352</v>
       </c>
       <c r="AL271" t="n">
-        <v>-0.03326204115871434</v>
+        <v>-0.03326204115871345</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.03279550096037902</v>
+        <v>0.03279550096037874</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.006903991232239788</v>
+        <v>0.006903991232239758</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3170366335916601</v>
+        <v>0.3170366335916608</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44327,10 +44327,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.171236182927453</v>
+        <v>7.171236182927454</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.03843608069356641</v>
+        <v>-0.0384360806935673</v>
       </c>
       <c r="AK272" t="n">
         <v>7.16747443083108</v>
@@ -44339,13 +44339,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.02972414459983895</v>
+        <v>0.02972414459983913</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.007158147882858998</v>
+        <v>0.007158147882859</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3270754385893867</v>
+        <v>0.3270754385893863</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44492,10 +44492,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.170425137628191</v>
+        <v>7.170425137628194</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.05102511321412884</v>
+        <v>-0.0510251132141315</v>
       </c>
       <c r="AK273" t="n">
         <v>7.168373097443463</v>
@@ -44504,13 +44504,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.02657019411530269</v>
+        <v>0.02657019411530295</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.007420436972250415</v>
+        <v>0.007420436972250398</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3357224795973284</v>
+        <v>0.3357224795973281</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44669,13 +44669,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.02366886174665103</v>
+        <v>0.02366886174665165</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.007679120311627263</v>
+        <v>0.007679120311627231</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3450219581941938</v>
+        <v>0.345021958194194</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44822,10 +44822,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI275" t="n">
-        <v>7.172249622131827</v>
+        <v>7.172249622131823</v>
       </c>
       <c r="AJ275" t="n">
-        <v>-0.05324966409349674</v>
+        <v>-0.05324966409349319</v>
       </c>
       <c r="AK275" t="n">
         <v>7.167365057101177</v>
@@ -44834,13 +44834,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.01956653131084185</v>
+        <v>0.01956653131084189</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008034860291676559</v>
+        <v>0.008034860291676519</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3572033251592189</v>
+        <v>0.3572033251592186</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -44987,10 +44987,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI276" t="n">
-        <v>7.171656420777024</v>
+        <v>7.171656420777023</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-0.05265646273869429</v>
+        <v>-0.0526564627386934</v>
       </c>
       <c r="AK276" t="n">
         <v>7.167567681415887</v>
@@ -44999,13 +44999,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01638396088890769</v>
+        <v>0.0163839608889081</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008326212487477964</v>
+        <v>0.008326212487477898</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.3674516177552961</v>
+        <v>0.3674516177552964</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45152,10 +45152,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.175289829564748</v>
+        <v>7.175289829564746</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.05628987152641773</v>
+        <v>-0.05628987152641596</v>
       </c>
       <c r="AK277" t="n">
         <v>7.167553154788029</v>
@@ -45164,13 +45164,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM277" t="n">
-        <v>0.01351198449095157</v>
+        <v>0.01351198449095179</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.008601682347582891</v>
+        <v>0.008601682347582911</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.3758646846617525</v>
+        <v>0.375864684661753</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45323,19 +45323,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK278" t="n">
-        <v>7.16746081477764</v>
+        <v>7.167460814777641</v>
       </c>
       <c r="AL278" t="n">
-        <v>-0.04846085673931011</v>
+        <v>-0.048460856739311</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.01196199498966369</v>
+        <v>0.01196199498966377</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.008797062853284063</v>
+        <v>0.008797062853284078</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.3847384959530242</v>
+        <v>0.3847384959530228</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45643,10 +45643,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI280" t="n">
-        <v>7.189678003526525</v>
+        <v>7.189678003526526</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-0.07117777082999144</v>
+        <v>-0.07117777082999321</v>
       </c>
       <c r="AK280" t="n">
         <v/>
@@ -45655,13 +45655,13 @@
         <v/>
       </c>
       <c r="AM280" t="n">
-        <v>0.007307555239791734</v>
+        <v>0.007307555239791735</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.009236289154790337</v>
+        <v>0.009236289154790363</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.401039717356949</v>
+        <v>0.4010397173569483</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45808,10 +45808,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI281" t="n">
-        <v>7.183919177237467</v>
+        <v>7.183919177237466</v>
       </c>
       <c r="AJ281" t="n">
-        <v>-0.05641912001700788</v>
+        <v>-0.056419120017007</v>
       </c>
       <c r="AK281" t="n">
         <v>7.168706858585229</v>
@@ -45820,13 +45820,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.006573598200530942</v>
+        <v>0.006573598200531427</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009378157495070056</v>
+        <v>0.009378157495070007</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4093166892046883</v>
+        <v>0.4093166892046876</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45985,13 +45985,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.005719699928660468</v>
+        <v>0.00571969992866044</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009535855797507643</v>
+        <v>0.009535855797507651</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4189456552735356</v>
+        <v>0.4189456552735351</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46138,10 +46138,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI283" t="n">
-        <v>7.183803634757356</v>
+        <v>7.183803634757355</v>
       </c>
       <c r="AJ283" t="n">
-        <v>-0.08380373012478781</v>
+        <v>-0.08380373012478692</v>
       </c>
       <c r="AK283" t="n">
         <v>7.157754776965645</v>
@@ -46150,13 +46150,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.007205793377056199</v>
+        <v>0.007205793377055721</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009541847058682544</v>
+        <v>0.00954184705868257</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4265135453780396</v>
+        <v>0.4265135453780416</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46309,19 +46309,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK284" t="n">
-        <v>7.153578345933642</v>
+        <v>7.153578345933643</v>
       </c>
       <c r="AL284" t="n">
-        <v>-0.01517826811381795</v>
+        <v>-0.01517826811381884</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.009937300636551308</v>
+        <v>0.009937300636551421</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.00947510825395563</v>
+        <v>0.009475108253955637</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4359288044119884</v>
+        <v>0.4359288044119891</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46468,10 +46468,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI285" t="n">
-        <v>7.175374323571331</v>
+        <v>7.175374323571332</v>
       </c>
       <c r="AJ285" t="n">
-        <v>-0.04917412444413394</v>
+        <v>-0.04917412444413483</v>
       </c>
       <c r="AK285" t="n">
         <v>7.155226204999164</v>
@@ -46480,13 +46480,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01039951522374721</v>
+        <v>0.01039951522374727</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009534227083684284</v>
+        <v>0.009534227083684297</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.446224869246465</v>
+        <v>0.4462248692464653</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46645,13 +46645,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01174445052819259</v>
+        <v>0.01174445052819296</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009539024405591096</v>
+        <v>0.009539024405591111</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4561706550234678</v>
+        <v>0.4561706550234662</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46798,10 +46798,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI287" t="n">
-        <v>7.176295466764674</v>
+        <v>7.176295466764673</v>
       </c>
       <c r="AJ287" t="n">
-        <v>-0.04989547286818929</v>
+        <v>-0.04989547286818841</v>
       </c>
       <c r="AK287" t="n">
         <v>7.150954883812801</v>
@@ -46810,13 +46810,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.01399948938427905</v>
+        <v>0.01399948938427885</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009474826008246758</v>
+        <v>0.009474826008246765</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4654004237248369</v>
+        <v>0.4654004237248376</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46975,13 +46975,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.01676993900799729</v>
+        <v>0.01676993900799728</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009377028877974699</v>
+        <v>0.00937702887797469</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.476700939638935</v>
+        <v>0.4767009396389351</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47143,10 +47143,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.009204864903404497</v>
+        <v>0.009204864903404482</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.4883841032893044</v>
+        <v>0.4883841032893032</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47305,13 +47305,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.02435543352765289</v>
+        <v>0.02435543352765317</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.009045821984022376</v>
+        <v>0.00904582198402234</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.4990078266507766</v>
+        <v>0.4990078266507749</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47458,10 +47458,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI291" t="n">
-        <v>7.175210595491395</v>
+        <v>7.175210595491394</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.04951059854315254</v>
+        <v>-0.04951059854315165</v>
       </c>
       <c r="AK291" t="n">
         <v>7.151444380572274</v>
@@ -47470,13 +47470,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.02840267381959001</v>
+        <v>0.02840267381959008</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008843610540066053</v>
+        <v>0.008843610540066056</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.5123725312709416</v>
+        <v>0.5123725312709417</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47626,7 +47626,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.05177635201934994</v>
+        <v>-0.05177635201935082</v>
       </c>
       <c r="AK292" t="n">
         <v>7.151307469847429</v>
@@ -47635,13 +47635,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.03189518855892823</v>
+        <v>0.03189518855892809</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008740250954211215</v>
+        <v>0.008740250954211236</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5303980242931245</v>
+        <v>0.5303980242931252</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47788,10 +47788,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI293" t="n">
-        <v>7.172173616645312</v>
+        <v>7.172173616645314</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.06197368836162021</v>
+        <v>-0.06197368836162287</v>
       </c>
       <c r="AK293" t="n">
         <v>7.152170779642037</v>
@@ -47800,13 +47800,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.03448417181877508</v>
+        <v>0.03448417181877479</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008638296330047493</v>
+        <v>0.008638296330047519</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.536400419244653</v>
+        <v>0.5364004192446541</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47956,7 +47956,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.08262387272163529</v>
+        <v>-0.08262387272163618</v>
       </c>
       <c r="AK294" t="n">
         <v>7.155242422656618</v>
@@ -47968,10 +47968,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008527848481957645</v>
+        <v>0.008527848481957647</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5479838817473677</v>
+        <v>0.5479838817473681</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48118,10 +48118,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI295" t="n">
-        <v>7.18418852599864</v>
+        <v>7.184188525998638</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.08518854888682359</v>
+        <v>-0.08518854888682181</v>
       </c>
       <c r="AK295" t="n">
         <v>7.174067278312125</v>
@@ -48130,13 +48130,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.03996026841105445</v>
+        <v>0.03996026841105382</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008497979041970659</v>
+        <v>0.008497979041970699</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5534995516418705</v>
+        <v>0.553499551641869</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48283,10 +48283,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.185513015749276</v>
+        <v>7.185513015749274</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.07571315384131694</v>
+        <v>-0.07571315384131516</v>
       </c>
       <c r="AK296" t="n">
         <v>7.175957423377739</v>
@@ -48295,13 +48295,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04233079818885077</v>
+        <v>0.04233079818885083</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008432709457890229</v>
+        <v>0.008432709457890224</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.5557951014363787</v>
+        <v>0.5557951014363788</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48454,19 +48454,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK297" t="n">
-        <v>7.174765662541793</v>
+        <v>7.174765662541792</v>
       </c>
       <c r="AL297" t="n">
-        <v>-0.05786569534818931</v>
+        <v>-0.05786569534818842</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04394124299371591</v>
+        <v>0.04394124299371556</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008396387260434499</v>
+        <v>0.008396387260434506</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5565519909812464</v>
+        <v>0.5565519909812453</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48613,10 +48613,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI298" t="n">
-        <v>7.185932916622859</v>
+        <v>7.18593291662286</v>
       </c>
       <c r="AJ298" t="n">
-        <v>-0.0141327800566966</v>
+        <v>-0.01413278005669749</v>
       </c>
       <c r="AK298" t="n">
         <v>7.172730869790855</v>
@@ -48625,13 +48625,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04590755972499789</v>
+        <v>0.04590755972499803</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008346613473328282</v>
+        <v>0.008346613473328291</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5588443644440741</v>
+        <v>0.5588443644440755</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48778,10 +48778,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI299" t="n">
-        <v>7.187602005018013</v>
+        <v>7.187602005018014</v>
       </c>
       <c r="AJ299" t="n">
-        <v>-0.05810209275604983</v>
+        <v>-0.0581020927560516</v>
       </c>
       <c r="AK299" t="n">
         <v>7.168923754586179</v>
@@ -48790,10 +48790,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04658552832149703</v>
+        <v>0.04658552832149689</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008354655440128402</v>
+        <v>0.008354655440128426</v>
       </c>
       <c r="AO299" t="n">
         <v>0.5613325805619827</v>
@@ -48955,13 +48955,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.04820692510781933</v>
+        <v>0.04820692510781883</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008303818071592001</v>
+        <v>0.008303818071592054</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5626464255878519</v>
+        <v>0.5626464255878516</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49120,13 +49120,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.04983084886774743</v>
+        <v>0.04983084886774771</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008251024544031704</v>
+        <v>0.008251024544031682</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5641340630354328</v>
+        <v>0.5641340630354323</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49285,13 +49285,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05170461329917111</v>
+        <v>0.05170461329917048</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008192726391276807</v>
+        <v>0.008192726391276836</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5658195968244528</v>
+        <v>0.5658195968244545</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49450,13 +49450,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05348369580043773</v>
+        <v>0.05348369580043772</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008143044151838245</v>
+        <v>0.008143044151838252</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5671346874885959</v>
+        <v>0.5671346874885956</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49603,10 +49603,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.175179910580594</v>
+        <v>7.175179910580593</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.05588002196975417</v>
+        <v>-0.05588002196975328</v>
       </c>
       <c r="AK304" t="n">
         <v>7.165699812335961</v>
@@ -49615,13 +49615,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05520982564369371</v>
+        <v>0.0552098256436935</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008124788470663676</v>
+        <v>0.008124788470663643</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5701242576280907</v>
+        <v>0.5701242576280905</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49768,10 +49768,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.173581841712227</v>
+        <v>7.173581841712229</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.05428195310138761</v>
+        <v>-0.05428195310138939</v>
       </c>
       <c r="AK305" t="n">
         <v>7.162626578418298</v>
@@ -49780,13 +49780,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05644890839995315</v>
+        <v>0.05644890839995281</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008105230252153435</v>
+        <v>0.008105230252153447</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5713754740215509</v>
+        <v>0.5713754740215494</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49933,10 +49933,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.176011726611837</v>
+        <v>7.176011726611838</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.06401173805592908</v>
+        <v>-0.06401173805592997</v>
       </c>
       <c r="AK306" t="n">
         <v>7.165542054185019</v>
@@ -49945,13 +49945,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05727663218544052</v>
+        <v>0.05727663218544039</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.00812403522652648</v>
+        <v>0.008124035226526509</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.573000414744258</v>
+        <v>0.5730004147442582</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50098,10 +50098,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.17698340522191</v>
+        <v>7.176983405221908</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.07778363334080662</v>
+        <v>-0.07778363334080485</v>
       </c>
       <c r="AK307" t="n">
         <v>7.170209849598846</v>
@@ -50110,13 +50110,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.05825580143844533</v>
+        <v>0.05825580143844532</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.008106527117828777</v>
+        <v>0.008106527117828759</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5728585525731363</v>
+        <v>0.5728585525731367</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50263,10 +50263,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.174841035863564</v>
+        <v>7.174841035863563</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.06734095956961905</v>
+        <v>-0.06734095956961816</v>
       </c>
       <c r="AK308" t="n">
         <v>7.166925629020364</v>
@@ -50275,13 +50275,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.05980113395910436</v>
+        <v>0.05980113395910441</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.008056914781095353</v>
+        <v>0.008056914781095341</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5723268395754473</v>
+        <v>0.5723268395754482</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50428,10 +50428,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.179777800337525</v>
+        <v>7.179777800337526</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.07227772404357946</v>
+        <v>-0.07227772404358035</v>
       </c>
       <c r="AK309" t="n">
         <v>7.163704513322672</v>
@@ -50443,10 +50443,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.008007544934860181</v>
+        <v>0.008007544934860184</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5724055344141883</v>
+        <v>0.5724055344141876</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50593,10 +50593,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.176651545551679</v>
+        <v>7.176651545551677</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.06915146925773374</v>
+        <v>-0.06915146925773197</v>
       </c>
       <c r="AK310" t="n">
         <v>7.163430147298699</v>
@@ -50605,13 +50605,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.06321929365037962</v>
+        <v>0.06321929365038026</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007927773212025854</v>
+        <v>0.007927773212025837</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.572463582881384</v>
+        <v>0.5724635828813827</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50758,10 +50758,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.173279688539583</v>
+        <v>7.173279688539582</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.06577961224563733</v>
+        <v>-0.06577961224563644</v>
       </c>
       <c r="AK311" t="n">
         <v>7.158871783064204</v>
@@ -50770,13 +50770,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06523048259292186</v>
+        <v>0.0652304825929222</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007809540836127948</v>
+        <v>0.007809540836127932</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5710090561291132</v>
+        <v>0.571009056129113</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50923,10 +50923,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI312" t="n">
-        <v>7.168542018724481</v>
+        <v>7.168542018724479</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.06194221098522323</v>
+        <v>-0.06194221098522146</v>
       </c>
       <c r="AK312" t="n">
         <v>7.152618309751275</v>
@@ -50935,13 +50935,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.067411943409599</v>
+        <v>0.06741194340959927</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007660511838810988</v>
+        <v>0.007660511838810949</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.5694124450603424</v>
+        <v>0.5694124450603408</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51088,10 +51088,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI313" t="n">
-        <v>7.161829635752616</v>
+        <v>7.161829635752617</v>
       </c>
       <c r="AJ313" t="n">
-        <v>-0.05962960447209831</v>
+        <v>-0.0596296044720992</v>
       </c>
       <c r="AK313" t="n">
         <v>7.144956229005203</v>
@@ -51100,13 +51100,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.06977835201573312</v>
+        <v>0.06977835201573281</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007516908058882096</v>
+        <v>0.007516908058882097</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5690369646398685</v>
+        <v>0.5690369646398684</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51256,7 +51256,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.07699331565738099</v>
+        <v>-0.07699331565738188</v>
       </c>
       <c r="AK314" t="n">
         <v>7.140422114543136</v>
@@ -51265,16 +51265,16 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.07195366789421653</v>
+        <v>0.07195366789421676</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.007394117938767417</v>
+        <v>0.007394117938767422</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5693040973288186</v>
+        <v>0.5693040973288199</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.387214816667044</v>
+        <v>-1.387214816667113</v>
       </c>
       <c r="AQ314" t="n">
         <v>5.862068965517241</v>
@@ -51430,16 +51430,16 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.07456301989532385</v>
+        <v>0.07456301989532414</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.007241314760732032</v>
+        <v>0.007241314760731996</v>
       </c>
       <c r="AO315" t="n">
         <v>0.5685877661607006</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.751355156100289</v>
+        <v>-1.751355156100307</v>
       </c>
       <c r="AQ315" t="n">
         <v>3.306474020561267</v>
@@ -51595,16 +51595,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.07747971887849656</v>
+        <v>0.07747971887849607</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.0070901436555387</v>
+        <v>0.007090143655538702</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5681709745664083</v>
+        <v>0.5681709745664091</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.719358275118384</v>
+        <v>-1.7193582751184</v>
       </c>
       <c r="AQ316" t="n">
         <v>4.919354838709678</v>
@@ -51748,10 +51748,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.165084051386049</v>
+        <v>7.165084051386047</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.08998410631768916</v>
+        <v>-0.08998410631768738</v>
       </c>
       <c r="AK317" t="n">
         <v>7.14582045097363</v>
@@ -51760,16 +51760,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08000072584212846</v>
+        <v>0.08000072584212836</v>
       </c>
       <c r="AN317" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5684087510734981</v>
+        <v>0.5684087510734968</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.920512463066454</v>
+        <v>-1.920512463066381</v>
       </c>
       <c r="AQ317" t="n">
         <v>2.432995055945876</v>
@@ -51913,10 +51913,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.161419741275552</v>
+        <v>7.161419741275553</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.08971964514518138</v>
+        <v>-0.08971964514518227</v>
       </c>
       <c r="AK318" t="n">
         <v>7.155707108847959</v>
@@ -51925,16 +51925,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08204996863507508</v>
+        <v>0.08204996863507528</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006919462921967476</v>
+        <v>0.006919462921967468</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5672869954461468</v>
+        <v>0.5672869954461461</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.839265028040945</v>
+        <v>-1.83926502804101</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.368951612903226</v>
@@ -52078,10 +52078,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.155488092579304</v>
+        <v>7.155488092579303</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.08548792091792734</v>
+        <v>-0.08548792091792645</v>
       </c>
       <c r="AK319" t="n">
         <v>7.150451326287159</v>
@@ -52090,16 +52090,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08469403553214168</v>
+        <v>0.08469403553214211</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006815201188096393</v>
+        <v>0.006815201188096372</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5663505631396779</v>
+        <v>0.5663505631396781</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.572203541131127</v>
+        <v>-1.572203541131099</v>
       </c>
       <c r="AQ319" t="n">
         <v>3.870573870573871</v>
@@ -52243,10 +52243,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.158832817363979</v>
+        <v>7.15883281736398</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.09523275404000398</v>
+        <v>-0.09523275404000575</v>
       </c>
       <c r="AK320" t="n">
         <v>7.147115644271845</v>
@@ -52255,16 +52255,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.08699523504893081</v>
+        <v>0.08699523504893142</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006735083295172709</v>
+        <v>0.006735083295172689</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5654743012892969</v>
+        <v>0.5654743012892984</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.998545444594283</v>
+        <v>-1.998545444594386</v>
       </c>
       <c r="AQ320" t="n">
         <v>1.538825757575758</v>
@@ -52408,10 +52408,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.161703459649028</v>
+        <v>7.161703459649029</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.090303294091167</v>
+        <v>-0.09030329409116788</v>
       </c>
       <c r="AK321" t="n">
         <v>7.152131804583207</v>
@@ -52420,16 +52420,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.08901512474159551</v>
+        <v>0.08901512474159586</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006668288608758136</v>
+        <v>0.006668288608758129</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5631673144521659</v>
+        <v>0.5631673144521655</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.696375567991948</v>
+        <v>-1.696375567992</v>
       </c>
       <c r="AQ321" t="n">
         <v>2.261768082663605</v>
@@ -52573,10 +52573,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.162535384813326</v>
+        <v>7.162535384813327</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.09293527952768166</v>
+        <v>-0.09293527952768255</v>
       </c>
       <c r="AK322" t="n">
         <v>7.157753883768605</v>
@@ -52585,16 +52585,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.09116436352661951</v>
+        <v>0.09116436352661936</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006624805625172231</v>
+        <v>0.006624805625172246</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5612585549312774</v>
+        <v>0.5612585549312785</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.77116632357484</v>
+        <v>-1.771166323574888</v>
       </c>
       <c r="AQ322" t="n">
         <v>2.985739750445632</v>
@@ -52738,10 +52738,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.166818450294679</v>
+        <v>7.166818450294681</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.0958183511125501</v>
+        <v>-0.09581835111255188</v>
       </c>
       <c r="AK323" t="n">
         <v>7.158620349112049</v>
@@ -52750,16 +52750,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09320704864741254</v>
+        <v>0.09320704864741212</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006594358041710158</v>
+        <v>0.006594358041710186</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5590514368572466</v>
+        <v>0.5590514368572459</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.85019582999533</v>
+        <v>-1.850195829995415</v>
       </c>
       <c r="AQ323" t="n">
         <v>1.470906337875838</v>
@@ -52903,10 +52903,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.157691007010206</v>
+        <v>7.157691007010208</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.0943908742587416</v>
+        <v>-0.09439087425874337</v>
       </c>
       <c r="AK324" t="n">
         <v>7.164942158928604</v>
@@ -52915,16 +52915,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.09491020692123933</v>
+        <v>0.09491020692123982</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006562900445417311</v>
+        <v>0.006562900445417306</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5551825155208145</v>
+        <v>0.5551825155208129</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.729349174402516</v>
+        <v>-1.729349174402595</v>
       </c>
       <c r="AQ324" t="n">
         <v>2.878151260504202</v>
@@ -53068,10 +53068,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.151776426431621</v>
+        <v>7.15177642643162</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.08777629673191356</v>
+        <v>-0.08777629673191267</v>
       </c>
       <c r="AK325" t="n">
         <v>7.154764404811184</v>
@@ -53080,16 +53080,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.097046810505102</v>
+        <v>0.0970468105051025</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006523984583215639</v>
+        <v>0.006523984583215632</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5522992358254805</v>
+        <v>0.5522992358254815</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.385185049809918</v>
+        <v>-1.385185049809873</v>
       </c>
       <c r="AQ325" t="n">
         <v>6.358440498060829</v>
@@ -53233,10 +53233,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI326" t="n">
-        <v>7.15099240431968</v>
+        <v>7.150992404319682</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.09309245238486596</v>
+        <v>-0.09309245238486774</v>
       </c>
       <c r="AK326" t="n">
         <v>7.150261540163492</v>
@@ -53245,16 +53245,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.09904197982498698</v>
+        <v>0.09904197982498671</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006505848878330736</v>
+        <v>0.006505848878330779</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5500699492277152</v>
+        <v>0.5500699492277157</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.595274724905276</v>
+        <v>-1.595274724905352</v>
       </c>
       <c r="AQ326" t="n">
         <v>4.206349206349207</v>
@@ -53398,10 +53398,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI327" t="n">
-        <v>7.147140093605204</v>
+        <v>7.147140093605207</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.09314019278733277</v>
+        <v>-0.09314019278733543</v>
       </c>
       <c r="AK327" t="n">
         <v>7.148879230661717</v>
@@ -53410,16 +53410,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.1013300516539148</v>
+        <v>0.1013300516539142</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006479631055951007</v>
+        <v>0.006479631055951091</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5478993564899665</v>
+        <v>0.5478993564899672</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.559279185803214</v>
+        <v>-1.559279185803325</v>
       </c>
       <c r="AQ327" t="n">
         <v>3.443951379509936</v>
@@ -53569,22 +53569,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK328" t="n">
-        <v>7.145816711184184</v>
+        <v>7.145816711184185</v>
       </c>
       <c r="AL328" t="n">
-        <v>-0.09881677984873516</v>
+        <v>-0.09881677984873605</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1033273874042088</v>
+        <v>0.1033273874042092</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006468712737497662</v>
+        <v>0.006468712737497656</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5455500876237902</v>
+        <v>0.5455500876237913</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.633678780047227</v>
+        <v>-1.633678780047215</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.045795795795796</v>
@@ -53731,7 +53731,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ329" t="n">
-        <v>-0.1028262052267701</v>
+        <v>-0.102826205226771</v>
       </c>
       <c r="AK329" t="n">
         <v>7.139092738717567</v>
@@ -53740,16 +53740,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1056457020972507</v>
+        <v>0.1056457020972505</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006435041090934165</v>
+        <v>0.006435041090934217</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5433399026839665</v>
+        <v>0.5433399026839674</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.899027440937709</v>
+        <v>-1.899027440937733</v>
       </c>
       <c r="AQ329" t="n">
         <v>2.721461187214611</v>
@@ -53896,7 +53896,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.099096096614959</v>
+        <v>-0.09909609661495811</v>
       </c>
       <c r="AK330" t="n">
         <v>7.140479586010682</v>
@@ -53905,16 +53905,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.10768023901916</v>
+        <v>0.1076802390191602</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006405465077205547</v>
+        <v>0.006405465077205527</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5402459241219614</v>
+        <v>0.5402459241219618</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.687116422037569</v>
+        <v>-1.687116422037517</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.667140825035561</v>
@@ -54058,10 +54058,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI331" t="n">
-        <v>7.145743344370562</v>
+        <v>7.145743344370558</v>
       </c>
       <c r="AJ331" t="n">
-        <v>-0.1052431803385794</v>
+        <v>-0.1052431803385758</v>
       </c>
       <c r="AK331" t="n">
         <v>7.136632587022158</v>
@@ -54070,16 +54070,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1100130126862077</v>
+        <v>0.1100130126862084</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006366554765990282</v>
+        <v>0.00636655476599019</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5375708073661647</v>
+        <v>0.5375708073661639</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.899194629591059</v>
+        <v>-1.8991946295909</v>
       </c>
       <c r="AQ331" t="n">
         <v>2.649350649350649</v>
@@ -54235,16 +54235,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1122475627674583</v>
+        <v>0.1122475627674581</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006337265512462553</v>
+        <v>0.00633726551246258</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5341613739773245</v>
+        <v>0.5341613739773232</v>
       </c>
       <c r="AP332" t="n">
-        <v>-1.572918871746104</v>
+        <v>-1.572918871746101</v>
       </c>
       <c r="AQ332" t="n">
         <v>3.221997300944669</v>
@@ -54388,10 +54388,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI333" t="n">
-        <v>7.142519733033009</v>
+        <v>7.14251973303301</v>
       </c>
       <c r="AJ333" t="n">
-        <v>-0.1016195026252946</v>
+        <v>-0.1016195026252955</v>
       </c>
       <c r="AK333" t="n">
         <v>7.135172643569136</v>
@@ -54400,16 +54400,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1146509166068179</v>
+        <v>0.114650916606818</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006337163869517243</v>
+        <v>0.006337163869517234</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5319767312874306</v>
+        <v>0.5319767312874311</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.662569740270745</v>
+        <v>-1.662569740270778</v>
       </c>
       <c r="AQ333" t="n">
         <v>2.548084826565839</v>
@@ -54565,16 +54565,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1171965158426952</v>
+        <v>0.1171965158426948</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006367653503792481</v>
+        <v>0.00636765350379247</v>
       </c>
       <c r="AO334" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP334" t="n">
-        <v>-2.104390790930698</v>
+        <v>-2.104390790930691</v>
       </c>
       <c r="AQ334" t="n">
         <v>1.266025641025641</v>
@@ -54718,10 +54718,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI335" t="n">
-        <v>7.140851085964109</v>
+        <v>7.140851085964112</v>
       </c>
       <c r="AJ335" t="n">
-        <v>-0.1128512080344217</v>
+        <v>-0.1128512080344244</v>
       </c>
       <c r="AK335" t="n">
         <v>7.142783913375006</v>
@@ -54730,16 +54730,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.119227205240256</v>
+        <v>0.1192272052402563</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006383133038709798</v>
+        <v>0.00638313303870985</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.5243060286247103</v>
+        <v>0.5243060286247104</v>
       </c>
       <c r="AP335" t="n">
-        <v>-1.999980781016792</v>
+        <v>-1.999980781016887</v>
       </c>
       <c r="AQ335" t="n">
         <v>2.500390686044694</v>
@@ -54883,10 +54883,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.139245392969567</v>
+        <v>7.139245392969565</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1112455150398795</v>
+        <v>-0.1112455150398777</v>
       </c>
       <c r="AK336" t="n">
         <v>7.141836927013541</v>
@@ -54895,16 +54895,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM336" t="n">
-        <v>0.1211746327267789</v>
+        <v>0.1211746327267792</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006404909068509476</v>
+        <v>0.006404909068509461</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5185318197199045</v>
+        <v>0.518531819719905</v>
       </c>
       <c r="AP336" t="n">
-        <v>-1.879907772594156</v>
+        <v>-1.879907772594078</v>
       </c>
       <c r="AQ336" t="n">
         <v>3.704268292682927</v>
@@ -55048,10 +55048,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.136520216281903</v>
+        <v>7.136520216281902</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.108520338352216</v>
+        <v>-0.1085203383522142</v>
       </c>
       <c r="AK337" t="n">
         <v>7.13958125183462</v>
@@ -55060,16 +55060,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1228335954516147</v>
+        <v>0.1228335954516143</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006430223802628449</v>
+        <v>0.006430223802628476</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.5122974965428477</v>
+        <v>0.5122974965428486</v>
       </c>
       <c r="AP337" t="n">
-        <v>-1.727357918499389</v>
+        <v>-1.727357918499316</v>
       </c>
       <c r="AQ337" t="n">
         <v>4.878774356686003</v>
@@ -55228,13 +55228,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006430805642792636</v>
+        <v>0.006430805642792618</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.5056597011855208</v>
+        <v>0.5056597011855207</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.463446639918009</v>
+        <v>-2.463446639918004</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.204994192799071</v>
@@ -55378,10 +55378,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.136562857934749</v>
+        <v>7.13656285793475</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.140462909051692</v>
+        <v>-0.1404629090516929</v>
       </c>
       <c r="AK339" t="n">
         <v>7.132705938528055</v>
@@ -55393,13 +55393,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006419568115912044</v>
+        <v>0.006419568115912051</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4979995576252224</v>
+        <v>0.4979995576252233</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.720289042953629</v>
+        <v>-2.720289042953653</v>
       </c>
       <c r="AQ339" t="n">
         <v>1.190644932671864</v>
@@ -55543,10 +55543,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.135435320996258</v>
+        <v>7.135435320996254</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.1393353721132016</v>
+        <v>-0.1393353721131971</v>
       </c>
       <c r="AK340" t="n">
         <v>7.134470034900207</v>
@@ -55555,16 +55555,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1290155516631957</v>
+        <v>0.1290155516631951</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006423940675024581</v>
+        <v>0.006423940675024553</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.489456156051701</v>
+        <v>0.4894561560517011</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.557572429280606</v>
+        <v>-2.557572429280455</v>
       </c>
       <c r="AQ340" t="n">
         <v>2.948504983388704</v>
@@ -55708,10 +55708,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.135221482968309</v>
+        <v>7.135221482968312</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1391215340852527</v>
+        <v>-0.1391215340852554</v>
       </c>
       <c r="AK341" t="n">
         <v>7.133435115388912</v>
@@ -55720,16 +55720,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1313692321875789</v>
+        <v>0.1313692321875792</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006422605647444513</v>
+        <v>0.006422605647444502</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4811392039904447</v>
+        <v>0.4811392039904442</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.444696267851527</v>
+        <v>-2.444696267851617</v>
       </c>
       <c r="AQ341" t="n">
         <v>4.077079107505071</v>
@@ -55873,10 +55873,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI342" t="n">
-        <v>7.129120131622726</v>
+        <v>7.129120131622732</v>
       </c>
       <c r="AJ342" t="n">
-        <v>-0.1360199653019256</v>
+        <v>-0.1360199653019309</v>
       </c>
       <c r="AK342" t="n">
         <v>7.132510325395203</v>
@@ -55885,16 +55885,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1334873867685099</v>
+        <v>0.1334873867685108</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006388619079873509</v>
+        <v>0.006388619079873553</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4724960612931043</v>
+        <v>0.4724960612931048</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.254840378259555</v>
+        <v>-2.254840378259721</v>
       </c>
       <c r="AQ342" t="n">
         <v>5.17970401691332</v>
@@ -56050,16 +56050,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1357975915367747</v>
+        <v>0.1357975915367741</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006324213907675097</v>
+        <v>0.006324213907675122</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4647750649852552</v>
+        <v>0.4647750649852558</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.331385793786239</v>
+        <v>-2.331385793786226</v>
       </c>
       <c r="AQ343" t="n">
         <v>2.860648327521632</v>
@@ -56203,10 +56203,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI344" t="n">
-        <v>7.122818285283529</v>
+        <v>7.122818285283532</v>
       </c>
       <c r="AJ344" t="n">
-        <v>-0.1394184172720543</v>
+        <v>-0.1394184172720578</v>
       </c>
       <c r="AK344" t="n">
         <v>7.123271418608565</v>
@@ -56215,16 +56215,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1386638579210687</v>
+        <v>0.1386638579210689</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.006222091828703702</v>
+        <v>0.006222091828703747</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4565264017486783</v>
+        <v>0.4565264017486775</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.204545221728734</v>
+        <v>-2.204545221728828</v>
       </c>
       <c r="AQ344" t="n">
         <v>3.939393939393939</v>
@@ -56380,16 +56380,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1423176752089984</v>
+        <v>0.1423176752089981</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.006093783709292283</v>
+        <v>0.006093783709292289</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4497199830569224</v>
+        <v>0.4497199830569214</v>
       </c>
       <c r="AP345" t="n">
-        <v>-1.830741702885553</v>
+        <v>-1.830741702885538</v>
       </c>
       <c r="AQ345" t="n">
         <v>8.889986418076306</v>
@@ -56533,10 +56533,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.133160404869088</v>
+        <v>7.13316040486909</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.1496604010543905</v>
+        <v>-0.1496604010543923</v>
       </c>
       <c r="AK346" t="n">
         <v>7.117219286120759</v>
@@ -56548,13 +56548,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.005984113522022494</v>
+        <v>0.005984113522022499</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4438783751010233</v>
+        <v>0.4438783751010228</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.385403684195726</v>
+        <v>-2.385403684195758</v>
       </c>
       <c r="AQ346" t="n">
         <v>7.765700483091787</v>
@@ -56698,10 +56698,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.12965322071209</v>
+        <v>7.129653220712091</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1524531894315722</v>
+        <v>-0.152453189431573</v>
       </c>
       <c r="AK347" t="n">
         <v>7.126254605494273</v>
@@ -56710,16 +56710,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1503893187551748</v>
+        <v>0.1503893187551739</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005963146506628741</v>
+        <v>0.005963146506628762</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4412018736247373</v>
+        <v>0.441201873624737</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.380336796004049</v>
+        <v>-2.380336796004052</v>
       </c>
       <c r="AQ347" t="n">
         <v>7.680491551459293</v>
@@ -56863,10 +56863,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.128380415829728</v>
+        <v>7.128380415829729</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1552802304354408</v>
+        <v>-0.1552802304354417</v>
       </c>
       <c r="AK348" t="n">
         <v>7.124321202568002</v>
@@ -56875,16 +56875,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1546287435667592</v>
+        <v>0.1546287435667593</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005975981199024843</v>
+        <v>0.005975981199024824</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4385827444686599</v>
+        <v>0.43858274446866</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.375569581173715</v>
+        <v>-2.375569581173716</v>
       </c>
       <c r="AQ348" t="n">
         <v>7.597132284921368</v>
@@ -57028,10 +57028,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.124429161493117</v>
+        <v>7.124429161493114</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1469291996400894</v>
+        <v>-0.1469291996400868</v>
       </c>
       <c r="AK349" t="n">
         <v>7.121152072356459</v>
@@ -57040,16 +57040,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1587808126513012</v>
+        <v>0.1587808126513008</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.00589922161993145</v>
+        <v>0.005899221619931436</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4336499747757657</v>
+        <v>0.4336499747757655</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.071444053426131</v>
+        <v>-2.071444053426039</v>
       </c>
       <c r="AQ349" t="n">
         <v>16.08375778155065</v>
@@ -57205,16 +57205,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1636493008978488</v>
+        <v>0.1636493008978486</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.005897856672615054</v>
+        <v>0.005897856672615022</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.434304834398872</v>
+        <v>0.4343048343988722</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.381707053311504</v>
+        <v>-2.381707053311488</v>
       </c>
       <c r="AQ350" t="n">
         <v>13.81870567375887</v>
@@ -57358,10 +57358,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.141397967314147</v>
+        <v>7.141397967314151</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.1753978872055049</v>
+        <v>-0.1753978872055084</v>
       </c>
       <c r="AK351" t="n">
         <v>7.12802266215534</v>
@@ -57370,16 +57370,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1676675897666615</v>
+        <v>0.1676675897666616</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.005952601612807557</v>
+        <v>0.005952601612807589</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4322693842687806</v>
+        <v>0.4322693842687804</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.667671235283137</v>
+        <v>-2.667671235283208</v>
       </c>
       <c r="AQ351" t="n">
         <v>12.62072707542051</v>
@@ -57523,10 +57523,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.140412492855504</v>
+        <v>7.140412492855501</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1723124219021352</v>
+        <v>-0.1723124219021317</v>
       </c>
       <c r="AK352" t="n">
         <v>7.137738577466652</v>
@@ -57535,16 +57535,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1710383543493657</v>
+        <v>0.1710383543493662</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.006068444256835448</v>
+        <v>0.00606844425683546</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4285062718639565</v>
+        <v>0.4285062718639572</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.487142522607826</v>
+        <v>-2.487142522607719</v>
       </c>
       <c r="AQ352" t="n">
         <v>19.77040816326531</v>
@@ -57688,10 +57688,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.138020503721587</v>
+        <v>7.138020503721584</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.169920432768218</v>
+        <v>-0.1699204327682153</v>
       </c>
       <c r="AK353" t="n">
         <v>7.13663078035759</v>
@@ -57700,16 +57700,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.176195682434215</v>
+        <v>0.1761956824342154</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.006402952059750722</v>
+        <v>0.006402952059750703</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4374093872433962</v>
+        <v>0.4374093872433956</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.343009734619097</v>
+        <v>-2.343009734619021</v>
       </c>
       <c r="AQ353" t="n">
         <v>19.55638862855358</v>
@@ -57853,28 +57853,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.136830620687384</v>
+        <v>7.136830620687383</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1769307183436339</v>
+        <v>-0.1769307183436331</v>
       </c>
       <c r="AK354" t="n">
-        <v>7.14004901784002</v>
+        <v>7.140049017840021</v>
       </c>
       <c r="AL354" t="n">
-        <v>-0.1801491154962704</v>
+        <v>-0.1801491154962713</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1796308914905975</v>
+        <v>0.1796308914905974</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.006948414844703821</v>
+        <v>0.006948414844703805</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4458727441769479</v>
+        <v>0.4458727441769483</v>
       </c>
       <c r="AP354" t="n">
-        <v>-2.433015356127483</v>
+        <v>-2.433015356127453</v>
       </c>
       <c r="AQ354" t="n">
         <v>17.8469387755102</v>
@@ -58014,10 +58014,10 @@
         <v/>
       </c>
       <c r="AI355" t="n">
-        <v>7.133638579266565</v>
+        <v>7.13363857926656</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1699387616090942</v>
+        <v>-0.1699387616090897</v>
       </c>
       <c r="AK355" t="n">
         <v>7.13798584867198</v>
@@ -58026,16 +58026,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1829391475229931</v>
+        <v>0.1829391475229935</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.007602047321544403</v>
+        <v>0.00760204732154433</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4545618931940824</v>
+        <v>0.4545618931940826</v>
       </c>
       <c r="AP355" t="n">
-        <v>-2.192268299666791</v>
+        <v>-2.192268299666683</v>
       </c>
       <c r="AQ355" t="n">
         <v>26.98019801980198</v>
@@ -58179,10 +58179,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI356" t="n">
-        <v>7.12640946890857</v>
+        <v>7.126409468908567</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1538094856932375</v>
+        <v>-0.1538094856932348</v>
       </c>
       <c r="AK356" t="n">
         <v>7.138565167526504</v>
@@ -58191,16 +58191,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1834764543657148</v>
+        <v>0.1834764543657157</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.007712839302340374</v>
+        <v>0.007712839302340297</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4511257152112026</v>
+        <v>0.4511257152112024</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.761104492054283</v>
+        <v>-1.761104492054221</v>
       </c>
       <c r="AQ356" t="n">
         <v>22.60843731431967</v>
@@ -58344,10 +58344,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI357" t="n">
-        <v>7.110999512759045</v>
+        <v>7.110999512759042</v>
       </c>
       <c r="AJ357" t="n">
-        <v>-0.1383995295437126</v>
+        <v>-0.1383995295437099</v>
       </c>
       <c r="AK357" t="n">
         <v>7.137040595974374</v>
@@ -58356,16 +58356,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1869739626316104</v>
+        <v>0.1869739626316108</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.00835460951998479</v>
+        <v>0.008354609519984808</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4618871834350119</v>
+        <v>0.4618871834350127</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.368717051122944</v>
+        <v>-1.368717051122884</v>
       </c>
       <c r="AQ357" t="n">
         <v>16.75242718446602</v>
@@ -58521,16 +58521,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.1901371272406391</v>
+        <v>0.1901371272406383</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.008787529863310189</v>
+        <v>0.008787529863310259</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4631528842621211</v>
+        <v>0.4631528842621208</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.405229583753368</v>
+        <v>-1.405229583753373</v>
       </c>
       <c r="AQ358" t="n">
         <v>10.21039603960396</v>
@@ -58674,10 +58674,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI359" t="n">
-        <v>7.10229338126412</v>
+        <v>7.102293381264122</v>
       </c>
       <c r="AJ359" t="n">
-        <v>-0.1477931828998624</v>
+        <v>-0.1477931828998642</v>
       </c>
       <c r="AK359" t="n">
         <v>7.113436809075056</v>
@@ -58686,16 +58686,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.1939456835457532</v>
+        <v>0.193945683545753</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.009306466714917722</v>
+        <v>0.009306466714917755</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4650211967660294</v>
+        <v>0.4650211967660295</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.547790886058297</v>
+        <v>-1.547790886058342</v>
       </c>
       <c r="AQ359" t="n">
         <v>11.12044817927171</v>
@@ -58851,16 +58851,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.1968971496416331</v>
+        <v>0.1968971496416338</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.009915270508004642</v>
+        <v>0.009915270508004639</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4658112293095933</v>
+        <v>0.4658112293095935</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.323847614466191</v>
+        <v>-1.323847614466194</v>
       </c>
       <c r="AQ360" t="n">
         <v>11.40318739695915</v>
@@ -59016,16 +59016,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2001574773810679</v>
+        <v>0.200157477381068</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.01045224758824684</v>
+        <v>0.01045224758824685</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4652001227613064</v>
+        <v>0.4652001227613058</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.585894032713987</v>
+        <v>-1.58589403271399</v>
       </c>
       <c r="AQ361" t="n">
         <v>5.153666427030913</v>
@@ -59169,10 +59169,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI362" t="n">
-        <v>7.112155432918446</v>
+        <v>7.112155432918444</v>
       </c>
       <c r="AJ362" t="n">
-        <v>-0.1611552192953987</v>
+        <v>-0.1611552192953969</v>
       </c>
       <c r="AK362" t="n">
         <v>7.115439870473561</v>
@@ -59181,16 +59181,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2059164257597553</v>
+        <v>0.2059164257597547</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01095806236007055</v>
+        <v>0.0109580623600705</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4647071558511969</v>
+        <v>0.4647071558511972</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.78212565773126</v>
+        <v>-1.782125657731223</v>
       </c>
       <c r="AQ362" t="n">
         <v>6.587301587301587</v>
@@ -59346,16 +59346,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2103846028094628</v>
+        <v>0.2103846028094625</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01138655624224677</v>
+        <v>0.01138655624224671</v>
       </c>
       <c r="AO363" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.810148439959766</v>
+        <v>-1.81014843995977</v>
       </c>
       <c r="AQ363" t="n">
         <v>11.2428596157175</v>
@@ -59499,10 +59499,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI364" t="n">
-        <v>7.110775793344653</v>
+        <v>7.110775793344654</v>
       </c>
       <c r="AJ364" t="n">
-        <v>-0.1730759985753663</v>
+        <v>-0.1730759985753672</v>
       </c>
       <c r="AK364" t="n">
         <v>7.127056499711662</v>
@@ -59511,16 +59511,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2137349114935569</v>
+        <v>0.2137349114935566</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01184277521890661</v>
+        <v>0.0118427752189066</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4573024605378193</v>
+        <v>0.4573024605378192</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.974952691681103</v>
+        <v>-1.974952691681126</v>
       </c>
       <c r="AQ364" t="n">
         <v>12.5785896346644</v>
@@ -59676,16 +59676,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2192999169256238</v>
+        <v>0.2192999169256231</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01242692746354282</v>
+        <v>0.01242692746354283</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4593518446085588</v>
+        <v>0.4593518446085587</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.53389908426528</v>
+        <v>-1.533899084265283</v>
       </c>
       <c r="AQ365" t="n">
         <v>14.21421421421421</v>
@@ -59829,28 +59829,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.095070446253633</v>
+        <v>7.095070446253632</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.1572705156811232</v>
+        <v>-0.1572705156811223</v>
       </c>
       <c r="AK366" t="n">
-        <v>7.099084322920755</v>
+        <v>7.099084322920754</v>
       </c>
       <c r="AL366" t="n">
-        <v>-0.1612843923482448</v>
+        <v>-0.1612843923482439</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2273791016644669</v>
+        <v>0.2273791016644665</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01301934706839999</v>
+        <v>0.01301934706840001</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4655241261491886</v>
+        <v>0.4655241261491888</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.566746911622516</v>
+        <v>-1.5667469116225</v>
       </c>
       <c r="AQ366" t="n">
         <v>12.26245085190039</v>
@@ -59994,10 +59994,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.077412848446851</v>
+        <v>7.077412848446856</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1386129903535895</v>
+        <v>-0.138612990353594</v>
       </c>
       <c r="AK367" t="n">
         <v>7.107752072150756</v>
@@ -60006,16 +60006,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2346680713248289</v>
+        <v>0.2346680713248287</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01366280940279216</v>
+        <v>0.01366280940279221</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4682122340216202</v>
+        <v>0.4682122340216205</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.136522825763405</v>
+        <v>-1.136522825763505</v>
       </c>
       <c r="AQ367" t="n">
         <v>19.68624296057924</v>
@@ -60159,10 +60159,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.067855559671527</v>
+        <v>7.067855559671529</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1458556283360775</v>
+        <v>-0.1458556283360801</v>
       </c>
       <c r="AK368" t="n">
         <v>7.100856094477853</v>
@@ -60171,16 +60171,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2404731763378842</v>
+        <v>0.2404731763378833</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01427110593278799</v>
+        <v>0.01427110593278805</v>
       </c>
       <c r="AO368" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.28355700537033</v>
+        <v>-1.283557005370389</v>
       </c>
       <c r="AQ368" t="n">
         <v>19.14414414414414</v>
@@ -60324,10 +60324,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.081794385763164</v>
+        <v>7.081794385763168</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1711942003688769</v>
+        <v>-0.1711942003688813</v>
       </c>
       <c r="AK369" t="n">
         <v>7.090764621929079</v>
@@ -60336,16 +60336,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2453259423721931</v>
+        <v>0.2453259423721924</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01502424352484369</v>
+        <v>0.01502424352484376</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.4756424387980298</v>
+        <v>0.4756424387980304</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.814459861875897</v>
+        <v>-1.814459861875991</v>
       </c>
       <c r="AQ369" t="n">
         <v>15.5667701863354</v>
@@ -60489,10 +60489,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.068234493406102</v>
+        <v>7.068234493406101</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1557345887735337</v>
+        <v>-0.1557345887735329</v>
       </c>
       <c r="AK370" t="n">
         <v>7.110983013755962</v>
@@ -60501,16 +60501,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2481172514763508</v>
+        <v>0.2481172514763511</v>
       </c>
       <c r="AN370" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4781214750573159</v>
+        <v>0.4781214750573156</v>
       </c>
       <c r="AP370" t="n">
-        <v>-1.452804883187617</v>
+        <v>-1.452804883187595</v>
       </c>
       <c r="AQ370" t="n">
         <v>19.33170582850168</v>
@@ -60654,28 +60654,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.047011693433886</v>
+        <v>7.04701169343388</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1469114622632315</v>
+        <v>-0.1469114622632253</v>
       </c>
       <c r="AK371" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL371" t="n">
-        <v>-0.1936362268489642</v>
+        <v>-0.1936362268489633</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2517176519946896</v>
+        <v>0.2517176519946887</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.01672959897123732</v>
+        <v>0.01672959897123727</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.482044795280705</v>
+        <v>0.4820447952807055</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.244932890532577</v>
+        <v>-1.244932890532441</v>
       </c>
       <c r="AQ371" t="n">
         <v>18.62348178137652</v>
@@ -60819,28 +60819,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.043635211714482</v>
+        <v>7.043635211714486</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.135635219343877</v>
+        <v>-0.1356352193438806</v>
       </c>
       <c r="AK372" t="n">
-        <v>7.069112439760902</v>
+        <v>7.069112439760901</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1611124473902965</v>
+        <v>-0.1611124473902956</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2568291528619773</v>
+        <v>0.2568291528619769</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01758784222749221</v>
+        <v>0.0175878422274923</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.4888256589627545</v>
+        <v>0.488825658962754</v>
       </c>
       <c r="AP372" t="n">
-        <v>-0.9891368860718699</v>
+        <v>-0.9891368860719471</v>
       </c>
       <c r="AQ372" t="n">
         <v>23.98305084745763</v>
@@ -60984,10 +60984,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.045320696769622</v>
+        <v>7.04532069676962</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1373207043990163</v>
+        <v>-0.1373207043990146</v>
       </c>
       <c r="AK373" t="n">
         <v>7.067486653848666</v>
@@ -60996,16 +60996,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2611441025487395</v>
+        <v>0.2611441025487396</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.01863884916361525</v>
+        <v>0.01863884916361523</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.4958891106408185</v>
+        <v>0.4958891106408189</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.017305448193841</v>
+        <v>-1.017305448193802</v>
       </c>
       <c r="AQ373" t="n">
         <v>21.6350333236743</v>
@@ -61149,10 +61149,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.052957186540217</v>
+        <v>7.052957186540212</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1449571941696117</v>
+        <v>-0.1449571941696064</v>
       </c>
       <c r="AK374" t="n">
         <v>7.066060765041626</v>
@@ -61161,16 +61161,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2646928033319798</v>
+        <v>0.2646928033319788</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.01961447184998982</v>
+        <v>0.0196144718499898</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.4990325267638059</v>
+        <v>0.4990325267638065</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.17302240203794</v>
+        <v>-1.173022402037825</v>
       </c>
       <c r="AQ374" t="n">
         <v>18.98504273504274</v>
@@ -61314,28 +61314,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI375" t="n">
-        <v>7.055218091951101</v>
+        <v>7.055218091951103</v>
       </c>
       <c r="AJ375" t="n">
-        <v>-0.1472180995804955</v>
+        <v>-0.1472180995804973</v>
       </c>
       <c r="AK375" t="n">
-        <v>7.064646745753511</v>
+        <v>7.06464674575351</v>
       </c>
       <c r="AL375" t="n">
-        <v>-0.1566467533829057</v>
+        <v>-0.1566467533829048</v>
       </c>
       <c r="AM375" t="n">
-        <v>0.2692457951306195</v>
+        <v>0.2692457951306194</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.02045122459205889</v>
+        <v>0.02045122459205891</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.5009265659871953</v>
+        <v>0.5009265659871951</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.210005799573701</v>
+        <v>-1.210005799573742</v>
       </c>
       <c r="AQ375" t="n">
         <v>18.01022552178176</v>
@@ -61479,10 +61479,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.050463258619342</v>
+        <v>7.050463258619345</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1423631304455135</v>
+        <v>-0.1423631304455171</v>
       </c>
       <c r="AK376" t="n">
         <v>7.063274589921972</v>
@@ -61491,16 +61491,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2738618637550985</v>
+        <v>0.2738618637550991</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02103732430364852</v>
+        <v>0.02103732430364855</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5007948901071727</v>
+        <v>0.5007948901071723</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.093899743579132</v>
+        <v>-1.09389974357921</v>
       </c>
       <c r="AQ376" t="n">
         <v>22.43077558892409</v>
@@ -61817,13 +61817,13 @@
         <v/>
       </c>
       <c r="AM378" t="n">
-        <v>0.280344119587675</v>
+        <v>0.2803441195876753</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02230845224183686</v>
+        <v>0.02230845224183688</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.5036776407221306</v>
+        <v>0.5036776407221312</v>
       </c>
       <c r="AP378" t="n">
         <v>-1.246491204623905</v>
@@ -61970,10 +61970,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.056824809597053</v>
+        <v>7.056824809597052</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.1737247767906567</v>
+        <v>-0.1737247767906558</v>
       </c>
       <c r="AK379" t="n">
         <v>7.071238163852278</v>
@@ -61982,16 +61982,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2841407798055449</v>
+        <v>0.2841407798055452</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02276542233315987</v>
+        <v>0.02276542233315985</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5036956996297977</v>
+        <v>0.5036956996297983</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.735499502858073</v>
+        <v>-1.735499502858054</v>
       </c>
       <c r="AQ379" t="n">
         <v>21.70148069804337</v>
@@ -62135,10 +62135,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.04726592259491</v>
+        <v>7.047265922594908</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.1780656929501347</v>
+        <v>-0.178065692950133</v>
       </c>
       <c r="AK380" t="n">
         <v>7.075283303194255</v>
@@ -62147,16 +62147,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2869603504542605</v>
+        <v>0.2869603504542598</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02324367830537832</v>
+        <v>0.02324367830537833</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5029697249741727</v>
+        <v>0.5029697249741724</v>
       </c>
       <c r="AP380" t="n">
-        <v>-1.797910715459853</v>
+        <v>-1.797910715459816</v>
       </c>
       <c r="AQ380" t="n">
         <v>10.56260162601626</v>
@@ -62300,10 +62300,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.030237372659574</v>
+        <v>7.030237372659579</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.189337428354154</v>
+        <v>-0.1893374283541593</v>
       </c>
       <c r="AK381" t="n">
         <v>7.061088020066238</v>
@@ -62312,16 +62312,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.2909556153842325</v>
+        <v>0.2909556153842324</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02343150180192449</v>
+        <v>0.02343150180192457</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.501187497763653</v>
+        <v>0.5011874977636526</v>
       </c>
       <c r="AP381" t="n">
-        <v>-1.998175164150586</v>
+        <v>-1.998175164150696</v>
       </c>
       <c r="AQ381" t="n">
         <v>2.412954429083461</v>
@@ -62465,10 +62465,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.074556523891909</v>
+        <v>7.074556523891907</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.2166563812222311</v>
+        <v>-0.2166563812222293</v>
       </c>
       <c r="AK382" t="n">
         <v>7.045371831199247</v>
@@ -62477,16 +62477,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.2963660759601011</v>
+        <v>0.2963660759601009</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02388105320115907</v>
+        <v>0.02388105320115906</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.5011837436137521</v>
+        <v>0.5011837436137511</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.500689639035226</v>
+        <v>-2.500689639035188</v>
       </c>
       <c r="AQ382" t="n">
         <v>14.79370078740157</v>
@@ -62630,10 +62630,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.103552248295395</v>
+        <v>7.103552248295403</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2215522788129736</v>
+        <v>-0.2215522788129807</v>
       </c>
       <c r="AK383" t="n">
         <v>7.078406423284397</v>
@@ -62642,16 +62642,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.29984079129971</v>
+        <v>0.2998407912997099</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02427773372157399</v>
+        <v>0.02427773372157407</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.4964684575356704</v>
+        <v>0.4964684575356701</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.525433235757391</v>
+        <v>-2.525433235757525</v>
       </c>
       <c r="AQ383" t="n">
         <v>19.43824404761905</v>
@@ -62807,16 +62807,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3035220749319825</v>
+        <v>0.3035220749319821</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02465824743687012</v>
+        <v>0.02465824743687013</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.4899948718309226</v>
+        <v>0.4899948718309223</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.237361550577034</v>
+        <v>-2.237361550577025</v>
       </c>
       <c r="AQ384" t="n">
         <v>23.21003479216261</v>
@@ -62960,10 +62960,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.12777959440025</v>
+        <v>7.127779594400253</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.2307797584322326</v>
+        <v>-0.2307797584322353</v>
       </c>
       <c r="AK385" t="n">
         <v>7.110202206771168</v>
@@ -62972,16 +62972,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3056770963992281</v>
+        <v>0.3056770963992276</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02512392944114572</v>
+        <v>0.02512392944114575</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4836004785809395</v>
+        <v>0.48360047858094</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.571887198688558</v>
+        <v>-2.571887198688598</v>
       </c>
       <c r="AQ385" t="n">
         <v>22.65024038461538</v>
@@ -63125,28 +63125,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.117424820782309</v>
+        <v>7.117424820782308</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2204249848142918</v>
+        <v>-0.2204249848142901</v>
       </c>
       <c r="AK386" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL386" t="n">
-        <v>-0.2182210070512509</v>
+        <v>-0.21822100705125</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3083414575758074</v>
+        <v>0.3083414575758079</v>
       </c>
       <c r="AN386" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.474982443940299</v>
+        <v>0.4749824439402989</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.311874447286236</v>
+        <v>-2.311874447286193</v>
       </c>
       <c r="AQ386" t="n">
         <v>25.17604591987692</v>
@@ -63290,10 +63290,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.116315246651977</v>
+        <v>7.116315246651979</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.2198151360257565</v>
+        <v>-0.2198151360257583</v>
       </c>
       <c r="AK387" t="n">
         <v>7.112470209890858</v>
@@ -63302,16 +63302,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3094443575020182</v>
+        <v>0.3094443575020188</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.0257875072203187</v>
+        <v>0.02578750722031873</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.4671039145039241</v>
+        <v>0.467103914503924</v>
       </c>
       <c r="AP387" t="n">
-        <v>-2.246620026390865</v>
+        <v>-2.246620026390889</v>
       </c>
       <c r="AQ387" t="n">
         <v>24.97668997668998</v>
@@ -63455,28 +63455,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.109165799046384</v>
+        <v>7.109165799046382</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.1981660241135224</v>
+        <v>-0.1981660241135206</v>
       </c>
       <c r="AK388" t="n">
-        <v>7.105086649080124</v>
+        <v>7.105086649080123</v>
       </c>
       <c r="AL388" t="n">
-        <v>-0.1940868741472626</v>
+        <v>-0.1940868741472617</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3112159059696454</v>
+        <v>0.3112159059696449</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.02619128791084346</v>
+        <v>0.02619128791084347</v>
       </c>
       <c r="AO388" t="n">
-        <v>0.4597800393113445</v>
+        <v>0.4597800393113443</v>
       </c>
       <c r="AP388" t="n">
-        <v>-1.809041966473271</v>
+        <v>-1.809041966473231</v>
       </c>
       <c r="AQ388" t="n">
         <v>26.295701084773</v>
@@ -63620,10 +63620,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.140476658697598</v>
+        <v>7.14047665869759</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.2639765289978913</v>
+        <v>-0.2639765289978833</v>
       </c>
       <c r="AK389" t="n">
         <v>7.107009848336411</v>
@@ -63632,16 +63632,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3120213667410843</v>
+        <v>0.3120213667410841</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02660872919284657</v>
+        <v>0.02660872919284651</v>
       </c>
       <c r="AO389" t="n">
-        <v>0.4527828726277016</v>
+        <v>0.4527828726277021</v>
       </c>
       <c r="AP389" t="n">
-        <v>-2.92634131629074</v>
+        <v>-2.926341316290596</v>
       </c>
       <c r="AQ389" t="n">
         <v>18.93374038896427</v>
@@ -63785,10 +63785,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.192104266103097</v>
+        <v>7.192104266103096</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.3266042928059782</v>
+        <v>-0.3266042928059765</v>
       </c>
       <c r="AK390" t="n">
         <v>7.130667004235951</v>
@@ -63797,16 +63797,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3119580514589064</v>
+        <v>0.3119580514589062</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02723917591229313</v>
+        <v>0.02723917591229311</v>
       </c>
       <c r="AO390" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP390" t="n">
-        <v>-3.817928756740285</v>
+        <v>-3.817928756740258</v>
       </c>
       <c r="AQ390" t="n">
         <v>21.7989417989418</v>
@@ -63962,7 +63962,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3060770546706492</v>
+        <v>0.3060770546706496</v>
       </c>
       <c r="AN391" t="n">
         <v>0.02737088803905663</v>
@@ -63971,7 +63971,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.687217725798318</v>
+        <v>-3.687217725798322</v>
       </c>
       <c r="AQ391" t="n">
         <v>19.39749780509219</v>
@@ -64115,10 +64115,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.16410590848237</v>
+        <v>7.164105908482372</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.2680058642318812</v>
+        <v>-0.2680058642318839</v>
       </c>
       <c r="AK392" t="n">
         <v>7.162206823443969</v>
@@ -64127,16 +64127,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.3021518080029227</v>
+        <v>0.3021518080029217</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02724691784252931</v>
+        <v>0.02724691784252936</v>
       </c>
       <c r="AO392" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP392" t="n">
-        <v>-2.573346866416288</v>
+        <v>-2.573346866416331</v>
       </c>
       <c r="AQ392" t="n">
         <v>23.6874831035415</v>
@@ -64280,10 +64280,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.165713254747866</v>
+        <v>7.165713254747862</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.2102131288628559</v>
+        <v>-0.2102131288628524</v>
       </c>
       <c r="AK393" t="n">
         <v>7.141021818380439</v>
@@ -64292,16 +64292,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.3004913268435098</v>
+        <v>0.3004913268435102</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02739193077523433</v>
+        <v>0.02739193077523432</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3752726470948202</v>
+        <v>0.3752726470948199</v>
       </c>
       <c r="AP393" t="n">
-        <v>-1.627744531597144</v>
+        <v>-1.627744531597089</v>
       </c>
       <c r="AQ393" t="n">
         <v>30.46142369991475</v>
@@ -64445,10 +64445,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.208249532027229</v>
+        <v>7.208249532027231</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3219494450521312</v>
+        <v>-0.321949445052133</v>
       </c>
       <c r="AK394" t="n">
         <v>7.146296571548195</v>
@@ -64457,16 +64457,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2982197220770054</v>
+        <v>0.2982197220770058</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02742417953210363</v>
+        <v>0.02742417953210373</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3625782951332472</v>
+        <v>0.3625782951332475</v>
       </c>
       <c r="AP394" t="n">
-        <v>-3.256367936666931</v>
+        <v>-3.256367936666958</v>
       </c>
       <c r="AQ394" t="n">
         <v>25.16672793152339</v>
@@ -64610,28 +64610,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.193412187855718</v>
+        <v>7.193412187855726</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3208121092729543</v>
+        <v>-0.3208121092729623</v>
       </c>
       <c r="AK395" t="n">
-        <v>7.176497065376474</v>
+        <v>7.176497065376473</v>
       </c>
       <c r="AL395" t="n">
-        <v>-0.3038969867937107</v>
+        <v>-0.3038969867937098</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2910761841041076</v>
+        <v>0.2910761841041086</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02685747952387152</v>
+        <v>0.02685747952387156</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.3370674577034428</v>
+        <v>0.3370674577034442</v>
       </c>
       <c r="AP395" t="n">
-        <v>-3.112137549565402</v>
+        <v>-3.112137549565511</v>
       </c>
       <c r="AQ395" t="n">
         <v>26.06625258799172</v>
@@ -64775,10 +64775,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.227115602342048</v>
+        <v>7.227115602342041</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3273157785810614</v>
+        <v>-0.3273157785810543</v>
       </c>
       <c r="AK396" t="n">
         <v>7.185469892270627</v>
@@ -64787,16 +64787,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2812269987605887</v>
+        <v>0.281226998760588</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02697180537422167</v>
+        <v>0.0269718053742217</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.3136210223326478</v>
+        <v>0.3136210223326474</v>
       </c>
       <c r="AP396" t="n">
-        <v>-3.08574377662453</v>
+        <v>-3.085743776624427</v>
       </c>
       <c r="AQ396" t="n">
         <v>26.96821266391142</v>
@@ -64940,10 +64940,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.187163192389372</v>
+        <v>7.187163192389367</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3014629665592938</v>
+        <v>-0.3014629665592885</v>
       </c>
       <c r="AK397" t="n">
         <v>7.208338760609084</v>
@@ -64952,16 +64952,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2681836981576122</v>
+        <v>0.2681836981576121</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02658698789673936</v>
+        <v>0.02658698789673927</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.285908150945263</v>
+        <v>0.2859081509452629</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.637149998460412</v>
+        <v>-2.63714999846034</v>
       </c>
       <c r="AQ397" t="n">
         <v>27.82696177062374</v>
@@ -65105,10 +65105,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.214951953115591</v>
+        <v>7.214951953115579</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.334951838674673</v>
+        <v>-0.3349518386746606</v>
       </c>
       <c r="AK398" t="n">
         <v>7.186200492654655</v>
@@ -65117,16 +65117,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2591628297636744</v>
+        <v>0.2591628297636748</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02587977479594339</v>
+        <v>0.02587977479594331</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.266108201492412</v>
+        <v>0.2661082014924122</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.99635759486535</v>
+        <v>-2.996357594865196</v>
       </c>
       <c r="AQ398" t="n">
         <v>27.30000495957943</v>
@@ -65270,10 +65270,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.197430004066455</v>
+        <v>7.197430004066453</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.305630077308642</v>
+        <v>-0.3056300773086402</v>
       </c>
       <c r="AK399" t="n">
         <v>7.201835396295348</v>
@@ -65282,16 +65282,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2466333883508319</v>
+        <v>0.2466333883508324</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.0247654344950328</v>
+        <v>0.02476543449503272</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.2401258754735003</v>
+        <v>0.2401258754735008</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.528667553133092</v>
+        <v>-2.528667553133083</v>
       </c>
       <c r="AQ399" t="n">
         <v>26.02210485133021</v>
@@ -65438,25 +65438,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.3291230670577869</v>
+        <v>-0.3291230670577878</v>
       </c>
       <c r="AK400" t="n">
-        <v>7.179650721554484</v>
+        <v>7.179650721554483</v>
       </c>
       <c r="AL400" t="n">
-        <v>-0.2786506986663007</v>
+        <v>-0.2786506986662998</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2377807761788571</v>
+        <v>0.2377807761788565</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.02334020127887793</v>
+        <v>0.02334020127887796</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.2171758918683914</v>
+        <v>0.2171758918683913</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.756739116666435</v>
+        <v>-2.75673911666646</v>
       </c>
       <c r="AQ400" t="n">
         <v>26.55895828309622</v>
@@ -65600,10 +65600,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.20852803773295</v>
+        <v>7.208528037732954</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2978281933725988</v>
+        <v>-0.2978281933726024</v>
       </c>
       <c r="AK401" t="n">
         <v>7.206616000051887</v>
@@ -65612,16 +65612,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.2255544515066686</v>
+        <v>0.2255544515066683</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.0206724522626571</v>
+        <v>0.0206724522626572</v>
       </c>
       <c r="AO401" t="n">
-        <v>0.1898019966940717</v>
+        <v>0.1898019966940708</v>
       </c>
       <c r="AP401" t="n">
-        <v>-2.296876954307927</v>
+        <v>-2.296876954307982</v>
       </c>
       <c r="AQ401" t="n">
         <v>16.2718797564688</v>
@@ -65765,10 +65765,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.19880309223843</v>
+        <v>7.198803092238432</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.287202979323391</v>
+        <v>-0.2872029793233928</v>
       </c>
       <c r="AK402" t="n">
         <v>7.18051307481679</v>
@@ -65777,16 +65777,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.2150441262650612</v>
+        <v>0.2150441262650616</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.01774895516388914</v>
+        <v>0.0177489551638892</v>
       </c>
       <c r="AO402" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.119327753717743</v>
+        <v>-2.119327753717773</v>
       </c>
       <c r="AQ402" t="n">
         <v>14.77597935726015</v>
@@ -65930,10 +65930,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.172424239411004</v>
+        <v>7.172424239411002</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2608241264959652</v>
+        <v>-0.2608241264959634</v>
       </c>
       <c r="AK403" t="n">
         <v>7.16705299197773</v>
@@ -65942,16 +65942,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.205433651489446</v>
+        <v>0.2054336514894463</v>
       </c>
       <c r="AN403" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO403" t="n">
-        <v>0.1417286033373026</v>
+        <v>0.1417286033373033</v>
       </c>
       <c r="AP403" t="n">
-        <v>-1.759310618264857</v>
+        <v>-1.759310618264842</v>
       </c>
       <c r="AQ403" t="n">
         <v>18.77082562014069</v>
@@ -66095,10 +66095,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.163756390646672</v>
+        <v>7.163756390646673</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2695565424716229</v>
+        <v>-0.2695565424716238</v>
       </c>
       <c r="AK404" t="n">
         <v>7.153532751444382</v>
@@ -66107,16 +66107,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.1941661953581061</v>
+        <v>0.1941661953581056</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.01312004055850013</v>
+        <v>0.01312004055850015</v>
       </c>
       <c r="AO404" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.841567079186516</v>
+        <v>-1.841567079186534</v>
       </c>
       <c r="AQ404" t="n">
         <v>25.11528101173355</v>
@@ -66260,10 +66260,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.158063699621738</v>
+        <v>7.158063699621736</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2875636118837006</v>
+        <v>-0.2875636118836988</v>
       </c>
       <c r="AK405" t="n">
         <v>7.150669702211316</v>
@@ -66272,16 +66272,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1839494937266881</v>
+        <v>0.183949493726688</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.01194074338472806</v>
+        <v>0.01194074338472802</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.1107549805175829</v>
+        <v>0.110754980517583</v>
       </c>
       <c r="AP405" t="n">
-        <v>-2.03099915444689</v>
+        <v>-2.030999154446876</v>
       </c>
       <c r="AQ405" t="n">
         <v>13.12612612612613</v>
@@ -66425,10 +66425,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.157435208014563</v>
+        <v>7.157435208014565</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.272335320166663</v>
+        <v>-0.2723353201666647</v>
       </c>
       <c r="AK406" t="n">
         <v>7.140926852093823</v>
@@ -66437,16 +66437,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1753430411611933</v>
+        <v>0.1753430411611928</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.00971765423202034</v>
+        <v>0.009717654232020439</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.09620195025422695</v>
+        <v>0.09620195025422784</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.816085835102861</v>
+        <v>-1.816085835102889</v>
       </c>
       <c r="AQ406" t="n">
         <v>21.08315925152229</v>
@@ -66590,10 +66590,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.150386811340072</v>
+        <v>7.15038681134007</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2679867754819174</v>
+        <v>-0.2679867754819156</v>
       </c>
       <c r="AK407" t="n">
         <v>7.142886401315924</v>
@@ -66602,16 +66602,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1664838398737872</v>
+        <v>0.1664838398737869</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.008089376136153875</v>
+        <v>0.008089376136153925</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.0848962688609296</v>
+        <v>0.08489626886092971</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.739134136482415</v>
+        <v>-1.7391341364824</v>
       </c>
       <c r="AQ407" t="n">
         <v>20.59649122807017</v>
@@ -66755,10 +66755,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.137094841694645</v>
+        <v>7.137094841694642</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2547949416397133</v>
+        <v>-0.2547949416397106</v>
       </c>
       <c r="AK408" t="n">
         <v>7.137840883333127</v>
@@ -66767,16 +66767,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1571907956492611</v>
+        <v>0.1571907956492617</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.006581947594647974</v>
+        <v>0.006581947594647856</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.07412699588694804</v>
+        <v>0.07412699588694738</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.560440892271773</v>
+        <v>-1.560440892271748</v>
       </c>
       <c r="AQ408" t="n">
         <v>20.77868675063845</v>
@@ -66920,10 +66920,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.123391234435203</v>
+        <v>7.1233912344352</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2666912908927221</v>
+        <v>-0.2666912908927195</v>
       </c>
       <c r="AK409" t="n">
         <v>7.12862724785568</v>
@@ -66932,16 +66932,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1487097707294961</v>
+        <v>0.1487097707294973</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005441006961990014</v>
+        <v>0.005441006961990058</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.06531270865715677</v>
+        <v>0.06531270865715666</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.683353509644539</v>
+        <v>-1.683353509644515</v>
       </c>
       <c r="AQ409" t="n">
         <v>14.40105946684894</v>
@@ -67085,10 +67085,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.11600731855288</v>
+        <v>7.116007318552882</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2873072529400869</v>
+        <v>-0.2873072529400895</v>
       </c>
       <c r="AK410" t="n">
         <v>7.118961040191934</v>
@@ -67097,16 +67097,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM410" t="n">
-        <v>0.1409513724492178</v>
+        <v>0.1409513724492179</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005644373135176822</v>
+        <v>0.005644373135176906</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.05986577613532174</v>
+        <v>0.0598657761353214</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.902826462226918</v>
+        <v>-1.902826462226957</v>
       </c>
       <c r="AQ410" t="n">
         <v>10.08011806873287</v>
@@ -67250,10 +67250,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.115262454587763</v>
+        <v>7.11526245458776</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2838625369852235</v>
+        <v>-0.2838625369852208</v>
       </c>
       <c r="AK411" t="n">
         <v>7.113208458946866</v>
@@ -67265,13 +67265,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005618445165739616</v>
+        <v>0.005618445165739529</v>
       </c>
       <c r="AO411" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.835305502148032</v>
+        <v>-1.835305502148007</v>
       </c>
       <c r="AQ411" t="n">
         <v>8.707958707958708</v>
@@ -67427,16 +67427,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM412" t="n">
-        <v>0.1248427026608149</v>
+        <v>0.1248427026608145</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005050876420738246</v>
+        <v>0.005050876420738303</v>
       </c>
       <c r="AO412" t="n">
-        <v>0.04692762159458042</v>
+        <v>0.04692762159457986</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.750285662434824</v>
+        <v>-1.750285662434831</v>
       </c>
       <c r="AQ412" t="n">
         <v>13.8093281282104</v>
@@ -67580,10 +67580,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI413" t="n">
-        <v>7.100218718661557</v>
+        <v>7.100218718661558</v>
       </c>
       <c r="AJ413" t="n">
-        <v>-0.2699188643829924</v>
+        <v>-0.2699188643829933</v>
       </c>
       <c r="AK413" t="n">
         <v>7.105971078464224</v>
@@ -67595,13 +67595,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005209570180715356</v>
+        <v>0.00520957018071537</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.0421970173931332</v>
+        <v>0.04219701739313308</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.628242528710586</v>
+        <v>-1.628242528710603</v>
       </c>
       <c r="AQ413" t="n">
         <v>14.99513145082765</v>
@@ -67745,10 +67745,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.097935875054437</v>
+        <v>7.097935875054439</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2822358208857363</v>
+        <v>-0.2822358208857381</v>
       </c>
       <c r="AK414" t="n">
         <v>7.101361129315627</v>
@@ -67757,16 +67757,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.1117472247487875</v>
+        <v>0.1117472247487876</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.005385102682029907</v>
+        <v>0.005385102682029925</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.03866992220359</v>
+        <v>0.03866992220359033</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.749707041474974</v>
+        <v>-1.749707041475001</v>
       </c>
       <c r="AQ414" t="n">
         <v>13.95264992188439</v>
@@ -67910,10 +67910,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI415" t="n">
-        <v>7.097978821692022</v>
+        <v>7.097978821692021</v>
       </c>
       <c r="AJ415" t="n">
-        <v>-0.2799789819093075</v>
+        <v>-0.2799789819093057</v>
       </c>
       <c r="AK415" t="n">
         <v>7.099648834314064</v>
@@ -67922,16 +67922,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.1065475925362033</v>
+        <v>0.1065475925362025</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005956926407440957</v>
+        <v>0.005956926407441003</v>
       </c>
       <c r="AO415" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.702251341870201</v>
+        <v>-1.702251341870187</v>
       </c>
       <c r="AQ415" t="n">
         <v>13.86075949367089</v>
@@ -68087,16 +68087,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.1013724682419977</v>
+        <v>0.1013724682419976</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.006126167203105798</v>
+        <v>0.006126167203105847</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.03348722035246332</v>
+        <v>0.03348722035246277</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.540086272869379</v>
+        <v>-1.540086272869385</v>
       </c>
       <c r="AQ416" t="n">
         <v>22.55166217430368</v>
@@ -68240,10 +68240,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI417" t="n">
-        <v>7.087097940453345</v>
+        <v>7.087097940453343</v>
       </c>
       <c r="AJ417" t="n">
-        <v>-0.2700980281913825</v>
+        <v>-0.2700980281913798</v>
       </c>
       <c r="AK417" t="n">
         <v>7.090805518999606</v>
@@ -68252,16 +68252,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.09919462776856321</v>
+        <v>0.09919462776856289</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.006113943880485972</v>
+        <v>0.006113943880485968</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.03204155062895153</v>
+        <v>0.03204155062895098</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.554670831775283</v>
+        <v>-1.554670831775259</v>
       </c>
       <c r="AQ417" t="n">
         <v>17.4266975308642</v>
@@ -68417,16 +68417,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.097507502547015</v>
+        <v>0.09750750254701511</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.005510714664730507</v>
+        <v>0.005510714664730422</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.03001455024934374</v>
+        <v>0.03001455024934274</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.613360789246392</v>
+        <v>-1.613360789246399</v>
       </c>
       <c r="AQ418" t="n">
         <v>14.21712456655108</v>
@@ -68582,16 +68582,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.09380549503386901</v>
+        <v>0.09380549503386949</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.004784904607979881</v>
+        <v>0.004784904607979855</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.02699383492044782</v>
+        <v>0.02699383492044827</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.570592769098327</v>
+        <v>-1.570592769098333</v>
       </c>
       <c r="AQ419" t="n">
         <v>17.8297199638663</v>
@@ -68735,10 +68735,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.097145375663951</v>
+        <v>7.097145375663948</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2729452223131208</v>
+        <v>-0.2729452223131181</v>
       </c>
       <c r="AK420" t="n">
         <v>7.093828611034739</v>
@@ -68747,16 +68747,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.08945254406056438</v>
+        <v>0.08945254406056392</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.004001520125414798</v>
+        <v>0.004001520125414807</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.02385555423225116</v>
+        <v>0.02385555423225172</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.536594443203972</v>
+        <v>-1.536594443203949</v>
       </c>
       <c r="AQ420" t="n">
         <v>22.01152630600483</v>
@@ -68900,10 +68900,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.088227962421951</v>
+        <v>7.088227962421954</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.262227748798904</v>
+        <v>-0.2622277487989066</v>
       </c>
       <c r="AK421" t="n">
         <v>7.092951699003613</v>
@@ -68912,16 +68912,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.07912491692886899</v>
+        <v>0.07912491692886864</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.003813743757049903</v>
+        <v>0.003813743757049957</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.01902803623666316</v>
+        <v>0.01902803623666371</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.402662234957516</v>
+        <v>-1.402662234957552</v>
       </c>
       <c r="AQ421" t="n">
         <v>34.95077872465472</v>
@@ -69065,10 +69065,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.082675656384673</v>
+        <v>7.082675656384675</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2467758265201709</v>
+        <v>-0.2467758265201727</v>
       </c>
       <c r="AK422" t="n">
         <v>7.085940899278786</v>
@@ -69077,16 +69077,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.07019093860911668</v>
+        <v>0.07019093860911679</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.003788844982403339</v>
+        <v>0.003788844982403293</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.01530727852465064</v>
+        <v>0.0153072785246503</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.219255624926024</v>
+        <v>-1.219255624926049</v>
       </c>
       <c r="AQ422" t="n">
         <v>32.91054255126112</v>
@@ -69230,10 +69230,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.082585232341567</v>
+        <v>7.082585232341569</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2597850728872215</v>
+        <v>-0.2597850728872233</v>
       </c>
       <c r="AK423" t="n">
         <v>7.080231185021037</v>
@@ -69242,16 +69242,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.0607230145131474</v>
+        <v>0.06072301451314636</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.003218097337044118</v>
+        <v>0.003218097337044184</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.01127031184523342</v>
+        <v>0.01127031184523331</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.354123018284604</v>
+        <v>-1.354123018284628</v>
       </c>
       <c r="AQ423" t="n">
         <v>33.01778542742398</v>
@@ -69395,10 +69395,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.082752176397555</v>
+        <v>7.082752176397554</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2453522168333464</v>
+        <v>-0.2453522168333455</v>
       </c>
       <c r="AK424" t="n">
         <v>7.078545045220129</v>
@@ -69407,16 +69407,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.04987769893955558</v>
+        <v>0.04987769893955601</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.002647769861786137</v>
+        <v>0.002647769861786034</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.00755590738572276</v>
+        <v>0.007555907385723093</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.183549452314946</v>
+        <v>-1.183549452314941</v>
       </c>
       <c r="AQ424" t="n">
         <v>34.60652659178685</v>
@@ -69560,10 +69560,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI425" t="n">
-        <v>7.073418742129174</v>
+        <v>7.073418742129173</v>
       </c>
       <c r="AJ425" t="n">
-        <v>-0.2359186467617427</v>
+        <v>-0.2359186467617418</v>
       </c>
       <c r="AK425" t="n">
         <v>7.075576762908686</v>
@@ -69572,16 +69572,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.03723342047483359</v>
+        <v>0.03723342047483347</v>
       </c>
       <c r="AN425" t="n">
-        <v>0.0007434096776329363</v>
+        <v>0.0007434096776329864</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.003691827899839573</v>
+        <v>0.003691827899840794</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.070919300606854</v>
+        <v>-1.070919300606848</v>
       </c>
       <c r="AQ425" t="n">
         <v>37.07633053221289</v>
@@ -69737,16 +69737,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM426" t="n">
-        <v>0.02391394499985428</v>
+        <v>0.02391394499985489</v>
       </c>
       <c r="AN426" t="n">
-        <v>0.0004638728584110997</v>
+        <v>0.0004638728584110585</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.00150427765126282</v>
+        <v>0.001504277651263042</v>
       </c>
       <c r="AP426" t="n">
-        <v>-1.11050563204875</v>
+        <v>-1.110505632048755</v>
       </c>
       <c r="AQ426" t="n">
         <v>34.78667081905948</v>
@@ -69890,10 +69890,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI427" t="n">
-        <v>7.061175551975939</v>
+        <v>7.06117555197594</v>
       </c>
       <c r="AJ427" t="n">
-        <v>-0.2336756854903435</v>
+        <v>-0.2336756854903443</v>
       </c>
       <c r="AK427" t="n">
         <v>7.061105294515807</v>
@@ -69902,16 +69902,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM427" t="n">
-        <v>0.01023096587809661</v>
+        <v>0.01023096587809607</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.0001641525470544823</v>
+        <v>-0.0001641525470544615</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.0002530929795961923</v>
+        <v>0.000253092979595082</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.032242914660647</v>
+        <v>-1.032242914660661</v>
       </c>
       <c r="AQ427" t="n">
         <v>39.87004103967168</v>
@@ -70067,16 +70067,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.001349940557734956</v>
+        <v>-0.001349940557734529</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.001242569541730382</v>
+        <v>-0.001242569541730301</v>
       </c>
       <c r="AO428" t="n">
-        <v>9.828375502929365e-05</v>
+        <v>9.828375502973774e-05</v>
       </c>
       <c r="AP428" t="n">
-        <v>-0.9364901210219889</v>
+        <v>-0.9364901210219928</v>
       </c>
       <c r="AQ428" t="n">
         <v>40.21566440185241</v>
@@ -70220,10 +70220,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.051845784111939</v>
+        <v>7.051845784111937</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2217457246026617</v>
+        <v>-0.22174572460266</v>
       </c>
       <c r="AK429" t="n">
         <v>7.04924004450221</v>
@@ -70232,16 +70232,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.01245927794565087</v>
+        <v>-0.0124592779456514</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.002690846636687106</v>
+        <v>-0.002690846636687166</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.0009149443224345521</v>
+        <v>0.000914944322433886</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.8888893481318413</v>
+        <v>-0.8888893481318249</v>
       </c>
       <c r="AQ429" t="n">
         <v>37.07230686982091</v>
@@ -70385,10 +70385,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.044932512363691</v>
+        <v>7.044932512363692</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.2339326420633983</v>
+        <v>-0.2339326420633991</v>
       </c>
       <c r="AK430" t="n">
         <v>7.044607485549974</v>
@@ -70397,16 +70397,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.02351974718911197</v>
+        <v>-0.0235197471891116</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.003286981705062079</v>
+        <v>-0.003286981705062081</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.002235402288773947</v>
+        <v>0.002235402288773058</v>
       </c>
       <c r="AP430" t="n">
-        <v>-1.019515488213925</v>
+        <v>-1.019515488213939</v>
       </c>
       <c r="AQ430" t="n">
         <v>35.1345995045417</v>
@@ -70550,10 +70550,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.041380724566422</v>
+        <v>7.04138072456642</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2399805399350745</v>
+        <v>-0.2399805399350727</v>
       </c>
       <c r="AK431" t="n">
         <v>7.036677431055121</v>
@@ -70562,16 +70562,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.03604973348542533</v>
+        <v>-0.03604973348542571</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003896888881646653</v>
+        <v>-0.003896888881646666</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.004508577134016534</v>
+        <v>0.004508577134016423</v>
       </c>
       <c r="AP431" t="n">
-        <v>-1.080586188982384</v>
+        <v>-1.080586188982368</v>
       </c>
       <c r="AQ431" t="n">
         <v>27.75274294670847</v>
@@ -70715,10 +70715,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.031781164871437</v>
+        <v>7.031781164871438</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2312812487947769</v>
+        <v>-0.2312812487947777</v>
       </c>
       <c r="AK432" t="n">
         <v>7.031531243279009</v>
@@ -70727,16 +70727,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.0496421115884523</v>
+        <v>-0.04964211158845258</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003622848094475932</v>
+        <v>-0.003622848094475877</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.007358432861332531</v>
+        <v>0.007358432861333086</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.9776792404870553</v>
+        <v>-0.9776792404870693</v>
       </c>
       <c r="AQ432" t="n">
         <v>35.29620661824052</v>
@@ -70892,16 +70892,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.06336633742876464</v>
+        <v>-0.06336633742876532</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.00383222203166729</v>
+        <v>-0.003832222031667326</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.0113935335626284</v>
+        <v>0.01139353356262962</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.9077068786391019</v>
+        <v>-0.9077068786391058</v>
       </c>
       <c r="AQ433" t="n">
         <v>35.93909601634321</v>
@@ -71045,10 +71045,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI434" t="n">
-        <v>7.012358254068223</v>
+        <v>7.012358254068221</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.220358437173692</v>
+        <v>-0.2203584371736902</v>
       </c>
       <c r="AK434" t="n">
         <v>7.010266108789461</v>
@@ -71057,16 +71057,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.07815930192347351</v>
+        <v>-0.07815930192347212</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.0037302018478894</v>
+        <v>-0.003730201847889384</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.01669360800688513</v>
+        <v>0.01669360800688602</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.8464978886523586</v>
+        <v>-0.8464978886523424</v>
       </c>
       <c r="AQ434" t="n">
         <v>35.15923365842881</v>
@@ -71210,10 +71210,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI435" t="n">
-        <v>7.001516536947593</v>
+        <v>7.001516536947591</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.2107164423431005</v>
+        <v>-0.2107164423430987</v>
       </c>
       <c r="AK435" t="n">
         <v>7.003692382618654</v>
@@ -71222,16 +71222,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.09225745624393369</v>
+        <v>-0.09225745624393285</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.003729646461095512</v>
+        <v>-0.003729646461095566</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.02283737241168637</v>
+        <v>0.02283737241168682</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.7351651051066752</v>
+        <v>-0.7351651051066588</v>
       </c>
       <c r="AQ435" t="n">
         <v>39.72846441947566</v>
@@ -71375,10 +71375,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI436" t="n">
-        <v>6.98285303226683</v>
+        <v>6.982853032266831</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.1977530490514976</v>
+        <v>-0.1977530490514985</v>
       </c>
       <c r="AK436" t="n">
         <v>6.994908837140057</v>
@@ -71387,16 +71387,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.1040956648961724</v>
+        <v>-0.1040956648961739</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.004775368000139335</v>
+        <v>-0.004775368000139281</v>
       </c>
       <c r="AO436" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.5873560645130924</v>
+        <v>-0.5873560645131055</v>
       </c>
       <c r="AQ436" t="n">
         <v>40.89169418809222</v>
@@ -71540,10 +71540,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.976537964100197</v>
+        <v>6.976537964100195</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1673381540721204</v>
+        <v>-0.1673381540721186</v>
       </c>
       <c r="AK437" t="n">
         <v>6.976048621620001</v>
@@ -71552,16 +71552,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1171809788132883</v>
+        <v>-0.1171809788132892</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.006568629287185546</v>
+        <v>-0.006568629287185491</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.03914952746580425</v>
+        <v>0.03914952746580436</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.244365528744401</v>
+        <v>-0.2443655287443834</v>
       </c>
       <c r="AQ437" t="n">
         <v>48.68742368742369</v>
@@ -71708,7 +71708,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1582257113591101</v>
+        <v>-0.1582257113591092</v>
       </c>
       <c r="AK438" t="n">
         <v>6.970728111892008</v>
@@ -71717,16 +71717,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.127636816539944</v>
+        <v>-0.127636816539943</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.007451019732577668</v>
+        <v>-0.00745101973257774</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.04750067483060583</v>
+        <v>0.04750067483060572</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.1411566897223107</v>
+        <v>-0.1411566897223032</v>
       </c>
       <c r="AQ438" t="n">
         <v>49.78866648552365</v>
@@ -71885,13 +71885,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.008628156625160088</v>
+        <v>-0.008628156625160163</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.05751510742764043</v>
+        <v>0.05751510742764121</v>
       </c>
       <c r="AP439" t="n">
-        <v>-0.02985731997459472</v>
+        <v>-0.02985731997459668</v>
       </c>
       <c r="AQ439" t="n">
         <v>51.95891065456283</v>
@@ -72035,10 +72035,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.950644730799358</v>
+        <v>6.950644730799363</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1501448147226974</v>
+        <v>-0.1501448147227027</v>
       </c>
       <c r="AK440" t="n">
         <v>6.959853578800648</v>
@@ -72047,16 +72047,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1469566450661546</v>
+        <v>-0.1469566450661556</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.009026348114251986</v>
+        <v>-0.009026348114251901</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.06603756167960417</v>
+        <v>0.06603756167960351</v>
       </c>
       <c r="AP440" t="n">
-        <v>-0.04957227832841285</v>
+        <v>-0.04957227832847518</v>
       </c>
       <c r="AQ440" t="n">
         <v>49.76960567124502</v>
@@ -72200,28 +72200,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.934622414140156</v>
+        <v>6.934622414140152</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1321226430219919</v>
+        <v>-0.1321226430219875</v>
       </c>
       <c r="AK441" t="n">
-        <v>6.94711441643572</v>
+        <v>6.947114416435721</v>
       </c>
       <c r="AL441" t="n">
-        <v>-0.1446146453175556</v>
+        <v>-0.1446146453175565</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1568781652619925</v>
+        <v>-0.1568781652619921</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.010042871337475</v>
+        <v>-0.01004287133747513</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.07699206242755485</v>
+        <v>0.07699206242755419</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.1550111672272632</v>
+        <v>0.1550111672273127</v>
       </c>
       <c r="AQ441" t="n">
         <v>58.94401589527817</v>
@@ -72365,10 +72365,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.928042396530076</v>
+        <v>6.928042396530073</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1335425224150857</v>
+        <v>-0.133542522415083</v>
       </c>
       <c r="AK442" t="n">
         <v>6.933186989735641</v>
@@ -72377,16 +72377,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1650917115670576</v>
+        <v>-0.1650917115670582</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.0106149464753251</v>
+        <v>-0.01061494647532512</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.08732871254562191</v>
+        <v>0.08732871254562202</v>
       </c>
       <c r="AP442" t="n">
-        <v>0.1384398386498393</v>
+        <v>0.1384398386498683</v>
       </c>
       <c r="AQ442" t="n">
         <v>55.65399624223154</v>
@@ -72530,10 +72530,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.941461393298105</v>
+        <v>6.941461393298106</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1469615191831144</v>
+        <v>-0.1469615191831153</v>
       </c>
       <c r="AK443" t="n">
         <v>6.925995477801935</v>
@@ -72542,16 +72542,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.1745447047691483</v>
+        <v>-0.1745447047691478</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01108963812755723</v>
+        <v>-0.01108963812755724</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.09935205695041804</v>
+        <v>0.09935205695041927</v>
       </c>
       <c r="AP443" t="n">
-        <v>-0.01497644213845123</v>
+        <v>-0.01497644213846336</v>
       </c>
       <c r="AQ443" t="n">
         <v>49.22214596202242</v>
@@ -72695,10 +72695,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.93323210397643</v>
+        <v>6.933232103976423</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1472323290435682</v>
+        <v>-0.147232329043562</v>
       </c>
       <c r="AK444" t="n">
         <v>6.938996539173566</v>
@@ -72707,16 +72707,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.1853013335308036</v>
+        <v>-0.1853013335308053</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01193987645426134</v>
+        <v>-0.01193987645426136</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1123648810347069</v>
+        <v>0.1123648810347067</v>
       </c>
       <c r="AP444" t="n">
-        <v>-0.01803400433169996</v>
+        <v>-0.01803400433163076</v>
       </c>
       <c r="AQ444" t="n">
         <v>44.95232436408907</v>
@@ -72860,10 +72860,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.928429644379657</v>
+        <v>6.928429644379658</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1496296336985043</v>
+        <v>-0.1496296336985061</v>
       </c>
       <c r="AK445" t="n">
         <v>6.93160690101155</v>
@@ -72875,13 +72875,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01257308415669778</v>
+        <v>-0.01257308415669775</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.125857898472412</v>
+        <v>0.1258578984724115</v>
       </c>
       <c r="AP445" t="n">
-        <v>-0.04547613693365601</v>
+        <v>-0.04547613693367852</v>
       </c>
       <c r="AQ445" t="n">
         <v>45.25195968645016</v>
@@ -73025,10 +73025,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.925068850639515</v>
+        <v>6.925068850639512</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1455688430101203</v>
+        <v>-0.1455688430101176</v>
       </c>
       <c r="AK446" t="n">
         <v>6.924763510572069</v>
@@ -73037,16 +73037,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM446" t="n">
-        <v>-0.2060805417157788</v>
+        <v>-0.2060805417157789</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01318646791849926</v>
+        <v>-0.01318646791849928</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1396251026736655</v>
+        <v>0.1396251026736647</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.001331178123722838</v>
+        <v>0.001331178123751393</v>
       </c>
       <c r="AQ446" t="n">
         <v>48.95703482090916</v>
@@ -73190,10 +73190,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.900929863197374</v>
+        <v>6.900929863197373</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1347297975845807</v>
+        <v>-0.1347297975845798</v>
       </c>
       <c r="AK447" t="n">
         <v>6.921049732547429</v>
@@ -73202,16 +73202,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2151279705591488</v>
+        <v>-0.2151279705591481</v>
       </c>
       <c r="AN447" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1518365696223548</v>
+        <v>0.1518365696223549</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.1262747588338355</v>
+        <v>0.1262747588338435</v>
       </c>
       <c r="AQ447" t="n">
         <v>49.97532894736842</v>
@@ -73355,10 +73355,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.895219010181459</v>
+        <v>6.89521901018146</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1302191436958635</v>
+        <v>-0.1302191436958644</v>
       </c>
       <c r="AK448" t="n">
         <v>6.89978353884127</v>
@@ -73370,13 +73370,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01278923357027009</v>
+        <v>-0.01278923357027006</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1644177475946104</v>
+        <v>0.1644177475946105</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.1780680365315467</v>
+        <v>0.1780680365315346</v>
       </c>
       <c r="AQ448" t="n">
         <v>47.61278246480211</v>
@@ -73520,10 +73520,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.879512239848579</v>
+        <v>6.87951223984858</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.1173123611559523</v>
+        <v>-0.1173123611559532</v>
       </c>
       <c r="AK449" t="n">
         <v>6.893260360395011</v>
@@ -73532,16 +73532,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.233692768734329</v>
+        <v>-0.233692768734328</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01245257184765153</v>
+        <v>-0.01245257184765156</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.179129523332087</v>
+        <v>0.1791295233320875</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.3270752588397787</v>
+        <v>0.3270752588397669</v>
       </c>
       <c r="AQ449" t="n">
         <v>51.00408075601375</v>
@@ -73685,10 +73685,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.882426232260446</v>
+        <v>6.882426232260437</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.1132263840853973</v>
+        <v>-0.1132263840853884</v>
       </c>
       <c r="AK450" t="n">
         <v>6.880758546638964</v>
@@ -73697,16 +73697,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.2433281856134891</v>
+        <v>-0.2433281856134888</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01202813951384066</v>
+        <v>-0.01202813951384067</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.1944608722019401</v>
+        <v>0.1944608722019407</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.3735609578737231</v>
+        <v>0.3735609578738251</v>
       </c>
       <c r="AQ450" t="n">
         <v>52.54948850803774</v>
@@ -73862,16 +73862,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2520264427810588</v>
+        <v>-0.25202644278106</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01246671652825437</v>
+        <v>-0.01246671652825434</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.2101991144027906</v>
+        <v>0.2101991144027905</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.9396869993792598</v>
+        <v>0.939686999379259</v>
       </c>
       <c r="AQ451" t="n">
         <v>65.32979171049863</v>
@@ -74015,10 +74015,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.841963898035317</v>
+        <v>6.841963898035326</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.07646382937076623</v>
+        <v>-0.07646382937077512</v>
       </c>
       <c r="AK452" t="n">
         <v>6.844785316397215</v>
@@ -74027,16 +74027,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2592973891940562</v>
+        <v>-0.2592973891940566</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01305068899435097</v>
+        <v>-0.01305068899435077</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2277185089957531</v>
+        <v>0.2277185089957524</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.7946882605952149</v>
+        <v>0.794688260595111</v>
       </c>
       <c r="AQ452" t="n">
         <v>58.60471170115841</v>
@@ -74180,28 +74180,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.845644916883085</v>
+        <v>6.845644916883079</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.08014484821853429</v>
+        <v>-0.08014484821852808</v>
       </c>
       <c r="AK453" t="n">
-        <v>6.849407886968131</v>
+        <v>6.849407886968132</v>
       </c>
       <c r="AL453" t="n">
-        <v>-0.08390781830358041</v>
+        <v>-0.08390781830358129</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.2668003223256257</v>
+        <v>-0.2668003223256254</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01367989020054944</v>
+        <v>-0.0136798902005495</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2456601220977563</v>
+        <v>0.2456601220977566</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7487140043297179</v>
+        <v>0.7487140043297899</v>
       </c>
       <c r="AQ453" t="n">
         <v>58.31271902700475</v>
@@ -74345,10 +74345,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.842084108625032</v>
+        <v>6.842084108625038</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.0695840704780597</v>
+        <v>-0.06958407047806503</v>
       </c>
       <c r="AK454" t="n">
         <v>6.852702018840203</v>
@@ -74357,16 +74357,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2735436467318143</v>
+        <v>-0.273543646731814</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.01403412282467997</v>
+        <v>-0.01403412282467991</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.2619835102172253</v>
+        <v>0.261983510217226</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.8683972750773455</v>
+        <v>0.8683972750772836</v>
       </c>
       <c r="AQ454" t="n">
         <v>63.58441955972757</v>
@@ -74510,10 +74510,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.863831060847773</v>
+        <v>6.863831060847785</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.09133102270080062</v>
+        <v>-0.09133102270081217</v>
       </c>
       <c r="AK455" t="n">
         <v>6.850973969550408</v>
@@ -74522,16 +74522,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.2787367835501612</v>
+        <v>-0.2787367835501617</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01406387644726603</v>
+        <v>-0.01406387644726588</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.2758112468611987</v>
+        <v>0.2758112468611976</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.6117510238643564</v>
+        <v>0.6117510238642219</v>
       </c>
       <c r="AQ455" t="n">
         <v>62.5530303030303</v>
@@ -74675,10 +74675,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.853037915615571</v>
+        <v>6.853037915615573</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.07753809490634289</v>
+        <v>-0.07753809490634467</v>
       </c>
       <c r="AK456" t="n">
         <v>6.873527983489108</v>
@@ -74690,13 +74690,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.013790177185657</v>
+        <v>-0.01379017718565697</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.285442546377481</v>
+        <v>0.2854425463774817</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.7703772441622895</v>
+        <v>0.7703772441622695</v>
       </c>
       <c r="AQ456" t="n">
         <v>68.73796844921122</v>
@@ -74852,7 +74852,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2865252693972544</v>
+        <v>-0.2865252693972545</v>
       </c>
       <c r="AN457" t="n">
         <v>-0.01327380582108439</v>
@@ -74861,7 +74861,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP457" t="n">
-        <v>0.5720048978375456</v>
+        <v>0.5720048978375459</v>
       </c>
       <c r="AQ457" t="n">
         <v>61.93811881188119</v>
@@ -75005,10 +75005,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.860047631936786</v>
+        <v>6.860047631936787</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.1030476624543644</v>
+        <v>-0.1030476624543653</v>
       </c>
       <c r="AK458" t="n">
         <v>6.865985861260643</v>
@@ -75017,16 +75017,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.290522309347949</v>
+        <v>-0.2905223093479492</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.01240158194086383</v>
+        <v>-0.01240158194086378</v>
       </c>
       <c r="AO458" t="n">
-        <v>0.3024992257449916</v>
+        <v>0.3024992257449914</v>
       </c>
       <c r="AP458" t="n">
-        <v>0.4675645678050873</v>
+        <v>0.4675645678050772</v>
       </c>
       <c r="AQ458" t="n">
         <v>58.16851702080729</v>
@@ -75170,10 +75170,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.801980414635013</v>
+        <v>6.801980414635016</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.04478065038330392</v>
+        <v>-0.04478065038330659</v>
       </c>
       <c r="AK459" t="n">
         <v>6.863576603094304</v>
@@ -75182,16 +75182,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.2950697019949103</v>
+        <v>-0.2950697019949104</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.0116105331596838</v>
+        <v>-0.01161053315968381</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3113800696686924</v>
+        <v>0.3113800696686918</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.14722151151879</v>
+        <v>1.147221511518761</v>
       </c>
       <c r="AQ459" t="n">
         <v>79.24917491749174</v>
@@ -75335,10 +75335,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.789283666813423</v>
+        <v>6.789283666813422</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.03208390256171434</v>
+        <v>-0.03208390256171256</v>
       </c>
       <c r="AK460" t="n">
         <v>6.809671190627447</v>
@@ -75347,16 +75347,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.2987092362344105</v>
+        <v>-0.2987092362344108</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.01030385953714813</v>
+        <v>-0.01030385953714808</v>
       </c>
       <c r="AO460" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.28818749803842</v>
+        <v>1.288187498038444</v>
       </c>
       <c r="AQ460" t="n">
         <v>82.03652529136127</v>
@@ -75500,10 +75500,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.789252537988938</v>
+        <v>6.789252537988933</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.02065255095890883</v>
+        <v>-0.0206525509589035</v>
       </c>
       <c r="AK461" t="n">
         <v>6.802840448144932</v>
@@ -75512,16 +75512,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3027504956929287</v>
+        <v>-0.3027504956929284</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.00881278602540958</v>
+        <v>-0.008812786025409641</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.332227117067963</v>
+        <v>0.3322271170679635</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.412097260525123</v>
+        <v>1.412097260525188</v>
       </c>
       <c r="AQ461" t="n">
         <v>83.09775366457262</v>
@@ -75665,10 +75665,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.774001672255927</v>
+        <v>6.774001672255932</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.005401685225897346</v>
+        <v>-0.005401685225902675</v>
       </c>
       <c r="AK462" t="n">
         <v>6.800260207803535</v>
@@ -75677,16 +75677,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3068099364477369</v>
+        <v>-0.3068099364477367</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.007070247176567734</v>
+        <v>-0.007070247176567688</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.3427146952658529</v>
+        <v>0.3427146952658534</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.577343453912065</v>
+        <v>1.577343453912008</v>
       </c>
       <c r="AQ462" t="n">
         <v>83.90243902439025</v>
@@ -75830,10 +75830,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.802628307046305</v>
+        <v>6.802628307046303</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.0281284138578286</v>
+        <v>-0.02812841385782594</v>
       </c>
       <c r="AK463" t="n">
         <v>6.781970485204615</v>
@@ -75842,16 +75842,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3121566752204096</v>
+        <v>-0.3121566752204101</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.005102880740085192</v>
+        <v>-0.005102880740085154</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3560731605465752</v>
+        <v>0.3560731605465757</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.303420740488044</v>
+        <v>1.303420740488078</v>
       </c>
       <c r="AQ463" t="n">
         <v>79.87303958177745</v>
@@ -75995,28 +75995,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.815944895083629</v>
+        <v>6.815944895083632</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.0259449332306021</v>
+        <v>-0.02594493323060476</v>
       </c>
       <c r="AK464" t="n">
-        <v>6.809638458820509</v>
+        <v>6.809638458820508</v>
       </c>
       <c r="AL464" t="n">
-        <v>-0.01963849696748188</v>
+        <v>-0.01963849696748099</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3181413841564625</v>
+        <v>-0.3181413841564619</v>
       </c>
       <c r="AN464" t="n">
-        <v>-0.003317316385138602</v>
+        <v>-0.003317316385138562</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.3690689225934927</v>
+        <v>0.3690689225934922</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.320112988335384</v>
+        <v>1.320112988335356</v>
       </c>
       <c r="AQ464" t="n">
         <v>81.66100362896702</v>
@@ -76160,10 +76160,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.821941449304759</v>
+        <v>6.821941449304753</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.0319414874517312</v>
+        <v>-0.03194148745172587</v>
       </c>
       <c r="AK465" t="n">
         <v>6.819973703544699</v>
@@ -76172,16 +76172,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3244228225822193</v>
+        <v>-0.3244228225822198</v>
       </c>
       <c r="AN465" t="n">
-        <v>-0.001700148658338674</v>
+        <v>-0.001700148658338742</v>
       </c>
       <c r="AO465" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.242734811900659</v>
+        <v>1.242734811900723</v>
       </c>
       <c r="AQ465" t="n">
         <v>78.39056776556777</v>
@@ -76325,10 +76325,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.826413262727742</v>
+        <v>6.826413262727749</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.03641330087471495</v>
+        <v>-0.03641330087472205</v>
       </c>
       <c r="AK466" t="n">
         <v>6.822087900644207</v>
@@ -76337,16 +76337,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3308797299382499</v>
+        <v>-0.3308797299382495</v>
       </c>
       <c r="AN466" t="n">
-        <v>-7.481797733216444e-05</v>
+        <v>-7.481797733213274e-05</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.3960788710418811</v>
+        <v>0.396078871041881</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.18397024508706</v>
+        <v>1.183970245086981</v>
       </c>
       <c r="AQ466" t="n">
         <v>78.98365042291209</v>
@@ -76490,10 +76490,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.812656647679548</v>
+        <v>6.81265664767955</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.01465678882334664</v>
+        <v>-0.01465678882334931</v>
       </c>
       <c r="AK467" t="n">
         <v>6.823881638371397</v>
@@ -76502,16 +76502,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3363418922753055</v>
+        <v>-0.3363418922753058</v>
       </c>
       <c r="AN467" t="n">
-        <v>0.001379920606120022</v>
+        <v>0.001379920606120097</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4081029523904164</v>
+        <v>0.4081029523904167</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.426200199707695</v>
+        <v>1.426200199707669</v>
       </c>
       <c r="AQ467" t="n">
         <v>83.57816711590297</v>
@@ -76655,10 +76655,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.802797817425507</v>
+        <v>6.802797817425505</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.009197735028045884</v>
+        <v>-0.009197735028044107</v>
       </c>
       <c r="AK468" t="n">
         <v>6.808320681191073</v>
@@ -76667,16 +76667,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3410659803634685</v>
+        <v>-0.3410659803634682</v>
       </c>
       <c r="AN468" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4198133218741356</v>
+        <v>0.4198133218741357</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.478216789207188</v>
+        <v>1.478216789207213</v>
       </c>
       <c r="AQ468" t="n">
         <v>83.65373918074005</v>
@@ -76826,22 +76826,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK469" t="n">
-        <v>6.795980661778267</v>
+        <v>6.795980661778266</v>
       </c>
       <c r="AL469" t="n">
-        <v>-0.002380579380806047</v>
+        <v>-0.002380579380805159</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3461577281601511</v>
+        <v>-0.3461577281601509</v>
       </c>
       <c r="AN469" t="n">
-        <v>0.004282887883574671</v>
+        <v>0.00428288788357468</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4328049372030962</v>
+        <v>0.4328049372030969</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.539467082609258</v>
+        <v>1.539467082609263</v>
       </c>
       <c r="AQ469" t="n">
         <v>84.90566037735849</v>
@@ -76985,10 +76985,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.800189882196235</v>
+        <v>6.800189882196236</v>
       </c>
       <c r="AJ470" t="n">
-        <v>-0.005989938653754301</v>
+        <v>-0.005989938653755189</v>
       </c>
       <c r="AK470" t="n">
         <v>6.78726841810145</v>
@@ -76997,16 +76997,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3502903933401412</v>
+        <v>-0.3502903933401418</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.005405808652032051</v>
+        <v>0.005405808652032067</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4450018361960529</v>
+        <v>0.4450018361960534</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.491748497297388</v>
+        <v>1.491748497297383</v>
       </c>
       <c r="AQ470" t="n">
         <v>83.80718419041381</v>
@@ -77150,10 +77150,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.79797208364255</v>
+        <v>6.797972083642554</v>
       </c>
       <c r="AJ471" t="n">
-        <v>-0.009372115686007376</v>
+        <v>-0.009372115686010929</v>
       </c>
       <c r="AK471" t="n">
         <v>6.791305278184372</v>
@@ -77162,16 +77162,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3548656112706069</v>
+        <v>-0.3548656112706071</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.006091291211178074</v>
+        <v>0.006091291211178139</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4593697101544711</v>
+        <v>0.4593697101544705</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.442519142421117</v>
+        <v>1.442519142421081</v>
       </c>
       <c r="AQ471" t="n">
         <v>82.48745240567671</v>
@@ -77315,10 +77315,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.800452644405181</v>
+        <v>6.800452644405178</v>
       </c>
       <c r="AJ472" t="n">
-        <v>-0.01185267644863774</v>
+        <v>-0.01185267644863508</v>
       </c>
       <c r="AK472" t="n">
         <v>6.789098969069376</v>
@@ -77333,10 +77333,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4721687943484544</v>
+        <v>0.4721687943484545</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.404392199013741</v>
+        <v>1.404392199013776</v>
       </c>
       <c r="AQ472" t="n">
         <v>79.31518593934199</v>
@@ -77480,10 +77480,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.778720347685821</v>
+        <v>6.778720347685814</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.01707986135958883</v>
+        <v>0.01707986135959594</v>
       </c>
       <c r="AK473" t="n">
         <v>6.790465135395929</v>
@@ -77492,16 +77492,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3625273381377937</v>
+        <v>-0.3625273381377933</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.007343464385960674</v>
+        <v>0.007343464385960585</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.4863203622043377</v>
+        <v>0.4863203622043382</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.718967726687749</v>
+        <v>1.718967726687834</v>
       </c>
       <c r="AQ473" t="n">
         <v>84.49074074074073</v>
@@ -77645,10 +77645,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.769755998762547</v>
+        <v>6.769755998762545</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.02364381202846833</v>
+        <v>0.02364381202847099</v>
       </c>
       <c r="AK474" t="n">
         <v>6.767889899932765</v>
@@ -77657,16 +77657,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3660007866474812</v>
+        <v>-0.3660007866474813</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.00826013782295415</v>
+        <v>0.008260137822954145</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.4997690914082398</v>
+        <v>0.4997690914082401</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.776447733059097</v>
+        <v>1.776447733059131</v>
       </c>
       <c r="AQ474" t="n">
         <v>85.25345622119815</v>
@@ -77810,10 +77810,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.789177604754239</v>
+        <v>6.789177604754244</v>
       </c>
       <c r="AJ475" t="n">
-        <v>0.01332216636392491</v>
+        <v>0.01332216636391959</v>
       </c>
       <c r="AK475" t="n">
         <v>6.759766754404358</v>
@@ -77822,16 +77822,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3700034659576358</v>
+        <v>-0.3700034659576351</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.00987171553454691</v>
+        <v>0.009871715534546958</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.5120623436103316</v>
+        <v>0.5120623436103324</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.645621086027352</v>
+        <v>1.645621086027296</v>
       </c>
       <c r="AQ475" t="n">
         <v>85.32527105921602</v>
@@ -77975,10 +77975,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.774331376960423</v>
+        <v>6.774331376960425</v>
       </c>
       <c r="AJ476" t="n">
-        <v>0.01776857573733093</v>
+        <v>0.01776857573732915</v>
       </c>
       <c r="AK476" t="n">
         <v>6.777856240868369</v>
@@ -77987,16 +77987,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3750442390024145</v>
+        <v>-0.3750442390024147</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01196068662558775</v>
+        <v>0.01196068662558781</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5238651846176465</v>
+        <v>0.5238651846176463</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.680943449342473</v>
+        <v>1.680943449342458</v>
       </c>
       <c r="AQ476" t="n">
         <v>84.47695200314055</v>
@@ -78152,16 +78152,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3816350905604304</v>
+        <v>-0.3816350905604307</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01460798460929558</v>
+        <v>0.01460798460929556</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.537958310473289</v>
+        <v>0.5379583104732891</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.627209299316994</v>
+        <v>1.627209299316998</v>
       </c>
       <c r="AQ477" t="n">
         <v>85.00614250614251</v>
@@ -78305,10 +78305,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.789815280543246</v>
+        <v>6.789815280543245</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.01031527291385181</v>
+        <v>-0.01031527291385093</v>
       </c>
       <c r="AK478" t="n">
         <v>6.744939020214936</v>
@@ -78317,16 +78317,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3872393091179336</v>
+        <v>-0.3872393091179339</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01685992867552227</v>
+        <v>0.01685992867552231</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5511317941481411</v>
+        <v>0.5511317941481415</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.344782590346758</v>
+        <v>1.344782590346771</v>
       </c>
       <c r="AQ478" t="n">
         <v>82.60150559016293</v>
@@ -78470,10 +78470,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.801295181477315</v>
+        <v>6.801295181477309</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.03129520055080093</v>
+        <v>-0.0312952005507956</v>
       </c>
       <c r="AK479" t="n">
         <v>6.772636231606738</v>
@@ -78482,16 +78482,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.393020019860339</v>
+        <v>-0.3930200198603389</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01873686412955489</v>
+        <v>0.01873686412955481</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5644439393662184</v>
+        <v>0.5644439393662187</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.10520581121148</v>
+        <v>1.105205811211542</v>
       </c>
       <c r="AQ479" t="n">
         <v>76.84604247104247</v>
@@ -78635,10 +78635,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.791632066062363</v>
+        <v>6.791632066062364</v>
       </c>
       <c r="AJ480" t="n">
-        <v>-0.0234321454080666</v>
+        <v>-0.02343214540806748</v>
       </c>
       <c r="AK480" t="n">
         <v>6.788619247652995</v>
@@ -78647,16 +78647,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3966294116439325</v>
+        <v>-0.3966294116439323</v>
       </c>
       <c r="AN480" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.576974471973372</v>
+        <v>0.5769744719733717</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.186476859823366</v>
+        <v>1.186476859823359</v>
       </c>
       <c r="AQ480" t="n">
         <v>74.69955156950672</v>
@@ -78800,10 +78800,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.779898505875916</v>
+        <v>6.779898505875918</v>
       </c>
       <c r="AJ481" t="n">
-        <v>-0.007398467728943814</v>
+        <v>-0.00739846772894559</v>
       </c>
       <c r="AK481" t="n">
         <v>6.776305653888958</v>
@@ -78812,16 +78812,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3980313152890726</v>
+        <v>-0.3980313152890724</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01933124704228378</v>
+        <v>0.0193312470422838</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.5877384296086169</v>
+        <v>0.5877384296086161</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.356475842636204</v>
+        <v>1.356475842636188</v>
       </c>
       <c r="AQ481" t="n">
         <v>76.57830278128949</v>
@@ -78965,10 +78965,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.771360892616113</v>
+        <v>6.771360892616116</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.001139145530859587</v>
+        <v>0.001139145530856922</v>
       </c>
       <c r="AK482" t="n">
         <v>6.76492936370744</v>
@@ -78977,16 +78977,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3979537985659305</v>
+        <v>-0.3979537985659302</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.0183584453609324</v>
+        <v>0.01835844536093246</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6001791687136281</v>
+        <v>0.6001791687136286</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.441515297066416</v>
+        <v>1.44151529706639</v>
       </c>
       <c r="AQ482" t="n">
         <v>77.56534508076359</v>
@@ -79130,10 +79130,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.751667781721844</v>
+        <v>6.751667781721842</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.02083225642512865</v>
+        <v>0.02083225642513042</v>
       </c>
       <c r="AK483" t="n">
         <v>6.753855191419989</v>
@@ -79142,16 +79142,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.3975762425746344</v>
+        <v>-0.3975762425746347</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01731206726614276</v>
+        <v>0.01731206726614282</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6129676701055393</v>
+        <v>0.6129676701055397</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.646360276993232</v>
+        <v>1.646360276993257</v>
       </c>
       <c r="AQ483" t="n">
         <v>82.96654246235056</v>
@@ -79295,10 +79295,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.729738669869288</v>
+        <v>6.72973866986929</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.03586153459848518</v>
+        <v>0.0358615345984834</v>
       </c>
       <c r="AK484" t="n">
         <v>6.736226026398153</v>
@@ -79307,16 +79307,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3964908591695859</v>
+        <v>-0.3964908591695858</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01740130648959376</v>
+        <v>0.01740130648959375</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6198907013195262</v>
+        <v>0.6198907013195265</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.795594927274907</v>
+        <v>1.795594927274892</v>
       </c>
       <c r="AQ484" t="n">
         <v>80.39647577092511</v>
@@ -79460,10 +79460,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.713320364291503</v>
+        <v>6.713320364291505</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.05917967385546952</v>
+        <v>0.05917967385546774</v>
       </c>
       <c r="AK485" t="n">
         <v>6.717723214958548</v>
@@ -79472,16 +79472,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.394760534481672</v>
+        <v>-0.3947605344816719</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01742962324324016</v>
+        <v>0.01742962324324019</v>
       </c>
       <c r="AO485" t="n">
-        <v>0.6272835381163622</v>
+        <v>0.6272835381163618</v>
       </c>
       <c r="AP485" t="n">
-        <v>2.028963267389809</v>
+        <v>2.028963267389796</v>
       </c>
       <c r="AQ485" t="n">
         <v>87.28070175438597</v>
@@ -79625,10 +79625,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.731179671396989</v>
+        <v>6.731179671396997</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.04132036674998396</v>
+        <v>0.04132036674997597</v>
       </c>
       <c r="AK486" t="n">
         <v>6.699415101064979</v>
@@ -79640,13 +79640,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.01766596732646103</v>
+        <v>0.0176659673264611</v>
       </c>
       <c r="AO486" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.816762279753399</v>
+        <v>1.816762279753319</v>
       </c>
       <c r="AQ486" t="n">
         <v>86.68311310232708</v>
@@ -79790,10 +79790,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.740946959621007</v>
+        <v>6.740946959621005</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.03085308157772371</v>
+        <v>0.03085308157772548</v>
       </c>
       <c r="AK487" t="n">
         <v>6.714685154719483</v>
@@ -79802,16 +79802,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.3929423394238508</v>
+        <v>-0.392942339423851</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.01842070378092631</v>
+        <v>0.0184207037809263</v>
       </c>
       <c r="AO487" t="n">
-        <v>0.640374511165978</v>
+        <v>0.6403745111659787</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.688819755019156</v>
+        <v>1.688819755019181</v>
       </c>
       <c r="AQ487" t="n">
         <v>84.57083958020989</v>
@@ -79955,10 +79955,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.7589577577717</v>
+        <v>6.758957757771704</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.006742105662137732</v>
+        <v>0.006742105662134179</v>
       </c>
       <c r="AK488" t="n">
         <v>6.722064699270507</v>
@@ -79967,16 +79967,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3931401656438959</v>
+        <v>-0.3931401656438955</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.01902711841846483</v>
+        <v>0.01902711841846487</v>
       </c>
       <c r="AO488" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.41867091232492</v>
+        <v>1.418670912324887</v>
       </c>
       <c r="AQ488" t="n">
         <v>80.32160972075135</v>
@@ -80120,10 +80120,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.763209774497792</v>
+        <v>6.763209774497788</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.007790133949473699</v>
+        <v>0.007790133949477251</v>
       </c>
       <c r="AK489" t="n">
         <v>6.739235851443908</v>
@@ -80132,16 +80132,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.3951733572725242</v>
+        <v>-0.3951733572725246</v>
       </c>
       <c r="AN489" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO489" t="n">
-        <v>0.6590798145480943</v>
+        <v>0.6590798145480942</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.420718764998806</v>
+        <v>1.420718764998849</v>
       </c>
       <c r="AQ489" t="n">
         <v>80.62186855290304</v>
@@ -80297,16 +80297,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3960001863323608</v>
+        <v>-0.396000186332361</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.02043272610569408</v>
+        <v>0.02043272610569401</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6685846444009622</v>
+        <v>0.6685846444009627</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.602984141316341</v>
+        <v>1.602984141316347</v>
       </c>
       <c r="AQ490" t="n">
         <v>81.12318509725139</v>
@@ -80450,10 +80450,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.714622134232894</v>
+        <v>6.714622134232888</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.04037798020802441</v>
+        <v>0.04037798020802974</v>
       </c>
       <c r="AK491" t="n">
         <v>6.746779913842831</v>
@@ -80462,16 +80462,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.396740905361911</v>
+        <v>-0.3967409053619114</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02120763540003751</v>
+        <v>0.02120763540003743</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.6777865296786982</v>
+        <v>0.6777865296786978</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.743725177744846</v>
+        <v>1.743725177744909</v>
       </c>
       <c r="AQ491" t="n">
         <v>83.76430537447487</v>
@@ -80615,28 +80615,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.731570059394423</v>
+        <v>6.73157005939442</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.01932973232310609</v>
+        <v>0.01932973232310964</v>
       </c>
       <c r="AK492" t="n">
-        <v>6.728823425344638</v>
+        <v>6.728823425344639</v>
       </c>
       <c r="AL492" t="n">
-        <v>0.02207636637289134</v>
+        <v>0.02207636637289045</v>
       </c>
       <c r="AM492" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.0220082962170377</v>
+        <v>0.02200829621703764</v>
       </c>
       <c r="AO492" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.508214089918481</v>
+        <v>1.508214089918522</v>
       </c>
       <c r="AQ492" t="n">
         <v>79.16330011670706</v>
@@ -80780,10 +80780,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.748064561399866</v>
+        <v>6.748064561399863</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.004235224214148126</v>
+        <v>0.00423522421415079</v>
       </c>
       <c r="AK493" t="n">
         <v>6.740096815166266</v>
@@ -80792,16 +80792,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.3976889317784199</v>
+        <v>-0.3976889317784196</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02268190844878654</v>
+        <v>0.02268190844878653</v>
       </c>
       <c r="AO493" t="n">
-        <v>0.6953567146475523</v>
+        <v>0.6953567146475526</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.339383633714908</v>
+        <v>1.339383633714939</v>
       </c>
       <c r="AQ493" t="n">
         <v>74.17924797037459</v>
@@ -80945,10 +80945,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.747226278872152</v>
+        <v>6.747226278872151</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.005973775296548745</v>
+        <v>0.005973775296550521</v>
       </c>
       <c r="AK494" t="n">
         <v>6.755554272205931</v>
@@ -80957,16 +80957,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4003515275861345</v>
+        <v>-0.400351527586135</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02398656672240618</v>
+        <v>0.02398656672240616</v>
       </c>
       <c r="AO494" t="n">
-        <v>0.7067969646460921</v>
+        <v>0.7067969646460924</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.34983246065289</v>
+        <v>1.349832460652912</v>
       </c>
       <c r="AQ494" t="n">
         <v>73.86614409547516</v>
@@ -81110,10 +81110,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.724989986752571</v>
+        <v>6.724989986752573</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.02471008267491914</v>
+        <v>0.02471008267491737</v>
       </c>
       <c r="AK495" t="n">
         <v>6.75925064743029</v>
@@ -81122,7 +81122,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.4017887258056133</v>
+        <v>-0.4017887258056131</v>
       </c>
       <c r="AN495" t="n">
         <v>0.02482212216928553</v>
@@ -81131,7 +81131,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.537934200391007</v>
+        <v>1.537934200390992</v>
       </c>
       <c r="AQ495" t="n">
         <v>77.32142857142857</v>
@@ -81275,28 +81275,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.738231277482312</v>
+        <v>6.738231277482303</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.01056852339049108</v>
+        <v>0.01056852339049996</v>
       </c>
       <c r="AK496" t="n">
-        <v>6.734775445902895</v>
+        <v>6.734775445902896</v>
       </c>
       <c r="AL496" t="n">
-        <v>0.01402435496990773</v>
+        <v>0.01402435496990684</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4022294042554291</v>
+        <v>-0.402229404255429</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02545790195722747</v>
+        <v>0.02545790195722734</v>
       </c>
       <c r="AO496" t="n">
-        <v>0.7273309315128231</v>
+        <v>0.7273309315128232</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.379757628265576</v>
+        <v>1.379757628265672</v>
       </c>
       <c r="AQ496" t="n">
         <v>74.71049844615358</v>
@@ -81440,10 +81440,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.718201282169581</v>
+        <v>6.718201282169575</v>
       </c>
       <c r="AJ497" t="n">
-        <v>0.02919852480673768</v>
+        <v>0.02919852480674301</v>
       </c>
       <c r="AK497" t="n">
         <v>6.753996132599221</v>
@@ -81452,16 +81452,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4027953816469058</v>
+        <v>-0.4027953816469059</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02608258444417638</v>
+        <v>0.02608258444417639</v>
       </c>
       <c r="AO497" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.565396263588755</v>
+        <v>1.565396263588813</v>
       </c>
       <c r="AQ497" t="n">
         <v>78.55027548209367</v>
@@ -81605,10 +81605,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.730898772467414</v>
+        <v>6.730898772467415</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.01650103450890406</v>
+        <v>0.01650103450890317</v>
       </c>
       <c r="AK498" t="n">
         <v>6.732394407262716</v>
@@ -81617,16 +81617,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4025099007694142</v>
+        <v>-0.402509900769414</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02634377330607651</v>
+        <v>0.02634377330607648</v>
       </c>
       <c r="AO498" t="n">
-        <v>0.746561519528266</v>
+        <v>0.7465615195282662</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.422631365509687</v>
+        <v>1.422631365509679</v>
       </c>
       <c r="AQ498" t="n">
         <v>79.06784146987005</v>
@@ -81782,16 +81782,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.4034224290251451</v>
+        <v>-0.4034224290251453</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02736182786837871</v>
+        <v>0.02736182786837866</v>
       </c>
       <c r="AO499" t="n">
-        <v>0.755189863471066</v>
+        <v>0.7551898634710656</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.28848874127045</v>
+        <v>1.288488741270451</v>
       </c>
       <c r="AQ499" t="n">
         <v>77.09998645170032</v>
@@ -81935,10 +81935,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI500" t="n">
-        <v>6.755708466794879</v>
+        <v>6.75570846679488</v>
       </c>
       <c r="AJ500" t="n">
-        <v>-0.01240850570479068</v>
+        <v>-0.01240850570479246</v>
       </c>
       <c r="AK500" t="n">
         <v>6.746865899087779</v>
@@ -81947,16 +81947,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4037073020769307</v>
+        <v>-0.4037073020769305</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02778289906564352</v>
+        <v>0.02778289906564353</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.7638221248099442</v>
+        <v>0.7638221248099444</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.106704203783623</v>
+        <v>1.106704203783605</v>
       </c>
       <c r="AQ500" t="n">
         <v>79.88914084152179</v>
@@ -82100,10 +82100,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.73601646973098</v>
+        <v>6.73601646973097</v>
       </c>
       <c r="AJ501" t="n">
-        <v>0.006783766017311343</v>
+        <v>0.006783766017321113</v>
       </c>
       <c r="AK501" t="n">
         <v>6.761018647414997</v>
@@ -82112,16 +82112,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.403510818895136</v>
+        <v>-0.4035108188951355</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02805871830419215</v>
+        <v>0.02805871830419202</v>
       </c>
       <c r="AO501" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.300975206946079</v>
+        <v>1.300975206946182</v>
       </c>
       <c r="AQ501" t="n">
         <v>83.63654538184727</v>
@@ -82280,13 +82280,13 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02827333203020888</v>
+        <v>0.02827333203020884</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7726830480787004</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.386408072754962</v>
+        <v>1.386408072754963</v>
       </c>
       <c r="AQ502" t="n">
         <v>84.10476741303809</v>
@@ -82430,10 +82430,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.725806144687715</v>
+        <v>6.725806144687716</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.01409396746438496</v>
+        <v>0.01409396746438318</v>
       </c>
       <c r="AK503" t="n">
         <v>6.744478107428201</v>
@@ -82442,16 +82442,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM503" t="n">
-        <v>-0.4027900432658338</v>
+        <v>-0.4027900432658339</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02891453613228628</v>
+        <v>0.0289145361322863</v>
       </c>
       <c r="AO503" t="n">
-        <v>0.7784357006627721</v>
+        <v>0.7784357006627718</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.361435739620025</v>
+        <v>1.361435739620007</v>
       </c>
       <c r="AQ503" t="n">
         <v>83.56281143456596</v>
@@ -82595,10 +82595,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.700854569500288</v>
+        <v>6.700854569500285</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.04174539464155735</v>
+        <v>0.04174539464156091</v>
       </c>
       <c r="AK504" t="n">
         <v>6.743301592583855</v>
@@ -82607,16 +82607,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.402742697458547</v>
+        <v>-0.4027426974585472</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.02955568036482276</v>
+        <v>0.0295556803648227</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7839391318357882</v>
+        <v>0.7839391318357879</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.637941562843737</v>
+        <v>1.637941562843773</v>
       </c>
       <c r="AQ504" t="n">
         <v>88.46316439848462</v>
@@ -82760,10 +82760,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.705597066237452</v>
+        <v>6.705597066237454</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.02390275065707925</v>
+        <v>0.02390275065707748</v>
       </c>
       <c r="AK505" t="n">
         <v>6.74285285202661</v>
@@ -82772,16 +82772,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.401588500320058</v>
+        <v>-0.4015885003200582</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.02985284499018426</v>
+        <v>0.02985284499018428</v>
       </c>
       <c r="AO505" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.44324674128027</v>
+        <v>1.443246741280252</v>
       </c>
       <c r="AQ505" t="n">
         <v>85.09516129032258</v>
@@ -82925,28 +82925,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.686024746022946</v>
+        <v>6.686024746022948</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.0364751013891631</v>
+        <v>0.03647510138916132</v>
       </c>
       <c r="AK506" t="n">
-        <v>6.744526329542678</v>
+        <v>6.744526329542679</v>
       </c>
       <c r="AL506" t="n">
-        <v>-0.02202648213056868</v>
+        <v>-0.02202648213056957</v>
       </c>
       <c r="AM506" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.02995529076246445</v>
+        <v>0.02995529076246446</v>
       </c>
       <c r="AO506" t="n">
-        <v>0.7933293013213367</v>
+        <v>0.7933293013213371</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.566182359822747</v>
+        <v>1.566182359822729</v>
       </c>
       <c r="AQ506" t="n">
         <v>84.34056224899598</v>
@@ -83090,10 +83090,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.689653251437546</v>
+        <v>6.689653251437547</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.03134694311201436</v>
+        <v>0.03134694311201347</v>
       </c>
       <c r="AK507" t="n">
         <v>6.730402461316146</v>
@@ -83102,16 +83102,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM507" t="n">
-        <v>-0.3993041981056888</v>
+        <v>-0.3993041981056886</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03010093147709741</v>
+        <v>0.03010093147709737</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.7985853639949437</v>
+        <v>0.7985853639949436</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.507036858820242</v>
+        <v>1.507036858820234</v>
       </c>
       <c r="AQ507" t="n">
         <v>85</v>
@@ -83255,10 +83255,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.716786041117415</v>
+        <v>6.716786041117424</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.00511394514967467</v>
+        <v>0.005113945149665788</v>
       </c>
       <c r="AK508" t="n">
         <v>6.728106442363027</v>
@@ -83267,16 +83267,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3976134529492091</v>
+        <v>-0.3976134529492094</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03006044259180324</v>
+        <v>0.03006044259180338</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.8026437279892851</v>
+        <v>0.8026437279892848</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.234777974751978</v>
+        <v>1.234777974751887</v>
       </c>
       <c r="AQ508" t="n">
         <v>81.59999999999999</v>
@@ -83420,10 +83420,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.721932795514441</v>
+        <v>6.72193279551444</v>
       </c>
       <c r="AJ509" t="n">
-        <v>-0.001632597913122424</v>
+        <v>-0.001632597913121536</v>
       </c>
       <c r="AK509" t="n">
         <v>6.752314636061016</v>
@@ -83435,13 +83435,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03043336917902489</v>
+        <v>0.03043336917902487</v>
       </c>
       <c r="AO509" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.163823515923089</v>
+        <v>1.163823515923099</v>
       </c>
       <c r="AQ509" t="n">
         <v>82.19999999999999</v>
@@ -83585,28 +83585,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.718669003366535</v>
+        <v>6.718669003366529</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.003830844045574544</v>
+        <v>0.003830844045580761</v>
       </c>
       <c r="AK510" t="n">
-        <v>6.750203856204787</v>
+        <v>6.750203856204786</v>
       </c>
       <c r="AL510" t="n">
-        <v>-0.02770400879267765</v>
+        <v>-0.02770400879267676</v>
       </c>
       <c r="AM510" t="n">
-        <v>-0.3969152632178358</v>
+        <v>-0.3969152632178359</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03100517332816438</v>
+        <v>0.03100517332816427</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8091236362457368</v>
+        <v>0.8091236362457366</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.217453571381047</v>
+        <v>1.217453571381112</v>
       </c>
       <c r="AQ510" t="n">
         <v>82.80000000000001</v>
@@ -83750,10 +83750,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.680190080689523</v>
+        <v>6.680190080689519</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.04230976672258624</v>
+        <v>0.04230976672259068</v>
       </c>
       <c r="AK511" t="n">
         <v>6.74780904069481</v>
@@ -83762,16 +83762,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM511" t="n">
-        <v>-0.3964565291282772</v>
+        <v>-0.3964565291282773</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03139664408873172</v>
+        <v>0.03139664408873165</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8123541153569376</v>
+        <v>0.8123541153569371</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.604493248424094</v>
+        <v>1.604493248424141</v>
       </c>
       <c r="AQ511" t="n">
         <v>89.8</v>
@@ -83915,10 +83915,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.671580974366952</v>
+        <v>6.671580974366949</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.05441885778636824</v>
+        <v>0.05441885778637179</v>
       </c>
       <c r="AK512" t="n">
         <v>6.701878095437348</v>
@@ -83930,13 +83930,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03163116863423027</v>
+        <v>0.03163116863423025</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8147568654710424</v>
+        <v>0.8147568654710426</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.717274375116457</v>
+        <v>1.717274375116494</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.2</v>
@@ -84080,28 +84080,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.656216276126097</v>
+        <v>6.656216276126093</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.06978355602722353</v>
+        <v>0.06978355602722708</v>
       </c>
       <c r="AK513" t="n">
-        <v>6.701765808189924</v>
+        <v>6.701765808189925</v>
       </c>
       <c r="AL513" t="n">
-        <v>0.02423402396339647</v>
+        <v>0.02423402396339558</v>
       </c>
       <c r="AM513" t="n">
-        <v>-0.3932426568003564</v>
+        <v>-0.3932426568003567</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.0319127327617218</v>
+        <v>0.03191273276172183</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8170879052811413</v>
+        <v>0.8170879052811416</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.858889534485343</v>
+        <v>1.858889534485379</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.59999999999999</v>
@@ -84251,19 +84251,19 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK514" t="n">
-        <v>6.682658801267993</v>
+        <v>6.682658801267994</v>
       </c>
       <c r="AL514" t="n">
-        <v>0.03754126053010243</v>
+        <v>0.03754126053010154</v>
       </c>
       <c r="AM514" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.03225018457163042</v>
+        <v>0.03225018457163047</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8195353634242114</v>
+        <v>0.8195353634242113</v>
       </c>
       <c r="AP514" t="n">
         <v>1.818117584748586</v>
@@ -84410,10 +84410,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.654231073451243</v>
+        <v>6.654231073451242</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.06476878921965579</v>
+        <v>0.06476878921965668</v>
       </c>
       <c r="AK515" t="n">
         <v>6.682840937292736</v>
@@ -84422,16 +84422,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM515" t="n">
-        <v>-0.3894836768645471</v>
+        <v>-0.3894836768645476</v>
       </c>
       <c r="AN515" t="n">
-        <v>0.03277193700354208</v>
+        <v>0.03277193700354209</v>
       </c>
       <c r="AO515" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.781104797300566</v>
+        <v>1.781104797300575</v>
       </c>
       <c r="AQ515" t="n">
         <v>90.2</v>
@@ -84575,10 +84575,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.650937329061554</v>
+        <v>6.650937329061552</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.06806253360934456</v>
+        <v>0.06806253360934633</v>
       </c>
       <c r="AK516" t="n">
         <v>6.698821600583909</v>
@@ -84587,16 +84587,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM516" t="n">
-        <v>-0.3885003849593205</v>
+        <v>-0.3885003849593203</v>
       </c>
       <c r="AN516" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO516" t="n">
-        <v>0.8264954348925954</v>
+        <v>0.8264954348925952</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.79987483353635</v>
+        <v>1.799874833536367</v>
       </c>
       <c r="AQ516" t="n">
         <v>91</v>
@@ -84740,10 +84740,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.651733245487365</v>
+        <v>6.651733245487366</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.05906692541107272</v>
+        <v>0.05906692541107184</v>
       </c>
       <c r="AK517" t="n">
         <v>6.69208631505748</v>
@@ -84752,16 +84752,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.3869746098498524</v>
+        <v>-0.3869746098498528</v>
       </c>
       <c r="AN517" t="n">
-        <v>0.0344188897752209</v>
+        <v>0.03441888977522091</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8294137131605728</v>
+        <v>0.8294137131605726</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.696616308981454</v>
+        <v>1.696616308981445</v>
       </c>
       <c r="AQ517" t="n">
         <v>90.40000000000001</v>
@@ -84905,10 +84905,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI518" t="n">
-        <v>6.632036771677474</v>
+        <v>6.632036771677475</v>
       </c>
       <c r="AJ518" t="n">
-        <v>0.07876339922096331</v>
+        <v>0.07876339922096243</v>
       </c>
       <c r="AK518" t="n">
         <v>6.692627206904497</v>
@@ -84926,7 +84926,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP518" t="n">
-        <v>1.875440190456854</v>
+        <v>1.875440190456846</v>
       </c>
       <c r="AQ518" t="n">
         <v>91</v>
@@ -85070,10 +85070,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.617259294346139</v>
+        <v>6.617259294346145</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.09324046914263029</v>
+        <v>0.09324046914262496</v>
       </c>
       <c r="AK519" t="n">
         <v>6.685306332307247</v>
@@ -85085,13 +85085,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03459091746240417</v>
+        <v>0.03459091746240425</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8328314813119074</v>
+        <v>0.8328314813119078</v>
       </c>
       <c r="AP519" t="n">
-        <v>1.998006000856745</v>
+        <v>1.998006000856694</v>
       </c>
       <c r="AQ519" t="n">
         <v>91</v>
@@ -85247,16 +85247,16 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM520" t="n">
-        <v>-0.379198503222778</v>
+        <v>-0.3791985032227784</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03468237364461174</v>
+        <v>0.03468237364461172</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8349203610870053</v>
+        <v>0.8349203610870052</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.31722822525293</v>
+        <v>2.317228225252932</v>
       </c>
       <c r="AQ520" t="n">
         <v>93</v>
@@ -85415,13 +85415,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03437427878524163</v>
+        <v>0.0343742787852416</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8337972329517069</v>
+        <v>0.8337972329517072</v>
       </c>
       <c r="AP521" t="n">
-        <v>2.426255822246373</v>
+        <v>2.426255822246376</v>
       </c>
       <c r="AQ521" t="n">
         <v>93.40000000000001</v>
@@ -85565,10 +85565,10 @@
         <v>-0.2483229054629721</v>
       </c>
       <c r="AI522" t="n">
-        <v>6.570789830572489</v>
+        <v>6.57078983057249</v>
       </c>
       <c r="AJ522" t="n">
-        <v>0.1372103525329802</v>
+        <v>0.1372103525329784</v>
       </c>
       <c r="AK522" t="n">
         <v>6.617345065810827</v>
@@ -85577,16 +85577,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM522" t="n">
-        <v>-0.3685435183382903</v>
+        <v>-0.3685435183382902</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03361173230743109</v>
+        <v>0.03361173230743112</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8313650598704547</v>
+        <v>0.8313650598704546</v>
       </c>
       <c r="AP522" t="n">
-        <v>2.332216400368044</v>
+        <v>2.33221640036803</v>
       </c>
       <c r="AQ522" t="n">
         <v>91.8</v>
@@ -85650,10 +85650,10 @@
         <v>0.004000022125244307</v>
       </c>
       <c r="I523" t="n">
-        <v>99.45999908447266</v>
+        <v>99.65000152587891</v>
       </c>
       <c r="J523" t="n">
-        <v>0</v>
+        <v>0.001910340269004829</v>
       </c>
       <c r="K523" t="n">
         <v>3.4261</v>
@@ -85689,16 +85689,16 @@
         <v>-3.69078534719845</v>
       </c>
       <c r="V523" t="n">
-        <v>6.5135</v>
+        <v>6.5986</v>
       </c>
       <c r="W523" t="n">
-        <v>-2.902417616006125</v>
+        <v>-1.63382096890734</v>
       </c>
       <c r="X523" t="n">
-        <v>-0.1392532658255785</v>
+        <v>1.184781054751416</v>
       </c>
       <c r="Y523" t="n">
-        <v>11.24497991967871</v>
+        <v>38.95582329317269</v>
       </c>
       <c r="Z523" t="inlineStr">
         <is>
@@ -85706,22 +85706,22 @@
         </is>
       </c>
       <c r="AA523" t="n">
-        <v>1.66121</v>
+        <v>1.66985</v>
       </c>
       <c r="AB523" t="n">
-        <v>1.61758</v>
+        <v>1.61985</v>
       </c>
       <c r="AC523" t="n">
-        <v>1.33356</v>
+        <v>1.34705</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.1812100000000001</v>
+        <v>0.1898500000000001</v>
       </c>
       <c r="AE523" t="n">
-        <v>1.785714285714286</v>
+        <v>10.31746031746032</v>
       </c>
       <c r="AF523" t="n">
-        <v>-0.3204632658255768</v>
+        <v>0.9949310547514134</v>
       </c>
       <c r="AG523" t="n">
         <v>6.955785239718927</v>
@@ -85730,10 +85730,10 @@
         <v>-0.2475852618441712</v>
       </c>
       <c r="AI523" t="n">
-        <v>6.568743061970063</v>
+        <v>6.574987720536736</v>
       </c>
       <c r="AJ523" t="n">
-        <v>0.1394569159046926</v>
+        <v>0.1332122573380197</v>
       </c>
       <c r="AK523" t="n">
         <v>6.613295682645951</v>
@@ -85742,49 +85742,214 @@
         <v>0.09490429522880461</v>
       </c>
       <c r="AM523" t="n">
-        <v>-0.362880333269974</v>
+        <v>-0.3628803332699742</v>
       </c>
       <c r="AN523" t="n">
-        <v>0.0328662017206236</v>
+        <v>0.03286620172062364</v>
       </c>
       <c r="AO523" t="n">
-        <v>0.82993355238613</v>
+        <v>0.8299335523861298</v>
       </c>
       <c r="AP523" t="n">
-        <v>2.323204012475593</v>
+        <v>2.265952574875376</v>
       </c>
       <c r="AQ523" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="AR523" t="n">
-        <v>-0.00381722595136601</v>
+        <v>-0.003607813311680667</v>
       </c>
       <c r="AS523" t="n">
-        <v>6.7095</v>
+        <v>6.709453757112515</v>
       </c>
       <c r="AT523" t="n">
-        <v>-0.009800000000000253</v>
+        <v>-0.009753757112514805</v>
       </c>
       <c r="AU523" t="n">
         <v>-0.009800000000000253</v>
       </c>
       <c r="AV523" t="n">
-        <v>-0.01299780575731089</v>
+        <v>-0.01299549361293661</v>
       </c>
       <c r="AW523" t="n">
-        <v>-0.01411381503904495</v>
+        <v>-0.01411304432425353</v>
       </c>
       <c r="AX523" t="n">
-        <v>0.01380007954151711</v>
+        <v>0.0137999639342984</v>
       </c>
       <c r="AY523" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="AZ523" t="n">
-        <v>85.93333333333332</v>
+        <v>85.87333333333333</v>
       </c>
       <c r="BA523" t="n">
-        <v>84.0331111111111</v>
+        <v>84.0211111111111</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C524" t="n">
+        <v>1.2439</v>
+      </c>
+      <c r="D524" t="n">
+        <v>3.4261</v>
+      </c>
+      <c r="E524" t="n">
+        <v>6.708199977874756</v>
+      </c>
+      <c r="F524" t="n">
+        <v>6.7052</v>
+      </c>
+      <c r="G524" t="n">
+        <v>6.694500000000001</v>
+      </c>
+      <c r="H524" t="n">
+        <v>-0.002999977874756254</v>
+      </c>
+      <c r="I524" t="n">
+        <v>99.65000152587891</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0</v>
+      </c>
+      <c r="K524" t="n">
+        <v>3.4261</v>
+      </c>
+      <c r="L524" t="n">
+        <v>3.145855</v>
+      </c>
+      <c r="M524" t="n">
+        <v>3.013231666666667</v>
+      </c>
+      <c r="N524" t="n">
+        <v>2.853261666666667</v>
+      </c>
+      <c r="O524" t="n">
+        <v>99.80000000000001</v>
+      </c>
+      <c r="P524" t="n">
+        <v>99.9001996007984</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R524" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="S524" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T524" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U524" t="n">
+        <v>-3.685239417692058</v>
+      </c>
+      <c r="V524" t="n">
+        <v>6.5063</v>
+      </c>
+      <c r="W524" t="n">
+        <v>-3.009748942200141</v>
+      </c>
+      <c r="X524" t="n">
+        <v>-0.2512749709742801</v>
+      </c>
+      <c r="Y524" t="n">
+        <v>8.032128514056225</v>
+      </c>
+      <c r="Z524" t="inlineStr">
+        <is>
+          <t>market_1y</t>
+        </is>
+      </c>
+      <c r="AA524" t="n">
+        <v>1.66985</v>
+      </c>
+      <c r="AB524" t="n">
+        <v>1.61985</v>
+      </c>
+      <c r="AC524" t="n">
+        <v>1.34705</v>
+      </c>
+      <c r="AD524" t="n">
+        <v>0.1898500000000001</v>
+      </c>
+      <c r="AE524" t="n">
+        <v>10.51587301587302</v>
+      </c>
+      <c r="AF524" t="n">
+        <v>-0.4411249709742826</v>
+      </c>
+      <c r="AG524" t="n">
+        <v>6.955413207677006</v>
+      </c>
+      <c r="AH524" t="n">
+        <v>-0.2472132298022505</v>
+      </c>
+      <c r="AI524" t="n">
+        <v>6.579580030173254</v>
+      </c>
+      <c r="AJ524" t="n">
+        <v>0.1286199477015018</v>
+      </c>
+      <c r="AK524" t="n">
+        <v>6.610494673717893</v>
+      </c>
+      <c r="AL524" t="n">
+        <v>0.09770530415686274</v>
+      </c>
+      <c r="AM524" t="n">
+        <v>-0.3578313453157059</v>
+      </c>
+      <c r="AN524" t="n">
+        <v>0.03253304912369535</v>
+      </c>
+      <c r="AO524" t="n">
+        <v>0.829501685468071</v>
+      </c>
+      <c r="AP524" t="n">
+        <v>2.196676662060362</v>
+      </c>
+      <c r="AQ524" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AR524" t="n">
+        <v>-0.00352227905831011</v>
+      </c>
+      <c r="AS524" t="n">
+        <v>6.7122</v>
+      </c>
+      <c r="AT524" t="n">
+        <v>-0.0176999999999996</v>
+      </c>
+      <c r="AU524" t="n">
+        <v>-0.0176999999999996</v>
+      </c>
+      <c r="AV524" t="n">
+        <v>-0.0124096093211771</v>
+      </c>
+      <c r="AW524" t="n">
+        <v>-0.01447825628154356</v>
+      </c>
+      <c r="AX524" t="n">
+        <v>0.01371035897773928</v>
+      </c>
+      <c r="AY524" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AZ524" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="BA524" t="n">
+        <v>81.48755555555556</v>
       </c>
     </row>
   </sheetData>
@@ -85991,7 +86156,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -86006,7 +86171,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -86021,7 +86186,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>99.46</t>
+          <t>99.65</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -86061,47 +86226,47 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>market_1y</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>market_1y</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -86111,22 +86276,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.363</t>
+          <t>-0.358</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0329</t>
+          <t>0.0325</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -86136,7 +86301,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -86146,24 +86311,24 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.7095</t>
+          <t>6.7122</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>0.01</t>
@@ -86171,7 +86336,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>81</t>
         </is>
       </c>
     </row>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -85677,13 +85677,13 @@
         <v>1.48</v>
       </c>
       <c r="R523" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="S523" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="T523" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U523" t="n">
         <v>-3.69078534719845</v>
@@ -85695,10 +85695,10 @@
         <v>-1.63382096890734</v>
       </c>
       <c r="X523" t="n">
-        <v>1.184781054751416</v>
+        <v>1.204454290557644</v>
       </c>
       <c r="Y523" t="n">
-        <v>38.95582329317269</v>
+        <v>39.75903614457831</v>
       </c>
       <c r="Z523" t="inlineStr">
         <is>
@@ -85721,7 +85721,7 @@
         <v>10.31746031746032</v>
       </c>
       <c r="AF523" t="n">
-        <v>0.9949310547514134</v>
+        <v>1.014604290557641</v>
       </c>
       <c r="AG523" t="n">
         <v>6.955785239718927</v>
@@ -85794,25 +85794,25 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>4.67</v>
+        <v>4.74</v>
       </c>
       <c r="C524" t="n">
         <v>1.2439</v>
       </c>
       <c r="D524" t="n">
-        <v>3.4261</v>
+        <v>3.4961</v>
       </c>
       <c r="E524" t="n">
-        <v>6.708199977874756</v>
+        <v>6.71120023727417</v>
       </c>
       <c r="F524" t="n">
-        <v>6.71012020111084</v>
+        <v>6.711150169372559</v>
       </c>
       <c r="G524" t="n">
         <v>6.694500000000001</v>
       </c>
       <c r="H524" t="n">
-        <v>0.001920223236083984</v>
+        <v>-5.006790161132812e-05</v>
       </c>
       <c r="I524" t="n">
         <v>99.65000152587891</v>
@@ -85821,49 +85821,49 @@
         <v>0</v>
       </c>
       <c r="K524" t="n">
-        <v>3.4261</v>
+        <v>3.4961</v>
       </c>
       <c r="L524" t="n">
-        <v>3.145855</v>
+        <v>3.149355</v>
       </c>
       <c r="M524" t="n">
-        <v>3.013231666666667</v>
+        <v>3.014398333333333</v>
       </c>
       <c r="N524" t="n">
-        <v>2.853261666666667</v>
+        <v>2.853845</v>
       </c>
       <c r="O524" t="n">
-        <v>99.80000000000001</v>
+        <v>100</v>
       </c>
       <c r="P524" t="n">
-        <v>99.9001996007984</v>
+        <v>100</v>
       </c>
       <c r="Q524" t="n">
         <v>1.48</v>
       </c>
       <c r="R524" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="S524" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="T524" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U524" t="n">
-        <v>-3.685239417692058</v>
+        <v>-3.500404749871521</v>
       </c>
       <c r="V524" t="n">
         <v>6.5063</v>
       </c>
       <c r="W524" t="n">
-        <v>-3.009748942200141</v>
+        <v>-3.053108684436934</v>
       </c>
       <c r="X524" t="n">
-        <v>-0.2512749709742801</v>
+        <v>-0.2771401556836972</v>
       </c>
       <c r="Y524" t="n">
-        <v>8.032128514056225</v>
+        <v>7.228915662650603</v>
       </c>
       <c r="Z524" t="inlineStr">
         <is>
@@ -85886,25 +85886,25 @@
         <v>10.51587301587302</v>
       </c>
       <c r="AF524" t="n">
-        <v>-0.4411249709742826</v>
+        <v>-0.4669901556836997</v>
       </c>
       <c r="AG524" t="n">
-        <v>6.955413207677006</v>
+        <v>6.946119409153104</v>
       </c>
       <c r="AH524" t="n">
-        <v>-0.2472132298022505</v>
+        <v>-0.2349191718789339</v>
       </c>
       <c r="AI524" t="n">
-        <v>6.579580030173254</v>
+        <v>6.554531836001155</v>
       </c>
       <c r="AJ524" t="n">
-        <v>0.1286199477015018</v>
+        <v>0.1566684012730146</v>
       </c>
       <c r="AK524" t="n">
         <v>6.610494673717893</v>
       </c>
       <c r="AL524" t="n">
-        <v>0.09770530415686274</v>
+        <v>0.1007055635562768</v>
       </c>
       <c r="AM524" t="n">
         <v>-0.3578313453157061</v>
@@ -85916,13 +85916,13 @@
         <v>0.8295016854680709</v>
       </c>
       <c r="AP524" t="n">
-        <v>2.196676662060358</v>
+        <v>2.451146565317861</v>
       </c>
       <c r="AQ524" t="n">
-        <v>91.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="AR524" t="n">
-        <v>-0.00352227905831011</v>
+        <v>-0.003535468258052979</v>
       </c>
       <c r="AS524" t="n">
         <v>6.7778000831604</v>
@@ -85946,10 +85946,10 @@
         <v>1.020408163265306</v>
       </c>
       <c r="AZ524" t="n">
-        <v>62.76714285714285</v>
+        <v>63.19714285714286</v>
       </c>
       <c r="BA524" t="n">
-        <v>64.07151014229476</v>
+        <v>64.15751014229475</v>
       </c>
     </row>
   </sheetData>
@@ -86176,7 +86176,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -86191,7 +86191,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -86211,12 +86211,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -86226,12 +86226,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -86266,17 +86266,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -86301,7 +86301,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41361,10 +41361,10 @@
         <v/>
       </c>
       <c r="AI254" t="n">
-        <v>7.16074252993424</v>
+        <v>7.160742529934239</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.01934266955216035</v>
+        <v>-0.01934266955215858</v>
       </c>
       <c r="AK254" t="n">
         <v>7.166224790710233</v>
@@ -41373,13 +41373,13 @@
         <v>-0.02482493032815292</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1026368091542317</v>
+        <v>0.1026368091542314</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002433131908989026</v>
+        <v>0.002433131908989014</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2688740668038501</v>
+        <v>0.2688740668038477</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41526,10 +41526,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI255" t="n">
-        <v>7.150419484347115</v>
+        <v>7.150419484347116</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.00901962396503464</v>
+        <v>-0.009019623965035528</v>
       </c>
       <c r="AK255" t="n">
         <v>7.161074530187645</v>
@@ -41538,13 +41538,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.102938554978808</v>
+        <v>0.1029385549788083</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002436328878122375</v>
+        <v>0.002436328878122382</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2711996176877889</v>
+        <v>0.2711996176877891</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41691,10 +41691,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.14851145777603</v>
+        <v>7.148511457776028</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.01601128611465263</v>
+        <v>-0.01601128611465086</v>
       </c>
       <c r="AK256" t="n">
         <v>7.150963414761942</v>
@@ -41703,13 +41703,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.1011329645838857</v>
+        <v>0.1011329645838851</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002517185580011383</v>
+        <v>0.002517185580011447</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2709113683260674</v>
+        <v>0.2709113683260677</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41868,13 +41868,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.09870181295186436</v>
+        <v>0.09870181295186471</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002644711580562605</v>
+        <v>0.002644711580562537</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2704892730019285</v>
+        <v>0.2704892730019304</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42021,10 +42021,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI258" t="n">
-        <v>7.153772633426657</v>
+        <v>7.153772633426659</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-0.03287247931288739</v>
+        <v>-0.03287247931288917</v>
       </c>
       <c r="AK258" t="n">
         <v>7.154757231824306</v>
@@ -42033,13 +42033,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.09555831842873888</v>
+        <v>0.09555831842873846</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.002822832879878049</v>
+        <v>0.002822832879878071</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2697410008595938</v>
+        <v>0.2697410008595936</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42186,10 +42186,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI259" t="n">
-        <v>7.153331199414497</v>
+        <v>7.153331199414496</v>
       </c>
       <c r="AJ259" t="n">
-        <v>-0.0326313169071728</v>
+        <v>-0.03263131690717191</v>
       </c>
       <c r="AK259" t="n">
         <v>7.15450652143491</v>
@@ -42198,13 +42198,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.09188440665249918</v>
+        <v>0.0918844066524992</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.003041971996730116</v>
+        <v>0.003041971996730133</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2698098046976254</v>
+        <v>0.2698098046976256</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42351,10 +42351,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI260" t="n">
-        <v>7.15694314831959</v>
+        <v>7.156943148319592</v>
       </c>
       <c r="AJ260" t="n">
-        <v>-0.0385430514262799</v>
+        <v>-0.03854305142628167</v>
       </c>
       <c r="AK260" t="n">
         <v>7.154505434137821</v>
@@ -42363,13 +42363,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.08748497753913362</v>
+        <v>0.08748497753913406</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003298336925509857</v>
+        <v>0.003298336925509862</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2682008942988222</v>
+        <v>0.2682008942988235</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42528,13 +42528,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.08245870840593096</v>
+        <v>0.0824587084059305</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003602928090795422</v>
+        <v>0.003602928090795432</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2685806390401518</v>
+        <v>0.2685806390401517</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42696,10 +42696,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.003819541738581439</v>
+        <v>0.003819541738581442</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2696768907787754</v>
+        <v>0.2696768907787764</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42846,10 +42846,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI263" t="n">
-        <v>7.154685377655176</v>
+        <v>7.154685377655177</v>
       </c>
       <c r="AJ263" t="n">
-        <v>-0.04048526245131878</v>
+        <v>-0.04048526245131967</v>
       </c>
       <c r="AK263" t="n">
         <v>7.15808570026938</v>
@@ -42858,13 +42858,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM263" t="n">
-        <v>0.07200163454913533</v>
+        <v>0.07200163454913491</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.004193740708391577</v>
+        <v>0.004193740708391541</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2701165988147326</v>
+        <v>0.270116598814735</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43011,10 +43011,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.158449213455078</v>
+        <v>7.158449213455076</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.05514911885058549</v>
+        <v>-0.05514911885058371</v>
       </c>
       <c r="AK264" t="n">
         <v>7.157644979270017</v>
@@ -43023,13 +43023,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.06676111471939436</v>
+        <v>0.06676111471939408</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.004505219337594384</v>
+        <v>0.00450521933759436</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.2733976337163387</v>
+        <v>0.2733976337163381</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43176,10 +43176,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.160761769069201</v>
+        <v>7.160761769069204</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.04786198879576364</v>
+        <v>-0.04786198879576631</v>
       </c>
       <c r="AK265" t="n">
         <v>7.159146249199162</v>
@@ -43188,10 +43188,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.06148465881746766</v>
+        <v>0.06148465881746725</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.004852471327681566</v>
+        <v>0.004852471327681615</v>
       </c>
       <c r="AO265" t="n">
         <v>0.2778048766368325</v>
@@ -43341,10 +43341,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI266" t="n">
-        <v>7.162478122158094</v>
+        <v>7.162478122158095</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-0.04957834188465693</v>
+        <v>-0.04957834188465782</v>
       </c>
       <c r="AK266" t="n">
         <v>7.159578986975002</v>
@@ -43353,13 +43353,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.05582594297075712</v>
+        <v>0.05582594297075769</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.005234102211236467</v>
+        <v>0.005234102211236422</v>
       </c>
       <c r="AO266" t="n">
-        <v>0.2824480243750598</v>
+        <v>0.282448024375059</v>
       </c>
       <c r="AP266" t="n">
         <v/>
@@ -43518,13 +43518,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.04949165986049463</v>
+        <v>0.04949165986049534</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.005677665039252918</v>
+        <v>0.005677665039252891</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.2878618994559794</v>
+        <v>0.2878618994559775</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43683,13 +43683,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.04287777011073606</v>
+        <v>0.04287777011073584</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.006155260602669625</v>
+        <v>0.006155260602669632</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.2948468705933236</v>
+        <v>0.2948468705933219</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43836,10 +43836,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI269" t="n">
-        <v>7.173971773133423</v>
+        <v>7.173971773133425</v>
       </c>
       <c r="AJ269" t="n">
-        <v>-0.04247200582995614</v>
+        <v>-0.04247200582995792</v>
       </c>
       <c r="AK269" t="n">
         <v>7.159255388854645</v>
@@ -43848,13 +43848,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.03486942009661778</v>
+        <v>0.0348694200966178</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.006728155724408201</v>
+        <v>0.006728155724408227</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.3044998756423967</v>
+        <v>0.304499875642397</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -44001,25 +44001,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.172030417300565</v>
+        <v>7.172030417300567</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.03823038754592645</v>
+        <v>-0.03823038754592822</v>
       </c>
       <c r="AK270" t="n">
-        <v>7.167062070913352</v>
+        <v>7.167062070913353</v>
       </c>
       <c r="AL270" t="n">
-        <v>-0.03326204115871345</v>
+        <v>-0.03326204115871434</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.03279550096037874</v>
+        <v>0.03279550096037902</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.006903991232239758</v>
+        <v>0.006903991232239788</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.3170366335916608</v>
+        <v>0.3170366335916601</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44166,10 +44166,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.171236182927454</v>
+        <v>7.171236182927453</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.0384360806935673</v>
+        <v>-0.03843608069356641</v>
       </c>
       <c r="AK271" t="n">
         <v>7.16747443083108</v>
@@ -44178,13 +44178,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.02972414459983913</v>
+        <v>0.02972414459983895</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.007158147882859</v>
+        <v>0.007158147882858998</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3270754385893863</v>
+        <v>0.3270754385893867</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44331,10 +44331,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.170425137628194</v>
+        <v>7.170425137628191</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.0510251132141315</v>
+        <v>-0.05102511321412884</v>
       </c>
       <c r="AK272" t="n">
         <v>7.168373097443463</v>
@@ -44343,13 +44343,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.02657019411530295</v>
+        <v>0.02657019411530269</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.007420436972250398</v>
+        <v>0.007420436972250415</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3357224795973281</v>
+        <v>0.3357224795973284</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44508,13 +44508,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.02366886174665165</v>
+        <v>0.02366886174665103</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.007679120311627231</v>
+        <v>0.007679120311627263</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.345021958194194</v>
+        <v>0.3450219581941938</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44661,10 +44661,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI274" t="n">
-        <v>7.172249622131823</v>
+        <v>7.172249622131827</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-0.05324966409349319</v>
+        <v>-0.05324966409349674</v>
       </c>
       <c r="AK274" t="n">
         <v>7.167365057101177</v>
@@ -44673,13 +44673,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.01956653131084189</v>
+        <v>0.01956653131084185</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.008034860291676519</v>
+        <v>0.008034860291676559</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3572033251592186</v>
+        <v>0.3572033251592189</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44826,10 +44826,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI275" t="n">
-        <v>7.171656420777023</v>
+        <v>7.171656420777024</v>
       </c>
       <c r="AJ275" t="n">
-        <v>-0.0526564627386934</v>
+        <v>-0.05265646273869429</v>
       </c>
       <c r="AK275" t="n">
         <v>7.167567681415887</v>
@@ -44838,13 +44838,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.0163839608889081</v>
+        <v>0.01638396088890769</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008326212487477898</v>
+        <v>0.008326212487477964</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3674516177552964</v>
+        <v>0.3674516177552961</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -44991,10 +44991,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI276" t="n">
-        <v>7.175289829564746</v>
+        <v>7.175289829564748</v>
       </c>
       <c r="AJ276" t="n">
-        <v>-0.05628987152641596</v>
+        <v>-0.05628987152641773</v>
       </c>
       <c r="AK276" t="n">
         <v>7.167553154788029</v>
@@ -45003,13 +45003,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01351198449095179</v>
+        <v>0.01351198449095157</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008601682347582911</v>
+        <v>0.008601682347582891</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.375864684661753</v>
+        <v>0.3758646846617525</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45162,19 +45162,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK277" t="n">
-        <v>7.167460814777641</v>
+        <v>7.16746081477764</v>
       </c>
       <c r="AL277" t="n">
-        <v>-0.048460856739311</v>
+        <v>-0.04846085673931011</v>
       </c>
       <c r="AM277" t="n">
-        <v>0.01196199498966377</v>
+        <v>0.01196199498966369</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.008797062853284078</v>
+        <v>0.008797062853284063</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.3847384959530228</v>
+        <v>0.3847384959530242</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45482,10 +45482,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI279" t="n">
-        <v>7.189678003526526</v>
+        <v>7.189678003526525</v>
       </c>
       <c r="AJ279" t="n">
-        <v>-0.07117777082999321</v>
+        <v>-0.07117777082999144</v>
       </c>
       <c r="AK279" t="n">
         <v/>
@@ -45494,13 +45494,13 @@
         <v/>
       </c>
       <c r="AM279" t="n">
-        <v>0.007307555239791735</v>
+        <v>0.007307555239791734</v>
       </c>
       <c r="AN279" t="n">
-        <v>0.009236289154790363</v>
+        <v>0.009236289154790337</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.4010397173569483</v>
+        <v>0.401039717356949</v>
       </c>
       <c r="AP279" t="n">
         <v/>
@@ -45647,10 +45647,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI280" t="n">
-        <v>7.183919177237466</v>
+        <v>7.183919177237467</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-0.056419120017007</v>
+        <v>-0.05641912001700788</v>
       </c>
       <c r="AK280" t="n">
         <v>7.168706858585229</v>
@@ -45659,13 +45659,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM280" t="n">
-        <v>0.006573598200531427</v>
+        <v>0.006573598200530942</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.009378157495070007</v>
+        <v>0.009378157495070056</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.4093166892046876</v>
+        <v>0.4093166892046883</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45824,13 +45824,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.00571969992866044</v>
+        <v>0.005719699928660468</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009535855797507651</v>
+        <v>0.009535855797507643</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4189456552735351</v>
+        <v>0.4189456552735356</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45977,10 +45977,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI282" t="n">
-        <v>7.183803634757355</v>
+        <v>7.183803634757356</v>
       </c>
       <c r="AJ282" t="n">
-        <v>-0.08380373012478692</v>
+        <v>-0.08380373012478781</v>
       </c>
       <c r="AK282" t="n">
         <v>7.157754776965645</v>
@@ -45989,13 +45989,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.007205793377055721</v>
+        <v>0.007205793377056199</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.00954184705868257</v>
+        <v>0.009541847058682544</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4265135453780416</v>
+        <v>0.4265135453780396</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46148,19 +46148,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK283" t="n">
-        <v>7.153578345933643</v>
+        <v>7.153578345933642</v>
       </c>
       <c r="AL283" t="n">
-        <v>-0.01517826811381884</v>
+        <v>-0.01517826811381795</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.009937300636551421</v>
+        <v>0.009937300636551308</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009475108253955637</v>
+        <v>0.00947510825395563</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4359288044119891</v>
+        <v>0.4359288044119884</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46307,10 +46307,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI284" t="n">
-        <v>7.175374323571332</v>
+        <v>7.175374323571331</v>
       </c>
       <c r="AJ284" t="n">
-        <v>-0.04917412444413483</v>
+        <v>-0.04917412444413394</v>
       </c>
       <c r="AK284" t="n">
         <v>7.155226204999164</v>
@@ -46319,13 +46319,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.01039951522374727</v>
+        <v>0.01039951522374721</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.009534227083684297</v>
+        <v>0.009534227083684284</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4462248692464653</v>
+        <v>0.446224869246465</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46484,13 +46484,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01174445052819296</v>
+        <v>0.01174445052819259</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009539024405591111</v>
+        <v>0.009539024405591096</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.4561706550234662</v>
+        <v>0.4561706550234678</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46637,10 +46637,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI286" t="n">
-        <v>7.176295466764673</v>
+        <v>7.176295466764674</v>
       </c>
       <c r="AJ286" t="n">
-        <v>-0.04989547286818841</v>
+        <v>-0.04989547286818929</v>
       </c>
       <c r="AK286" t="n">
         <v>7.150954883812801</v>
@@ -46649,13 +46649,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01399948938427885</v>
+        <v>0.01399948938427905</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009474826008246765</v>
+        <v>0.009474826008246758</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4654004237248376</v>
+        <v>0.4654004237248369</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46814,13 +46814,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.01676993900799728</v>
+        <v>0.01676993900799729</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.00937702887797469</v>
+        <v>0.009377028877974699</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4767009396389351</v>
+        <v>0.476700939638935</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46982,10 +46982,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009204864903404482</v>
+        <v>0.009204864903404497</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.4883841032893032</v>
+        <v>0.4883841032893044</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47144,13 +47144,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM289" t="n">
-        <v>0.02435543352765317</v>
+        <v>0.02435543352765289</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.00904582198402234</v>
+        <v>0.009045821984022376</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.4990078266507749</v>
+        <v>0.4990078266507766</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47297,10 +47297,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI290" t="n">
-        <v>7.175210595491394</v>
+        <v>7.175210595491395</v>
       </c>
       <c r="AJ290" t="n">
-        <v>-0.04951059854315165</v>
+        <v>-0.04951059854315254</v>
       </c>
       <c r="AK290" t="n">
         <v>7.151444380572274</v>
@@ -47309,13 +47309,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.02840267381959008</v>
+        <v>0.02840267381959001</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.008843610540066056</v>
+        <v>0.008843610540066053</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.5123725312709417</v>
+        <v>0.5123725312709416</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47465,7 +47465,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.05177635201935082</v>
+        <v>-0.05177635201934994</v>
       </c>
       <c r="AK291" t="n">
         <v>7.151307469847429</v>
@@ -47474,13 +47474,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.03189518855892809</v>
+        <v>0.03189518855892823</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008740250954211236</v>
+        <v>0.008740250954211215</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.5303980242931252</v>
+        <v>0.5303980242931245</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47627,10 +47627,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI292" t="n">
-        <v>7.172173616645314</v>
+        <v>7.172173616645312</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.06197368836162287</v>
+        <v>-0.06197368836162021</v>
       </c>
       <c r="AK292" t="n">
         <v>7.152170779642037</v>
@@ -47639,13 +47639,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.03448417181877479</v>
+        <v>0.03448417181877508</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008638296330047519</v>
+        <v>0.008638296330047493</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5364004192446541</v>
+        <v>0.536400419244653</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47795,7 +47795,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.08262387272163618</v>
+        <v>-0.08262387272163529</v>
       </c>
       <c r="AK293" t="n">
         <v>7.155242422656618</v>
@@ -47807,10 +47807,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008527848481957647</v>
+        <v>0.008527848481957645</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.5479838817473681</v>
+        <v>0.5479838817473677</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47957,10 +47957,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI294" t="n">
-        <v>7.184188525998638</v>
+        <v>7.18418852599864</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.08518854888682181</v>
+        <v>-0.08518854888682359</v>
       </c>
       <c r="AK294" t="n">
         <v>7.174067278312125</v>
@@ -47969,13 +47969,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM294" t="n">
-        <v>0.03996026841105382</v>
+        <v>0.03996026841105445</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008497979041970699</v>
+        <v>0.008497979041970659</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.553499551641869</v>
+        <v>0.5534995516418705</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48122,10 +48122,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI295" t="n">
-        <v>7.185513015749274</v>
+        <v>7.185513015749276</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.07571315384131516</v>
+        <v>-0.07571315384131694</v>
       </c>
       <c r="AK295" t="n">
         <v>7.175957423377739</v>
@@ -48134,13 +48134,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.04233079818885083</v>
+        <v>0.04233079818885077</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008432709457890224</v>
+        <v>0.008432709457890229</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5557951014363788</v>
+        <v>0.5557951014363787</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48293,19 +48293,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK296" t="n">
-        <v>7.174765662541792</v>
+        <v>7.174765662541793</v>
       </c>
       <c r="AL296" t="n">
-        <v>-0.05786569534818842</v>
+        <v>-0.05786569534818931</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04394124299371556</v>
+        <v>0.04394124299371591</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008396387260434506</v>
+        <v>0.008396387260434499</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.5565519909812453</v>
+        <v>0.5565519909812464</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48452,10 +48452,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI297" t="n">
-        <v>7.18593291662286</v>
+        <v>7.185932916622859</v>
       </c>
       <c r="AJ297" t="n">
-        <v>-0.01413278005669749</v>
+        <v>-0.0141327800566966</v>
       </c>
       <c r="AK297" t="n">
         <v>7.172730869790855</v>
@@ -48464,13 +48464,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04590755972499803</v>
+        <v>0.04590755972499789</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008346613473328291</v>
+        <v>0.008346613473328282</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5588443644440755</v>
+        <v>0.5588443644440741</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48617,10 +48617,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI298" t="n">
-        <v>7.187602005018014</v>
+        <v>7.187602005018013</v>
       </c>
       <c r="AJ298" t="n">
-        <v>-0.0581020927560516</v>
+        <v>-0.05810209275604983</v>
       </c>
       <c r="AK298" t="n">
         <v>7.168923754586179</v>
@@ -48629,10 +48629,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04658552832149689</v>
+        <v>0.04658552832149703</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008354655440128426</v>
+        <v>0.008354655440128402</v>
       </c>
       <c r="AO298" t="n">
         <v>0.5613325805619827</v>
@@ -48794,13 +48794,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04820692510781883</v>
+        <v>0.04820692510781933</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008303818071592054</v>
+        <v>0.008303818071592001</v>
       </c>
       <c r="AO299" t="n">
-        <v>0.5626464255878516</v>
+        <v>0.5626464255878519</v>
       </c>
       <c r="AP299" t="n">
         <v/>
@@ -48959,13 +48959,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.04983084886774771</v>
+        <v>0.04983084886774743</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008251024544031682</v>
+        <v>0.008251024544031704</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5641340630354323</v>
+        <v>0.5641340630354328</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49124,13 +49124,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.05170461329917048</v>
+        <v>0.05170461329917111</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008192726391276836</v>
+        <v>0.008192726391276807</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5658195968244545</v>
+        <v>0.5658195968244528</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49289,13 +49289,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05348369580043772</v>
+        <v>0.05348369580043773</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008143044151838252</v>
+        <v>0.008143044151838245</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5671346874885956</v>
+        <v>0.5671346874885959</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49442,10 +49442,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI303" t="n">
-        <v>7.175179910580593</v>
+        <v>7.175179910580594</v>
       </c>
       <c r="AJ303" t="n">
-        <v>-0.05588002196975328</v>
+        <v>-0.05588002196975417</v>
       </c>
       <c r="AK303" t="n">
         <v>7.165699812335961</v>
@@ -49454,13 +49454,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.0552098256436935</v>
+        <v>0.05520982564369371</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008124788470663643</v>
+        <v>0.008124788470663676</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5701242576280905</v>
+        <v>0.5701242576280907</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49607,10 +49607,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.173581841712229</v>
+        <v>7.173581841712227</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.05428195310138939</v>
+        <v>-0.05428195310138761</v>
       </c>
       <c r="AK304" t="n">
         <v>7.162626578418298</v>
@@ -49619,13 +49619,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05644890839995281</v>
+        <v>0.05644890839995315</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008105230252153447</v>
+        <v>0.008105230252153435</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5713754740215494</v>
+        <v>0.5713754740215509</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49772,10 +49772,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.176011726611838</v>
+        <v>7.176011726611837</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.06401173805592997</v>
+        <v>-0.06401173805592908</v>
       </c>
       <c r="AK305" t="n">
         <v>7.165542054185019</v>
@@ -49784,13 +49784,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05727663218544039</v>
+        <v>0.05727663218544052</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008124035226526509</v>
+        <v>0.00812403522652648</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5730004147442582</v>
+        <v>0.573000414744258</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49937,10 +49937,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.176983405221908</v>
+        <v>7.17698340522191</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.07778363334080485</v>
+        <v>-0.07778363334080662</v>
       </c>
       <c r="AK306" t="n">
         <v>7.170209849598846</v>
@@ -49949,13 +49949,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05825580143844532</v>
+        <v>0.05825580143844533</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.008106527117828759</v>
+        <v>0.008106527117828777</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.5728585525731367</v>
+        <v>0.5728585525731363</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50102,10 +50102,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.174841035863563</v>
+        <v>7.174841035863564</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.06734095956961816</v>
+        <v>-0.06734095956961905</v>
       </c>
       <c r="AK307" t="n">
         <v>7.166925629020364</v>
@@ -50114,13 +50114,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.05980113395910441</v>
+        <v>0.05980113395910436</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.008056914781095341</v>
+        <v>0.008056914781095353</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5723268395754482</v>
+        <v>0.5723268395754473</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50267,10 +50267,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.179777800337526</v>
+        <v>7.179777800337525</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.07227772404358035</v>
+        <v>-0.07227772404357946</v>
       </c>
       <c r="AK308" t="n">
         <v>7.163704513322672</v>
@@ -50282,10 +50282,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.008007544934860184</v>
+        <v>0.008007544934860181</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5724055344141876</v>
+        <v>0.5724055344141883</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50432,10 +50432,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.176651545551677</v>
+        <v>7.176651545551679</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.06915146925773197</v>
+        <v>-0.06915146925773374</v>
       </c>
       <c r="AK309" t="n">
         <v>7.163430147298699</v>
@@ -50444,13 +50444,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM309" t="n">
-        <v>0.06321929365038026</v>
+        <v>0.06321929365037962</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.007927773212025837</v>
+        <v>0.007927773212025854</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5724635828813827</v>
+        <v>0.572463582881384</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50597,10 +50597,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.173279688539582</v>
+        <v>7.173279688539583</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.06577961224563644</v>
+        <v>-0.06577961224563733</v>
       </c>
       <c r="AK310" t="n">
         <v>7.158871783064204</v>
@@ -50609,13 +50609,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.0652304825929222</v>
+        <v>0.06523048259292186</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007809540836127932</v>
+        <v>0.007809540836127948</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.571009056129113</v>
+        <v>0.5710090561291132</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50762,10 +50762,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.168542018724479</v>
+        <v>7.168542018724481</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.06194221098522146</v>
+        <v>-0.06194221098522323</v>
       </c>
       <c r="AK311" t="n">
         <v>7.152618309751275</v>
@@ -50774,13 +50774,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06741194340959927</v>
+        <v>0.067411943409599</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007660511838810949</v>
+        <v>0.007660511838810988</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5694124450603408</v>
+        <v>0.5694124450603424</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50927,10 +50927,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI312" t="n">
-        <v>7.161829635752617</v>
+        <v>7.161829635752616</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.0596296044720992</v>
+        <v>-0.05962960447209831</v>
       </c>
       <c r="AK312" t="n">
         <v>7.144956229005203</v>
@@ -50939,13 +50939,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.06977835201573281</v>
+        <v>0.06977835201573312</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007516908058882097</v>
+        <v>0.007516908058882096</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.5690369646398684</v>
+        <v>0.5690369646398685</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51095,7 +51095,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ313" t="n">
-        <v>-0.07699331565738188</v>
+        <v>-0.07699331565738099</v>
       </c>
       <c r="AK313" t="n">
         <v>7.140422114543136</v>
@@ -51104,13 +51104,13 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.07195366789421676</v>
+        <v>0.07195366789421653</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007394117938767422</v>
+        <v>0.007394117938767417</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5693040973288199</v>
+        <v>0.5693040973288186</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51269,16 +51269,16 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.07456301989532414</v>
+        <v>0.07456301989532385</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.007241314760731996</v>
+        <v>0.007241314760732032</v>
       </c>
       <c r="AO314" t="n">
         <v>0.5685877661607006</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.747050849919316</v>
+        <v>-1.747050849919297</v>
       </c>
       <c r="AQ314" t="n">
         <v>3.347457627118644</v>
@@ -51434,16 +51434,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.07747971887849607</v>
+        <v>0.07747971887849656</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.007090143655538702</v>
+        <v>0.0070901436555387</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.5681709745664091</v>
+        <v>0.5681709745664083</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.714775477944791</v>
+        <v>-1.714775477944774</v>
       </c>
       <c r="AQ315" t="n">
         <v>4.959016393442623</v>
@@ -51587,10 +51587,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI316" t="n">
-        <v>7.165084051386047</v>
+        <v>7.165084051386049</v>
       </c>
       <c r="AJ316" t="n">
-        <v>-0.08998410631768738</v>
+        <v>-0.08998410631768916</v>
       </c>
       <c r="AK316" t="n">
         <v>7.14582045097363</v>
@@ -51599,16 +51599,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.08000072584212836</v>
+        <v>0.08000072584212846</v>
       </c>
       <c r="AN316" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5684087510734968</v>
+        <v>0.5684087510734981</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.918272844943656</v>
+        <v>-1.918272844943728</v>
       </c>
       <c r="AQ316" t="n">
         <v>2.445795875198308</v>
@@ -51752,10 +51752,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.161419741275553</v>
+        <v>7.161419741275552</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.08971964514518227</v>
+        <v>-0.08971964514518138</v>
       </c>
       <c r="AK317" t="n">
         <v>7.155707108847959</v>
@@ -51764,16 +51764,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08204996863507528</v>
+        <v>0.08204996863507508</v>
       </c>
       <c r="AN317" t="n">
-        <v>0.006919462921967468</v>
+        <v>0.006919462921967476</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5672869954461461</v>
+        <v>0.5672869954461468</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.836036264369584</v>
+        <v>-1.836036264369517</v>
       </c>
       <c r="AQ317" t="n">
         <v>2.393753200204813</v>
@@ -51917,10 +51917,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.155488092579303</v>
+        <v>7.155488092579304</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.08548792091792645</v>
+        <v>-0.08548792091792734</v>
       </c>
       <c r="AK318" t="n">
         <v>7.150451326287159</v>
@@ -51929,16 +51929,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08469403553214211</v>
+        <v>0.08469403553214168</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006815201188096372</v>
+        <v>0.006815201188096393</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5663505631396781</v>
+        <v>0.5663505631396779</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.566065338893367</v>
+        <v>-1.566065338893395</v>
       </c>
       <c r="AQ318" t="n">
         <v>3.918650793650793</v>
@@ -52082,10 +52082,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.15883281736398</v>
+        <v>7.158832817363979</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.09523275404000575</v>
+        <v>-0.09523275404000398</v>
       </c>
       <c r="AK319" t="n">
         <v>7.147115644271845</v>
@@ -52094,16 +52094,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08699523504893142</v>
+        <v>0.08699523504893081</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006735083295172689</v>
+        <v>0.006735083295172709</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5654743012892984</v>
+        <v>0.5654743012892969</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.997166657650127</v>
+        <v>-1.997166657650022</v>
       </c>
       <c r="AQ319" t="n">
         <v>1.550480769230769</v>
@@ -52247,10 +52247,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.161703459649029</v>
+        <v>7.161703459649028</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.09030329409116788</v>
+        <v>-0.090303294091167</v>
       </c>
       <c r="AK320" t="n">
         <v>7.152131804583207</v>
@@ -52259,16 +52259,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.08901512474159586</v>
+        <v>0.08901512474159551</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006668288608758129</v>
+        <v>0.006668288608758136</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5631673144521655</v>
+        <v>0.5631673144521659</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.691698167555203</v>
+        <v>-1.691698167555149</v>
       </c>
       <c r="AQ320" t="n">
         <v>2.284382284382284</v>
@@ -52412,10 +52412,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.162535384813327</v>
+        <v>7.162535384813326</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.09293527952768255</v>
+        <v>-0.09293527952768166</v>
       </c>
       <c r="AK321" t="n">
         <v>7.157753883768605</v>
@@ -52424,16 +52424,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.09116436352661936</v>
+        <v>0.09116436352661951</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006624805625172246</v>
+        <v>0.006624805625172231</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5612585549312785</v>
+        <v>0.5612585549312774</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.767389998737694</v>
+        <v>-1.767389998737644</v>
       </c>
       <c r="AQ321" t="n">
         <v>3.007688828584351</v>
@@ -52577,10 +52577,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.166818450294681</v>
+        <v>7.166818450294679</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.09581835111255188</v>
+        <v>-0.0958183511125501</v>
       </c>
       <c r="AK322" t="n">
         <v>7.158620349112049</v>
@@ -52589,16 +52589,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.09320704864741212</v>
+        <v>0.09320704864741254</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006594358041710186</v>
+        <v>0.006594358041710158</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5590514368572459</v>
+        <v>0.5590514368572466</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.847275012727517</v>
+        <v>-1.84727501272743</v>
       </c>
       <c r="AQ322" t="n">
         <v>1.481562774363477</v>
@@ -52742,10 +52742,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.157691007010208</v>
+        <v>7.157691007010206</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.09439087425874337</v>
+        <v>-0.0943908742587416</v>
       </c>
       <c r="AK323" t="n">
         <v>7.164942158928604</v>
@@ -52754,16 +52754,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09491020692123982</v>
+        <v>0.09491020692123933</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006562900445417306</v>
+        <v>0.006562900445417311</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5551825155208129</v>
+        <v>0.5551825155208145</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.72521115778676</v>
+        <v>-1.72521115778668</v>
       </c>
       <c r="AQ323" t="n">
         <v>2.90920716112532</v>
@@ -52907,10 +52907,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.15177642643162</v>
+        <v>7.151776426431621</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.08777629673191267</v>
+        <v>-0.08777629673191356</v>
       </c>
       <c r="AK324" t="n">
         <v>7.154764404811184</v>
@@ -52919,16 +52919,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.0970468105051025</v>
+        <v>0.097046810505102</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006523984583215632</v>
+        <v>0.006523984583215639</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5522992358254815</v>
+        <v>0.5522992358254805</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.377617943930153</v>
+        <v>-1.377617943930198</v>
       </c>
       <c r="AQ324" t="n">
         <v>6.438923395445134</v>
@@ -53072,10 +53072,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.150992404319682</v>
+        <v>7.15099240431968</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.09309245238486774</v>
+        <v>-0.09309245238486596</v>
       </c>
       <c r="AK325" t="n">
         <v>7.150261540163492</v>
@@ -53084,16 +53084,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.09904197982498671</v>
+        <v>0.09904197982498698</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006505848878330779</v>
+        <v>0.006505848878330736</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5500699492277157</v>
+        <v>0.5500699492277152</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.590146417249081</v>
+        <v>-1.590146417249004</v>
       </c>
       <c r="AQ325" t="n">
         <v>4.245472837022133</v>
@@ -53237,10 +53237,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI326" t="n">
-        <v>7.147140093605207</v>
+        <v>7.147140093605204</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.09314019278733543</v>
+        <v>-0.09314019278733277</v>
       </c>
       <c r="AK326" t="n">
         <v>7.148879230661717</v>
@@ -53249,16 +53249,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.1013300516539142</v>
+        <v>0.1013300516539148</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006479631055951091</v>
+        <v>0.006479631055951007</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5478993564899672</v>
+        <v>0.5478993564899665</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.553948602584716</v>
+        <v>-1.553948602584604</v>
       </c>
       <c r="AQ326" t="n">
         <v>3.482003129890454</v>
@@ -53408,22 +53408,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK327" t="n">
-        <v>7.145816711184185</v>
+        <v>7.145816711184184</v>
       </c>
       <c r="AL327" t="n">
-        <v>-0.09881677984873605</v>
+        <v>-0.09881677984873516</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.1033273874042092</v>
+        <v>0.1033273874042088</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006468712737497656</v>
+        <v>0.006468712737497662</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5455500876237913</v>
+        <v>0.5455500876237902</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.629282185949435</v>
+        <v>-1.629282185949447</v>
       </c>
       <c r="AQ327" t="n">
         <v>2.064307458143074</v>
@@ -53570,7 +53570,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ328" t="n">
-        <v>-0.102826205226771</v>
+        <v>-0.1028262052267701</v>
       </c>
       <c r="AK328" t="n">
         <v>7.139092738717567</v>
@@ -53579,16 +53579,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1056457020972505</v>
+        <v>0.1056457020972507</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006435041090934217</v>
+        <v>0.006435041090934165</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5433399026839674</v>
+        <v>0.5433399026839665</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.897372056415481</v>
+        <v>-1.897372056415457</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.730470196223621</v>
@@ -53735,7 +53735,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ329" t="n">
-        <v>-0.09909609661495811</v>
+        <v>-0.099096096614959</v>
       </c>
       <c r="AK329" t="n">
         <v>7.140479586010682</v>
@@ -53744,16 +53744,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1076802390191602</v>
+        <v>0.10768023901916</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006405465077205527</v>
+        <v>0.006405465077205547</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5402459241219618</v>
+        <v>0.5402459241219614</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.683352602077191</v>
+        <v>-1.683352602077243</v>
       </c>
       <c r="AQ329" t="n">
         <v>2.684684684684685</v>
@@ -53897,10 +53897,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI330" t="n">
-        <v>7.145743344370558</v>
+        <v>7.145743344370562</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.1052431803385758</v>
+        <v>-0.1052431803385794</v>
       </c>
       <c r="AK330" t="n">
         <v>7.136632587022158</v>
@@ -53909,16 +53909,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.1100130126862084</v>
+        <v>0.1100130126862077</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.00636655476599019</v>
+        <v>0.006366554765990282</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5375708073661639</v>
+        <v>0.5375708073661647</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.89754466547331</v>
+        <v>-1.897544665473469</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.657894736842105</v>
@@ -54074,16 +54074,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1122475627674581</v>
+        <v>0.1122475627674583</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.00633726551246258</v>
+        <v>0.006337265512462553</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5341613739773232</v>
+        <v>0.5341613739773245</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.568124600971053</v>
+        <v>-1.568124600971055</v>
       </c>
       <c r="AQ331" t="n">
         <v>3.255297334244703</v>
@@ -54227,10 +54227,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI332" t="n">
-        <v>7.14251973303301</v>
+        <v>7.142519733033009</v>
       </c>
       <c r="AJ332" t="n">
-        <v>-0.1016195026252955</v>
+        <v>-0.1016195026252946</v>
       </c>
       <c r="AK332" t="n">
         <v>7.135172643569136</v>
@@ -54239,16 +54239,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.114650916606818</v>
+        <v>0.1146509166068179</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006337163869517234</v>
+        <v>0.006337163869517243</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5319767312874311</v>
+        <v>0.5319767312874306</v>
       </c>
       <c r="AP332" t="n">
-        <v>-1.658783102525386</v>
+        <v>-1.658783102525352</v>
       </c>
       <c r="AQ332" t="n">
         <v>2.572427572427572</v>
@@ -54404,16 +54404,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1171965158426948</v>
+        <v>0.1171965158426952</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.00636765350379247</v>
+        <v>0.006367653503792481</v>
       </c>
       <c r="AO333" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP333" t="n">
-        <v>-2.104725969419196</v>
+        <v>-2.104725969419202</v>
       </c>
       <c r="AQ333" t="n">
         <v>1.273937033430704</v>
@@ -54557,10 +54557,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI334" t="n">
-        <v>7.140851085964112</v>
+        <v>7.140851085964109</v>
       </c>
       <c r="AJ334" t="n">
-        <v>-0.1128512080344244</v>
+        <v>-0.1128512080344217</v>
       </c>
       <c r="AK334" t="n">
         <v>7.142783913375006</v>
@@ -54569,16 +54569,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1192272052402563</v>
+        <v>0.119227205240256</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.00638313303870985</v>
+        <v>0.006383133038709798</v>
       </c>
       <c r="AO334" t="n">
-        <v>0.5243060286247104</v>
+        <v>0.5243060286247103</v>
       </c>
       <c r="AP334" t="n">
-        <v>-1.999147626744425</v>
+        <v>-1.999147626744327</v>
       </c>
       <c r="AQ334" t="n">
         <v>2.515822784810127</v>
@@ -54722,10 +54722,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI335" t="n">
-        <v>7.139245392969565</v>
+        <v>7.139245392969567</v>
       </c>
       <c r="AJ335" t="n">
-        <v>-0.1112455150398777</v>
+        <v>-0.1112455150398795</v>
       </c>
       <c r="AK335" t="n">
         <v>7.141836927013541</v>
@@ -54734,16 +54734,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.1211746327267792</v>
+        <v>0.1211746327267789</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006404909068509461</v>
+        <v>0.006404909068509476</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.518531819719905</v>
+        <v>0.5185318197199045</v>
       </c>
       <c r="AP335" t="n">
-        <v>-1.877902810888236</v>
+        <v>-1.877902810888315</v>
       </c>
       <c r="AQ335" t="n">
         <v>3.726851851851852</v>
@@ -54887,10 +54887,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.136520216281902</v>
+        <v>7.136520216281903</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1085203383522142</v>
+        <v>-0.108520338352216</v>
       </c>
       <c r="AK336" t="n">
         <v>7.13958125183462</v>
@@ -54899,16 +54899,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM336" t="n">
-        <v>0.1228335954516143</v>
+        <v>0.1228335954516147</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006430223802628476</v>
+        <v>0.006430223802628449</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5122974965428486</v>
+        <v>0.5122974965428477</v>
       </c>
       <c r="AP336" t="n">
-        <v>-1.724005973971329</v>
+        <v>-1.724005973971403</v>
       </c>
       <c r="AQ336" t="n">
         <v>4.908160192713038</v>
@@ -55067,13 +55067,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006430805642792618</v>
+        <v>0.006430805642792636</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.5056597011855207</v>
+        <v>0.5056597011855208</v>
       </c>
       <c r="AP337" t="n">
-        <v>-2.466082822626627</v>
+        <v>-2.466082822626631</v>
       </c>
       <c r="AQ337" t="n">
         <v>1.212165736115193</v>
@@ -55217,10 +55217,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI338" t="n">
-        <v>7.13656285793475</v>
+        <v>7.136562857934749</v>
       </c>
       <c r="AJ338" t="n">
-        <v>-0.1404629090516929</v>
+        <v>-0.140462909051692</v>
       </c>
       <c r="AK338" t="n">
         <v>7.132705938528055</v>
@@ -55232,13 +55232,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006419568115912051</v>
+        <v>0.006419568115912044</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.4979995576252233</v>
+        <v>0.4979995576252224</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.72393398925766</v>
+        <v>-2.723933989257635</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.197647733792312</v>
@@ -55382,10 +55382,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.135435320996254</v>
+        <v>7.135435320996258</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.1393353721131971</v>
+        <v>-0.1393353721132016</v>
       </c>
       <c r="AK339" t="n">
         <v>7.134470034900207</v>
@@ -55394,16 +55394,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM339" t="n">
-        <v>0.1290155516631951</v>
+        <v>0.1290155516631957</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006423940675024553</v>
+        <v>0.006423940675024581</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4894561560517011</v>
+        <v>0.489456156051701</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.55912664103183</v>
+        <v>-2.559126641031981</v>
       </c>
       <c r="AQ339" t="n">
         <v>2.96218487394958</v>
@@ -55547,10 +55547,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.135221482968312</v>
+        <v>7.135221482968309</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.1391215340852554</v>
+        <v>-0.1391215340852527</v>
       </c>
       <c r="AK340" t="n">
         <v>7.133435115388912</v>
@@ -55559,16 +55559,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1313692321875792</v>
+        <v>0.1313692321875789</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006422605647444502</v>
+        <v>0.006422605647444513</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.4811392039904442</v>
+        <v>0.4811392039904447</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.444856859148843</v>
+        <v>-2.444856859148751</v>
       </c>
       <c r="AQ340" t="n">
         <v>4.097127222982216</v>
@@ -55712,10 +55712,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.129120131622732</v>
+        <v>7.129120131622726</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1360199653019309</v>
+        <v>-0.1360199653019256</v>
       </c>
       <c r="AK341" t="n">
         <v>7.132510325395203</v>
@@ -55724,16 +55724,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1334873867685108</v>
+        <v>0.1334873867685099</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006388619079873553</v>
+        <v>0.006388619079873509</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4724960612931048</v>
+        <v>0.4724960612931043</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.25337477106884</v>
+        <v>-2.253374771068672</v>
       </c>
       <c r="AQ341" t="n">
         <v>5.20582731889869</v>
@@ -55889,16 +55889,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1357975915367741</v>
+        <v>0.1357975915367747</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006324213907675122</v>
+        <v>0.006324213907675097</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4647750649852558</v>
+        <v>0.4647750649852552</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.330110951616984</v>
+        <v>-2.330110951616997</v>
       </c>
       <c r="AQ342" t="n">
         <v>2.867032392894462</v>
@@ -56042,10 +56042,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI343" t="n">
-        <v>7.122818285283532</v>
+        <v>7.122818285283529</v>
       </c>
       <c r="AJ343" t="n">
-        <v>-0.1394184172720578</v>
+        <v>-0.1394184172720543</v>
       </c>
       <c r="AK343" t="n">
         <v>7.123271418608565</v>
@@ -56054,16 +56054,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1386638579210689</v>
+        <v>0.1386638579210687</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006222091828703747</v>
+        <v>0.006222091828703702</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4565264017486775</v>
+        <v>0.4565264017486783</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.202249820930837</v>
+        <v>-2.202249820930741</v>
       </c>
       <c r="AQ343" t="n">
         <v>3.958120531154239</v>
@@ -56219,16 +56219,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1423176752089981</v>
+        <v>0.1423176752089984</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.006093783709292289</v>
+        <v>0.006093783709292283</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4497199830569214</v>
+        <v>0.4497199830569224</v>
       </c>
       <c r="AP344" t="n">
-        <v>-1.826129355478982</v>
+        <v>-1.826129355478997</v>
       </c>
       <c r="AQ344" t="n">
         <v>8.938826466916355</v>
@@ -56372,10 +56372,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI345" t="n">
-        <v>7.13316040486909</v>
+        <v>7.133160404869088</v>
       </c>
       <c r="AJ345" t="n">
-        <v>-0.1496604010543923</v>
+        <v>-0.1496604010543905</v>
       </c>
       <c r="AK345" t="n">
         <v>7.117219286120759</v>
@@ -56387,13 +56387,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.005984113522022499</v>
+        <v>0.005984113522022494</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4438783751010228</v>
+        <v>0.4438783751010233</v>
       </c>
       <c r="AP345" t="n">
-        <v>-2.383948193528485</v>
+        <v>-2.383948193528453</v>
       </c>
       <c r="AQ345" t="n">
         <v>7.771672771672771</v>
@@ -56537,10 +56537,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.129653220712091</v>
+        <v>7.12965322071209</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.152453189431573</v>
+        <v>-0.1524531894315722</v>
       </c>
       <c r="AK346" t="n">
         <v>7.126254605494273</v>
@@ -56549,16 +56549,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM346" t="n">
-        <v>0.1503893187551739</v>
+        <v>0.1503893187551748</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.005963146506628762</v>
+        <v>0.005963146506628741</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.441201873624737</v>
+        <v>0.4412018736247373</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.378539213893077</v>
+        <v>-2.378539213893073</v>
       </c>
       <c r="AQ346" t="n">
         <v>7.686335403726708</v>
@@ -56702,10 +56702,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.128380415829729</v>
+        <v>7.128380415829728</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1552802304354417</v>
+        <v>-0.1552802304354408</v>
       </c>
       <c r="AK347" t="n">
         <v>7.124321202568002</v>
@@ -56714,16 +56714,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1546287435667593</v>
+        <v>0.1546287435667592</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005975981199024824</v>
+        <v>0.005975981199024843</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.43858274446866</v>
+        <v>0.4385827444686599</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.373460496777943</v>
+        <v>-2.373460496777939</v>
       </c>
       <c r="AQ347" t="n">
         <v>7.602851799906499</v>
@@ -56867,10 +56867,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.124429161493114</v>
+        <v>7.124429161493117</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1469291996400868</v>
+        <v>-0.1469291996400894</v>
       </c>
       <c r="AK348" t="n">
         <v>7.121152072356459</v>
@@ -56879,16 +56879,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1587808126513008</v>
+        <v>0.1587808126513012</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005899221619931436</v>
+        <v>0.00589922161993145</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4336499747757655</v>
+        <v>0.4336499747757657</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.067615726703166</v>
+        <v>-2.067615726703258</v>
       </c>
       <c r="AQ348" t="n">
         <v>16.106154198124</v>
@@ -57044,16 +57044,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1636493008978486</v>
+        <v>0.1636493008978488</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.005897856672615022</v>
+        <v>0.005897856672615054</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4343048343988722</v>
+        <v>0.434304834398872</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.379299932963062</v>
+        <v>-2.379299932963078</v>
       </c>
       <c r="AQ349" t="n">
         <v>13.82418812989922</v>
@@ -57197,10 +57197,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI350" t="n">
-        <v>7.141397967314151</v>
+        <v>7.141397967314147</v>
       </c>
       <c r="AJ350" t="n">
-        <v>-0.1753978872055084</v>
+        <v>-0.1753978872055049</v>
       </c>
       <c r="AK350" t="n">
         <v>7.12802266215534</v>
@@ -57209,16 +57209,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1676675897666616</v>
+        <v>0.1676675897666615</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.005952601612807589</v>
+        <v>0.005952601612807557</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.4322693842687804</v>
+        <v>0.4322693842687806</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.666213337795703</v>
+        <v>-2.666213337795631</v>
       </c>
       <c r="AQ350" t="n">
         <v>12.62609649122807</v>
@@ -57362,10 +57362,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.140412492855501</v>
+        <v>7.140412492855504</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.1723124219021317</v>
+        <v>-0.1723124219021352</v>
       </c>
       <c r="AK351" t="n">
         <v>7.137738577466652</v>
@@ -57374,16 +57374,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1710383543493662</v>
+        <v>0.1710383543493657</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.00606844425683546</v>
+        <v>0.006068444256835448</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4285062718639572</v>
+        <v>0.4285062718639565</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.484503876551758</v>
+        <v>-2.484503876551866</v>
       </c>
       <c r="AQ351" t="n">
         <v>19.78092783505155</v>
@@ -57527,10 +57527,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.138020503721584</v>
+        <v>7.138020503721587</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1699204327682153</v>
+        <v>-0.169920432768218</v>
       </c>
       <c r="AK352" t="n">
         <v>7.13663078035759</v>
@@ -57539,16 +57539,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1761956824342154</v>
+        <v>0.176195682434215</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.006402952059750703</v>
+        <v>0.006402952059750722</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4374093872433956</v>
+        <v>0.4374093872433962</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.339539137329532</v>
+        <v>-2.339539137329609</v>
       </c>
       <c r="AQ352" t="n">
         <v>19.57184935830002</v>
@@ -57692,28 +57692,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.136830620687383</v>
+        <v>7.136830620687384</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.1769307183436331</v>
+        <v>-0.1769307183436339</v>
       </c>
       <c r="AK353" t="n">
-        <v>7.140049017840021</v>
+        <v>7.14004901784002</v>
       </c>
       <c r="AL353" t="n">
-        <v>-0.1801491154962713</v>
+        <v>-0.1801491154962704</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.1796308914905974</v>
+        <v>0.1796308914905975</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.006948414844703805</v>
+        <v>0.006948414844703821</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4458727441769483</v>
+        <v>0.4458727441769479</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.429725176265745</v>
+        <v>-2.429725176265773</v>
       </c>
       <c r="AQ353" t="n">
         <v>17.85198928056071</v>
@@ -57853,10 +57853,10 @@
         <v/>
       </c>
       <c r="AI354" t="n">
-        <v>7.13363857926656</v>
+        <v>7.133638579266565</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1699387616090897</v>
+        <v>-0.1699387616090942</v>
       </c>
       <c r="AK354" t="n">
         <v>7.13798584867198</v>
@@ -57865,16 +57865,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1829391475229935</v>
+        <v>0.1829391475229931</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.00760204732154433</v>
+        <v>0.007602047321544403</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4545618931940826</v>
+        <v>0.4545618931940824</v>
       </c>
       <c r="AP354" t="n">
-        <v>-2.187901460946118</v>
+        <v>-2.187901460946225</v>
       </c>
       <c r="AQ354" t="n">
         <v>27</v>
@@ -58018,10 +58018,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI355" t="n">
-        <v>7.126409468908567</v>
+        <v>7.12640946890857</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1538094856932348</v>
+        <v>-0.1538094856932375</v>
       </c>
       <c r="AK355" t="n">
         <v>7.138565167526504</v>
@@ -58030,16 +58030,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1834764543657157</v>
+        <v>0.1834764543657148</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.007712839302340297</v>
+        <v>0.007712839302340374</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4511257152112024</v>
+        <v>0.4511257152112026</v>
       </c>
       <c r="AP355" t="n">
-        <v>-1.755049451768825</v>
+        <v>-1.755049451768886</v>
       </c>
       <c r="AQ355" t="n">
         <v>22.64726472647265</v>
@@ -58183,10 +58183,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI356" t="n">
-        <v>7.110999512759042</v>
+        <v>7.110999512759045</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1383995295437099</v>
+        <v>-0.1383995295437126</v>
       </c>
       <c r="AK356" t="n">
         <v>7.137040595974374</v>
@@ -58195,16 +58195,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1869739626316108</v>
+        <v>0.1869739626316104</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.008354609519984808</v>
+        <v>0.00835460951998479</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4618871834350127</v>
+        <v>0.4618871834350119</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.36117170161433</v>
+        <v>-1.36117170161439</v>
       </c>
       <c r="AQ356" t="n">
         <v>16.83333333333333</v>
@@ -58360,16 +58360,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1901371272406383</v>
+        <v>0.1901371272406391</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.008787529863310259</v>
+        <v>0.008787529863310189</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4631528842621208</v>
+        <v>0.4631528842621211</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.397972679085658</v>
+        <v>-1.397972679085653</v>
       </c>
       <c r="AQ357" t="n">
         <v>10.27107565125445</v>
@@ -58513,10 +58513,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI358" t="n">
-        <v>7.102293381264122</v>
+        <v>7.10229338126412</v>
       </c>
       <c r="AJ358" t="n">
-        <v>-0.1477931828998642</v>
+        <v>-0.1477931828998624</v>
       </c>
       <c r="AK358" t="n">
         <v>7.113436809075056</v>
@@ -58525,16 +58525,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.193945683545753</v>
+        <v>0.1939456835457532</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.009306466714917755</v>
+        <v>0.009306466714917722</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4650211967660295</v>
+        <v>0.4650211967660294</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.541264897302136</v>
+        <v>-1.541264897302089</v>
       </c>
       <c r="AQ358" t="n">
         <v>11.17081447963801</v>
@@ -58690,16 +58690,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.1968971496416338</v>
+        <v>0.1968971496416331</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.009915270508004639</v>
+        <v>0.009915270508004642</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4658112293095935</v>
+        <v>0.4658112293095933</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.31649049592788</v>
+        <v>-1.316490495927876</v>
       </c>
       <c r="AQ359" t="n">
         <v>11.48404993065187</v>
@@ -58855,16 +58855,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.200157477381068</v>
+        <v>0.2001574773810679</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.01045224758824685</v>
+        <v>0.01045224758824684</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4652001227613058</v>
+        <v>0.4652001227613064</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.579791331180152</v>
+        <v>-1.579791331180149</v>
       </c>
       <c r="AQ360" t="n">
         <v>5.197750362844703</v>
@@ -59008,10 +59008,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI361" t="n">
-        <v>7.112155432918444</v>
+        <v>7.112155432918446</v>
       </c>
       <c r="AJ361" t="n">
-        <v>-0.1611552192953969</v>
+        <v>-0.1611552192953987</v>
       </c>
       <c r="AK361" t="n">
         <v>7.115439870473561</v>
@@ -59020,16 +59020,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2059164257597547</v>
+        <v>0.2059164257597553</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.0109580623600705</v>
+        <v>0.01095806236007055</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4647071558511972</v>
+        <v>0.4647071558511969</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.776960795982061</v>
+        <v>-1.776960795982097</v>
       </c>
       <c r="AQ361" t="n">
         <v>6.613262127280819</v>
@@ -59185,16 +59185,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2103846028094625</v>
+        <v>0.2103846028094628</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01138655624224671</v>
+        <v>0.01138655624224677</v>
       </c>
       <c r="AO362" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.805176669449944</v>
+        <v>-1.805176669449939</v>
       </c>
       <c r="AQ362" t="n">
         <v>11.26834381551363</v>
@@ -59338,10 +59338,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI363" t="n">
-        <v>7.110775793344654</v>
+        <v>7.110775793344653</v>
       </c>
       <c r="AJ363" t="n">
-        <v>-0.1730759985753672</v>
+        <v>-0.1730759985753663</v>
       </c>
       <c r="AK363" t="n">
         <v>7.127056499711662</v>
@@ -59350,16 +59350,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2137349114935566</v>
+        <v>0.2137349114935569</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.0118427752189066</v>
+        <v>0.01184277521890661</v>
       </c>
       <c r="AO363" t="n">
-        <v>0.4573024605378192</v>
+        <v>0.4573024605378193</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.970721347282121</v>
+        <v>-1.970721347282097</v>
       </c>
       <c r="AQ363" t="n">
         <v>12.59110006001886</v>
@@ -59515,16 +59515,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2192999169256231</v>
+        <v>0.2192999169256238</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01242692746354283</v>
+        <v>0.01242692746354282</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4593518446085587</v>
+        <v>0.4593518446085588</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.52788252440829</v>
+        <v>-1.527882524408286</v>
       </c>
       <c r="AQ364" t="n">
         <v>14.25925925925926</v>
@@ -59668,28 +59668,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI365" t="n">
-        <v>7.095070446253632</v>
+        <v>7.095070446253633</v>
       </c>
       <c r="AJ365" t="n">
-        <v>-0.1572705156811223</v>
+        <v>-0.1572705156811232</v>
       </c>
       <c r="AK365" t="n">
-        <v>7.099084322920754</v>
+        <v>7.099084322920755</v>
       </c>
       <c r="AL365" t="n">
-        <v>-0.1612843923482439</v>
+        <v>-0.1612843923482448</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2273791016644665</v>
+        <v>0.2273791016644669</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01301934706840001</v>
+        <v>0.01301934706839999</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4655241261491888</v>
+        <v>0.4655241261491886</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.560976287055567</v>
+        <v>-1.560976287055583</v>
       </c>
       <c r="AQ365" t="n">
         <v>12.30266964211918</v>
@@ -59833,10 +59833,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.077412848446856</v>
+        <v>7.077412848446851</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.138612990353594</v>
+        <v>-0.1386129903535895</v>
       </c>
       <c r="AK366" t="n">
         <v>7.107752072150756</v>
@@ -59845,16 +59845,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2346680713248287</v>
+        <v>0.2346680713248289</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01366280940279221</v>
+        <v>0.01366280940279216</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4682122340216205</v>
+        <v>0.4682122340216202</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.128995443400246</v>
+        <v>-1.128995443400145</v>
       </c>
       <c r="AQ366" t="n">
         <v>19.78896103896104</v>
@@ -59998,10 +59998,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.067855559671529</v>
+        <v>7.067855559671527</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1458556283360801</v>
+        <v>-0.1458556283360775</v>
       </c>
       <c r="AK367" t="n">
         <v>7.100856094477853</v>
@@ -60010,16 +60010,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2404731763378833</v>
+        <v>0.2404731763378842</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01427110593278805</v>
+        <v>0.01427110593278799</v>
       </c>
       <c r="AO367" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.276791017470117</v>
+        <v>-1.276791017470057</v>
       </c>
       <c r="AQ367" t="n">
         <v>19.21789045682851</v>
@@ -60163,10 +60163,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.081794385763168</v>
+        <v>7.081794385763164</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1711942003688813</v>
+        <v>-0.1711942003688769</v>
       </c>
       <c r="AK368" t="n">
         <v>7.090764621929079</v>
@@ -60175,16 +60175,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2453259423721924</v>
+        <v>0.2453259423721931</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01502424352484376</v>
+        <v>0.01502424352484369</v>
       </c>
       <c r="AO368" t="n">
-        <v>0.4756424387980304</v>
+        <v>0.4756424387980298</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.810119419882235</v>
+        <v>-1.81011941988214</v>
       </c>
       <c r="AQ368" t="n">
         <v>15.58583959899749</v>
@@ -60328,10 +60328,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.068234493406101</v>
+        <v>7.068234493406102</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1557345887735329</v>
+        <v>-0.1557345887735337</v>
       </c>
       <c r="AK369" t="n">
         <v>7.110983013755962</v>
@@ -60340,16 +60340,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2481172514763511</v>
+        <v>0.2481172514763508</v>
       </c>
       <c r="AN369" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.4781214750573156</v>
+        <v>0.4781214750573159</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.446962704064594</v>
+        <v>-1.446962704064616</v>
       </c>
       <c r="AQ369" t="n">
         <v>19.37668333974606</v>
@@ -60493,28 +60493,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.04701169343388</v>
+        <v>7.047011693433886</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1469114622632253</v>
+        <v>-0.1469114622632315</v>
       </c>
       <c r="AK370" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL370" t="n">
-        <v>-0.1936362268489633</v>
+        <v>-0.1936362268489642</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2517176519946887</v>
+        <v>0.2517176519946896</v>
       </c>
       <c r="AN370" t="n">
-        <v>0.01672959897123727</v>
+        <v>0.01672959897123732</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4820447952807055</v>
+        <v>0.482044795280705</v>
       </c>
       <c r="AP370" t="n">
-        <v>-1.238268438219663</v>
+        <v>-1.238268438219799</v>
       </c>
       <c r="AQ370" t="n">
         <v>18.70084694494858</v>
@@ -60658,28 +60658,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.043635211714486</v>
+        <v>7.043635211714482</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1356352193438806</v>
+        <v>-0.135635219343877</v>
       </c>
       <c r="AK371" t="n">
-        <v>7.069112439760901</v>
+        <v>7.069112439760902</v>
       </c>
       <c r="AL371" t="n">
-        <v>-0.1611124473902956</v>
+        <v>-0.1611124473902965</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2568291528619769</v>
+        <v>0.2568291528619773</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.0175878422274923</v>
+        <v>0.01758784222749221</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.488825658962754</v>
+        <v>0.4888256589627545</v>
       </c>
       <c r="AP371" t="n">
-        <v>-0.9814129795049584</v>
+        <v>-0.9814129795048806</v>
       </c>
       <c r="AQ371" t="n">
         <v>24.1025641025641</v>
@@ -60823,10 +60823,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.04532069676962</v>
+        <v>7.045320696769622</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.1373207043990146</v>
+        <v>-0.1373207043990163</v>
       </c>
       <c r="AK372" t="n">
         <v>7.067486653848666</v>
@@ -60835,16 +60835,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2611441025487396</v>
+        <v>0.2611441025487395</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01863884916361523</v>
+        <v>0.01863884916361525</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.4958891106408189</v>
+        <v>0.4958891106408185</v>
       </c>
       <c r="AP372" t="n">
-        <v>-1.009808424846927</v>
+        <v>-1.009808424846966</v>
       </c>
       <c r="AQ372" t="n">
         <v>21.7489772063121</v>
@@ -60988,10 +60988,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.052957186540212</v>
+        <v>7.052957186540217</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1449571941696064</v>
+        <v>-0.1449571941696117</v>
       </c>
       <c r="AK373" t="n">
         <v>7.066060765041626</v>
@@ -61000,16 +61000,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2646928033319788</v>
+        <v>0.2646928033319798</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.0196144718499898</v>
+        <v>0.01961447184998982</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.4990325267638065</v>
+        <v>0.4990325267638059</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.166351458434145</v>
+        <v>-1.16635145843426</v>
       </c>
       <c r="AQ373" t="n">
         <v>19.06557494792789</v>
@@ -61153,28 +61153,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.055218091951103</v>
+        <v>7.055218091951101</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1472180995804973</v>
+        <v>-0.1472180995804955</v>
       </c>
       <c r="AK374" t="n">
-        <v>7.06464674575351</v>
+        <v>7.064646745753511</v>
       </c>
       <c r="AL374" t="n">
-        <v>-0.1566467533829048</v>
+        <v>-0.1566467533829057</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2692457951306194</v>
+        <v>0.2692457951306195</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.02045122459205891</v>
+        <v>0.02045122459205889</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.5009265659871951</v>
+        <v>0.5009265659871953</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.203609071588874</v>
+        <v>-1.203609071588834</v>
       </c>
       <c r="AQ374" t="n">
         <v>18.07909604519774</v>
@@ -61318,10 +61318,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI375" t="n">
-        <v>7.050463258619345</v>
+        <v>7.050463258619342</v>
       </c>
       <c r="AJ375" t="n">
-        <v>-0.1423631304455171</v>
+        <v>-0.1423631304455135</v>
       </c>
       <c r="AK375" t="n">
         <v>7.063274589921972</v>
@@ -61330,16 +61330,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM375" t="n">
-        <v>0.2738618637550991</v>
+        <v>0.2738618637550985</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.02103732430364855</v>
+        <v>0.02103732430364852</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.5007948901071723</v>
+        <v>0.5007948901071727</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.087047157347476</v>
+        <v>-1.087047157347398</v>
       </c>
       <c r="AQ375" t="n">
         <v>22.51545246197653</v>
@@ -61656,16 +61656,16 @@
         <v/>
       </c>
       <c r="AM377" t="n">
-        <v>0.2803441195876753</v>
+        <v>0.280344119587675</v>
       </c>
       <c r="AN377" t="n">
-        <v>0.02230845224183688</v>
+        <v>0.02230845224183686</v>
       </c>
       <c r="AO377" t="n">
-        <v>0.5036776407221312</v>
+        <v>0.5036776407221306</v>
       </c>
       <c r="AP377" t="n">
-        <v>-1.240469901342109</v>
+        <v>-1.24046990134211</v>
       </c>
       <c r="AQ377" t="n">
         <v>24.73242108115432</v>
@@ -61809,10 +61809,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI378" t="n">
-        <v>7.056824809597052</v>
+        <v>7.056824809597053</v>
       </c>
       <c r="AJ378" t="n">
-        <v>-0.1737247767906558</v>
+        <v>-0.1737247767906567</v>
       </c>
       <c r="AK378" t="n">
         <v>7.071238163852278</v>
@@ -61821,16 +61821,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM378" t="n">
-        <v>0.2841407798055452</v>
+        <v>0.2841407798055449</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02276542233315985</v>
+        <v>0.02276542233315987</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.5036956996297983</v>
+        <v>0.5036956996297977</v>
       </c>
       <c r="AP378" t="n">
-        <v>-1.731904723858127</v>
+        <v>-1.731904723858146</v>
       </c>
       <c r="AQ378" t="n">
         <v>21.71131547381048</v>
@@ -61974,10 +61974,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.047265922594908</v>
+        <v>7.04726592259491</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.178065692950133</v>
+        <v>-0.1780656929501347</v>
       </c>
       <c r="AK379" t="n">
         <v>7.075283303194255</v>
@@ -61986,16 +61986,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2869603504542598</v>
+        <v>0.2869603504542605</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02324367830537833</v>
+        <v>0.02324367830537832</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5029697249741724</v>
+        <v>0.5029697249741727</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.794655947125261</v>
+        <v>-1.794655947125298</v>
       </c>
       <c r="AQ379" t="n">
         <v>10.56582743246787</v>
@@ -62139,10 +62139,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.030237372659579</v>
+        <v>7.030237372659574</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.1893374283541593</v>
+        <v>-0.189337428354154</v>
       </c>
       <c r="AK380" t="n">
         <v>7.061088020066238</v>
@@ -62151,16 +62151,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2909556153842324</v>
+        <v>0.2909556153842325</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02343150180192457</v>
+        <v>0.02343150180192449</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5011874977636526</v>
+        <v>0.501187497763653</v>
       </c>
       <c r="AP380" t="n">
-        <v>-1.995867432252799</v>
+        <v>-1.995867432252689</v>
       </c>
       <c r="AQ380" t="n">
         <v>2.416129032258064</v>
@@ -62304,10 +62304,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.074556523891907</v>
+        <v>7.074556523891909</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.2166563812222293</v>
+        <v>-0.2166563812222311</v>
       </c>
       <c r="AK381" t="n">
         <v>7.045371831199247</v>
@@ -62316,16 +62316,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.2963660759601009</v>
+        <v>0.2963660759601011</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02388105320115906</v>
+        <v>0.02388105320115907</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.5011837436137511</v>
+        <v>0.5011837436137521</v>
       </c>
       <c r="AP381" t="n">
-        <v>-2.500511004141982</v>
+        <v>-2.50051100414202</v>
       </c>
       <c r="AQ381" t="n">
         <v>14.7968253968254</v>
@@ -62469,10 +62469,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.103552248295403</v>
+        <v>7.103552248295395</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.2215522788129807</v>
+        <v>-0.2215522788129736</v>
       </c>
       <c r="AK382" t="n">
         <v>7.078406423284397</v>
@@ -62481,16 +62481,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.2998407912997099</v>
+        <v>0.29984079129971</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02427773372157407</v>
+        <v>0.02427773372157399</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.4964684575356701</v>
+        <v>0.4964684575356704</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.525110632656068</v>
+        <v>-2.525110632655932</v>
       </c>
       <c r="AQ382" t="n">
         <v>19.44131983502062</v>
@@ -62646,16 +62646,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.3035220749319821</v>
+        <v>0.3035220749319825</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02465824743687013</v>
+        <v>0.02465824743687012</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.4899948718309223</v>
+        <v>0.4899948718309226</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.23568219987259</v>
+        <v>-2.235682199872597</v>
       </c>
       <c r="AQ383" t="n">
         <v>23.21911909448819</v>
@@ -62799,10 +62799,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI384" t="n">
-        <v>7.127779594400253</v>
+        <v>7.12777959440025</v>
       </c>
       <c r="AJ384" t="n">
-        <v>-0.2307797584322353</v>
+        <v>-0.2307797584322326</v>
       </c>
       <c r="AK384" t="n">
         <v>7.110202206771168</v>
@@ -62811,16 +62811,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3056770963992276</v>
+        <v>0.3056770963992281</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02512392944114575</v>
+        <v>0.02512392944114572</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.48360047858094</v>
+        <v>0.4836004785809395</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.571380587954148</v>
+        <v>-2.571380587954108</v>
       </c>
       <c r="AQ384" t="n">
         <v>22.65322189922481</v>
@@ -62964,28 +62964,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.117424820782308</v>
+        <v>7.117424820782309</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.2204249848142901</v>
+        <v>-0.2204249848142918</v>
       </c>
       <c r="AK385" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL385" t="n">
-        <v>-0.21822100705125</v>
+        <v>-0.2182210070512509</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3083414575758079</v>
+        <v>0.3083414575758074</v>
       </c>
       <c r="AN385" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4749824439402989</v>
+        <v>0.474982443940299</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.310186935699684</v>
+        <v>-2.310186935699726</v>
       </c>
       <c r="AQ385" t="n">
         <v>25.18485390578414</v>
@@ -63129,10 +63129,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.116315246651979</v>
+        <v>7.116315246651977</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2198151360257583</v>
+        <v>-0.2198151360257565</v>
       </c>
       <c r="AK386" t="n">
         <v>7.112470209890858</v>
@@ -63141,16 +63141,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3094443575020188</v>
+        <v>0.3094443575020182</v>
       </c>
       <c r="AN386" t="n">
-        <v>0.02578750722031873</v>
+        <v>0.0257875072203187</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.467103914503924</v>
+        <v>0.4671039145039241</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.244592729417366</v>
+        <v>-2.244592729417341</v>
       </c>
       <c r="AQ386" t="n">
         <v>24.98825601879037</v>
@@ -63294,28 +63294,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.109165799046382</v>
+        <v>7.109165799046384</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.1981660241135206</v>
+        <v>-0.1981660241135224</v>
       </c>
       <c r="AK387" t="n">
-        <v>7.105086649080123</v>
+        <v>7.105086649080124</v>
       </c>
       <c r="AL387" t="n">
-        <v>-0.1940868741472617</v>
+        <v>-0.1940868741472626</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3112159059696449</v>
+        <v>0.3112159059696454</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.02619128791084347</v>
+        <v>0.02619128791084346</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.4597800393113443</v>
+        <v>0.4597800393113445</v>
       </c>
       <c r="AP387" t="n">
-        <v>-1.805342281525792</v>
+        <v>-1.805342281525831</v>
       </c>
       <c r="AQ387" t="n">
         <v>26.31563728891973</v>
@@ -63459,10 +63459,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.14047665869759</v>
+        <v>7.140476658697598</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.2639765289978833</v>
+        <v>-0.2639765289978913</v>
       </c>
       <c r="AK388" t="n">
         <v>7.107009848336411</v>
@@ -63471,16 +63471,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3120213667410841</v>
+        <v>0.3120213667410843</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.02660872919284651</v>
+        <v>0.02660872919284657</v>
       </c>
       <c r="AO388" t="n">
-        <v>0.4527828726277021</v>
+        <v>0.4527828726277016</v>
       </c>
       <c r="AP388" t="n">
-        <v>-2.926525521844932</v>
+        <v>-2.926525521845077</v>
       </c>
       <c r="AQ388" t="n">
         <v>18.93654591023012</v>
@@ -63624,10 +63624,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.192104266103096</v>
+        <v>7.192104266103097</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.3266042928059765</v>
+        <v>-0.3266042928059782</v>
       </c>
       <c r="AK389" t="n">
         <v>7.130667004235951</v>
@@ -63636,16 +63636,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3119580514589062</v>
+        <v>0.3119580514589064</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02723917591229311</v>
+        <v>0.02723917591229313</v>
       </c>
       <c r="AO389" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP389" t="n">
-        <v>-3.819878067727012</v>
+        <v>-3.819878067727037</v>
       </c>
       <c r="AQ389" t="n">
         <v>21.80170575692964</v>
@@ -63801,7 +63801,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3060770546706496</v>
+        <v>0.3060770546706492</v>
       </c>
       <c r="AN390" t="n">
         <v>0.02737088803905663</v>
@@ -63810,7 +63810,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP390" t="n">
-        <v>-3.687605685732569</v>
+        <v>-3.687605685732565</v>
       </c>
       <c r="AQ390" t="n">
         <v>19.40022111663903</v>
@@ -63954,10 +63954,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI391" t="n">
-        <v>7.164105908482372</v>
+        <v>7.16410590848237</v>
       </c>
       <c r="AJ391" t="n">
-        <v>-0.2680058642318839</v>
+        <v>-0.2680058642318812</v>
       </c>
       <c r="AK391" t="n">
         <v>7.162206823443969</v>
@@ -63966,16 +63966,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3021518080029217</v>
+        <v>0.3021518080029227</v>
       </c>
       <c r="AN391" t="n">
-        <v>0.02724691784252936</v>
+        <v>0.02724691784252931</v>
       </c>
       <c r="AO391" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP391" t="n">
-        <v>-2.57053351494494</v>
+        <v>-2.570533514944897</v>
       </c>
       <c r="AQ391" t="n">
         <v>23.69553376906318</v>
@@ -64119,10 +64119,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.165713254747862</v>
+        <v>7.165713254747866</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.2102131288628524</v>
+        <v>-0.2102131288628559</v>
       </c>
       <c r="AK392" t="n">
         <v>7.141021818380439</v>
@@ -64131,16 +64131,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.3004913268435102</v>
+        <v>0.3004913268435098</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02739193077523432</v>
+        <v>0.02739193077523433</v>
       </c>
       <c r="AO392" t="n">
-        <v>0.3752726470948199</v>
+        <v>0.3752726470948202</v>
       </c>
       <c r="AP392" t="n">
-        <v>-1.622506315391895</v>
+        <v>-1.62250631539195</v>
       </c>
       <c r="AQ392" t="n">
         <v>30.48787033061399</v>
@@ -64284,10 +64284,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.208249532027231</v>
+        <v>7.208249532027229</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.321949445052133</v>
+        <v>-0.3219494450521312</v>
       </c>
       <c r="AK393" t="n">
         <v>7.146296571548195</v>
@@ -64296,16 +64296,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.2982197220770058</v>
+        <v>0.2982197220770054</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02742417953210373</v>
+        <v>0.02742417953210363</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3625782951332475</v>
+        <v>0.3625782951332472</v>
       </c>
       <c r="AP393" t="n">
-        <v>-3.254902570581985</v>
+        <v>-3.254902570581956</v>
       </c>
       <c r="AQ393" t="n">
         <v>25.17454776261504</v>
@@ -64449,28 +64449,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.193412187855726</v>
+        <v>7.193412187855718</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3208121092729623</v>
+        <v>-0.3208121092729543</v>
       </c>
       <c r="AK394" t="n">
-        <v>7.176497065376473</v>
+        <v>7.176497065376474</v>
       </c>
       <c r="AL394" t="n">
-        <v>-0.3038969867937098</v>
+        <v>-0.3038969867937107</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2910761841041086</v>
+        <v>0.2910761841041076</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02685747952387156</v>
+        <v>0.02685747952387152</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3370674577034442</v>
+        <v>0.3370674577034428</v>
       </c>
       <c r="AP394" t="n">
-        <v>-3.109921360957079</v>
+        <v>-3.109921360956968</v>
       </c>
       <c r="AQ394" t="n">
         <v>26.0765300802836</v>
@@ -64614,10 +64614,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.227115602342041</v>
+        <v>7.227115602342048</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3273157785810543</v>
+        <v>-0.3273157785810614</v>
       </c>
       <c r="AK395" t="n">
         <v>7.185469892270627</v>
@@ -64626,16 +64626,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.281226998760588</v>
+        <v>0.2812269987605887</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.0269718053742217</v>
+        <v>0.02697180537422167</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.3136210223326474</v>
+        <v>0.3136210223326478</v>
       </c>
       <c r="AP395" t="n">
-        <v>-3.083113339494347</v>
+        <v>-3.083113339494449</v>
       </c>
       <c r="AQ395" t="n">
         <v>26.97327852004111</v>
@@ -64779,10 +64779,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.187163192389367</v>
+        <v>7.187163192389372</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3014629665592885</v>
+        <v>-0.3014629665592938</v>
       </c>
       <c r="AK396" t="n">
         <v>7.208338760609084</v>
@@ -64791,16 +64791,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2681836981576121</v>
+        <v>0.2681836981576122</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02658698789673927</v>
+        <v>0.02658698789673936</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.2859081509452629</v>
+        <v>0.285908150945263</v>
       </c>
       <c r="AP396" t="n">
-        <v>-2.633491494913968</v>
+        <v>-2.633491494914038</v>
       </c>
       <c r="AQ396" t="n">
         <v>27.8419452887538</v>
@@ -64944,10 +64944,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.214951953115579</v>
+        <v>7.214951953115591</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3349518386746606</v>
+        <v>-0.334951838674673</v>
       </c>
       <c r="AK397" t="n">
         <v>7.186200492654655</v>
@@ -64956,16 +64956,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2591628297636748</v>
+        <v>0.2591628297636744</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02587977479594331</v>
+        <v>0.02587977479594339</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.2661082014924122</v>
+        <v>0.266108201492412</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.993133945204733</v>
+        <v>-2.993133945204886</v>
       </c>
       <c r="AQ397" t="n">
         <v>27.30246728598542</v>
@@ -65109,10 +65109,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.197430004066453</v>
+        <v>7.197430004066455</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.3056300773086402</v>
+        <v>-0.305630077308642</v>
       </c>
       <c r="AK398" t="n">
         <v>7.201835396295348</v>
@@ -65121,16 +65121,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2466333883508324</v>
+        <v>0.2466333883508319</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02476543449503272</v>
+        <v>0.0247654344950328</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.2401258754735008</v>
+        <v>0.2401258754735003</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.52453807526201</v>
+        <v>-2.524538075262018</v>
       </c>
       <c r="AQ398" t="n">
         <v>26.03910174332709</v>
@@ -65277,25 +65277,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.3291230670577878</v>
+        <v>-0.3291230670577869</v>
       </c>
       <c r="AK399" t="n">
-        <v>7.179650721554483</v>
+        <v>7.179650721554484</v>
       </c>
       <c r="AL399" t="n">
-        <v>-0.2786506986662998</v>
+        <v>-0.2786506986663007</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2377807761788565</v>
+        <v>0.2377807761788571</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.02334020127887796</v>
+        <v>0.02334020127887793</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.2171758918683913</v>
+        <v>0.2171758918683914</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.752873232964097</v>
+        <v>-2.752873232964071</v>
       </c>
       <c r="AQ399" t="n">
         <v>26.56614219114219</v>
@@ -65439,10 +65439,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI400" t="n">
-        <v>7.208528037732954</v>
+        <v>7.20852803773295</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.2978281933726024</v>
+        <v>-0.2978281933725988</v>
       </c>
       <c r="AK400" t="n">
         <v>7.206616000051887</v>
@@ -65451,16 +65451,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2255544515066683</v>
+        <v>0.2255544515066686</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.0206724522626572</v>
+        <v>0.0206724522626571</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.1898019966940708</v>
+        <v>0.1898019966940717</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.292255555770648</v>
+        <v>-2.292255555770593</v>
       </c>
       <c r="AQ400" t="n">
         <v>16.29549808429119</v>
@@ -65604,10 +65604,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.198803092238432</v>
+        <v>7.19880309223843</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2872029793233928</v>
+        <v>-0.287202979323391</v>
       </c>
       <c r="AK401" t="n">
         <v>7.18051307481679</v>
@@ -65616,16 +65616,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.2150441262650616</v>
+        <v>0.2150441262650612</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.0177489551638892</v>
+        <v>0.01774895516388914</v>
       </c>
       <c r="AO401" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP401" t="n">
-        <v>-2.114450406224792</v>
+        <v>-2.114450406224762</v>
       </c>
       <c r="AQ401" t="n">
         <v>14.80160604629192</v>
@@ -65769,10 +65769,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.172424239411002</v>
+        <v>7.172424239411004</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.2608241264959634</v>
+        <v>-0.2608241264959652</v>
       </c>
       <c r="AK402" t="n">
         <v>7.16705299197773</v>
@@ -65781,16 +65781,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.2054336514894463</v>
+        <v>0.205433651489446</v>
       </c>
       <c r="AN402" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO402" t="n">
-        <v>0.1417286033373033</v>
+        <v>0.1417286033373026</v>
       </c>
       <c r="AP402" t="n">
-        <v>-1.753918644461344</v>
+        <v>-1.753918644461359</v>
       </c>
       <c r="AQ402" t="n">
         <v>18.80300065231572</v>
@@ -65934,10 +65934,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.163756390646673</v>
+        <v>7.163756390646672</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2695565424716238</v>
+        <v>-0.2695565424716229</v>
       </c>
       <c r="AK403" t="n">
         <v>7.153532751444382</v>
@@ -65946,16 +65946,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.1941661953581056</v>
+        <v>0.1941661953581061</v>
       </c>
       <c r="AN403" t="n">
-        <v>0.01312004055850015</v>
+        <v>0.01312004055850013</v>
       </c>
       <c r="AO403" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP403" t="n">
-        <v>-1.836364117888404</v>
+        <v>-1.836364117888386</v>
       </c>
       <c r="AQ403" t="n">
         <v>25.14248942820372</v>
@@ -66099,10 +66099,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.158063699621736</v>
+        <v>7.158063699621738</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2875636118836988</v>
+        <v>-0.2875636118837006</v>
       </c>
       <c r="AK404" t="n">
         <v>7.150669702211316</v>
@@ -66111,16 +66111,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.183949493726688</v>
+        <v>0.1839494937266881</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.01194074338472802</v>
+        <v>0.01194074338472806</v>
       </c>
       <c r="AO404" t="n">
-        <v>0.110754980517583</v>
+        <v>0.1107549805175829</v>
       </c>
       <c r="AP404" t="n">
-        <v>-2.026143060475432</v>
+        <v>-2.026143060475445</v>
       </c>
       <c r="AQ404" t="n">
         <v>13.1507346272447</v>
@@ -66264,10 +66264,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.157435208014565</v>
+        <v>7.157435208014563</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2723353201666647</v>
+        <v>-0.272335320166663</v>
       </c>
       <c r="AK405" t="n">
         <v>7.140926852093823</v>
@@ -66276,16 +66276,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1753430411611928</v>
+        <v>0.1753430411611933</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.009717654232020439</v>
+        <v>0.00971765423202034</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.09620195025422784</v>
+        <v>0.09620195025422695</v>
       </c>
       <c r="AP405" t="n">
-        <v>-1.810937453185908</v>
+        <v>-1.810937453185879</v>
       </c>
       <c r="AQ405" t="n">
         <v>21.11185682326622</v>
@@ -66429,10 +66429,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.15038681134007</v>
+        <v>7.150386811340072</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.2679867754819156</v>
+        <v>-0.2679867754819174</v>
       </c>
       <c r="AK406" t="n">
         <v>7.142886401315924</v>
@@ -66441,16 +66441,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1664838398737869</v>
+        <v>0.1664838398737872</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.008089376136153925</v>
+        <v>0.008089376136153875</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.08489626886092971</v>
+        <v>0.0848962688609296</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.733919044573081</v>
+        <v>-1.733919044573096</v>
       </c>
       <c r="AQ406" t="n">
         <v>20.63134657836645</v>
@@ -66594,10 +66594,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.137094841694642</v>
+        <v>7.137094841694645</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2547949416397106</v>
+        <v>-0.2547949416397133</v>
       </c>
       <c r="AK407" t="n">
         <v>7.137840883333127</v>
@@ -66606,16 +66606,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1571907956492617</v>
+        <v>0.1571907956492611</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.006581947594647856</v>
+        <v>0.006581947594647974</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.07412699588694738</v>
+        <v>0.07412699588694804</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.554994403670321</v>
+        <v>-1.554994403670346</v>
       </c>
       <c r="AQ407" t="n">
         <v>20.81953642384106</v>
@@ -66759,10 +66759,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.1233912344352</v>
+        <v>7.123391234435203</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2666912908927195</v>
+        <v>-0.2666912908927221</v>
       </c>
       <c r="AK408" t="n">
         <v>7.12862724785568</v>
@@ -66771,16 +66771,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1487097707294973</v>
+        <v>0.1487097707294961</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.005441006961990058</v>
+        <v>0.005441006961990014</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.06531270865715666</v>
+        <v>0.06531270865715677</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.678171256844134</v>
+        <v>-1.678171256844158</v>
       </c>
       <c r="AQ408" t="n">
         <v>14.43713450292398</v>
@@ -66924,10 +66924,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.116007318552882</v>
+        <v>7.11600731855288</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2873072529400895</v>
+        <v>-0.2873072529400869</v>
       </c>
       <c r="AK409" t="n">
         <v>7.118961040191934</v>
@@ -66936,16 +66936,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1409513724492179</v>
+        <v>0.1409513724492178</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005644373135176906</v>
+        <v>0.005644373135176822</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.0598657761353214</v>
+        <v>0.05986577613532174</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.898060678102354</v>
+        <v>-1.898060678102314</v>
       </c>
       <c r="AQ409" t="n">
         <v>10.10525422290128</v>
@@ -67089,10 +67089,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.11526245458776</v>
+        <v>7.115262454587763</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2838625369852208</v>
+        <v>-0.2838625369852235</v>
       </c>
       <c r="AK410" t="n">
         <v>7.113208458946866</v>
@@ -67104,13 +67104,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005618445165739529</v>
+        <v>0.005618445165739616</v>
       </c>
       <c r="AO410" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.830475451497037</v>
+        <v>-1.83047545149706</v>
       </c>
       <c r="AQ410" t="n">
         <v>8.736908253037285</v>
@@ -67266,16 +67266,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM411" t="n">
-        <v>0.1248427026608145</v>
+        <v>0.1248427026608149</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005050876420738303</v>
+        <v>0.005050876420738246</v>
       </c>
       <c r="AO411" t="n">
-        <v>0.04692762159457986</v>
+        <v>0.04692762159458042</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.745364898333158</v>
+        <v>-1.745364898333151</v>
       </c>
       <c r="AQ411" t="n">
         <v>13.83995037220844</v>
@@ -67419,10 +67419,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI412" t="n">
-        <v>7.100218718661558</v>
+        <v>7.100218718661557</v>
       </c>
       <c r="AJ412" t="n">
-        <v>-0.2699188643829933</v>
+        <v>-0.2699188643829924</v>
       </c>
       <c r="AK412" t="n">
         <v>7.105971078464224</v>
@@ -67434,13 +67434,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.00520957018071537</v>
+        <v>0.005209570180715356</v>
       </c>
       <c r="AO412" t="n">
-        <v>0.04219701739313308</v>
+        <v>0.0421970173931332</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.623170113169739</v>
+        <v>-1.623170113169721</v>
       </c>
       <c r="AQ412" t="n">
         <v>15.02939735423812</v>
@@ -67584,10 +67584,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI413" t="n">
-        <v>7.097935875054439</v>
+        <v>7.097935875054437</v>
       </c>
       <c r="AJ413" t="n">
-        <v>-0.2822358208857381</v>
+        <v>-0.2822358208857363</v>
       </c>
       <c r="AK413" t="n">
         <v>7.101361129315627</v>
@@ -67596,16 +67596,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM413" t="n">
-        <v>0.1117472247487876</v>
+        <v>0.1117472247487875</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005385102682029925</v>
+        <v>0.005385102682029907</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.03866992220359033</v>
+        <v>0.03866992220359</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.744896560482916</v>
+        <v>-1.744896560482889</v>
       </c>
       <c r="AQ413" t="n">
         <v>13.98250423284689</v>
@@ -67749,10 +67749,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.097978821692021</v>
+        <v>7.097978821692022</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2799789819093057</v>
+        <v>-0.2799789819093075</v>
       </c>
       <c r="AK414" t="n">
         <v>7.099648834314064</v>
@@ -67761,16 +67761,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.1065475925362025</v>
+        <v>0.1065475925362033</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.005956926407441003</v>
+        <v>0.005956926407440957</v>
       </c>
       <c r="AO414" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.697411314544321</v>
+        <v>-1.697411314544335</v>
       </c>
       <c r="AQ414" t="n">
         <v>13.89220603455139</v>
@@ -67926,16 +67926,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.1013724682419976</v>
+        <v>0.1013724682419977</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.006126167203105847</v>
+        <v>0.006126167203105798</v>
       </c>
       <c r="AO415" t="n">
-        <v>0.03348722035246277</v>
+        <v>0.03348722035246332</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.535018001497656</v>
+        <v>-1.53501800149765</v>
       </c>
       <c r="AQ415" t="n">
         <v>22.59630503144654</v>
@@ -68079,10 +68079,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI416" t="n">
-        <v>7.087097940453343</v>
+        <v>7.087097940453345</v>
       </c>
       <c r="AJ416" t="n">
-        <v>-0.2700980281913798</v>
+        <v>-0.2700980281913825</v>
       </c>
       <c r="AK416" t="n">
         <v>7.090805518999606</v>
@@ -68091,16 +68091,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.09919462776856289</v>
+        <v>0.09919462776856321</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.006113943880485968</v>
+        <v>0.006113943880485972</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.03204155062895098</v>
+        <v>0.03204155062895153</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.549683779790894</v>
+        <v>-1.549683779790917</v>
       </c>
       <c r="AQ416" t="n">
         <v>17.46312111801242</v>
@@ -68256,16 +68256,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.09750750254701511</v>
+        <v>0.097507502547015</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.005510714664730422</v>
+        <v>0.005510714664730507</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.03001455024934274</v>
+        <v>0.03001455024934374</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.608532568103946</v>
+        <v>-1.608532568103939</v>
       </c>
       <c r="AQ417" t="n">
         <v>14.2512077294686</v>
@@ -68421,16 +68421,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.09380549503386949</v>
+        <v>0.09380549503386901</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.004784904607979855</v>
+        <v>0.004784904607979881</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.02699383492044827</v>
+        <v>0.02699383492044782</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.565740428316655</v>
+        <v>-1.565740428316649</v>
       </c>
       <c r="AQ418" t="n">
         <v>17.86525789593274</v>
@@ -68574,10 +68574,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI419" t="n">
-        <v>7.097145375663948</v>
+        <v>7.097145375663951</v>
       </c>
       <c r="AJ419" t="n">
-        <v>-0.2729452223131181</v>
+        <v>-0.2729452223131208</v>
       </c>
       <c r="AK419" t="n">
         <v>7.093828611034739</v>
@@ -68586,16 +68586,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.08945254406056392</v>
+        <v>0.08945254406056438</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.004001520125414807</v>
+        <v>0.004001520125414798</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.02385555423225172</v>
+        <v>0.02385555423225116</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.531733062735162</v>
+        <v>-1.531733062735185</v>
       </c>
       <c r="AQ419" t="n">
         <v>22.04848122100853</v>
@@ -68739,10 +68739,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.088227962421954</v>
+        <v>7.088227962421951</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2622277487989066</v>
+        <v>-0.262227748798904</v>
       </c>
       <c r="AK420" t="n">
         <v>7.092951699003613</v>
@@ -68751,16 +68751,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.07912491692886864</v>
+        <v>0.07912491692886899</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.003813743757049957</v>
+        <v>0.003813743757049903</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.01902803623666371</v>
+        <v>0.01902803623666316</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.397605931661167</v>
+        <v>-1.397605931661131</v>
       </c>
       <c r="AQ420" t="n">
         <v>35.00554323725056</v>
@@ -68904,10 +68904,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.082675656384675</v>
+        <v>7.082675656384673</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.2467758265201727</v>
+        <v>-0.2467758265201709</v>
       </c>
       <c r="AK421" t="n">
         <v>7.085940899278786</v>
@@ -68916,16 +68916,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.07019093860911679</v>
+        <v>0.07019093860911668</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.003788844982403293</v>
+        <v>0.003788844982403339</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.0153072785246503</v>
+        <v>0.01530727852465064</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.213905388082079</v>
+        <v>-1.213905388082054</v>
       </c>
       <c r="AQ421" t="n">
         <v>32.97006206644761</v>
@@ -69069,10 +69069,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.082585232341569</v>
+        <v>7.082585232341567</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2597850728872233</v>
+        <v>-0.2597850728872215</v>
       </c>
       <c r="AK422" t="n">
         <v>7.080231185021037</v>
@@ -69081,16 +69081,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.06072301451314636</v>
+        <v>0.0607230145131474</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.003218097337044184</v>
+        <v>0.003218097337044118</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.01127031184523331</v>
+        <v>0.01127031184523342</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.349082330956625</v>
+        <v>-1.3490823309566</v>
       </c>
       <c r="AQ422" t="n">
         <v>33.07481422696775</v>
@@ -69234,10 +69234,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.082752176397554</v>
+        <v>7.082752176397555</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2453522168333455</v>
+        <v>-0.2453522168333464</v>
       </c>
       <c r="AK423" t="n">
         <v>7.078545045220129</v>
@@ -69246,16 +69246,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.04987769893955601</v>
+        <v>0.04987769893955558</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.002647769861786034</v>
+        <v>0.002647769861786137</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.007555907385723093</v>
+        <v>0.00755590738572276</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.178227506138542</v>
+        <v>-1.178227506138547</v>
       </c>
       <c r="AQ423" t="n">
         <v>34.66816367265469</v>
@@ -69399,10 +69399,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.073418742129173</v>
+        <v>7.073418742129174</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2359186467617418</v>
+        <v>-0.2359186467617427</v>
       </c>
       <c r="AK424" t="n">
         <v>7.075576762908686</v>
@@ -69411,16 +69411,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.03723342047483347</v>
+        <v>0.03723342047483359</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.0007434096776329864</v>
+        <v>0.0007434096776329363</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.003691827899840794</v>
+        <v>0.003691827899839573</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.065421659448079</v>
+        <v>-1.065421659448085</v>
       </c>
       <c r="AQ424" t="n">
         <v>37.13898281205974</v>
@@ -69576,16 +69576,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.02391394499985489</v>
+        <v>0.02391394499985428</v>
       </c>
       <c r="AN425" t="n">
-        <v>0.0004638728584110585</v>
+        <v>0.0004638728584110997</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.001504277651263042</v>
+        <v>0.00150427765126282</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.105133591288585</v>
+        <v>-1.10513359128858</v>
       </c>
       <c r="AQ425" t="n">
         <v>34.84859032370345</v>
@@ -69729,10 +69729,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI426" t="n">
-        <v>7.06117555197594</v>
+        <v>7.061175551975939</v>
       </c>
       <c r="AJ426" t="n">
-        <v>-0.2336756854903443</v>
+        <v>-0.2336756854903435</v>
       </c>
       <c r="AK426" t="n">
         <v>7.061105294515807</v>
@@ -69741,16 +69741,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM426" t="n">
-        <v>0.01023096587809607</v>
+        <v>0.01023096587809661</v>
       </c>
       <c r="AN426" t="n">
-        <v>-0.0001641525470544615</v>
+        <v>-0.0001641525470544823</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.000253092979595082</v>
+        <v>0.0002530929795961923</v>
       </c>
       <c r="AP426" t="n">
-        <v>-1.026755897919682</v>
+        <v>-1.026755897919668</v>
       </c>
       <c r="AQ426" t="n">
         <v>39.93464052287581</v>
@@ -69906,16 +69906,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM427" t="n">
-        <v>-0.001349940557734529</v>
+        <v>-0.001349940557734956</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.001242569541730301</v>
+        <v>-0.001242569541730382</v>
       </c>
       <c r="AO427" t="n">
-        <v>9.828375502973774e-05</v>
+        <v>9.828375502929365e-05</v>
       </c>
       <c r="AP427" t="n">
-        <v>-0.930846295384863</v>
+        <v>-0.9308462953848593</v>
       </c>
       <c r="AQ427" t="n">
         <v>40.2828777369781</v>
@@ -70059,10 +70059,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI428" t="n">
-        <v>7.051845784111937</v>
+        <v>7.051845784111939</v>
       </c>
       <c r="AJ428" t="n">
-        <v>-0.22174572460266</v>
+        <v>-0.2217457246026617</v>
       </c>
       <c r="AK428" t="n">
         <v>7.04924004450221</v>
@@ -70071,16 +70071,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.0124592779456514</v>
+        <v>-0.01245927794565087</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.002690846636687166</v>
+        <v>-0.002690846636687106</v>
       </c>
       <c r="AO428" t="n">
-        <v>0.000914944322433886</v>
+        <v>0.0009149443224345521</v>
       </c>
       <c r="AP428" t="n">
-        <v>-0.8831846613298671</v>
+        <v>-0.8831846613298829</v>
       </c>
       <c r="AQ428" t="n">
         <v>37.14040865707756</v>
@@ -70224,10 +70224,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.044932512363692</v>
+        <v>7.044932512363691</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2339326420633991</v>
+        <v>-0.2339326420633983</v>
       </c>
       <c r="AK429" t="n">
         <v>7.044607485549974</v>
@@ -70236,16 +70236,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.0235197471891116</v>
+        <v>-0.02351974718911197</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.003286981705062081</v>
+        <v>-0.003286981705062079</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.002235402288773058</v>
+        <v>0.002235402288773947</v>
       </c>
       <c r="AP429" t="n">
-        <v>-1.014131495610588</v>
+        <v>-1.014131495610574</v>
       </c>
       <c r="AQ429" t="n">
         <v>35.1969968772839</v>
@@ -70389,10 +70389,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.04138072456642</v>
+        <v>7.041380724566422</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.2399805399350727</v>
+        <v>-0.2399805399350745</v>
       </c>
       <c r="AK430" t="n">
         <v>7.036677431055121</v>
@@ -70401,16 +70401,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.03604973348542571</v>
+        <v>-0.03604973348542533</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.003896888881646666</v>
+        <v>-0.003896888881646653</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.004508577134016423</v>
+        <v>0.004508577134016534</v>
       </c>
       <c r="AP430" t="n">
-        <v>-1.075377833979213</v>
+        <v>-1.075377833979229</v>
       </c>
       <c r="AQ430" t="n">
         <v>27.8128078817734</v>
@@ -70554,10 +70554,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.031781164871438</v>
+        <v>7.031781164871437</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2312812487947777</v>
+        <v>-0.2312812487947769</v>
       </c>
       <c r="AK431" t="n">
         <v>7.031531243279009</v>
@@ -70566,16 +70566,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.04964211158845258</v>
+        <v>-0.0496421115884523</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003622848094475877</v>
+        <v>-0.003622848094475932</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.007358432861333086</v>
+        <v>0.007358432861332531</v>
       </c>
       <c r="AP431" t="n">
-        <v>-0.9722861091319298</v>
+        <v>-0.9722861091319155</v>
       </c>
       <c r="AQ431" t="n">
         <v>35.36201298701299</v>
@@ -70731,16 +70731,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.06336633742876532</v>
+        <v>-0.06336633742876464</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003832222031667326</v>
+        <v>-0.00383222203166729</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.01139353356262962</v>
+        <v>0.0113935335626284</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.9021966051229211</v>
+        <v>-0.9021966051229171</v>
       </c>
       <c r="AQ432" t="n">
         <v>36.00892398561891</v>
@@ -70884,10 +70884,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI433" t="n">
-        <v>7.012358254068221</v>
+        <v>7.012358254068223</v>
       </c>
       <c r="AJ433" t="n">
-        <v>-0.2203584371736902</v>
+        <v>-0.220358437173692</v>
       </c>
       <c r="AK433" t="n">
         <v>7.010266108789461</v>
@@ -70896,16 +70896,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.07815930192347212</v>
+        <v>-0.07815930192347351</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.003730201847889384</v>
+        <v>-0.0037302018478894</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.01669360800688602</v>
+        <v>0.01669360800688513</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.8408858759026222</v>
+        <v>-0.8408858759026382</v>
       </c>
       <c r="AQ433" t="n">
         <v>35.23455849679426</v>
@@ -71049,10 +71049,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI434" t="n">
-        <v>7.001516536947591</v>
+        <v>7.001516536947593</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.2107164423430987</v>
+        <v>-0.2107164423431005</v>
       </c>
       <c r="AK434" t="n">
         <v>7.003692382618654</v>
@@ -71061,16 +71061,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.09225745624393285</v>
+        <v>-0.09225745624393369</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.003729646461095566</v>
+        <v>-0.003729646461095512</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.02283737241168682</v>
+        <v>0.02283737241168637</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.7293311864083497</v>
+        <v>-0.7293311864083659</v>
       </c>
       <c r="AQ434" t="n">
         <v>39.80760780867491</v>
@@ -71214,10 +71214,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI435" t="n">
-        <v>6.982853032266831</v>
+        <v>6.98285303226683</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.1977530490514985</v>
+        <v>-0.1977530490514976</v>
       </c>
       <c r="AK435" t="n">
         <v>6.994908837140057</v>
@@ -71226,16 +71226,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.1040956648961739</v>
+        <v>-0.1040956648961724</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.004775368000139281</v>
+        <v>-0.004775368000139335</v>
       </c>
       <c r="AO435" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.5812075365285228</v>
+        <v>-0.5812075365285095</v>
       </c>
       <c r="AQ435" t="n">
         <v>40.97610180012415</v>
@@ -71379,10 +71379,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI436" t="n">
-        <v>6.976537964100195</v>
+        <v>6.976537964100197</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.1673381540721186</v>
+        <v>-0.1673381540721204</v>
       </c>
       <c r="AK436" t="n">
         <v>6.976048621620001</v>
@@ -71391,16 +71391,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.1171809788132892</v>
+        <v>-0.1171809788132883</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.006568629287185491</v>
+        <v>-0.006568629287185546</v>
       </c>
       <c r="AO436" t="n">
-        <v>0.03914952746580436</v>
+        <v>0.03914952746580425</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.2374324494717015</v>
+        <v>-0.2374324494717194</v>
       </c>
       <c r="AQ436" t="n">
         <v>48.78759975445058</v>
@@ -71547,7 +71547,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1582257113591092</v>
+        <v>-0.1582257113591101</v>
       </c>
       <c r="AK437" t="n">
         <v>6.970728111892008</v>
@@ -71556,16 +71556,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.127636816539943</v>
+        <v>-0.127636816539944</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.00745101973257774</v>
+        <v>-0.007451019732577668</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.04750067483060572</v>
+        <v>0.04750067483060583</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.1339985174508675</v>
+        <v>-0.1339985174508753</v>
       </c>
       <c r="AQ437" t="n">
         <v>49.89375265618359</v>
@@ -71724,13 +71724,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.008628156625160163</v>
+        <v>-0.008628156625160088</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.05751510742764121</v>
+        <v>0.05751510742764043</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.02245304906258103</v>
+        <v>-0.02245304906257907</v>
       </c>
       <c r="AQ438" t="n">
         <v>52.07770371704798</v>
@@ -71874,10 +71874,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI439" t="n">
-        <v>6.950644730799363</v>
+        <v>6.950644730799358</v>
       </c>
       <c r="AJ439" t="n">
-        <v>-0.1501448147227027</v>
+        <v>-0.1501448147226974</v>
       </c>
       <c r="AK439" t="n">
         <v>6.959853578800648</v>
@@ -71886,16 +71886,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM439" t="n">
-        <v>-0.1469566450661556</v>
+        <v>-0.1469566450661546</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.009026348114251901</v>
+        <v>-0.009026348114251986</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.06603756167960351</v>
+        <v>0.06603756167960417</v>
       </c>
       <c r="AP439" t="n">
-        <v>-0.04223509378763642</v>
+        <v>-0.04223509378757428</v>
       </c>
       <c r="AQ439" t="n">
         <v>49.88417676407698</v>
@@ -72039,28 +72039,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.934622414140152</v>
+        <v>6.934622414140156</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1321226430219875</v>
+        <v>-0.1321226430219919</v>
       </c>
       <c r="AK440" t="n">
-        <v>6.947114416435721</v>
+        <v>6.94711441643572</v>
       </c>
       <c r="AL440" t="n">
-        <v>-0.1446146453175565</v>
+        <v>-0.1446146453175556</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1568781652619921</v>
+        <v>-0.1568781652619925</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.01004287133747513</v>
+        <v>-0.010042871337475</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.07699206242755419</v>
+        <v>0.07699206242755485</v>
       </c>
       <c r="AP440" t="n">
-        <v>0.1628202489810339</v>
+        <v>0.1628202489809846</v>
       </c>
       <c r="AQ440" t="n">
         <v>59.09077555816686</v>
@@ -72204,10 +72204,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.928042396530073</v>
+        <v>6.928042396530076</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.133542522415083</v>
+        <v>-0.1335425224150857</v>
       </c>
       <c r="AK441" t="n">
         <v>6.933186989735641</v>
@@ -72216,16 +72216,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1650917115670582</v>
+        <v>-0.1650917115670576</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.01061494647532512</v>
+        <v>-0.0106149464753251</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.08732871254562202</v>
+        <v>0.08732871254562191</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.1461854460826935</v>
+        <v>0.1461854460826641</v>
       </c>
       <c r="AQ441" t="n">
         <v>55.79918628305725</v>
@@ -72369,10 +72369,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.941461393298106</v>
+        <v>6.941461393298105</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1469615191831153</v>
+        <v>-0.1469615191831144</v>
       </c>
       <c r="AK442" t="n">
         <v>6.925995477801935</v>
@@ -72381,16 +72381,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1745447047691478</v>
+        <v>-0.1745447047691483</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.01108963812755724</v>
+        <v>-0.01108963812755723</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.09935205695041927</v>
+        <v>0.09935205695041804</v>
       </c>
       <c r="AP442" t="n">
-        <v>-0.007624658121660367</v>
+        <v>-0.007624658121648223</v>
       </c>
       <c r="AQ442" t="n">
         <v>49.34161347823587</v>
@@ -72534,10 +72534,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.933232103976423</v>
+        <v>6.93323210397643</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.147232329043562</v>
+        <v>-0.1472323290435682</v>
       </c>
       <c r="AK443" t="n">
         <v>6.938996539173566</v>
@@ -72546,16 +72546,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.1853013335308053</v>
+        <v>-0.1853013335308036</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01193987645426136</v>
+        <v>-0.01193987645426134</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.1123648810347067</v>
+        <v>0.1123648810347069</v>
       </c>
       <c r="AP443" t="n">
-        <v>-0.01070905637840105</v>
+        <v>-0.01070905637847076</v>
       </c>
       <c r="AQ443" t="n">
         <v>45.06912049152349</v>
@@ -72699,10 +72699,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.928429644379658</v>
+        <v>6.928429644379657</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1496296336985061</v>
+        <v>-0.1496296336985043</v>
       </c>
       <c r="AK444" t="n">
         <v>6.93160690101155</v>
@@ -72714,13 +72714,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01257308415669775</v>
+        <v>-0.01257308415669778</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1258578984724115</v>
+        <v>0.125857898472412</v>
       </c>
       <c r="AP444" t="n">
-        <v>-0.03823784802776846</v>
+        <v>-0.03823784802774591</v>
       </c>
       <c r="AQ444" t="n">
         <v>45.36474164133739</v>
@@ -72864,10 +72864,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.925068850639512</v>
+        <v>6.925068850639515</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1455688430101176</v>
+        <v>-0.1455688430101203</v>
       </c>
       <c r="AK445" t="n">
         <v>6.924763510572069</v>
@@ -72876,16 +72876,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM445" t="n">
-        <v>-0.2060805417157789</v>
+        <v>-0.2060805417157788</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01318646791849928</v>
+        <v>-0.01318646791849926</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.1396251026736647</v>
+        <v>0.1396251026736655</v>
       </c>
       <c r="AP445" t="n">
-        <v>0.008666512625864322</v>
+        <v>0.008666512625835357</v>
       </c>
       <c r="AQ445" t="n">
         <v>49.08103592314119</v>
@@ -73029,10 +73029,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.900929863197373</v>
+        <v>6.900929863197374</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1347297975845798</v>
+        <v>-0.1347297975845807</v>
       </c>
       <c r="AK446" t="n">
         <v>6.921049732547429</v>
@@ -73041,16 +73041,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM446" t="n">
-        <v>-0.2151279705591481</v>
+        <v>-0.2151279705591488</v>
       </c>
       <c r="AN446" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1518365696223549</v>
+        <v>0.1518365696223548</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.1339004809152564</v>
+        <v>0.1339004809152479</v>
       </c>
       <c r="AQ446" t="n">
         <v>50.11848994213282</v>
@@ -73194,10 +73194,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.89521901018146</v>
+        <v>6.895219010181459</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1302191436958644</v>
+        <v>-0.1302191436958635</v>
       </c>
       <c r="AK447" t="n">
         <v>6.89978353884127</v>
@@ -73209,13 +73209,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN447" t="n">
-        <v>-0.01278923357027006</v>
+        <v>-0.01278923357027009</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1644177475946105</v>
+        <v>0.1644177475946104</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.1858002194478095</v>
+        <v>0.1858002194478216</v>
       </c>
       <c r="AQ447" t="n">
         <v>47.75850785340315</v>
@@ -73359,10 +73359,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.87951223984858</v>
+        <v>6.879512239848579</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1173123611559532</v>
+        <v>-0.1173123611559523</v>
       </c>
       <c r="AK448" t="n">
         <v>6.893260360395011</v>
@@ -73371,16 +73371,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM448" t="n">
-        <v>-0.233692768734328</v>
+        <v>-0.233692768734329</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01245257184765156</v>
+        <v>-0.01245257184765153</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1791295233320875</v>
+        <v>0.179129523332087</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.3351516091176316</v>
+        <v>0.3351516091176434</v>
       </c>
       <c r="AQ448" t="n">
         <v>51.15231001727116</v>
@@ -73524,10 +73524,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.882426232260437</v>
+        <v>6.882426232260446</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.1132263840853884</v>
+        <v>-0.1132263840853973</v>
       </c>
       <c r="AK449" t="n">
         <v>6.880758546638964</v>
@@ -73536,16 +73536,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.2433281856134888</v>
+        <v>-0.2433281856134891</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01202813951384067</v>
+        <v>-0.01202813951384066</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.1944608722019407</v>
+        <v>0.1944608722019401</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.3817210456291396</v>
+        <v>0.3817210456290377</v>
       </c>
       <c r="AQ449" t="n">
         <v>52.69884087388495</v>
@@ -73701,16 +73701,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.25202644278106</v>
+        <v>-0.2520264427810588</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01246671652825434</v>
+        <v>-0.01246671652825437</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.2101991144027905</v>
+        <v>0.2101991144027906</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.9491638078956258</v>
+        <v>0.9491638078956266</v>
       </c>
       <c r="AQ450" t="n">
         <v>65.52471583399418</v>
@@ -73854,10 +73854,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI451" t="n">
-        <v>6.841963898035326</v>
+        <v>6.841963898035317</v>
       </c>
       <c r="AJ451" t="n">
-        <v>-0.07646382937077512</v>
+        <v>-0.07646382937076623</v>
       </c>
       <c r="AK451" t="n">
         <v>6.844785316397215</v>
@@ -73866,16 +73866,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2592973891940566</v>
+        <v>-0.2592973891940562</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01305068899435077</v>
+        <v>-0.01305068899435097</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.2277185089957524</v>
+        <v>0.2277185089957531</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.8037312953588597</v>
+        <v>0.8037312953589637</v>
       </c>
       <c r="AQ451" t="n">
         <v>58.78859236002093</v>
@@ -74019,28 +74019,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.845644916883079</v>
+        <v>6.845644916883085</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.08014484821852808</v>
+        <v>-0.08014484821853429</v>
       </c>
       <c r="AK452" t="n">
-        <v>6.849407886968132</v>
+        <v>6.849407886968131</v>
       </c>
       <c r="AL452" t="n">
-        <v>-0.08390781830358129</v>
+        <v>-0.08390781830358041</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2668003223256254</v>
+        <v>-0.2668003223256257</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.0136798902005495</v>
+        <v>-0.01367989020054944</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2456601220977566</v>
+        <v>0.2456601220977563</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.7575760789072111</v>
+        <v>0.7575760789071387</v>
       </c>
       <c r="AQ452" t="n">
         <v>58.49217859732726</v>
@@ -74184,10 +74184,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.842084108625038</v>
+        <v>6.842084108625032</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.06958407047806503</v>
+        <v>-0.0695840704780597</v>
       </c>
       <c r="AK453" t="n">
         <v>6.852702018840203</v>
@@ -74196,16 +74196,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.273543646731814</v>
+        <v>-0.2735436467318143</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01403412282467991</v>
+        <v>-0.01403412282467997</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.261983510217226</v>
+        <v>0.2619835102172253</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.8774602160380599</v>
+        <v>0.8774602160381219</v>
       </c>
       <c r="AQ453" t="n">
         <v>63.77095831410553</v>
@@ -74349,10 +74349,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.863831060847785</v>
+        <v>6.863831060847773</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.09133102270081217</v>
+        <v>-0.09133102270080062</v>
       </c>
       <c r="AK454" t="n">
         <v>6.850973969550408</v>
@@ -74361,16 +74361,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2787367835501617</v>
+        <v>-0.2787367835501612</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.01406387644726588</v>
+        <v>-0.01406387644726603</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.2758112468611976</v>
+        <v>0.2758112468611987</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.6201564125477783</v>
+        <v>0.6201564125479134</v>
       </c>
       <c r="AQ454" t="n">
         <v>62.71509060453784</v>
@@ -74514,10 +74514,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.853037915615573</v>
+        <v>6.853037915615571</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.07753809490634467</v>
+        <v>-0.07753809490634289</v>
       </c>
       <c r="AK455" t="n">
         <v>6.873527983489108</v>
@@ -74529,13 +74529,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01379017718565697</v>
+        <v>-0.013790177185657</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.2854425463774817</v>
+        <v>0.285442546377481</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.7790847177232256</v>
+        <v>0.7790847177232453</v>
       </c>
       <c r="AQ455" t="n">
         <v>68.91582914572865</v>
@@ -74691,7 +74691,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM456" t="n">
-        <v>-0.2865252693972545</v>
+        <v>-0.2865252693972544</v>
       </c>
       <c r="AN456" t="n">
         <v>-0.01327380582108439</v>
@@ -74700,7 +74700,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.5802070644516254</v>
+        <v>0.5802070644516248</v>
       </c>
       <c r="AQ456" t="n">
         <v>62.09328358208955</v>
@@ -74844,10 +74844,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI457" t="n">
-        <v>6.860047631936787</v>
+        <v>6.860047631936786</v>
       </c>
       <c r="AJ457" t="n">
-        <v>-0.1030476624543653</v>
+        <v>-0.1030476624543644</v>
       </c>
       <c r="AK457" t="n">
         <v>6.865985861260643</v>
@@ -74856,16 +74856,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2905223093479492</v>
+        <v>-0.290522309347949</v>
       </c>
       <c r="AN457" t="n">
-        <v>-0.01240158194086378</v>
+        <v>-0.01240158194086383</v>
       </c>
       <c r="AO457" t="n">
-        <v>0.3024992257449914</v>
+        <v>0.3024992257449916</v>
       </c>
       <c r="AP457" t="n">
-        <v>0.4754899470836775</v>
+        <v>0.475489947083688</v>
       </c>
       <c r="AQ457" t="n">
         <v>58.3123984040195</v>
@@ -75009,10 +75009,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.801980414635016</v>
+        <v>6.801980414635013</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.04478065038330659</v>
+        <v>-0.04478065038330392</v>
       </c>
       <c r="AK458" t="n">
         <v>6.863576603094304</v>
@@ -75021,16 +75021,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.2950697019949104</v>
+        <v>-0.2950697019949103</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.01161053315968381</v>
+        <v>-0.0116105331596838</v>
       </c>
       <c r="AO458" t="n">
-        <v>0.3113800696686918</v>
+        <v>0.3113800696686924</v>
       </c>
       <c r="AP458" t="n">
-        <v>1.156569632246534</v>
+        <v>1.156569632246562</v>
       </c>
       <c r="AQ458" t="n">
         <v>79.47495488465103</v>
@@ -75174,10 +75174,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.789283666813422</v>
+        <v>6.789283666813423</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.03208390256171256</v>
+        <v>-0.03208390256171434</v>
       </c>
       <c r="AK459" t="n">
         <v>6.809671190627447</v>
@@ -75186,16 +75186,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.2987092362344108</v>
+        <v>-0.2987092362344105</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.01030385953714808</v>
+        <v>-0.01030385953714813</v>
       </c>
       <c r="AO459" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.29768466829375</v>
+        <v>1.297684668293726</v>
       </c>
       <c r="AQ459" t="n">
         <v>82.2732541292379</v>
@@ -75339,10 +75339,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.789252537988933</v>
+        <v>6.789252537988938</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.0206525509589035</v>
+        <v>-0.02065255095890883</v>
       </c>
       <c r="AK460" t="n">
         <v>6.802840448144932</v>
@@ -75351,16 +75351,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.3027504956929284</v>
+        <v>-0.3027504956929287</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.008812786025409641</v>
+        <v>-0.00881278602540958</v>
       </c>
       <c r="AO460" t="n">
-        <v>0.3322271170679635</v>
+        <v>0.332227117067963</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.421666194018807</v>
+        <v>1.421666194018742</v>
       </c>
       <c r="AQ460" t="n">
         <v>83.09301769488283</v>
@@ -75504,10 +75504,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.774001672255932</v>
+        <v>6.774001672255927</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.005401685225902675</v>
+        <v>-0.005401685225897346</v>
       </c>
       <c r="AK461" t="n">
         <v>6.800260207803535</v>
@@ -75516,16 +75516,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3068099364477367</v>
+        <v>-0.3068099364477369</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.007070247176567688</v>
+        <v>-0.007070247176567734</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.3427146952658534</v>
+        <v>0.3427146952658529</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.587013587941499</v>
+        <v>1.587013587941557</v>
       </c>
       <c r="AQ461" t="n">
         <v>83.90243902439025</v>
@@ -75669,10 +75669,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.802628307046303</v>
+        <v>6.802628307046305</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.02812841385782594</v>
+        <v>-0.0281284138578286</v>
       </c>
       <c r="AK462" t="n">
         <v>6.781970485204615</v>
@@ -75681,16 +75681,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3121566752204101</v>
+        <v>-0.3121566752204096</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.005102880740085154</v>
+        <v>-0.005102880740085192</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.3560731605465757</v>
+        <v>0.3560731605465752</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.31238607050744</v>
+        <v>1.312386070507406</v>
       </c>
       <c r="AQ462" t="n">
         <v>80.10529524881572</v>
@@ -75834,28 +75834,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.815944895083632</v>
+        <v>6.815944895083629</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.02594493323060476</v>
+        <v>-0.0259449332306021</v>
       </c>
       <c r="AK463" t="n">
-        <v>6.809638458820508</v>
+        <v>6.809638458820509</v>
       </c>
       <c r="AL463" t="n">
-        <v>-0.01963849696748099</v>
+        <v>-0.01963849696748188</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3181413841564619</v>
+        <v>-0.3181413841564625</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.003317316385138562</v>
+        <v>-0.003317316385138602</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3690689225934922</v>
+        <v>0.3690689225934927</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.328949075642543</v>
+        <v>1.328949075642571</v>
       </c>
       <c r="AQ463" t="n">
         <v>81.89218691936082</v>
@@ -75999,10 +75999,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.821941449304753</v>
+        <v>6.821941449304759</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.03194148745172587</v>
+        <v>-0.0319414874517312</v>
       </c>
       <c r="AK464" t="n">
         <v>6.819973703544699</v>
@@ -76011,16 +76011,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3244228225822198</v>
+        <v>-0.3244228225822193</v>
       </c>
       <c r="AN464" t="n">
-        <v>-0.001700148658338742</v>
+        <v>-0.001700148658338674</v>
       </c>
       <c r="AO464" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.251286692747105</v>
+        <v>1.251286692747041</v>
       </c>
       <c r="AQ464" t="n">
         <v>78.61727088700772</v>
@@ -76164,10 +76164,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.826413262727749</v>
+        <v>6.826413262727742</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.03641330087472205</v>
+        <v>-0.03641330087471495</v>
       </c>
       <c r="AK465" t="n">
         <v>6.822087900644207</v>
@@ -76176,16 +76176,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3308797299382495</v>
+        <v>-0.3308797299382499</v>
       </c>
       <c r="AN465" t="n">
-        <v>-7.481797733213274e-05</v>
+        <v>-7.481797733216444e-05</v>
       </c>
       <c r="AO465" t="n">
-        <v>0.396078871041881</v>
+        <v>0.3960788710418811</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.19229061095663</v>
+        <v>1.192290610956709</v>
       </c>
       <c r="AQ465" t="n">
         <v>79.20369104579632</v>
@@ -76329,10 +76329,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.81265664767955</v>
+        <v>6.812656647679548</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.01465678882334931</v>
+        <v>-0.01465678882334664</v>
       </c>
       <c r="AK466" t="n">
         <v>6.823881638371397</v>
@@ -76341,16 +76341,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3363418922753058</v>
+        <v>-0.3363418922753055</v>
       </c>
       <c r="AN466" t="n">
-        <v>0.001379920606120097</v>
+        <v>0.001379920606120022</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.4081029523904167</v>
+        <v>0.4081029523904164</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.434763742365879</v>
+        <v>1.434763742365905</v>
       </c>
       <c r="AQ466" t="n">
         <v>83.57481381178064</v>
@@ -76494,10 +76494,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.802797817425505</v>
+        <v>6.802797817425507</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.009197735028044107</v>
+        <v>-0.009197735028045884</v>
       </c>
       <c r="AK467" t="n">
         <v>6.808320681191073</v>
@@ -76506,16 +76506,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3410659803634682</v>
+        <v>-0.3410659803634685</v>
       </c>
       <c r="AN467" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4198133218741357</v>
+        <v>0.4198133218741356</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.486677771927086</v>
+        <v>1.486677771927061</v>
       </c>
       <c r="AQ467" t="n">
         <v>83.65152463560761</v>
@@ -76665,22 +76665,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK468" t="n">
-        <v>6.795980661778266</v>
+        <v>6.795980661778267</v>
       </c>
       <c r="AL468" t="n">
-        <v>-0.002380579380805159</v>
+        <v>-0.002380579380806047</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3461577281601509</v>
+        <v>-0.3461577281601511</v>
       </c>
       <c r="AN468" t="n">
-        <v>0.00428288788357468</v>
+        <v>0.004282887883574671</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4328049372030969</v>
+        <v>0.4328049372030962</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.547823652399483</v>
+        <v>1.547823652399479</v>
       </c>
       <c r="AQ468" t="n">
         <v>84.90566037735849</v>
@@ -76824,10 +76824,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI469" t="n">
-        <v>6.800189882196236</v>
+        <v>6.800189882196235</v>
       </c>
       <c r="AJ469" t="n">
-        <v>-0.005989938653755189</v>
+        <v>-0.005989938653754301</v>
       </c>
       <c r="AK469" t="n">
         <v>6.78726841810145</v>
@@ -76836,16 +76836,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3502903933401418</v>
+        <v>-0.3502903933401412</v>
       </c>
       <c r="AN469" t="n">
-        <v>0.005405808652032067</v>
+        <v>0.005405808652032051</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4450018361960534</v>
+        <v>0.4450018361960529</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.499846910714732</v>
+        <v>1.499846910714738</v>
       </c>
       <c r="AQ469" t="n">
         <v>83.8050107498574</v>
@@ -76989,10 +76989,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.797972083642554</v>
+        <v>6.79797208364255</v>
       </c>
       <c r="AJ470" t="n">
-        <v>-0.009372115686010929</v>
+        <v>-0.009372115686007376</v>
       </c>
       <c r="AK470" t="n">
         <v>6.791305278184372</v>
@@ -77001,16 +77001,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3548656112706071</v>
+        <v>-0.3548656112706069</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.006091291211178139</v>
+        <v>0.006091291211178074</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4593697101544705</v>
+        <v>0.4593697101544711</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.450376496300136</v>
+        <v>1.450376496300172</v>
       </c>
       <c r="AQ470" t="n">
         <v>82.48206911540969</v>
@@ -77154,10 +77154,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.800452644405178</v>
+        <v>6.800452644405181</v>
       </c>
       <c r="AJ471" t="n">
-        <v>-0.01185267644863508</v>
+        <v>-0.01185267644863774</v>
       </c>
       <c r="AK471" t="n">
         <v>6.789098969069376</v>
@@ -77172,10 +77172,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4721687943484545</v>
+        <v>0.4721687943484544</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.412039194687948</v>
+        <v>1.412039194687914</v>
       </c>
       <c r="AQ471" t="n">
         <v>79.30878552971576</v>
@@ -77319,10 +77319,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.778720347685814</v>
+        <v>6.778720347685821</v>
       </c>
       <c r="AJ472" t="n">
-        <v>0.01707986135959594</v>
+        <v>0.01707986135958883</v>
       </c>
       <c r="AK472" t="n">
         <v>6.790465135395929</v>
@@ -77331,16 +77331,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM472" t="n">
-        <v>-0.3625273381377933</v>
+        <v>-0.3625273381377937</v>
       </c>
       <c r="AN472" t="n">
-        <v>0.007343464385960585</v>
+        <v>0.007343464385960674</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4863203622043382</v>
+        <v>0.4863203622043377</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.726794044290147</v>
+        <v>1.726794044290063</v>
       </c>
       <c r="AQ472" t="n">
         <v>84.49074074074073</v>
@@ -77484,10 +77484,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.769755998762545</v>
+        <v>6.769755998762547</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.02364381202847099</v>
+        <v>0.02364381202846833</v>
       </c>
       <c r="AK473" t="n">
         <v>6.767889899932765</v>
@@ -77496,16 +77496,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3660007866474813</v>
+        <v>-0.3660007866474812</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.008260137822954145</v>
+        <v>0.00826013782295415</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.4997690914082401</v>
+        <v>0.4997690914082398</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.784096966502868</v>
+        <v>1.784096966502835</v>
       </c>
       <c r="AQ473" t="n">
         <v>85.25345622119815</v>
@@ -77649,10 +77649,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.789177604754244</v>
+        <v>6.789177604754239</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.01332216636391959</v>
+        <v>0.01332216636392491</v>
       </c>
       <c r="AK474" t="n">
         <v>6.759766754404358</v>
@@ -77661,16 +77661,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3700034659576351</v>
+        <v>-0.3700034659576358</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.009871715534546958</v>
+        <v>0.00987171553454691</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.5120623436103324</v>
+        <v>0.5120623436103316</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.652914640137256</v>
+        <v>1.652914640137312</v>
       </c>
       <c r="AQ474" t="n">
         <v>85.32319550919526</v>
@@ -77814,10 +77814,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.774331376960425</v>
+        <v>6.774331376960423</v>
       </c>
       <c r="AJ475" t="n">
-        <v>0.01776857573732915</v>
+        <v>0.01776857573733093</v>
       </c>
       <c r="AK475" t="n">
         <v>6.777856240868369</v>
@@ -77826,16 +77826,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3750442390024147</v>
+        <v>-0.3750442390024145</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.01196068662558781</v>
+        <v>0.01196068662558775</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.5238651846176463</v>
+        <v>0.5238651846176465</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.688064816833308</v>
+        <v>1.688064816833324</v>
       </c>
       <c r="AQ475" t="n">
         <v>84.47592361975924</v>
@@ -77991,16 +77991,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3816350905604307</v>
+        <v>-0.3816350905604304</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01460798460929556</v>
+        <v>0.01460798460929558</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5379583104732891</v>
+        <v>0.537958310473289</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.634085273781229</v>
+        <v>1.634085273781225</v>
       </c>
       <c r="AQ476" t="n">
         <v>85.00308515014397</v>
@@ -78144,10 +78144,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI477" t="n">
-        <v>6.789815280543245</v>
+        <v>6.789815280543246</v>
       </c>
       <c r="AJ477" t="n">
-        <v>-0.01031527291385093</v>
+        <v>-0.01031527291385181</v>
       </c>
       <c r="AK477" t="n">
         <v>6.744939020214936</v>
@@ -78156,16 +78156,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3872393091179339</v>
+        <v>-0.3872393091179336</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01685992867552231</v>
+        <v>0.01685992867552227</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.5511317941481415</v>
+        <v>0.5511317941481411</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.351268977384413</v>
+        <v>1.3512689773844</v>
       </c>
       <c r="AQ477" t="n">
         <v>82.59039582568994</v>
@@ -78309,10 +78309,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.801295181477309</v>
+        <v>6.801295181477315</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.0312952005507956</v>
+        <v>-0.03129520055080093</v>
       </c>
       <c r="AK478" t="n">
         <v>6.772636231606738</v>
@@ -78321,16 +78321,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3930200198603389</v>
+        <v>-0.393020019860339</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01873686412955481</v>
+        <v>0.01873686412955489</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5644439393662187</v>
+        <v>0.5644439393662184</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.111395060671059</v>
+        <v>1.111395060670998</v>
       </c>
       <c r="AQ478" t="n">
         <v>77.04823657738456</v>
@@ -78474,10 +78474,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.791632066062364</v>
+        <v>6.791632066062363</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.02343214540806748</v>
+        <v>-0.0234321454080666</v>
       </c>
       <c r="AK479" t="n">
         <v>6.788619247652995</v>
@@ -78486,16 +78486,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.3966294116439323</v>
+        <v>-0.3966294116439325</v>
       </c>
       <c r="AN479" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5769744719733717</v>
+        <v>0.576974471973372</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.192638315903155</v>
+        <v>1.192638315903163</v>
       </c>
       <c r="AQ479" t="n">
         <v>74.68169442664959</v>
@@ -78639,10 +78639,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.779898505875918</v>
+        <v>6.779898505875916</v>
       </c>
       <c r="AJ480" t="n">
-        <v>-0.00739846772894559</v>
+        <v>-0.007398467728943814</v>
       </c>
       <c r="AK480" t="n">
         <v>6.776305653888958</v>
@@ -78651,16 +78651,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3980313152890724</v>
+        <v>-0.3980313152890726</v>
       </c>
       <c r="AN480" t="n">
-        <v>0.0193312470422838</v>
+        <v>0.01933124704228378</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.5877384296086161</v>
+        <v>0.5877384296086169</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.362651795439232</v>
+        <v>1.362651795439249</v>
       </c>
       <c r="AQ480" t="n">
         <v>76.57043650793651</v>
@@ -78804,10 +78804,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.771360892616116</v>
+        <v>6.771360892616113</v>
       </c>
       <c r="AJ481" t="n">
-        <v>0.001139145530856922</v>
+        <v>0.001139145530859587</v>
       </c>
       <c r="AK481" t="n">
         <v>6.76492936370744</v>
@@ -78816,16 +78816,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3979537985659302</v>
+        <v>-0.3979537985659305</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01835844536093246</v>
+        <v>0.0183584453609324</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.6001791687136286</v>
+        <v>0.6001791687136281</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.44761945547675</v>
+        <v>1.447619455476777</v>
       </c>
       <c r="AQ481" t="n">
         <v>77.56047197640117</v>
@@ -78969,10 +78969,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.751667781721842</v>
+        <v>6.751667781721844</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.02083225642513042</v>
+        <v>0.02083225642512865</v>
       </c>
       <c r="AK482" t="n">
         <v>6.753855191419989</v>
@@ -78981,16 +78981,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3975762425746347</v>
+        <v>-0.3975762425746344</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.01731206726614282</v>
+        <v>0.01731206726614276</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6129676701055397</v>
+        <v>0.6129676701055393</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.652433919415649</v>
+        <v>1.652433919415626</v>
       </c>
       <c r="AQ482" t="n">
         <v>82.96557639078398</v>
@@ -79134,10 +79134,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.72973866986929</v>
+        <v>6.729738669869288</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.0358615345984834</v>
+        <v>0.03586153459848518</v>
       </c>
       <c r="AK483" t="n">
         <v>6.736226026398153</v>
@@ -79146,16 +79146,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.3964908591695858</v>
+        <v>-0.3964908591695859</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01740130648959375</v>
+        <v>0.01740130648959376</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6198907013195265</v>
+        <v>0.6198907013195262</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.801557827614175</v>
+        <v>1.80155782761419</v>
       </c>
       <c r="AQ483" t="n">
         <v>80.39647577092511</v>
@@ -79299,10 +79299,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.713320364291505</v>
+        <v>6.713320364291503</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.05917967385546774</v>
+        <v>0.05917967385546952</v>
       </c>
       <c r="AK484" t="n">
         <v>6.717723214958548</v>
@@ -79311,16 +79311,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3947605344816719</v>
+        <v>-0.394760534481672</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01742962324324019</v>
+        <v>0.01742962324324016</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6272835381163618</v>
+        <v>0.6272835381163622</v>
       </c>
       <c r="AP484" t="n">
-        <v>2.034796471975834</v>
+        <v>2.034796471975848</v>
       </c>
       <c r="AQ484" t="n">
         <v>87.28070175438597</v>
@@ -79464,10 +79464,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.731179671396997</v>
+        <v>6.731179671396989</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.04132036674997597</v>
+        <v>0.04132036674998396</v>
       </c>
       <c r="AK485" t="n">
         <v>6.699415101064979</v>
@@ -79479,13 +79479,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.0176659673264611</v>
+        <v>0.01766596732646103</v>
       </c>
       <c r="AO485" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP485" t="n">
-        <v>1.822287937402728</v>
+        <v>1.822287937402809</v>
       </c>
       <c r="AQ485" t="n">
         <v>86.68217201442947</v>
@@ -79629,10 +79629,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.740946959621005</v>
+        <v>6.740946959621007</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.03085308157772548</v>
+        <v>0.03085308157772371</v>
       </c>
       <c r="AK486" t="n">
         <v>6.714685154719483</v>
@@ -79641,16 +79641,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM486" t="n">
-        <v>-0.392942339423851</v>
+        <v>-0.3929423394238508</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.0184207037809263</v>
+        <v>0.01842070378092631</v>
       </c>
       <c r="AO486" t="n">
-        <v>0.6403745111659787</v>
+        <v>0.640374511165978</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.694121550775872</v>
+        <v>1.694121550775848</v>
       </c>
       <c r="AQ486" t="n">
         <v>84.56804065499718</v>
@@ -79794,10 +79794,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.758957757771704</v>
+        <v>6.7589577577717</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.006742105662134179</v>
+        <v>0.006742105662137732</v>
       </c>
       <c r="AK487" t="n">
         <v>6.722064699270507</v>
@@ -79806,16 +79806,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.3931401656438955</v>
+        <v>-0.3931401656438959</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.01902711841846487</v>
+        <v>0.01902711841846483</v>
       </c>
       <c r="AO487" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.423756665141781</v>
+        <v>1.423756665141814</v>
       </c>
       <c r="AQ487" t="n">
         <v>80.31236005373935</v>
@@ -79959,10 +79959,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.763209774497788</v>
+        <v>6.763209774497792</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.007790133949477251</v>
+        <v>0.007790133949473699</v>
       </c>
       <c r="AK488" t="n">
         <v>6.739235851443908</v>
@@ -79971,16 +79971,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3951733572725246</v>
+        <v>-0.3951733572725242</v>
       </c>
       <c r="AN488" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO488" t="n">
-        <v>0.6590798145480942</v>
+        <v>0.6590798145480943</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.425691102178843</v>
+        <v>1.425691102178801</v>
       </c>
       <c r="AQ488" t="n">
         <v>80.61269794287406</v>
@@ -80136,16 +80136,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.396000186332361</v>
+        <v>-0.3960001863323608</v>
       </c>
       <c r="AN489" t="n">
-        <v>0.02043272610569401</v>
+        <v>0.02043272610569408</v>
       </c>
       <c r="AO489" t="n">
-        <v>0.6685846444009627</v>
+        <v>0.6685846444009622</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.607866162312591</v>
+        <v>1.607866162312586</v>
       </c>
       <c r="AQ489" t="n">
         <v>81.11954807233778</v>
@@ -80289,10 +80289,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI490" t="n">
-        <v>6.714622134232888</v>
+        <v>6.714622134232894</v>
       </c>
       <c r="AJ490" t="n">
-        <v>0.04037798020802974</v>
+        <v>0.04037798020802441</v>
       </c>
       <c r="AK490" t="n">
         <v>6.746779913842831</v>
@@ -80301,16 +80301,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3967409053619114</v>
+        <v>-0.396740905361911</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.02120763540003743</v>
+        <v>0.02120763540003751</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6777865296786978</v>
+        <v>0.6777865296786982</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.748474068949984</v>
+        <v>1.748474068949922</v>
       </c>
       <c r="AQ490" t="n">
         <v>83.76250227314057</v>
@@ -80454,28 +80454,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.73157005939442</v>
+        <v>6.731570059394423</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.01932973232310964</v>
+        <v>0.01932973232310609</v>
       </c>
       <c r="AK491" t="n">
-        <v>6.728823425344639</v>
+        <v>6.728823425344638</v>
       </c>
       <c r="AL491" t="n">
-        <v>0.02207636637289045</v>
+        <v>0.02207636637289134</v>
       </c>
       <c r="AM491" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02200829621703764</v>
+        <v>0.0220082962170377</v>
       </c>
       <c r="AO491" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.512798467968243</v>
+        <v>1.512798467968202</v>
       </c>
       <c r="AQ491" t="n">
         <v>79.15614857554995</v>
@@ -80619,10 +80619,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.748064561399863</v>
+        <v>6.748064561399866</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.00423522421415079</v>
+        <v>0.004235224214148126</v>
       </c>
       <c r="AK492" t="n">
         <v>6.740096815166266</v>
@@ -80631,16 +80631,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM492" t="n">
-        <v>-0.3976889317784196</v>
+        <v>-0.3976889317784199</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.02268190844878653</v>
+        <v>0.02268190844878654</v>
       </c>
       <c r="AO492" t="n">
-        <v>0.6953567146475526</v>
+        <v>0.6953567146475523</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.343849828522187</v>
+        <v>1.343849828522157</v>
       </c>
       <c r="AQ492" t="n">
         <v>74.16595151255095</v>
@@ -80784,10 +80784,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.747226278872151</v>
+        <v>6.747226278872152</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.005973775296550521</v>
+        <v>0.005973775296548745</v>
       </c>
       <c r="AK493" t="n">
         <v>6.755554272205931</v>
@@ -80796,16 +80796,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.400351527586135</v>
+        <v>-0.4003515275861345</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02398656672240616</v>
+        <v>0.02398656672240618</v>
       </c>
       <c r="AO493" t="n">
-        <v>0.7067969646460924</v>
+        <v>0.7067969646460921</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.354205923149349</v>
+        <v>1.354205923149328</v>
       </c>
       <c r="AQ493" t="n">
         <v>73.85295890508101</v>
@@ -80949,10 +80949,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.724989986752573</v>
+        <v>6.724989986752571</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.02471008267491737</v>
+        <v>0.02471008267491914</v>
       </c>
       <c r="AK494" t="n">
         <v>6.75925064743029</v>
@@ -80961,7 +80961,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4017887258056131</v>
+        <v>-0.4017887258056133</v>
       </c>
       <c r="AN494" t="n">
         <v>0.02482212216928553</v>
@@ -80970,7 +80970,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.542202842029855</v>
+        <v>1.542202842029871</v>
       </c>
       <c r="AQ494" t="n">
         <v>77.31619844590556</v>
@@ -81114,28 +81114,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.738231277482303</v>
+        <v>6.738231277482312</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.01056852339049996</v>
+        <v>0.01056852339049108</v>
       </c>
       <c r="AK495" t="n">
-        <v>6.734775445902896</v>
+        <v>6.734775445902895</v>
       </c>
       <c r="AL495" t="n">
-        <v>0.01402435496990684</v>
+        <v>0.01402435496990773</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.402229404255429</v>
+        <v>-0.4022294042554291</v>
       </c>
       <c r="AN495" t="n">
-        <v>0.02545790195722734</v>
+        <v>0.02545790195722747</v>
       </c>
       <c r="AO495" t="n">
-        <v>0.7273309315128232</v>
+        <v>0.7273309315128231</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.383925936185805</v>
+        <v>1.383925936185709</v>
       </c>
       <c r="AQ495" t="n">
         <v>74.69839609483961</v>
@@ -81279,10 +81279,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.718201282169575</v>
+        <v>6.718201282169581</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.02919852480674301</v>
+        <v>0.02919852480673768</v>
       </c>
       <c r="AK496" t="n">
         <v>6.753996132599221</v>
@@ -81291,16 +81291,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4027953816469059</v>
+        <v>-0.4027953816469058</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02608258444417639</v>
+        <v>0.02608258444417638</v>
       </c>
       <c r="AO496" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.56944615641164</v>
+        <v>1.569446156411583</v>
       </c>
       <c r="AQ496" t="n">
         <v>78.54598893499308</v>
@@ -81444,10 +81444,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.730898772467415</v>
+        <v>6.730898772467414</v>
       </c>
       <c r="AJ497" t="n">
-        <v>0.01650103450890317</v>
+        <v>0.01650103450890406</v>
       </c>
       <c r="AK497" t="n">
         <v>6.732394407262716</v>
@@ -81456,16 +81456,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.402509900769414</v>
+        <v>-0.4025099007694142</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02634377330607648</v>
+        <v>0.02634377330607651</v>
       </c>
       <c r="AO497" t="n">
-        <v>0.7465615195282662</v>
+        <v>0.746561519528266</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.426589599757333</v>
+        <v>1.426589599757341</v>
       </c>
       <c r="AQ497" t="n">
         <v>79.05678817598847</v>
@@ -81621,16 +81621,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4034224290251453</v>
+        <v>-0.4034224290251451</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02736182786837866</v>
+        <v>0.02736182786837871</v>
       </c>
       <c r="AO498" t="n">
-        <v>0.7551898634710656</v>
+        <v>0.755189863471066</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.292377454135955</v>
+        <v>1.292377454135954</v>
       </c>
       <c r="AQ498" t="n">
         <v>77.08312076998946</v>
@@ -81774,10 +81774,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI499" t="n">
-        <v>6.75570846679488</v>
+        <v>6.755708466794879</v>
       </c>
       <c r="AJ499" t="n">
-        <v>-0.01240850570479246</v>
+        <v>-0.01240850570479068</v>
       </c>
       <c r="AK499" t="n">
         <v>6.746865899087779</v>
@@ -81786,16 +81786,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.4037073020769305</v>
+        <v>-0.4037073020769307</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02778289906564353</v>
+        <v>0.02778289906564352</v>
       </c>
       <c r="AO499" t="n">
-        <v>0.7638221248099444</v>
+        <v>0.7638221248099442</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.110551359343203</v>
+        <v>1.110551359343221</v>
       </c>
       <c r="AQ499" t="n">
         <v>79.86237603723941</v>
@@ -81939,10 +81939,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI500" t="n">
-        <v>6.73601646973097</v>
+        <v>6.73601646973098</v>
       </c>
       <c r="AJ500" t="n">
-        <v>0.006783766017321113</v>
+        <v>0.006783766017311343</v>
       </c>
       <c r="AK500" t="n">
         <v>6.761018647414997</v>
@@ -81951,16 +81951,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4035108188951355</v>
+        <v>-0.403510818895136</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02805871830419202</v>
+        <v>0.02805871830419215</v>
       </c>
       <c r="AO500" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.304722339904909</v>
+        <v>1.304722339904807</v>
       </c>
       <c r="AQ500" t="n">
         <v>83.621612579458</v>
@@ -82119,7 +82119,7 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02827333203020884</v>
+        <v>0.02827333203020888</v>
       </c>
       <c r="AO501" t="n">
         <v>0.7726830480787004</v>
@@ -82269,10 +82269,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI502" t="n">
-        <v>6.725806144687716</v>
+        <v>6.725806144687715</v>
       </c>
       <c r="AJ502" t="n">
-        <v>0.01409396746438318</v>
+        <v>0.01409396746438496</v>
       </c>
       <c r="AK502" t="n">
         <v>6.744478107428201</v>
@@ -82281,16 +82281,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM502" t="n">
-        <v>-0.4027900432658339</v>
+        <v>-0.4027900432658338</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.0289145361322863</v>
+        <v>0.02891453613228628</v>
       </c>
       <c r="AO502" t="n">
-        <v>0.7784357006627718</v>
+        <v>0.7784357006627721</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.365006718117265</v>
+        <v>1.365006718117283</v>
       </c>
       <c r="AQ502" t="n">
         <v>83.54975148941773</v>
@@ -82434,10 +82434,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.700854569500285</v>
+        <v>6.700854569500288</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.04174539464156091</v>
+        <v>0.04174539464155735</v>
       </c>
       <c r="AK503" t="n">
         <v>6.743301592583855</v>
@@ -82446,16 +82446,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM503" t="n">
-        <v>-0.4027426974585472</v>
+        <v>-0.402742697458547</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.0295556803648227</v>
+        <v>0.02955568036482276</v>
       </c>
       <c r="AO503" t="n">
-        <v>0.7839391318357879</v>
+        <v>0.7839391318357882</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.641342082788135</v>
+        <v>1.641342082788098</v>
       </c>
       <c r="AQ503" t="n">
         <v>88.46235470811023</v>
@@ -82599,10 +82599,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.705597066237454</v>
+        <v>6.705597066237452</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.02390275065707748</v>
+        <v>0.02390275065707925</v>
       </c>
       <c r="AK504" t="n">
         <v>6.74285285202661</v>
@@ -82611,16 +82611,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.4015885003200582</v>
+        <v>-0.401588500320058</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.02985284499018428</v>
+        <v>0.02985284499018426</v>
       </c>
       <c r="AO504" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.446604328365808</v>
+        <v>1.446604328365827</v>
       </c>
       <c r="AQ504" t="n">
         <v>85.08793237465994</v>
@@ -82764,28 +82764,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.686024746022948</v>
+        <v>6.686024746022946</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.03647510138916132</v>
+        <v>0.0364751013891631</v>
       </c>
       <c r="AK505" t="n">
-        <v>6.744526329542679</v>
+        <v>6.744526329542678</v>
       </c>
       <c r="AL505" t="n">
-        <v>-0.02202648213056957</v>
+        <v>-0.02202648213056868</v>
       </c>
       <c r="AM505" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.02995529076246446</v>
+        <v>0.02995529076246445</v>
       </c>
       <c r="AO505" t="n">
-        <v>0.7933293013213371</v>
+        <v>0.7933293013213367</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.566182359822729</v>
+        <v>1.566182359822747</v>
       </c>
       <c r="AQ505" t="n">
         <v>84.34056224899598</v>
@@ -82929,10 +82929,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.689653251437547</v>
+        <v>6.689653251437546</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.03134694311201347</v>
+        <v>0.03134694311201436</v>
       </c>
       <c r="AK506" t="n">
         <v>6.730402461316146</v>
@@ -82941,16 +82941,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM506" t="n">
-        <v>-0.3993041981056886</v>
+        <v>-0.3993041981056888</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.03010093147709737</v>
+        <v>0.03010093147709741</v>
       </c>
       <c r="AO506" t="n">
-        <v>0.7985853639949436</v>
+        <v>0.7985853639949437</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.507036858820233</v>
+        <v>1.507036858820243</v>
       </c>
       <c r="AQ506" t="n">
         <v>85</v>
@@ -83094,10 +83094,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.716786041117424</v>
+        <v>6.716786041117415</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.005113945149665788</v>
+        <v>0.00511394514967467</v>
       </c>
       <c r="AK507" t="n">
         <v>6.728106442363027</v>
@@ -83106,16 +83106,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM507" t="n">
-        <v>-0.3976134529492094</v>
+        <v>-0.3976134529492091</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03006044259180338</v>
+        <v>0.03006044259180324</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.8026437279892848</v>
+        <v>0.8026437279892851</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.234777974751887</v>
+        <v>1.234777974751978</v>
       </c>
       <c r="AQ507" t="n">
         <v>81.59999999999999</v>
@@ -83259,10 +83259,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.72193279551444</v>
+        <v>6.721932795514441</v>
       </c>
       <c r="AJ508" t="n">
-        <v>-0.001632597913121536</v>
+        <v>-0.001632597913122424</v>
       </c>
       <c r="AK508" t="n">
         <v>6.752314636061016</v>
@@ -83274,13 +83274,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03043336917902487</v>
+        <v>0.03043336917902489</v>
       </c>
       <c r="AO508" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.163823515923099</v>
+        <v>1.16382351592309</v>
       </c>
       <c r="AQ508" t="n">
         <v>82.19999999999999</v>
@@ -83424,28 +83424,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.718669003366529</v>
+        <v>6.718669003366535</v>
       </c>
       <c r="AJ509" t="n">
-        <v>0.003830844045580761</v>
+        <v>0.003830844045574544</v>
       </c>
       <c r="AK509" t="n">
-        <v>6.750203856204786</v>
+        <v>6.750203856204787</v>
       </c>
       <c r="AL509" t="n">
-        <v>-0.02770400879267676</v>
+        <v>-0.02770400879267765</v>
       </c>
       <c r="AM509" t="n">
-        <v>-0.3969152632178359</v>
+        <v>-0.3969152632178358</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03100517332816427</v>
+        <v>0.03100517332816438</v>
       </c>
       <c r="AO509" t="n">
-        <v>0.8091236362457366</v>
+        <v>0.8091236362457368</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.217453571381111</v>
+        <v>1.217453571381048</v>
       </c>
       <c r="AQ509" t="n">
         <v>82.80000000000001</v>
@@ -83589,10 +83589,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.680190080689519</v>
+        <v>6.680190080689523</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.04230976672259068</v>
+        <v>0.04230976672258624</v>
       </c>
       <c r="AK510" t="n">
         <v>6.74780904069481</v>
@@ -83601,16 +83601,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM510" t="n">
-        <v>-0.3964565291282773</v>
+        <v>-0.3964565291282772</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03139664408873165</v>
+        <v>0.03139664408873172</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8123541153569371</v>
+        <v>0.8123541153569376</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.60449324842414</v>
+        <v>1.604493248424095</v>
       </c>
       <c r="AQ510" t="n">
         <v>89.8</v>
@@ -83754,10 +83754,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.671580974366949</v>
+        <v>6.671580974366952</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.05441885778637179</v>
+        <v>0.05441885778636824</v>
       </c>
       <c r="AK511" t="n">
         <v>6.701878095437348</v>
@@ -83769,13 +83769,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03163116863423025</v>
+        <v>0.03163116863423027</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8147568654710426</v>
+        <v>0.8147568654710424</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.717274375116493</v>
+        <v>1.717274375116458</v>
       </c>
       <c r="AQ511" t="n">
         <v>90.2</v>
@@ -83919,28 +83919,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.656216276126093</v>
+        <v>6.656216276126097</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.06978355602722708</v>
+        <v>0.06978355602722353</v>
       </c>
       <c r="AK512" t="n">
-        <v>6.701765808189925</v>
+        <v>6.701765808189924</v>
       </c>
       <c r="AL512" t="n">
-        <v>0.02423402396339558</v>
+        <v>0.02423402396339647</v>
       </c>
       <c r="AM512" t="n">
-        <v>-0.3932426568003567</v>
+        <v>-0.3932426568003564</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03191273276172183</v>
+        <v>0.0319127327617218</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8170879052811416</v>
+        <v>0.8170879052811413</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.858889534485378</v>
+        <v>1.858889534485344</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.59999999999999</v>
@@ -84090,22 +84090,22 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK513" t="n">
-        <v>6.682658801267994</v>
+        <v>6.682658801267993</v>
       </c>
       <c r="AL513" t="n">
-        <v>0.03754126053010154</v>
+        <v>0.03754126053010243</v>
       </c>
       <c r="AM513" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.03225018457163047</v>
+        <v>0.03225018457163042</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8195353634242113</v>
+        <v>0.8195353634242114</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.818117584748586</v>
+        <v>1.818117584748587</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.2</v>
@@ -84249,10 +84249,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI514" t="n">
-        <v>6.654231073451242</v>
+        <v>6.654231073451243</v>
       </c>
       <c r="AJ514" t="n">
-        <v>0.06476878921965668</v>
+        <v>0.06476878921965579</v>
       </c>
       <c r="AK514" t="n">
         <v>6.682840937292736</v>
@@ -84261,16 +84261,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM514" t="n">
-        <v>-0.3894836768645476</v>
+        <v>-0.3894836768645471</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.03277193700354209</v>
+        <v>0.03277193700354208</v>
       </c>
       <c r="AO514" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP514" t="n">
-        <v>1.781104797300574</v>
+        <v>1.781104797300567</v>
       </c>
       <c r="AQ514" t="n">
         <v>90.2</v>
@@ -84414,10 +84414,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.650937329061552</v>
+        <v>6.650937329061554</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.06806253360934633</v>
+        <v>0.06806253360934456</v>
       </c>
       <c r="AK515" t="n">
         <v>6.698821600583909</v>
@@ -84426,16 +84426,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM515" t="n">
-        <v>-0.3885003849593203</v>
+        <v>-0.3885003849593205</v>
       </c>
       <c r="AN515" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO515" t="n">
-        <v>0.8264954348925952</v>
+        <v>0.8264954348925954</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.799874833536367</v>
+        <v>1.799874833536351</v>
       </c>
       <c r="AQ515" t="n">
         <v>91</v>
@@ -84579,10 +84579,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.651733245487366</v>
+        <v>6.651733245487365</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.05906692541107184</v>
+        <v>0.05906692541107272</v>
       </c>
       <c r="AK516" t="n">
         <v>6.69208631505748</v>
@@ -84591,16 +84591,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM516" t="n">
-        <v>-0.3869746098498528</v>
+        <v>-0.3869746098498524</v>
       </c>
       <c r="AN516" t="n">
-        <v>0.03441888977522091</v>
+        <v>0.0344188897752209</v>
       </c>
       <c r="AO516" t="n">
-        <v>0.8294137131605726</v>
+        <v>0.8294137131605728</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.696616308981445</v>
+        <v>1.696616308981455</v>
       </c>
       <c r="AQ516" t="n">
         <v>90.40000000000001</v>
@@ -84744,10 +84744,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.632036771677475</v>
+        <v>6.632036771677474</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.07876339922096243</v>
+        <v>0.07876339922096331</v>
       </c>
       <c r="AK517" t="n">
         <v>6.692627206904497</v>
@@ -84765,7 +84765,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.875440190456845</v>
+        <v>1.875440190456855</v>
       </c>
       <c r="AQ517" t="n">
         <v>91</v>
@@ -84909,10 +84909,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI518" t="n">
-        <v>6.617259294346145</v>
+        <v>6.617259294346139</v>
       </c>
       <c r="AJ518" t="n">
-        <v>0.09324046914262496</v>
+        <v>0.09324046914263029</v>
       </c>
       <c r="AK518" t="n">
         <v>6.685306332307247</v>
@@ -84924,13 +84924,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN518" t="n">
-        <v>0.03459091746240425</v>
+        <v>0.03459091746240417</v>
       </c>
       <c r="AO518" t="n">
-        <v>0.8328314813119078</v>
+        <v>0.8328314813119074</v>
       </c>
       <c r="AP518" t="n">
-        <v>1.998006000856694</v>
+        <v>1.998006000856746</v>
       </c>
       <c r="AQ518" t="n">
         <v>91</v>
@@ -85086,13 +85086,13 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM519" t="n">
-        <v>-0.3791985032227784</v>
+        <v>-0.379198503222778</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03468237364461172</v>
+        <v>0.03468237364461174</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8349203610870052</v>
+        <v>0.8349203610870053</v>
       </c>
       <c r="AP519" t="n">
         <v>2.317228225252932</v>
@@ -85254,13 +85254,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.0343742787852416</v>
+        <v>0.03437427878524163</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8337972329517072</v>
+        <v>0.8337972329517069</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.426255822246375</v>
+        <v>2.426255822246374</v>
       </c>
       <c r="AQ520" t="n">
         <v>93.40000000000001</v>
@@ -85404,10 +85404,10 @@
         <v>-0.2483229054629721</v>
       </c>
       <c r="AI521" t="n">
-        <v>6.57078983057249</v>
+        <v>6.570789830572489</v>
       </c>
       <c r="AJ521" t="n">
-        <v>0.1372103525329784</v>
+        <v>0.1372103525329802</v>
       </c>
       <c r="AK521" t="n">
         <v>6.617345065810827</v>
@@ -85416,16 +85416,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM521" t="n">
-        <v>-0.3685435183382902</v>
+        <v>-0.3685435183382903</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03361173230743112</v>
+        <v>0.03361173230743109</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8313650598704546</v>
+        <v>0.8313650598704547</v>
       </c>
       <c r="AP521" t="n">
-        <v>2.33221640036803</v>
+        <v>2.332216400368046</v>
       </c>
       <c r="AQ521" t="n">
         <v>91.8</v>
@@ -85569,10 +85569,10 @@
         <v>-0.2475852618441712</v>
       </c>
       <c r="AI522" t="n">
-        <v>6.574987720536736</v>
+        <v>6.574987720536733</v>
       </c>
       <c r="AJ522" t="n">
-        <v>0.1332122573380197</v>
+        <v>0.1332122573380232</v>
       </c>
       <c r="AK522" t="n">
         <v>6.613295682645951</v>
@@ -85581,16 +85581,16 @@
         <v>0.09490429522880461</v>
       </c>
       <c r="AM522" t="n">
-        <v>-0.3628803332699742</v>
+        <v>-0.362880333269974</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03286620172062364</v>
+        <v>0.0328662017206236</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8299335523861298</v>
+        <v>0.82993355238613</v>
       </c>
       <c r="AP522" t="n">
-        <v>2.265952574875376</v>
+        <v>2.265952574875408</v>
       </c>
       <c r="AQ522" t="n">
         <v>91.8</v>
@@ -85746,16 +85746,16 @@
         <v>0.1007055635562768</v>
       </c>
       <c r="AM523" t="n">
-        <v>-0.3578313453157059</v>
+        <v>-0.3578313453157061</v>
       </c>
       <c r="AN523" t="n">
-        <v>0.03253304912369535</v>
+        <v>0.03253304912369537</v>
       </c>
       <c r="AO523" t="n">
-        <v>0.829501685468071</v>
+        <v>0.8295016854680709</v>
       </c>
       <c r="AP523" t="n">
-        <v>2.256510029904999</v>
+        <v>2.256510029904998</v>
       </c>
       <c r="AQ523" t="n">
         <v>92.40000000000001</v>
@@ -85810,13 +85810,13 @@
         <v>6.705999851226807</v>
       </c>
       <c r="F524" t="n">
-        <v>6.702600002288818</v>
+        <v>6.702250003814697</v>
       </c>
       <c r="G524" t="n">
         <v>6.6951</v>
       </c>
       <c r="H524" t="n">
-        <v>-0.003399848937988281</v>
+        <v>-0.003749847412109375</v>
       </c>
       <c r="I524" t="n">
         <v>100.3099975585938</v>
@@ -85914,13 +85914,13 @@
         <v>-0.3533816852595308</v>
       </c>
       <c r="AN524" t="n">
-        <v>0.03276281973018107</v>
+        <v>0.03276281973018108</v>
       </c>
       <c r="AO524" t="n">
-        <v>0.8294865216719108</v>
+        <v>0.8294865216719109</v>
       </c>
       <c r="AP524" t="n">
-        <v>1.879095330401617</v>
+        <v>1.879095330401616</v>
       </c>
       <c r="AQ524" t="n">
         <v>91.8</v>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41365,10 +41365,10 @@
         <v>0.02830263755936446</v>
       </c>
       <c r="AI254" t="n">
-        <v>7.150419484347116</v>
+        <v>7.150419484347115</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.009019623965035528</v>
+        <v>-0.00901962396503464</v>
       </c>
       <c r="AK254" t="n">
         <v>7.161074530187645</v>
@@ -41377,13 +41377,13 @@
         <v>-0.01967466980556498</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1029385549788083</v>
+        <v>0.102938554978808</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002436328878122382</v>
+        <v>0.002436328878122375</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2711996176877891</v>
+        <v>0.2711996176877889</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41530,10 +41530,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI255" t="n">
-        <v>7.148511457776028</v>
+        <v>7.14851145777603</v>
       </c>
       <c r="AJ255" t="n">
-        <v>-0.01601128611465086</v>
+        <v>-0.01601128611465263</v>
       </c>
       <c r="AK255" t="n">
         <v>7.150963414761942</v>
@@ -41542,13 +41542,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.1011329645838851</v>
+        <v>0.1011329645838857</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002517185580011447</v>
+        <v>0.002517185580011383</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2709113683260677</v>
+        <v>0.2709113683260674</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41707,13 +41707,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.09870181295186471</v>
+        <v>0.09870181295186436</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002644711580562537</v>
+        <v>0.002644711580562605</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2704892730019304</v>
+        <v>0.2704892730019285</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41860,10 +41860,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.153772633426659</v>
+        <v>7.153772633426657</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.03287247931288917</v>
+        <v>-0.03287247931288739</v>
       </c>
       <c r="AK257" t="n">
         <v>7.154757231824306</v>
@@ -41872,13 +41872,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.09555831842873846</v>
+        <v>0.09555831842873888</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.002822832879878071</v>
+        <v>0.002822832879878049</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2697410008595936</v>
+        <v>0.2697410008595938</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42025,10 +42025,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI258" t="n">
-        <v>7.153331199414496</v>
+        <v>7.153331199414497</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-0.03263131690717191</v>
+        <v>-0.0326313169071728</v>
       </c>
       <c r="AK258" t="n">
         <v>7.15450652143491</v>
@@ -42037,13 +42037,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.0918844066524992</v>
+        <v>0.09188440665249918</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.003041971996730133</v>
+        <v>0.003041971996730116</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2698098046976256</v>
+        <v>0.2698098046976254</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42190,10 +42190,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI259" t="n">
-        <v>7.156943148319592</v>
+        <v>7.15694314831959</v>
       </c>
       <c r="AJ259" t="n">
-        <v>-0.03854305142628167</v>
+        <v>-0.0385430514262799</v>
       </c>
       <c r="AK259" t="n">
         <v>7.154505434137821</v>
@@ -42202,13 +42202,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.08748497753913406</v>
+        <v>0.08748497753913362</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.003298336925509862</v>
+        <v>0.003298336925509857</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2682008942988235</v>
+        <v>0.2682008942988222</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42367,13 +42367,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM260" t="n">
-        <v>0.0824587084059305</v>
+        <v>0.08245870840593096</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003602928090795432</v>
+        <v>0.003602928090795422</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2685806390401517</v>
+        <v>0.2685806390401518</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42535,10 +42535,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.003819541738581442</v>
+        <v>0.003819541738581439</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2696768907787764</v>
+        <v>0.2696768907787754</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42685,10 +42685,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI262" t="n">
-        <v>7.154685377655177</v>
+        <v>7.154685377655176</v>
       </c>
       <c r="AJ262" t="n">
-        <v>-0.04048526245131967</v>
+        <v>-0.04048526245131878</v>
       </c>
       <c r="AK262" t="n">
         <v>7.15808570026938</v>
@@ -42697,13 +42697,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.07200163454913491</v>
+        <v>0.07200163454913533</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.004193740708391541</v>
+        <v>0.004193740708391577</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.270116598814735</v>
+        <v>0.2701165988147326</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42850,10 +42850,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI263" t="n">
-        <v>7.158449213455076</v>
+        <v>7.158449213455078</v>
       </c>
       <c r="AJ263" t="n">
-        <v>-0.05514911885058371</v>
+        <v>-0.05514911885058549</v>
       </c>
       <c r="AK263" t="n">
         <v>7.157644979270017</v>
@@ -42862,13 +42862,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM263" t="n">
-        <v>0.06676111471939408</v>
+        <v>0.06676111471939436</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.00450521933759436</v>
+        <v>0.004505219337594384</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.2733976337163381</v>
+        <v>0.2733976337163387</v>
       </c>
       <c r="AP263" t="n">
         <v/>
@@ -43015,10 +43015,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.160761769069204</v>
+        <v>7.160761769069201</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.04786198879576631</v>
+        <v>-0.04786198879576364</v>
       </c>
       <c r="AK264" t="n">
         <v>7.159146249199162</v>
@@ -43027,10 +43027,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.06148465881746725</v>
+        <v>0.06148465881746766</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.004852471327681615</v>
+        <v>0.004852471327681566</v>
       </c>
       <c r="AO264" t="n">
         <v>0.2778048766368325</v>
@@ -43180,10 +43180,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI265" t="n">
-        <v>7.162478122158095</v>
+        <v>7.162478122158094</v>
       </c>
       <c r="AJ265" t="n">
-        <v>-0.04957834188465782</v>
+        <v>-0.04957834188465693</v>
       </c>
       <c r="AK265" t="n">
         <v>7.159578986975002</v>
@@ -43192,13 +43192,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.05582594297075769</v>
+        <v>0.05582594297075712</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.005234102211236422</v>
+        <v>0.005234102211236467</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.282448024375059</v>
+        <v>0.2824480243750598</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43357,13 +43357,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.04949165986049534</v>
+        <v>0.04949165986049463</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.005677665039252891</v>
+        <v>0.005677665039252918</v>
       </c>
       <c r="AO266" t="n">
-        <v>0.2878618994559775</v>
+        <v>0.2878618994559794</v>
       </c>
       <c r="AP266" t="n">
         <v/>
@@ -43522,13 +43522,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.04287777011073584</v>
+        <v>0.04287777011073606</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.006155260602669632</v>
+        <v>0.006155260602669625</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.2948468705933219</v>
+        <v>0.2948468705933236</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43675,10 +43675,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI268" t="n">
-        <v>7.173971773133425</v>
+        <v>7.173971773133423</v>
       </c>
       <c r="AJ268" t="n">
-        <v>-0.04247200582995792</v>
+        <v>-0.04247200582995614</v>
       </c>
       <c r="AK268" t="n">
         <v>7.159255388854645</v>
@@ -43687,13 +43687,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.0348694200966178</v>
+        <v>0.03486942009661778</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.006728155724408227</v>
+        <v>0.006728155724408201</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.304499875642397</v>
+        <v>0.3044998756423967</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43840,25 +43840,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI269" t="n">
-        <v>7.172030417300567</v>
+        <v>7.172030417300565</v>
       </c>
       <c r="AJ269" t="n">
-        <v>-0.03823038754592822</v>
+        <v>-0.03823038754592645</v>
       </c>
       <c r="AK269" t="n">
-        <v>7.167062070913353</v>
+        <v>7.167062070913352</v>
       </c>
       <c r="AL269" t="n">
-        <v>-0.03326204115871434</v>
+        <v>-0.03326204115871345</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.03279550096037902</v>
+        <v>0.03279550096037874</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.006903991232239788</v>
+        <v>0.006903991232239758</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.3170366335916601</v>
+        <v>0.3170366335916608</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -44005,10 +44005,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.171236182927453</v>
+        <v>7.171236182927454</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.03843608069356641</v>
+        <v>-0.0384360806935673</v>
       </c>
       <c r="AK270" t="n">
         <v>7.16747443083108</v>
@@ -44017,13 +44017,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.02972414459983895</v>
+        <v>0.02972414459983913</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.007158147882858998</v>
+        <v>0.007158147882859</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.3270754385893867</v>
+        <v>0.3270754385893863</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44170,10 +44170,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI271" t="n">
-        <v>7.170425137628191</v>
+        <v>7.170425137628194</v>
       </c>
       <c r="AJ271" t="n">
-        <v>-0.05102511321412884</v>
+        <v>-0.0510251132141315</v>
       </c>
       <c r="AK271" t="n">
         <v>7.168373097443463</v>
@@ -44182,13 +44182,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.02657019411530269</v>
+        <v>0.02657019411530295</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.007420436972250415</v>
+        <v>0.007420436972250398</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3357224795973284</v>
+        <v>0.3357224795973281</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44347,13 +44347,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.02366886174665103</v>
+        <v>0.02366886174665165</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.007679120311627263</v>
+        <v>0.007679120311627231</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3450219581941938</v>
+        <v>0.345021958194194</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44500,10 +44500,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.172249622131827</v>
+        <v>7.172249622131823</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.05324966409349674</v>
+        <v>-0.05324966409349319</v>
       </c>
       <c r="AK273" t="n">
         <v>7.167365057101177</v>
@@ -44512,13 +44512,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.01956653131084185</v>
+        <v>0.01956653131084189</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.008034860291676559</v>
+        <v>0.008034860291676519</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3572033251592189</v>
+        <v>0.3572033251592186</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44665,10 +44665,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI274" t="n">
-        <v>7.171656420777024</v>
+        <v>7.171656420777023</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-0.05265646273869429</v>
+        <v>-0.0526564627386934</v>
       </c>
       <c r="AK274" t="n">
         <v>7.167567681415887</v>
@@ -44677,13 +44677,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.01638396088890769</v>
+        <v>0.0163839608889081</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.008326212487477964</v>
+        <v>0.008326212487477898</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3674516177552961</v>
+        <v>0.3674516177552964</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44830,10 +44830,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI275" t="n">
-        <v>7.175289829564748</v>
+        <v>7.175289829564746</v>
       </c>
       <c r="AJ275" t="n">
-        <v>-0.05628987152641773</v>
+        <v>-0.05628987152641596</v>
       </c>
       <c r="AK275" t="n">
         <v>7.167553154788029</v>
@@ -44842,13 +44842,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.01351198449095157</v>
+        <v>0.01351198449095179</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008601682347582891</v>
+        <v>0.008601682347582911</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3758646846617525</v>
+        <v>0.375864684661753</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -45001,19 +45001,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK276" t="n">
-        <v>7.16746081477764</v>
+        <v>7.167460814777641</v>
       </c>
       <c r="AL276" t="n">
-        <v>-0.04846085673931011</v>
+        <v>-0.048460856739311</v>
       </c>
       <c r="AM276" t="n">
-        <v>0.01196199498966369</v>
+        <v>0.01196199498966377</v>
       </c>
       <c r="AN276" t="n">
-        <v>0.008797062853284063</v>
+        <v>0.008797062853284078</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.3847384959530242</v>
+        <v>0.3847384959530228</v>
       </c>
       <c r="AP276" t="n">
         <v/>
@@ -45321,10 +45321,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI278" t="n">
-        <v>7.189678003526525</v>
+        <v>7.189678003526526</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-0.07117777082999144</v>
+        <v>-0.07117777082999321</v>
       </c>
       <c r="AK278" t="n">
         <v/>
@@ -45333,13 +45333,13 @@
         <v/>
       </c>
       <c r="AM278" t="n">
-        <v>0.007307555239791734</v>
+        <v>0.007307555239791735</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.009236289154790337</v>
+        <v>0.009236289154790363</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.401039717356949</v>
+        <v>0.4010397173569483</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45486,10 +45486,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI279" t="n">
-        <v>7.183919177237467</v>
+        <v>7.183919177237466</v>
       </c>
       <c r="AJ279" t="n">
-        <v>-0.05641912001700788</v>
+        <v>-0.056419120017007</v>
       </c>
       <c r="AK279" t="n">
         <v>7.168706858585229</v>
@@ -45498,13 +45498,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM279" t="n">
-        <v>0.006573598200530942</v>
+        <v>0.006573598200531427</v>
       </c>
       <c r="AN279" t="n">
-        <v>0.009378157495070056</v>
+        <v>0.009378157495070007</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.4093166892046883</v>
+        <v>0.4093166892046876</v>
       </c>
       <c r="AP279" t="n">
         <v/>
@@ -45663,13 +45663,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM280" t="n">
-        <v>0.005719699928660468</v>
+        <v>0.00571969992866044</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.009535855797507643</v>
+        <v>0.009535855797507651</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.4189456552735356</v>
+        <v>0.4189456552735351</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45816,10 +45816,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI281" t="n">
-        <v>7.183803634757356</v>
+        <v>7.183803634757355</v>
       </c>
       <c r="AJ281" t="n">
-        <v>-0.08380373012478781</v>
+        <v>-0.08380373012478692</v>
       </c>
       <c r="AK281" t="n">
         <v>7.157754776965645</v>
@@ -45828,13 +45828,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.007205793377056199</v>
+        <v>0.007205793377055721</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009541847058682544</v>
+        <v>0.00954184705868257</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4265135453780396</v>
+        <v>0.4265135453780416</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45987,19 +45987,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK282" t="n">
-        <v>7.153578345933642</v>
+        <v>7.153578345933643</v>
       </c>
       <c r="AL282" t="n">
-        <v>-0.01517826811381795</v>
+        <v>-0.01517826811381884</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.009937300636551308</v>
+        <v>0.009937300636551421</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.00947510825395563</v>
+        <v>0.009475108253955637</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4359288044119884</v>
+        <v>0.4359288044119891</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46146,10 +46146,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI283" t="n">
-        <v>7.175374323571331</v>
+        <v>7.175374323571332</v>
       </c>
       <c r="AJ283" t="n">
-        <v>-0.04917412444413394</v>
+        <v>-0.04917412444413483</v>
       </c>
       <c r="AK283" t="n">
         <v>7.155226204999164</v>
@@ -46158,13 +46158,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.01039951522374721</v>
+        <v>0.01039951522374727</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009534227083684284</v>
+        <v>0.009534227083684297</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.446224869246465</v>
+        <v>0.4462248692464653</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46323,13 +46323,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.01174445052819259</v>
+        <v>0.01174445052819296</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.009539024405591096</v>
+        <v>0.009539024405591111</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4561706550234678</v>
+        <v>0.4561706550234662</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46476,10 +46476,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI285" t="n">
-        <v>7.176295466764674</v>
+        <v>7.176295466764673</v>
       </c>
       <c r="AJ285" t="n">
-        <v>-0.04989547286818929</v>
+        <v>-0.04989547286818841</v>
       </c>
       <c r="AK285" t="n">
         <v>7.150954883812801</v>
@@ -46488,13 +46488,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01399948938427905</v>
+        <v>0.01399948938427885</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009474826008246758</v>
+        <v>0.009474826008246765</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.4654004237248369</v>
+        <v>0.4654004237248376</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46653,13 +46653,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM286" t="n">
-        <v>0.01676993900799729</v>
+        <v>0.01676993900799728</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009377028877974699</v>
+        <v>0.00937702887797469</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.476700939638935</v>
+        <v>0.4767009396389351</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46821,10 +46821,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009204864903404497</v>
+        <v>0.009204864903404482</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4883841032893044</v>
+        <v>0.4883841032893032</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46983,13 +46983,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.02435543352765289</v>
+        <v>0.02435543352765317</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.009045821984022376</v>
+        <v>0.00904582198402234</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.4990078266507766</v>
+        <v>0.4990078266507749</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47136,10 +47136,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI289" t="n">
-        <v>7.175210595491395</v>
+        <v>7.175210595491394</v>
       </c>
       <c r="AJ289" t="n">
-        <v>-0.04951059854315254</v>
+        <v>-0.04951059854315165</v>
       </c>
       <c r="AK289" t="n">
         <v>7.151444380572274</v>
@@ -47148,13 +47148,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM289" t="n">
-        <v>0.02840267381959001</v>
+        <v>0.02840267381959008</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.008843610540066053</v>
+        <v>0.008843610540066056</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.5123725312709416</v>
+        <v>0.5123725312709417</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47304,7 +47304,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ290" t="n">
-        <v>-0.05177635201934994</v>
+        <v>-0.05177635201935082</v>
       </c>
       <c r="AK290" t="n">
         <v>7.151307469847429</v>
@@ -47313,13 +47313,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.03189518855892823</v>
+        <v>0.03189518855892809</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.008740250954211215</v>
+        <v>0.008740250954211236</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.5303980242931245</v>
+        <v>0.5303980242931252</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47466,10 +47466,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI291" t="n">
-        <v>7.172173616645312</v>
+        <v>7.172173616645314</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.06197368836162021</v>
+        <v>-0.06197368836162287</v>
       </c>
       <c r="AK291" t="n">
         <v>7.152170779642037</v>
@@ -47478,13 +47478,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM291" t="n">
-        <v>0.03448417181877508</v>
+        <v>0.03448417181877479</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008638296330047493</v>
+        <v>0.008638296330047519</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.536400419244653</v>
+        <v>0.5364004192446541</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47634,7 +47634,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.08262387272163529</v>
+        <v>-0.08262387272163618</v>
       </c>
       <c r="AK292" t="n">
         <v>7.155242422656618</v>
@@ -47646,10 +47646,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008527848481957645</v>
+        <v>0.008527848481957647</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5479838817473677</v>
+        <v>0.5479838817473681</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47796,10 +47796,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI293" t="n">
-        <v>7.18418852599864</v>
+        <v>7.184188525998638</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.08518854888682359</v>
+        <v>-0.08518854888682181</v>
       </c>
       <c r="AK293" t="n">
         <v>7.174067278312125</v>
@@ -47808,13 +47808,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.03996026841105445</v>
+        <v>0.03996026841105382</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008497979041970659</v>
+        <v>0.008497979041970699</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.5534995516418705</v>
+        <v>0.553499551641869</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47961,10 +47961,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI294" t="n">
-        <v>7.185513015749276</v>
+        <v>7.185513015749274</v>
       </c>
       <c r="AJ294" t="n">
-        <v>-0.07571315384131694</v>
+        <v>-0.07571315384131516</v>
       </c>
       <c r="AK294" t="n">
         <v>7.175957423377739</v>
@@ -47973,13 +47973,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM294" t="n">
-        <v>0.04233079818885077</v>
+        <v>0.04233079818885083</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008432709457890229</v>
+        <v>0.008432709457890224</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5557951014363787</v>
+        <v>0.5557951014363788</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48132,19 +48132,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK295" t="n">
-        <v>7.174765662541793</v>
+        <v>7.174765662541792</v>
       </c>
       <c r="AL295" t="n">
-        <v>-0.05786569534818931</v>
+        <v>-0.05786569534818842</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.04394124299371591</v>
+        <v>0.04394124299371556</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008396387260434499</v>
+        <v>0.008396387260434506</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5565519909812464</v>
+        <v>0.5565519909812453</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48291,10 +48291,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.185932916622859</v>
+        <v>7.18593291662286</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.0141327800566966</v>
+        <v>-0.01413278005669749</v>
       </c>
       <c r="AK296" t="n">
         <v>7.172730869790855</v>
@@ -48303,13 +48303,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04590755972499789</v>
+        <v>0.04590755972499803</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008346613473328282</v>
+        <v>0.008346613473328291</v>
       </c>
       <c r="AO296" t="n">
-        <v>0.5588443644440741</v>
+        <v>0.5588443644440755</v>
       </c>
       <c r="AP296" t="n">
         <v/>
@@ -48456,10 +48456,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI297" t="n">
-        <v>7.187602005018013</v>
+        <v>7.187602005018014</v>
       </c>
       <c r="AJ297" t="n">
-        <v>-0.05810209275604983</v>
+        <v>-0.0581020927560516</v>
       </c>
       <c r="AK297" t="n">
         <v>7.168923754586179</v>
@@ -48468,10 +48468,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04658552832149703</v>
+        <v>0.04658552832149689</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008354655440128402</v>
+        <v>0.008354655440128426</v>
       </c>
       <c r="AO297" t="n">
         <v>0.5613325805619827</v>
@@ -48633,13 +48633,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04820692510781933</v>
+        <v>0.04820692510781883</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008303818071592001</v>
+        <v>0.008303818071592054</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5626464255878519</v>
+        <v>0.5626464255878516</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48798,13 +48798,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.04983084886774743</v>
+        <v>0.04983084886774771</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008251024544031704</v>
+        <v>0.008251024544031682</v>
       </c>
       <c r="AO299" t="n">
-        <v>0.5641340630354328</v>
+        <v>0.5641340630354323</v>
       </c>
       <c r="AP299" t="n">
         <v/>
@@ -48963,13 +48963,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.05170461329917111</v>
+        <v>0.05170461329917048</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008192726391276807</v>
+        <v>0.008192726391276836</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5658195968244528</v>
+        <v>0.5658195968244545</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49128,13 +49128,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.05348369580043773</v>
+        <v>0.05348369580043772</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008143044151838245</v>
+        <v>0.008143044151838252</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5671346874885959</v>
+        <v>0.5671346874885956</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49281,10 +49281,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI302" t="n">
-        <v>7.175179910580594</v>
+        <v>7.175179910580593</v>
       </c>
       <c r="AJ302" t="n">
-        <v>-0.05588002196975417</v>
+        <v>-0.05588002196975328</v>
       </c>
       <c r="AK302" t="n">
         <v>7.165699812335961</v>
@@ -49293,13 +49293,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05520982564369371</v>
+        <v>0.0552098256436935</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008124788470663676</v>
+        <v>0.008124788470663643</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5701242576280907</v>
+        <v>0.5701242576280905</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49446,10 +49446,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI303" t="n">
-        <v>7.173581841712227</v>
+        <v>7.173581841712229</v>
       </c>
       <c r="AJ303" t="n">
-        <v>-0.05428195310138761</v>
+        <v>-0.05428195310138939</v>
       </c>
       <c r="AK303" t="n">
         <v>7.162626578418298</v>
@@ -49458,13 +49458,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05644890839995315</v>
+        <v>0.05644890839995281</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008105230252153435</v>
+        <v>0.008105230252153447</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5713754740215509</v>
+        <v>0.5713754740215494</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49611,10 +49611,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.176011726611837</v>
+        <v>7.176011726611838</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.06401173805592908</v>
+        <v>-0.06401173805592997</v>
       </c>
       <c r="AK304" t="n">
         <v>7.165542054185019</v>
@@ -49623,13 +49623,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05727663218544052</v>
+        <v>0.05727663218544039</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.00812403522652648</v>
+        <v>0.008124035226526509</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.573000414744258</v>
+        <v>0.5730004147442582</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49776,10 +49776,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.17698340522191</v>
+        <v>7.176983405221908</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.07778363334080662</v>
+        <v>-0.07778363334080485</v>
       </c>
       <c r="AK305" t="n">
         <v>7.170209849598846</v>
@@ -49788,13 +49788,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05825580143844533</v>
+        <v>0.05825580143844532</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008106527117828777</v>
+        <v>0.008106527117828759</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5728585525731363</v>
+        <v>0.5728585525731367</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49941,10 +49941,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.174841035863564</v>
+        <v>7.174841035863563</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.06734095956961905</v>
+        <v>-0.06734095956961816</v>
       </c>
       <c r="AK306" t="n">
         <v>7.166925629020364</v>
@@ -49953,13 +49953,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM306" t="n">
-        <v>0.05980113395910436</v>
+        <v>0.05980113395910441</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.008056914781095353</v>
+        <v>0.008056914781095341</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.5723268395754473</v>
+        <v>0.5723268395754482</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50106,10 +50106,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.179777800337525</v>
+        <v>7.179777800337526</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.07227772404357946</v>
+        <v>-0.07227772404358035</v>
       </c>
       <c r="AK307" t="n">
         <v>7.163704513322672</v>
@@ -50121,10 +50121,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.008007544934860181</v>
+        <v>0.008007544934860184</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5724055344141883</v>
+        <v>0.5724055344141876</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50271,10 +50271,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.176651545551679</v>
+        <v>7.176651545551677</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.06915146925773374</v>
+        <v>-0.06915146925773197</v>
       </c>
       <c r="AK308" t="n">
         <v>7.163430147298699</v>
@@ -50283,13 +50283,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.06321929365037962</v>
+        <v>0.06321929365038026</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.007927773212025854</v>
+        <v>0.007927773212025837</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.572463582881384</v>
+        <v>0.5724635828813827</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50436,10 +50436,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.173279688539583</v>
+        <v>7.173279688539582</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.06577961224563733</v>
+        <v>-0.06577961224563644</v>
       </c>
       <c r="AK309" t="n">
         <v>7.158871783064204</v>
@@ -50448,13 +50448,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM309" t="n">
-        <v>0.06523048259292186</v>
+        <v>0.0652304825929222</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.007809540836127948</v>
+        <v>0.007809540836127932</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5710090561291132</v>
+        <v>0.571009056129113</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50601,10 +50601,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.168542018724481</v>
+        <v>7.168542018724479</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.06194221098522323</v>
+        <v>-0.06194221098522146</v>
       </c>
       <c r="AK310" t="n">
         <v>7.152618309751275</v>
@@ -50613,13 +50613,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.067411943409599</v>
+        <v>0.06741194340959927</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007660511838810988</v>
+        <v>0.007660511838810949</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.5694124450603424</v>
+        <v>0.5694124450603408</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50766,10 +50766,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI311" t="n">
-        <v>7.161829635752616</v>
+        <v>7.161829635752617</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.05962960447209831</v>
+        <v>-0.0596296044720992</v>
       </c>
       <c r="AK311" t="n">
         <v>7.144956229005203</v>
@@ -50778,13 +50778,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.06977835201573312</v>
+        <v>0.06977835201573281</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007516908058882096</v>
+        <v>0.007516908058882097</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5690369646398685</v>
+        <v>0.5690369646398684</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50934,7 +50934,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ312" t="n">
-        <v>-0.07699331565738099</v>
+        <v>-0.07699331565738188</v>
       </c>
       <c r="AK312" t="n">
         <v>7.140422114543136</v>
@@ -50943,13 +50943,13 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.07195366789421653</v>
+        <v>0.07195366789421676</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007394117938767417</v>
+        <v>0.007394117938767422</v>
       </c>
       <c r="AO312" t="n">
-        <v>0.5693040973288186</v>
+        <v>0.5693040973288199</v>
       </c>
       <c r="AP312" t="n">
         <v/>
@@ -51108,10 +51108,10 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.07456301989532385</v>
+        <v>0.07456301989532414</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007241314760732032</v>
+        <v>0.007241314760731996</v>
       </c>
       <c r="AO313" t="n">
         <v>0.5685877661607006</v>
@@ -51273,16 +51273,16 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.07747971887849656</v>
+        <v>0.07747971887849607</v>
       </c>
       <c r="AN314" t="n">
-        <v>0.0070901436555387</v>
+        <v>0.007090143655538702</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5681709745664083</v>
+        <v>0.5681709745664091</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.724190261446932</v>
+        <v>-1.724190261446947</v>
       </c>
       <c r="AQ314" t="n">
         <v>5</v>
@@ -51426,10 +51426,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI315" t="n">
-        <v>7.165084051386049</v>
+        <v>7.165084051386047</v>
       </c>
       <c r="AJ315" t="n">
-        <v>-0.08998410631768916</v>
+        <v>-0.08998410631768738</v>
       </c>
       <c r="AK315" t="n">
         <v>7.14582045097363</v>
@@ -51438,16 +51438,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.08000072584212846</v>
+        <v>0.08000072584212836</v>
       </c>
       <c r="AN315" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.5684087510734981</v>
+        <v>0.5684087510734968</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.931790754663661</v>
+        <v>-1.931790754663584</v>
       </c>
       <c r="AQ315" t="n">
         <v>2.459016393442623</v>
@@ -51591,10 +51591,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI316" t="n">
-        <v>7.161419741275552</v>
+        <v>7.161419741275553</v>
       </c>
       <c r="AJ316" t="n">
-        <v>-0.08971964514518138</v>
+        <v>-0.08971964514518227</v>
       </c>
       <c r="AK316" t="n">
         <v>7.155707108847959</v>
@@ -51603,16 +51603,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.08204996863507508</v>
+        <v>0.08204996863507528</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.006919462921967476</v>
+        <v>0.006919462921967468</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5672869954461468</v>
+        <v>0.5672869954461461</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.846952005518314</v>
+        <v>-1.846952005518379</v>
       </c>
       <c r="AQ316" t="n">
         <v>2.419354838709677</v>
@@ -51756,10 +51756,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.155488092579304</v>
+        <v>7.155488092579303</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.08548792091792734</v>
+        <v>-0.08548792091792645</v>
       </c>
       <c r="AK317" t="n">
         <v>7.150451326287159</v>
@@ -51768,16 +51768,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08469403553214168</v>
+        <v>0.08469403553214211</v>
       </c>
       <c r="AN317" t="n">
-        <v>0.006815201188096393</v>
+        <v>0.006815201188096372</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5663505631396779</v>
+        <v>0.5663505631396781</v>
       </c>
       <c r="AP317" t="n">
-        <v>-1.570680960734236</v>
+        <v>-1.570680960734205</v>
       </c>
       <c r="AQ317" t="n">
         <v>3.968253968253968</v>
@@ -51921,10 +51921,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.158832817363979</v>
+        <v>7.15883281736398</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.09523275404000398</v>
+        <v>-0.09523275404000575</v>
       </c>
       <c r="AK318" t="n">
         <v>7.147115644271845</v>
@@ -51933,16 +51933,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08699523504893081</v>
+        <v>0.08699523504893142</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006735083295172709</v>
+        <v>0.006735083295172689</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5654743012892969</v>
+        <v>0.5654743012892984</v>
       </c>
       <c r="AP318" t="n">
-        <v>-2.010588329611717</v>
+        <v>-2.01058832961182</v>
       </c>
       <c r="AQ318" t="n">
         <v>1.5625</v>
@@ -52086,10 +52086,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.161703459649028</v>
+        <v>7.161703459649029</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.090303294091167</v>
+        <v>-0.09030329409116788</v>
       </c>
       <c r="AK319" t="n">
         <v>7.152131804583207</v>
@@ -52098,16 +52098,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.08901512474159551</v>
+        <v>0.08901512474159586</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006668288608758136</v>
+        <v>0.006668288608758129</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5631673144521659</v>
+        <v>0.5631673144521655</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.69819382429421</v>
+        <v>-1.698193824294262</v>
       </c>
       <c r="AQ319" t="n">
         <v>2.307692307692308</v>
@@ -52251,10 +52251,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.162535384813326</v>
+        <v>7.162535384813327</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.09293527952768166</v>
+        <v>-0.09293527952768255</v>
       </c>
       <c r="AK320" t="n">
         <v>7.157753883768605</v>
@@ -52263,16 +52263,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.09116436352661951</v>
+        <v>0.09116436352661936</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006624805625172231</v>
+        <v>0.006624805625172246</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5612585549312774</v>
+        <v>0.5612585549312785</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.775154010940289</v>
+        <v>-1.775154010940337</v>
       </c>
       <c r="AQ320" t="n">
         <v>3.03030303030303</v>
@@ -52416,10 +52416,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.166818450294679</v>
+        <v>7.166818450294681</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.0958183511125501</v>
+        <v>-0.09581835111255188</v>
       </c>
       <c r="AK321" t="n">
         <v>7.158620349112049</v>
@@ -52428,16 +52428,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.09320704864741254</v>
+        <v>0.09320704864741212</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006594358041710158</v>
+        <v>0.006594358041710186</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5590514368572466</v>
+        <v>0.5590514368572459</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.856211366608896</v>
+        <v>-1.856211366608981</v>
       </c>
       <c r="AQ321" t="n">
         <v>1.492537313432836</v>
@@ -52581,10 +52581,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.157691007010206</v>
+        <v>7.157691007010208</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.0943908742587416</v>
+        <v>-0.09439087425874337</v>
       </c>
       <c r="AK322" t="n">
         <v>7.164942158928604</v>
@@ -52593,16 +52593,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.09491020692123933</v>
+        <v>0.09491020692123982</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006562900445417311</v>
+        <v>0.006562900445417306</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5551825155208145</v>
+        <v>0.5551825155208129</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.731418901810068</v>
+        <v>-1.731418901810147</v>
       </c>
       <c r="AQ322" t="n">
         <v>2.941176470588236</v>
@@ -52746,10 +52746,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.151776426431621</v>
+        <v>7.15177642643162</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.08777629673191356</v>
+        <v>-0.08777629673191267</v>
       </c>
       <c r="AK323" t="n">
         <v>7.154764404811184</v>
@@ -52758,16 +52758,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.097046810505102</v>
+        <v>0.0970468105051025</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006523984583215639</v>
+        <v>0.006523984583215632</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5522992358254805</v>
+        <v>0.5522992358254815</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.377058849156416</v>
+        <v>-1.377058849156369</v>
       </c>
       <c r="AQ323" t="n">
         <v>6.521739130434782</v>
@@ -52911,10 +52911,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.15099240431968</v>
+        <v>7.150992404319682</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.09309245238486596</v>
+        <v>-0.09309245238486774</v>
       </c>
       <c r="AK324" t="n">
         <v>7.150261540163492</v>
@@ -52923,16 +52923,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.09904197982498698</v>
+        <v>0.09904197982498671</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006505848878330736</v>
+        <v>0.006505848878330779</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5500699492277152</v>
+        <v>0.5500699492277157</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.593774347668997</v>
+        <v>-1.593774347669072</v>
       </c>
       <c r="AQ324" t="n">
         <v>4.285714285714286</v>
@@ -53076,10 +53076,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI325" t="n">
-        <v>7.147140093605204</v>
+        <v>7.147140093605207</v>
       </c>
       <c r="AJ325" t="n">
-        <v>-0.09314019278733277</v>
+        <v>-0.09314019278733543</v>
       </c>
       <c r="AK325" t="n">
         <v>7.148879230661717</v>
@@ -53088,16 +53088,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.1013300516539148</v>
+        <v>0.1013300516539142</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006479631055951007</v>
+        <v>0.006479631055951091</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5478993564899665</v>
+        <v>0.5478993564899672</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.556872644832726</v>
+        <v>-1.556872644832838</v>
       </c>
       <c r="AQ325" t="n">
         <v>3.52112676056338</v>
@@ -53247,22 +53247,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK326" t="n">
-        <v>7.145816711184184</v>
+        <v>7.145816711184185</v>
       </c>
       <c r="AL326" t="n">
-        <v>-0.09881677984873516</v>
+        <v>-0.09881677984873605</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.1033273874042088</v>
+        <v>0.1033273874042092</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006468712737497662</v>
+        <v>0.006468712737497656</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5455500876237902</v>
+        <v>0.5455500876237913</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.633583092819398</v>
+        <v>-1.633583092819383</v>
       </c>
       <c r="AQ326" t="n">
         <v>2.083333333333333</v>
@@ -53409,7 +53409,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.1028262052267701</v>
+        <v>-0.102826205226771</v>
       </c>
       <c r="AK327" t="n">
         <v>7.139092738717567</v>
@@ -53418,16 +53418,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.1056457020972507</v>
+        <v>0.1056457020972505</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006435041090934165</v>
+        <v>0.006435041090934217</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5433399026839665</v>
+        <v>0.5433399026839674</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.906283391421584</v>
+        <v>-1.906283391421605</v>
       </c>
       <c r="AQ327" t="n">
         <v>2.73972602739726</v>
@@ -53574,7 +53574,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ328" t="n">
-        <v>-0.099096096614959</v>
+        <v>-0.09909609661495811</v>
       </c>
       <c r="AK328" t="n">
         <v>7.140479586010682</v>
@@ -53583,16 +53583,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.10768023901916</v>
+        <v>0.1076802390191602</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006405465077205547</v>
+        <v>0.006405465077205527</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5402459241219614</v>
+        <v>0.5402459241219618</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.688157425632867</v>
+        <v>-1.688157425632812</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.702702702702703</v>
@@ -53736,10 +53736,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI329" t="n">
-        <v>7.145743344370562</v>
+        <v>7.145743344370558</v>
       </c>
       <c r="AJ329" t="n">
-        <v>-0.1052431803385794</v>
+        <v>-0.1052431803385758</v>
       </c>
       <c r="AK329" t="n">
         <v>7.136632587022158</v>
@@ -53748,16 +53748,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1100130126862077</v>
+        <v>0.1100130126862084</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006366554765990282</v>
+        <v>0.00636655476599019</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5375708073661647</v>
+        <v>0.5375708073661639</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.905796083052539</v>
+        <v>-1.905796083052374</v>
       </c>
       <c r="AQ329" t="n">
         <v>2.666666666666667</v>
@@ -53913,16 +53913,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.1122475627674583</v>
+        <v>0.1122475627674581</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006337265512462553</v>
+        <v>0.00633726551246258</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5341613739773245</v>
+        <v>0.5341613739773232</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.570534804148656</v>
+        <v>-1.570534804148652</v>
       </c>
       <c r="AQ330" t="n">
         <v>3.289473684210526</v>
@@ -54066,10 +54066,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI331" t="n">
-        <v>7.142519733033009</v>
+        <v>7.14251973303301</v>
       </c>
       <c r="AJ331" t="n">
-        <v>-0.1016195026252946</v>
+        <v>-0.1016195026252955</v>
       </c>
       <c r="AK331" t="n">
         <v>7.135172643569136</v>
@@ -54078,16 +54078,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1146509166068179</v>
+        <v>0.114650916606818</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006337163869517243</v>
+        <v>0.006337163869517234</v>
       </c>
       <c r="AO331" t="n">
-        <v>0.5319767312874306</v>
+        <v>0.5319767312874311</v>
       </c>
       <c r="AP331" t="n">
-        <v>-1.662697443788121</v>
+        <v>-1.662697443788154</v>
       </c>
       <c r="AQ331" t="n">
         <v>2.597402597402597</v>
@@ -54243,16 +54243,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1171965158426952</v>
+        <v>0.1171965158426948</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006367653503792481</v>
+        <v>0.00636765350379247</v>
       </c>
       <c r="AO332" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP332" t="n">
-        <v>-2.115533294915587</v>
+        <v>-2.115533294915579</v>
       </c>
       <c r="AQ332" t="n">
         <v>1.282051282051282</v>
@@ -54396,10 +54396,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI333" t="n">
-        <v>7.140851085964109</v>
+        <v>7.140851085964112</v>
       </c>
       <c r="AJ333" t="n">
-        <v>-0.1128512080344217</v>
+        <v>-0.1128512080344244</v>
       </c>
       <c r="AK333" t="n">
         <v>7.142783913375006</v>
@@ -54408,16 +54408,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.119227205240256</v>
+        <v>0.1192272052402563</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006383133038709798</v>
+        <v>0.00638313303870985</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5243060286247103</v>
+        <v>0.5243060286247104</v>
       </c>
       <c r="AP333" t="n">
-        <v>-2.007643048538807</v>
+        <v>-2.007643048538904</v>
       </c>
       <c r="AQ333" t="n">
         <v>2.531645569620253</v>
@@ -54561,10 +54561,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI334" t="n">
-        <v>7.139245392969567</v>
+        <v>7.139245392969565</v>
       </c>
       <c r="AJ334" t="n">
-        <v>-0.1112455150398795</v>
+        <v>-0.1112455150398777</v>
       </c>
       <c r="AK334" t="n">
         <v>7.141836927013541</v>
@@ -54573,16 +54573,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1211746327267789</v>
+        <v>0.1211746327267792</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006404909068509476</v>
+        <v>0.006404909068509461</v>
       </c>
       <c r="AO334" t="n">
-        <v>0.5185318197199045</v>
+        <v>0.518531819719905</v>
       </c>
       <c r="AP334" t="n">
-        <v>-1.884116354524714</v>
+        <v>-1.884116354524633</v>
       </c>
       <c r="AQ334" t="n">
         <v>3.75</v>
@@ -54726,10 +54726,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI335" t="n">
-        <v>7.136520216281903</v>
+        <v>7.136520216281902</v>
       </c>
       <c r="AJ335" t="n">
-        <v>-0.108520338352216</v>
+        <v>-0.1085203383522142</v>
       </c>
       <c r="AK335" t="n">
         <v>7.13958125183462</v>
@@ -54738,16 +54738,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM335" t="n">
-        <v>0.1228335954516147</v>
+        <v>0.1228335954516143</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006430223802628449</v>
+        <v>0.006430223802628476</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.5122974965428477</v>
+        <v>0.5122974965428486</v>
       </c>
       <c r="AP335" t="n">
-        <v>-1.727677144982902</v>
+        <v>-1.727677144982826</v>
       </c>
       <c r="AQ335" t="n">
         <v>4.938271604938271</v>
@@ -54906,13 +54906,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006430805642792636</v>
+        <v>0.006430805642792618</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.5056597011855208</v>
+        <v>0.5056597011855207</v>
       </c>
       <c r="AP336" t="n">
-        <v>-2.479703864912859</v>
+        <v>-2.479703864912851</v>
       </c>
       <c r="AQ336" t="n">
         <v>1.219512195121951</v>
@@ -55056,10 +55056,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.136562857934749</v>
+        <v>7.13656285793475</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.140462909051692</v>
+        <v>-0.1404629090516929</v>
       </c>
       <c r="AK337" t="n">
         <v>7.132705938528055</v>
@@ -55071,13 +55071,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006419568115912044</v>
+        <v>0.006419568115912051</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.4979995576252224</v>
+        <v>0.4979995576252233</v>
       </c>
       <c r="AP337" t="n">
-        <v>-2.739065656385232</v>
+        <v>-2.739065656385255</v>
       </c>
       <c r="AQ337" t="n">
         <v>1.204819277108434</v>
@@ -55221,10 +55221,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI338" t="n">
-        <v>7.135435320996258</v>
+        <v>7.135435320996254</v>
       </c>
       <c r="AJ338" t="n">
-        <v>-0.1393353721132016</v>
+        <v>-0.1393353721131971</v>
       </c>
       <c r="AK338" t="n">
         <v>7.134470034900207</v>
@@ -55233,16 +55233,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM338" t="n">
-        <v>0.1290155516631957</v>
+        <v>0.1290155516631951</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006423940675024581</v>
+        <v>0.006423940675024553</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.489456156051701</v>
+        <v>0.4894561560517011</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.570509620796308</v>
+        <v>-2.570509620796153</v>
       </c>
       <c r="AQ338" t="n">
         <v>2.976190476190476</v>
@@ -55386,10 +55386,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.135221482968309</v>
+        <v>7.135221482968312</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.1391215340852527</v>
+        <v>-0.1391215340852554</v>
       </c>
       <c r="AK339" t="n">
         <v>7.133435115388912</v>
@@ -55398,16 +55398,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM339" t="n">
-        <v>0.1313692321875789</v>
+        <v>0.1313692321875792</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006422605647444513</v>
+        <v>0.006422605647444502</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4811392039904447</v>
+        <v>0.4811392039904442</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.453683672072927</v>
+        <v>-2.453683672073018</v>
       </c>
       <c r="AQ339" t="n">
         <v>4.117647058823529</v>
@@ -55551,10 +55551,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI340" t="n">
-        <v>7.129120131622726</v>
+        <v>7.129120131622732</v>
       </c>
       <c r="AJ340" t="n">
-        <v>-0.1360199653019256</v>
+        <v>-0.1360199653019309</v>
       </c>
       <c r="AK340" t="n">
         <v>7.132510325395203</v>
@@ -55563,16 +55563,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1334873867685099</v>
+        <v>0.1334873867685108</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006388619079873509</v>
+        <v>0.006388619079873553</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.4724960612931043</v>
+        <v>0.4724960612931048</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.259259404734778</v>
+        <v>-2.259259404734945</v>
       </c>
       <c r="AQ340" t="n">
         <v>5.232558139534884</v>
@@ -55728,16 +55728,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1357975915367747</v>
+        <v>0.1357975915367741</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006324213907675097</v>
+        <v>0.006324213907675122</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4647750649852552</v>
+        <v>0.4647750649852558</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.336135860701614</v>
+        <v>-2.336135860701599</v>
       </c>
       <c r="AQ341" t="n">
         <v>2.873563218390804</v>
@@ -55881,10 +55881,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI342" t="n">
-        <v>7.122818285283529</v>
+        <v>7.122818285283532</v>
       </c>
       <c r="AJ342" t="n">
-        <v>-0.1394184172720543</v>
+        <v>-0.1394184172720578</v>
       </c>
       <c r="AK342" t="n">
         <v>7.123271418608565</v>
@@ -55893,16 +55893,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1386638579210687</v>
+        <v>0.1386638579210689</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006222091828703702</v>
+        <v>0.006222091828703747</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4565264017486783</v>
+        <v>0.4565264017486775</v>
       </c>
       <c r="AP342" t="n">
-        <v>-2.206385751326466</v>
+        <v>-2.206385751326561</v>
       </c>
       <c r="AQ342" t="n">
         <v>3.977272727272728</v>
@@ -56058,16 +56058,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM343" t="n">
-        <v>0.1423176752089984</v>
+        <v>0.1423176752089981</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.006093783709292283</v>
+        <v>0.006093783709292289</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4497199830569224</v>
+        <v>0.4497199830569214</v>
       </c>
       <c r="AP343" t="n">
-        <v>-1.826228951530581</v>
+        <v>-1.826228951530564</v>
       </c>
       <c r="AQ343" t="n">
         <v>8.988764044943821</v>
@@ -56211,10 +56211,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI344" t="n">
-        <v>7.133160404869088</v>
+        <v>7.13316040486909</v>
       </c>
       <c r="AJ344" t="n">
-        <v>-0.1496604010543905</v>
+        <v>-0.1496604010543923</v>
       </c>
       <c r="AK344" t="n">
         <v>7.117219286120759</v>
@@ -56226,13 +56226,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.005984113522022494</v>
+        <v>0.005984113522022499</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4438783751010233</v>
+        <v>0.4438783751010228</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.38913520545355</v>
+        <v>-2.389135205453581</v>
       </c>
       <c r="AQ344" t="n">
         <v>7.777777777777777</v>
@@ -56376,10 +56376,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI345" t="n">
-        <v>7.12965322071209</v>
+        <v>7.129653220712091</v>
       </c>
       <c r="AJ345" t="n">
-        <v>-0.1524531894315722</v>
+        <v>-0.152453189431573</v>
       </c>
       <c r="AK345" t="n">
         <v>7.126254605494273</v>
@@ -56388,16 +56388,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1503893187551748</v>
+        <v>0.1503893187551739</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.005963146506628741</v>
+        <v>0.005963146506628762</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4412018736247373</v>
+        <v>0.441201873624737</v>
       </c>
       <c r="AP345" t="n">
-        <v>-2.383015193652481</v>
+        <v>-2.383015193652484</v>
       </c>
       <c r="AQ345" t="n">
         <v>7.692307692307692</v>
@@ -56541,10 +56541,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.128380415829728</v>
+        <v>7.128380415829729</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.1552802304354408</v>
+        <v>-0.1552802304354417</v>
       </c>
       <c r="AK346" t="n">
         <v>7.124321202568002</v>
@@ -56553,16 +56553,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM346" t="n">
-        <v>0.1546287435667592</v>
+        <v>0.1546287435667593</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.005975981199024843</v>
+        <v>0.005975981199024824</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4385827444686599</v>
+        <v>0.43858274446866</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.377284613910015</v>
+        <v>-2.377284613910016</v>
       </c>
       <c r="AQ346" t="n">
         <v>7.608695652173913</v>
@@ -56706,10 +56706,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI347" t="n">
-        <v>7.124429161493117</v>
+        <v>7.124429161493114</v>
       </c>
       <c r="AJ347" t="n">
-        <v>-0.1469291996400894</v>
+        <v>-0.1469291996400868</v>
       </c>
       <c r="AK347" t="n">
         <v>7.121152072356459</v>
@@ -56718,16 +56718,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1587808126513012</v>
+        <v>0.1587808126513008</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.00589922161993145</v>
+        <v>0.005899221619931436</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4336499747757657</v>
+        <v>0.4336499747757655</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.068462761629601</v>
+        <v>-2.068462761629508</v>
       </c>
       <c r="AQ347" t="n">
         <v>16.12903225806452</v>
@@ -56883,16 +56883,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1636493008978488</v>
+        <v>0.1636493008978486</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005897856672615054</v>
+        <v>0.005897856672615022</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.434304834398872</v>
+        <v>0.4343048343988722</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.382353247202333</v>
+        <v>-2.382353247202315</v>
       </c>
       <c r="AQ348" t="n">
         <v>13.82978723404255</v>
@@ -57036,10 +57036,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.141397967314147</v>
+        <v>7.141397967314151</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1753978872055049</v>
+        <v>-0.1753978872055084</v>
       </c>
       <c r="AK349" t="n">
         <v>7.12802266215534</v>
@@ -57048,16 +57048,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1676675897666615</v>
+        <v>0.1676675897666616</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.005952601612807557</v>
+        <v>0.005952601612807589</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4322693842687806</v>
+        <v>0.4322693842687804</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.670736759395985</v>
+        <v>-2.670736759396056</v>
       </c>
       <c r="AQ349" t="n">
         <v>12.63157894736842</v>
@@ -57201,10 +57201,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI350" t="n">
-        <v>7.140412492855504</v>
+        <v>7.140412492855501</v>
       </c>
       <c r="AJ350" t="n">
-        <v>-0.1723124219021352</v>
+        <v>-0.1723124219021317</v>
       </c>
       <c r="AK350" t="n">
         <v>7.137738577466652</v>
@@ -57213,16 +57213,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1710383543493657</v>
+        <v>0.1710383543493662</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.006068444256835448</v>
+        <v>0.00606844425683546</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.4285062718639565</v>
+        <v>0.4285062718639572</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.486991520523586</v>
+        <v>-2.486991520523476</v>
       </c>
       <c r="AQ350" t="n">
         <v>19.79166666666667</v>
@@ -57366,10 +57366,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.138020503721587</v>
+        <v>7.138020503721584</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.169920432768218</v>
+        <v>-0.1699204327682153</v>
       </c>
       <c r="AK351" t="n">
         <v>7.13663078035759</v>
@@ -57378,16 +57378,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.176195682434215</v>
+        <v>0.1761956824342154</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.006402952059750722</v>
+        <v>0.006402952059750703</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4374093872433962</v>
+        <v>0.4374093872433956</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.340555038223798</v>
+        <v>-2.340555038223719</v>
       </c>
       <c r="AQ351" t="n">
         <v>19.58762886597938</v>
@@ -57531,28 +57531,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI352" t="n">
-        <v>7.136830620687384</v>
+        <v>7.136830620687383</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1769307183436339</v>
+        <v>-0.1769307183436331</v>
       </c>
       <c r="AK352" t="n">
-        <v>7.14004901784002</v>
+        <v>7.140049017840021</v>
       </c>
       <c r="AL352" t="n">
-        <v>-0.1801491154962704</v>
+        <v>-0.1801491154962713</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1796308914905975</v>
+        <v>0.1796308914905974</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.006948414844703821</v>
+        <v>0.006948414844703805</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4458727441769479</v>
+        <v>0.4458727441769483</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.430939046003628</v>
+        <v>-2.430939046003598</v>
       </c>
       <c r="AQ352" t="n">
         <v>17.85714285714286</v>
@@ -57692,10 +57692,10 @@
         <v/>
       </c>
       <c r="AI353" t="n">
-        <v>7.133638579266565</v>
+        <v>7.13363857926656</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.1699387616090942</v>
+        <v>-0.1699387616090897</v>
       </c>
       <c r="AK353" t="n">
         <v>7.13798584867198</v>
@@ -57704,16 +57704,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.1829391475229931</v>
+        <v>0.1829391475229935</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.007602047321544403</v>
+        <v>0.00760204732154433</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4545618931940824</v>
+        <v>0.4545618931940826</v>
       </c>
       <c r="AP353" t="n">
-        <v>-2.187248633823291</v>
+        <v>-2.187248633823181</v>
       </c>
       <c r="AQ353" t="n">
         <v>27.02020202020202</v>
@@ -57857,10 +57857,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.12640946890857</v>
+        <v>7.126409468908567</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1538094856932375</v>
+        <v>-0.1538094856932348</v>
       </c>
       <c r="AK354" t="n">
         <v>7.138565167526504</v>
@@ -57869,16 +57869,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1834764543657148</v>
+        <v>0.1834764543657157</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.007712839302340374</v>
+        <v>0.007712839302340297</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4511257152112026</v>
+        <v>0.4511257152112024</v>
       </c>
       <c r="AP354" t="n">
-        <v>-1.751542964205509</v>
+        <v>-1.751542964205447</v>
       </c>
       <c r="AQ354" t="n">
         <v>22.68686868686869</v>
@@ -58022,10 +58022,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI355" t="n">
-        <v>7.110999512759045</v>
+        <v>7.110999512759042</v>
       </c>
       <c r="AJ355" t="n">
-        <v>-0.1383995295437126</v>
+        <v>-0.1383995295437099</v>
       </c>
       <c r="AK355" t="n">
         <v>7.137040595974374</v>
@@ -58034,16 +58034,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1869739626316104</v>
+        <v>0.1869739626316108</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.00835460951998479</v>
+        <v>0.008354609519984808</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4618871834350119</v>
+        <v>0.4618871834350127</v>
       </c>
       <c r="AP355" t="n">
-        <v>-1.355171190637946</v>
+        <v>-1.355171190637885</v>
       </c>
       <c r="AQ355" t="n">
         <v>16.91584158415841</v>
@@ -58199,16 +58199,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1901371272406391</v>
+        <v>0.1901371272406383</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.008787529863310189</v>
+        <v>0.008787529863310259</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4631528842621211</v>
+        <v>0.4631528842621208</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.392347055140759</v>
+        <v>-1.392347055140763</v>
       </c>
       <c r="AQ356" t="n">
         <v>10.3329450592118</v>
@@ -58352,10 +58352,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI357" t="n">
-        <v>7.10229338126412</v>
+        <v>7.102293381264122</v>
       </c>
       <c r="AJ357" t="n">
-        <v>-0.1477931828998624</v>
+        <v>-0.1477931828998642</v>
       </c>
       <c r="AK357" t="n">
         <v>7.113436809075056</v>
@@ -58364,16 +58364,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1939456835457532</v>
+        <v>0.193945683545753</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.009306466714917722</v>
+        <v>0.009306466714917755</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4650211967660294</v>
+        <v>0.4650211967660295</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.536709546819528</v>
+        <v>-1.536709546819574</v>
       </c>
       <c r="AQ357" t="n">
         <v>11.22215876641919</v>
@@ -58529,16 +58529,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.1968971496416331</v>
+        <v>0.1968971496416338</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.009915270508004642</v>
+        <v>0.009915270508004639</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4658112293095933</v>
+        <v>0.4658112293095935</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.310548373380441</v>
+        <v>-1.310548373380444</v>
       </c>
       <c r="AQ358" t="n">
         <v>11.56646751306945</v>
@@ -58694,16 +58694,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.2001574773810679</v>
+        <v>0.200157477381068</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.01045224758824684</v>
+        <v>0.01045224758824685</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4652001227613064</v>
+        <v>0.4652001227613058</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.57572647047327</v>
+        <v>-1.575726470473273</v>
       </c>
       <c r="AQ359" t="n">
         <v>5.242673992673993</v>
@@ -58847,10 +58847,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI360" t="n">
-        <v>7.112155432918446</v>
+        <v>7.112155432918444</v>
       </c>
       <c r="AJ360" t="n">
-        <v>-0.1611552192953987</v>
+        <v>-0.1611552192953969</v>
       </c>
       <c r="AK360" t="n">
         <v>7.115439870473561</v>
@@ -58859,16 +58859,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.2059164257597553</v>
+        <v>0.2059164257597547</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.01095806236007055</v>
+        <v>0.0109580623600705</v>
       </c>
       <c r="AO360" t="n">
-        <v>0.4647071558511969</v>
+        <v>0.4647071558511972</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.774265403257154</v>
+        <v>-1.774265403257117</v>
       </c>
       <c r="AQ360" t="n">
         <v>6.639712488769093</v>
@@ -59024,16 +59024,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2103846028094628</v>
+        <v>0.2103846028094625</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.01138655624224677</v>
+        <v>0.01138655624224671</v>
       </c>
       <c r="AO361" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.802693641697059</v>
+        <v>-1.802693641697064</v>
       </c>
       <c r="AQ361" t="n">
         <v>11.29430435549286</v>
@@ -59177,10 +59177,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI362" t="n">
-        <v>7.110775793344653</v>
+        <v>7.110775793344654</v>
       </c>
       <c r="AJ362" t="n">
-        <v>-0.1730759985753663</v>
+        <v>-0.1730759985753672</v>
       </c>
       <c r="AK362" t="n">
         <v>7.127056499711662</v>
@@ -59189,16 +59189,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2137349114935569</v>
+        <v>0.2137349114935566</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01184277521890661</v>
+        <v>0.0118427752189066</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4573024605378193</v>
+        <v>0.4573024605378192</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.969292156016974</v>
+        <v>-1.969292156016998</v>
       </c>
       <c r="AQ362" t="n">
         <v>12.60384215991693</v>
@@ -59354,16 +59354,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2192999169256238</v>
+        <v>0.2192999169256231</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01242692746354282</v>
+        <v>0.01242692746354283</v>
       </c>
       <c r="AO363" t="n">
-        <v>0.4593518446085588</v>
+        <v>0.4593518446085587</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.523646799099699</v>
+        <v>-1.523646799099702</v>
       </c>
       <c r="AQ363" t="n">
         <v>14.30513081889229</v>
@@ -59507,28 +59507,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI364" t="n">
-        <v>7.095070446253633</v>
+        <v>7.095070446253632</v>
       </c>
       <c r="AJ364" t="n">
-        <v>-0.1572705156811232</v>
+        <v>-0.1572705156811223</v>
       </c>
       <c r="AK364" t="n">
-        <v>7.099084322920755</v>
+        <v>7.099084322920754</v>
       </c>
       <c r="AL364" t="n">
-        <v>-0.1612843923482448</v>
+        <v>-0.1612843923482439</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2273791016644669</v>
+        <v>0.2273791016644665</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01301934706839999</v>
+        <v>0.01301934706840001</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4655241261491886</v>
+        <v>0.4655241261491888</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.557042908539596</v>
+        <v>-1.55704290853958</v>
       </c>
       <c r="AQ364" t="n">
         <v>12.34361968306922</v>
@@ -59672,10 +59672,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI365" t="n">
-        <v>7.077412848446851</v>
+        <v>7.077412848446856</v>
       </c>
       <c r="AJ365" t="n">
-        <v>-0.1386129903535895</v>
+        <v>-0.138612990353594</v>
       </c>
       <c r="AK365" t="n">
         <v>7.107752072150756</v>
@@ -59684,16 +59684,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2346680713248289</v>
+        <v>0.2346680713248287</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01366280940279216</v>
+        <v>0.01366280940279221</v>
       </c>
       <c r="AO365" t="n">
-        <v>0.4682122340216202</v>
+        <v>0.4682122340216205</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.122352298790636</v>
+        <v>-1.122352298790738</v>
       </c>
       <c r="AQ365" t="n">
         <v>19.89352989352989</v>
@@ -59837,10 +59837,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.067855559671527</v>
+        <v>7.067855559671529</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.1458556283360775</v>
+        <v>-0.1458556283360801</v>
       </c>
       <c r="AK366" t="n">
         <v>7.100856094477853</v>
@@ -59849,16 +59849,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2404731763378842</v>
+        <v>0.2404731763378833</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01427110593278799</v>
+        <v>0.01427110593278805</v>
       </c>
       <c r="AO366" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.271236148417158</v>
+        <v>-1.271236148417218</v>
       </c>
       <c r="AQ366" t="n">
         <v>19.29295366795367</v>
@@ -60002,10 +60002,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.081794385763164</v>
+        <v>7.081794385763168</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1711942003688769</v>
+        <v>-0.1711942003688813</v>
       </c>
       <c r="AK367" t="n">
         <v>7.090764621929079</v>
@@ -60014,16 +60014,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2453259423721931</v>
+        <v>0.2453259423721924</v>
       </c>
       <c r="AN367" t="n">
-        <v>0.01502424352484369</v>
+        <v>0.01502424352484376</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4756424387980298</v>
+        <v>0.4756424387980304</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.808118861364563</v>
+        <v>-1.808118861364658</v>
       </c>
       <c r="AQ367" t="n">
         <v>15.60524652338812</v>
@@ -60167,10 +60167,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.068234493406102</v>
+        <v>7.068234493406101</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1557345887735337</v>
+        <v>-0.1557345887735329</v>
       </c>
       <c r="AK368" t="n">
         <v>7.110983013755962</v>
@@ -60179,16 +60179,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2481172514763508</v>
+        <v>0.2481172514763511</v>
       </c>
       <c r="AN368" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO368" t="n">
-        <v>0.4781214750573159</v>
+        <v>0.4781214750573156</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.442667685740082</v>
+        <v>-1.442667685740059</v>
       </c>
       <c r="AQ368" t="n">
         <v>19.42244993013507</v>
@@ -60332,28 +60332,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.047011693433886</v>
+        <v>7.04701169343388</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1469114622632315</v>
+        <v>-0.1469114622632253</v>
       </c>
       <c r="AK369" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL369" t="n">
-        <v>-0.1936362268489642</v>
+        <v>-0.1936362268489633</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2517176519946896</v>
+        <v>0.2517176519946887</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01672959897123732</v>
+        <v>0.01672959897123727</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.482044795280705</v>
+        <v>0.4820447952807055</v>
       </c>
       <c r="AP369" t="n">
-        <v>-1.232706276738699</v>
+        <v>-1.232706276738561</v>
       </c>
       <c r="AQ369" t="n">
         <v>18.77955758962624</v>
@@ -60497,28 +60497,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.043635211714482</v>
+        <v>7.043635211714486</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.135635219343877</v>
+        <v>-0.1356352193438806</v>
       </c>
       <c r="AK370" t="n">
-        <v>7.069112439760902</v>
+        <v>7.069112439760901</v>
       </c>
       <c r="AL370" t="n">
-        <v>-0.1611124473902965</v>
+        <v>-0.1611124473902956</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2568291528619773</v>
+        <v>0.2568291528619769</v>
       </c>
       <c r="AN370" t="n">
-        <v>0.01758784222749221</v>
+        <v>0.0175878422274923</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4888256589627545</v>
+        <v>0.488825658962754</v>
       </c>
       <c r="AP370" t="n">
-        <v>-0.974252753824209</v>
+        <v>-0.9742527538242869</v>
       </c>
       <c r="AQ370" t="n">
         <v>24.22413793103448</v>
@@ -60662,10 +60662,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.045320696769622</v>
+        <v>7.04532069676962</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1373207043990163</v>
+        <v>-0.1373207043990146</v>
       </c>
       <c r="AK371" t="n">
         <v>7.067486653848666</v>
@@ -60674,16 +60674,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2611441025487395</v>
+        <v>0.2611441025487396</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.01863884916361525</v>
+        <v>0.01863884916361523</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.4958891106408185</v>
+        <v>0.4958891106408189</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.002942367458539</v>
+        <v>-1.0029423674585</v>
       </c>
       <c r="AQ371" t="n">
         <v>21.86486884762747</v>
@@ -60827,10 +60827,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.052957186540217</v>
+        <v>7.052957186540212</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.1449571941696117</v>
+        <v>-0.1449571941696064</v>
       </c>
       <c r="AK372" t="n">
         <v>7.066060765041626</v>
@@ -60839,16 +60839,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2646928033319798</v>
+        <v>0.2646928033319788</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.01961447184998982</v>
+        <v>0.0196144718499898</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.4990325267638059</v>
+        <v>0.4990325267638065</v>
       </c>
       <c r="AP372" t="n">
-        <v>-1.160646340175406</v>
+        <v>-1.16064634017529</v>
       </c>
       <c r="AQ372" t="n">
         <v>19.14747211357381</v>
@@ -60992,28 +60992,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.055218091951101</v>
+        <v>7.055218091951103</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1472180995804955</v>
+        <v>-0.1472180995804973</v>
       </c>
       <c r="AK373" t="n">
-        <v>7.064646745753511</v>
+        <v>7.06464674575351</v>
       </c>
       <c r="AL373" t="n">
-        <v>-0.1566467533829057</v>
+        <v>-0.1566467533829048</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2692457951306195</v>
+        <v>0.2692457951306194</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.02045122459205889</v>
+        <v>0.02045122459205891</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.5009265659871953</v>
+        <v>0.5009265659871951</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.198258571472453</v>
+        <v>-1.198258571472493</v>
       </c>
       <c r="AQ373" t="n">
         <v>18.14912405640222</v>
@@ -61157,10 +61157,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI374" t="n">
-        <v>7.050463258619342</v>
+        <v>7.050463258619345</v>
       </c>
       <c r="AJ374" t="n">
-        <v>-0.1423631304455135</v>
+        <v>-0.1423631304455171</v>
       </c>
       <c r="AK374" t="n">
         <v>7.063274589921972</v>
@@ -61169,16 +61169,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM374" t="n">
-        <v>0.2738618637550985</v>
+        <v>0.2738618637550991</v>
       </c>
       <c r="AN374" t="n">
-        <v>0.02103732430364852</v>
+        <v>0.02103732430364855</v>
       </c>
       <c r="AO374" t="n">
-        <v>0.5007948901071727</v>
+        <v>0.5007948901071723</v>
       </c>
       <c r="AP374" t="n">
-        <v>-1.081000849094784</v>
+        <v>-1.081000849094862</v>
       </c>
       <c r="AQ374" t="n">
         <v>22.6015406162465</v>
@@ -61495,16 +61495,16 @@
         <v/>
       </c>
       <c r="AM376" t="n">
-        <v>0.280344119587675</v>
+        <v>0.2803441195876753</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02230845224183686</v>
+        <v>0.02230845224183688</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5036776407221306</v>
+        <v>0.5036776407221312</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.235576310663277</v>
+        <v>-1.235576310663276</v>
       </c>
       <c r="AQ376" t="n">
         <v>24.79338842975207</v>
@@ -61648,10 +61648,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI377" t="n">
-        <v>7.056824809597053</v>
+        <v>7.056824809597052</v>
       </c>
       <c r="AJ377" t="n">
-        <v>-0.1737247767906567</v>
+        <v>-0.1737247767906558</v>
       </c>
       <c r="AK377" t="n">
         <v>7.071238163852278</v>
@@ -61660,16 +61660,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM377" t="n">
-        <v>0.2841407798055449</v>
+        <v>0.2841407798055452</v>
       </c>
       <c r="AN377" t="n">
-        <v>0.02276542233315987</v>
+        <v>0.02276542233315985</v>
       </c>
       <c r="AO377" t="n">
-        <v>0.5036956996297977</v>
+        <v>0.5036956996297983</v>
       </c>
       <c r="AP377" t="n">
-        <v>-1.730428938919804</v>
+        <v>-1.730428938919785</v>
       </c>
       <c r="AQ377" t="n">
         <v>21.72131147540984</v>
@@ -61813,10 +61813,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI378" t="n">
-        <v>7.04726592259491</v>
+        <v>7.047265922594908</v>
       </c>
       <c r="AJ378" t="n">
-        <v>-0.1780656929501347</v>
+        <v>-0.178065692950133</v>
       </c>
       <c r="AK378" t="n">
         <v>7.075283303194255</v>
@@ -61825,16 +61825,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM378" t="n">
-        <v>0.2869603504542605</v>
+        <v>0.2869603504542598</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02324367830537832</v>
+        <v>0.02324367830537833</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.5029697249741727</v>
+        <v>0.5029697249741724</v>
       </c>
       <c r="AP378" t="n">
-        <v>-1.793610726664527</v>
+        <v>-1.793610726664491</v>
       </c>
       <c r="AQ378" t="n">
         <v>10.56910569105691</v>
@@ -61978,10 +61978,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.030237372659574</v>
+        <v>7.030237372659579</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.189337428354154</v>
+        <v>-0.1893374283541593</v>
       </c>
       <c r="AK379" t="n">
         <v>7.061088020066238</v>
@@ -61990,16 +61990,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2909556153842325</v>
+        <v>0.2909556153842324</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02343150180192449</v>
+        <v>0.02343150180192457</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.501187497763653</v>
+        <v>0.5011874977636526</v>
       </c>
       <c r="AP379" t="n">
-        <v>-1.996113206815226</v>
+        <v>-1.996113206815337</v>
       </c>
       <c r="AQ379" t="n">
         <v>2.419354838709677</v>
@@ -62143,10 +62143,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.074556523891909</v>
+        <v>7.074556523891907</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.2166563812222311</v>
+        <v>-0.2166563812222293</v>
       </c>
       <c r="AK380" t="n">
         <v>7.045371831199247</v>
@@ -62155,16 +62155,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2963660759601011</v>
+        <v>0.2963660759601009</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02388105320115907</v>
+        <v>0.02388105320115906</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.5011837436137521</v>
+        <v>0.5011837436137511</v>
       </c>
       <c r="AP380" t="n">
-        <v>-2.503727930712481</v>
+        <v>-2.503727930712443</v>
       </c>
       <c r="AQ380" t="n">
         <v>14.8</v>
@@ -62308,10 +62308,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI381" t="n">
-        <v>7.103552248295395</v>
+        <v>7.103552248295403</v>
       </c>
       <c r="AJ381" t="n">
-        <v>-0.2215522788129736</v>
+        <v>-0.2215522788129807</v>
       </c>
       <c r="AK381" t="n">
         <v>7.078406423284397</v>
@@ -62320,16 +62320,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.29984079129971</v>
+        <v>0.2998407912997099</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02427773372157399</v>
+        <v>0.02427773372157407</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.4964684575356704</v>
+        <v>0.4964684575356701</v>
       </c>
       <c r="AP381" t="n">
-        <v>-2.528080341989682</v>
+        <v>-2.528080341989817</v>
       </c>
       <c r="AQ381" t="n">
         <v>19.44444444444444</v>
@@ -62485,16 +62485,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.3035220749319825</v>
+        <v>0.3035220749319821</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02465824743687012</v>
+        <v>0.02465824743687013</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.4899948718309226</v>
+        <v>0.4899948718309223</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.236682718707529</v>
+        <v>-2.236682718707521</v>
       </c>
       <c r="AQ382" t="n">
         <v>23.22834645669291</v>
@@ -62638,10 +62638,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.12777959440025</v>
+        <v>7.127779594400253</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2307797584322326</v>
+        <v>-0.2307797584322353</v>
       </c>
       <c r="AK383" t="n">
         <v>7.110202206771168</v>
@@ -62650,16 +62650,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.3056770963992281</v>
+        <v>0.3056770963992276</v>
       </c>
       <c r="AN383" t="n">
-        <v>0.02512392944114572</v>
+        <v>0.02512392944114575</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.4836004785809395</v>
+        <v>0.48360047858094</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.574000190382281</v>
+        <v>-2.574000190382322</v>
       </c>
       <c r="AQ383" t="n">
         <v>22.65625</v>
@@ -62803,28 +62803,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI384" t="n">
-        <v>7.117424820782309</v>
+        <v>7.117424820782308</v>
       </c>
       <c r="AJ384" t="n">
-        <v>-0.2204249848142918</v>
+        <v>-0.2204249848142901</v>
       </c>
       <c r="AK384" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL384" t="n">
-        <v>-0.2182210070512509</v>
+        <v>-0.21822100705125</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3083414575758074</v>
+        <v>0.3083414575758079</v>
       </c>
       <c r="AN384" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.474982443940299</v>
+        <v>0.4749824439402989</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.311094238470707</v>
+        <v>-2.311094238470664</v>
       </c>
       <c r="AQ384" t="n">
         <v>25.1937984496124</v>
@@ -62968,10 +62968,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.116315246651977</v>
+        <v>7.116315246651979</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.2198151360257565</v>
+        <v>-0.2198151360257583</v>
       </c>
       <c r="AK385" t="n">
         <v>7.112470209890858</v>
@@ -62980,16 +62980,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3094443575020182</v>
+        <v>0.3094443575020188</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.0257875072203187</v>
+        <v>0.02578750722031873</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4671039145039241</v>
+        <v>0.467103914503924</v>
       </c>
       <c r="AP385" t="n">
-        <v>-2.244976743889282</v>
+        <v>-2.244976743889306</v>
       </c>
       <c r="AQ385" t="n">
         <v>25</v>
@@ -63133,28 +63133,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.109165799046384</v>
+        <v>7.109165799046382</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.1981660241135224</v>
+        <v>-0.1981660241135206</v>
       </c>
       <c r="AK386" t="n">
-        <v>7.105086649080124</v>
+        <v>7.105086649080123</v>
       </c>
       <c r="AL386" t="n">
-        <v>-0.1940868741472626</v>
+        <v>-0.1940868741472617</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3112159059696454</v>
+        <v>0.3112159059696449</v>
       </c>
       <c r="AN386" t="n">
-        <v>0.02619128791084346</v>
+        <v>0.02619128791084347</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.4597800393113445</v>
+        <v>0.4597800393113443</v>
       </c>
       <c r="AP386" t="n">
-        <v>-1.803328015553823</v>
+        <v>-1.803328015553783</v>
       </c>
       <c r="AQ386" t="n">
         <v>26.33587786259542</v>
@@ -63298,10 +63298,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.140476658697598</v>
+        <v>7.14047665869759</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.2639765289978913</v>
+        <v>-0.2639765289978833</v>
       </c>
       <c r="AK387" t="n">
         <v>7.107009848336411</v>
@@ -63310,16 +63310,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3120213667410843</v>
+        <v>0.3120213667410841</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.02660872919284657</v>
+        <v>0.02660872919284651</v>
       </c>
       <c r="AO387" t="n">
-        <v>0.4527828726277016</v>
+        <v>0.4527828726277021</v>
       </c>
       <c r="AP387" t="n">
-        <v>-2.929950705628223</v>
+        <v>-2.929950705628078</v>
       </c>
       <c r="AQ387" t="n">
         <v>18.93939393939394</v>
@@ -63463,10 +63463,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI388" t="n">
-        <v>7.192104266103097</v>
+        <v>7.192104266103096</v>
       </c>
       <c r="AJ388" t="n">
-        <v>-0.3266042928059782</v>
+        <v>-0.3266042928059765</v>
       </c>
       <c r="AK388" t="n">
         <v>7.130667004235951</v>
@@ -63475,16 +63475,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3119580514589064</v>
+        <v>0.3119580514589062</v>
       </c>
       <c r="AN388" t="n">
-        <v>0.02723917591229313</v>
+        <v>0.02723917591229311</v>
       </c>
       <c r="AO388" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP388" t="n">
-        <v>-3.825906053379875</v>
+        <v>-3.825906053379849</v>
       </c>
       <c r="AQ388" t="n">
         <v>21.80451127819549</v>
@@ -63640,7 +63640,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3060770546706492</v>
+        <v>0.3060770546706496</v>
       </c>
       <c r="AN389" t="n">
         <v>0.02737088803905663</v>
@@ -63649,7 +63649,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP389" t="n">
-        <v>-3.691517232479182</v>
+        <v>-3.691517232479185</v>
       </c>
       <c r="AQ389" t="n">
         <v>19.40298507462687</v>
@@ -63793,10 +63793,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.16410590848237</v>
+        <v>7.164105908482372</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.2680058642318812</v>
+        <v>-0.2680058642318839</v>
       </c>
       <c r="AK390" t="n">
         <v>7.162206823443969</v>
@@ -63805,16 +63805,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3021518080029227</v>
+        <v>0.3021518080029217</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02724691784252931</v>
+        <v>0.02724691784252936</v>
       </c>
       <c r="AO390" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP390" t="n">
-        <v>-2.569798150288845</v>
+        <v>-2.569798150288888</v>
       </c>
       <c r="AQ390" t="n">
         <v>23.7037037037037</v>
@@ -63958,10 +63958,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI391" t="n">
-        <v>7.165713254747866</v>
+        <v>7.165713254747862</v>
       </c>
       <c r="AJ391" t="n">
-        <v>-0.2102131288628559</v>
+        <v>-0.2102131288628524</v>
       </c>
       <c r="AK391" t="n">
         <v>7.141021818380439</v>
@@ -63970,16 +63970,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.3004913268435098</v>
+        <v>0.3004913268435102</v>
       </c>
       <c r="AN391" t="n">
-        <v>0.02739193077523433</v>
+        <v>0.02739193077523432</v>
       </c>
       <c r="AO391" t="n">
-        <v>0.3752726470948202</v>
+        <v>0.3752726470948199</v>
       </c>
       <c r="AP391" t="n">
-        <v>-1.61822820385486</v>
+        <v>-1.618228203854805</v>
       </c>
       <c r="AQ391" t="n">
         <v>30.51470588235294</v>
@@ -64123,10 +64123,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.208249532027229</v>
+        <v>7.208249532027231</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.3219494450521312</v>
+        <v>-0.321949445052133</v>
       </c>
       <c r="AK392" t="n">
         <v>7.146296571548195</v>
@@ -64135,16 +64135,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.2982197220770054</v>
+        <v>0.2982197220770058</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02742417953210363</v>
+        <v>0.02742417953210373</v>
       </c>
       <c r="AO392" t="n">
-        <v>0.3625782951332472</v>
+        <v>0.3625782951332475</v>
       </c>
       <c r="AP392" t="n">
-        <v>-3.256089008048478</v>
+        <v>-3.256089008048506</v>
       </c>
       <c r="AQ392" t="n">
         <v>25.18248175182482</v>
@@ -64288,28 +64288,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.193412187855718</v>
+        <v>7.193412187855726</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.3208121092729543</v>
+        <v>-0.3208121092729623</v>
       </c>
       <c r="AK393" t="n">
-        <v>7.176497065376474</v>
+        <v>7.176497065376473</v>
       </c>
       <c r="AL393" t="n">
-        <v>-0.3038969867937107</v>
+        <v>-0.3038969867937098</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.2910761841041076</v>
+        <v>0.2910761841041086</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02685747952387152</v>
+        <v>0.02685747952387156</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3370674577034428</v>
+        <v>0.3370674577034442</v>
       </c>
       <c r="AP393" t="n">
-        <v>-3.110043925481275</v>
+        <v>-3.110043925481386</v>
       </c>
       <c r="AQ393" t="n">
         <v>26.08695652173913</v>
@@ -64453,10 +64453,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.227115602342048</v>
+        <v>7.227115602342041</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3273157785810614</v>
+        <v>-0.3273157785810543</v>
       </c>
       <c r="AK394" t="n">
         <v>7.185469892270627</v>
@@ -64465,16 +64465,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2812269987605887</v>
+        <v>0.281226998760588</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02697180537422167</v>
+        <v>0.0269718053742217</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.3136210223326478</v>
+        <v>0.3136210223326474</v>
       </c>
       <c r="AP394" t="n">
-        <v>-3.082654657593006</v>
+        <v>-3.082654657592904</v>
       </c>
       <c r="AQ394" t="n">
         <v>26.97841726618705</v>
@@ -64618,10 +64618,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.187163192389372</v>
+        <v>7.187163192389367</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3014629665592938</v>
+        <v>-0.3014629665592885</v>
       </c>
       <c r="AK395" t="n">
         <v>7.208338760609084</v>
@@ -64630,16 +64630,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2681836981576122</v>
+        <v>0.2681836981576121</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02658698789673936</v>
+        <v>0.02658698789673927</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.285908150945263</v>
+        <v>0.2859081509452629</v>
       </c>
       <c r="AP395" t="n">
-        <v>-2.631500409705249</v>
+        <v>-2.631500409705178</v>
       </c>
       <c r="AQ395" t="n">
         <v>27.85714285714285</v>
@@ -64783,10 +64783,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.214951953115591</v>
+        <v>7.214951953115579</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.334951838674673</v>
+        <v>-0.3349518386746606</v>
       </c>
       <c r="AK396" t="n">
         <v>7.186200492654655</v>
@@ -64795,16 +64795,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2591628297636744</v>
+        <v>0.2591628297636748</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02587977479594339</v>
+        <v>0.02587977479594331</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.266108201492412</v>
+        <v>0.2661082014924122</v>
       </c>
       <c r="AP396" t="n">
-        <v>-2.991802545616129</v>
+        <v>-2.991802545615974</v>
       </c>
       <c r="AQ396" t="n">
         <v>27.30496453900709</v>
@@ -64948,10 +64948,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI397" t="n">
-        <v>7.197430004066455</v>
+        <v>7.197430004066453</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.305630077308642</v>
+        <v>-0.3056300773086402</v>
       </c>
       <c r="AK397" t="n">
         <v>7.201835396295348</v>
@@ -64960,16 +64960,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2466333883508319</v>
+        <v>0.2466333883508324</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.0247654344950328</v>
+        <v>0.02476543449503272</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.2401258754735003</v>
+        <v>0.2401258754735008</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.521834653469916</v>
+        <v>-2.521834653469907</v>
       </c>
       <c r="AQ397" t="n">
         <v>26.05633802816902</v>
@@ -65116,25 +65116,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.3291230670577869</v>
+        <v>-0.3291230670577878</v>
       </c>
       <c r="AK398" t="n">
-        <v>7.179650721554484</v>
+        <v>7.179650721554483</v>
       </c>
       <c r="AL398" t="n">
-        <v>-0.2786506986663007</v>
+        <v>-0.2786506986662998</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2377807761788571</v>
+        <v>0.2377807761788565</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.02334020127887793</v>
+        <v>0.02334020127887796</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.2171758918683914</v>
+        <v>0.2171758918683913</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.750558250506315</v>
+        <v>-2.750558250506341</v>
       </c>
       <c r="AQ398" t="n">
         <v>26.57342657342658</v>
@@ -65278,10 +65278,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.20852803773295</v>
+        <v>7.208528037732954</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.2978281933725988</v>
+        <v>-0.2978281933726024</v>
       </c>
       <c r="AK399" t="n">
         <v>7.206616000051887</v>
@@ -65290,16 +65290,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2255544515066686</v>
+        <v>0.2255544515066683</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.0206724522626571</v>
+        <v>0.0206724522626572</v>
       </c>
       <c r="AO399" t="n">
-        <v>0.1898019966940717</v>
+        <v>0.1898019966940708</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.288775912977311</v>
+        <v>-2.288775912977366</v>
       </c>
       <c r="AQ399" t="n">
         <v>16.31944444444444</v>
@@ -65443,10 +65443,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI400" t="n">
-        <v>7.19880309223843</v>
+        <v>7.198803092238432</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.287202979323391</v>
+        <v>-0.2872029793233928</v>
       </c>
       <c r="AK400" t="n">
         <v>7.18051307481679</v>
@@ -65455,16 +65455,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2150441262650612</v>
+        <v>0.2150441262650616</v>
       </c>
       <c r="AN400" t="n">
-        <v>0.01774895516388914</v>
+        <v>0.0177489551638892</v>
       </c>
       <c r="AO400" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP400" t="n">
-        <v>-2.110552313023714</v>
+        <v>-2.110552313023745</v>
       </c>
       <c r="AQ400" t="n">
         <v>14.82758620689655</v>
@@ -65608,10 +65608,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.172424239411004</v>
+        <v>7.172424239411002</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2608241264959652</v>
+        <v>-0.2608241264959634</v>
       </c>
       <c r="AK401" t="n">
         <v>7.16705299197773</v>
@@ -65620,16 +65620,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.205433651489446</v>
+        <v>0.2054336514894463</v>
       </c>
       <c r="AN401" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO401" t="n">
-        <v>0.1417286033373026</v>
+        <v>0.1417286033373033</v>
       </c>
       <c r="AP401" t="n">
-        <v>-1.749216029070048</v>
+        <v>-1.749216029070033</v>
       </c>
       <c r="AQ401" t="n">
         <v>18.83561643835617</v>
@@ -65773,10 +65773,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.163756390646672</v>
+        <v>7.163756390646673</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.2695565424716229</v>
+        <v>-0.2695565424716238</v>
       </c>
       <c r="AK402" t="n">
         <v>7.153532751444382</v>
@@ -65785,16 +65785,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.1941661953581061</v>
+        <v>0.1941661953581056</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.01312004055850013</v>
+        <v>0.01312004055850015</v>
       </c>
       <c r="AO402" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP402" t="n">
-        <v>-1.831906238706977</v>
+        <v>-1.831906238706995</v>
       </c>
       <c r="AQ402" t="n">
         <v>25.17006802721088</v>
@@ -65938,10 +65938,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.158063699621738</v>
+        <v>7.158063699621736</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2875636118837006</v>
+        <v>-0.2875636118836988</v>
       </c>
       <c r="AK403" t="n">
         <v>7.150669702211316</v>
@@ -65950,16 +65950,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.1839494937266881</v>
+        <v>0.183949493726688</v>
       </c>
       <c r="AN403" t="n">
-        <v>0.01194074338472806</v>
+        <v>0.01194074338472802</v>
       </c>
       <c r="AO403" t="n">
-        <v>0.1107549805175829</v>
+        <v>0.110754980517583</v>
       </c>
       <c r="AP403" t="n">
-        <v>-2.02216299447262</v>
+        <v>-2.022162994472606</v>
       </c>
       <c r="AQ403" t="n">
         <v>13.17567567567568</v>
@@ -66103,10 +66103,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.157435208014563</v>
+        <v>7.157435208014565</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.272335320166663</v>
+        <v>-0.2723353201666647</v>
       </c>
       <c r="AK404" t="n">
         <v>7.140926852093823</v>
@@ -66115,16 +66115,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.1753430411611933</v>
+        <v>0.1753430411611928</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.00971765423202034</v>
+        <v>0.009717654232020439</v>
       </c>
       <c r="AO404" t="n">
-        <v>0.09620195025422695</v>
+        <v>0.09620195025422784</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.806494995112574</v>
+        <v>-1.806494995112603</v>
       </c>
       <c r="AQ404" t="n">
         <v>21.14093959731544</v>
@@ -66268,10 +66268,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.150386811340072</v>
+        <v>7.15038681134007</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2679867754819174</v>
+        <v>-0.2679867754819156</v>
       </c>
       <c r="AK405" t="n">
         <v>7.142886401315924</v>
@@ -66280,16 +66280,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1664838398737872</v>
+        <v>0.1664838398737869</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.008089376136153875</v>
+        <v>0.008089376136153925</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.0848962688609296</v>
+        <v>0.08489626886092971</v>
       </c>
       <c r="AP405" t="n">
-        <v>-1.729347037888961</v>
+        <v>-1.729347037888946</v>
       </c>
       <c r="AQ405" t="n">
         <v>20.66666666666666</v>
@@ -66433,10 +66433,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.137094841694645</v>
+        <v>7.137094841694642</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.2547949416397133</v>
+        <v>-0.2547949416397106</v>
       </c>
       <c r="AK406" t="n">
         <v>7.137840883333127</v>
@@ -66445,16 +66445,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1571907956492611</v>
+        <v>0.1571907956492617</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.006581947594647974</v>
+        <v>0.006581947594647856</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.07412699588694804</v>
+        <v>0.07412699588694738</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.550057084078563</v>
+        <v>-1.550057084078537</v>
       </c>
       <c r="AQ406" t="n">
         <v>20.86092715231788</v>
@@ -66598,10 +66598,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.123391234435203</v>
+        <v>7.1233912344352</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2666912908927221</v>
+        <v>-0.2666912908927195</v>
       </c>
       <c r="AK407" t="n">
         <v>7.12862724785568</v>
@@ -66610,16 +66610,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1487097707294961</v>
+        <v>0.1487097707294973</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.005441006961990014</v>
+        <v>0.005441006961990058</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.06531270865715677</v>
+        <v>0.06531270865715666</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.673584650939876</v>
+        <v>-1.673584650939852</v>
       </c>
       <c r="AQ407" t="n">
         <v>14.47368421052632</v>
@@ -66763,10 +66763,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.11600731855288</v>
+        <v>7.116007318552882</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2873072529400869</v>
+        <v>-0.2873072529400895</v>
       </c>
       <c r="AK408" t="n">
         <v>7.118961040191934</v>
@@ -66775,16 +66775,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM408" t="n">
-        <v>0.1409513724492178</v>
+        <v>0.1409513724492179</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.005644373135176822</v>
+        <v>0.005644373135176906</v>
       </c>
       <c r="AO408" t="n">
-        <v>0.05986577613532174</v>
+        <v>0.0598657761353214</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.894040927372167</v>
+        <v>-1.894040927372207</v>
       </c>
       <c r="AQ408" t="n">
         <v>10.13071895424837</v>
@@ -66928,10 +66928,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI409" t="n">
-        <v>7.115262454587763</v>
+        <v>7.11526245458776</v>
       </c>
       <c r="AJ409" t="n">
-        <v>-0.2838625369852235</v>
+        <v>-0.2838625369852208</v>
       </c>
       <c r="AK409" t="n">
         <v>7.113208458946866</v>
@@ -66943,13 +66943,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005618445165739616</v>
+        <v>0.005618445165739529</v>
       </c>
       <c r="AO409" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.826335379416645</v>
+        <v>-1.826335379416621</v>
       </c>
       <c r="AQ409" t="n">
         <v>8.766233766233768</v>
@@ -67105,16 +67105,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM410" t="n">
-        <v>0.1248427026608149</v>
+        <v>0.1248427026608145</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005050876420738246</v>
+        <v>0.005050876420738303</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.04692762159458042</v>
+        <v>0.04692762159457986</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.74106842125536</v>
+        <v>-1.741068421255368</v>
       </c>
       <c r="AQ410" t="n">
         <v>13.87096774193548</v>
@@ -67258,10 +67258,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.100218718661557</v>
+        <v>7.100218718661558</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2699188643829924</v>
+        <v>-0.2699188643829933</v>
       </c>
       <c r="AK411" t="n">
         <v>7.105971078464224</v>
@@ -67273,13 +67273,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005209570180715356</v>
+        <v>0.00520957018071537</v>
       </c>
       <c r="AO411" t="n">
-        <v>0.0421970173931332</v>
+        <v>0.04219701739313308</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.618633410158811</v>
+        <v>-1.618633410158829</v>
       </c>
       <c r="AQ411" t="n">
         <v>15.06410256410257</v>
@@ -67423,10 +67423,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI412" t="n">
-        <v>7.097935875054437</v>
+        <v>7.097935875054439</v>
       </c>
       <c r="AJ412" t="n">
-        <v>-0.2822358208857363</v>
+        <v>-0.2822358208857381</v>
       </c>
       <c r="AK412" t="n">
         <v>7.101361129315627</v>
@@ -67435,16 +67435,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM412" t="n">
-        <v>0.1117472247487875</v>
+        <v>0.1117472247487876</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005385102682029907</v>
+        <v>0.005385102682029925</v>
       </c>
       <c r="AO412" t="n">
-        <v>0.03866992220359</v>
+        <v>0.03866992220359033</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.740701375623203</v>
+        <v>-1.740701375623231</v>
       </c>
       <c r="AQ412" t="n">
         <v>14.01273885350319</v>
@@ -67588,10 +67588,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI413" t="n">
-        <v>7.097978821692022</v>
+        <v>7.097978821692021</v>
       </c>
       <c r="AJ413" t="n">
-        <v>-0.2799789819093075</v>
+        <v>-0.2799789819093057</v>
       </c>
       <c r="AK413" t="n">
         <v>7.099648834314064</v>
@@ -67600,16 +67600,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM413" t="n">
-        <v>0.1065475925362033</v>
+        <v>0.1065475925362025</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.005956926407440957</v>
+        <v>0.005956926407441003</v>
       </c>
       <c r="AO413" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.693149677356166</v>
+        <v>-1.693149677356153</v>
       </c>
       <c r="AQ413" t="n">
         <v>13.92405063291139</v>
@@ -67765,16 +67765,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.1013724682419977</v>
+        <v>0.1013724682419976</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.006126167203105798</v>
+        <v>0.006126167203105847</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.03348722035246332</v>
+        <v>0.03348722035246277</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.53041582738988</v>
+        <v>-1.530415827389887</v>
       </c>
       <c r="AQ414" t="n">
         <v>22.64150943396226</v>
@@ -67918,10 +67918,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI415" t="n">
-        <v>7.087097940453345</v>
+        <v>7.087097940453343</v>
       </c>
       <c r="AJ415" t="n">
-        <v>-0.2700980281913825</v>
+        <v>-0.2700980281913798</v>
       </c>
       <c r="AK415" t="n">
         <v>7.090805518999606</v>
@@ -67930,16 +67930,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.09919462776856321</v>
+        <v>0.09919462776856289</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.006113943880485972</v>
+        <v>0.006113943880485968</v>
       </c>
       <c r="AO415" t="n">
-        <v>0.03204155062895153</v>
+        <v>0.03204155062895098</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.545171215177022</v>
+        <v>-1.545171215176998</v>
       </c>
       <c r="AQ415" t="n">
         <v>17.5</v>
@@ -68095,16 +68095,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.097507502547015</v>
+        <v>0.09750750254701511</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.005510714664730507</v>
+        <v>0.005510714664730422</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.03001455024934374</v>
+        <v>0.03001455024934274</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.604216011107125</v>
+        <v>-1.604216011107132</v>
       </c>
       <c r="AQ416" t="n">
         <v>14.28571428571428</v>
@@ -68260,16 +68260,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.09380549503386901</v>
+        <v>0.09380549503386949</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.004784904607979881</v>
+        <v>0.004784904607979855</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.02699383492044782</v>
+        <v>0.02699383492044827</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.561369277734914</v>
+        <v>-1.561369277734921</v>
       </c>
       <c r="AQ417" t="n">
         <v>17.90123456790123</v>
@@ -68413,10 +68413,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI418" t="n">
-        <v>7.097145375663951</v>
+        <v>7.097145375663948</v>
       </c>
       <c r="AJ418" t="n">
-        <v>-0.2729452223131208</v>
+        <v>-0.2729452223131181</v>
       </c>
       <c r="AK418" t="n">
         <v>7.093828611034739</v>
@@ -68425,16 +68425,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.08945254406056438</v>
+        <v>0.08945254406056392</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.004001520125414798</v>
+        <v>0.004001520125414807</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.02385555423225116</v>
+        <v>0.02385555423225172</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.527328912556631</v>
+        <v>-1.527328912556609</v>
       </c>
       <c r="AQ418" t="n">
         <v>22.08588957055215</v>
@@ -68578,10 +68578,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI419" t="n">
-        <v>7.088227962421951</v>
+        <v>7.088227962421954</v>
       </c>
       <c r="AJ419" t="n">
-        <v>-0.262227748798904</v>
+        <v>-0.2622277487989066</v>
       </c>
       <c r="AK419" t="n">
         <v>7.092951699003613</v>
@@ -68590,16 +68590,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.07912491692886899</v>
+        <v>0.07912491692886864</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.003813743757049903</v>
+        <v>0.003813743757049957</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.01902803623666316</v>
+        <v>0.01902803623666371</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.392918498873579</v>
+        <v>-1.392918498873616</v>
       </c>
       <c r="AQ419" t="n">
         <v>35.0609756097561</v>
@@ -68743,10 +68743,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.082675656384673</v>
+        <v>7.082675656384675</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2467758265201709</v>
+        <v>-0.2467758265201727</v>
       </c>
       <c r="AK420" t="n">
         <v>7.085940899278786</v>
@@ -68755,16 +68755,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.07019093860911668</v>
+        <v>0.07019093860911679</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.003788844982403339</v>
+        <v>0.003788844982403293</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.01530727852465064</v>
+        <v>0.0153072785246503</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.208804870503794</v>
+        <v>-1.208804870503819</v>
       </c>
       <c r="AQ420" t="n">
         <v>33.03030303030303</v>
@@ -68908,10 +68908,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.082585232341567</v>
+        <v>7.082585232341569</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.2597850728872215</v>
+        <v>-0.2597850728872233</v>
       </c>
       <c r="AK421" t="n">
         <v>7.080231185021037</v>
@@ -68920,16 +68920,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.0607230145131474</v>
+        <v>0.06072301451314636</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.003218097337044118</v>
+        <v>0.003218097337044184</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.01127031184523342</v>
+        <v>0.01127031184523331</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.344380622119975</v>
+        <v>-1.34438062212</v>
       </c>
       <c r="AQ421" t="n">
         <v>33.13253012048193</v>
@@ -69073,10 +69073,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.082752176397555</v>
+        <v>7.082752176397554</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2453522168333464</v>
+        <v>-0.2453522168333455</v>
       </c>
       <c r="AK422" t="n">
         <v>7.078545045220129</v>
@@ -69085,16 +69085,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.04987769893955558</v>
+        <v>0.04987769893955601</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.002647769861786137</v>
+        <v>0.002647769861786034</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.00755590738572276</v>
+        <v>0.007555907385723093</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.173134633900218</v>
+        <v>-1.173134633900213</v>
       </c>
       <c r="AQ422" t="n">
         <v>34.73053892215569</v>
@@ -69238,10 +69238,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI423" t="n">
-        <v>7.073418742129174</v>
+        <v>7.073418742129173</v>
       </c>
       <c r="AJ423" t="n">
-        <v>-0.2359186467617427</v>
+        <v>-0.2359186467617418</v>
       </c>
       <c r="AK423" t="n">
         <v>7.075576762908686</v>
@@ -69250,16 +69250,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.03723342047483359</v>
+        <v>0.03723342047483347</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.0007434096776329363</v>
+        <v>0.0007434096776329864</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.003691827899839573</v>
+        <v>0.003691827899840794</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.060081682130245</v>
+        <v>-1.060081682130239</v>
       </c>
       <c r="AQ423" t="n">
         <v>37.20238095238095</v>
@@ -69415,16 +69415,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.02391394499985428</v>
+        <v>0.02391394499985489</v>
       </c>
       <c r="AN424" t="n">
-        <v>0.0004638728584110997</v>
+        <v>0.0004638728584110585</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.00150427765126282</v>
+        <v>0.001504277651263042</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.099947050574542</v>
+        <v>-1.099947050574547</v>
       </c>
       <c r="AQ424" t="n">
         <v>34.9112426035503</v>
@@ -69568,10 +69568,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI425" t="n">
-        <v>7.061175551975939</v>
+        <v>7.06117555197594</v>
       </c>
       <c r="AJ425" t="n">
-        <v>-0.2336756854903435</v>
+        <v>-0.2336756854903443</v>
       </c>
       <c r="AK425" t="n">
         <v>7.061105294515807</v>
@@ -69580,16 +69580,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM425" t="n">
-        <v>0.01023096587809661</v>
+        <v>0.01023096587809607</v>
       </c>
       <c r="AN425" t="n">
-        <v>-0.0001641525470544823</v>
+        <v>-0.0001641525470544615</v>
       </c>
       <c r="AO425" t="n">
-        <v>0.0002530929795961923</v>
+        <v>0.000253092979595082</v>
       </c>
       <c r="AP425" t="n">
-        <v>-1.021405570334845</v>
+        <v>-1.021405570334859</v>
       </c>
       <c r="AQ425" t="n">
         <v>40</v>
@@ -69745,16 +69745,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM426" t="n">
-        <v>-0.001349940557734956</v>
+        <v>-0.001349940557734529</v>
       </c>
       <c r="AN426" t="n">
-        <v>-0.001242569541730382</v>
+        <v>-0.001242569541730301</v>
       </c>
       <c r="AO426" t="n">
-        <v>9.828375502929365e-05</v>
+        <v>9.828375502973774e-05</v>
       </c>
       <c r="AP426" t="n">
-        <v>-0.9252791364203169</v>
+        <v>-0.9252791364203211</v>
       </c>
       <c r="AQ426" t="n">
         <v>40.35087719298245</v>
@@ -69898,10 +69898,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI427" t="n">
-        <v>7.051845784111939</v>
+        <v>7.051845784111937</v>
       </c>
       <c r="AJ427" t="n">
-        <v>-0.2217457246026617</v>
+        <v>-0.22174572460266</v>
       </c>
       <c r="AK427" t="n">
         <v>7.04924004450221</v>
@@ -69910,16 +69910,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM427" t="n">
-        <v>-0.01245927794565087</v>
+        <v>-0.0124592779456514</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.002690846636687106</v>
+        <v>-0.002690846636687166</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.0009149443224345521</v>
+        <v>0.000914944322433886</v>
       </c>
       <c r="AP427" t="n">
-        <v>-0.8775280003086806</v>
+        <v>-0.8775280003086646</v>
       </c>
       <c r="AQ427" t="n">
         <v>37.2093023255814</v>
@@ -70063,10 +70063,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI428" t="n">
-        <v>7.044932512363691</v>
+        <v>7.044932512363692</v>
       </c>
       <c r="AJ428" t="n">
-        <v>-0.2339326420633983</v>
+        <v>-0.2339326420633991</v>
       </c>
       <c r="AK428" t="n">
         <v>7.044607485549974</v>
@@ -70075,16 +70075,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.02351974718911197</v>
+        <v>-0.0235197471891116</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.003286981705062079</v>
+        <v>-0.003286981705062081</v>
       </c>
       <c r="AO428" t="n">
-        <v>0.002235402288773947</v>
+        <v>0.002235402288773058</v>
       </c>
       <c r="AP428" t="n">
-        <v>-1.008882750685935</v>
+        <v>-1.00888275068595</v>
       </c>
       <c r="AQ428" t="n">
         <v>35.26011560693642</v>
@@ -70228,10 +70228,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.041380724566422</v>
+        <v>7.04138072456642</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2399805399350745</v>
+        <v>-0.2399805399350727</v>
       </c>
       <c r="AK429" t="n">
         <v>7.036677431055121</v>
@@ -70240,16 +70240,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.03604973348542533</v>
+        <v>-0.03604973348542571</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.003896888881646653</v>
+        <v>-0.003896888881646666</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.004508577134016534</v>
+        <v>0.004508577134016423</v>
       </c>
       <c r="AP429" t="n">
-        <v>-1.070346391470265</v>
+        <v>-1.07034639147025</v>
       </c>
       <c r="AQ429" t="n">
         <v>27.87356321839081</v>
@@ -70393,10 +70393,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI430" t="n">
-        <v>7.031781164871437</v>
+        <v>7.031781164871438</v>
       </c>
       <c r="AJ430" t="n">
-        <v>-0.2312812487947769</v>
+        <v>-0.2312812487947777</v>
       </c>
       <c r="AK430" t="n">
         <v>7.031531243279009</v>
@@ -70405,16 +70405,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.0496421115884523</v>
+        <v>-0.04964211158845258</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.003622848094475932</v>
+        <v>-0.003622848094475877</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.007358432861332531</v>
+        <v>0.007358432861333086</v>
       </c>
       <c r="AP430" t="n">
-        <v>-0.9670051132634342</v>
+        <v>-0.9670051132634485</v>
       </c>
       <c r="AQ430" t="n">
         <v>35.42857142857143</v>
@@ -70570,16 +70570,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.06336633742876464</v>
+        <v>-0.06336633742876532</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.00383222203166729</v>
+        <v>-0.003832222031667326</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.0113935335626284</v>
+        <v>0.01139353356262962</v>
       </c>
       <c r="AP431" t="n">
-        <v>-0.8967551965613164</v>
+        <v>-0.8967551965613205</v>
       </c>
       <c r="AQ431" t="n">
         <v>36.07954545454545</v>
@@ -70723,10 +70723,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.012358254068223</v>
+        <v>7.012358254068221</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.220358437173692</v>
+        <v>-0.2203584371736902</v>
       </c>
       <c r="AK432" t="n">
         <v>7.010266108789461</v>
@@ -70735,16 +70735,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.07815930192347351</v>
+        <v>-0.07815930192347212</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.0037302018478894</v>
+        <v>-0.003730201847889384</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.01669360800688513</v>
+        <v>0.01669360800688602</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.8353051695135095</v>
+        <v>-0.8353051695134933</v>
       </c>
       <c r="AQ432" t="n">
         <v>35.31073446327683</v>
@@ -70888,10 +70888,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI433" t="n">
-        <v>7.001516536947593</v>
+        <v>7.001516536947591</v>
       </c>
       <c r="AJ433" t="n">
-        <v>-0.2107164423431005</v>
+        <v>-0.2107164423430987</v>
       </c>
       <c r="AK433" t="n">
         <v>7.003692382618654</v>
@@ -70900,16 +70900,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.09225745624393369</v>
+        <v>-0.09225745624393285</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.003729646461095512</v>
+        <v>-0.003729646461095566</v>
       </c>
       <c r="AO433" t="n">
-        <v>0.02283737241168637</v>
+        <v>0.02283737241168682</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.7234583812261211</v>
+        <v>-0.723458381226105</v>
       </c>
       <c r="AQ433" t="n">
         <v>39.8876404494382</v>
@@ -71053,10 +71053,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI434" t="n">
-        <v>6.98285303226683</v>
+        <v>6.982853032266831</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.1977530490514976</v>
+        <v>-0.1977530490514985</v>
       </c>
       <c r="AK434" t="n">
         <v>6.994908837140057</v>
@@ -71065,16 +71065,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.1040956648961724</v>
+        <v>-0.1040956648961739</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.004775368000139335</v>
+        <v>-0.004775368000139281</v>
       </c>
       <c r="AO434" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.5749259873546715</v>
+        <v>-0.5749259873546847</v>
       </c>
       <c r="AQ434" t="n">
         <v>41.06145251396648</v>
@@ -71218,10 +71218,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI435" t="n">
-        <v>6.976537964100197</v>
+        <v>6.976537964100195</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.1673381540721204</v>
+        <v>-0.1673381540721186</v>
       </c>
       <c r="AK435" t="n">
         <v>6.976048621620001</v>
@@ -71230,16 +71230,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.1171809788132883</v>
+        <v>-0.1171809788132892</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.006568629287185546</v>
+        <v>-0.006568629287185491</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.03914952746580425</v>
+        <v>0.03914952746580436</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.2301445167791662</v>
+        <v>-0.2301445167791489</v>
       </c>
       <c r="AQ435" t="n">
         <v>48.88888888888889</v>
@@ -71386,7 +71386,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ436" t="n">
-        <v>-0.1582257113591101</v>
+        <v>-0.1582257113591092</v>
       </c>
       <c r="AK436" t="n">
         <v>6.970728111892008</v>
@@ -71395,16 +71395,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM436" t="n">
-        <v>-0.127636816539944</v>
+        <v>-0.127636816539943</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.007451019732577668</v>
+        <v>-0.00745101973257774</v>
       </c>
       <c r="AO436" t="n">
-        <v>0.04750067483060583</v>
+        <v>0.04750067483060572</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.1264197539900239</v>
+        <v>-0.1264197539900158</v>
       </c>
       <c r="AQ436" t="n">
         <v>50</v>
@@ -71563,13 +71563,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.008628156625160088</v>
+        <v>-0.008628156625160163</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.05751510742764043</v>
+        <v>0.05751510742764121</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.01455716888858717</v>
+        <v>-0.01455716888858911</v>
       </c>
       <c r="AQ437" t="n">
         <v>52.1978021978022</v>
@@ -71713,10 +71713,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI438" t="n">
-        <v>6.950644730799358</v>
+        <v>6.950644730799363</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1501448147226974</v>
+        <v>-0.1501448147227027</v>
       </c>
       <c r="AK438" t="n">
         <v>6.959853578800648</v>
@@ -71725,16 +71725,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.1469566450661546</v>
+        <v>-0.1469566450661556</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.009026348114251986</v>
+        <v>-0.009026348114251901</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.06603756167960417</v>
+        <v>0.06603756167960351</v>
       </c>
       <c r="AP438" t="n">
-        <v>-0.03442073040257095</v>
+        <v>-0.03442073040263358</v>
       </c>
       <c r="AQ438" t="n">
         <v>50</v>
@@ -71878,28 +71878,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI439" t="n">
-        <v>6.934622414140156</v>
+        <v>6.934622414140152</v>
       </c>
       <c r="AJ439" t="n">
-        <v>-0.1321226430219919</v>
+        <v>-0.1321226430219875</v>
       </c>
       <c r="AK439" t="n">
-        <v>6.94711441643572</v>
+        <v>6.947114416435721</v>
       </c>
       <c r="AL439" t="n">
-        <v>-0.1446146453175556</v>
+        <v>-0.1446146453175565</v>
       </c>
       <c r="AM439" t="n">
-        <v>-0.1568781652619925</v>
+        <v>-0.1568781652619921</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.010042871337475</v>
+        <v>-0.01004287133747513</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.07699206242755485</v>
+        <v>0.07699206242755419</v>
       </c>
       <c r="AP439" t="n">
-        <v>0.1712380528020885</v>
+        <v>0.171238052802138</v>
       </c>
       <c r="AQ439" t="n">
         <v>59.23913043478261</v>
@@ -72043,10 +72043,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.928042396530076</v>
+        <v>6.928042396530073</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1335425224150857</v>
+        <v>-0.133542522415083</v>
       </c>
       <c r="AK440" t="n">
         <v>6.933186989735641</v>
@@ -72055,16 +72055,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1650917115670576</v>
+        <v>-0.1650917115670582</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.0106149464753251</v>
+        <v>-0.01061494647532512</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.08732871254562191</v>
+        <v>0.08732871254562202</v>
       </c>
       <c r="AP440" t="n">
-        <v>0.1545270908702242</v>
+        <v>0.1545270908702531</v>
       </c>
       <c r="AQ440" t="n">
         <v>55.94594594594594</v>
@@ -72208,10 +72208,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.941461393298105</v>
+        <v>6.941461393298106</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1469615191831144</v>
+        <v>-0.1469615191831153</v>
       </c>
       <c r="AK441" t="n">
         <v>6.925995477801935</v>
@@ -72220,16 +72220,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1745447047691483</v>
+        <v>-0.1745447047691478</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.01108963812755723</v>
+        <v>-0.01108963812755724</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.09935205695041804</v>
+        <v>0.09935205695041927</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.0002217230226866503</v>
+        <v>0.0002217230226744898</v>
       </c>
       <c r="AQ441" t="n">
         <v>49.46236559139784</v>
@@ -72373,10 +72373,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.93323210397643</v>
+        <v>6.933232103976423</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1472323290435682</v>
+        <v>-0.147232329043562</v>
       </c>
       <c r="AK442" t="n">
         <v>6.938996539173566</v>
@@ -72385,16 +72385,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM442" t="n">
-        <v>-0.1853013335308036</v>
+        <v>-0.1853013335308053</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.01193987645426134</v>
+        <v>-0.01193987645426136</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.1123648810347069</v>
+        <v>0.1123648810347067</v>
       </c>
       <c r="AP442" t="n">
-        <v>-0.002893039975078939</v>
+        <v>-0.002893039975008993</v>
       </c>
       <c r="AQ442" t="n">
         <v>45.18716577540107</v>
@@ -72538,10 +72538,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.928429644379657</v>
+        <v>6.928429644379658</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1496296336985043</v>
+        <v>-0.1496296336985061</v>
       </c>
       <c r="AK443" t="n">
         <v>6.93160690101155</v>
@@ -72553,13 +72553,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01257308415669778</v>
+        <v>-0.01257308415669775</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.125857898472412</v>
+        <v>0.1258578984724115</v>
       </c>
       <c r="AP443" t="n">
-        <v>-0.03052785499598967</v>
+        <v>-0.03052785499601227</v>
       </c>
       <c r="AQ443" t="n">
         <v>45.47872340425532</v>
@@ -72703,10 +72703,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.925068850639515</v>
+        <v>6.925068850639512</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1455688430101203</v>
+        <v>-0.1455688430101176</v>
       </c>
       <c r="AK444" t="n">
         <v>6.924763510572069</v>
@@ -72715,16 +72715,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.2060805417157788</v>
+        <v>-0.2060805417157789</v>
       </c>
       <c r="AN444" t="n">
-        <v>-0.01318646791849926</v>
+        <v>-0.01318646791849928</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1396251026736655</v>
+        <v>0.1396251026736647</v>
       </c>
       <c r="AP444" t="n">
-        <v>0.01650249294536955</v>
+        <v>0.01650249294539831</v>
       </c>
       <c r="AQ444" t="n">
         <v>49.2063492063492</v>
@@ -72868,10 +72868,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.900929863197374</v>
+        <v>6.900929863197373</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1347297975845807</v>
+        <v>-0.1347297975845798</v>
       </c>
       <c r="AK445" t="n">
         <v>6.921049732547429</v>
@@ -72880,16 +72880,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM445" t="n">
-        <v>-0.2151279705591488</v>
+        <v>-0.2151279705591481</v>
       </c>
       <c r="AN445" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.1518365696223548</v>
+        <v>0.1518365696223549</v>
       </c>
       <c r="AP445" t="n">
-        <v>0.1421064183695394</v>
+        <v>0.1421064183695479</v>
       </c>
       <c r="AQ445" t="n">
         <v>50.26315789473685</v>
@@ -73033,10 +73033,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.895219010181459</v>
+        <v>6.89521901018146</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1302191436958635</v>
+        <v>-0.1302191436958644</v>
       </c>
       <c r="AK446" t="n">
         <v>6.89978353884127</v>
@@ -73048,13 +73048,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01278923357027009</v>
+        <v>-0.01278923357027006</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1644177475946104</v>
+        <v>0.1644177475946105</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.1941443936487497</v>
+        <v>0.1941443936487376</v>
       </c>
       <c r="AQ446" t="n">
         <v>47.90575916230367</v>
@@ -73198,10 +73198,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.879512239848579</v>
+        <v>6.87951223984858</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1173123611559523</v>
+        <v>-0.1173123611559532</v>
       </c>
       <c r="AK447" t="n">
         <v>6.893260360395011</v>
@@ -73210,16 +73210,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.233692768734329</v>
+        <v>-0.233692768734328</v>
       </c>
       <c r="AN447" t="n">
-        <v>-0.01245257184765153</v>
+        <v>-0.01245257184765156</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.179129523332087</v>
+        <v>0.1791295233320875</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.3439341529553133</v>
+        <v>0.3439341529553017</v>
       </c>
       <c r="AQ447" t="n">
         <v>51.30208333333334</v>
@@ -73363,10 +73363,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI448" t="n">
-        <v>6.882426232260446</v>
+        <v>6.882426232260437</v>
       </c>
       <c r="AJ448" t="n">
-        <v>-0.1132263840853973</v>
+        <v>-0.1132263840853884</v>
       </c>
       <c r="AK448" t="n">
         <v>6.880758546638964</v>
@@ -73375,16 +73375,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM448" t="n">
-        <v>-0.2433281856134891</v>
+        <v>-0.2433281856134888</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01202813951384066</v>
+        <v>-0.01202813951384067</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.1944608722019401</v>
+        <v>0.1944608722019407</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.3906145992170963</v>
+        <v>0.3906145992171987</v>
       </c>
       <c r="AQ448" t="n">
         <v>52.84974093264249</v>
@@ -73540,16 +73540,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.2520264427810588</v>
+        <v>-0.25202644278106</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01246671652825437</v>
+        <v>-0.01246671652825434</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.2101991144027906</v>
+        <v>0.2101991144027905</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.9597294456821833</v>
+        <v>0.9597294456821829</v>
       </c>
       <c r="AQ449" t="n">
         <v>65.72164948453609</v>
@@ -73693,10 +73693,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.841963898035317</v>
+        <v>6.841963898035326</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.07646382937076623</v>
+        <v>-0.07646382937077512</v>
       </c>
       <c r="AK450" t="n">
         <v>6.844785316397215</v>
@@ -73705,16 +73705,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.2592973891940562</v>
+        <v>-0.2592973891940566</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01305068899435097</v>
+        <v>-0.01305068899435077</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.2277185089957531</v>
+        <v>0.2277185089957524</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.8137630324157031</v>
+        <v>0.8137630324155991</v>
       </c>
       <c r="AQ450" t="n">
         <v>58.97435897435898</v>
@@ -73858,28 +73858,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI451" t="n">
-        <v>6.845644916883085</v>
+        <v>6.845644916883079</v>
       </c>
       <c r="AJ451" t="n">
-        <v>-0.08014484821853429</v>
+        <v>-0.08014484821852808</v>
       </c>
       <c r="AK451" t="n">
-        <v>6.849407886968131</v>
+        <v>6.849407886968132</v>
       </c>
       <c r="AL451" t="n">
-        <v>-0.08390781830358041</v>
+        <v>-0.08390781830358129</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2668003223256257</v>
+        <v>-0.2668003223256254</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01367989020054944</v>
+        <v>-0.0136798902005495</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.2456601220977563</v>
+        <v>0.2456601220977566</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.7673910819524771</v>
+        <v>0.7673910819525497</v>
       </c>
       <c r="AQ451" t="n">
         <v>58.67346938775511</v>
@@ -74023,10 +74023,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.842084108625032</v>
+        <v>6.842084108625038</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.0695840704780597</v>
+        <v>-0.06958407047806503</v>
       </c>
       <c r="AK452" t="n">
         <v>6.852702018840203</v>
@@ -74035,16 +74035,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2735436467318143</v>
+        <v>-0.273543646731814</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01403412282467997</v>
+        <v>-0.01403412282467991</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2619835102172253</v>
+        <v>0.261983510217226</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.8875429188270075</v>
+        <v>0.8875429188269452</v>
       </c>
       <c r="AQ452" t="n">
         <v>63.95939086294417</v>
@@ -74188,10 +74188,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.863831060847773</v>
+        <v>6.863831060847785</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.09133102270080062</v>
+        <v>-0.09133102270081217</v>
       </c>
       <c r="AK453" t="n">
         <v>6.850973969550408</v>
@@ -74200,16 +74200,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM453" t="n">
-        <v>-0.2787367835501612</v>
+        <v>-0.2787367835501617</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01406387644726603</v>
+        <v>-0.01406387644726588</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2758112468611987</v>
+        <v>0.2758112468611976</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.6294168309402517</v>
+        <v>0.6294168309401165</v>
       </c>
       <c r="AQ453" t="n">
         <v>62.87878787878788</v>
@@ -74353,10 +74353,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI454" t="n">
-        <v>6.853037915615571</v>
+        <v>6.853037915615573</v>
       </c>
       <c r="AJ454" t="n">
-        <v>-0.07753809490634289</v>
+        <v>-0.07753809490634467</v>
       </c>
       <c r="AK454" t="n">
         <v>6.873527983489108</v>
@@ -74368,13 +74368,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN454" t="n">
-        <v>-0.013790177185657</v>
+        <v>-0.01379017718565697</v>
       </c>
       <c r="AO454" t="n">
-        <v>0.285442546377481</v>
+        <v>0.2854425463774817</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.7887389244851651</v>
+        <v>0.7887389244851456</v>
       </c>
       <c r="AQ454" t="n">
         <v>69.09547738693468</v>
@@ -74530,7 +74530,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.2865252693972544</v>
+        <v>-0.2865252693972545</v>
       </c>
       <c r="AN455" t="n">
         <v>-0.01327380582108439</v>
@@ -74539,7 +74539,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.5892297130393329</v>
+        <v>0.5892297130393334</v>
       </c>
       <c r="AQ455" t="n">
         <v>62.25</v>
@@ -74683,10 +74683,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.860047631936786</v>
+        <v>6.860047631936787</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.1030476624543644</v>
+        <v>-0.1030476624543653</v>
       </c>
       <c r="AK456" t="n">
         <v>6.865985861260643</v>
@@ -74695,16 +74695,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM456" t="n">
-        <v>-0.290522309347949</v>
+        <v>-0.2905223093479492</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.01240158194086383</v>
+        <v>-0.01240158194086378</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.3024992257449916</v>
+        <v>0.3024992257449914</v>
       </c>
       <c r="AP456" t="n">
-        <v>0.4841686497047967</v>
+        <v>0.4841686497047863</v>
       </c>
       <c r="AQ456" t="n">
         <v>58.45771144278607</v>
@@ -74848,10 +74848,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI457" t="n">
-        <v>6.801980414635013</v>
+        <v>6.801980414635016</v>
       </c>
       <c r="AJ457" t="n">
-        <v>-0.04478065038330392</v>
+        <v>-0.04478065038330659</v>
       </c>
       <c r="AK457" t="n">
         <v>6.863576603094304</v>
@@ -74860,16 +74860,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2950697019949103</v>
+        <v>-0.2950697019949104</v>
       </c>
       <c r="AN457" t="n">
-        <v>-0.0116105331596838</v>
+        <v>-0.01161053315968381</v>
       </c>
       <c r="AO457" t="n">
-        <v>0.3113800696686924</v>
+        <v>0.3113800696686918</v>
       </c>
       <c r="AP457" t="n">
-        <v>1.167071957583111</v>
+        <v>1.167071957583083</v>
       </c>
       <c r="AQ457" t="n">
         <v>79.70297029702971</v>
@@ -75013,10 +75013,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.789283666813423</v>
+        <v>6.789283666813422</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.03208390256171434</v>
+        <v>-0.03208390256171256</v>
       </c>
       <c r="AK458" t="n">
         <v>6.809671190627447</v>
@@ -75025,16 +75025,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.2987092362344105</v>
+        <v>-0.2987092362344108</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.01030385953714813</v>
+        <v>-0.01030385953714808</v>
       </c>
       <c r="AO458" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP458" t="n">
-        <v>1.3084035405388</v>
+        <v>1.308403540538825</v>
       </c>
       <c r="AQ458" t="n">
         <v>82.51231527093596</v>
@@ -75178,10 +75178,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.789252537988938</v>
+        <v>6.789252537988933</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.02065255095890883</v>
+        <v>-0.0206525509589035</v>
       </c>
       <c r="AK459" t="n">
         <v>6.802840448144932</v>
@@ -75190,16 +75190,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.3027504956929287</v>
+        <v>-0.3027504956929284</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.00881278602540958</v>
+        <v>-0.008812786025409641</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.332227117067963</v>
+        <v>0.3322271170679635</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.43250939236508</v>
+        <v>1.432509392365146</v>
       </c>
       <c r="AQ459" t="n">
         <v>83.33333333333334</v>
@@ -75343,10 +75343,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.774001672255927</v>
+        <v>6.774001672255932</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.005401685225897346</v>
+        <v>-0.005401685225902675</v>
       </c>
       <c r="AK460" t="n">
         <v>6.800260207803535</v>
@@ -75355,16 +75355,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.3068099364477369</v>
+        <v>-0.3068099364477367</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.007070247176567734</v>
+        <v>-0.007070247176567688</v>
       </c>
       <c r="AO460" t="n">
-        <v>0.3427146952658529</v>
+        <v>0.3427146952658534</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.598027860157056</v>
+        <v>1.598027860156998</v>
       </c>
       <c r="AQ460" t="n">
         <v>83.90243902439025</v>
@@ -75508,10 +75508,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.802628307046305</v>
+        <v>6.802628307046303</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.0281284138578286</v>
+        <v>-0.02812841385782594</v>
       </c>
       <c r="AK461" t="n">
         <v>6.781970485204615</v>
@@ -75520,16 +75520,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3121566752204096</v>
+        <v>-0.3121566752204101</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.005102880740085192</v>
+        <v>-0.005102880740085154</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.3560731605465752</v>
+        <v>0.3560731605465757</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.322523164322986</v>
+        <v>1.32252316432302</v>
       </c>
       <c r="AQ461" t="n">
         <v>80.33980582524272</v>
@@ -75673,28 +75673,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.815944895083629</v>
+        <v>6.815944895083632</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.0259449332306021</v>
+        <v>-0.02594493323060476</v>
       </c>
       <c r="AK462" t="n">
-        <v>6.809638458820509</v>
+        <v>6.809638458820508</v>
       </c>
       <c r="AL462" t="n">
-        <v>-0.01963849696748188</v>
+        <v>-0.01963849696748099</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3181413841564625</v>
+        <v>-0.3181413841564619</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.003317316385138602</v>
+        <v>-0.003317316385138562</v>
       </c>
       <c r="AO462" t="n">
-        <v>0.3690689225934927</v>
+        <v>0.3690689225934922</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.338949589565835</v>
+        <v>1.338949589565807</v>
       </c>
       <c r="AQ462" t="n">
         <v>82.1256038647343</v>
@@ -75838,10 +75838,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.821941449304759</v>
+        <v>6.821941449304753</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.0319414874517312</v>
+        <v>-0.03194148745172587</v>
       </c>
       <c r="AK463" t="n">
         <v>6.819973703544699</v>
@@ -75850,16 +75850,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3244228225822193</v>
+        <v>-0.3244228225822198</v>
       </c>
       <c r="AN463" t="n">
-        <v>-0.001700148658338674</v>
+        <v>-0.001700148658338742</v>
       </c>
       <c r="AO463" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.260946083348039</v>
+        <v>1.260946083348104</v>
       </c>
       <c r="AQ463" t="n">
         <v>78.84615384615385</v>
@@ -76003,10 +76003,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.826413262727742</v>
+        <v>6.826413262727749</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.03641330087471495</v>
+        <v>-0.03641330087472205</v>
       </c>
       <c r="AK464" t="n">
         <v>6.822087900644207</v>
@@ -76015,16 +76015,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3308797299382499</v>
+        <v>-0.3308797299382495</v>
       </c>
       <c r="AN464" t="n">
-        <v>-7.481797733216444e-05</v>
+        <v>-7.481797733213274e-05</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.3960788710418811</v>
+        <v>0.396078871041881</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.201673955857811</v>
+        <v>1.201673955857732</v>
       </c>
       <c r="AQ464" t="n">
         <v>79.42583732057416</v>
@@ -76168,10 +76168,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.812656647679548</v>
+        <v>6.81265664767955</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.01465678882334664</v>
+        <v>-0.01465678882334931</v>
       </c>
       <c r="AK465" t="n">
         <v>6.823881638371397</v>
@@ -76180,16 +76180,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3363418922753055</v>
+        <v>-0.3363418922753058</v>
       </c>
       <c r="AN465" t="n">
-        <v>0.001379920606120022</v>
+        <v>0.001379920606120097</v>
       </c>
       <c r="AO465" t="n">
-        <v>0.4081029523904164</v>
+        <v>0.4081029523904167</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.444501255718839</v>
+        <v>1.444501255718812</v>
       </c>
       <c r="AQ465" t="n">
         <v>83.57142857142858</v>
@@ -76333,10 +76333,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI466" t="n">
-        <v>6.802797817425507</v>
+        <v>6.802797817425505</v>
       </c>
       <c r="AJ466" t="n">
-        <v>-0.009197735028045884</v>
+        <v>-0.009197735028044107</v>
       </c>
       <c r="AK466" t="n">
         <v>6.808320681191073</v>
@@ -76345,16 +76345,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3410659803634685</v>
+        <v>-0.3410659803634682</v>
       </c>
       <c r="AN466" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.4198133218741356</v>
+        <v>0.4198133218741357</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.496320293037209</v>
+        <v>1.496320293037234</v>
       </c>
       <c r="AQ466" t="n">
         <v>83.64928909952607</v>
@@ -76504,22 +76504,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK467" t="n">
-        <v>6.795980661778267</v>
+        <v>6.795980661778266</v>
       </c>
       <c r="AL467" t="n">
-        <v>-0.002380579380806047</v>
+        <v>-0.002380579380805159</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3461577281601511</v>
+        <v>-0.3461577281601509</v>
       </c>
       <c r="AN467" t="n">
-        <v>0.004282887883574671</v>
+        <v>0.00428288788357468</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4328049372030962</v>
+        <v>0.4328049372030969</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.557372155580718</v>
+        <v>1.557372155580722</v>
       </c>
       <c r="AQ467" t="n">
         <v>84.90566037735849</v>
@@ -76663,10 +76663,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.800189882196235</v>
+        <v>6.800189882196236</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.005989938653754301</v>
+        <v>-0.005989938653755189</v>
       </c>
       <c r="AK468" t="n">
         <v>6.78726841810145</v>
@@ -76675,16 +76675,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3502903933401412</v>
+        <v>-0.3502903933401418</v>
       </c>
       <c r="AN468" t="n">
-        <v>0.005405808652032051</v>
+        <v>0.005405808652032067</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4450018361960529</v>
+        <v>0.4450018361960534</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.509093923734655</v>
+        <v>1.509093923734649</v>
       </c>
       <c r="AQ468" t="n">
         <v>83.80281690140845</v>
@@ -76828,10 +76828,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI469" t="n">
-        <v>6.79797208364255</v>
+        <v>6.797972083642554</v>
       </c>
       <c r="AJ469" t="n">
-        <v>-0.009372115686007376</v>
+        <v>-0.009372115686010929</v>
       </c>
       <c r="AK469" t="n">
         <v>6.791305278184372</v>
@@ -76840,16 +76840,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM469" t="n">
-        <v>-0.3548656112706069</v>
+        <v>-0.3548656112706071</v>
       </c>
       <c r="AN469" t="n">
-        <v>0.006091291211178074</v>
+        <v>0.006091291211178139</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4593697101544711</v>
+        <v>0.4593697101544705</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.459340654430508</v>
+        <v>1.459340654430472</v>
       </c>
       <c r="AQ469" t="n">
         <v>82.4766355140187</v>
@@ -76993,10 +76993,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.800452644405181</v>
+        <v>6.800452644405178</v>
       </c>
       <c r="AJ470" t="n">
-        <v>-0.01185267644863774</v>
+        <v>-0.01185267644863508</v>
       </c>
       <c r="AK470" t="n">
         <v>6.789098969069376</v>
@@ -77011,10 +77011,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4721687943484544</v>
+        <v>0.4721687943484545</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.420758423733292</v>
+        <v>1.420758423733326</v>
       </c>
       <c r="AQ470" t="n">
         <v>79.30232558139535</v>
@@ -77158,10 +77158,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.778720347685821</v>
+        <v>6.778720347685814</v>
       </c>
       <c r="AJ471" t="n">
-        <v>0.01707986135958883</v>
+        <v>0.01707986135959594</v>
       </c>
       <c r="AK471" t="n">
         <v>6.790465135395929</v>
@@ -77170,16 +77170,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3625273381377937</v>
+        <v>-0.3625273381377933</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.007343464385960674</v>
+        <v>0.007343464385960585</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4863203622043377</v>
+        <v>0.4863203622043382</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.735818113096423</v>
+        <v>1.735818113096508</v>
       </c>
       <c r="AQ471" t="n">
         <v>84.49074074074073</v>
@@ -77323,10 +77323,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.769755998762547</v>
+        <v>6.769755998762545</v>
       </c>
       <c r="AJ472" t="n">
-        <v>0.02364381202846833</v>
+        <v>0.02364381202847099</v>
       </c>
       <c r="AK472" t="n">
         <v>6.767889899932765</v>
@@ -77335,16 +77335,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM472" t="n">
-        <v>-0.3660007866474812</v>
+        <v>-0.3660007866474813</v>
       </c>
       <c r="AN472" t="n">
-        <v>0.00826013782295415</v>
+        <v>0.008260137822954145</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.4997690914082398</v>
+        <v>0.4997690914082401</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.792944555386005</v>
+        <v>1.792944555386039</v>
       </c>
       <c r="AQ472" t="n">
         <v>85.25345622119815</v>
@@ -77488,10 +77488,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.789177604754239</v>
+        <v>6.789177604754244</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.01332216636392491</v>
+        <v>0.01332216636391959</v>
       </c>
       <c r="AK473" t="n">
         <v>6.759766754404358</v>
@@ -77500,16 +77500,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3700034659576358</v>
+        <v>-0.3700034659576351</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.00987171553454691</v>
+        <v>0.009871715534546958</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.5120623436103316</v>
+        <v>0.5120623436103324</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.661325671000316</v>
+        <v>1.661325671000259</v>
       </c>
       <c r="AQ473" t="n">
         <v>85.3211009174312</v>
@@ -77653,10 +77653,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI474" t="n">
-        <v>6.774331376960423</v>
+        <v>6.774331376960425</v>
       </c>
       <c r="AJ474" t="n">
-        <v>0.01776857573733093</v>
+        <v>0.01776857573732915</v>
       </c>
       <c r="AK474" t="n">
         <v>6.777856240868369</v>
@@ -77665,16 +77665,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3750442390024145</v>
+        <v>-0.3750442390024147</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.01196068662558775</v>
+        <v>0.01196068662558781</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.5238651846176465</v>
+        <v>0.5238651846176463</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.696297597637856</v>
+        <v>1.696297597637841</v>
       </c>
       <c r="AQ474" t="n">
         <v>84.47488584474885</v>
@@ -77830,16 +77830,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3816350905604304</v>
+        <v>-0.3816350905604307</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.01460798460929558</v>
+        <v>0.01460798460929556</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.537958310473289</v>
+        <v>0.5379583104732891</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.642029572156369</v>
+        <v>1.642029572156373</v>
       </c>
       <c r="AQ475" t="n">
         <v>85</v>
@@ -77983,10 +77983,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.789815280543246</v>
+        <v>6.789815280543245</v>
       </c>
       <c r="AJ476" t="n">
-        <v>-0.01031527291385181</v>
+        <v>-0.01031527291385093</v>
       </c>
       <c r="AK476" t="n">
         <v>6.744939020214936</v>
@@ -77995,16 +77995,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3872393091179336</v>
+        <v>-0.3872393091179339</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01685992867552227</v>
+        <v>0.01685992867552231</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5511317941481411</v>
+        <v>0.5511317941481415</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.358690801077947</v>
+        <v>1.35869080107796</v>
       </c>
       <c r="AQ476" t="n">
         <v>82.57918552036199</v>
@@ -78148,10 +78148,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI477" t="n">
-        <v>6.801295181477315</v>
+        <v>6.801295181477309</v>
       </c>
       <c r="AJ477" t="n">
-        <v>-0.03129520055080093</v>
+        <v>-0.0312952005507956</v>
       </c>
       <c r="AK477" t="n">
         <v>6.772636231606738</v>
@@ -78160,16 +78160,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.393020019860339</v>
+        <v>-0.3930200198603389</v>
       </c>
       <c r="AN477" t="n">
-        <v>0.01873686412955489</v>
+        <v>0.01873686412955481</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.5644439393662184</v>
+        <v>0.5644439393662187</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.118411120406287</v>
+        <v>1.118411120406348</v>
       </c>
       <c r="AQ477" t="n">
         <v>77.25225225225225</v>
@@ -78313,10 +78313,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.791632066062363</v>
+        <v>6.791632066062364</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.0234321454080666</v>
+        <v>-0.02343214540806748</v>
       </c>
       <c r="AK478" t="n">
         <v>6.788619247652995</v>
@@ -78325,16 +78325,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3966294116439325</v>
+        <v>-0.3966294116439323</v>
       </c>
       <c r="AN478" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.576974471973372</v>
+        <v>0.5769744719733717</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.199651101846855</v>
+        <v>1.199651101846848</v>
       </c>
       <c r="AQ478" t="n">
         <v>74.88789237668162</v>
@@ -78478,10 +78478,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.779898505875916</v>
+        <v>6.779898505875918</v>
       </c>
       <c r="AJ479" t="n">
-        <v>-0.007398467728943814</v>
+        <v>-0.00739846772894559</v>
       </c>
       <c r="AK479" t="n">
         <v>6.776305653888958</v>
@@ -78490,16 +78490,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.3980313152890726</v>
+        <v>-0.3980313152890724</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01933124704228378</v>
+        <v>0.0193312470422838</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.5877384296086169</v>
+        <v>0.5877384296086161</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.369736655492007</v>
+        <v>1.36973665549199</v>
       </c>
       <c r="AQ479" t="n">
         <v>76.5625</v>
@@ -78643,10 +78643,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.771360892616113</v>
+        <v>6.771360892616116</v>
       </c>
       <c r="AJ480" t="n">
-        <v>0.001139145530859587</v>
+        <v>0.001139145530856922</v>
       </c>
       <c r="AK480" t="n">
         <v>6.76492936370744</v>
@@ -78655,16 +78655,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3979537985659305</v>
+        <v>-0.3979537985659302</v>
       </c>
       <c r="AN480" t="n">
-        <v>0.0183584453609324</v>
+        <v>0.01835844536093246</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.6001791687136281</v>
+        <v>0.6001791687136286</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.454653277351469</v>
+        <v>1.454653277351443</v>
       </c>
       <c r="AQ480" t="n">
         <v>77.55555555555556</v>
@@ -78808,10 +78808,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.751667781721844</v>
+        <v>6.751667781721842</v>
       </c>
       <c r="AJ481" t="n">
-        <v>0.02083225642512865</v>
+        <v>0.02083225642513042</v>
       </c>
       <c r="AK481" t="n">
         <v>6.753855191419989</v>
@@ -78820,16 +78820,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3975762425746344</v>
+        <v>-0.3975762425746347</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01731206726614276</v>
+        <v>0.01731206726614282</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.6129676701055393</v>
+        <v>0.6129676701055397</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.659500463226858</v>
+        <v>1.659500463226881</v>
       </c>
       <c r="AQ481" t="n">
         <v>82.9646017699115</v>
@@ -78973,10 +78973,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.729738669869288</v>
+        <v>6.72973866986929</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.03586153459848518</v>
+        <v>0.0358615345984834</v>
       </c>
       <c r="AK482" t="n">
         <v>6.736226026398153</v>
@@ -78985,16 +78985,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3964908591695859</v>
+        <v>-0.3964908591695858</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.01740130648959376</v>
+        <v>0.01740130648959375</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6198907013195262</v>
+        <v>0.6198907013195265</v>
       </c>
       <c r="AP482" t="n">
-        <v>1.80855005143257</v>
+        <v>1.808550051432555</v>
       </c>
       <c r="AQ482" t="n">
         <v>80.39647577092511</v>
@@ -79138,10 +79138,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.713320364291503</v>
+        <v>6.713320364291505</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.05917967385546952</v>
+        <v>0.05917967385546774</v>
       </c>
       <c r="AK483" t="n">
         <v>6.717723214958548</v>
@@ -79150,16 +79150,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM483" t="n">
-        <v>-0.394760534481672</v>
+        <v>-0.3947605344816719</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01742962324324016</v>
+        <v>0.01742962324324019</v>
       </c>
       <c r="AO483" t="n">
-        <v>0.6272835381163622</v>
+        <v>0.6272835381163618</v>
       </c>
       <c r="AP483" t="n">
-        <v>2.041719324181404</v>
+        <v>2.04171932418139</v>
       </c>
       <c r="AQ483" t="n">
         <v>87.28070175438597</v>
@@ -79303,10 +79303,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.731179671396989</v>
+        <v>6.731179671396997</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.04132036674998396</v>
+        <v>0.04132036674997597</v>
       </c>
       <c r="AK484" t="n">
         <v>6.699415101064979</v>
@@ -79318,13 +79318,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01766596732646103</v>
+        <v>0.0176659673264611</v>
       </c>
       <c r="AO484" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.828804405210595</v>
+        <v>1.828804405210515</v>
       </c>
       <c r="AQ484" t="n">
         <v>86.68122270742359</v>
@@ -79468,10 +79468,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.740946959621007</v>
+        <v>6.740946959621005</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.03085308157772371</v>
+        <v>0.03085308157772548</v>
       </c>
       <c r="AK485" t="n">
         <v>6.714685154719483</v>
@@ -79480,16 +79480,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.3929423394238508</v>
+        <v>-0.392942339423851</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01842070378092631</v>
+        <v>0.0184207037809263</v>
       </c>
       <c r="AO485" t="n">
-        <v>0.640374511165978</v>
+        <v>0.6403745111659787</v>
       </c>
       <c r="AP485" t="n">
-        <v>1.700351196224833</v>
+        <v>1.700351196224859</v>
       </c>
       <c r="AQ485" t="n">
         <v>84.56521739130434</v>
@@ -79633,10 +79633,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.7589577577717</v>
+        <v>6.758957757771704</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.006742105662137732</v>
+        <v>0.006742105662134179</v>
       </c>
       <c r="AK486" t="n">
         <v>6.722064699270507</v>
@@ -79645,16 +79645,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM486" t="n">
-        <v>-0.3931401656438959</v>
+        <v>-0.3931401656438955</v>
       </c>
       <c r="AN486" t="n">
-        <v>0.01902711841846483</v>
+        <v>0.01902711841846487</v>
       </c>
       <c r="AO486" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.429664264337194</v>
+        <v>1.429664264337161</v>
       </c>
       <c r="AQ486" t="n">
         <v>80.30303030303031</v>
@@ -79798,10 +79798,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI487" t="n">
-        <v>6.763209774497792</v>
+        <v>6.763209774497788</v>
       </c>
       <c r="AJ487" t="n">
-        <v>0.007790133949473699</v>
+        <v>0.007790133949477251</v>
       </c>
       <c r="AK487" t="n">
         <v>6.739235851443908</v>
@@ -79810,16 +79810,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.3951733572725242</v>
+        <v>-0.3951733572725246</v>
       </c>
       <c r="AN487" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO487" t="n">
-        <v>0.6590798145480943</v>
+        <v>0.6590798145480942</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.431474962471599</v>
+        <v>1.431474962471641</v>
       </c>
       <c r="AQ487" t="n">
         <v>80.60344827586206</v>
@@ -79975,16 +79975,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3960001863323608</v>
+        <v>-0.396000186332361</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.02043272610569408</v>
+        <v>0.02043272610569401</v>
       </c>
       <c r="AO488" t="n">
-        <v>0.6685846444009622</v>
+        <v>0.6685846444009627</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.613607390103175</v>
+        <v>1.61360739010318</v>
       </c>
       <c r="AQ488" t="n">
         <v>81.11587982832619</v>
@@ -80128,10 +80128,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.714622134232894</v>
+        <v>6.714622134232888</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.04037798020802441</v>
+        <v>0.04037798020802974</v>
       </c>
       <c r="AK489" t="n">
         <v>6.746779913842831</v>
@@ -80140,16 +80140,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM489" t="n">
-        <v>-0.396740905361911</v>
+        <v>-0.3967409053619114</v>
       </c>
       <c r="AN489" t="n">
-        <v>0.02120763540003751</v>
+        <v>0.02120763540003743</v>
       </c>
       <c r="AO489" t="n">
-        <v>0.6777865296786982</v>
+        <v>0.6777865296786978</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.754112131763462</v>
+        <v>1.754112131763524</v>
       </c>
       <c r="AQ489" t="n">
         <v>83.76068376068376</v>
@@ -80293,28 +80293,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI490" t="n">
-        <v>6.731570059394423</v>
+        <v>6.73157005939442</v>
       </c>
       <c r="AJ490" t="n">
-        <v>0.01932973232310609</v>
+        <v>0.01932973232310964</v>
       </c>
       <c r="AK490" t="n">
-        <v>6.728823425344638</v>
+        <v>6.728823425344639</v>
       </c>
       <c r="AL490" t="n">
-        <v>0.02207636637289134</v>
+        <v>0.02207636637289045</v>
       </c>
       <c r="AM490" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.0220082962170377</v>
+        <v>0.02200829621703764</v>
       </c>
       <c r="AO490" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.518183573399403</v>
+        <v>1.518183573399444</v>
       </c>
       <c r="AQ490" t="n">
         <v>79.14893617021276</v>
@@ -80458,10 +80458,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.748064561399866</v>
+        <v>6.748064561399863</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.004235224214148126</v>
+        <v>0.00423522421415079</v>
       </c>
       <c r="AK491" t="n">
         <v>6.740096815166266</v>
@@ -80470,16 +80470,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.3976889317784199</v>
+        <v>-0.3976889317784196</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02268190844878654</v>
+        <v>0.02268190844878653</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.6953567146475523</v>
+        <v>0.6953567146475526</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.349053884490984</v>
+        <v>1.349053884491015</v>
       </c>
       <c r="AQ491" t="n">
         <v>74.15254237288136</v>
@@ -80623,10 +80623,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.747226278872152</v>
+        <v>6.747226278872151</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.005973775296548745</v>
+        <v>0.005973775296550521</v>
       </c>
       <c r="AK492" t="n">
         <v>6.755554272205931</v>
@@ -80635,16 +80635,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM492" t="n">
-        <v>-0.4003515275861345</v>
+        <v>-0.400351527586135</v>
       </c>
       <c r="AN492" t="n">
-        <v>0.02398656672240618</v>
+        <v>0.02398656672240616</v>
       </c>
       <c r="AO492" t="n">
-        <v>0.7067969646460921</v>
+        <v>0.7067969646460924</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.359311645485312</v>
+        <v>1.359311645485334</v>
       </c>
       <c r="AQ492" t="n">
         <v>73.83966244725738</v>
@@ -80788,10 +80788,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.724989986752571</v>
+        <v>6.724989986752573</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.02471008267491914</v>
+        <v>0.02471008267491737</v>
       </c>
       <c r="AK493" t="n">
         <v>6.75925064743029</v>
@@ -80800,7 +80800,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.4017887258056133</v>
+        <v>-0.4017887258056131</v>
       </c>
       <c r="AN493" t="n">
         <v>0.02482212216928553</v>
@@ -80809,7 +80809,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.547250446574062</v>
+        <v>1.547250446574046</v>
       </c>
       <c r="AQ493" t="n">
         <v>77.31092436974789</v>
@@ -80953,28 +80953,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.738231277482312</v>
+        <v>6.738231277482303</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.01056852339049108</v>
+        <v>0.01056852339049996</v>
       </c>
       <c r="AK494" t="n">
-        <v>6.734775445902895</v>
+        <v>6.734775445902896</v>
       </c>
       <c r="AL494" t="n">
-        <v>0.01402435496990773</v>
+        <v>0.01402435496990684</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4022294042554291</v>
+        <v>-0.402229404255429</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02545790195722747</v>
+        <v>0.02545790195722734</v>
       </c>
       <c r="AO494" t="n">
-        <v>0.7273309315128231</v>
+        <v>0.7273309315128232</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.388816030834972</v>
+        <v>1.388816030835067</v>
       </c>
       <c r="AQ494" t="n">
         <v>74.68619246861924</v>
@@ -81118,10 +81118,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.718201282169581</v>
+        <v>6.718201282169575</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.02919852480673768</v>
+        <v>0.02919852480674301</v>
       </c>
       <c r="AK495" t="n">
         <v>6.753996132599221</v>
@@ -81130,16 +81130,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.4027953816469058</v>
+        <v>-0.4027953816469059</v>
       </c>
       <c r="AN495" t="n">
-        <v>0.02608258444417638</v>
+        <v>0.02608258444417639</v>
       </c>
       <c r="AO495" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.574261851122703</v>
+        <v>1.57426185112276</v>
       </c>
       <c r="AQ495" t="n">
         <v>78.54166666666666</v>
@@ -81283,10 +81283,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI496" t="n">
-        <v>6.730898772467414</v>
+        <v>6.730898772467415</v>
       </c>
       <c r="AJ496" t="n">
-        <v>0.01650103450890406</v>
+        <v>0.01650103450890317</v>
       </c>
       <c r="AK496" t="n">
         <v>6.732394407262716</v>
@@ -81295,16 +81295,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4025099007694142</v>
+        <v>-0.402509900769414</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02634377330607651</v>
+        <v>0.02634377330607648</v>
       </c>
       <c r="AO496" t="n">
-        <v>0.746561519528266</v>
+        <v>0.7465615195282662</v>
       </c>
       <c r="AP496" t="n">
-        <v>1.431262346040811</v>
+        <v>1.431262346040803</v>
       </c>
       <c r="AQ496" t="n">
         <v>79.04564315352697</v>
@@ -81460,16 +81460,16 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4034224290251451</v>
+        <v>-0.4034224290251453</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02736182786837871</v>
+        <v>0.02736182786837866</v>
       </c>
       <c r="AO497" t="n">
-        <v>0.755189863471066</v>
+        <v>0.7551898634710656</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.296934473650141</v>
+        <v>1.296934473650142</v>
       </c>
       <c r="AQ497" t="n">
         <v>77.06611570247935</v>
@@ -81613,10 +81613,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.755708466794879</v>
+        <v>6.75570846679488</v>
       </c>
       <c r="AJ498" t="n">
-        <v>-0.01240850570479068</v>
+        <v>-0.01240850570479246</v>
       </c>
       <c r="AK498" t="n">
         <v>6.746865899087779</v>
@@ -81625,16 +81625,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4037073020769307</v>
+        <v>-0.4037073020769305</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02778289906564352</v>
+        <v>0.02778289906564353</v>
       </c>
       <c r="AO498" t="n">
-        <v>0.7638221248099442</v>
+        <v>0.7638221248099444</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.115009582818696</v>
+        <v>1.115009582818678</v>
       </c>
       <c r="AQ498" t="n">
         <v>79.83539094650206</v>
@@ -81778,10 +81778,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI499" t="n">
-        <v>6.73601646973098</v>
+        <v>6.73601646973097</v>
       </c>
       <c r="AJ499" t="n">
-        <v>0.006783766017311343</v>
+        <v>0.006783766017321113</v>
       </c>
       <c r="AK499" t="n">
         <v>6.761018647414997</v>
@@ -81790,16 +81790,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM499" t="n">
-        <v>-0.403510818895136</v>
+        <v>-0.4035108188951355</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02805871830419215</v>
+        <v>0.02805871830419202</v>
       </c>
       <c r="AO499" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP499" t="n">
-        <v>1.309128225856541</v>
+        <v>1.309128225856644</v>
       </c>
       <c r="AQ499" t="n">
         <v>83.60655737704917</v>
@@ -81958,7 +81958,7 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02827333203020888</v>
+        <v>0.02827333203020884</v>
       </c>
       <c r="AO500" t="n">
         <v>0.7726830480787004</v>
@@ -82108,10 +82108,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.725806144687715</v>
+        <v>6.725806144687716</v>
       </c>
       <c r="AJ501" t="n">
-        <v>0.01409396746438496</v>
+        <v>0.01409396746438318</v>
       </c>
       <c r="AK501" t="n">
         <v>6.744478107428201</v>
@@ -82120,16 +82120,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.4027900432658338</v>
+        <v>-0.4027900432658339</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02891453613228628</v>
+        <v>0.0289145361322863</v>
       </c>
       <c r="AO501" t="n">
-        <v>0.7784357006627721</v>
+        <v>0.7784357006627718</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.369237488708931</v>
+        <v>1.369237488708913</v>
       </c>
       <c r="AQ501" t="n">
         <v>83.53658536585365</v>
@@ -82273,10 +82273,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI502" t="n">
-        <v>6.700854569500288</v>
+        <v>6.700854569500285</v>
       </c>
       <c r="AJ502" t="n">
-        <v>0.04174539464155735</v>
+        <v>0.04174539464156091</v>
       </c>
       <c r="AK502" t="n">
         <v>6.743301592583855</v>
@@ -82285,16 +82285,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM502" t="n">
-        <v>-0.402742697458547</v>
+        <v>-0.4027426974585472</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02955568036482276</v>
+        <v>0.0295556803648227</v>
       </c>
       <c r="AO502" t="n">
-        <v>0.7839391318357882</v>
+        <v>0.7839391318357879</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.645465762050723</v>
+        <v>1.64546576205076</v>
       </c>
       <c r="AQ502" t="n">
         <v>88.46153846153845</v>
@@ -82438,10 +82438,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.705597066237452</v>
+        <v>6.705597066237454</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.02390275065707925</v>
+        <v>0.02390275065707748</v>
       </c>
       <c r="AK503" t="n">
         <v>6.74285285202661</v>
@@ -82450,16 +82450,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM503" t="n">
-        <v>-0.401588500320058</v>
+        <v>-0.4015885003200582</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02985284499018426</v>
+        <v>0.02985284499018428</v>
       </c>
       <c r="AO503" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.450624921065368</v>
+        <v>1.450624921065349</v>
       </c>
       <c r="AQ503" t="n">
         <v>85.08064516129033</v>
@@ -82603,28 +82603,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.686024746022946</v>
+        <v>6.686024746022948</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.0364751013891631</v>
+        <v>0.03647510138916132</v>
       </c>
       <c r="AK504" t="n">
-        <v>6.744526329542678</v>
+        <v>6.744526329542679</v>
       </c>
       <c r="AL504" t="n">
-        <v>-0.02202648213056868</v>
+        <v>-0.02202648213056957</v>
       </c>
       <c r="AM504" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.02995529076246445</v>
+        <v>0.02995529076246446</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7933293013213367</v>
+        <v>0.7933293013213371</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.570091188080506</v>
+        <v>1.570091188080488</v>
       </c>
       <c r="AQ504" t="n">
         <v>84.33734939759037</v>
@@ -82768,10 +82768,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.689653251437546</v>
+        <v>6.689653251437547</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.03134694311201436</v>
+        <v>0.03134694311201347</v>
       </c>
       <c r="AK505" t="n">
         <v>6.730402461316146</v>
@@ -82780,16 +82780,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.3993041981056888</v>
+        <v>-0.3993041981056886</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.03010093147709741</v>
+        <v>0.03010093147709737</v>
       </c>
       <c r="AO505" t="n">
-        <v>0.7985853639949437</v>
+        <v>0.7985853639949436</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.507036858820242</v>
+        <v>1.507036858820234</v>
       </c>
       <c r="AQ505" t="n">
         <v>85</v>
@@ -82933,10 +82933,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.716786041117415</v>
+        <v>6.716786041117424</v>
       </c>
       <c r="AJ506" t="n">
-        <v>0.00511394514967467</v>
+        <v>0.005113945149665788</v>
       </c>
       <c r="AK506" t="n">
         <v>6.728106442363027</v>
@@ -82945,16 +82945,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM506" t="n">
-        <v>-0.3976134529492091</v>
+        <v>-0.3976134529492094</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.03006044259180324</v>
+        <v>0.03006044259180338</v>
       </c>
       <c r="AO506" t="n">
-        <v>0.8026437279892851</v>
+        <v>0.8026437279892848</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.234777974751978</v>
+        <v>1.234777974751887</v>
       </c>
       <c r="AQ506" t="n">
         <v>81.59999999999999</v>
@@ -83098,10 +83098,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.721932795514441</v>
+        <v>6.72193279551444</v>
       </c>
       <c r="AJ507" t="n">
-        <v>-0.001632597913122424</v>
+        <v>-0.001632597913121536</v>
       </c>
       <c r="AK507" t="n">
         <v>6.752314636061016</v>
@@ -83113,13 +83113,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03043336917902489</v>
+        <v>0.03043336917902487</v>
       </c>
       <c r="AO507" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.163823515923089</v>
+        <v>1.163823515923099</v>
       </c>
       <c r="AQ507" t="n">
         <v>82.19999999999999</v>
@@ -83263,28 +83263,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.718669003366535</v>
+        <v>6.718669003366529</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.003830844045574544</v>
+        <v>0.003830844045580761</v>
       </c>
       <c r="AK508" t="n">
-        <v>6.750203856204787</v>
+        <v>6.750203856204786</v>
       </c>
       <c r="AL508" t="n">
-        <v>-0.02770400879267765</v>
+        <v>-0.02770400879267676</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3969152632178358</v>
+        <v>-0.3969152632178359</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03100517332816438</v>
+        <v>0.03100517332816427</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.8091236362457368</v>
+        <v>0.8091236362457366</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.217453571381047</v>
+        <v>1.217453571381111</v>
       </c>
       <c r="AQ508" t="n">
         <v>82.80000000000001</v>
@@ -83428,10 +83428,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.680190080689523</v>
+        <v>6.680190080689519</v>
       </c>
       <c r="AJ509" t="n">
-        <v>0.04230976672258624</v>
+        <v>0.04230976672259068</v>
       </c>
       <c r="AK509" t="n">
         <v>6.74780904069481</v>
@@ -83440,16 +83440,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM509" t="n">
-        <v>-0.3964565291282772</v>
+        <v>-0.3964565291282773</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03139664408873172</v>
+        <v>0.03139664408873165</v>
       </c>
       <c r="AO509" t="n">
-        <v>0.8123541153569376</v>
+        <v>0.8123541153569371</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.604493248424094</v>
+        <v>1.60449324842414</v>
       </c>
       <c r="AQ509" t="n">
         <v>89.8</v>
@@ -83593,10 +83593,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.671580974366952</v>
+        <v>6.671580974366949</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.05441885778636824</v>
+        <v>0.05441885778637179</v>
       </c>
       <c r="AK510" t="n">
         <v>6.701878095437348</v>
@@ -83608,13 +83608,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03163116863423027</v>
+        <v>0.03163116863423025</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8147568654710424</v>
+        <v>0.8147568654710426</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.717274375116457</v>
+        <v>1.717274375116493</v>
       </c>
       <c r="AQ510" t="n">
         <v>90.2</v>
@@ -83758,28 +83758,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI511" t="n">
-        <v>6.656216276126097</v>
+        <v>6.656216276126093</v>
       </c>
       <c r="AJ511" t="n">
-        <v>0.06978355602722353</v>
+        <v>0.06978355602722708</v>
       </c>
       <c r="AK511" t="n">
-        <v>6.701765808189924</v>
+        <v>6.701765808189925</v>
       </c>
       <c r="AL511" t="n">
-        <v>0.02423402396339647</v>
+        <v>0.02423402396339558</v>
       </c>
       <c r="AM511" t="n">
-        <v>-0.3932426568003564</v>
+        <v>-0.3932426568003567</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.0319127327617218</v>
+        <v>0.03191273276172183</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8170879052811413</v>
+        <v>0.8170879052811416</v>
       </c>
       <c r="AP511" t="n">
-        <v>1.858889534485343</v>
+        <v>1.858889534485378</v>
       </c>
       <c r="AQ511" t="n">
         <v>90.59999999999999</v>
@@ -83929,22 +83929,22 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK512" t="n">
-        <v>6.682658801267993</v>
+        <v>6.682658801267994</v>
       </c>
       <c r="AL512" t="n">
-        <v>0.03754126053010243</v>
+        <v>0.03754126053010154</v>
       </c>
       <c r="AM512" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03225018457163042</v>
+        <v>0.03225018457163047</v>
       </c>
       <c r="AO512" t="n">
-        <v>0.8195353634242114</v>
+        <v>0.8195353634242113</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.818117584748587</v>
+        <v>1.818117584748586</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.2</v>
@@ -84088,10 +84088,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.654231073451243</v>
+        <v>6.654231073451242</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.06476878921965579</v>
+        <v>0.06476878921965668</v>
       </c>
       <c r="AK513" t="n">
         <v>6.682840937292736</v>
@@ -84100,16 +84100,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM513" t="n">
-        <v>-0.3894836768645471</v>
+        <v>-0.3894836768645476</v>
       </c>
       <c r="AN513" t="n">
-        <v>0.03277193700354208</v>
+        <v>0.03277193700354209</v>
       </c>
       <c r="AO513" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.781104797300566</v>
+        <v>1.781104797300574</v>
       </c>
       <c r="AQ513" t="n">
         <v>90.2</v>
@@ -84253,10 +84253,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI514" t="n">
-        <v>6.650937329061554</v>
+        <v>6.650937329061552</v>
       </c>
       <c r="AJ514" t="n">
-        <v>0.06806253360934456</v>
+        <v>0.06806253360934633</v>
       </c>
       <c r="AK514" t="n">
         <v>6.698821600583909</v>
@@ -84265,16 +84265,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM514" t="n">
-        <v>-0.3885003849593205</v>
+        <v>-0.3885003849593203</v>
       </c>
       <c r="AN514" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8264954348925954</v>
+        <v>0.8264954348925952</v>
       </c>
       <c r="AP514" t="n">
-        <v>1.79987483353635</v>
+        <v>1.799874833536367</v>
       </c>
       <c r="AQ514" t="n">
         <v>91</v>
@@ -84418,10 +84418,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.651733245487365</v>
+        <v>6.651733245487366</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.05906692541107272</v>
+        <v>0.05906692541107184</v>
       </c>
       <c r="AK515" t="n">
         <v>6.69208631505748</v>
@@ -84430,16 +84430,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM515" t="n">
-        <v>-0.3869746098498524</v>
+        <v>-0.3869746098498528</v>
       </c>
       <c r="AN515" t="n">
-        <v>0.0344188897752209</v>
+        <v>0.03441888977522091</v>
       </c>
       <c r="AO515" t="n">
-        <v>0.8294137131605728</v>
+        <v>0.8294137131605726</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.696616308981454</v>
+        <v>1.696616308981445</v>
       </c>
       <c r="AQ515" t="n">
         <v>90.40000000000001</v>
@@ -84583,10 +84583,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.632036771677474</v>
+        <v>6.632036771677475</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.07876339922096331</v>
+        <v>0.07876339922096243</v>
       </c>
       <c r="AK516" t="n">
         <v>6.692627206904497</v>
@@ -84604,7 +84604,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.875440190456855</v>
+        <v>1.875440190456845</v>
       </c>
       <c r="AQ516" t="n">
         <v>91</v>
@@ -84748,10 +84748,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI517" t="n">
-        <v>6.617259294346139</v>
+        <v>6.617259294346145</v>
       </c>
       <c r="AJ517" t="n">
-        <v>0.09324046914263029</v>
+        <v>0.09324046914262496</v>
       </c>
       <c r="AK517" t="n">
         <v>6.685306332307247</v>
@@ -84763,13 +84763,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN517" t="n">
-        <v>0.03459091746240417</v>
+        <v>0.03459091746240425</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8328314813119074</v>
+        <v>0.8328314813119078</v>
       </c>
       <c r="AP517" t="n">
-        <v>1.998006000856745</v>
+        <v>1.998006000856694</v>
       </c>
       <c r="AQ517" t="n">
         <v>91</v>
@@ -84925,16 +84925,16 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM518" t="n">
-        <v>-0.379198503222778</v>
+        <v>-0.3791985032227784</v>
       </c>
       <c r="AN518" t="n">
-        <v>0.03468237364461174</v>
+        <v>0.03468237364461172</v>
       </c>
       <c r="AO518" t="n">
-        <v>0.8349203610870053</v>
+        <v>0.8349203610870052</v>
       </c>
       <c r="AP518" t="n">
-        <v>2.317228225252931</v>
+        <v>2.317228225252932</v>
       </c>
       <c r="AQ518" t="n">
         <v>93</v>
@@ -85093,13 +85093,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03437427878524163</v>
+        <v>0.0343742787852416</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8337972329517069</v>
+        <v>0.8337972329517072</v>
       </c>
       <c r="AP519" t="n">
-        <v>2.426255822246373</v>
+        <v>2.426255822246375</v>
       </c>
       <c r="AQ519" t="n">
         <v>93.40000000000001</v>
@@ -85243,10 +85243,10 @@
         <v>-0.2483229054629721</v>
       </c>
       <c r="AI520" t="n">
-        <v>6.570789830572489</v>
+        <v>6.57078983057249</v>
       </c>
       <c r="AJ520" t="n">
-        <v>0.1372103525329802</v>
+        <v>0.1372103525329784</v>
       </c>
       <c r="AK520" t="n">
         <v>6.617345065810827</v>
@@ -85255,16 +85255,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM520" t="n">
-        <v>-0.3685435183382903</v>
+        <v>-0.3685435183382902</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03361173230743109</v>
+        <v>0.03361173230743112</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8313650598704547</v>
+        <v>0.8313650598704546</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.332216400368045</v>
+        <v>2.33221640036803</v>
       </c>
       <c r="AQ520" t="n">
         <v>91.8</v>
@@ -85408,10 +85408,10 @@
         <v>-0.2475852618441712</v>
       </c>
       <c r="AI521" t="n">
-        <v>6.574987720536733</v>
+        <v>6.574987720536736</v>
       </c>
       <c r="AJ521" t="n">
-        <v>0.1332122573380232</v>
+        <v>0.1332122573380197</v>
       </c>
       <c r="AK521" t="n">
         <v>6.613295682645951</v>
@@ -85420,16 +85420,16 @@
         <v>0.09490429522880461</v>
       </c>
       <c r="AM521" t="n">
-        <v>-0.362880333269974</v>
+        <v>-0.3628803332699742</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.0328662017206236</v>
+        <v>0.03286620172062364</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.82993355238613</v>
+        <v>0.8299335523861298</v>
       </c>
       <c r="AP521" t="n">
-        <v>2.265952574875406</v>
+        <v>2.265952574875376</v>
       </c>
       <c r="AQ521" t="n">
         <v>91.8</v>
@@ -85585,16 +85585,16 @@
         <v>0.1007055635562768</v>
       </c>
       <c r="AM522" t="n">
-        <v>-0.3578313453157061</v>
+        <v>-0.3578313453157059</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03253304912369537</v>
+        <v>0.03253304912369535</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8295016854680709</v>
+        <v>0.829501685468071</v>
       </c>
       <c r="AP522" t="n">
-        <v>2.256510029904997</v>
+        <v>2.256510029905</v>
       </c>
       <c r="AQ522" t="n">
         <v>92.40000000000001</v>
@@ -85753,13 +85753,13 @@
         <v>-0.3533816852595308</v>
       </c>
       <c r="AN523" t="n">
-        <v>0.03276281973018108</v>
+        <v>0.03276281973018107</v>
       </c>
       <c r="AO523" t="n">
-        <v>0.8294865216719109</v>
+        <v>0.8294865216719108</v>
       </c>
       <c r="AP523" t="n">
-        <v>1.905883880717604</v>
+        <v>1.905883880717606</v>
       </c>
       <c r="AQ523" t="n">
         <v>91.8</v>
@@ -85814,13 +85814,13 @@
         <v>6.705999851226807</v>
       </c>
       <c r="F524" t="n">
-        <v>6.695519924163818</v>
+        <v>6.69582986831665</v>
       </c>
       <c r="G524" t="n">
         <v>6.6886</v>
       </c>
       <c r="H524" t="n">
-        <v>-0.01047992706298828</v>
+        <v>-0.01016998291015625</v>
       </c>
       <c r="I524" t="n">
         <v>100.2200012207031</v>
@@ -85903,10 +85903,10 @@
         <v>-0.2288666674853745</v>
       </c>
       <c r="AI524" t="n">
-        <v>6.609458957036644</v>
+        <v>6.609458957036646</v>
       </c>
       <c r="AJ524" t="n">
-        <v>0.09654089419016287</v>
+        <v>0.0965408941901611</v>
       </c>
       <c r="AK524" t="n">
         <v>6.62059441621928</v>
@@ -85915,16 +85915,16 @@
         <v>0.08540543500752662</v>
       </c>
       <c r="AM524" t="n">
-        <v>-0.350362421245722</v>
+        <v>-0.3503624212457221</v>
       </c>
       <c r="AN524" t="n">
-        <v>0.03312067555156334</v>
+        <v>0.03312067555156335</v>
       </c>
       <c r="AO524" t="n">
-        <v>0.8307181423026834</v>
+        <v>0.8307181423026831</v>
       </c>
       <c r="AP524" t="n">
-        <v>1.860215899982009</v>
+        <v>1.860215899981995</v>
       </c>
       <c r="AQ524" t="n">
         <v>92.59999999999999</v>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41365,10 +41365,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI254" t="n">
-        <v>7.148511457776028</v>
+        <v>7.14851145777603</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.01601128611465086</v>
+        <v>-0.01601128611465263</v>
       </c>
       <c r="AK254" t="n">
         <v>7.150963414761942</v>
@@ -41377,13 +41377,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1011329645838851</v>
+        <v>0.1011329645838857</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002517185580011447</v>
+        <v>0.002517185580011383</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2709113683260677</v>
+        <v>0.2709113683260674</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41542,13 +41542,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.09870181295186471</v>
+        <v>0.09870181295186436</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002644711580562537</v>
+        <v>0.002644711580562605</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2704892730019304</v>
+        <v>0.2704892730019285</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41695,10 +41695,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.153772633426659</v>
+        <v>7.153772633426657</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.03287247931288917</v>
+        <v>-0.03287247931288739</v>
       </c>
       <c r="AK256" t="n">
         <v>7.154757231824306</v>
@@ -41707,13 +41707,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.09555831842873846</v>
+        <v>0.09555831842873888</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002822832879878071</v>
+        <v>0.002822832879878049</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2697410008595936</v>
+        <v>0.2697410008595938</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41860,10 +41860,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.153331199414496</v>
+        <v>7.153331199414497</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.03263131690717191</v>
+        <v>-0.0326313169071728</v>
       </c>
       <c r="AK257" t="n">
         <v>7.15450652143491</v>
@@ -41872,13 +41872,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.0918844066524992</v>
+        <v>0.09188440665249918</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.003041971996730133</v>
+        <v>0.003041971996730116</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2698098046976256</v>
+        <v>0.2698098046976254</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42025,10 +42025,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI258" t="n">
-        <v>7.156943148319592</v>
+        <v>7.15694314831959</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-0.03854305142628167</v>
+        <v>-0.0385430514262799</v>
       </c>
       <c r="AK258" t="n">
         <v>7.154505434137821</v>
@@ -42037,13 +42037,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.08748497753913406</v>
+        <v>0.08748497753913362</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.003298336925509862</v>
+        <v>0.003298336925509857</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2682008942988235</v>
+        <v>0.2682008942988222</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42202,13 +42202,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.0824587084059305</v>
+        <v>0.08245870840593096</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.003602928090795432</v>
+        <v>0.003602928090795422</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2685806390401517</v>
+        <v>0.2685806390401518</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42370,10 +42370,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003819541738581442</v>
+        <v>0.003819541738581439</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2696768907787764</v>
+        <v>0.2696768907787754</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42520,10 +42520,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.154685377655177</v>
+        <v>7.154685377655176</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.04048526245131967</v>
+        <v>-0.04048526245131878</v>
       </c>
       <c r="AK261" t="n">
         <v>7.15808570026938</v>
@@ -42532,13 +42532,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.07200163454913491</v>
+        <v>0.07200163454913533</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.004193740708391541</v>
+        <v>0.004193740708391577</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.270116598814735</v>
+        <v>0.2701165988147326</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42685,10 +42685,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI262" t="n">
-        <v>7.158449213455076</v>
+        <v>7.158449213455078</v>
       </c>
       <c r="AJ262" t="n">
-        <v>-0.05514911885058371</v>
+        <v>-0.05514911885058549</v>
       </c>
       <c r="AK262" t="n">
         <v>7.157644979270017</v>
@@ -42697,13 +42697,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.06676111471939408</v>
+        <v>0.06676111471939436</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.00450521933759436</v>
+        <v>0.004505219337594384</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2733976337163381</v>
+        <v>0.2733976337163387</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42850,10 +42850,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI263" t="n">
-        <v>7.160761769069204</v>
+        <v>7.160761769069201</v>
       </c>
       <c r="AJ263" t="n">
-        <v>-0.04786198879576631</v>
+        <v>-0.04786198879576364</v>
       </c>
       <c r="AK263" t="n">
         <v>7.159146249199162</v>
@@ -42862,10 +42862,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM263" t="n">
-        <v>0.06148465881746725</v>
+        <v>0.06148465881746766</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.004852471327681615</v>
+        <v>0.004852471327681566</v>
       </c>
       <c r="AO263" t="n">
         <v>0.2778048766368325</v>
@@ -43015,10 +43015,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.162478122158095</v>
+        <v>7.162478122158094</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.04957834188465782</v>
+        <v>-0.04957834188465693</v>
       </c>
       <c r="AK264" t="n">
         <v>7.159578986975002</v>
@@ -43027,13 +43027,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.05582594297075769</v>
+        <v>0.05582594297075712</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.005234102211236422</v>
+        <v>0.005234102211236467</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.282448024375059</v>
+        <v>0.2824480243750598</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43192,13 +43192,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.04949165986049534</v>
+        <v>0.04949165986049463</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.005677665039252891</v>
+        <v>0.005677665039252918</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.2878618994559775</v>
+        <v>0.2878618994559794</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43357,13 +43357,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.04287777011073584</v>
+        <v>0.04287777011073606</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.006155260602669632</v>
+        <v>0.006155260602669625</v>
       </c>
       <c r="AO266" t="n">
-        <v>0.2948468705933219</v>
+        <v>0.2948468705933236</v>
       </c>
       <c r="AP266" t="n">
         <v/>
@@ -43510,10 +43510,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.173971773133425</v>
+        <v>7.173971773133423</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04247200582995792</v>
+        <v>-0.04247200582995614</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159255388854645</v>
@@ -43522,13 +43522,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.0348694200966178</v>
+        <v>0.03486942009661778</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.006728155724408227</v>
+        <v>0.006728155724408201</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.304499875642397</v>
+        <v>0.3044998756423967</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43675,25 +43675,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI268" t="n">
-        <v>7.172030417300567</v>
+        <v>7.172030417300565</v>
       </c>
       <c r="AJ268" t="n">
-        <v>-0.03823038754592822</v>
+        <v>-0.03823038754592645</v>
       </c>
       <c r="AK268" t="n">
-        <v>7.167062070913353</v>
+        <v>7.167062070913352</v>
       </c>
       <c r="AL268" t="n">
-        <v>-0.03326204115871434</v>
+        <v>-0.03326204115871345</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.03279550096037902</v>
+        <v>0.03279550096037874</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.006903991232239788</v>
+        <v>0.006903991232239758</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.3170366335916601</v>
+        <v>0.3170366335916608</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43840,10 +43840,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI269" t="n">
-        <v>7.171236182927453</v>
+        <v>7.171236182927454</v>
       </c>
       <c r="AJ269" t="n">
-        <v>-0.03843608069356641</v>
+        <v>-0.0384360806935673</v>
       </c>
       <c r="AK269" t="n">
         <v>7.16747443083108</v>
@@ -43852,13 +43852,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.02972414459983895</v>
+        <v>0.02972414459983913</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.007158147882858998</v>
+        <v>0.007158147882859</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.3270754385893867</v>
+        <v>0.3270754385893863</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -44005,10 +44005,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.170425137628191</v>
+        <v>7.170425137628194</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.05102511321412884</v>
+        <v>-0.0510251132141315</v>
       </c>
       <c r="AK270" t="n">
         <v>7.168373097443463</v>
@@ -44017,13 +44017,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.02657019411530269</v>
+        <v>0.02657019411530295</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.007420436972250415</v>
+        <v>0.007420436972250398</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.3357224795973284</v>
+        <v>0.3357224795973281</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44182,13 +44182,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.02366886174665103</v>
+        <v>0.02366886174665165</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.007679120311627263</v>
+        <v>0.007679120311627231</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.3450219581941938</v>
+        <v>0.345021958194194</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44335,10 +44335,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.172249622131827</v>
+        <v>7.172249622131823</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.05324966409349674</v>
+        <v>-0.05324966409349319</v>
       </c>
       <c r="AK272" t="n">
         <v>7.167365057101177</v>
@@ -44347,13 +44347,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.01956653131084185</v>
+        <v>0.01956653131084189</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.008034860291676559</v>
+        <v>0.008034860291676519</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3572033251592189</v>
+        <v>0.3572033251592186</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44500,10 +44500,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.171656420777024</v>
+        <v>7.171656420777023</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.05265646273869429</v>
+        <v>-0.0526564627386934</v>
       </c>
       <c r="AK273" t="n">
         <v>7.167567681415887</v>
@@ -44512,13 +44512,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.01638396088890769</v>
+        <v>0.0163839608889081</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.008326212487477964</v>
+        <v>0.008326212487477898</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3674516177552961</v>
+        <v>0.3674516177552964</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44665,10 +44665,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI274" t="n">
-        <v>7.175289829564748</v>
+        <v>7.175289829564746</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-0.05628987152641773</v>
+        <v>-0.05628987152641596</v>
       </c>
       <c r="AK274" t="n">
         <v>7.167553154788029</v>
@@ -44677,13 +44677,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.01351198449095157</v>
+        <v>0.01351198449095179</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.008601682347582891</v>
+        <v>0.008601682347582911</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.3758646846617525</v>
+        <v>0.375864684661753</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44836,19 +44836,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK275" t="n">
-        <v>7.16746081477764</v>
+        <v>7.167460814777641</v>
       </c>
       <c r="AL275" t="n">
-        <v>-0.04846085673931011</v>
+        <v>-0.048460856739311</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.01196199498966369</v>
+        <v>0.01196199498966377</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008797062853284063</v>
+        <v>0.008797062853284078</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3847384959530242</v>
+        <v>0.3847384959530228</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -45156,10 +45156,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.189678003526525</v>
+        <v>7.189678003526526</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.07117777082999144</v>
+        <v>-0.07117777082999321</v>
       </c>
       <c r="AK277" t="n">
         <v/>
@@ -45168,13 +45168,13 @@
         <v/>
       </c>
       <c r="AM277" t="n">
-        <v>0.007307555239791734</v>
+        <v>0.007307555239791735</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.009236289154790337</v>
+        <v>0.009236289154790363</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.401039717356949</v>
+        <v>0.4010397173569483</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45321,10 +45321,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI278" t="n">
-        <v>7.183919177237467</v>
+        <v>7.183919177237466</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-0.05641912001700788</v>
+        <v>-0.056419120017007</v>
       </c>
       <c r="AK278" t="n">
         <v>7.168706858585229</v>
@@ -45333,13 +45333,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.006573598200530942</v>
+        <v>0.006573598200531427</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.009378157495070056</v>
+        <v>0.009378157495070007</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.4093166892046883</v>
+        <v>0.4093166892046876</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45498,13 +45498,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM279" t="n">
-        <v>0.005719699928660468</v>
+        <v>0.00571969992866044</v>
       </c>
       <c r="AN279" t="n">
-        <v>0.009535855797507643</v>
+        <v>0.009535855797507651</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.4189456552735356</v>
+        <v>0.4189456552735351</v>
       </c>
       <c r="AP279" t="n">
         <v/>
@@ -45651,10 +45651,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI280" t="n">
-        <v>7.183803634757356</v>
+        <v>7.183803634757355</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-0.08380373012478781</v>
+        <v>-0.08380373012478692</v>
       </c>
       <c r="AK280" t="n">
         <v>7.157754776965645</v>
@@ -45663,13 +45663,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM280" t="n">
-        <v>0.007205793377056199</v>
+        <v>0.007205793377055721</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.009541847058682544</v>
+        <v>0.00954184705868257</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.4265135453780396</v>
+        <v>0.4265135453780416</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45822,19 +45822,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK281" t="n">
-        <v>7.153578345933642</v>
+        <v>7.153578345933643</v>
       </c>
       <c r="AL281" t="n">
-        <v>-0.01517826811381795</v>
+        <v>-0.01517826811381884</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.009937300636551308</v>
+        <v>0.009937300636551421</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.00947510825395563</v>
+        <v>0.009475108253955637</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4359288044119884</v>
+        <v>0.4359288044119891</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45981,10 +45981,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI282" t="n">
-        <v>7.175374323571331</v>
+        <v>7.175374323571332</v>
       </c>
       <c r="AJ282" t="n">
-        <v>-0.04917412444413394</v>
+        <v>-0.04917412444413483</v>
       </c>
       <c r="AK282" t="n">
         <v>7.155226204999164</v>
@@ -45993,13 +45993,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.01039951522374721</v>
+        <v>0.01039951522374727</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009534227083684284</v>
+        <v>0.009534227083684297</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.446224869246465</v>
+        <v>0.4462248692464653</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46158,13 +46158,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.01174445052819259</v>
+        <v>0.01174445052819296</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009539024405591096</v>
+        <v>0.009539024405591111</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4561706550234678</v>
+        <v>0.4561706550234662</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46311,10 +46311,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI284" t="n">
-        <v>7.176295466764674</v>
+        <v>7.176295466764673</v>
       </c>
       <c r="AJ284" t="n">
-        <v>-0.04989547286818929</v>
+        <v>-0.04989547286818841</v>
       </c>
       <c r="AK284" t="n">
         <v>7.150954883812801</v>
@@ -46323,13 +46323,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.01399948938427905</v>
+        <v>0.01399948938427885</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.009474826008246758</v>
+        <v>0.009474826008246765</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4654004237248369</v>
+        <v>0.4654004237248376</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46488,13 +46488,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01676993900799729</v>
+        <v>0.01676993900799728</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.009377028877974699</v>
+        <v>0.00937702887797469</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.476700939638935</v>
+        <v>0.4767009396389351</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46656,10 +46656,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009204864903404497</v>
+        <v>0.009204864903404482</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4883841032893044</v>
+        <v>0.4883841032893032</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46818,13 +46818,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.02435543352765289</v>
+        <v>0.02435543352765317</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.009045821984022376</v>
+        <v>0.00904582198402234</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4990078266507766</v>
+        <v>0.4990078266507749</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46971,10 +46971,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI288" t="n">
-        <v>7.175210595491395</v>
+        <v>7.175210595491394</v>
       </c>
       <c r="AJ288" t="n">
-        <v>-0.04951059854315254</v>
+        <v>-0.04951059854315165</v>
       </c>
       <c r="AK288" t="n">
         <v>7.151444380572274</v>
@@ -46983,13 +46983,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.02840267381959001</v>
+        <v>0.02840267381959008</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.008843610540066053</v>
+        <v>0.008843610540066056</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.5123725312709416</v>
+        <v>0.5123725312709417</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47139,7 +47139,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ289" t="n">
-        <v>-0.05177635201934994</v>
+        <v>-0.05177635201935082</v>
       </c>
       <c r="AK289" t="n">
         <v>7.151307469847429</v>
@@ -47148,13 +47148,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM289" t="n">
-        <v>0.03189518855892823</v>
+        <v>0.03189518855892809</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.008740250954211215</v>
+        <v>0.008740250954211236</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.5303980242931245</v>
+        <v>0.5303980242931252</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47301,10 +47301,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI290" t="n">
-        <v>7.172173616645312</v>
+        <v>7.172173616645314</v>
       </c>
       <c r="AJ290" t="n">
-        <v>-0.06197368836162021</v>
+        <v>-0.06197368836162287</v>
       </c>
       <c r="AK290" t="n">
         <v>7.152170779642037</v>
@@ -47313,13 +47313,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.03448417181877508</v>
+        <v>0.03448417181877479</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.008638296330047493</v>
+        <v>0.008638296330047519</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.536400419244653</v>
+        <v>0.5364004192446541</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47469,7 +47469,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.08262387272163529</v>
+        <v>-0.08262387272163618</v>
       </c>
       <c r="AK291" t="n">
         <v>7.155242422656618</v>
@@ -47481,10 +47481,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008527848481957645</v>
+        <v>0.008527848481957647</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.5479838817473677</v>
+        <v>0.5479838817473681</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47631,10 +47631,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI292" t="n">
-        <v>7.18418852599864</v>
+        <v>7.184188525998638</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.08518854888682359</v>
+        <v>-0.08518854888682181</v>
       </c>
       <c r="AK292" t="n">
         <v>7.174067278312125</v>
@@ -47643,13 +47643,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.03996026841105445</v>
+        <v>0.03996026841105382</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008497979041970659</v>
+        <v>0.008497979041970699</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.5534995516418705</v>
+        <v>0.553499551641869</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47796,10 +47796,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI293" t="n">
-        <v>7.185513015749276</v>
+        <v>7.185513015749274</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.07571315384131694</v>
+        <v>-0.07571315384131516</v>
       </c>
       <c r="AK293" t="n">
         <v>7.175957423377739</v>
@@ -47808,13 +47808,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.04233079818885077</v>
+        <v>0.04233079818885083</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008432709457890229</v>
+        <v>0.008432709457890224</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.5557951014363787</v>
+        <v>0.5557951014363788</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47967,19 +47967,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK294" t="n">
-        <v>7.174765662541793</v>
+        <v>7.174765662541792</v>
       </c>
       <c r="AL294" t="n">
-        <v>-0.05786569534818931</v>
+        <v>-0.05786569534818842</v>
       </c>
       <c r="AM294" t="n">
-        <v>0.04394124299371591</v>
+        <v>0.04394124299371556</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008396387260434499</v>
+        <v>0.008396387260434506</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5565519909812464</v>
+        <v>0.5565519909812453</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48126,10 +48126,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI295" t="n">
-        <v>7.185932916622859</v>
+        <v>7.18593291662286</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.0141327800566966</v>
+        <v>-0.01413278005669749</v>
       </c>
       <c r="AK295" t="n">
         <v>7.172730869790855</v>
@@ -48138,13 +48138,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.04590755972499789</v>
+        <v>0.04590755972499803</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008346613473328282</v>
+        <v>0.008346613473328291</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5588443644440741</v>
+        <v>0.5588443644440755</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48291,10 +48291,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.187602005018013</v>
+        <v>7.187602005018014</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.05810209275604983</v>
+        <v>-0.0581020927560516</v>
       </c>
       <c r="AK296" t="n">
         <v>7.168923754586179</v>
@@ -48303,10 +48303,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04658552832149703</v>
+        <v>0.04658552832149689</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008354655440128402</v>
+        <v>0.008354655440128426</v>
       </c>
       <c r="AO296" t="n">
         <v>0.5613325805619827</v>
@@ -48468,13 +48468,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04820692510781933</v>
+        <v>0.04820692510781883</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008303818071592001</v>
+        <v>0.008303818071592054</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5626464255878519</v>
+        <v>0.5626464255878516</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48633,13 +48633,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04983084886774743</v>
+        <v>0.04983084886774771</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008251024544031704</v>
+        <v>0.008251024544031682</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5641340630354328</v>
+        <v>0.5641340630354323</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48798,13 +48798,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.05170461329917111</v>
+        <v>0.05170461329917048</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008192726391276807</v>
+        <v>0.008192726391276836</v>
       </c>
       <c r="AO299" t="n">
-        <v>0.5658195968244528</v>
+        <v>0.5658195968244545</v>
       </c>
       <c r="AP299" t="n">
         <v/>
@@ -48963,13 +48963,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.05348369580043773</v>
+        <v>0.05348369580043772</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008143044151838245</v>
+        <v>0.008143044151838252</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5671346874885959</v>
+        <v>0.5671346874885956</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49116,10 +49116,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI301" t="n">
-        <v>7.175179910580594</v>
+        <v>7.175179910580593</v>
       </c>
       <c r="AJ301" t="n">
-        <v>-0.05588002196975417</v>
+        <v>-0.05588002196975328</v>
       </c>
       <c r="AK301" t="n">
         <v>7.165699812335961</v>
@@ -49128,13 +49128,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.05520982564369371</v>
+        <v>0.0552098256436935</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008124788470663676</v>
+        <v>0.008124788470663643</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5701242576280907</v>
+        <v>0.5701242576280905</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49281,10 +49281,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI302" t="n">
-        <v>7.173581841712227</v>
+        <v>7.173581841712229</v>
       </c>
       <c r="AJ302" t="n">
-        <v>-0.05428195310138761</v>
+        <v>-0.05428195310138939</v>
       </c>
       <c r="AK302" t="n">
         <v>7.162626578418298</v>
@@ -49293,13 +49293,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05644890839995315</v>
+        <v>0.05644890839995281</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008105230252153435</v>
+        <v>0.008105230252153447</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5713754740215509</v>
+        <v>0.5713754740215494</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49446,10 +49446,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI303" t="n">
-        <v>7.176011726611837</v>
+        <v>7.176011726611838</v>
       </c>
       <c r="AJ303" t="n">
-        <v>-0.06401173805592908</v>
+        <v>-0.06401173805592997</v>
       </c>
       <c r="AK303" t="n">
         <v>7.165542054185019</v>
@@ -49458,13 +49458,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05727663218544052</v>
+        <v>0.05727663218544039</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.00812403522652648</v>
+        <v>0.008124035226526509</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.573000414744258</v>
+        <v>0.5730004147442582</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49611,10 +49611,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.17698340522191</v>
+        <v>7.176983405221908</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.07778363334080662</v>
+        <v>-0.07778363334080485</v>
       </c>
       <c r="AK304" t="n">
         <v>7.170209849598846</v>
@@ -49623,13 +49623,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05825580143844533</v>
+        <v>0.05825580143844532</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008106527117828777</v>
+        <v>0.008106527117828759</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5728585525731363</v>
+        <v>0.5728585525731367</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49776,10 +49776,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.174841035863564</v>
+        <v>7.174841035863563</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.06734095956961905</v>
+        <v>-0.06734095956961816</v>
       </c>
       <c r="AK305" t="n">
         <v>7.166925629020364</v>
@@ -49788,13 +49788,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05980113395910436</v>
+        <v>0.05980113395910441</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008056914781095353</v>
+        <v>0.008056914781095341</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5723268395754473</v>
+        <v>0.5723268395754482</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49941,10 +49941,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.179777800337525</v>
+        <v>7.179777800337526</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.07227772404357946</v>
+        <v>-0.07227772404358035</v>
       </c>
       <c r="AK306" t="n">
         <v>7.163704513322672</v>
@@ -49956,10 +49956,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.008007544934860181</v>
+        <v>0.008007544934860184</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.5724055344141883</v>
+        <v>0.5724055344141876</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50106,10 +50106,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.176651545551679</v>
+        <v>7.176651545551677</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.06915146925773374</v>
+        <v>-0.06915146925773197</v>
       </c>
       <c r="AK307" t="n">
         <v>7.163430147298699</v>
@@ -50118,13 +50118,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.06321929365037962</v>
+        <v>0.06321929365038026</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.007927773212025854</v>
+        <v>0.007927773212025837</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.572463582881384</v>
+        <v>0.5724635828813827</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50271,10 +50271,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.173279688539583</v>
+        <v>7.173279688539582</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.06577961224563733</v>
+        <v>-0.06577961224563644</v>
       </c>
       <c r="AK308" t="n">
         <v>7.158871783064204</v>
@@ -50283,13 +50283,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.06523048259292186</v>
+        <v>0.0652304825929222</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.007809540836127948</v>
+        <v>0.007809540836127932</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.5710090561291132</v>
+        <v>0.571009056129113</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50436,10 +50436,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.168542018724481</v>
+        <v>7.168542018724479</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.06194221098522323</v>
+        <v>-0.06194221098522146</v>
       </c>
       <c r="AK309" t="n">
         <v>7.152618309751275</v>
@@ -50448,13 +50448,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM309" t="n">
-        <v>0.067411943409599</v>
+        <v>0.06741194340959927</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.007660511838810988</v>
+        <v>0.007660511838810949</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5694124450603424</v>
+        <v>0.5694124450603408</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50601,10 +50601,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.161829635752616</v>
+        <v>7.161829635752617</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.05962960447209831</v>
+        <v>-0.0596296044720992</v>
       </c>
       <c r="AK310" t="n">
         <v>7.144956229005203</v>
@@ -50613,13 +50613,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.06977835201573312</v>
+        <v>0.06977835201573281</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007516908058882096</v>
+        <v>0.007516908058882097</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.5690369646398685</v>
+        <v>0.5690369646398684</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50769,7 +50769,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.07699331565738099</v>
+        <v>-0.07699331565738188</v>
       </c>
       <c r="AK311" t="n">
         <v>7.140422114543136</v>
@@ -50778,13 +50778,13 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.07195366789421653</v>
+        <v>0.07195366789421676</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007394117938767417</v>
+        <v>0.007394117938767422</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5693040973288186</v>
+        <v>0.5693040973288199</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50943,10 +50943,10 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.07456301989532385</v>
+        <v>0.07456301989532414</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007241314760732032</v>
+        <v>0.007241314760731996</v>
       </c>
       <c r="AO312" t="n">
         <v>0.5685877661607006</v>
@@ -51108,13 +51108,13 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.07747971887849656</v>
+        <v>0.07747971887849607</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.0070901436555387</v>
+        <v>0.007090143655538702</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5681709745664083</v>
+        <v>0.5681709745664091</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51261,10 +51261,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI314" t="n">
-        <v>7.165084051386049</v>
+        <v>7.165084051386047</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.08998410631768916</v>
+        <v>-0.08998410631768738</v>
       </c>
       <c r="AK314" t="n">
         <v>7.14582045097363</v>
@@ -51273,16 +51273,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.08000072584212846</v>
+        <v>0.08000072584212836</v>
       </c>
       <c r="AN314" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5684087510734981</v>
+        <v>0.5684087510734968</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.98837751168381</v>
+        <v>-1.988377511683731</v>
       </c>
       <c r="AQ314" t="n">
         <v>2.5</v>
@@ -51426,10 +51426,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI315" t="n">
-        <v>7.161419741275552</v>
+        <v>7.161419741275553</v>
       </c>
       <c r="AJ315" t="n">
-        <v>-0.08971964514518138</v>
+        <v>-0.08971964514518227</v>
       </c>
       <c r="AK315" t="n">
         <v>7.155707108847959</v>
@@ -51438,16 +51438,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.08204996863507508</v>
+        <v>0.08204996863507528</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.006919462921967476</v>
+        <v>0.006919462921967468</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.5672869954461468</v>
+        <v>0.5672869954461461</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.896343483293307</v>
+        <v>-1.896343483293377</v>
       </c>
       <c r="AQ315" t="n">
         <v>2.459016393442623</v>
@@ -51591,10 +51591,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI316" t="n">
-        <v>7.155488092579304</v>
+        <v>7.155488092579303</v>
       </c>
       <c r="AJ316" t="n">
-        <v>-0.08548792091792734</v>
+        <v>-0.08548792091792645</v>
       </c>
       <c r="AK316" t="n">
         <v>7.150451326287159</v>
@@ -51603,16 +51603,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.08469403553214168</v>
+        <v>0.08469403553214211</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.006815201188096393</v>
+        <v>0.006815201188096372</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5663505631396779</v>
+        <v>0.5663505631396781</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.605047536006375</v>
+        <v>-1.605047536006344</v>
       </c>
       <c r="AQ316" t="n">
         <v>4.032258064516129</v>
@@ -51756,10 +51756,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.158832817363979</v>
+        <v>7.15883281736398</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.09523275404000398</v>
+        <v>-0.09523275404000575</v>
       </c>
       <c r="AK317" t="n">
         <v>7.147115644271845</v>
@@ -51768,16 +51768,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08699523504893081</v>
+        <v>0.08699523504893142</v>
       </c>
       <c r="AN317" t="n">
-        <v>0.006735083295172709</v>
+        <v>0.006735083295172689</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5654743012892969</v>
+        <v>0.5654743012892984</v>
       </c>
       <c r="AP317" t="n">
-        <v>-2.063097093716959</v>
+        <v>-2.063097093717068</v>
       </c>
       <c r="AQ317" t="n">
         <v>1.587301587301587</v>
@@ -51921,10 +51921,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.161703459649028</v>
+        <v>7.161703459649029</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.090303294091167</v>
+        <v>-0.09030329409116788</v>
       </c>
       <c r="AK318" t="n">
         <v>7.152131804583207</v>
@@ -51933,16 +51933,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08901512474159551</v>
+        <v>0.08901512474159586</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006668288608758136</v>
+        <v>0.006668288608758129</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5631673144521659</v>
+        <v>0.5631673144521655</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.73461210167722</v>
+        <v>-1.734612101677275</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.34375</v>
@@ -52086,10 +52086,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.162535384813326</v>
+        <v>7.162535384813327</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.09293527952768166</v>
+        <v>-0.09293527952768255</v>
       </c>
       <c r="AK319" t="n">
         <v>7.157753883768605</v>
@@ -52098,16 +52098,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.09116436352661951</v>
+        <v>0.09116436352661936</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006624805625172231</v>
+        <v>0.006624805625172246</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5612585549312774</v>
+        <v>0.5612585549312785</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.813360317430168</v>
+        <v>-1.813360317430219</v>
       </c>
       <c r="AQ319" t="n">
         <v>3.076923076923077</v>
@@ -52251,10 +52251,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.166818450294679</v>
+        <v>7.166818450294681</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.0958183511125501</v>
+        <v>-0.09581835111255188</v>
       </c>
       <c r="AK320" t="n">
         <v>7.158620349112049</v>
@@ -52263,16 +52263,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.09320704864741254</v>
+        <v>0.09320704864741212</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006594358041710158</v>
+        <v>0.006594358041710186</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5590514368572466</v>
+        <v>0.5590514368572459</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.89596672457632</v>
+        <v>-1.895966724576408</v>
       </c>
       <c r="AQ320" t="n">
         <v>1.515151515151515</v>
@@ -52416,10 +52416,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.157691007010206</v>
+        <v>7.157691007010208</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.0943908742587416</v>
+        <v>-0.09439087425874337</v>
       </c>
       <c r="AK321" t="n">
         <v>7.164942158928604</v>
@@ -52428,16 +52428,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.09491020692123933</v>
+        <v>0.09491020692123982</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006562900445417311</v>
+        <v>0.006562900445417306</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5551825155208145</v>
+        <v>0.5551825155208129</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.764565208721948</v>
+        <v>-1.76456520872203</v>
       </c>
       <c r="AQ321" t="n">
         <v>2.985074626865671</v>
@@ -52581,10 +52581,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.151776426431621</v>
+        <v>7.15177642643162</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.08777629673191356</v>
+        <v>-0.08777629673191267</v>
       </c>
       <c r="AK322" t="n">
         <v>7.154764404811184</v>
@@ -52593,16 +52593,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.097046810505102</v>
+        <v>0.0970468105051025</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006523984583215639</v>
+        <v>0.006523984583215632</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5522992358254805</v>
+        <v>0.5522992358254815</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.395417465036362</v>
+        <v>-1.395417465036313</v>
       </c>
       <c r="AQ322" t="n">
         <v>6.617647058823529</v>
@@ -52746,10 +52746,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.15099240431968</v>
+        <v>7.150992404319682</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.09309245238486596</v>
+        <v>-0.09309245238486774</v>
       </c>
       <c r="AK323" t="n">
         <v>7.150261540163492</v>
@@ -52758,16 +52758,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09904197982498698</v>
+        <v>0.09904197982498671</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006505848878330736</v>
+        <v>0.006505848878330779</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5500699492277152</v>
+        <v>0.5500699492277157</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.620209616693131</v>
+        <v>-1.62020961669321</v>
       </c>
       <c r="AQ323" t="n">
         <v>4.347826086956522</v>
@@ -52911,10 +52911,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.147140093605204</v>
+        <v>7.147140093605207</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.09314019278733277</v>
+        <v>-0.09314019278733543</v>
       </c>
       <c r="AK324" t="n">
         <v>7.148879230661717</v>
@@ -52923,16 +52923,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.1013300516539148</v>
+        <v>0.1013300516539142</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006479631055951007</v>
+        <v>0.006479631055951091</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5478993564899665</v>
+        <v>0.5478993564899672</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.581244845226278</v>
+        <v>-1.581244845226393</v>
       </c>
       <c r="AQ324" t="n">
         <v>3.571428571428572</v>
@@ -53082,22 +53082,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK325" t="n">
-        <v>7.145816711184184</v>
+        <v>7.145816711184185</v>
       </c>
       <c r="AL325" t="n">
-        <v>-0.09881677984873516</v>
+        <v>-0.09881677984873605</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.1033273874042088</v>
+        <v>0.1033273874042092</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006468712737497662</v>
+        <v>0.006468712737497656</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5455500876237902</v>
+        <v>0.5455500876237913</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.660158210133191</v>
+        <v>-1.660158210133175</v>
       </c>
       <c r="AQ325" t="n">
         <v>2.112676056338028</v>
@@ -53244,7 +53244,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.1028262052267701</v>
+        <v>-0.102826205226771</v>
       </c>
       <c r="AK326" t="n">
         <v>7.139092738717567</v>
@@ -53253,16 +53253,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.1056457020972507</v>
+        <v>0.1056457020972505</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006435041090934165</v>
+        <v>0.006435041090934217</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5433399026839665</v>
+        <v>0.5433399026839674</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.94150056920768</v>
+        <v>-1.941500569207702</v>
       </c>
       <c r="AQ326" t="n">
         <v>2.777777777777778</v>
@@ -53409,7 +53409,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.099096096614959</v>
+        <v>-0.09909609661495811</v>
       </c>
       <c r="AK327" t="n">
         <v>7.140479586010682</v>
@@ -53418,16 +53418,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.10768023901916</v>
+        <v>0.1076802390191602</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006405465077205547</v>
+        <v>0.006405465077205527</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5402459241219614</v>
+        <v>0.5402459241219618</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.714497414188951</v>
+        <v>-1.714497414188894</v>
       </c>
       <c r="AQ327" t="n">
         <v>2.73972602739726</v>
@@ -53571,10 +53571,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI328" t="n">
-        <v>7.145743344370562</v>
+        <v>7.145743344370558</v>
       </c>
       <c r="AJ328" t="n">
-        <v>-0.1052431803385794</v>
+        <v>-0.1052431803385758</v>
       </c>
       <c r="AK328" t="n">
         <v>7.136632587022158</v>
@@ -53583,16 +53583,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1100130126862077</v>
+        <v>0.1100130126862084</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.006366554765990282</v>
+        <v>0.00636655476599019</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5375708073661647</v>
+        <v>0.5375708073661639</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.938373670414857</v>
+        <v>-1.938373670414687</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.702702702702703</v>
@@ -53748,16 +53748,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1122475627674583</v>
+        <v>0.1122475627674581</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.006337265512462553</v>
+        <v>0.00633726551246258</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5341613739773245</v>
+        <v>0.5341613739773232</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.591025362058573</v>
+        <v>-1.591025362058569</v>
       </c>
       <c r="AQ329" t="n">
         <v>3.333333333333334</v>
@@ -53901,10 +53901,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI330" t="n">
-        <v>7.142519733033009</v>
+        <v>7.14251973303301</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.1016195026252946</v>
+        <v>-0.1016195026252955</v>
       </c>
       <c r="AK330" t="n">
         <v>7.135172643569136</v>
@@ -53913,16 +53913,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.1146509166068179</v>
+        <v>0.114650916606818</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006337163869517243</v>
+        <v>0.006337163869517234</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5319767312874306</v>
+        <v>0.5319767312874311</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.685657147129841</v>
+        <v>-1.685657147129874</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.631578947368421</v>
@@ -54078,16 +54078,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1171965158426952</v>
+        <v>0.1171965158426948</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.006367653503792481</v>
+        <v>0.00636765350379247</v>
       </c>
       <c r="AO331" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP331" t="n">
-        <v>-2.151331574347173</v>
+        <v>-2.151331574347164</v>
       </c>
       <c r="AQ331" t="n">
         <v>1.298701298701299</v>
@@ -54231,10 +54231,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI332" t="n">
-        <v>7.140851085964109</v>
+        <v>7.140851085964112</v>
       </c>
       <c r="AJ332" t="n">
-        <v>-0.1128512080344217</v>
+        <v>-0.1128512080344244</v>
       </c>
       <c r="AK332" t="n">
         <v>7.142783913375006</v>
@@ -54243,16 +54243,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.119227205240256</v>
+        <v>0.1192272052402563</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.006383133038709798</v>
+        <v>0.00638313303870985</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5243060286247103</v>
+        <v>0.5243060286247104</v>
       </c>
       <c r="AP332" t="n">
-        <v>-2.038368479509989</v>
+        <v>-2.038368479510088</v>
       </c>
       <c r="AQ332" t="n">
         <v>2.564102564102564</v>
@@ -54396,10 +54396,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI333" t="n">
-        <v>7.139245392969567</v>
+        <v>7.139245392969565</v>
       </c>
       <c r="AJ333" t="n">
-        <v>-0.1112455150398795</v>
+        <v>-0.1112455150398777</v>
       </c>
       <c r="AK333" t="n">
         <v>7.141836927013541</v>
@@ -54408,16 +54408,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1211746327267789</v>
+        <v>0.1211746327267792</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006404909068509476</v>
+        <v>0.006404909068509461</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.5185318197199045</v>
+        <v>0.518531819719905</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.909934895071841</v>
+        <v>-1.909934895071758</v>
       </c>
       <c r="AQ333" t="n">
         <v>3.79746835443038</v>
@@ -54561,10 +54561,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI334" t="n">
-        <v>7.136520216281903</v>
+        <v>7.136520216281902</v>
       </c>
       <c r="AJ334" t="n">
-        <v>-0.108520338352216</v>
+        <v>-0.1085203383522142</v>
       </c>
       <c r="AK334" t="n">
         <v>7.13958125183462</v>
@@ -54573,16 +54573,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1228335954516147</v>
+        <v>0.1228335954516143</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006430223802628449</v>
+        <v>0.006430223802628476</v>
       </c>
       <c r="AO334" t="n">
-        <v>0.5122974965428477</v>
+        <v>0.5122974965428486</v>
       </c>
       <c r="AP334" t="n">
-        <v>-1.748195911884376</v>
+        <v>-1.748195911884297</v>
       </c>
       <c r="AQ334" t="n">
         <v>5</v>
@@ -54741,13 +54741,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006430805642792636</v>
+        <v>0.006430805642792618</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.5056597011855208</v>
+        <v>0.5056597011855207</v>
       </c>
       <c r="AP335" t="n">
-        <v>-2.518543666780585</v>
+        <v>-2.518543666780579</v>
       </c>
       <c r="AQ335" t="n">
         <v>1.234567901234568</v>
@@ -54891,10 +54891,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.136562857934749</v>
+        <v>7.13656285793475</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.140462909051692</v>
+        <v>-0.1404629090516929</v>
       </c>
       <c r="AK336" t="n">
         <v>7.132705938528055</v>
@@ -54906,13 +54906,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006419568115912044</v>
+        <v>0.006419568115912051</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.4979995576252224</v>
+        <v>0.4979995576252233</v>
       </c>
       <c r="AP336" t="n">
-        <v>-2.78015736493144</v>
+        <v>-2.780157364931463</v>
       </c>
       <c r="AQ336" t="n">
         <v>1.219512195121951</v>
@@ -55056,10 +55056,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.135435320996258</v>
+        <v>7.135435320996254</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.1393353721132016</v>
+        <v>-0.1393353721131971</v>
       </c>
       <c r="AK337" t="n">
         <v>7.134470034900207</v>
@@ -55068,16 +55068,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1290155516631957</v>
+        <v>0.1290155516631951</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006423940675024581</v>
+        <v>0.006423940675024553</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.489456156051701</v>
+        <v>0.4894561560517011</v>
       </c>
       <c r="AP337" t="n">
-        <v>-2.604030180601917</v>
+        <v>-2.604030180601759</v>
       </c>
       <c r="AQ337" t="n">
         <v>3.012048192771084</v>
@@ -55221,10 +55221,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI338" t="n">
-        <v>7.135221482968309</v>
+        <v>7.135221482968312</v>
       </c>
       <c r="AJ338" t="n">
-        <v>-0.1391215340852527</v>
+        <v>-0.1391215340852554</v>
       </c>
       <c r="AK338" t="n">
         <v>7.133435115388912</v>
@@ -55233,16 +55233,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM338" t="n">
-        <v>0.1313692321875789</v>
+        <v>0.1313692321875792</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006422605647444513</v>
+        <v>0.006422605647444502</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.4811392039904447</v>
+        <v>0.4811392039904442</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.481964435352737</v>
+        <v>-2.481964435352832</v>
       </c>
       <c r="AQ338" t="n">
         <v>4.166666666666666</v>
@@ -55386,10 +55386,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.129120131622726</v>
+        <v>7.129120131622732</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.1360199653019256</v>
+        <v>-0.1360199653019309</v>
       </c>
       <c r="AK339" t="n">
         <v>7.132510325395203</v>
@@ -55398,16 +55398,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM339" t="n">
-        <v>0.1334873867685099</v>
+        <v>0.1334873867685108</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006388619079873509</v>
+        <v>0.006388619079873553</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4724960612931043</v>
+        <v>0.4724960612931048</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.28166103682911</v>
+        <v>-2.281661036829281</v>
       </c>
       <c r="AQ339" t="n">
         <v>5.294117647058823</v>
@@ -55563,16 +55563,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1357975915367747</v>
+        <v>0.1357975915367741</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006324213907675097</v>
+        <v>0.006324213907675122</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.4647750649852552</v>
+        <v>0.4647750649852558</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.358420913553955</v>
+        <v>-2.358420913553941</v>
       </c>
       <c r="AQ340" t="n">
         <v>2.906976744186047</v>
@@ -55716,10 +55716,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.122818285283529</v>
+        <v>7.122818285283532</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1394184172720543</v>
+        <v>-0.1394184172720578</v>
       </c>
       <c r="AK341" t="n">
         <v>7.123271418608565</v>
@@ -55728,16 +55728,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1386638579210687</v>
+        <v>0.1386638579210689</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006222091828703702</v>
+        <v>0.006222091828703747</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4565264017486783</v>
+        <v>0.4565264017486775</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.224844990801964</v>
+        <v>-2.224844990802061</v>
       </c>
       <c r="AQ341" t="n">
         <v>4.022988505747126</v>
@@ -55893,16 +55893,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1423176752089984</v>
+        <v>0.1423176752089981</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006093783709292283</v>
+        <v>0.006093783709292289</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4497199830569224</v>
+        <v>0.4497199830569214</v>
       </c>
       <c r="AP342" t="n">
-        <v>-1.837002738664126</v>
+        <v>-1.837002738664109</v>
       </c>
       <c r="AQ342" t="n">
         <v>9.090909090909092</v>
@@ -56046,10 +56046,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI343" t="n">
-        <v>7.133160404869088</v>
+        <v>7.13316040486909</v>
       </c>
       <c r="AJ343" t="n">
-        <v>-0.1496604010543905</v>
+        <v>-0.1496604010543923</v>
       </c>
       <c r="AK343" t="n">
         <v>7.117219286120759</v>
@@ -56061,13 +56061,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.005984113522022494</v>
+        <v>0.005984113522022499</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4438783751010233</v>
+        <v>0.4438783751010228</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.408870938511893</v>
+        <v>-2.408870938511925</v>
       </c>
       <c r="AQ343" t="n">
         <v>7.865168539325842</v>
@@ -56211,10 +56211,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI344" t="n">
-        <v>7.12965322071209</v>
+        <v>7.129653220712091</v>
       </c>
       <c r="AJ344" t="n">
-        <v>-0.1524531894315722</v>
+        <v>-0.152453189431573</v>
       </c>
       <c r="AK344" t="n">
         <v>7.126254605494273</v>
@@ -56223,16 +56223,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1503893187551748</v>
+        <v>0.1503893187551739</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.005963146506628741</v>
+        <v>0.005963146506628762</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.4412018736247373</v>
+        <v>0.441201873624737</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.401162905304161</v>
+        <v>-2.401162905304164</v>
       </c>
       <c r="AQ344" t="n">
         <v>7.777777777777777</v>
@@ -56376,10 +56376,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI345" t="n">
-        <v>7.128380415829728</v>
+        <v>7.128380415829729</v>
       </c>
       <c r="AJ345" t="n">
-        <v>-0.1552802304354408</v>
+        <v>-0.1552802304354417</v>
       </c>
       <c r="AK345" t="n">
         <v>7.124321202568002</v>
@@ -56388,16 +56388,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1546287435667592</v>
+        <v>0.1546287435667593</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.005975981199024843</v>
+        <v>0.005975981199024824</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.4385827444686599</v>
+        <v>0.43858274446866</v>
       </c>
       <c r="AP345" t="n">
-        <v>-2.393976252441821</v>
+        <v>-2.393976252441823</v>
       </c>
       <c r="AQ345" t="n">
         <v>7.692307692307692</v>
@@ -56541,10 +56541,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.124429161493117</v>
+        <v>7.124429161493114</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.1469291996400894</v>
+        <v>-0.1469291996400868</v>
       </c>
       <c r="AK346" t="n">
         <v>7.121152072356459</v>
@@ -56553,16 +56553,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM346" t="n">
-        <v>0.1587808126513012</v>
+        <v>0.1587808126513008</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.00589922161993145</v>
+        <v>0.005899221619931436</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4336499747757657</v>
+        <v>0.4336499747757655</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.079541096596248</v>
+        <v>-2.079541096596154</v>
       </c>
       <c r="AQ346" t="n">
         <v>16.30434782608696</v>
@@ -56718,16 +56718,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1636493008978488</v>
+        <v>0.1636493008978486</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005897856672615054</v>
+        <v>0.005897856672615022</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.434304834398872</v>
+        <v>0.4343048343988722</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.39714021279369</v>
+        <v>-2.397140212793674</v>
       </c>
       <c r="AQ347" t="n">
         <v>13.97849462365591</v>
@@ -56871,10 +56871,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.141397967314147</v>
+        <v>7.141397967314151</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1753978872055049</v>
+        <v>-0.1753978872055084</v>
       </c>
       <c r="AK348" t="n">
         <v>7.12802266215534</v>
@@ -56883,16 +56883,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1676675897666615</v>
+        <v>0.1676675897666616</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005952601612807557</v>
+        <v>0.005952601612807589</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4322693842687806</v>
+        <v>0.4322693842687804</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.687935210063305</v>
+        <v>-2.687935210063377</v>
       </c>
       <c r="AQ348" t="n">
         <v>12.76595744680851</v>
@@ -57036,10 +57036,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.140412492855504</v>
+        <v>7.140412492855501</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1723124219021352</v>
+        <v>-0.1723124219021317</v>
       </c>
       <c r="AK349" t="n">
         <v>7.137738577466652</v>
@@ -57048,16 +57048,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1710383543493657</v>
+        <v>0.1710383543493662</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.006068444256835448</v>
+        <v>0.00606844425683546</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4285062718639565</v>
+        <v>0.4285062718639572</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.500349987380126</v>
+        <v>-2.500349987380015</v>
       </c>
       <c r="AQ349" t="n">
         <v>20</v>
@@ -57201,10 +57201,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI350" t="n">
-        <v>7.138020503721587</v>
+        <v>7.138020503721584</v>
       </c>
       <c r="AJ350" t="n">
-        <v>-0.169920432768218</v>
+        <v>-0.1699204327682153</v>
       </c>
       <c r="AK350" t="n">
         <v>7.13663078035759</v>
@@ -57213,16 +57213,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.176195682434215</v>
+        <v>0.1761956824342154</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.006402952059750722</v>
+        <v>0.006402952059750703</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.4374093872433962</v>
+        <v>0.4374093872433956</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.351093557116616</v>
+        <v>-2.351093557116537</v>
       </c>
       <c r="AQ350" t="n">
         <v>19.79166666666666</v>
@@ -57366,28 +57366,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.136830620687384</v>
+        <v>7.136830620687383</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.1769307183436339</v>
+        <v>-0.1769307183436331</v>
       </c>
       <c r="AK351" t="n">
-        <v>7.14004901784002</v>
+        <v>7.140049017840021</v>
       </c>
       <c r="AL351" t="n">
-        <v>-0.1801491154962704</v>
+        <v>-0.1801491154962713</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1796308914905975</v>
+        <v>0.1796308914905974</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.006948414844703821</v>
+        <v>0.006948414844703805</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4458727441769479</v>
+        <v>0.4458727441769483</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.441641144721009</v>
+        <v>-2.441641144720979</v>
       </c>
       <c r="AQ351" t="n">
         <v>18.04123711340206</v>
@@ -57527,10 +57527,10 @@
         <v/>
       </c>
       <c r="AI352" t="n">
-        <v>7.133638579266565</v>
+        <v>7.13363857926656</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1699387616090942</v>
+        <v>-0.1699387616090897</v>
       </c>
       <c r="AK352" t="n">
         <v>7.13798584867198</v>
@@ -57539,16 +57539,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1829391475229931</v>
+        <v>0.1829391475229935</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.007602047321544403</v>
+        <v>0.00760204732154433</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4545618931940824</v>
+        <v>0.4545618931940826</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.194466762595206</v>
+        <v>-2.194466762595095</v>
       </c>
       <c r="AQ352" t="n">
         <v>27.04081632653061</v>
@@ -57692,10 +57692,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.12640946890857</v>
+        <v>7.126409468908567</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.1538094856932375</v>
+        <v>-0.1538094856932348</v>
       </c>
       <c r="AK353" t="n">
         <v>7.138565167526504</v>
@@ -57704,16 +57704,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.1834764543657148</v>
+        <v>0.1834764543657157</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.007712839302340374</v>
+        <v>0.007712839302340297</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4511257152112026</v>
+        <v>0.4511257152112024</v>
       </c>
       <c r="AP353" t="n">
-        <v>-1.753575478488488</v>
+        <v>-1.753575478488427</v>
       </c>
       <c r="AQ353" t="n">
         <v>22.9179550608122</v>
@@ -57857,10 +57857,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.110999512759045</v>
+        <v>7.110999512759042</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1383995295437126</v>
+        <v>-0.1383995295437099</v>
       </c>
       <c r="AK354" t="n">
         <v>7.137040595974374</v>
@@ -57869,16 +57869,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1869739626316104</v>
+        <v>0.1869739626316108</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.00835460951998479</v>
+        <v>0.008354609519984808</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4618871834350119</v>
+        <v>0.4618871834350127</v>
       </c>
       <c r="AP354" t="n">
-        <v>-1.352715240325604</v>
+        <v>-1.352715240325543</v>
       </c>
       <c r="AQ354" t="n">
         <v>17.08585858585858</v>
@@ -58034,16 +58034,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1901371272406391</v>
+        <v>0.1901371272406383</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.008787529863310189</v>
+        <v>0.008787529863310259</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4631528842621211</v>
+        <v>0.4631528842621208</v>
       </c>
       <c r="AP355" t="n">
-        <v>-1.39041914507014</v>
+        <v>-1.390419145070144</v>
       </c>
       <c r="AQ355" t="n">
         <v>10.43564356435644</v>
@@ -58187,10 +58187,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI356" t="n">
-        <v>7.10229338126412</v>
+        <v>7.102293381264122</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1477931828998624</v>
+        <v>-0.1477931828998642</v>
       </c>
       <c r="AK356" t="n">
         <v>7.113436809075056</v>
@@ -58199,16 +58199,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.1939456835457532</v>
+        <v>0.193945683545753</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.009306466714917722</v>
+        <v>0.009306466714917755</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4650211967660294</v>
+        <v>0.4650211967660295</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.536498147639932</v>
+        <v>-1.536498147639978</v>
       </c>
       <c r="AQ356" t="n">
         <v>11.33275092215104</v>
@@ -58364,16 +58364,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1968971496416331</v>
+        <v>0.1968971496416338</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.009915270508004642</v>
+        <v>0.009915270508004639</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4658112293095933</v>
+        <v>0.4658112293095935</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.307847521398089</v>
+        <v>-1.307847521398092</v>
       </c>
       <c r="AQ357" t="n">
         <v>11.67904054825814</v>
@@ -58529,16 +58529,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.2001574773810679</v>
+        <v>0.200157477381068</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.01045224758824684</v>
+        <v>0.01045224758824685</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4652001227613064</v>
+        <v>0.4652001227613058</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.576101274924247</v>
+        <v>-1.57610127492425</v>
       </c>
       <c r="AQ358" t="n">
         <v>5.293129200896192</v>
@@ -58682,10 +58682,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI359" t="n">
-        <v>7.112155432918446</v>
+        <v>7.112155432918444</v>
       </c>
       <c r="AJ359" t="n">
-        <v>-0.1611552192953987</v>
+        <v>-0.1611552192953969</v>
       </c>
       <c r="AK359" t="n">
         <v>7.115439870473561</v>
@@ -58694,16 +58694,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.2059164257597553</v>
+        <v>0.2059164257597547</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.01095806236007055</v>
+        <v>0.0109580623600705</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4647071558511969</v>
+        <v>0.4647071558511972</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.776827470000052</v>
+        <v>-1.776827470000016</v>
       </c>
       <c r="AQ359" t="n">
         <v>6.703296703296703</v>
@@ -58859,16 +58859,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.2103846028094628</v>
+        <v>0.2103846028094625</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.01138655624224677</v>
+        <v>0.01138655624224671</v>
       </c>
       <c r="AO360" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.805481046668102</v>
+        <v>-1.805481046668107</v>
       </c>
       <c r="AQ360" t="n">
         <v>11.40161725067385</v>
@@ -59012,10 +59012,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI361" t="n">
-        <v>7.110775793344653</v>
+        <v>7.110775793344654</v>
       </c>
       <c r="AJ361" t="n">
-        <v>-0.1730759985753663</v>
+        <v>-0.1730759985753672</v>
       </c>
       <c r="AK361" t="n">
         <v>7.127056499711662</v>
@@ -59024,16 +59024,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2137349114935569</v>
+        <v>0.2137349114935566</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.01184277521890661</v>
+        <v>0.0118427752189066</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4573024605378193</v>
+        <v>0.4573024605378192</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.973713661270149</v>
+        <v>-1.973713661270174</v>
       </c>
       <c r="AQ361" t="n">
         <v>12.72262387585964</v>
@@ -59189,16 +59189,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2192999169256238</v>
+        <v>0.2192999169256231</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01242692746354282</v>
+        <v>0.01242692746354283</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4593518446085588</v>
+        <v>0.4593518446085587</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.523267153843554</v>
+        <v>-1.523267153843557</v>
       </c>
       <c r="AQ362" t="n">
         <v>14.43838698511596</v>
@@ -59342,28 +59342,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI363" t="n">
-        <v>7.095070446253633</v>
+        <v>7.095070446253632</v>
       </c>
       <c r="AJ363" t="n">
-        <v>-0.1572705156811232</v>
+        <v>-0.1572705156811223</v>
       </c>
       <c r="AK363" t="n">
-        <v>7.099084322920755</v>
+        <v>7.099084322920754</v>
       </c>
       <c r="AL363" t="n">
-        <v>-0.1612843923482448</v>
+        <v>-0.1612843923482439</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2273791016644669</v>
+        <v>0.2273791016644665</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01301934706839999</v>
+        <v>0.01301934706840001</v>
       </c>
       <c r="AO363" t="n">
-        <v>0.4655241261491886</v>
+        <v>0.4655241261491888</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.557058675067598</v>
+        <v>-1.557058675067582</v>
       </c>
       <c r="AQ363" t="n">
         <v>12.45752633367312</v>
@@ -59507,10 +59507,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI364" t="n">
-        <v>7.077412848446851</v>
+        <v>7.077412848446856</v>
       </c>
       <c r="AJ364" t="n">
-        <v>-0.1386129903535895</v>
+        <v>-0.138612990353594</v>
       </c>
       <c r="AK364" t="n">
         <v>7.107752072150756</v>
@@ -59519,16 +59519,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2346680713248289</v>
+        <v>0.2346680713248287</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01366280940279216</v>
+        <v>0.01366280940279221</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4682122340216202</v>
+        <v>0.4682122340216205</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.117810522366985</v>
+        <v>-1.117810522367088</v>
       </c>
       <c r="AQ364" t="n">
         <v>20.07506255212677</v>
@@ -59672,10 +59672,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI365" t="n">
-        <v>7.067855559671527</v>
+        <v>7.067855559671529</v>
       </c>
       <c r="AJ365" t="n">
-        <v>-0.1458556283360775</v>
+        <v>-0.1458556283360801</v>
       </c>
       <c r="AK365" t="n">
         <v>7.100856094477853</v>
@@ -59684,16 +59684,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2404731763378842</v>
+        <v>0.2404731763378833</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01427110593278799</v>
+        <v>0.01427110593278805</v>
       </c>
       <c r="AO365" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.26840273524282</v>
+        <v>-1.268402735242881</v>
       </c>
       <c r="AQ365" t="n">
         <v>19.46764946764947</v>
@@ -59837,10 +59837,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.081794385763164</v>
+        <v>7.081794385763168</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.1711942003688769</v>
+        <v>-0.1711942003688813</v>
       </c>
       <c r="AK366" t="n">
         <v>7.090764621929079</v>
@@ -59849,16 +59849,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2453259423721931</v>
+        <v>0.2453259423721924</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01502424352484369</v>
+        <v>0.01502424352484376</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4756424387980298</v>
+        <v>0.4756424387980304</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.810992524290867</v>
+        <v>-1.810992524290963</v>
       </c>
       <c r="AQ366" t="n">
         <v>15.74565637065637</v>
@@ -60002,10 +60002,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.068234493406102</v>
+        <v>7.068234493406101</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1557345887735337</v>
+        <v>-0.1557345887735329</v>
       </c>
       <c r="AK367" t="n">
         <v>7.110983013755962</v>
@@ -60014,16 +60014,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2481172514763508</v>
+        <v>0.2481172514763511</v>
       </c>
       <c r="AN367" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4781214750573159</v>
+        <v>0.4781214750573156</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.441711805760857</v>
+        <v>-1.441711805760835</v>
       </c>
       <c r="AQ367" t="n">
         <v>19.59544879898862</v>
@@ -60167,28 +60167,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.047011693433886</v>
+        <v>7.04701169343388</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1469114622632315</v>
+        <v>-0.1469114622632253</v>
       </c>
       <c r="AK368" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL368" t="n">
-        <v>-0.1936362268489642</v>
+        <v>-0.1936362268489633</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2517176519946896</v>
+        <v>0.2517176519946887</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01672959897123732</v>
+        <v>0.01672959897123727</v>
       </c>
       <c r="AO368" t="n">
-        <v>0.482044795280705</v>
+        <v>0.4820447952807055</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.229621277013041</v>
+        <v>-1.229621277012902</v>
       </c>
       <c r="AQ368" t="n">
         <v>18.94503959012576</v>
@@ -60332,28 +60332,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.043635211714482</v>
+        <v>7.043635211714486</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.135635219343877</v>
+        <v>-0.1356352193438806</v>
       </c>
       <c r="AK369" t="n">
-        <v>7.069112439760902</v>
+        <v>7.069112439760901</v>
       </c>
       <c r="AL369" t="n">
-        <v>-0.1611124473902965</v>
+        <v>-0.1611124473902956</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2568291528619773</v>
+        <v>0.2568291528619769</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.01758784222749221</v>
+        <v>0.0175878422274923</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.4888256589627545</v>
+        <v>0.488825658962754</v>
       </c>
       <c r="AP369" t="n">
-        <v>-0.968532398806207</v>
+        <v>-0.9685323988062863</v>
       </c>
       <c r="AQ369" t="n">
         <v>24.43554538520213</v>
@@ -60497,10 +60497,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.045320696769622</v>
+        <v>7.04532069676962</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1373207043990163</v>
+        <v>-0.1373207043990146</v>
       </c>
       <c r="AK370" t="n">
         <v>7.067486653848666</v>
@@ -60509,16 +60509,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2611441025487395</v>
+        <v>0.2611441025487396</v>
       </c>
       <c r="AN370" t="n">
-        <v>0.01863884916361525</v>
+        <v>0.01863884916361523</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4958891106408185</v>
+        <v>0.4958891106408189</v>
       </c>
       <c r="AP370" t="n">
-        <v>-0.9976392040422545</v>
+        <v>-0.9976392040422146</v>
       </c>
       <c r="AQ370" t="n">
         <v>22.05397301349325</v>
@@ -60662,10 +60662,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.052957186540217</v>
+        <v>7.052957186540212</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1449571941696117</v>
+        <v>-0.1449571941696064</v>
       </c>
       <c r="AK371" t="n">
         <v>7.066060765041626</v>
@@ -60674,16 +60674,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2646928033319798</v>
+        <v>0.2646928033319788</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.01961447184998982</v>
+        <v>0.0196144718499898</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.4990325267638059</v>
+        <v>0.4990325267638065</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.157136980079441</v>
+        <v>-1.157136980079324</v>
       </c>
       <c r="AQ371" t="n">
         <v>19.31181844974948</v>
@@ -60827,28 +60827,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.055218091951101</v>
+        <v>7.055218091951103</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.1472180995804955</v>
+        <v>-0.1472180995804973</v>
       </c>
       <c r="AK372" t="n">
-        <v>7.064646745753511</v>
+        <v>7.06464674575351</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1566467533829057</v>
+        <v>-0.1566467533829048</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2692457951306195</v>
+        <v>0.2692457951306194</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.02045122459205889</v>
+        <v>0.02045122459205891</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.5009265659871953</v>
+        <v>0.5009265659871951</v>
       </c>
       <c r="AP372" t="n">
-        <v>-1.195249767038319</v>
+        <v>-1.19524976703836</v>
       </c>
       <c r="AQ372" t="n">
         <v>18.30363610024627</v>
@@ -60992,10 +60992,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.050463258619342</v>
+        <v>7.050463258619345</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1423631304455135</v>
+        <v>-0.1423631304455171</v>
       </c>
       <c r="AK373" t="n">
         <v>7.063274589921972</v>
@@ -61004,16 +61004,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2738618637550985</v>
+        <v>0.2738618637550991</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.02103732430364852</v>
+        <v>0.02103732430364855</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.5007948901071727</v>
+        <v>0.5007948901071723</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.076832434365704</v>
+        <v>-1.076832434365783</v>
       </c>
       <c r="AQ373" t="n">
         <v>22.79233727389261</v>
@@ -61330,16 +61330,16 @@
         <v/>
       </c>
       <c r="AM375" t="n">
-        <v>0.280344119587675</v>
+        <v>0.2803441195876753</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.02230845224183686</v>
+        <v>0.02230845224183688</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.5036776407221306</v>
+        <v>0.5036776407221312</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.233165332293828</v>
+        <v>-1.233165332293827</v>
       </c>
       <c r="AQ375" t="n">
         <v>25</v>
@@ -61483,10 +61483,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.056824809597053</v>
+        <v>7.056824809597052</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1737247767906567</v>
+        <v>-0.1737247767906558</v>
       </c>
       <c r="AK376" t="n">
         <v>7.071238163852278</v>
@@ -61495,16 +61495,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2841407798055449</v>
+        <v>0.2841407798055452</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02276542233315987</v>
+        <v>0.02276542233315985</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5036956996297977</v>
+        <v>0.5036956996297983</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.733307247689765</v>
+        <v>-1.733307247689745</v>
       </c>
       <c r="AQ376" t="n">
         <v>21.90082644628099</v>
@@ -61648,10 +61648,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI377" t="n">
-        <v>7.04726592259491</v>
+        <v>7.047265922594908</v>
       </c>
       <c r="AJ377" t="n">
-        <v>-0.1780656929501347</v>
+        <v>-0.178065692950133</v>
       </c>
       <c r="AK377" t="n">
         <v>7.075283303194255</v>
@@ -61660,16 +61660,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM377" t="n">
-        <v>0.2869603504542605</v>
+        <v>0.2869603504542598</v>
       </c>
       <c r="AN377" t="n">
-        <v>0.02324367830537832</v>
+        <v>0.02324367830537833</v>
       </c>
       <c r="AO377" t="n">
-        <v>0.5029697249741727</v>
+        <v>0.5029697249741724</v>
       </c>
       <c r="AP377" t="n">
-        <v>-1.797075952444579</v>
+        <v>-1.797075952444542</v>
       </c>
       <c r="AQ377" t="n">
         <v>10.65573770491803</v>
@@ -61813,10 +61813,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI378" t="n">
-        <v>7.030237372659574</v>
+        <v>7.030237372659579</v>
       </c>
       <c r="AJ378" t="n">
-        <v>-0.189337428354154</v>
+        <v>-0.1893374283541593</v>
       </c>
       <c r="AK378" t="n">
         <v>7.061088020066238</v>
@@ -61825,16 +61825,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM378" t="n">
-        <v>0.2909556153842325</v>
+        <v>0.2909556153842324</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02343150180192449</v>
+        <v>0.02343150180192457</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.501187497763653</v>
+        <v>0.5011874977636526</v>
       </c>
       <c r="AP378" t="n">
-        <v>-2.001502618066346</v>
+        <v>-2.001502618066459</v>
       </c>
       <c r="AQ378" t="n">
         <v>2.439024390243902</v>
@@ -61978,10 +61978,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.074556523891909</v>
+        <v>7.074556523891907</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.2166563812222311</v>
+        <v>-0.2166563812222293</v>
       </c>
       <c r="AK379" t="n">
         <v>7.045371831199247</v>
@@ -61990,16 +61990,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2963660759601011</v>
+        <v>0.2963660759601009</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02388105320115907</v>
+        <v>0.02388105320115906</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5011837436137521</v>
+        <v>0.5011837436137511</v>
       </c>
       <c r="AP379" t="n">
-        <v>-2.513652032800262</v>
+        <v>-2.513652032800223</v>
       </c>
       <c r="AQ379" t="n">
         <v>14.91935483870968</v>
@@ -62143,10 +62143,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.103552248295395</v>
+        <v>7.103552248295403</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.2215522788129736</v>
+        <v>-0.2215522788129807</v>
       </c>
       <c r="AK380" t="n">
         <v>7.078406423284397</v>
@@ -62155,16 +62155,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.29984079129971</v>
+        <v>0.2998407912997099</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02427773372157399</v>
+        <v>0.02427773372157407</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.4964684575356704</v>
+        <v>0.4964684575356701</v>
       </c>
       <c r="AP380" t="n">
-        <v>-2.537533612885102</v>
+        <v>-2.537533612885238</v>
       </c>
       <c r="AQ380" t="n">
         <v>19.6</v>
@@ -62320,16 +62320,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.3035220749319825</v>
+        <v>0.3035220749319821</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02465824743687012</v>
+        <v>0.02465824743687013</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.4899948718309226</v>
+        <v>0.4899948718309223</v>
       </c>
       <c r="AP381" t="n">
-        <v>-2.242993256171588</v>
+        <v>-2.242993256171579</v>
       </c>
       <c r="AQ381" t="n">
         <v>23.41269841269841</v>
@@ -62473,10 +62473,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.12777959440025</v>
+        <v>7.127779594400253</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.2307797584322326</v>
+        <v>-0.2307797584322353</v>
       </c>
       <c r="AK382" t="n">
         <v>7.110202206771168</v>
@@ -62485,16 +62485,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.3056770963992281</v>
+        <v>0.3056770963992276</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02512392944114572</v>
+        <v>0.02512392944114575</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.4836004785809395</v>
+        <v>0.48360047858094</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.58274150505993</v>
+        <v>-2.58274150505997</v>
       </c>
       <c r="AQ382" t="n">
         <v>22.83464566929134</v>
@@ -62638,28 +62638,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.117424820782309</v>
+        <v>7.117424820782308</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2204249848142918</v>
+        <v>-0.2204249848142901</v>
       </c>
       <c r="AK383" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL383" t="n">
-        <v>-0.2182210070512509</v>
+        <v>-0.21822100705125</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.3083414575758074</v>
+        <v>0.3083414575758079</v>
       </c>
       <c r="AN383" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.474982443940299</v>
+        <v>0.4749824439402989</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.317107881992696</v>
+        <v>-2.317107881992653</v>
       </c>
       <c r="AQ383" t="n">
         <v>25.390625</v>
@@ -62803,10 +62803,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI384" t="n">
-        <v>7.116315246651977</v>
+        <v>7.116315246651979</v>
       </c>
       <c r="AJ384" t="n">
-        <v>-0.2198151360257565</v>
+        <v>-0.2198151360257583</v>
       </c>
       <c r="AK384" t="n">
         <v>7.112470209890858</v>
@@ -62815,16 +62815,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3094443575020182</v>
+        <v>0.3094443575020188</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.0257875072203187</v>
+        <v>0.02578750722031873</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.4671039145039241</v>
+        <v>0.467103914503924</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.250106354245415</v>
+        <v>-2.25010635424544</v>
       </c>
       <c r="AQ384" t="n">
         <v>25.1937984496124</v>
@@ -62968,28 +62968,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.109165799046384</v>
+        <v>7.109165799046382</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.1981660241135224</v>
+        <v>-0.1981660241135206</v>
       </c>
       <c r="AK385" t="n">
-        <v>7.105086649080124</v>
+        <v>7.105086649080123</v>
       </c>
       <c r="AL385" t="n">
-        <v>-0.1940868741472626</v>
+        <v>-0.1940868741472617</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3112159059696454</v>
+        <v>0.3112159059696449</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02619128791084346</v>
+        <v>0.02619128791084347</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4597800393113445</v>
+        <v>0.4597800393113443</v>
       </c>
       <c r="AP385" t="n">
-        <v>-1.804694563734948</v>
+        <v>-1.804694563734907</v>
       </c>
       <c r="AQ385" t="n">
         <v>26.53846153846154</v>
@@ -63133,10 +63133,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.140476658697598</v>
+        <v>7.14047665869759</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2639765289978913</v>
+        <v>-0.2639765289978833</v>
       </c>
       <c r="AK386" t="n">
         <v>7.107009848336411</v>
@@ -63145,16 +63145,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3120213667410843</v>
+        <v>0.3120213667410841</v>
       </c>
       <c r="AN386" t="n">
-        <v>0.02660872919284657</v>
+        <v>0.02660872919284651</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.4527828726277016</v>
+        <v>0.4527828726277021</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.939625212524932</v>
+        <v>-2.939625212524785</v>
       </c>
       <c r="AQ386" t="n">
         <v>19.08396946564886</v>
@@ -63298,10 +63298,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.192104266103097</v>
+        <v>7.192104266103096</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.3266042928059782</v>
+        <v>-0.3266042928059765</v>
       </c>
       <c r="AK387" t="n">
         <v>7.130667004235951</v>
@@ -63310,16 +63310,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3119580514589064</v>
+        <v>0.3119580514589062</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.02723917591229313</v>
+        <v>0.02723917591229311</v>
       </c>
       <c r="AO387" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP387" t="n">
-        <v>-3.839693371807441</v>
+        <v>-3.839693371807415</v>
       </c>
       <c r="AQ387" t="n">
         <v>21.96969696969697</v>
@@ -63475,7 +63475,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3060770546706492</v>
+        <v>0.3060770546706496</v>
       </c>
       <c r="AN388" t="n">
         <v>0.02737088803905663</v>
@@ -63484,7 +63484,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP388" t="n">
-        <v>-3.702123811175261</v>
+        <v>-3.702123811175266</v>
       </c>
       <c r="AQ388" t="n">
         <v>19.54887218045113</v>
@@ -63628,10 +63628,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.16410590848237</v>
+        <v>7.164105908482372</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.2680058642318812</v>
+        <v>-0.2680058642318839</v>
       </c>
       <c r="AK389" t="n">
         <v>7.162206823443969</v>
@@ -63640,16 +63640,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3021518080029227</v>
+        <v>0.3021518080029217</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02724691784252931</v>
+        <v>0.02724691784252936</v>
       </c>
       <c r="AO389" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP389" t="n">
-        <v>-2.573075475175223</v>
+        <v>-2.573075475175267</v>
       </c>
       <c r="AQ389" t="n">
         <v>23.88059701492537</v>
@@ -63793,10 +63793,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.165713254747866</v>
+        <v>7.165713254747862</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.2102131288628559</v>
+        <v>-0.2102131288628524</v>
       </c>
       <c r="AK390" t="n">
         <v>7.141021818380439</v>
@@ -63805,16 +63805,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3004913268435098</v>
+        <v>0.3004913268435102</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02739193077523433</v>
+        <v>0.02739193077523432</v>
       </c>
       <c r="AO390" t="n">
-        <v>0.3752726470948202</v>
+        <v>0.3752726470948199</v>
       </c>
       <c r="AP390" t="n">
-        <v>-1.615899255612529</v>
+        <v>-1.615899255612474</v>
       </c>
       <c r="AQ390" t="n">
         <v>30.74074074074074</v>
@@ -63958,10 +63958,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI391" t="n">
-        <v>7.208249532027229</v>
+        <v>7.208249532027231</v>
       </c>
       <c r="AJ391" t="n">
-        <v>-0.3219494450521312</v>
+        <v>-0.321949445052133</v>
       </c>
       <c r="AK391" t="n">
         <v>7.146296571548195</v>
@@ -63970,16 +63970,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.2982197220770054</v>
+        <v>0.2982197220770058</v>
       </c>
       <c r="AN391" t="n">
-        <v>0.02742417953210363</v>
+        <v>0.02742417953210373</v>
       </c>
       <c r="AO391" t="n">
-        <v>0.3625782951332472</v>
+        <v>0.3625782951332475</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.262311010331393</v>
+        <v>-3.262311010331421</v>
       </c>
       <c r="AQ391" t="n">
         <v>25.36764705882353</v>
@@ -64123,28 +64123,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.193412187855718</v>
+        <v>7.193412187855726</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.3208121092729543</v>
+        <v>-0.3208121092729623</v>
       </c>
       <c r="AK392" t="n">
-        <v>7.176497065376474</v>
+        <v>7.176497065376473</v>
       </c>
       <c r="AL392" t="n">
-        <v>-0.3038969867937107</v>
+        <v>-0.3038969867937098</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.2910761841041076</v>
+        <v>0.2910761841041086</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02685747952387152</v>
+        <v>0.02685747952387156</v>
       </c>
       <c r="AO392" t="n">
-        <v>0.3370674577034428</v>
+        <v>0.3370674577034442</v>
       </c>
       <c r="AP392" t="n">
-        <v>-3.114608684051217</v>
+        <v>-3.114608684051328</v>
       </c>
       <c r="AQ392" t="n">
         <v>26.27737226277372</v>
@@ -64288,10 +64288,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.227115602342048</v>
+        <v>7.227115602342041</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.3273157785810614</v>
+        <v>-0.3273157785810543</v>
       </c>
       <c r="AK393" t="n">
         <v>7.185469892270627</v>
@@ -64300,16 +64300,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.2812269987605887</v>
+        <v>0.281226998760588</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.02697180537422167</v>
+        <v>0.0269718053742217</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3136210223326478</v>
+        <v>0.3136210223326474</v>
       </c>
       <c r="AP393" t="n">
-        <v>-3.086315120704791</v>
+        <v>-3.086315120704688</v>
       </c>
       <c r="AQ393" t="n">
         <v>27.17391304347826</v>
@@ -64453,10 +64453,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.187163192389372</v>
+        <v>7.187163192389367</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3014629665592938</v>
+        <v>-0.3014629665592885</v>
       </c>
       <c r="AK394" t="n">
         <v>7.208338760609084</v>
@@ -64465,16 +64465,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2681836981576122</v>
+        <v>0.2681836981576121</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02658698789673936</v>
+        <v>0.02658698789673927</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.285908150945263</v>
+        <v>0.2859081509452629</v>
       </c>
       <c r="AP394" t="n">
-        <v>-2.632696204720104</v>
+        <v>-2.632696204720034</v>
       </c>
       <c r="AQ394" t="n">
         <v>28.05755395683453</v>
@@ -64618,10 +64618,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.214951953115591</v>
+        <v>7.214951953115579</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.334951838674673</v>
+        <v>-0.3349518386746606</v>
       </c>
       <c r="AK395" t="n">
         <v>7.186200492654655</v>
@@ -64630,16 +64630,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2591628297636744</v>
+        <v>0.2591628297636748</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02587977479594339</v>
+        <v>0.02587977479594331</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.266108201492412</v>
+        <v>0.2661082014924122</v>
       </c>
       <c r="AP395" t="n">
-        <v>-2.994052922510599</v>
+        <v>-2.994052922510445</v>
       </c>
       <c r="AQ395" t="n">
         <v>27.5</v>
@@ -64783,10 +64783,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.197430004066455</v>
+        <v>7.197430004066453</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.305630077308642</v>
+        <v>-0.3056300773086402</v>
       </c>
       <c r="AK396" t="n">
         <v>7.201835396295348</v>
@@ -64795,16 +64795,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2466333883508319</v>
+        <v>0.2466333883508324</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.0247654344950328</v>
+        <v>0.02476543449503272</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.2401258754735003</v>
+        <v>0.2401258754735008</v>
       </c>
       <c r="AP396" t="n">
-        <v>-2.521856098757837</v>
+        <v>-2.521856098757829</v>
       </c>
       <c r="AQ396" t="n">
         <v>26.24113475177305</v>
@@ -64951,25 +64951,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3291230670577869</v>
+        <v>-0.3291230670577878</v>
       </c>
       <c r="AK397" t="n">
-        <v>7.179650721554484</v>
+        <v>7.179650721554483</v>
       </c>
       <c r="AL397" t="n">
-        <v>-0.2786506986663007</v>
+        <v>-0.2786506986662998</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2377807761788571</v>
+        <v>0.2377807761788565</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02334020127887793</v>
+        <v>0.02334020127887796</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.2171758918683914</v>
+        <v>0.2171758918683913</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.751183602296446</v>
+        <v>-2.751183602296473</v>
       </c>
       <c r="AQ397" t="n">
         <v>26.76056338028169</v>
@@ -65113,10 +65113,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.20852803773295</v>
+        <v>7.208528037732954</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.2978281933725988</v>
+        <v>-0.2978281933726024</v>
       </c>
       <c r="AK398" t="n">
         <v>7.206616000051887</v>
@@ -65125,16 +65125,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2255544515066686</v>
+        <v>0.2255544515066683</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.0206724522626571</v>
+        <v>0.0206724522626572</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.1898019966940717</v>
+        <v>0.1898019966940708</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.287488640557774</v>
+        <v>-2.287488640557831</v>
       </c>
       <c r="AQ398" t="n">
         <v>16.43356643356643</v>
@@ -65278,10 +65278,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.19880309223843</v>
+        <v>7.198803092238432</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.287202979323391</v>
+        <v>-0.2872029793233928</v>
       </c>
       <c r="AK399" t="n">
         <v>7.18051307481679</v>
@@ -65290,16 +65290,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2150441262650612</v>
+        <v>0.2150441262650616</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.01774895516388914</v>
+        <v>0.0177489551638892</v>
       </c>
       <c r="AO399" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.108546902541137</v>
+        <v>-2.108546902541169</v>
       </c>
       <c r="AQ399" t="n">
         <v>14.93055555555556</v>
@@ -65443,10 +65443,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI400" t="n">
-        <v>7.172424239411004</v>
+        <v>7.172424239411002</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.2608241264959652</v>
+        <v>-0.2608241264959634</v>
       </c>
       <c r="AK400" t="n">
         <v>7.16705299197773</v>
@@ -65455,16 +65455,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.205433651489446</v>
+        <v>0.2054336514894463</v>
       </c>
       <c r="AN400" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.1417286033373026</v>
+        <v>0.1417286033373033</v>
       </c>
       <c r="AP400" t="n">
-        <v>-1.745878920107403</v>
+        <v>-1.745878920107388</v>
       </c>
       <c r="AQ400" t="n">
         <v>18.96551724137931</v>
@@ -65608,10 +65608,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.163756390646672</v>
+        <v>7.163756390646673</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2695565424716229</v>
+        <v>-0.2695565424716238</v>
       </c>
       <c r="AK401" t="n">
         <v>7.153532751444382</v>
@@ -65620,16 +65620,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.1941661953581061</v>
+        <v>0.1941661953581056</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.01312004055850013</v>
+        <v>0.01312004055850015</v>
       </c>
       <c r="AO401" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP401" t="n">
-        <v>-1.828909997258109</v>
+        <v>-1.828909997258128</v>
       </c>
       <c r="AQ401" t="n">
         <v>25.34246575342466</v>
@@ -65773,10 +65773,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.158063699621738</v>
+        <v>7.158063699621736</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.2875636118837006</v>
+        <v>-0.2875636118836988</v>
       </c>
       <c r="AK402" t="n">
         <v>7.150669702211316</v>
@@ -65785,16 +65785,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.1839494937266881</v>
+        <v>0.183949493726688</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.01194074338472806</v>
+        <v>0.01194074338472802</v>
       </c>
       <c r="AO402" t="n">
-        <v>0.1107549805175829</v>
+        <v>0.110754980517583</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.019875210260029</v>
+        <v>-2.019875210260015</v>
       </c>
       <c r="AQ402" t="n">
         <v>13.26530612244898</v>
@@ -65938,10 +65938,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.157435208014563</v>
+        <v>7.157435208014565</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.272335320166663</v>
+        <v>-0.2723353201666647</v>
       </c>
       <c r="AK403" t="n">
         <v>7.140926852093823</v>
@@ -65950,16 +65950,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.1753430411611933</v>
+        <v>0.1753430411611928</v>
       </c>
       <c r="AN403" t="n">
-        <v>0.00971765423202034</v>
+        <v>0.009717654232020439</v>
       </c>
       <c r="AO403" t="n">
-        <v>0.09620195025422695</v>
+        <v>0.09620195025422784</v>
       </c>
       <c r="AP403" t="n">
-        <v>-1.803435138632542</v>
+        <v>-1.803435138632572</v>
       </c>
       <c r="AQ403" t="n">
         <v>21.28378378378378</v>
@@ -66103,10 +66103,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.150386811340072</v>
+        <v>7.15038681134007</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2679867754819174</v>
+        <v>-0.2679867754819156</v>
       </c>
       <c r="AK404" t="n">
         <v>7.142886401315924</v>
@@ -66115,16 +66115,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.1664838398737872</v>
+        <v>0.1664838398737869</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.008089376136153875</v>
+        <v>0.008089376136153925</v>
       </c>
       <c r="AO404" t="n">
-        <v>0.0848962688609296</v>
+        <v>0.08489626886092971</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.72604130332999</v>
+        <v>-1.726041303329976</v>
       </c>
       <c r="AQ404" t="n">
         <v>20.80536912751678</v>
@@ -66268,10 +66268,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.137094841694645</v>
+        <v>7.137094841694642</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2547949416397133</v>
+        <v>-0.2547949416397106</v>
       </c>
       <c r="AK405" t="n">
         <v>7.137840883333127</v>
@@ -66280,16 +66280,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1571907956492611</v>
+        <v>0.1571907956492617</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.006581947594647974</v>
+        <v>0.006581947594647856</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.07412699588694804</v>
+        <v>0.07412699588694738</v>
       </c>
       <c r="AP405" t="n">
-        <v>-1.546143135458699</v>
+        <v>-1.546143135458674</v>
       </c>
       <c r="AQ405" t="n">
         <v>21</v>
@@ -66433,10 +66433,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.123391234435203</v>
+        <v>7.1233912344352</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.2666912908927221</v>
+        <v>-0.2666912908927195</v>
       </c>
       <c r="AK406" t="n">
         <v>7.12862724785568</v>
@@ -66445,16 +66445,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1487097707294961</v>
+        <v>0.1487097707294973</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.005441006961990014</v>
+        <v>0.005441006961990058</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.06531270865715677</v>
+        <v>0.06531270865715666</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.670173140076265</v>
+        <v>-1.670173140076241</v>
       </c>
       <c r="AQ406" t="n">
         <v>14.56953642384106</v>
@@ -66598,10 +66598,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.11600731855288</v>
+        <v>7.116007318552882</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2873072529400869</v>
+        <v>-0.2873072529400895</v>
       </c>
       <c r="AK407" t="n">
         <v>7.118961040191934</v>
@@ -66610,16 +66610,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1409513724492178</v>
+        <v>0.1409513724492179</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.005644373135176822</v>
+        <v>0.005644373135176906</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.05986577613532174</v>
+        <v>0.0598657761353214</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.891461410212574</v>
+        <v>-1.891461410212615</v>
       </c>
       <c r="AQ407" t="n">
         <v>10.19736842105263</v>
@@ -66763,10 +66763,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.115262454587763</v>
+        <v>7.11526245458776</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2838625369852235</v>
+        <v>-0.2838625369852208</v>
       </c>
       <c r="AK408" t="n">
         <v>7.113208458946866</v>
@@ -66778,13 +66778,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.005618445165739616</v>
+        <v>0.005618445165739529</v>
       </c>
       <c r="AO408" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.823531845613289</v>
+        <v>-1.823531845613265</v>
       </c>
       <c r="AQ408" t="n">
         <v>8.823529411764707</v>
@@ -66940,16 +66940,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1248427026608149</v>
+        <v>0.1248427026608145</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005050876420738246</v>
+        <v>0.005050876420738303</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.04692762159458042</v>
+        <v>0.04692762159457986</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.737988099332821</v>
+        <v>-1.73798809933283</v>
       </c>
       <c r="AQ409" t="n">
         <v>13.96103896103896</v>
@@ -67093,10 +67093,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.100218718661557</v>
+        <v>7.100218718661558</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2699188643829924</v>
+        <v>-0.2699188643829933</v>
       </c>
       <c r="AK410" t="n">
         <v>7.105971078464224</v>
@@ -67108,13 +67108,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.005209570180715356</v>
+        <v>0.00520957018071537</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.0421970173931332</v>
+        <v>0.04219701739313308</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.615152291713709</v>
+        <v>-1.615152291713727</v>
       </c>
       <c r="AQ410" t="n">
         <v>15.16129032258065</v>
@@ -67258,10 +67258,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.097935875054437</v>
+        <v>7.097935875054439</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2822358208857363</v>
+        <v>-0.2822358208857381</v>
       </c>
       <c r="AK411" t="n">
         <v>7.101361129315627</v>
@@ -67270,16 +67270,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM411" t="n">
-        <v>0.1117472247487875</v>
+        <v>0.1117472247487876</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005385102682029907</v>
+        <v>0.005385102682029925</v>
       </c>
       <c r="AO411" t="n">
-        <v>0.03866992220359</v>
+        <v>0.03866992220359033</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.737700494527099</v>
+        <v>-1.737700494527127</v>
       </c>
       <c r="AQ411" t="n">
         <v>14.1025641025641</v>
@@ -67423,10 +67423,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI412" t="n">
-        <v>7.097978821692022</v>
+        <v>7.097978821692021</v>
       </c>
       <c r="AJ412" t="n">
-        <v>-0.2799789819093075</v>
+        <v>-0.2799789819093057</v>
       </c>
       <c r="AK412" t="n">
         <v>7.099648834314064</v>
@@ -67435,16 +67435,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM412" t="n">
-        <v>0.1065475925362033</v>
+        <v>0.1065475925362025</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005956926407440957</v>
+        <v>0.005956926407441003</v>
       </c>
       <c r="AO412" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.690013917359405</v>
+        <v>-1.690013917359392</v>
       </c>
       <c r="AQ412" t="n">
         <v>14.01273885350319</v>
@@ -67600,16 +67600,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM413" t="n">
-        <v>0.1013724682419977</v>
+        <v>0.1013724682419976</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.006126167203105798</v>
+        <v>0.006126167203105847</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.03348722035246332</v>
+        <v>0.03348722035246277</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.526737752078189</v>
+        <v>-1.526737752078196</v>
       </c>
       <c r="AQ413" t="n">
         <v>22.78481012658228</v>
@@ -67753,10 +67753,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.087097940453345</v>
+        <v>7.087097940453343</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2700980281913825</v>
+        <v>-0.2700980281913798</v>
       </c>
       <c r="AK414" t="n">
         <v>7.090805518999606</v>
@@ -67765,16 +67765,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.09919462776856321</v>
+        <v>0.09919462776856289</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.006113943880485972</v>
+        <v>0.006113943880485968</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.03204155062895153</v>
+        <v>0.03204155062895098</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.541595404791005</v>
+        <v>-1.541595404790982</v>
       </c>
       <c r="AQ414" t="n">
         <v>17.61006289308176</v>
@@ -67930,16 +67930,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.097507502547015</v>
+        <v>0.09750750254701511</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005510714664730507</v>
+        <v>0.005510714664730422</v>
       </c>
       <c r="AO415" t="n">
-        <v>0.03001455024934374</v>
+        <v>0.03001455024934274</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.600899787479524</v>
+        <v>-1.600899787479531</v>
       </c>
       <c r="AQ415" t="n">
         <v>14.375</v>
@@ -68095,16 +68095,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.09380549503386901</v>
+        <v>0.09380549503386949</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.004784904607979881</v>
+        <v>0.004784904607979855</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.02699383492044782</v>
+        <v>0.02699383492044827</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.557942280302812</v>
+        <v>-1.55794228030282</v>
       </c>
       <c r="AQ416" t="n">
         <v>18.01242236024845</v>
@@ -68248,10 +68248,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI417" t="n">
-        <v>7.097145375663951</v>
+        <v>7.097145375663948</v>
       </c>
       <c r="AJ417" t="n">
-        <v>-0.2729452223131208</v>
+        <v>-0.2729452223131181</v>
       </c>
       <c r="AK417" t="n">
         <v>7.093828611034739</v>
@@ -68260,16 +68260,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.08945254406056438</v>
+        <v>0.08945254406056392</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.004001520125414798</v>
+        <v>0.004001520125414807</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.02385555423225116</v>
+        <v>0.02385555423225172</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.523824448003748</v>
+        <v>-1.523824448003726</v>
       </c>
       <c r="AQ417" t="n">
         <v>22.22222222222222</v>
@@ -68413,10 +68413,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI418" t="n">
-        <v>7.088227962421951</v>
+        <v>7.088227962421954</v>
       </c>
       <c r="AJ418" t="n">
-        <v>-0.262227748798904</v>
+        <v>-0.2622277487989066</v>
       </c>
       <c r="AK418" t="n">
         <v>7.092951699003613</v>
@@ -68425,16 +68425,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.07912491692886899</v>
+        <v>0.07912491692886864</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.003813743757049903</v>
+        <v>0.003813743757049957</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.01902803623666316</v>
+        <v>0.01902803623666371</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.388972796501187</v>
+        <v>-1.388972796501224</v>
       </c>
       <c r="AQ418" t="n">
         <v>35.2760736196319</v>
@@ -68578,10 +68578,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI419" t="n">
-        <v>7.082675656384673</v>
+        <v>7.082675656384675</v>
       </c>
       <c r="AJ419" t="n">
-        <v>-0.2467758265201709</v>
+        <v>-0.2467758265201727</v>
       </c>
       <c r="AK419" t="n">
         <v>7.085940899278786</v>
@@ -68590,16 +68590,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.07019093860911668</v>
+        <v>0.07019093860911679</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.003788844982403339</v>
+        <v>0.003788844982403293</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.01530727852465064</v>
+        <v>0.0153072785246503</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.204234266049821</v>
+        <v>-1.204234266049846</v>
       </c>
       <c r="AQ419" t="n">
         <v>33.23170731707317</v>
@@ -68743,10 +68743,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.082585232341567</v>
+        <v>7.082585232341569</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2597850728872215</v>
+        <v>-0.2597850728872233</v>
       </c>
       <c r="AK420" t="n">
         <v>7.080231185021037</v>
@@ -68755,16 +68755,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.0607230145131474</v>
+        <v>0.06072301451314636</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.003218097337044118</v>
+        <v>0.003218097337044184</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.01127031184523342</v>
+        <v>0.01127031184523331</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.340364881437316</v>
+        <v>-1.340364881437342</v>
       </c>
       <c r="AQ420" t="n">
         <v>33.33333333333334</v>
@@ -68908,10 +68908,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.082752176397555</v>
+        <v>7.082752176397554</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.2453522168333464</v>
+        <v>-0.2453522168333455</v>
       </c>
       <c r="AK421" t="n">
         <v>7.078545045220129</v>
@@ -68920,16 +68920,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.04987769893955558</v>
+        <v>0.04987769893955601</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.002647769861786137</v>
+        <v>0.002647769861786034</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.00755590738572276</v>
+        <v>0.007555907385723093</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.168532659260679</v>
+        <v>-1.168532659260674</v>
       </c>
       <c r="AQ421" t="n">
         <v>34.93975903614458</v>
@@ -69073,10 +69073,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.073418742129174</v>
+        <v>7.073418742129173</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2359186467617427</v>
+        <v>-0.2359186467617418</v>
       </c>
       <c r="AK422" t="n">
         <v>7.075576762908686</v>
@@ -69085,16 +69085,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.03723342047483359</v>
+        <v>0.03723342047483347</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.0007434096776329363</v>
+        <v>0.0007434096776329864</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.003691827899839573</v>
+        <v>0.003691827899840794</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.055105738952285</v>
+        <v>-1.05510573895228</v>
       </c>
       <c r="AQ422" t="n">
         <v>37.4251497005988</v>
@@ -69250,16 +69250,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.02391394499985428</v>
+        <v>0.02391394499985489</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.0004638728584110997</v>
+        <v>0.0004638728584110585</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.00150427765126282</v>
+        <v>0.001504277651263042</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.095172559240732</v>
+        <v>-1.095172559240736</v>
       </c>
       <c r="AQ423" t="n">
         <v>35.11904761904762</v>
@@ -69403,10 +69403,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.061175551975939</v>
+        <v>7.06117555197594</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2336756854903435</v>
+        <v>-0.2336756854903443</v>
       </c>
       <c r="AK424" t="n">
         <v>7.061105294515807</v>
@@ -69415,16 +69415,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.01023096587809661</v>
+        <v>0.01023096587809607</v>
       </c>
       <c r="AN424" t="n">
-        <v>-0.0001641525470544823</v>
+        <v>-0.0001641525470544615</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.0002530929795961923</v>
+        <v>0.000253092979595082</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.0163804668533</v>
+        <v>-1.016380466853314</v>
       </c>
       <c r="AQ424" t="n">
         <v>40.23668639053254</v>
@@ -69580,16 +69580,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM425" t="n">
-        <v>-0.001349940557734956</v>
+        <v>-0.001349940557734529</v>
       </c>
       <c r="AN425" t="n">
-        <v>-0.001242569541730382</v>
+        <v>-0.001242569541730301</v>
       </c>
       <c r="AO425" t="n">
-        <v>9.828375502929365e-05</v>
+        <v>9.828375502973774e-05</v>
       </c>
       <c r="AP425" t="n">
-        <v>-0.9199308462067871</v>
+        <v>-0.9199308462067914</v>
       </c>
       <c r="AQ425" t="n">
         <v>40.58823529411764</v>
@@ -69733,10 +69733,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI426" t="n">
-        <v>7.051845784111939</v>
+        <v>7.051845784111937</v>
       </c>
       <c r="AJ426" t="n">
-        <v>-0.2217457246026617</v>
+        <v>-0.22174572460266</v>
       </c>
       <c r="AK426" t="n">
         <v>7.04924004450221</v>
@@ -69745,16 +69745,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM426" t="n">
-        <v>-0.01245927794565087</v>
+        <v>-0.0124592779456514</v>
       </c>
       <c r="AN426" t="n">
-        <v>-0.002690846636687106</v>
+        <v>-0.002690846636687166</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.0009149443224345521</v>
+        <v>0.000914944322433886</v>
       </c>
       <c r="AP426" t="n">
-        <v>-0.872039164838088</v>
+        <v>-0.8720391648380724</v>
       </c>
       <c r="AQ426" t="n">
         <v>37.42690058479532</v>
@@ -69898,10 +69898,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI427" t="n">
-        <v>7.044932512363691</v>
+        <v>7.044932512363692</v>
       </c>
       <c r="AJ427" t="n">
-        <v>-0.2339326420633983</v>
+        <v>-0.2339326420633991</v>
       </c>
       <c r="AK427" t="n">
         <v>7.044607485549974</v>
@@ -69910,16 +69910,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM427" t="n">
-        <v>-0.02351974718911197</v>
+        <v>-0.0235197471891116</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.003286981705062079</v>
+        <v>-0.003286981705062081</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.002235402288773947</v>
+        <v>0.002235402288773058</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.003954290846168</v>
+        <v>-1.003954290846183</v>
       </c>
       <c r="AQ427" t="n">
         <v>35.46511627906976</v>
@@ -70063,10 +70063,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI428" t="n">
-        <v>7.041380724566422</v>
+        <v>7.04138072456642</v>
       </c>
       <c r="AJ428" t="n">
-        <v>-0.2399805399350745</v>
+        <v>-0.2399805399350727</v>
       </c>
       <c r="AK428" t="n">
         <v>7.036677431055121</v>
@@ -70075,16 +70075,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.03604973348542533</v>
+        <v>-0.03604973348542571</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.003896888881646653</v>
+        <v>-0.003896888881646666</v>
       </c>
       <c r="AO428" t="n">
-        <v>0.004508577134016534</v>
+        <v>0.004508577134016423</v>
       </c>
       <c r="AP428" t="n">
-        <v>-1.065707503421595</v>
+        <v>-1.06570750342158</v>
       </c>
       <c r="AQ428" t="n">
         <v>28.03468208092486</v>
@@ -70228,10 +70228,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.031781164871437</v>
+        <v>7.031781164871438</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2312812487947769</v>
+        <v>-0.2312812487947777</v>
       </c>
       <c r="AK429" t="n">
         <v>7.031531243279009</v>
@@ -70240,16 +70240,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.0496421115884523</v>
+        <v>-0.04964211158845258</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.003622848094475932</v>
+        <v>-0.003622848094475877</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.007358432861332531</v>
+        <v>0.007358432861333086</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.9620021970824676</v>
+        <v>-0.9620021970824821</v>
       </c>
       <c r="AQ429" t="n">
         <v>35.63218390804597</v>
@@ -70405,16 +70405,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.06336633742876464</v>
+        <v>-0.06336633742876532</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.00383222203166729</v>
+        <v>-0.003832222031667326</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.0113935335626284</v>
+        <v>0.01139353356262962</v>
       </c>
       <c r="AP430" t="n">
-        <v>-0.8915152845393376</v>
+        <v>-0.8915152845393419</v>
       </c>
       <c r="AQ430" t="n">
         <v>36.28571428571429</v>
@@ -70558,10 +70558,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.012358254068223</v>
+        <v>7.012358254068221</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.220358437173692</v>
+        <v>-0.2203584371736902</v>
       </c>
       <c r="AK431" t="n">
         <v>7.010266108789461</v>
@@ -70570,16 +70570,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.07815930192347351</v>
+        <v>-0.07815930192347212</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.0037302018478894</v>
+        <v>-0.003730201847889384</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.01669360800688513</v>
+        <v>0.01669360800688602</v>
       </c>
       <c r="AP431" t="n">
-        <v>-0.8298595079411905</v>
+        <v>-0.8298595079411745</v>
       </c>
       <c r="AQ431" t="n">
         <v>35.51136363636363</v>
@@ -70723,10 +70723,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.001516536947593</v>
+        <v>7.001516536947591</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2107164423431005</v>
+        <v>-0.2107164423430987</v>
       </c>
       <c r="AK432" t="n">
         <v>7.003692382618654</v>
@@ -70735,16 +70735,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.09225745624393369</v>
+        <v>-0.09225745624393285</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003729646461095512</v>
+        <v>-0.003729646461095566</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.02283737241168637</v>
+        <v>0.02283737241168682</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.7175971148724907</v>
+        <v>-0.7175971148724744</v>
       </c>
       <c r="AQ432" t="n">
         <v>40.11299435028249</v>
@@ -70888,10 +70888,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI433" t="n">
-        <v>6.98285303226683</v>
+        <v>6.982853032266831</v>
       </c>
       <c r="AJ433" t="n">
-        <v>-0.1977530490514976</v>
+        <v>-0.1977530490514985</v>
       </c>
       <c r="AK433" t="n">
         <v>6.994908837140057</v>
@@ -70900,16 +70900,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.1040956648961724</v>
+        <v>-0.1040956648961739</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.004775368000139335</v>
+        <v>-0.004775368000139281</v>
       </c>
       <c r="AO433" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.5684906885650866</v>
+        <v>-0.5684906885651003</v>
       </c>
       <c r="AQ433" t="n">
         <v>41.29213483146067</v>
@@ -71053,10 +71053,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI434" t="n">
-        <v>6.976537964100197</v>
+        <v>6.976537964100195</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.1673381540721204</v>
+        <v>-0.1673381540721186</v>
       </c>
       <c r="AK434" t="n">
         <v>6.976048621620001</v>
@@ -71065,16 +71065,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.1171809788132883</v>
+        <v>-0.1171809788132892</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.006568629287185546</v>
+        <v>-0.006568629287185491</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.03914952746580425</v>
+        <v>0.03914952746580436</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.2223140460906322</v>
+        <v>-0.2223140460906146</v>
       </c>
       <c r="AQ434" t="n">
         <v>49.16201117318435</v>
@@ -71221,7 +71221,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.1582257113591101</v>
+        <v>-0.1582257113591092</v>
       </c>
       <c r="AK435" t="n">
         <v>6.970728111892008</v>
@@ -71230,16 +71230,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.127636816539944</v>
+        <v>-0.127636816539943</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.007451019732577668</v>
+        <v>-0.00745101973257774</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.04750067483060583</v>
+        <v>0.04750067483060572</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.1181830488027858</v>
+        <v>-0.1181830488027779</v>
       </c>
       <c r="AQ435" t="n">
         <v>50.27777777777779</v>
@@ -71398,13 +71398,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.008628156625160088</v>
+        <v>-0.008628156625160163</v>
       </c>
       <c r="AO436" t="n">
-        <v>0.05751510742764043</v>
+        <v>0.05751510742764121</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.005878665741872089</v>
+        <v>-0.005878665741873697</v>
       </c>
       <c r="AQ436" t="n">
         <v>52.48618784530387</v>
@@ -71548,10 +71548,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.950644730799358</v>
+        <v>6.950644730799363</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1501448147226974</v>
+        <v>-0.1501448147227027</v>
       </c>
       <c r="AK437" t="n">
         <v>6.959853578800648</v>
@@ -71560,16 +71560,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1469566450661546</v>
+        <v>-0.1469566450661556</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.009026348114251986</v>
+        <v>-0.009026348114251901</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.06603756167960417</v>
+        <v>0.06603756167960351</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.02584869659753125</v>
+        <v>-0.02584869659759381</v>
       </c>
       <c r="AQ437" t="n">
         <v>50.27472527472527</v>
@@ -71713,28 +71713,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI438" t="n">
-        <v>6.934622414140156</v>
+        <v>6.934622414140152</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1321226430219919</v>
+        <v>-0.1321226430219875</v>
       </c>
       <c r="AK438" t="n">
-        <v>6.94711441643572</v>
+        <v>6.947114416435721</v>
       </c>
       <c r="AL438" t="n">
-        <v>-0.1446146453175556</v>
+        <v>-0.1446146453175565</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.1568781652619925</v>
+        <v>-0.1568781652619921</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.010042871337475</v>
+        <v>-0.01004287133747513</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.07699206242755485</v>
+        <v>0.07699206242755419</v>
       </c>
       <c r="AP438" t="n">
-        <v>0.1806443022076252</v>
+        <v>0.1806443022076749</v>
       </c>
       <c r="AQ438" t="n">
         <v>59.56284153005465</v>
@@ -71878,10 +71878,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI439" t="n">
-        <v>6.928042396530076</v>
+        <v>6.928042396530073</v>
       </c>
       <c r="AJ439" t="n">
-        <v>-0.1335425224150857</v>
+        <v>-0.133542522415083</v>
       </c>
       <c r="AK439" t="n">
         <v>6.933186989735641</v>
@@ -71890,16 +71890,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM439" t="n">
-        <v>-0.1650917115670576</v>
+        <v>-0.1650917115670582</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.0106149464753251</v>
+        <v>-0.01061494647532512</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.08732871254562191</v>
+        <v>0.08732871254562202</v>
       </c>
       <c r="AP439" t="n">
-        <v>0.1638353991090848</v>
+        <v>0.1638353991091144</v>
       </c>
       <c r="AQ439" t="n">
         <v>56.25</v>
@@ -72043,10 +72043,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.941461393298105</v>
+        <v>6.941461393298106</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1469615191831144</v>
+        <v>-0.1469615191831153</v>
       </c>
       <c r="AK440" t="n">
         <v>6.925995477801935</v>
@@ -72055,16 +72055,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1745447047691483</v>
+        <v>-0.1745447047691478</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.01108963812755723</v>
+        <v>-0.01108963812755724</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.09935205695041804</v>
+        <v>0.09935205695041927</v>
       </c>
       <c r="AP440" t="n">
-        <v>0.008857437085365438</v>
+        <v>0.008857437085353572</v>
       </c>
       <c r="AQ440" t="n">
         <v>49.72972972972973</v>
@@ -72208,10 +72208,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.93323210397643</v>
+        <v>6.933232103976423</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.1472323290435682</v>
+        <v>-0.147232329043562</v>
       </c>
       <c r="AK441" t="n">
         <v>6.938996539173566</v>
@@ -72220,16 +72220,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1853013335308036</v>
+        <v>-0.1853013335308053</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.01193987645426134</v>
+        <v>-0.01193987645426136</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.1123648810347069</v>
+        <v>0.1123648810347067</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.005706446015392532</v>
+        <v>0.005706446015462478</v>
       </c>
       <c r="AQ441" t="n">
         <v>45.43010752688172</v>
@@ -72373,10 +72373,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.928429644379657</v>
+        <v>6.928429644379658</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1496296336985043</v>
+        <v>-0.1496296336985061</v>
       </c>
       <c r="AK442" t="n">
         <v>6.93160690101155</v>
@@ -72388,13 +72388,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.01257308415669778</v>
+        <v>-0.01257308415669775</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.125857898472412</v>
+        <v>0.1258578984724115</v>
       </c>
       <c r="AP442" t="n">
-        <v>-0.02206800494322776</v>
+        <v>-0.02206800494325076</v>
       </c>
       <c r="AQ442" t="n">
         <v>45.72192513368984</v>
@@ -72538,10 +72538,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.925068850639515</v>
+        <v>6.925068850639512</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1455688430101203</v>
+        <v>-0.1455688430101176</v>
       </c>
       <c r="AK443" t="n">
         <v>6.924763510572069</v>
@@ -72550,16 +72550,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.2060805417157788</v>
+        <v>-0.2060805417157789</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01318646791849926</v>
+        <v>-0.01318646791849928</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.1396251026736655</v>
+        <v>0.1396251026736647</v>
       </c>
       <c r="AP443" t="n">
-        <v>0.02513933444016338</v>
+        <v>0.02513933444019229</v>
       </c>
       <c r="AQ443" t="n">
         <v>49.46808510638298</v>
@@ -72703,10 +72703,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.900929863197374</v>
+        <v>6.900929863197373</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1347297975845807</v>
+        <v>-0.1347297975845798</v>
       </c>
       <c r="AK444" t="n">
         <v>6.921049732547429</v>
@@ -72715,16 +72715,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.2151279705591488</v>
+        <v>-0.2151279705591481</v>
       </c>
       <c r="AN444" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1518365696223548</v>
+        <v>0.1518365696223549</v>
       </c>
       <c r="AP444" t="n">
-        <v>0.1512529636671445</v>
+        <v>0.151252963667153</v>
       </c>
       <c r="AQ444" t="n">
         <v>50.52910052910053</v>
@@ -72868,10 +72868,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.895219010181459</v>
+        <v>6.89521901018146</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1302191436958635</v>
+        <v>-0.1302191436958644</v>
       </c>
       <c r="AK445" t="n">
         <v>6.89978353884127</v>
@@ -72883,13 +72883,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01278923357027009</v>
+        <v>-0.01278923357027006</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.1644177475946104</v>
+        <v>0.1644177475946105</v>
       </c>
       <c r="AP445" t="n">
-        <v>0.2034852657846063</v>
+        <v>0.2034852657845942</v>
       </c>
       <c r="AQ445" t="n">
         <v>48.1578947368421</v>
@@ -73033,10 +73033,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.879512239848579</v>
+        <v>6.87951223984858</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1173123611559523</v>
+        <v>-0.1173123611559532</v>
       </c>
       <c r="AK446" t="n">
         <v>6.893260360395011</v>
@@ -73045,16 +73045,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM446" t="n">
-        <v>-0.233692768734329</v>
+        <v>-0.233692768734328</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01245257184765153</v>
+        <v>-0.01245257184765156</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.179129523332087</v>
+        <v>0.1791295233320875</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.35387898726864</v>
+        <v>0.3538789872686283</v>
       </c>
       <c r="AQ446" t="n">
         <v>51.57068062827225</v>
@@ -73198,10 +73198,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.882426232260446</v>
+        <v>6.882426232260437</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1132263840853973</v>
+        <v>-0.1132263840853884</v>
       </c>
       <c r="AK447" t="n">
         <v>6.880758546638964</v>
@@ -73210,16 +73210,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2433281856134891</v>
+        <v>-0.2433281856134888</v>
       </c>
       <c r="AN447" t="n">
-        <v>-0.01202813951384066</v>
+        <v>-0.01202813951384067</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1944608722019401</v>
+        <v>0.1944608722019407</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.400718859435147</v>
+        <v>0.4007188594352498</v>
       </c>
       <c r="AQ447" t="n">
         <v>53.125</v>
@@ -73375,16 +73375,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM448" t="n">
-        <v>-0.2520264427810588</v>
+        <v>-0.25202644278106</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01246671652825437</v>
+        <v>-0.01246671652825434</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.2101991144027906</v>
+        <v>0.2101991144027905</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.9721302198060143</v>
+        <v>0.9721302198060142</v>
       </c>
       <c r="AQ448" t="n">
         <v>66.06217616580309</v>
@@ -73528,10 +73528,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.841963898035317</v>
+        <v>6.841963898035326</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.07646382937076623</v>
+        <v>-0.07646382937077512</v>
       </c>
       <c r="AK449" t="n">
         <v>6.844785316397215</v>
@@ -73540,16 +73540,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.2592973891940562</v>
+        <v>-0.2592973891940566</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01305068899435097</v>
+        <v>-0.01305068899435077</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.2277185089957531</v>
+        <v>0.2277185089957524</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.8254556631441549</v>
+        <v>0.8254556631440507</v>
       </c>
       <c r="AQ449" t="n">
         <v>59.27835051546391</v>
@@ -73693,28 +73693,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.845644916883085</v>
+        <v>6.845644916883079</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.08014484821853429</v>
+        <v>-0.08014484821852808</v>
       </c>
       <c r="AK450" t="n">
-        <v>6.849407886968131</v>
+        <v>6.849407886968132</v>
       </c>
       <c r="AL450" t="n">
-        <v>-0.08390781830358041</v>
+        <v>-0.08390781830358129</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.2668003223256257</v>
+        <v>-0.2668003223256254</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.01367989020054944</v>
+        <v>-0.0136798902005495</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.2456601220977563</v>
+        <v>0.2456601220977566</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.7788054311405267</v>
+        <v>0.7788054311405997</v>
       </c>
       <c r="AQ450" t="n">
         <v>58.97435897435898</v>
@@ -73858,10 +73858,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI451" t="n">
-        <v>6.842084108625032</v>
+        <v>6.842084108625038</v>
       </c>
       <c r="AJ451" t="n">
-        <v>-0.0695840704780597</v>
+        <v>-0.06958407047806503</v>
       </c>
       <c r="AK451" t="n">
         <v>6.852702018840203</v>
@@ -73870,16 +73870,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.2735436467318143</v>
+        <v>-0.273543646731814</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01403412282467997</v>
+        <v>-0.01403412282467991</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.2619835102172253</v>
+        <v>0.261983510217226</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.8993437222326349</v>
+        <v>0.8993437222325723</v>
       </c>
       <c r="AQ451" t="n">
         <v>64.28571428571428</v>
@@ -74023,10 +74023,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.863831060847773</v>
+        <v>6.863831060847785</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.09133102270080062</v>
+        <v>-0.09133102270081217</v>
       </c>
       <c r="AK452" t="n">
         <v>6.850973969550408</v>
@@ -74035,16 +74035,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2787367835501612</v>
+        <v>-0.2787367835501617</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01406387644726603</v>
+        <v>-0.01406387644726588</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2758112468611987</v>
+        <v>0.2758112468611976</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.6401069829084844</v>
+        <v>0.6401069829083486</v>
       </c>
       <c r="AQ452" t="n">
         <v>63.19796954314721</v>
@@ -74188,10 +74188,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.853037915615571</v>
+        <v>6.853037915615573</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.07753809490634289</v>
+        <v>-0.07753809490634467</v>
       </c>
       <c r="AK453" t="n">
         <v>6.873527983489108</v>
@@ -74203,13 +74203,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.013790177185657</v>
+        <v>-0.01379017718565697</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.285442546377481</v>
+        <v>0.2854425463774817</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7999851756792368</v>
+        <v>0.7999851756792175</v>
       </c>
       <c r="AQ453" t="n">
         <v>69.44444444444443</v>
@@ -74365,7 +74365,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2865252693972544</v>
+        <v>-0.2865252693972545</v>
       </c>
       <c r="AN454" t="n">
         <v>-0.01327380582108439</v>
@@ -74374,7 +74374,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.5996233412815115</v>
+        <v>0.5996233412815121</v>
       </c>
       <c r="AQ454" t="n">
         <v>62.56281407035176</v>
@@ -74518,10 +74518,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.860047631936786</v>
+        <v>6.860047631936787</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.1030476624543644</v>
+        <v>-0.1030476624543653</v>
       </c>
       <c r="AK455" t="n">
         <v>6.865985861260643</v>
@@ -74530,16 +74530,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.290522309347949</v>
+        <v>-0.2905223093479492</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01240158194086383</v>
+        <v>-0.01240158194086378</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.3024992257449916</v>
+        <v>0.3024992257449914</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.4941009333209337</v>
+        <v>0.4941009333209234</v>
       </c>
       <c r="AQ455" t="n">
         <v>58.75</v>
@@ -74683,10 +74683,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.801980414635013</v>
+        <v>6.801980414635016</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.04478065038330392</v>
+        <v>-0.04478065038330659</v>
       </c>
       <c r="AK456" t="n">
         <v>6.863576603094304</v>
@@ -74695,16 +74695,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM456" t="n">
-        <v>-0.2950697019949103</v>
+        <v>-0.2950697019949104</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.0116105331596838</v>
+        <v>-0.01161053315968381</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.3113800696686924</v>
+        <v>0.3113800696686918</v>
       </c>
       <c r="AP456" t="n">
-        <v>1.179534937195622</v>
+        <v>1.179534937195594</v>
       </c>
       <c r="AQ456" t="n">
         <v>80.09950248756219</v>
@@ -74848,10 +74848,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI457" t="n">
-        <v>6.789283666813423</v>
+        <v>6.789283666813422</v>
       </c>
       <c r="AJ457" t="n">
-        <v>-0.03208390256171434</v>
+        <v>-0.03208390256171256</v>
       </c>
       <c r="AK457" t="n">
         <v>6.809671190627447</v>
@@ -74860,16 +74860,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2987092362344105</v>
+        <v>-0.2987092362344108</v>
       </c>
       <c r="AN457" t="n">
-        <v>-0.01030385953714813</v>
+        <v>-0.01030385953714808</v>
       </c>
       <c r="AO457" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP457" t="n">
-        <v>1.321204242911485</v>
+        <v>1.321204242911509</v>
       </c>
       <c r="AQ457" t="n">
         <v>82.92079207920793</v>
@@ -75013,10 +75013,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.789252537988938</v>
+        <v>6.789252537988933</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.02065255095890883</v>
+        <v>-0.0206525509589035</v>
       </c>
       <c r="AK458" t="n">
         <v>6.802840448144932</v>
@@ -75025,16 +75025,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.3027504956929287</v>
+        <v>-0.3027504956929284</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.00881278602540958</v>
+        <v>-0.008812786025409641</v>
       </c>
       <c r="AO458" t="n">
-        <v>0.332227117067963</v>
+        <v>0.3322271170679635</v>
       </c>
       <c r="AP458" t="n">
-        <v>1.445529712541089</v>
+        <v>1.445529712541155</v>
       </c>
       <c r="AQ458" t="n">
         <v>83.74384236453203</v>
@@ -75178,10 +75178,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.774001672255927</v>
+        <v>6.774001672255932</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.005401685225897346</v>
+        <v>-0.005401685225902675</v>
       </c>
       <c r="AK459" t="n">
         <v>6.800260207803535</v>
@@ -75190,16 +75190,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.3068099364477369</v>
+        <v>-0.3068099364477367</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.007070247176567734</v>
+        <v>-0.007070247176567688</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3427146952658529</v>
+        <v>0.3427146952658534</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.611345626774747</v>
+        <v>1.611345626774689</v>
       </c>
       <c r="AQ459" t="n">
         <v>84.06862745098039</v>
@@ -75343,10 +75343,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.802628307046305</v>
+        <v>6.802628307046303</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.0281284138578286</v>
+        <v>-0.02812841385782594</v>
       </c>
       <c r="AK460" t="n">
         <v>6.781970485204615</v>
@@ -75355,16 +75355,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.3121566752204096</v>
+        <v>-0.3121566752204101</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.005102880740085192</v>
+        <v>-0.005102880740085154</v>
       </c>
       <c r="AO460" t="n">
-        <v>0.3560731605465752</v>
+        <v>0.3560731605465757</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.334661797517615</v>
+        <v>1.33466179751765</v>
       </c>
       <c r="AQ460" t="n">
         <v>80.73170731707317</v>
@@ -75508,28 +75508,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.815944895083629</v>
+        <v>6.815944895083632</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.0259449332306021</v>
+        <v>-0.02594493323060476</v>
       </c>
       <c r="AK461" t="n">
-        <v>6.809638458820509</v>
+        <v>6.809638458820508</v>
       </c>
       <c r="AL461" t="n">
-        <v>-0.01963849696748188</v>
+        <v>-0.01963849696748099</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3181413841564625</v>
+        <v>-0.3181413841564619</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.003317316385138602</v>
+        <v>-0.003317316385138562</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.3690689225934927</v>
+        <v>0.3690689225934922</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.350940944408107</v>
+        <v>1.35094094440808</v>
       </c>
       <c r="AQ461" t="n">
         <v>82.52427184466021</v>
@@ -75673,10 +75673,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.821941449304759</v>
+        <v>6.821941449304753</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.0319414874517312</v>
+        <v>-0.03194148745172587</v>
       </c>
       <c r="AK462" t="n">
         <v>6.819973703544699</v>
@@ -75685,16 +75685,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3244228225822193</v>
+        <v>-0.3244228225822198</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.001700148658338674</v>
+        <v>-0.001700148658338742</v>
       </c>
       <c r="AO462" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.272497711914774</v>
+        <v>1.272497711914839</v>
       </c>
       <c r="AQ462" t="n">
         <v>79.22705314009661</v>
@@ -75838,10 +75838,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.826413262727742</v>
+        <v>6.826413262727749</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.03641330087471495</v>
+        <v>-0.03641330087472205</v>
       </c>
       <c r="AK463" t="n">
         <v>6.822087900644207</v>
@@ -75850,16 +75850,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3308797299382499</v>
+        <v>-0.3308797299382495</v>
       </c>
       <c r="AN463" t="n">
-        <v>-7.481797733216444e-05</v>
+        <v>-7.481797733213274e-05</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.3960788710418811</v>
+        <v>0.396078871041881</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.212872589244893</v>
+        <v>1.212872589244813</v>
       </c>
       <c r="AQ463" t="n">
         <v>79.80769230769231</v>
@@ -76003,10 +76003,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.812656647679548</v>
+        <v>6.81265664767955</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.01465678882334664</v>
+        <v>-0.01465678882334931</v>
       </c>
       <c r="AK464" t="n">
         <v>6.823881638371397</v>
@@ -76015,16 +76015,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3363418922753055</v>
+        <v>-0.3363418922753058</v>
       </c>
       <c r="AN464" t="n">
-        <v>0.001379920606120022</v>
+        <v>0.001379920606120097</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.4081029523904164</v>
+        <v>0.4081029523904167</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.45625296765571</v>
+        <v>1.456252967655684</v>
       </c>
       <c r="AQ464" t="n">
         <v>83.97129186602871</v>
@@ -76168,10 +76168,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.802797817425507</v>
+        <v>6.802797817425505</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.009197735028045884</v>
+        <v>-0.009197735028044107</v>
       </c>
       <c r="AK465" t="n">
         <v>6.808320681191073</v>
@@ -76180,16 +76180,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3410659803634685</v>
+        <v>-0.3410659803634682</v>
       </c>
       <c r="AN465" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO465" t="n">
-        <v>0.4198133218741356</v>
+        <v>0.4198133218741357</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.507992928081006</v>
+        <v>1.507992928081032</v>
       </c>
       <c r="AQ465" t="n">
         <v>84.04761904761904</v>
@@ -76339,22 +76339,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK466" t="n">
-        <v>6.795980661778267</v>
+        <v>6.795980661778266</v>
       </c>
       <c r="AL466" t="n">
-        <v>-0.002380579380806047</v>
+        <v>-0.002380579380805159</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3461577281601511</v>
+        <v>-0.3461577281601509</v>
       </c>
       <c r="AN466" t="n">
-        <v>0.004282887883574671</v>
+        <v>0.00428288788357468</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.4328049372030962</v>
+        <v>0.4328049372030969</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.568971829556582</v>
+        <v>1.568971829556587</v>
       </c>
       <c r="AQ466" t="n">
         <v>85.07109004739337</v>
@@ -76498,10 +76498,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.800189882196235</v>
+        <v>6.800189882196236</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.005989938653754301</v>
+        <v>-0.005989938653755189</v>
       </c>
       <c r="AK467" t="n">
         <v>6.78726841810145</v>
@@ -76510,16 +76510,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3502903933401412</v>
+        <v>-0.3502903933401418</v>
       </c>
       <c r="AN467" t="n">
-        <v>0.005405808652032051</v>
+        <v>0.005405808652032067</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4450018361960529</v>
+        <v>0.4450018361960534</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.520317609051734</v>
+        <v>1.520317609051729</v>
       </c>
       <c r="AQ467" t="n">
         <v>83.9622641509434</v>
@@ -76663,10 +76663,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.79797208364255</v>
+        <v>6.797972083642554</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.009372115686007376</v>
+        <v>-0.009372115686010929</v>
       </c>
       <c r="AK468" t="n">
         <v>6.791305278184372</v>
@@ -76675,16 +76675,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3548656112706069</v>
+        <v>-0.3548656112706071</v>
       </c>
       <c r="AN468" t="n">
-        <v>0.006091291211178074</v>
+        <v>0.006091291211178139</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4593697101544711</v>
+        <v>0.4593697101544705</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.470209466853863</v>
+        <v>1.470209466853828</v>
       </c>
       <c r="AQ468" t="n">
         <v>82.86384976525821</v>
@@ -76828,10 +76828,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI469" t="n">
-        <v>6.800452644405181</v>
+        <v>6.800452644405178</v>
       </c>
       <c r="AJ469" t="n">
-        <v>-0.01185267644863774</v>
+        <v>-0.01185267644863508</v>
       </c>
       <c r="AK469" t="n">
         <v>6.789098969069376</v>
@@ -76846,10 +76846,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4721687943484544</v>
+        <v>0.4721687943484545</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.431322929350403</v>
+        <v>1.431322929350439</v>
       </c>
       <c r="AQ469" t="n">
         <v>79.67289719626169</v>
@@ -76993,10 +76993,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.778720347685821</v>
+        <v>6.778720347685814</v>
       </c>
       <c r="AJ470" t="n">
-        <v>0.01707986135958883</v>
+        <v>0.01707986135959594</v>
       </c>
       <c r="AK470" t="n">
         <v>6.790465135395929</v>
@@ -77005,16 +77005,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3625273381377937</v>
+        <v>-0.3625273381377933</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.007343464385960674</v>
+        <v>0.007343464385960585</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4863203622043377</v>
+        <v>0.4863203622043382</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.746913751099119</v>
+        <v>1.746913751099204</v>
       </c>
       <c r="AQ470" t="n">
         <v>84.65116279069767</v>
@@ -77158,10 +77158,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.769755998762547</v>
+        <v>6.769755998762545</v>
       </c>
       <c r="AJ471" t="n">
-        <v>0.02364381202846833</v>
+        <v>0.02364381202847099</v>
       </c>
       <c r="AK471" t="n">
         <v>6.767889899932765</v>
@@ -77170,16 +77170,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3660007866474812</v>
+        <v>-0.3660007866474813</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.00826013782295415</v>
+        <v>0.008260137822954145</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4997690914082398</v>
+        <v>0.4997690914082401</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.803867771120641</v>
+        <v>1.803867771120674</v>
       </c>
       <c r="AQ471" t="n">
         <v>85.41666666666667</v>
@@ -77323,10 +77323,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.789177604754239</v>
+        <v>6.789177604754244</v>
       </c>
       <c r="AJ472" t="n">
-        <v>0.01332216636392491</v>
+        <v>0.01332216636391959</v>
       </c>
       <c r="AK472" t="n">
         <v>6.759766754404358</v>
@@ -77335,16 +77335,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM472" t="n">
-        <v>-0.3700034659576358</v>
+        <v>-0.3700034659576351</v>
       </c>
       <c r="AN472" t="n">
-        <v>0.00987171553454691</v>
+        <v>0.009871715534546958</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.5120623436103316</v>
+        <v>0.5120623436103324</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.671670611528654</v>
+        <v>1.671670611528598</v>
       </c>
       <c r="AQ472" t="n">
         <v>85.48387096774194</v>
@@ -77488,10 +77488,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.774331376960423</v>
+        <v>6.774331376960425</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.01776857573733093</v>
+        <v>0.01776857573732915</v>
       </c>
       <c r="AK473" t="n">
         <v>6.777856240868369</v>
@@ -77500,16 +77500,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3750442390024145</v>
+        <v>-0.3750442390024147</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.01196068662558775</v>
+        <v>0.01196068662558781</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.5238651846176465</v>
+        <v>0.5238651846176463</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.70645603513652</v>
+        <v>1.706456035136504</v>
       </c>
       <c r="AQ473" t="n">
         <v>84.63302752293578</v>
@@ -77665,16 +77665,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3816350905604304</v>
+        <v>-0.3816350905604307</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.01460798460929558</v>
+        <v>0.01460798460929556</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.537958310473289</v>
+        <v>0.5379583104732891</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.651824891106274</v>
+        <v>1.651824891106279</v>
       </c>
       <c r="AQ474" t="n">
         <v>85.15981735159818</v>
@@ -77818,10 +77818,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.789815280543246</v>
+        <v>6.789815280543245</v>
       </c>
       <c r="AJ475" t="n">
-        <v>-0.01031527291385181</v>
+        <v>-0.01031527291385093</v>
       </c>
       <c r="AK475" t="n">
         <v>6.744939020214936</v>
@@ -77830,16 +77830,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3872393091179336</v>
+        <v>-0.3872393091179339</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.01685992867552227</v>
+        <v>0.01685992867552231</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.5511317941481411</v>
+        <v>0.5511317941481415</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.367727610243434</v>
+        <v>1.367727610243447</v>
       </c>
       <c r="AQ475" t="n">
         <v>82.95454545454545</v>
@@ -77983,10 +77983,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.801295181477315</v>
+        <v>6.801295181477309</v>
       </c>
       <c r="AJ476" t="n">
-        <v>-0.03129520055080093</v>
+        <v>-0.0312952005507956</v>
       </c>
       <c r="AK476" t="n">
         <v>6.772636231606738</v>
@@ -77995,16 +77995,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.393020019860339</v>
+        <v>-0.3930200198603389</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01873686412955489</v>
+        <v>0.01873686412955481</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5644439393662184</v>
+        <v>0.5644439393662187</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.126848917540616</v>
+        <v>1.126848917540677</v>
       </c>
       <c r="AQ476" t="n">
         <v>77.60180995475113</v>
@@ -78148,10 +78148,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI477" t="n">
-        <v>6.791632066062363</v>
+        <v>6.791632066062364</v>
       </c>
       <c r="AJ477" t="n">
-        <v>-0.0234321454080666</v>
+        <v>-0.02343214540806748</v>
       </c>
       <c r="AK477" t="n">
         <v>6.788619247652995</v>
@@ -78160,16 +78160,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3966294116439325</v>
+        <v>-0.3966294116439323</v>
       </c>
       <c r="AN477" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.576974471973372</v>
+        <v>0.5769744719733717</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.20813089547704</v>
+        <v>1.208130895477032</v>
       </c>
       <c r="AQ477" t="n">
         <v>75.22522522522523</v>
@@ -78313,10 +78313,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.779898505875916</v>
+        <v>6.779898505875918</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.007398467728943814</v>
+        <v>-0.00739846772894559</v>
       </c>
       <c r="AK478" t="n">
         <v>6.776305653888958</v>
@@ -78325,16 +78325,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3980313152890726</v>
+        <v>-0.3980313152890724</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.01933124704228378</v>
+        <v>0.0193312470422838</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5877384296086169</v>
+        <v>0.5877384296086161</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.37839336685457</v>
+        <v>1.378393366854553</v>
       </c>
       <c r="AQ478" t="n">
         <v>76.68161434977578</v>
@@ -78478,10 +78478,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.771360892616113</v>
+        <v>6.771360892616116</v>
       </c>
       <c r="AJ479" t="n">
-        <v>0.001139145530859587</v>
+        <v>0.001139145530856922</v>
       </c>
       <c r="AK479" t="n">
         <v>6.76492936370744</v>
@@ -78490,16 +78490,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.3979537985659305</v>
+        <v>-0.3979537985659302</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.0183584453609324</v>
+        <v>0.01835844536093246</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.6001791687136281</v>
+        <v>0.6001791687136286</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.46329795038702</v>
+        <v>1.463297950386995</v>
       </c>
       <c r="AQ479" t="n">
         <v>77.67857142857142</v>
@@ -78643,10 +78643,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.751667781721844</v>
+        <v>6.751667781721842</v>
       </c>
       <c r="AJ480" t="n">
-        <v>0.02083225642512865</v>
+        <v>0.02083225642513042</v>
       </c>
       <c r="AK480" t="n">
         <v>6.753855191419989</v>
@@ -78655,16 +78655,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3975762425746344</v>
+        <v>-0.3975762425746347</v>
       </c>
       <c r="AN480" t="n">
-        <v>0.01731206726614276</v>
+        <v>0.01731206726614282</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.6129676701055393</v>
+        <v>0.6129676701055397</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.668293556056609</v>
+        <v>1.668293556056633</v>
       </c>
       <c r="AQ480" t="n">
         <v>83.11111111111111</v>
@@ -78808,10 +78808,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.729738669869288</v>
+        <v>6.72973866986929</v>
       </c>
       <c r="AJ481" t="n">
-        <v>0.03586153459848518</v>
+        <v>0.0358615345984834</v>
       </c>
       <c r="AK481" t="n">
         <v>6.736226026398153</v>
@@ -78820,16 +78820,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3964908591695859</v>
+        <v>-0.3964908591695858</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01740130648959376</v>
+        <v>0.01740130648959375</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.6198907013195262</v>
+        <v>0.6198907013195265</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.817336727992024</v>
+        <v>1.817336727992009</v>
       </c>
       <c r="AQ481" t="n">
         <v>80.53097345132743</v>
@@ -78973,10 +78973,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.713320364291503</v>
+        <v>6.713320364291505</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.05917967385546952</v>
+        <v>0.05917967385546774</v>
       </c>
       <c r="AK482" t="n">
         <v>6.717723214958548</v>
@@ -78985,16 +78985,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.394760534481672</v>
+        <v>-0.3947605344816719</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.01742962324324016</v>
+        <v>0.01742962324324019</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6272835381163622</v>
+        <v>0.6272835381163618</v>
       </c>
       <c r="AP482" t="n">
-        <v>2.050548117521371</v>
+        <v>2.050548117521357</v>
       </c>
       <c r="AQ482" t="n">
         <v>87.44493392070484</v>
@@ -79138,10 +79138,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.731179671396989</v>
+        <v>6.731179671396997</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.04132036674998396</v>
+        <v>0.04132036674997597</v>
       </c>
       <c r="AK483" t="n">
         <v>6.699415101064979</v>
@@ -79153,13 +79153,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.01766596732646103</v>
+        <v>0.0176659673264611</v>
       </c>
       <c r="AO483" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.837051154471614</v>
+        <v>1.837051154471533</v>
       </c>
       <c r="AQ483" t="n">
         <v>86.84210526315789</v>
@@ -79303,10 +79303,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.740946959621007</v>
+        <v>6.740946959621005</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.03085308157772371</v>
+        <v>0.03085308157772548</v>
       </c>
       <c r="AK484" t="n">
         <v>6.714685154719483</v>
@@ -79315,16 +79315,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.3929423394238508</v>
+        <v>-0.392942339423851</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.01842070378092631</v>
+        <v>0.0184207037809263</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.640374511165978</v>
+        <v>0.6403745111659787</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.708199635372431</v>
+        <v>1.708199635372456</v>
       </c>
       <c r="AQ484" t="n">
         <v>84.71615720524017</v>
@@ -79468,10 +79468,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.7589577577717</v>
+        <v>6.758957757771704</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.006742105662137732</v>
+        <v>0.006742105662134179</v>
       </c>
       <c r="AK485" t="n">
         <v>6.722064699270507</v>
@@ -79480,16 +79480,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.3931401656438959</v>
+        <v>-0.3931401656438955</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01902711841846483</v>
+        <v>0.01902711841846487</v>
       </c>
       <c r="AO485" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP485" t="n">
-        <v>1.437000826386082</v>
+        <v>1.437000826386048</v>
       </c>
       <c r="AQ485" t="n">
         <v>80.43478260869566</v>
@@ -79633,10 +79633,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.763209774497792</v>
+        <v>6.763209774497788</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.007790133949473699</v>
+        <v>0.007790133949477251</v>
       </c>
       <c r="AK486" t="n">
         <v>6.739235851443908</v>
@@ -79645,16 +79645,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM486" t="n">
-        <v>-0.3951733572725242</v>
+        <v>-0.3951733572725246</v>
       </c>
       <c r="AN486" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO486" t="n">
-        <v>0.6590798145480943</v>
+        <v>0.6590798145480942</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.438670607116181</v>
+        <v>1.438670607116224</v>
       </c>
       <c r="AQ486" t="n">
         <v>80.73593073593074</v>
@@ -79810,16 +79810,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.3960001863323608</v>
+        <v>-0.396000186332361</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.02043272610569408</v>
+        <v>0.02043272610569401</v>
       </c>
       <c r="AO487" t="n">
-        <v>0.6685846444009622</v>
+        <v>0.6685846444009627</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.620848360850703</v>
+        <v>1.620848360850708</v>
       </c>
       <c r="AQ487" t="n">
         <v>81.25</v>
@@ -79963,10 +79963,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.714622134232894</v>
+        <v>6.714622134232888</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.04037798020802441</v>
+        <v>0.04037798020802974</v>
       </c>
       <c r="AK488" t="n">
         <v>6.746779913842831</v>
@@ -79975,16 +79975,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.396740905361911</v>
+        <v>-0.3967409053619114</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.02120763540003751</v>
+        <v>0.02120763540003743</v>
       </c>
       <c r="AO488" t="n">
-        <v>0.6777865296786982</v>
+        <v>0.6777865296786978</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.761306144067079</v>
+        <v>1.761306144067141</v>
       </c>
       <c r="AQ488" t="n">
         <v>83.90557939914163</v>
@@ -80128,28 +80128,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.731570059394423</v>
+        <v>6.73157005939442</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.01932973232310609</v>
+        <v>0.01932973232310964</v>
       </c>
       <c r="AK489" t="n">
-        <v>6.728823425344638</v>
+        <v>6.728823425344639</v>
       </c>
       <c r="AL489" t="n">
-        <v>0.02207636637289134</v>
+        <v>0.02207636637289045</v>
       </c>
       <c r="AM489" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN489" t="n">
-        <v>0.0220082962170377</v>
+        <v>0.02200829621703764</v>
       </c>
       <c r="AO489" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.524965965273205</v>
+        <v>1.524965965273247</v>
       </c>
       <c r="AQ489" t="n">
         <v>79.27350427350427</v>
@@ -80293,10 +80293,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI490" t="n">
-        <v>6.748064561399866</v>
+        <v>6.748064561399863</v>
       </c>
       <c r="AJ490" t="n">
-        <v>0.004235224214148126</v>
+        <v>0.00423522421415079</v>
       </c>
       <c r="AK490" t="n">
         <v>6.740096815166266</v>
@@ -80305,16 +80305,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3976889317784199</v>
+        <v>-0.3976889317784196</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.02268190844878654</v>
+        <v>0.02268190844878653</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6953567146475523</v>
+        <v>0.6953567146475526</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.355542505445795</v>
+        <v>1.355542505445825</v>
       </c>
       <c r="AQ490" t="n">
         <v>74.25531914893617</v>
@@ -80458,10 +80458,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.747226278872152</v>
+        <v>6.747226278872151</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.005973775296548745</v>
+        <v>0.005973775296550521</v>
       </c>
       <c r="AK491" t="n">
         <v>6.755554272205931</v>
@@ -80470,16 +80470,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.4003515275861345</v>
+        <v>-0.400351527586135</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02398656672240618</v>
+        <v>0.02398656672240616</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.7067969646460921</v>
+        <v>0.7067969646460924</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.365693002475583</v>
+        <v>1.365693002475604</v>
       </c>
       <c r="AQ491" t="n">
         <v>73.94067796610169</v>
@@ -80623,10 +80623,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.724989986752571</v>
+        <v>6.724989986752573</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.02471008267491914</v>
+        <v>0.02471008267491737</v>
       </c>
       <c r="AK492" t="n">
         <v>6.75925064743029</v>
@@ -80635,7 +80635,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM492" t="n">
-        <v>-0.4017887258056133</v>
+        <v>-0.4017887258056131</v>
       </c>
       <c r="AN492" t="n">
         <v>0.02482212216928553</v>
@@ -80644,7 +80644,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.553659964165104</v>
+        <v>1.553659964165089</v>
       </c>
       <c r="AQ492" t="n">
         <v>77.42616033755274</v>
@@ -80788,28 +80788,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.738231277482312</v>
+        <v>6.738231277482303</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.01056852339049108</v>
+        <v>0.01056852339049996</v>
       </c>
       <c r="AK493" t="n">
-        <v>6.734775445902895</v>
+        <v>6.734775445902896</v>
       </c>
       <c r="AL493" t="n">
-        <v>0.01402435496990773</v>
+        <v>0.01402435496990684</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.4022294042554291</v>
+        <v>-0.402229404255429</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02545790195722747</v>
+        <v>0.02545790195722734</v>
       </c>
       <c r="AO493" t="n">
-        <v>0.7273309315128231</v>
+        <v>0.7273309315128232</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.394965385482541</v>
+        <v>1.394965385482637</v>
       </c>
       <c r="AQ493" t="n">
         <v>74.78991596638656</v>
@@ -80953,10 +80953,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.718201282169581</v>
+        <v>6.718201282169575</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.02919852480673768</v>
+        <v>0.02919852480674301</v>
       </c>
       <c r="AK494" t="n">
         <v>6.753996132599221</v>
@@ -80965,16 +80965,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4027953816469058</v>
+        <v>-0.4027953816469059</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02608258444417638</v>
+        <v>0.02608258444417639</v>
       </c>
       <c r="AO494" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.580418325639223</v>
+        <v>1.58041832563928</v>
       </c>
       <c r="AQ494" t="n">
         <v>78.66108786610879</v>
@@ -81118,10 +81118,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.730898772467414</v>
+        <v>6.730898772467415</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.01650103450890406</v>
+        <v>0.01650103450890317</v>
       </c>
       <c r="AK495" t="n">
         <v>6.732394407262716</v>
@@ -81130,16 +81130,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.4025099007694142</v>
+        <v>-0.402509900769414</v>
       </c>
       <c r="AN495" t="n">
-        <v>0.02634377330607651</v>
+        <v>0.02634377330607648</v>
       </c>
       <c r="AO495" t="n">
-        <v>0.746561519528266</v>
+        <v>0.7465615195282662</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.437183781016376</v>
+        <v>1.437183781016368</v>
       </c>
       <c r="AQ495" t="n">
         <v>79.16666666666666</v>
@@ -81295,13 +81295,13 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4034224290251451</v>
+        <v>-0.4034224290251453</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02736182786837871</v>
+        <v>0.02736182786837866</v>
       </c>
       <c r="AO496" t="n">
-        <v>0.755189863471066</v>
+        <v>0.7551898634710656</v>
       </c>
       <c r="AP496" t="n">
         <v>1.302657079643351</v>
@@ -81448,10 +81448,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.755708466794879</v>
+        <v>6.75570846679488</v>
       </c>
       <c r="AJ497" t="n">
-        <v>-0.01240850570479068</v>
+        <v>-0.01240850570479246</v>
       </c>
       <c r="AK497" t="n">
         <v>6.746865899087779</v>
@@ -81460,16 +81460,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4037073020769307</v>
+        <v>-0.4037073020769305</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02778289906564352</v>
+        <v>0.02778289906564353</v>
       </c>
       <c r="AO497" t="n">
-        <v>0.7638221248099442</v>
+        <v>0.7638221248099444</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.120529895849335</v>
+        <v>1.120529895849317</v>
       </c>
       <c r="AQ497" t="n">
         <v>80.16528925619835</v>
@@ -81613,10 +81613,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.73601646973098</v>
+        <v>6.73601646973097</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.006783766017311343</v>
+        <v>0.006783766017321113</v>
       </c>
       <c r="AK498" t="n">
         <v>6.761018647414997</v>
@@ -81625,16 +81625,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.403510818895136</v>
+        <v>-0.4035108188951355</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02805871830419215</v>
+        <v>0.02805871830419202</v>
       </c>
       <c r="AO498" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.314684197600847</v>
+        <v>1.314684197600949</v>
       </c>
       <c r="AQ498" t="n">
         <v>83.74485596707819</v>
@@ -81793,7 +81793,7 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02827333203020888</v>
+        <v>0.02827333203020884</v>
       </c>
       <c r="AO499" t="n">
         <v>0.7726830480787004</v>
@@ -81943,10 +81943,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI500" t="n">
-        <v>6.725806144687715</v>
+        <v>6.725806144687716</v>
       </c>
       <c r="AJ500" t="n">
-        <v>0.01409396746438496</v>
+        <v>0.01409396746438318</v>
       </c>
       <c r="AK500" t="n">
         <v>6.744478107428201</v>
@@ -81955,16 +81955,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4027900432658338</v>
+        <v>-0.4027900432658339</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.02891453613228628</v>
+        <v>0.0289145361322863</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.7784357006627721</v>
+        <v>0.7784357006627718</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.374622432787288</v>
+        <v>1.374622432787269</v>
       </c>
       <c r="AQ500" t="n">
         <v>83.67346938775509</v>
@@ -82108,10 +82108,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.700854569500288</v>
+        <v>6.700854569500285</v>
       </c>
       <c r="AJ501" t="n">
-        <v>0.04174539464155735</v>
+        <v>0.04174539464156091</v>
       </c>
       <c r="AK501" t="n">
         <v>6.743301592583855</v>
@@ -82120,16 +82120,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.402742697458547</v>
+        <v>-0.4027426974585472</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.02955568036482276</v>
+        <v>0.0295556803648227</v>
       </c>
       <c r="AO501" t="n">
-        <v>0.7839391318357882</v>
+        <v>0.7839391318357879</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.650860867528298</v>
+        <v>1.650860867528334</v>
       </c>
       <c r="AQ501" t="n">
         <v>88.6178861788618</v>
@@ -82273,10 +82273,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI502" t="n">
-        <v>6.705597066237452</v>
+        <v>6.705597066237454</v>
       </c>
       <c r="AJ502" t="n">
-        <v>0.02390275065707925</v>
+        <v>0.02390275065707748</v>
       </c>
       <c r="AK502" t="n">
         <v>6.74285285202661</v>
@@ -82285,16 +82285,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM502" t="n">
-        <v>-0.401588500320058</v>
+        <v>-0.4015885003200582</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02985284499018426</v>
+        <v>0.02985284499018428</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.455808053167875</v>
+        <v>1.455808053167857</v>
       </c>
       <c r="AQ502" t="n">
         <v>85.22267206477733</v>
@@ -82438,28 +82438,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.686024746022946</v>
+        <v>6.686024746022948</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.0364751013891631</v>
+        <v>0.03647510138916132</v>
       </c>
       <c r="AK503" t="n">
-        <v>6.744526329542678</v>
+        <v>6.744526329542679</v>
       </c>
       <c r="AL503" t="n">
-        <v>-0.02202648213056868</v>
+        <v>-0.02202648213056957</v>
       </c>
       <c r="AM503" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02995529076246445</v>
+        <v>0.02995529076246446</v>
       </c>
       <c r="AO503" t="n">
-        <v>0.7933293013213367</v>
+        <v>0.7933293013213371</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.575202902620216</v>
+        <v>1.575202902620198</v>
       </c>
       <c r="AQ503" t="n">
         <v>84.4758064516129</v>
@@ -82603,10 +82603,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.689653251437546</v>
+        <v>6.689653251437547</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.03134694311201436</v>
+        <v>0.03134694311201347</v>
       </c>
       <c r="AK504" t="n">
         <v>6.730402461316146</v>
@@ -82615,16 +82615,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.3993041981056888</v>
+        <v>-0.3993041981056886</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.03010093147709741</v>
+        <v>0.03010093147709737</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7985853639949437</v>
+        <v>0.7985853639949436</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.512005484392179</v>
+        <v>1.51200548439217</v>
       </c>
       <c r="AQ504" t="n">
         <v>85.14056224899599</v>
@@ -82768,10 +82768,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.716786041117415</v>
+        <v>6.716786041117424</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.00511394514967467</v>
+        <v>0.005113945149665788</v>
       </c>
       <c r="AK505" t="n">
         <v>6.728106442363027</v>
@@ -82780,16 +82780,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.3976134529492091</v>
+        <v>-0.3976134529492094</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.03006044259180324</v>
+        <v>0.03006044259180338</v>
       </c>
       <c r="AO505" t="n">
-        <v>0.8026437279892851</v>
+        <v>0.8026437279892848</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.234777974751978</v>
+        <v>1.234777974751887</v>
       </c>
       <c r="AQ505" t="n">
         <v>81.59999999999999</v>
@@ -82933,10 +82933,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.721932795514441</v>
+        <v>6.72193279551444</v>
       </c>
       <c r="AJ506" t="n">
-        <v>-0.001632597913122424</v>
+        <v>-0.001632597913121536</v>
       </c>
       <c r="AK506" t="n">
         <v>6.752314636061016</v>
@@ -82948,13 +82948,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.03043336917902489</v>
+        <v>0.03043336917902487</v>
       </c>
       <c r="AO506" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.163823515923089</v>
+        <v>1.163823515923099</v>
       </c>
       <c r="AQ506" t="n">
         <v>82.19999999999999</v>
@@ -83098,28 +83098,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.718669003366535</v>
+        <v>6.718669003366529</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.003830844045574544</v>
+        <v>0.003830844045580761</v>
       </c>
       <c r="AK507" t="n">
-        <v>6.750203856204787</v>
+        <v>6.750203856204786</v>
       </c>
       <c r="AL507" t="n">
-        <v>-0.02770400879267765</v>
+        <v>-0.02770400879267676</v>
       </c>
       <c r="AM507" t="n">
-        <v>-0.3969152632178358</v>
+        <v>-0.3969152632178359</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03100517332816438</v>
+        <v>0.03100517332816427</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.8091236362457368</v>
+        <v>0.8091236362457366</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.217453571381047</v>
+        <v>1.217453571381111</v>
       </c>
       <c r="AQ507" t="n">
         <v>82.80000000000001</v>
@@ -83263,10 +83263,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.680190080689523</v>
+        <v>6.680190080689519</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.04230976672258624</v>
+        <v>0.04230976672259068</v>
       </c>
       <c r="AK508" t="n">
         <v>6.74780904069481</v>
@@ -83275,16 +83275,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3964565291282772</v>
+        <v>-0.3964565291282773</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03139664408873172</v>
+        <v>0.03139664408873165</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.8123541153569376</v>
+        <v>0.8123541153569371</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.604493248424094</v>
+        <v>1.60449324842414</v>
       </c>
       <c r="AQ508" t="n">
         <v>89.8</v>
@@ -83428,10 +83428,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.671580974366952</v>
+        <v>6.671580974366949</v>
       </c>
       <c r="AJ509" t="n">
-        <v>0.05441885778636824</v>
+        <v>0.05441885778637179</v>
       </c>
       <c r="AK509" t="n">
         <v>6.701878095437348</v>
@@ -83443,13 +83443,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03163116863423027</v>
+        <v>0.03163116863423025</v>
       </c>
       <c r="AO509" t="n">
-        <v>0.8147568654710424</v>
+        <v>0.8147568654710426</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.717274375116458</v>
+        <v>1.717274375116493</v>
       </c>
       <c r="AQ509" t="n">
         <v>90.2</v>
@@ -83593,28 +83593,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.656216276126097</v>
+        <v>6.656216276126093</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.06978355602722353</v>
+        <v>0.06978355602722708</v>
       </c>
       <c r="AK510" t="n">
-        <v>6.701765808189924</v>
+        <v>6.701765808189925</v>
       </c>
       <c r="AL510" t="n">
-        <v>0.02423402396339647</v>
+        <v>0.02423402396339558</v>
       </c>
       <c r="AM510" t="n">
-        <v>-0.3932426568003564</v>
+        <v>-0.3932426568003567</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.0319127327617218</v>
+        <v>0.03191273276172183</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8170879052811413</v>
+        <v>0.8170879052811416</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.858889534485343</v>
+        <v>1.858889534485378</v>
       </c>
       <c r="AQ510" t="n">
         <v>90.59999999999999</v>
@@ -83764,19 +83764,19 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK511" t="n">
-        <v>6.682658801267993</v>
+        <v>6.682658801267994</v>
       </c>
       <c r="AL511" t="n">
-        <v>0.03754126053010243</v>
+        <v>0.03754126053010154</v>
       </c>
       <c r="AM511" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03225018457163042</v>
+        <v>0.03225018457163047</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8195353634242114</v>
+        <v>0.8195353634242113</v>
       </c>
       <c r="AP511" t="n">
         <v>1.818117584748586</v>
@@ -83923,10 +83923,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.654231073451243</v>
+        <v>6.654231073451242</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.06476878921965579</v>
+        <v>0.06476878921965668</v>
       </c>
       <c r="AK512" t="n">
         <v>6.682840937292736</v>
@@ -83935,16 +83935,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM512" t="n">
-        <v>-0.3894836768645471</v>
+        <v>-0.3894836768645476</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03277193700354208</v>
+        <v>0.03277193700354209</v>
       </c>
       <c r="AO512" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.781104797300566</v>
+        <v>1.781104797300574</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.2</v>
@@ -84088,10 +84088,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.650937329061554</v>
+        <v>6.650937329061552</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.06806253360934456</v>
+        <v>0.06806253360934633</v>
       </c>
       <c r="AK513" t="n">
         <v>6.698821600583909</v>
@@ -84100,16 +84100,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM513" t="n">
-        <v>-0.3885003849593205</v>
+        <v>-0.3885003849593203</v>
       </c>
       <c r="AN513" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8264954348925954</v>
+        <v>0.8264954348925952</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.79987483353635</v>
+        <v>1.799874833536367</v>
       </c>
       <c r="AQ513" t="n">
         <v>91</v>
@@ -84253,10 +84253,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI514" t="n">
-        <v>6.651733245487365</v>
+        <v>6.651733245487366</v>
       </c>
       <c r="AJ514" t="n">
-        <v>0.05906692541107272</v>
+        <v>0.05906692541107184</v>
       </c>
       <c r="AK514" t="n">
         <v>6.69208631505748</v>
@@ -84265,16 +84265,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM514" t="n">
-        <v>-0.3869746098498524</v>
+        <v>-0.3869746098498528</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.0344188897752209</v>
+        <v>0.03441888977522091</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8294137131605728</v>
+        <v>0.8294137131605726</v>
       </c>
       <c r="AP514" t="n">
-        <v>1.696616308981454</v>
+        <v>1.696616308981445</v>
       </c>
       <c r="AQ514" t="n">
         <v>90.40000000000001</v>
@@ -84418,10 +84418,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.632036771677474</v>
+        <v>6.632036771677475</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.07876339922096331</v>
+        <v>0.07876339922096243</v>
       </c>
       <c r="AK515" t="n">
         <v>6.692627206904497</v>
@@ -84439,7 +84439,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.875440190456854</v>
+        <v>1.875440190456845</v>
       </c>
       <c r="AQ515" t="n">
         <v>91</v>
@@ -84583,10 +84583,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.617259294346139</v>
+        <v>6.617259294346145</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.09324046914263029</v>
+        <v>0.09324046914262496</v>
       </c>
       <c r="AK516" t="n">
         <v>6.685306332307247</v>
@@ -84598,13 +84598,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN516" t="n">
-        <v>0.03459091746240417</v>
+        <v>0.03459091746240425</v>
       </c>
       <c r="AO516" t="n">
-        <v>0.8328314813119074</v>
+        <v>0.8328314813119078</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.998006000856745</v>
+        <v>1.998006000856694</v>
       </c>
       <c r="AQ516" t="n">
         <v>91</v>
@@ -84760,16 +84760,16 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.379198503222778</v>
+        <v>-0.3791985032227784</v>
       </c>
       <c r="AN517" t="n">
-        <v>0.03468237364461174</v>
+        <v>0.03468237364461172</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8349203610870053</v>
+        <v>0.8349203610870052</v>
       </c>
       <c r="AP517" t="n">
-        <v>2.317228225252931</v>
+        <v>2.317228225252932</v>
       </c>
       <c r="AQ517" t="n">
         <v>93</v>
@@ -84928,13 +84928,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN518" t="n">
-        <v>0.03437427878524163</v>
+        <v>0.0343742787852416</v>
       </c>
       <c r="AO518" t="n">
-        <v>0.8337972329517069</v>
+        <v>0.8337972329517072</v>
       </c>
       <c r="AP518" t="n">
-        <v>2.426255822246373</v>
+        <v>2.426255822246375</v>
       </c>
       <c r="AQ518" t="n">
         <v>93.40000000000001</v>
@@ -85078,10 +85078,10 @@
         <v>-0.2483229054629721</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.570789830572489</v>
+        <v>6.57078983057249</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.1372103525329802</v>
+        <v>0.1372103525329784</v>
       </c>
       <c r="AK519" t="n">
         <v>6.617345065810827</v>
@@ -85090,16 +85090,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM519" t="n">
-        <v>-0.3685435183382903</v>
+        <v>-0.3685435183382902</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03361173230743109</v>
+        <v>0.03361173230743112</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8313650598704547</v>
+        <v>0.8313650598704546</v>
       </c>
       <c r="AP519" t="n">
-        <v>2.332216400368044</v>
+        <v>2.33221640036803</v>
       </c>
       <c r="AQ519" t="n">
         <v>91.8</v>
@@ -85243,10 +85243,10 @@
         <v>-0.2475852618441712</v>
       </c>
       <c r="AI520" t="n">
-        <v>6.574987720536733</v>
+        <v>6.574987720536736</v>
       </c>
       <c r="AJ520" t="n">
-        <v>0.1332122573380232</v>
+        <v>0.1332122573380197</v>
       </c>
       <c r="AK520" t="n">
         <v>6.613295682645951</v>
@@ -85255,16 +85255,16 @@
         <v>0.09490429522880461</v>
       </c>
       <c r="AM520" t="n">
-        <v>-0.362880333269974</v>
+        <v>-0.3628803332699742</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.0328662017206236</v>
+        <v>0.03286620172062364</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.82993355238613</v>
+        <v>0.8299335523861298</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.265952574875406</v>
+        <v>2.265952574875376</v>
       </c>
       <c r="AQ520" t="n">
         <v>91.8</v>
@@ -85420,16 +85420,16 @@
         <v>0.1007055635562768</v>
       </c>
       <c r="AM521" t="n">
-        <v>-0.3578313453157061</v>
+        <v>-0.3578313453157059</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03253304912369537</v>
+        <v>0.03253304912369535</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.8295016854680709</v>
+        <v>0.829501685468071</v>
       </c>
       <c r="AP521" t="n">
-        <v>2.256510029904997</v>
+        <v>2.256510029905</v>
       </c>
       <c r="AQ521" t="n">
         <v>92.40000000000001</v>
@@ -85588,13 +85588,13 @@
         <v>-0.3533816852595308</v>
       </c>
       <c r="AN522" t="n">
-        <v>0.03276281973018108</v>
+        <v>0.03276281973018107</v>
       </c>
       <c r="AO522" t="n">
-        <v>0.8294865216719109</v>
+        <v>0.8294865216719108</v>
       </c>
       <c r="AP522" t="n">
-        <v>1.905883880717604</v>
+        <v>1.905883880717606</v>
       </c>
       <c r="AQ522" t="n">
         <v>91.8</v>
@@ -85738,10 +85738,10 @@
         <v>-0.2155562137535618</v>
       </c>
       <c r="AI523" t="n">
-        <v>6.578171592819401</v>
+        <v>6.578171592819403</v>
       </c>
       <c r="AJ523" t="n">
-        <v>0.1292282523038901</v>
+        <v>0.1292282523038883</v>
       </c>
       <c r="AK523" t="n">
         <v>6.62059441621928</v>
@@ -85750,16 +85750,16 @@
         <v>0.08680542890401099</v>
       </c>
       <c r="AM523" t="n">
-        <v>-0.350362421245722</v>
+        <v>-0.3503624212457221</v>
       </c>
       <c r="AN523" t="n">
-        <v>0.03312067555156334</v>
+        <v>0.03312067555156335</v>
       </c>
       <c r="AO523" t="n">
-        <v>0.8307181423026834</v>
+        <v>0.8307181423026831</v>
       </c>
       <c r="AP523" t="n">
-        <v>2.154339795941636</v>
+        <v>2.154339795941623</v>
       </c>
       <c r="AQ523" t="n">
         <v>94</v>

--- a/docs/usdcny_tracker.xlsx
+++ b/docs/usdcny_tracker.xlsx
@@ -41365,10 +41365,10 @@
         <v>0.03605989982577285</v>
       </c>
       <c r="AI254" t="n">
-        <v>7.14851145777603</v>
+        <v>7.148511457776028</v>
       </c>
       <c r="AJ254" t="n">
-        <v>-0.01601128611465263</v>
+        <v>-0.01601128611465086</v>
       </c>
       <c r="AK254" t="n">
         <v>7.150963414761942</v>
@@ -41377,13 +41377,13 @@
         <v>-0.01846324310056513</v>
       </c>
       <c r="AM254" t="n">
-        <v>0.1011329645838857</v>
+        <v>0.1011329645838851</v>
       </c>
       <c r="AN254" t="n">
-        <v>0.002517185580011383</v>
+        <v>0.002517185580011447</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.2709113683260674</v>
+        <v>0.2709113683260677</v>
       </c>
       <c r="AP254" t="n">
         <v/>
@@ -41542,13 +41542,13 @@
         <v>-0.02009657268700504</v>
       </c>
       <c r="AM255" t="n">
-        <v>0.09870181295186436</v>
+        <v>0.09870181295186471</v>
       </c>
       <c r="AN255" t="n">
-        <v>0.002644711580562605</v>
+        <v>0.002644711580562537</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.2704892730019285</v>
+        <v>0.2704892730019304</v>
       </c>
       <c r="AP255" t="n">
         <v/>
@@ -41695,10 +41695,10 @@
         <v>0.06023453660656486</v>
       </c>
       <c r="AI256" t="n">
-        <v>7.153772633426657</v>
+        <v>7.153772633426659</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-0.03287247931288739</v>
+        <v>-0.03287247931288917</v>
       </c>
       <c r="AK256" t="n">
         <v>7.154757231824306</v>
@@ -41707,13 +41707,13 @@
         <v>-0.03385707771053603</v>
       </c>
       <c r="AM256" t="n">
-        <v>0.09555831842873888</v>
+        <v>0.09555831842873846</v>
       </c>
       <c r="AN256" t="n">
-        <v>0.002822832879878049</v>
+        <v>0.002822832879878071</v>
       </c>
       <c r="AO256" t="n">
-        <v>0.2697410008595938</v>
+        <v>0.2697410008595936</v>
       </c>
       <c r="AP256" t="n">
         <v/>
@@ -41860,10 +41860,10 @@
         <v>0.07366682469408126</v>
       </c>
       <c r="AI257" t="n">
-        <v>7.153331199414497</v>
+        <v>7.153331199414496</v>
       </c>
       <c r="AJ257" t="n">
-        <v>-0.0326313169071728</v>
+        <v>-0.03263131690717191</v>
       </c>
       <c r="AK257" t="n">
         <v>7.15450652143491</v>
@@ -41872,13 +41872,13 @@
         <v>-0.03380663892758573</v>
       </c>
       <c r="AM257" t="n">
-        <v>0.09188440665249918</v>
+        <v>0.0918844066524992</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.003041971996730116</v>
+        <v>0.003041971996730133</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.2698098046976254</v>
+        <v>0.2698098046976256</v>
       </c>
       <c r="AP257" t="n">
         <v/>
@@ -42025,10 +42025,10 @@
         <v>0.0838833176731173</v>
       </c>
       <c r="AI258" t="n">
-        <v>7.15694314831959</v>
+        <v>7.156943148319592</v>
       </c>
       <c r="AJ258" t="n">
-        <v>-0.0385430514262799</v>
+        <v>-0.03854305142628167</v>
       </c>
       <c r="AK258" t="n">
         <v>7.154505434137821</v>
@@ -42037,13 +42037,13 @@
         <v>-0.03610533724451059</v>
       </c>
       <c r="AM258" t="n">
-        <v>0.08748497753913362</v>
+        <v>0.08748497753913406</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.003298336925509857</v>
+        <v>0.003298336925509862</v>
       </c>
       <c r="AO258" t="n">
-        <v>0.2682008942988222</v>
+        <v>0.2682008942988235</v>
       </c>
       <c r="AP258" t="n">
         <v/>
@@ -42202,13 +42202,13 @@
         <v>-0.03485259480488789</v>
       </c>
       <c r="AM259" t="n">
-        <v>0.08245870840593096</v>
+        <v>0.0824587084059305</v>
       </c>
       <c r="AN259" t="n">
-        <v>0.003602928090795422</v>
+        <v>0.003602928090795432</v>
       </c>
       <c r="AO259" t="n">
-        <v>0.2685806390401518</v>
+        <v>0.2685806390401517</v>
       </c>
       <c r="AP259" t="n">
         <v/>
@@ -42370,10 +42370,10 @@
         <v>0.07850999177228171</v>
       </c>
       <c r="AN260" t="n">
-        <v>0.003819541738581439</v>
+        <v>0.003819541738581442</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.2696768907787754</v>
+        <v>0.2696768907787764</v>
       </c>
       <c r="AP260" t="n">
         <v/>
@@ -42520,10 +42520,10 @@
         <v>0.08832013912158398</v>
       </c>
       <c r="AI261" t="n">
-        <v>7.154685377655176</v>
+        <v>7.154685377655177</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-0.04048526245131878</v>
+        <v>-0.04048526245131967</v>
       </c>
       <c r="AK261" t="n">
         <v>7.15808570026938</v>
@@ -42532,13 +42532,13 @@
         <v>-0.04388558506552265</v>
       </c>
       <c r="AM261" t="n">
-        <v>0.07200163454913533</v>
+        <v>0.07200163454913491</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.004193740708391577</v>
+        <v>0.004193740708391541</v>
       </c>
       <c r="AO261" t="n">
-        <v>0.2701165988147326</v>
+        <v>0.270116598814735</v>
       </c>
       <c r="AP261" t="n">
         <v/>
@@ -42685,10 +42685,10 @@
         <v>0.07738804339094063</v>
       </c>
       <c r="AI262" t="n">
-        <v>7.158449213455078</v>
+        <v>7.158449213455076</v>
       </c>
       <c r="AJ262" t="n">
-        <v>-0.05514911885058549</v>
+        <v>-0.05514911885058371</v>
       </c>
       <c r="AK262" t="n">
         <v>7.157644979270017</v>
@@ -42697,13 +42697,13 @@
         <v>-0.05434488466552523</v>
       </c>
       <c r="AM262" t="n">
-        <v>0.06676111471939436</v>
+        <v>0.06676111471939408</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.004505219337594384</v>
+        <v>0.00450521933759436</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.2733976337163387</v>
+        <v>0.2733976337163381</v>
       </c>
       <c r="AP262" t="n">
         <v/>
@@ -42850,10 +42850,10 @@
         <v>0.070619162961159</v>
       </c>
       <c r="AI263" t="n">
-        <v>7.160761769069201</v>
+        <v>7.160761769069204</v>
       </c>
       <c r="AJ263" t="n">
-        <v>-0.04786198879576364</v>
+        <v>-0.04786198879576631</v>
       </c>
       <c r="AK263" t="n">
         <v>7.159146249199162</v>
@@ -42862,10 +42862,10 @@
         <v>-0.04624646892572493</v>
       </c>
       <c r="AM263" t="n">
-        <v>0.06148465881746766</v>
+        <v>0.06148465881746725</v>
       </c>
       <c r="AN263" t="n">
-        <v>0.004852471327681566</v>
+        <v>0.004852471327681615</v>
       </c>
       <c r="AO263" t="n">
         <v>0.2778048766368325</v>
@@ -43015,10 +43015,10 @@
         <v>0.05854783757191928</v>
       </c>
       <c r="AI264" t="n">
-        <v>7.162478122158094</v>
+        <v>7.162478122158095</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-0.04957834188465693</v>
+        <v>-0.04957834188465782</v>
       </c>
       <c r="AK264" t="n">
         <v>7.159578986975002</v>
@@ -43027,13 +43027,13 @@
         <v>-0.04667920670156445</v>
       </c>
       <c r="AM264" t="n">
-        <v>0.05582594297075712</v>
+        <v>0.05582594297075769</v>
       </c>
       <c r="AN264" t="n">
-        <v>0.005234102211236467</v>
+        <v>0.005234102211236422</v>
       </c>
       <c r="AO264" t="n">
-        <v>0.2824480243750598</v>
+        <v>0.282448024375059</v>
       </c>
       <c r="AP264" t="n">
         <v/>
@@ -43192,13 +43192,13 @@
         <v>-0.05041301594614023</v>
       </c>
       <c r="AM265" t="n">
-        <v>0.04949165986049463</v>
+        <v>0.04949165986049534</v>
       </c>
       <c r="AN265" t="n">
-        <v>0.005677665039252918</v>
+        <v>0.005677665039252891</v>
       </c>
       <c r="AO265" t="n">
-        <v>0.2878618994559794</v>
+        <v>0.2878618994559775</v>
       </c>
       <c r="AP265" t="n">
         <v/>
@@ -43357,13 +43357,13 @@
         <v>-0.04366872967721758</v>
       </c>
       <c r="AM266" t="n">
-        <v>0.04287777011073606</v>
+        <v>0.04287777011073584</v>
       </c>
       <c r="AN266" t="n">
-        <v>0.006155260602669625</v>
+        <v>0.006155260602669632</v>
       </c>
       <c r="AO266" t="n">
-        <v>0.2948468705933236</v>
+        <v>0.2948468705933219</v>
       </c>
       <c r="AP266" t="n">
         <v/>
@@ -43510,10 +43510,10 @@
         <v>0.06597820147444544</v>
       </c>
       <c r="AI267" t="n">
-        <v>7.173971773133423</v>
+        <v>7.173971773133425</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-0.04247200582995614</v>
+        <v>-0.04247200582995792</v>
       </c>
       <c r="AK267" t="n">
         <v>7.159255388854645</v>
@@ -43522,13 +43522,13 @@
         <v>-0.0277556215511785</v>
       </c>
       <c r="AM267" t="n">
-        <v>0.03486942009661778</v>
+        <v>0.0348694200966178</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.006728155724408201</v>
+        <v>0.006728155724408227</v>
       </c>
       <c r="AO267" t="n">
-        <v>0.3044998756423967</v>
+        <v>0.304499875642397</v>
       </c>
       <c r="AP267" t="n">
         <v/>
@@ -43675,25 +43675,25 @@
         <v>0.03450387599475935</v>
       </c>
       <c r="AI268" t="n">
-        <v>7.172030417300565</v>
+        <v>7.172030417300567</v>
       </c>
       <c r="AJ268" t="n">
-        <v>-0.03823038754592645</v>
+        <v>-0.03823038754592822</v>
       </c>
       <c r="AK268" t="n">
-        <v>7.167062070913352</v>
+        <v>7.167062070913353</v>
       </c>
       <c r="AL268" t="n">
-        <v>-0.03326204115871345</v>
+        <v>-0.03326204115871434</v>
       </c>
       <c r="AM268" t="n">
-        <v>0.03279550096037874</v>
+        <v>0.03279550096037902</v>
       </c>
       <c r="AN268" t="n">
-        <v>0.006903991232239758</v>
+        <v>0.006903991232239788</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.3170366335916608</v>
+        <v>0.3170366335916601</v>
       </c>
       <c r="AP268" t="n">
         <v/>
@@ -43840,10 +43840,10 @@
         <v>0.01496577045940839</v>
       </c>
       <c r="AI269" t="n">
-        <v>7.171236182927454</v>
+        <v>7.171236182927453</v>
       </c>
       <c r="AJ269" t="n">
-        <v>-0.0384360806935673</v>
+        <v>-0.03843608069356641</v>
       </c>
       <c r="AK269" t="n">
         <v>7.16747443083108</v>
@@ -43852,13 +43852,13 @@
         <v>-0.03467432859719377</v>
       </c>
       <c r="AM269" t="n">
-        <v>0.02972414459983913</v>
+        <v>0.02972414459983895</v>
       </c>
       <c r="AN269" t="n">
-        <v>0.007158147882859</v>
+        <v>0.007158147882858998</v>
       </c>
       <c r="AO269" t="n">
-        <v>0.3270754385893863</v>
+        <v>0.3270754385893867</v>
       </c>
       <c r="AP269" t="n">
         <v/>
@@ -44005,10 +44005,10 @@
         <v>0.000726259767448667</v>
       </c>
       <c r="AI270" t="n">
-        <v>7.170425137628194</v>
+        <v>7.170425137628191</v>
       </c>
       <c r="AJ270" t="n">
-        <v>-0.0510251132141315</v>
+        <v>-0.05102511321412884</v>
       </c>
       <c r="AK270" t="n">
         <v>7.168373097443463</v>
@@ -44017,13 +44017,13 @@
         <v>-0.04897307302940046</v>
       </c>
       <c r="AM270" t="n">
-        <v>0.02657019411530295</v>
+        <v>0.02657019411530269</v>
       </c>
       <c r="AN270" t="n">
-        <v>0.007420436972250398</v>
+        <v>0.007420436972250415</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.3357224795973281</v>
+        <v>0.3357224795973284</v>
       </c>
       <c r="AP270" t="n">
         <v/>
@@ -44182,13 +44182,13 @@
         <v>-0.04799018991142567</v>
       </c>
       <c r="AM271" t="n">
-        <v>0.02366886174665165</v>
+        <v>0.02366886174665103</v>
       </c>
       <c r="AN271" t="n">
-        <v>0.007679120311627231</v>
+        <v>0.007679120311627263</v>
       </c>
       <c r="AO271" t="n">
-        <v>0.345021958194194</v>
+        <v>0.3450219581941938</v>
       </c>
       <c r="AP271" t="n">
         <v/>
@@ -44335,10 +44335,10 @@
         <v>-0.01429980258852481</v>
       </c>
       <c r="AI272" t="n">
-        <v>7.172249622131823</v>
+        <v>7.172249622131827</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-0.05324966409349319</v>
+        <v>-0.05324966409349674</v>
       </c>
       <c r="AK272" t="n">
         <v>7.167365057101177</v>
@@ -44347,13 +44347,13 @@
         <v>-0.04836509906284725</v>
       </c>
       <c r="AM272" t="n">
-        <v>0.01956653131084189</v>
+        <v>0.01956653131084185</v>
       </c>
       <c r="AN272" t="n">
-        <v>0.008034860291676519</v>
+        <v>0.008034860291676559</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.3572033251592186</v>
+        <v>0.3572033251592189</v>
       </c>
       <c r="AP272" t="n">
         <v/>
@@ -44500,10 +44500,10 @@
         <v>-0.03963265513592606</v>
       </c>
       <c r="AI273" t="n">
-        <v>7.171656420777023</v>
+        <v>7.171656420777024</v>
       </c>
       <c r="AJ273" t="n">
-        <v>-0.0526564627386934</v>
+        <v>-0.05265646273869429</v>
       </c>
       <c r="AK273" t="n">
         <v>7.167567681415887</v>
@@ -44512,13 +44512,13 @@
         <v>-0.04856772337755721</v>
       </c>
       <c r="AM273" t="n">
-        <v>0.0163839608889081</v>
+        <v>0.01638396088890769</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.008326212487477898</v>
+        <v>0.008326212487477964</v>
       </c>
       <c r="AO273" t="n">
-        <v>0.3674516177552964</v>
+        <v>0.3674516177552961</v>
       </c>
       <c r="AP273" t="n">
         <v/>
@@ -44665,10 +44665,10 @@
         <v>-0.05031378947558718</v>
       </c>
       <c r="AI274" t="n">
-        <v>7.175289829564746</v>
+        <v>7.175289829564748</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-0.05628987152641596</v>
+        <v>-0.05628987152641773</v>
       </c>
       <c r="AK274" t="n">
         <v>7.167553154788029</v>
@@ -44677,13 +44677,13 @@
         <v>-0.04855319674969927</v>
       </c>
       <c r="AM274" t="n">
-        <v>0.01351198449095179</v>
+        <v>0.01351198449095157</v>
       </c>
       <c r="AN274" t="n">
-        <v>0.008601682347582911</v>
+        <v>0.008601682347582891</v>
       </c>
       <c r="AO274" t="n">
-        <v>0.375864684661753</v>
+        <v>0.3758646846617525</v>
       </c>
       <c r="AP274" t="n">
         <v/>
@@ -44836,19 +44836,19 @@
         <v>-0.06053731539109197</v>
       </c>
       <c r="AK275" t="n">
-        <v>7.167460814777641</v>
+        <v>7.16746081477764</v>
       </c>
       <c r="AL275" t="n">
-        <v>-0.048460856739311</v>
+        <v>-0.04846085673931011</v>
       </c>
       <c r="AM275" t="n">
-        <v>0.01196199498966377</v>
+        <v>0.01196199498966369</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.008797062853284078</v>
+        <v>0.008797062853284063</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.3847384959530228</v>
+        <v>0.3847384959530242</v>
       </c>
       <c r="AP275" t="n">
         <v/>
@@ -45156,10 +45156,10 @@
         <v>-0.04908749944312341</v>
       </c>
       <c r="AI277" t="n">
-        <v>7.189678003526526</v>
+        <v>7.189678003526525</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-0.07117777082999321</v>
+        <v>-0.07117777082999144</v>
       </c>
       <c r="AK277" t="n">
         <v/>
@@ -45168,13 +45168,13 @@
         <v/>
       </c>
       <c r="AM277" t="n">
-        <v>0.007307555239791735</v>
+        <v>0.007307555239791734</v>
       </c>
       <c r="AN277" t="n">
-        <v>0.009236289154790363</v>
+        <v>0.009236289154790337</v>
       </c>
       <c r="AO277" t="n">
-        <v>0.4010397173569483</v>
+        <v>0.401039717356949</v>
       </c>
       <c r="AP277" t="n">
         <v/>
@@ -45321,10 +45321,10 @@
         <v>-0.0602716731514974</v>
       </c>
       <c r="AI278" t="n">
-        <v>7.183919177237466</v>
+        <v>7.183919177237467</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-0.056419120017007</v>
+        <v>-0.05641912001700788</v>
       </c>
       <c r="AK278" t="n">
         <v>7.168706858585229</v>
@@ -45333,13 +45333,13 @@
         <v>-0.04120680136476995</v>
       </c>
       <c r="AM278" t="n">
-        <v>0.006573598200531427</v>
+        <v>0.006573598200530942</v>
       </c>
       <c r="AN278" t="n">
-        <v>0.009378157495070007</v>
+        <v>0.009378157495070056</v>
       </c>
       <c r="AO278" t="n">
-        <v>0.4093166892046876</v>
+        <v>0.4093166892046883</v>
       </c>
       <c r="AP278" t="n">
         <v/>
@@ -45498,13 +45498,13 @@
         <v>-0.05819279691304491</v>
       </c>
       <c r="AM279" t="n">
-        <v>0.00571969992866044</v>
+        <v>0.005719699928660468</v>
       </c>
       <c r="AN279" t="n">
-        <v>0.009535855797507651</v>
+        <v>0.009535855797507643</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.4189456552735351</v>
+        <v>0.4189456552735356</v>
       </c>
       <c r="AP279" t="n">
         <v/>
@@ -45651,10 +45651,10 @@
         <v>-0.1051462201792015</v>
       </c>
       <c r="AI280" t="n">
-        <v>7.183803634757355</v>
+        <v>7.183803634757356</v>
       </c>
       <c r="AJ280" t="n">
-        <v>-0.08380373012478692</v>
+        <v>-0.08380373012478781</v>
       </c>
       <c r="AK280" t="n">
         <v>7.157754776965645</v>
@@ -45663,13 +45663,13 @@
         <v>-0.05775487233307697</v>
       </c>
       <c r="AM280" t="n">
-        <v>0.007205793377055721</v>
+        <v>0.007205793377056199</v>
       </c>
       <c r="AN280" t="n">
-        <v>0.00954184705868257</v>
+        <v>0.009541847058682544</v>
       </c>
       <c r="AO280" t="n">
-        <v>0.4265135453780416</v>
+        <v>0.4265135453780396</v>
       </c>
       <c r="AP280" t="n">
         <v/>
@@ -45822,19 +45822,19 @@
         <v>-0.04186112720060375</v>
       </c>
       <c r="AK281" t="n">
-        <v>7.153578345933643</v>
+        <v>7.153578345933642</v>
       </c>
       <c r="AL281" t="n">
-        <v>-0.01517826811381884</v>
+        <v>-0.01517826811381795</v>
       </c>
       <c r="AM281" t="n">
-        <v>0.009937300636551421</v>
+        <v>0.009937300636551308</v>
       </c>
       <c r="AN281" t="n">
-        <v>0.009475108253955637</v>
+        <v>0.00947510825395563</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.4359288044119891</v>
+        <v>0.4359288044119884</v>
       </c>
       <c r="AP281" t="n">
         <v/>
@@ -45981,10 +45981,10 @@
         <v>-0.0993026708649456</v>
       </c>
       <c r="AI282" t="n">
-        <v>7.175374323571332</v>
+        <v>7.175374323571331</v>
       </c>
       <c r="AJ282" t="n">
-        <v>-0.04917412444413483</v>
+        <v>-0.04917412444413394</v>
       </c>
       <c r="AK282" t="n">
         <v>7.155226204999164</v>
@@ -45993,13 +45993,13 @@
         <v>-0.02902600587196691</v>
       </c>
       <c r="AM282" t="n">
-        <v>0.01039951522374727</v>
+        <v>0.01039951522374721</v>
       </c>
       <c r="AN282" t="n">
-        <v>0.009534227083684297</v>
+        <v>0.009534227083684284</v>
       </c>
       <c r="AO282" t="n">
-        <v>0.4462248692464653</v>
+        <v>0.446224869246465</v>
       </c>
       <c r="AP282" t="n">
         <v/>
@@ -46158,13 +46158,13 @@
         <v>-0.02211721731157024</v>
       </c>
       <c r="AM283" t="n">
-        <v>0.01174445052819296</v>
+        <v>0.01174445052819259</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.009539024405591111</v>
+        <v>0.009539024405591096</v>
       </c>
       <c r="AO283" t="n">
-        <v>0.4561706550234662</v>
+        <v>0.4561706550234678</v>
       </c>
       <c r="AP283" t="n">
         <v/>
@@ -46311,10 +46311,10 @@
         <v>-0.09256710934012702</v>
       </c>
       <c r="AI284" t="n">
-        <v>7.176295466764673</v>
+        <v>7.176295466764674</v>
       </c>
       <c r="AJ284" t="n">
-        <v>-0.04989547286818841</v>
+        <v>-0.04989547286818929</v>
       </c>
       <c r="AK284" t="n">
         <v>7.150954883812801</v>
@@ -46323,13 +46323,13 @@
         <v>-0.02455488991631682</v>
       </c>
       <c r="AM284" t="n">
-        <v>0.01399948938427885</v>
+        <v>0.01399948938427905</v>
       </c>
       <c r="AN284" t="n">
-        <v>0.009474826008246765</v>
+        <v>0.009474826008246758</v>
       </c>
       <c r="AO284" t="n">
-        <v>0.4654004237248376</v>
+        <v>0.4654004237248369</v>
       </c>
       <c r="AP284" t="n">
         <v/>
@@ -46488,13 +46488,13 @@
         <v>-0.03029690774014515</v>
       </c>
       <c r="AM285" t="n">
-        <v>0.01676993900799728</v>
+        <v>0.01676993900799729</v>
       </c>
       <c r="AN285" t="n">
-        <v>0.00937702887797469</v>
+        <v>0.009377028877974699</v>
       </c>
       <c r="AO285" t="n">
-        <v>0.4767009396389351</v>
+        <v>0.476700939638935</v>
       </c>
       <c r="AP285" t="n">
         <v/>
@@ -46656,10 +46656,10 @@
         <v>0.02078303625607592</v>
       </c>
       <c r="AN286" t="n">
-        <v>0.009204864903404482</v>
+        <v>0.009204864903404497</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.4883841032893032</v>
+        <v>0.4883841032893044</v>
       </c>
       <c r="AP286" t="n">
         <v/>
@@ -46818,13 +46818,13 @@
         <v>-0.02196025087507625</v>
       </c>
       <c r="AM287" t="n">
-        <v>0.02435543352765317</v>
+        <v>0.02435543352765289</v>
       </c>
       <c r="AN287" t="n">
-        <v>0.00904582198402234</v>
+        <v>0.009045821984022376</v>
       </c>
       <c r="AO287" t="n">
-        <v>0.4990078266507749</v>
+        <v>0.4990078266507766</v>
       </c>
       <c r="AP287" t="n">
         <v/>
@@ -46971,10 +46971,10 @@
         <v>-0.09293491351397787</v>
       </c>
       <c r="AI288" t="n">
-        <v>7.175210595491394</v>
+        <v>7.175210595491395</v>
       </c>
       <c r="AJ288" t="n">
-        <v>-0.04951059854315165</v>
+        <v>-0.04951059854315254</v>
       </c>
       <c r="AK288" t="n">
         <v>7.151444380572274</v>
@@ -46983,13 +46983,13 @@
         <v>-0.02574438362403164</v>
       </c>
       <c r="AM288" t="n">
-        <v>0.02840267381959008</v>
+        <v>0.02840267381959001</v>
       </c>
       <c r="AN288" t="n">
-        <v>0.008843610540066056</v>
+        <v>0.008843610540066053</v>
       </c>
       <c r="AO288" t="n">
-        <v>0.5123725312709417</v>
+        <v>0.5123725312709416</v>
       </c>
       <c r="AP288" t="n">
         <v/>
@@ -47139,7 +47139,7 @@
         <v>7.172876300902407</v>
       </c>
       <c r="AJ289" t="n">
-        <v>-0.05177635201935082</v>
+        <v>-0.05177635201934994</v>
       </c>
       <c r="AK289" t="n">
         <v>7.151307469847429</v>
@@ -47148,13 +47148,13 @@
         <v>-0.03020752096437196</v>
       </c>
       <c r="AM289" t="n">
-        <v>0.03189518855892809</v>
+        <v>0.03189518855892823</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.008740250954211236</v>
+        <v>0.008740250954211215</v>
       </c>
       <c r="AO289" t="n">
-        <v>0.5303980242931252</v>
+        <v>0.5303980242931245</v>
       </c>
       <c r="AP289" t="n">
         <v/>
@@ -47301,10 +47301,10 @@
         <v>-0.1437954235802437</v>
       </c>
       <c r="AI290" t="n">
-        <v>7.172173616645314</v>
+        <v>7.172173616645312</v>
       </c>
       <c r="AJ290" t="n">
-        <v>-0.06197368836162287</v>
+        <v>-0.06197368836162021</v>
       </c>
       <c r="AK290" t="n">
         <v>7.152170779642037</v>
@@ -47313,13 +47313,13 @@
         <v>-0.04197085135834566</v>
       </c>
       <c r="AM290" t="n">
-        <v>0.03448417181877479</v>
+        <v>0.03448417181877508</v>
       </c>
       <c r="AN290" t="n">
-        <v>0.008638296330047519</v>
+        <v>0.008638296330047493</v>
       </c>
       <c r="AO290" t="n">
-        <v>0.5364004192446541</v>
+        <v>0.536400419244653</v>
       </c>
       <c r="AP290" t="n">
         <v/>
@@ -47469,7 +47469,7 @@
         <v>7.181424055064165</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-0.08262387272163618</v>
+        <v>-0.08262387272163529</v>
       </c>
       <c r="AK291" t="n">
         <v>7.155242422656618</v>
@@ -47481,10 +47481,10 @@
         <v>0.03784058849303745</v>
       </c>
       <c r="AN291" t="n">
-        <v>0.008527848481957647</v>
+        <v>0.008527848481957645</v>
       </c>
       <c r="AO291" t="n">
-        <v>0.5479838817473681</v>
+        <v>0.5479838817473677</v>
       </c>
       <c r="AP291" t="n">
         <v/>
@@ -47631,10 +47631,10 @@
         <v>-0.2138699739470606</v>
       </c>
       <c r="AI292" t="n">
-        <v>7.184188525998638</v>
+        <v>7.18418852599864</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-0.08518854888682181</v>
+        <v>-0.08518854888682359</v>
       </c>
       <c r="AK292" t="n">
         <v>7.174067278312125</v>
@@ -47643,13 +47643,13 @@
         <v>-0.07506730120030891</v>
       </c>
       <c r="AM292" t="n">
-        <v>0.03996026841105382</v>
+        <v>0.03996026841105445</v>
       </c>
       <c r="AN292" t="n">
-        <v>0.008497979041970699</v>
+        <v>0.008497979041970659</v>
       </c>
       <c r="AO292" t="n">
-        <v>0.553499551641869</v>
+        <v>0.5534995516418705</v>
       </c>
       <c r="AP292" t="n">
         <v/>
@@ -47796,10 +47796,10 @@
         <v>-0.2129374582072066</v>
       </c>
       <c r="AI293" t="n">
-        <v>7.185513015749274</v>
+        <v>7.185513015749276</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-0.07571315384131516</v>
+        <v>-0.07571315384131694</v>
       </c>
       <c r="AK293" t="n">
         <v>7.175957423377739</v>
@@ -47808,13 +47808,13 @@
         <v>-0.06615756146977958</v>
       </c>
       <c r="AM293" t="n">
-        <v>0.04233079818885083</v>
+        <v>0.04233079818885077</v>
       </c>
       <c r="AN293" t="n">
-        <v>0.008432709457890224</v>
+        <v>0.008432709457890229</v>
       </c>
       <c r="AO293" t="n">
-        <v>0.5557951014363788</v>
+        <v>0.5557951014363787</v>
       </c>
       <c r="AP293" t="n">
         <v/>
@@ -47967,19 +47967,19 @@
         <v>-0.06806937067198415</v>
       </c>
       <c r="AK294" t="n">
-        <v>7.174765662541792</v>
+        <v>7.174765662541793</v>
       </c>
       <c r="AL294" t="n">
-        <v>-0.05786569534818842</v>
+        <v>-0.05786569534818931</v>
       </c>
       <c r="AM294" t="n">
-        <v>0.04394124299371556</v>
+        <v>0.04394124299371591</v>
       </c>
       <c r="AN294" t="n">
-        <v>0.008396387260434506</v>
+        <v>0.008396387260434499</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.5565519909812453</v>
+        <v>0.5565519909812464</v>
       </c>
       <c r="AP294" t="n">
         <v/>
@@ -48126,10 +48126,10 @@
         <v>-0.1625350000743673</v>
       </c>
       <c r="AI295" t="n">
-        <v>7.18593291662286</v>
+        <v>7.185932916622859</v>
       </c>
       <c r="AJ295" t="n">
-        <v>-0.01413278005669749</v>
+        <v>-0.0141327800566966</v>
       </c>
       <c r="AK295" t="n">
         <v>7.172730869790855</v>
@@ -48138,13 +48138,13 @@
         <v>-0.0009307332246928368</v>
       </c>
       <c r="AM295" t="n">
-        <v>0.04590755972499803</v>
+        <v>0.04590755972499789</v>
       </c>
       <c r="AN295" t="n">
-        <v>0.008346613473328291</v>
+        <v>0.008346613473328282</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.5588443644440755</v>
+        <v>0.5588443644440741</v>
       </c>
       <c r="AP295" t="n">
         <v/>
@@ -48291,10 +48291,10 @@
         <v>-0.1975827263561092</v>
       </c>
       <c r="AI296" t="n">
-        <v>7.187602005018014</v>
+        <v>7.187602005018013</v>
       </c>
       <c r="AJ296" t="n">
-        <v>-0.0581020927560516</v>
+        <v>-0.05810209275604983</v>
       </c>
       <c r="AK296" t="n">
         <v>7.168923754586179</v>
@@ -48303,10 +48303,10 @@
         <v>-0.03942384232421592</v>
       </c>
       <c r="AM296" t="n">
-        <v>0.04658552832149689</v>
+        <v>0.04658552832149703</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.008354655440128426</v>
+        <v>0.008354655440128402</v>
       </c>
       <c r="AO296" t="n">
         <v>0.5613325805619827</v>
@@ -48468,13 +48468,13 @@
         <v>-0.0481634168034546</v>
       </c>
       <c r="AM297" t="n">
-        <v>0.04820692510781883</v>
+        <v>0.04820692510781933</v>
       </c>
       <c r="AN297" t="n">
-        <v>0.008303818071592054</v>
+        <v>0.008303818071592001</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.5626464255878516</v>
+        <v>0.5626464255878519</v>
       </c>
       <c r="AP297" t="n">
         <v/>
@@ -48633,13 +48633,13 @@
         <v>-0.04682475108676254</v>
       </c>
       <c r="AM298" t="n">
-        <v>0.04983084886774771</v>
+        <v>0.04983084886774743</v>
       </c>
       <c r="AN298" t="n">
-        <v>0.008251024544031682</v>
+        <v>0.008251024544031704</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.5641340630354323</v>
+        <v>0.5641340630354328</v>
       </c>
       <c r="AP298" t="n">
         <v/>
@@ -48798,13 +48798,13 @@
         <v>-0.04377692986925563</v>
       </c>
       <c r="AM299" t="n">
-        <v>0.05170461329917048</v>
+        <v>0.05170461329917111</v>
       </c>
       <c r="AN299" t="n">
-        <v>0.008192726391276836</v>
+        <v>0.008192726391276807</v>
       </c>
       <c r="AO299" t="n">
-        <v>0.5658195968244545</v>
+        <v>0.5658195968244528</v>
       </c>
       <c r="AP299" t="n">
         <v/>
@@ -48963,13 +48963,13 @@
         <v>-0.04686532642971564</v>
       </c>
       <c r="AM300" t="n">
-        <v>0.05348369580043772</v>
+        <v>0.05348369580043773</v>
       </c>
       <c r="AN300" t="n">
-        <v>0.008143044151838252</v>
+        <v>0.008143044151838245</v>
       </c>
       <c r="AO300" t="n">
-        <v>0.5671346874885956</v>
+        <v>0.5671346874885959</v>
       </c>
       <c r="AP300" t="n">
         <v/>
@@ -49116,10 +49116,10 @@
         <v>-0.2206523140034822</v>
       </c>
       <c r="AI301" t="n">
-        <v>7.175179910580593</v>
+        <v>7.175179910580594</v>
       </c>
       <c r="AJ301" t="n">
-        <v>-0.05588002196975328</v>
+        <v>-0.05588002196975417</v>
       </c>
       <c r="AK301" t="n">
         <v>7.165699812335961</v>
@@ -49128,13 +49128,13 @@
         <v>-0.04639992372512136</v>
       </c>
       <c r="AM301" t="n">
-        <v>0.0552098256436935</v>
+        <v>0.05520982564369371</v>
       </c>
       <c r="AN301" t="n">
-        <v>0.008124788470663643</v>
+        <v>0.008124788470663676</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.5701242576280905</v>
+        <v>0.5701242576280907</v>
       </c>
       <c r="AP301" t="n">
         <v/>
@@ -49281,10 +49281,10 @@
         <v>-0.2139978497244117</v>
       </c>
       <c r="AI302" t="n">
-        <v>7.173581841712229</v>
+        <v>7.173581841712227</v>
       </c>
       <c r="AJ302" t="n">
-        <v>-0.05428195310138939</v>
+        <v>-0.05428195310138761</v>
       </c>
       <c r="AK302" t="n">
         <v>7.162626578418298</v>
@@ -49293,13 +49293,13 @@
         <v>-0.0433266898074578</v>
       </c>
       <c r="AM302" t="n">
-        <v>0.05644890839995281</v>
+        <v>0.05644890839995315</v>
       </c>
       <c r="AN302" t="n">
-        <v>0.008105230252153447</v>
+        <v>0.008105230252153435</v>
       </c>
       <c r="AO302" t="n">
-        <v>0.5713754740215494</v>
+        <v>0.5713754740215509</v>
       </c>
       <c r="AP302" t="n">
         <v/>
@@ -49446,10 +49446,10 @@
         <v>-0.2255875315995155</v>
       </c>
       <c r="AI303" t="n">
-        <v>7.176011726611838</v>
+        <v>7.176011726611837</v>
       </c>
       <c r="AJ303" t="n">
-        <v>-0.06401173805592997</v>
+        <v>-0.06401173805592908</v>
       </c>
       <c r="AK303" t="n">
         <v>7.165542054185019</v>
@@ -49458,13 +49458,13 @@
         <v>-0.05354206562911124</v>
       </c>
       <c r="AM303" t="n">
-        <v>0.05727663218544039</v>
+        <v>0.05727663218544052</v>
       </c>
       <c r="AN303" t="n">
-        <v>0.008124035226526509</v>
+        <v>0.00812403522652648</v>
       </c>
       <c r="AO303" t="n">
-        <v>0.5730004147442582</v>
+        <v>0.573000414744258</v>
       </c>
       <c r="AP303" t="n">
         <v/>
@@ -49611,10 +49611,10 @@
         <v>-0.23600166872325</v>
       </c>
       <c r="AI304" t="n">
-        <v>7.176983405221908</v>
+        <v>7.17698340522191</v>
       </c>
       <c r="AJ304" t="n">
-        <v>-0.07778363334080485</v>
+        <v>-0.07778363334080662</v>
       </c>
       <c r="AK304" t="n">
         <v>7.170209849598846</v>
@@ -49623,13 +49623,13 @@
         <v>-0.0710100777177427</v>
       </c>
       <c r="AM304" t="n">
-        <v>0.05825580143844532</v>
+        <v>0.05825580143844533</v>
       </c>
       <c r="AN304" t="n">
-        <v>0.008106527117828759</v>
+        <v>0.008106527117828777</v>
       </c>
       <c r="AO304" t="n">
-        <v>0.5728585525731367</v>
+        <v>0.5728585525731363</v>
       </c>
       <c r="AP304" t="n">
         <v/>
@@ -49776,10 +49776,10 @@
         <v>-0.2217684408926868</v>
       </c>
       <c r="AI305" t="n">
-        <v>7.174841035863563</v>
+        <v>7.174841035863564</v>
       </c>
       <c r="AJ305" t="n">
-        <v>-0.06734095956961816</v>
+        <v>-0.06734095956961905</v>
       </c>
       <c r="AK305" t="n">
         <v>7.166925629020364</v>
@@ -49788,13 +49788,13 @@
         <v>-0.05942555272641847</v>
       </c>
       <c r="AM305" t="n">
-        <v>0.05980113395910441</v>
+        <v>0.05980113395910436</v>
       </c>
       <c r="AN305" t="n">
-        <v>0.008056914781095341</v>
+        <v>0.008056914781095353</v>
       </c>
       <c r="AO305" t="n">
-        <v>0.5723268395754482</v>
+        <v>0.5723268395754473</v>
       </c>
       <c r="AP305" t="n">
         <v/>
@@ -49941,10 +49941,10 @@
         <v>-0.2313975039992577</v>
       </c>
       <c r="AI306" t="n">
-        <v>7.179777800337526</v>
+        <v>7.179777800337525</v>
       </c>
       <c r="AJ306" t="n">
-        <v>-0.07227772404358035</v>
+        <v>-0.07227772404357946</v>
       </c>
       <c r="AK306" t="n">
         <v>7.163704513322672</v>
@@ -49956,10 +49956,10 @@
         <v>0.06123176845175175</v>
       </c>
       <c r="AN306" t="n">
-        <v>0.008007544934860184</v>
+        <v>0.008007544934860181</v>
       </c>
       <c r="AO306" t="n">
-        <v>0.5724055344141876</v>
+        <v>0.5724055344141883</v>
       </c>
       <c r="AP306" t="n">
         <v/>
@@ -50106,10 +50106,10 @@
         <v>-0.2654192580687731</v>
       </c>
       <c r="AI307" t="n">
-        <v>7.176651545551677</v>
+        <v>7.176651545551679</v>
       </c>
       <c r="AJ307" t="n">
-        <v>-0.06915146925773197</v>
+        <v>-0.06915146925773374</v>
       </c>
       <c r="AK307" t="n">
         <v>7.163430147298699</v>
@@ -50118,13 +50118,13 @@
         <v>-0.05593007100475411</v>
       </c>
       <c r="AM307" t="n">
-        <v>0.06321929365038026</v>
+        <v>0.06321929365037962</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.007927773212025837</v>
+        <v>0.007927773212025854</v>
       </c>
       <c r="AO307" t="n">
-        <v>0.5724635828813827</v>
+        <v>0.572463582881384</v>
       </c>
       <c r="AP307" t="n">
         <v/>
@@ -50271,10 +50271,10 @@
         <v>-0.2822241096256803</v>
       </c>
       <c r="AI308" t="n">
-        <v>7.173279688539582</v>
+        <v>7.173279688539583</v>
       </c>
       <c r="AJ308" t="n">
-        <v>-0.06577961224563644</v>
+        <v>-0.06577961224563733</v>
       </c>
       <c r="AK308" t="n">
         <v>7.158871783064204</v>
@@ -50283,13 +50283,13 @@
         <v>-0.05137170677025882</v>
       </c>
       <c r="AM308" t="n">
-        <v>0.0652304825929222</v>
+        <v>0.06523048259292186</v>
       </c>
       <c r="AN308" t="n">
-        <v>0.007809540836127932</v>
+        <v>0.007809540836127948</v>
       </c>
       <c r="AO308" t="n">
-        <v>0.571009056129113</v>
+        <v>0.5710090561291132</v>
       </c>
       <c r="AP308" t="n">
         <v/>
@@ -50436,10 +50436,10 @@
         <v>-0.2721538773773498</v>
       </c>
       <c r="AI309" t="n">
-        <v>7.168542018724479</v>
+        <v>7.168542018724481</v>
       </c>
       <c r="AJ309" t="n">
-        <v>-0.06194221098522146</v>
+        <v>-0.06194221098522323</v>
       </c>
       <c r="AK309" t="n">
         <v>7.152618309751275</v>
@@ -50448,13 +50448,13 @@
         <v>-0.04601850201201696</v>
       </c>
       <c r="AM309" t="n">
-        <v>0.06741194340959927</v>
+        <v>0.067411943409599</v>
       </c>
       <c r="AN309" t="n">
-        <v>0.007660511838810949</v>
+        <v>0.007660511838810988</v>
       </c>
       <c r="AO309" t="n">
-        <v>0.5694124450603408</v>
+        <v>0.5694124450603424</v>
       </c>
       <c r="AP309" t="n">
         <v/>
@@ -50601,10 +50601,10 @@
         <v>-0.2675606045328731</v>
       </c>
       <c r="AI310" t="n">
-        <v>7.161829635752617</v>
+        <v>7.161829635752616</v>
       </c>
       <c r="AJ310" t="n">
-        <v>-0.0596296044720992</v>
+        <v>-0.05962960447209831</v>
       </c>
       <c r="AK310" t="n">
         <v>7.144956229005203</v>
@@ -50613,13 +50613,13 @@
         <v>-0.04275619772468531</v>
       </c>
       <c r="AM310" t="n">
-        <v>0.06977835201573281</v>
+        <v>0.06977835201573312</v>
       </c>
       <c r="AN310" t="n">
-        <v>0.007516908058882097</v>
+        <v>0.007516908058882096</v>
       </c>
       <c r="AO310" t="n">
-        <v>0.5690369646398684</v>
+        <v>0.5690369646398685</v>
       </c>
       <c r="AP310" t="n">
         <v/>
@@ -50769,7 +50769,7 @@
         <v>7.161493151625399</v>
       </c>
       <c r="AJ311" t="n">
-        <v>-0.07699331565738188</v>
+        <v>-0.07699331565738099</v>
       </c>
       <c r="AK311" t="n">
         <v>7.140422114543136</v>
@@ -50778,13 +50778,13 @@
         <v>-0.05592227857511833</v>
       </c>
       <c r="AM311" t="n">
-        <v>0.07195366789421676</v>
+        <v>0.07195366789421653</v>
       </c>
       <c r="AN311" t="n">
-        <v>0.007394117938767422</v>
+        <v>0.007394117938767417</v>
       </c>
       <c r="AO311" t="n">
-        <v>0.5693040973288199</v>
+        <v>0.5693040973288186</v>
       </c>
       <c r="AP311" t="n">
         <v/>
@@ -50943,10 +50943,10 @@
         <v>-0.06626438186446837</v>
       </c>
       <c r="AM312" t="n">
-        <v>0.07456301989532414</v>
+        <v>0.07456301989532385</v>
       </c>
       <c r="AN312" t="n">
-        <v>0.007241314760731996</v>
+        <v>0.007241314760732032</v>
       </c>
       <c r="AO312" t="n">
         <v>0.5685877661607006</v>
@@ -51108,13 +51108,13 @@
         <v>-0.06553096641284206</v>
       </c>
       <c r="AM313" t="n">
-        <v>0.07747971887849607</v>
+        <v>0.07747971887849656</v>
       </c>
       <c r="AN313" t="n">
-        <v>0.007090143655538702</v>
+        <v>0.0070901436555387</v>
       </c>
       <c r="AO313" t="n">
-        <v>0.5681709745664091</v>
+        <v>0.5681709745664083</v>
       </c>
       <c r="AP313" t="n">
         <v/>
@@ -51261,10 +51261,10 @@
         <v>-0.3036781468995891</v>
       </c>
       <c r="AI314" t="n">
-        <v>7.165084051386047</v>
+        <v>7.165084051386049</v>
       </c>
       <c r="AJ314" t="n">
-        <v>-0.08998410631768738</v>
+        <v>-0.08998410631768916</v>
       </c>
       <c r="AK314" t="n">
         <v>7.14582045097363</v>
@@ -51273,16 +51273,16 @@
         <v>-0.07072050590527112</v>
       </c>
       <c r="AM314" t="n">
-        <v>0.08000072584212836</v>
+        <v>0.08000072584212846</v>
       </c>
       <c r="AN314" t="n">
         <v>0.00698867205589912</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.5684087510734968</v>
+        <v>0.5684087510734981</v>
       </c>
       <c r="AP314" t="n">
-        <v>-1.988377511683731</v>
+        <v>-1.98837751168381</v>
       </c>
       <c r="AQ314" t="n">
         <v>2.5</v>
@@ -51426,10 +51426,10 @@
         <v>-0.3351409963047667</v>
       </c>
       <c r="AI315" t="n">
-        <v>7.161419741275553</v>
+        <v>7.161419741275552</v>
       </c>
       <c r="AJ315" t="n">
-        <v>-0.08971964514518227</v>
+        <v>-0.08971964514518138</v>
       </c>
       <c r="AK315" t="n">
         <v>7.155707108847959</v>
@@ -51438,16 +51438,16 @@
         <v>-0.08400701271758759</v>
       </c>
       <c r="AM315" t="n">
-        <v>0.08204996863507528</v>
+        <v>0.08204996863507508</v>
       </c>
       <c r="AN315" t="n">
-        <v>0.006919462921967468</v>
+        <v>0.006919462921967476</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.5672869954461461</v>
+        <v>0.5672869954461468</v>
       </c>
       <c r="AP315" t="n">
-        <v>-1.896343483293377</v>
+        <v>-1.896343483293307</v>
       </c>
       <c r="AQ315" t="n">
         <v>2.459016393442623</v>
@@ -51591,10 +51591,10 @@
         <v>-0.3494490385718745</v>
       </c>
       <c r="AI316" t="n">
-        <v>7.155488092579303</v>
+        <v>7.155488092579304</v>
       </c>
       <c r="AJ316" t="n">
-        <v>-0.08548792091792645</v>
+        <v>-0.08548792091792734</v>
       </c>
       <c r="AK316" t="n">
         <v>7.150451326287159</v>
@@ -51603,16 +51603,16 @@
         <v>-0.08045115462578245</v>
       </c>
       <c r="AM316" t="n">
-        <v>0.08469403553214211</v>
+        <v>0.08469403553214168</v>
       </c>
       <c r="AN316" t="n">
-        <v>0.006815201188096372</v>
+        <v>0.006815201188096393</v>
       </c>
       <c r="AO316" t="n">
-        <v>0.5663505631396781</v>
+        <v>0.5663505631396779</v>
       </c>
       <c r="AP316" t="n">
-        <v>-1.605047536006344</v>
+        <v>-1.605047536006375</v>
       </c>
       <c r="AQ316" t="n">
         <v>4.032258064516129</v>
@@ -51756,10 +51756,10 @@
         <v>-0.3557799054506994</v>
       </c>
       <c r="AI317" t="n">
-        <v>7.15883281736398</v>
+        <v>7.158832817363979</v>
       </c>
       <c r="AJ317" t="n">
-        <v>-0.09523275404000575</v>
+        <v>-0.09523275404000398</v>
       </c>
       <c r="AK317" t="n">
         <v>7.147115644271845</v>
@@ -51768,16 +51768,16 @@
         <v>-0.08351558094787048</v>
       </c>
       <c r="AM317" t="n">
-        <v>0.08699523504893142</v>
+        <v>0.08699523504893081</v>
       </c>
       <c r="AN317" t="n">
-        <v>0.006735083295172689</v>
+        <v>0.006735083295172709</v>
       </c>
       <c r="AO317" t="n">
-        <v>0.5654743012892984</v>
+        <v>0.5654743012892969</v>
       </c>
       <c r="AP317" t="n">
-        <v>-2.063097093717068</v>
+        <v>-2.063097093716959</v>
       </c>
       <c r="AQ317" t="n">
         <v>1.587301587301587</v>
@@ -51921,10 +51921,10 @@
         <v>-0.3632934184713195</v>
       </c>
       <c r="AI318" t="n">
-        <v>7.161703459649029</v>
+        <v>7.161703459649028</v>
       </c>
       <c r="AJ318" t="n">
-        <v>-0.09030329409116788</v>
+        <v>-0.090303294091167</v>
       </c>
       <c r="AK318" t="n">
         <v>7.152131804583207</v>
@@ -51933,16 +51933,16 @@
         <v>-0.08073163902534564</v>
       </c>
       <c r="AM318" t="n">
-        <v>0.08901512474159586</v>
+        <v>0.08901512474159551</v>
       </c>
       <c r="AN318" t="n">
-        <v>0.006668288608758129</v>
+        <v>0.006668288608758136</v>
       </c>
       <c r="AO318" t="n">
-        <v>0.5631673144521655</v>
+        <v>0.5631673144521659</v>
       </c>
       <c r="AP318" t="n">
-        <v>-1.734612101677275</v>
+        <v>-1.73461210167722</v>
       </c>
       <c r="AQ318" t="n">
         <v>2.34375</v>
@@ -52086,10 +52086,10 @@
         <v>-0.3615670622017326</v>
       </c>
       <c r="AI319" t="n">
-        <v>7.162535384813327</v>
+        <v>7.162535384813326</v>
       </c>
       <c r="AJ319" t="n">
-        <v>-0.09293527952768255</v>
+        <v>-0.09293527952768166</v>
       </c>
       <c r="AK319" t="n">
         <v>7.157753883768605</v>
@@ -52098,16 +52098,16 @@
         <v>-0.08815377848296091</v>
       </c>
       <c r="AM319" t="n">
-        <v>0.09116436352661936</v>
+        <v>0.09116436352661951</v>
       </c>
       <c r="AN319" t="n">
-        <v>0.006624805625172246</v>
+        <v>0.006624805625172231</v>
       </c>
       <c r="AO319" t="n">
-        <v>0.5612585549312785</v>
+        <v>0.5612585549312774</v>
       </c>
       <c r="AP319" t="n">
-        <v>-1.813360317430219</v>
+        <v>-1.813360317430168</v>
       </c>
       <c r="AQ319" t="n">
         <v>3.076923076923077</v>
@@ -52251,10 +52251,10 @@
         <v>-0.3699685236925987</v>
       </c>
       <c r="AI320" t="n">
-        <v>7.166818450294681</v>
+        <v>7.166818450294679</v>
       </c>
       <c r="AJ320" t="n">
-        <v>-0.09581835111255188</v>
+        <v>-0.0958183511125501</v>
       </c>
       <c r="AK320" t="n">
         <v>7.158620349112049</v>
@@ -52263,16 +52263,16 @@
         <v>-0.08762024992991968</v>
       </c>
       <c r="AM320" t="n">
-        <v>0.09320704864741212</v>
+        <v>0.09320704864741254</v>
       </c>
       <c r="AN320" t="n">
-        <v>0.006594358041710186</v>
+        <v>0.006594358041710158</v>
       </c>
       <c r="AO320" t="n">
-        <v>0.5590514368572459</v>
+        <v>0.5590514368572466</v>
       </c>
       <c r="AP320" t="n">
-        <v>-1.895966724576408</v>
+        <v>-1.89596672457632</v>
       </c>
       <c r="AQ320" t="n">
         <v>1.515151515151515</v>
@@ -52416,10 +52416,10 @@
         <v>-0.3878706131836447</v>
       </c>
       <c r="AI321" t="n">
-        <v>7.157691007010208</v>
+        <v>7.157691007010206</v>
       </c>
       <c r="AJ321" t="n">
-        <v>-0.09439087425874337</v>
+        <v>-0.0943908742587416</v>
       </c>
       <c r="AK321" t="n">
         <v>7.164942158928604</v>
@@ -52428,16 +52428,16 @@
         <v>-0.1016420261771387</v>
       </c>
       <c r="AM321" t="n">
-        <v>0.09491020692123982</v>
+        <v>0.09491020692123933</v>
       </c>
       <c r="AN321" t="n">
-        <v>0.006562900445417306</v>
+        <v>0.006562900445417311</v>
       </c>
       <c r="AO321" t="n">
-        <v>0.5551825155208129</v>
+        <v>0.5551825155208145</v>
       </c>
       <c r="AP321" t="n">
-        <v>-1.76456520872203</v>
+        <v>-1.764565208721948</v>
       </c>
       <c r="AQ321" t="n">
         <v>2.985074626865671</v>
@@ -52581,10 +52581,10 @@
         <v>-0.3918468637202563</v>
       </c>
       <c r="AI322" t="n">
-        <v>7.15177642643162</v>
+        <v>7.151776426431621</v>
       </c>
       <c r="AJ322" t="n">
-        <v>-0.08777629673191267</v>
+        <v>-0.08777629673191356</v>
       </c>
       <c r="AK322" t="n">
         <v>7.154764404811184</v>
@@ -52593,16 +52593,16 @@
         <v>-0.09076427511147678</v>
       </c>
       <c r="AM322" t="n">
-        <v>0.0970468105051025</v>
+        <v>0.097046810505102</v>
       </c>
       <c r="AN322" t="n">
-        <v>0.006523984583215632</v>
+        <v>0.006523984583215639</v>
       </c>
       <c r="AO322" t="n">
-        <v>0.5522992358254815</v>
+        <v>0.5522992358254805</v>
       </c>
       <c r="AP322" t="n">
-        <v>-1.395417465036313</v>
+        <v>-1.395417465036362</v>
       </c>
       <c r="AQ322" t="n">
         <v>6.617647058823529</v>
@@ -52746,10 +52746,10 @@
         <v>-0.3916447439110531</v>
       </c>
       <c r="AI323" t="n">
-        <v>7.150992404319682</v>
+        <v>7.15099240431968</v>
       </c>
       <c r="AJ323" t="n">
-        <v>-0.09309245238486774</v>
+        <v>-0.09309245238486596</v>
       </c>
       <c r="AK323" t="n">
         <v>7.150261540163492</v>
@@ -52758,16 +52758,16 @@
         <v>-0.09236158822867768</v>
       </c>
       <c r="AM323" t="n">
-        <v>0.09904197982498671</v>
+        <v>0.09904197982498698</v>
       </c>
       <c r="AN323" t="n">
-        <v>0.006505848878330779</v>
+        <v>0.006505848878330736</v>
       </c>
       <c r="AO323" t="n">
-        <v>0.5500699492277157</v>
+        <v>0.5500699492277152</v>
       </c>
       <c r="AP323" t="n">
-        <v>-1.62020961669321</v>
+        <v>-1.620209616693131</v>
       </c>
       <c r="AQ323" t="n">
         <v>4.347826086956522</v>
@@ -52911,10 +52911,10 @@
         <v>-0.3988412977451103</v>
       </c>
       <c r="AI324" t="n">
-        <v>7.147140093605207</v>
+        <v>7.147140093605204</v>
       </c>
       <c r="AJ324" t="n">
-        <v>-0.09314019278733543</v>
+        <v>-0.09314019278733277</v>
       </c>
       <c r="AK324" t="n">
         <v>7.148879230661717</v>
@@ -52923,16 +52923,16 @@
         <v>-0.09487932984384617</v>
       </c>
       <c r="AM324" t="n">
-        <v>0.1013300516539142</v>
+        <v>0.1013300516539148</v>
       </c>
       <c r="AN324" t="n">
-        <v>0.006479631055951091</v>
+        <v>0.006479631055951007</v>
       </c>
       <c r="AO324" t="n">
-        <v>0.5478993564899672</v>
+        <v>0.5478993564899665</v>
       </c>
       <c r="AP324" t="n">
-        <v>-1.581244845226393</v>
+        <v>-1.581244845226278</v>
       </c>
       <c r="AQ324" t="n">
         <v>3.571428571428572</v>
@@ -53082,22 +53082,22 @@
         <v>-0.09566610762749406</v>
       </c>
       <c r="AK325" t="n">
-        <v>7.145816711184185</v>
+        <v>7.145816711184184</v>
       </c>
       <c r="AL325" t="n">
-        <v>-0.09881677984873605</v>
+        <v>-0.09881677984873516</v>
       </c>
       <c r="AM325" t="n">
-        <v>0.1033273874042092</v>
+        <v>0.1033273874042088</v>
       </c>
       <c r="AN325" t="n">
-        <v>0.006468712737497656</v>
+        <v>0.006468712737497662</v>
       </c>
       <c r="AO325" t="n">
-        <v>0.5455500876237913</v>
+        <v>0.5455500876237902</v>
       </c>
       <c r="AP325" t="n">
-        <v>-1.660158210133175</v>
+        <v>-1.660158210133191</v>
       </c>
       <c r="AQ325" t="n">
         <v>2.112676056338028</v>
@@ -53244,7 +53244,7 @@
         <v>7.144526091548792</v>
       </c>
       <c r="AJ326" t="n">
-        <v>-0.102826205226771</v>
+        <v>-0.1028262052267701</v>
       </c>
       <c r="AK326" t="n">
         <v>7.139092738717567</v>
@@ -53253,16 +53253,16 @@
         <v>-0.0973928523955454</v>
       </c>
       <c r="AM326" t="n">
-        <v>0.1056457020972505</v>
+        <v>0.1056457020972507</v>
       </c>
       <c r="AN326" t="n">
-        <v>0.006435041090934217</v>
+        <v>0.006435041090934165</v>
       </c>
       <c r="AO326" t="n">
-        <v>0.5433399026839674</v>
+        <v>0.5433399026839665</v>
       </c>
       <c r="AP326" t="n">
-        <v>-1.941500569207702</v>
+        <v>-1.94150056920768</v>
       </c>
       <c r="AQ326" t="n">
         <v>2.777777777777778</v>
@@ -53409,7 +53409,7 @@
         <v>7.1420963178674</v>
       </c>
       <c r="AJ327" t="n">
-        <v>-0.09909609661495811</v>
+        <v>-0.099096096614959</v>
       </c>
       <c r="AK327" t="n">
         <v>7.140479586010682</v>
@@ -53418,16 +53418,16 @@
         <v>-0.09747936475824037</v>
       </c>
       <c r="AM327" t="n">
-        <v>0.1076802390191602</v>
+        <v>0.10768023901916</v>
       </c>
       <c r="AN327" t="n">
-        <v>0.006405465077205527</v>
+        <v>0.006405465077205547</v>
       </c>
       <c r="AO327" t="n">
-        <v>0.5402459241219618</v>
+        <v>0.5402459241219614</v>
       </c>
       <c r="AP327" t="n">
-        <v>-1.714497414188894</v>
+        <v>-1.714497414188951</v>
       </c>
       <c r="AQ327" t="n">
         <v>2.73972602739726</v>
@@ -53571,10 +53571,10 @@
         <v>-0.4015468715636477</v>
       </c>
       <c r="AI328" t="n">
-        <v>7.145743344370558</v>
+        <v>7.145743344370562</v>
       </c>
       <c r="AJ328" t="n">
-        <v>-0.1052431803385758</v>
+        <v>-0.1052431803385794</v>
       </c>
       <c r="AK328" t="n">
         <v>7.136632587022158</v>
@@ -53583,16 +53583,16 @@
         <v>-0.09613242299017521</v>
       </c>
       <c r="AM328" t="n">
-        <v>0.1100130126862084</v>
+        <v>0.1100130126862077</v>
       </c>
       <c r="AN328" t="n">
-        <v>0.00636655476599019</v>
+        <v>0.006366554765990282</v>
       </c>
       <c r="AO328" t="n">
-        <v>0.5375708073661639</v>
+        <v>0.5375708073661647</v>
       </c>
       <c r="AP328" t="n">
-        <v>-1.938373670414687</v>
+        <v>-1.938373670414857</v>
       </c>
       <c r="AQ328" t="n">
         <v>2.702702702702703</v>
@@ -53748,16 +53748,16 @@
         <v>-0.1003826761731075</v>
       </c>
       <c r="AM329" t="n">
-        <v>0.1122475627674581</v>
+        <v>0.1122475627674583</v>
       </c>
       <c r="AN329" t="n">
-        <v>0.00633726551246258</v>
+        <v>0.006337265512462553</v>
       </c>
       <c r="AO329" t="n">
-        <v>0.5341613739773232</v>
+        <v>0.5341613739773245</v>
       </c>
       <c r="AP329" t="n">
-        <v>-1.591025362058569</v>
+        <v>-1.591025362058573</v>
       </c>
       <c r="AQ329" t="n">
         <v>3.333333333333334</v>
@@ -53901,10 +53901,10 @@
         <v>-0.4194458068451228</v>
       </c>
       <c r="AI330" t="n">
-        <v>7.14251973303301</v>
+        <v>7.142519733033009</v>
       </c>
       <c r="AJ330" t="n">
-        <v>-0.1016195026252955</v>
+        <v>-0.1016195026252946</v>
       </c>
       <c r="AK330" t="n">
         <v>7.135172643569136</v>
@@ -53913,16 +53913,16 @@
         <v>-0.09427241316142165</v>
       </c>
       <c r="AM330" t="n">
-        <v>0.114650916606818</v>
+        <v>0.1146509166068179</v>
       </c>
       <c r="AN330" t="n">
-        <v>0.006337163869517234</v>
+        <v>0.006337163869517243</v>
       </c>
       <c r="AO330" t="n">
-        <v>0.5319767312874311</v>
+        <v>0.5319767312874306</v>
       </c>
       <c r="AP330" t="n">
-        <v>-1.685657147129874</v>
+        <v>-1.685657147129841</v>
       </c>
       <c r="AQ330" t="n">
         <v>2.631578947368421</v>
@@ -54078,16 +54078,16 @@
         <v>-0.1157443855426425</v>
       </c>
       <c r="AM331" t="n">
-        <v>0.1171965158426948</v>
+        <v>0.1171965158426952</v>
       </c>
       <c r="AN331" t="n">
-        <v>0.00636765350379247</v>
+        <v>0.006367653503792481</v>
       </c>
       <c r="AO331" t="n">
         <v>0.5297997924290396</v>
       </c>
       <c r="AP331" t="n">
-        <v>-2.151331574347164</v>
+        <v>-2.151331574347173</v>
       </c>
       <c r="AQ331" t="n">
         <v>1.298701298701299</v>
@@ -54231,10 +54231,10 @@
         <v>-0.4546428959546889</v>
       </c>
       <c r="AI332" t="n">
-        <v>7.140851085964112</v>
+        <v>7.140851085964109</v>
       </c>
       <c r="AJ332" t="n">
-        <v>-0.1128512080344244</v>
+        <v>-0.1128512080344217</v>
       </c>
       <c r="AK332" t="n">
         <v>7.142783913375006</v>
@@ -54243,16 +54243,16 @@
         <v>-0.1147840354453189</v>
       </c>
       <c r="AM332" t="n">
-        <v>0.1192272052402563</v>
+        <v>0.119227205240256</v>
       </c>
       <c r="AN332" t="n">
-        <v>0.00638313303870985</v>
+        <v>0.006383133038709798</v>
       </c>
       <c r="AO332" t="n">
-        <v>0.5243060286247104</v>
+        <v>0.5243060286247103</v>
       </c>
       <c r="AP332" t="n">
-        <v>-2.038368479510088</v>
+        <v>-2.038368479509989</v>
       </c>
       <c r="AQ332" t="n">
         <v>2.564102564102564</v>
@@ -54396,10 +54396,10 @@
         <v>-0.4514109361425884</v>
       </c>
       <c r="AI333" t="n">
-        <v>7.139245392969565</v>
+        <v>7.139245392969567</v>
       </c>
       <c r="AJ333" t="n">
-        <v>-0.1112455150398777</v>
+        <v>-0.1112455150398795</v>
       </c>
       <c r="AK333" t="n">
         <v>7.141836927013541</v>
@@ -54408,16 +54408,16 @@
         <v>-0.1138370490838536</v>
       </c>
       <c r="AM333" t="n">
-        <v>0.1211746327267792</v>
+        <v>0.1211746327267789</v>
       </c>
       <c r="AN333" t="n">
-        <v>0.006404909068509461</v>
+        <v>0.006404909068509476</v>
       </c>
       <c r="AO333" t="n">
-        <v>0.518531819719905</v>
+        <v>0.5185318197199045</v>
       </c>
       <c r="AP333" t="n">
-        <v>-1.909934895071758</v>
+        <v>-1.909934895071841</v>
       </c>
       <c r="AQ333" t="n">
         <v>3.79746835443038</v>
@@ -54561,10 +54561,10 @@
         <v>-0.4456818656992843</v>
       </c>
       <c r="AI334" t="n">
-        <v>7.136520216281902</v>
+        <v>7.136520216281903</v>
       </c>
       <c r="AJ334" t="n">
-        <v>-0.1085203383522142</v>
+        <v>-0.108520338352216</v>
       </c>
       <c r="AK334" t="n">
         <v>7.13958125183462</v>
@@ -54573,16 +54573,16 @@
         <v>-0.1115813739049329</v>
       </c>
       <c r="AM334" t="n">
-        <v>0.1228335954516143</v>
+        <v>0.1228335954516147</v>
       </c>
       <c r="AN334" t="n">
-        <v>0.006430223802628476</v>
+        <v>0.006430223802628449</v>
       </c>
       <c r="AO334" t="n">
-        <v>0.5122974965428486</v>
+        <v>0.5122974965428477</v>
       </c>
       <c r="AP334" t="n">
-        <v>-1.748195911884297</v>
+        <v>-1.748195911884376</v>
       </c>
       <c r="AQ334" t="n">
         <v>5</v>
@@ -54741,13 +54741,13 @@
         <v>0.1242273613249475</v>
       </c>
       <c r="AN335" t="n">
-        <v>0.006430805642792618</v>
+        <v>0.006430805642792636</v>
       </c>
       <c r="AO335" t="n">
-        <v>0.5056597011855207</v>
+        <v>0.5056597011855208</v>
       </c>
       <c r="AP335" t="n">
-        <v>-2.518543666780579</v>
+        <v>-2.518543666780585</v>
       </c>
       <c r="AQ335" t="n">
         <v>1.234567901234568</v>
@@ -54891,10 +54891,10 @@
         <v>-0.4840529494402279</v>
       </c>
       <c r="AI336" t="n">
-        <v>7.13656285793475</v>
+        <v>7.136562857934749</v>
       </c>
       <c r="AJ336" t="n">
-        <v>-0.1404629090516929</v>
+        <v>-0.140462909051692</v>
       </c>
       <c r="AK336" t="n">
         <v>7.132705938528055</v>
@@ -54906,13 +54906,13 @@
         <v>0.1266923315791516</v>
       </c>
       <c r="AN336" t="n">
-        <v>0.006419568115912051</v>
+        <v>0.006419568115912044</v>
       </c>
       <c r="AO336" t="n">
-        <v>0.4979995576252233</v>
+        <v>0.4979995576252224</v>
       </c>
       <c r="AP336" t="n">
-        <v>-2.780157364931463</v>
+        <v>-2.78015736493144</v>
       </c>
       <c r="AQ336" t="n">
         <v>1.219512195121951</v>
@@ -55056,10 +55056,10 @@
         <v>-0.4823371026895638</v>
       </c>
       <c r="AI337" t="n">
-        <v>7.135435320996254</v>
+        <v>7.135435320996258</v>
       </c>
       <c r="AJ337" t="n">
-        <v>-0.1393353721131971</v>
+        <v>-0.1393353721132016</v>
       </c>
       <c r="AK337" t="n">
         <v>7.134470034900207</v>
@@ -55068,16 +55068,16 @@
         <v>-0.13837008601715</v>
       </c>
       <c r="AM337" t="n">
-        <v>0.1290155516631951</v>
+        <v>0.1290155516631957</v>
       </c>
       <c r="AN337" t="n">
-        <v>0.006423940675024553</v>
+        <v>0.006423940675024581</v>
       </c>
       <c r="AO337" t="n">
-        <v>0.4894561560517011</v>
+        <v>0.489456156051701</v>
       </c>
       <c r="AP337" t="n">
-        <v>-2.604030180601759</v>
+        <v>-2.604030180601917</v>
       </c>
       <c r="AQ337" t="n">
         <v>3.012048192771084</v>
@@ -55221,10 +55221,10 @@
         <v>-0.4702399637485986</v>
       </c>
       <c r="AI338" t="n">
-        <v>7.135221482968312</v>
+        <v>7.135221482968309</v>
       </c>
       <c r="AJ338" t="n">
-        <v>-0.1391215340852554</v>
+        <v>-0.1391215340852527</v>
       </c>
       <c r="AK338" t="n">
         <v>7.133435115388912</v>
@@ -55233,16 +55233,16 @@
         <v>-0.1373351665058555</v>
       </c>
       <c r="AM338" t="n">
-        <v>0.1313692321875792</v>
+        <v>0.1313692321875789</v>
       </c>
       <c r="AN338" t="n">
-        <v>0.006422605647444502</v>
+        <v>0.006422605647444513</v>
       </c>
       <c r="AO338" t="n">
-        <v>0.4811392039904442</v>
+        <v>0.4811392039904447</v>
       </c>
       <c r="AP338" t="n">
-        <v>-2.481964435352832</v>
+        <v>-2.481964435352737</v>
       </c>
       <c r="AQ338" t="n">
         <v>4.166666666666666</v>
@@ -55386,10 +55386,10 @@
         <v>-0.4677967551610873</v>
       </c>
       <c r="AI339" t="n">
-        <v>7.129120131622732</v>
+        <v>7.129120131622726</v>
       </c>
       <c r="AJ339" t="n">
-        <v>-0.1360199653019309</v>
+        <v>-0.1360199653019256</v>
       </c>
       <c r="AK339" t="n">
         <v>7.132510325395203</v>
@@ -55398,16 +55398,16 @@
         <v>-0.1394101590744024</v>
       </c>
       <c r="AM339" t="n">
-        <v>0.1334873867685108</v>
+        <v>0.1334873867685099</v>
       </c>
       <c r="AN339" t="n">
-        <v>0.006388619079873553</v>
+        <v>0.006388619079873509</v>
       </c>
       <c r="AO339" t="n">
-        <v>0.4724960612931048</v>
+        <v>0.4724960612931043</v>
       </c>
       <c r="AP339" t="n">
-        <v>-2.281661036829281</v>
+        <v>-2.28166103682911</v>
       </c>
       <c r="AQ339" t="n">
         <v>5.294117647058823</v>
@@ -55563,16 +55563,16 @@
         <v>-0.1376903678117394</v>
       </c>
       <c r="AM340" t="n">
-        <v>0.1357975915367741</v>
+        <v>0.1357975915367747</v>
       </c>
       <c r="AN340" t="n">
-        <v>0.006324213907675122</v>
+        <v>0.006324213907675097</v>
       </c>
       <c r="AO340" t="n">
-        <v>0.4647750649852558</v>
+        <v>0.4647750649852552</v>
       </c>
       <c r="AP340" t="n">
-        <v>-2.358420913553941</v>
+        <v>-2.358420913553955</v>
       </c>
       <c r="AQ340" t="n">
         <v>2.906976744186047</v>
@@ -55716,10 +55716,10 @@
         <v>-0.4782968221045021</v>
       </c>
       <c r="AI341" t="n">
-        <v>7.122818285283532</v>
+        <v>7.122818285283529</v>
       </c>
       <c r="AJ341" t="n">
-        <v>-0.1394184172720578</v>
+        <v>-0.1394184172720543</v>
       </c>
       <c r="AK341" t="n">
         <v>7.123271418608565</v>
@@ -55728,16 +55728,16 @@
         <v>-0.13987155059709</v>
       </c>
       <c r="AM341" t="n">
-        <v>0.1386638579210689</v>
+        <v>0.1386638579210687</v>
       </c>
       <c r="AN341" t="n">
-        <v>0.006222091828703747</v>
+        <v>0.006222091828703702</v>
       </c>
       <c r="AO341" t="n">
-        <v>0.4565264017486775</v>
+        <v>0.4565264017486783</v>
       </c>
       <c r="AP341" t="n">
-        <v>-2.224844990802061</v>
+        <v>-2.224844990801964</v>
       </c>
       <c r="AQ341" t="n">
         <v>4.022988505747126</v>
@@ -55893,16 +55893,16 @@
         <v>-0.1179176736116263</v>
       </c>
       <c r="AM342" t="n">
-        <v>0.1423176752089981</v>
+        <v>0.1423176752089984</v>
       </c>
       <c r="AN342" t="n">
-        <v>0.006093783709292289</v>
+        <v>0.006093783709292283</v>
       </c>
       <c r="AO342" t="n">
-        <v>0.4497199830569214</v>
+        <v>0.4497199830569224</v>
       </c>
       <c r="AP342" t="n">
-        <v>-1.837002738664109</v>
+        <v>-1.837002738664126</v>
       </c>
       <c r="AQ342" t="n">
         <v>9.090909090909092</v>
@@ -56046,10 +56046,10 @@
         <v>-0.4197884336852109</v>
       </c>
       <c r="AI343" t="n">
-        <v>7.13316040486909</v>
+        <v>7.133160404869088</v>
       </c>
       <c r="AJ343" t="n">
-        <v>-0.1496604010543923</v>
+        <v>-0.1496604010543905</v>
       </c>
       <c r="AK343" t="n">
         <v>7.117219286120759</v>
@@ -56061,13 +56061,13 @@
         <v>0.1458607275562278</v>
       </c>
       <c r="AN343" t="n">
-        <v>0.005984113522022499</v>
+        <v>0.005984113522022494</v>
       </c>
       <c r="AO343" t="n">
-        <v>0.4438783751010228</v>
+        <v>0.4438783751010233</v>
       </c>
       <c r="AP343" t="n">
-        <v>-2.408870938511925</v>
+        <v>-2.408870938511893</v>
       </c>
       <c r="AQ343" t="n">
         <v>7.865168539325842</v>
@@ -56211,10 +56211,10 @@
         <v>-0.422871708132643</v>
       </c>
       <c r="AI344" t="n">
-        <v>7.129653220712091</v>
+        <v>7.12965322071209</v>
       </c>
       <c r="AJ344" t="n">
-        <v>-0.152453189431573</v>
+        <v>-0.1524531894315722</v>
       </c>
       <c r="AK344" t="n">
         <v>7.126254605494273</v>
@@ -56223,16 +56223,16 @@
         <v>-0.1490545742137552</v>
       </c>
       <c r="AM344" t="n">
-        <v>0.1503893187551739</v>
+        <v>0.1503893187551748</v>
       </c>
       <c r="AN344" t="n">
-        <v>0.005963146506628762</v>
+        <v>0.005963146506628741</v>
       </c>
       <c r="AO344" t="n">
-        <v>0.441201873624737</v>
+        <v>0.4412018736247373</v>
       </c>
       <c r="AP344" t="n">
-        <v>-2.401162905304164</v>
+        <v>-2.401162905304161</v>
       </c>
       <c r="AQ344" t="n">
         <v>7.777777777777777</v>
@@ -56376,10 +56376,10 @@
         <v>-0.4378105601271827</v>
       </c>
       <c r="AI345" t="n">
-        <v>7.128380415829729</v>
+        <v>7.128380415829728</v>
       </c>
       <c r="AJ345" t="n">
-        <v>-0.1552802304354417</v>
+        <v>-0.1552802304354408</v>
       </c>
       <c r="AK345" t="n">
         <v>7.124321202568002</v>
@@ -56388,16 +56388,16 @@
         <v>-0.1512210171737154</v>
       </c>
       <c r="AM345" t="n">
-        <v>0.1546287435667593</v>
+        <v>0.1546287435667592</v>
       </c>
       <c r="AN345" t="n">
-        <v>0.005975981199024824</v>
+        <v>0.005975981199024843</v>
       </c>
       <c r="AO345" t="n">
-        <v>0.43858274446866</v>
+        <v>0.4385827444686599</v>
       </c>
       <c r="AP345" t="n">
-        <v>-2.393976252441823</v>
+        <v>-2.393976252441821</v>
       </c>
       <c r="AQ345" t="n">
         <v>7.692307692307692</v>
@@ -56541,10 +56541,10 @@
         <v>-0.3847879981822233</v>
       </c>
       <c r="AI346" t="n">
-        <v>7.124429161493114</v>
+        <v>7.124429161493117</v>
       </c>
       <c r="AJ346" t="n">
-        <v>-0.1469291996400868</v>
+        <v>-0.1469291996400894</v>
       </c>
       <c r="AK346" t="n">
         <v>7.121152072356459</v>
@@ -56553,16 +56553,16 @@
         <v>-0.1436521105034316</v>
       </c>
       <c r="AM346" t="n">
-        <v>0.1587808126513008</v>
+        <v>0.1587808126513012</v>
       </c>
       <c r="AN346" t="n">
-        <v>0.005899221619931436</v>
+        <v>0.00589922161993145</v>
       </c>
       <c r="AO346" t="n">
-        <v>0.4336499747757655</v>
+        <v>0.4336499747757657</v>
       </c>
       <c r="AP346" t="n">
-        <v>-2.079541096596154</v>
+        <v>-2.079541096596248</v>
       </c>
       <c r="AQ346" t="n">
         <v>16.30434782608696</v>
@@ -56718,16 +56718,16 @@
         <v>-0.1434406571511193</v>
       </c>
       <c r="AM347" t="n">
-        <v>0.1636493008978486</v>
+        <v>0.1636493008978488</v>
       </c>
       <c r="AN347" t="n">
-        <v>0.005897856672615022</v>
+        <v>0.005897856672615054</v>
       </c>
       <c r="AO347" t="n">
-        <v>0.4343048343988722</v>
+        <v>0.434304834398872</v>
       </c>
       <c r="AP347" t="n">
-        <v>-2.397140212793674</v>
+        <v>-2.39714021279369</v>
       </c>
       <c r="AQ347" t="n">
         <v>13.97849462365591</v>
@@ -56871,10 +56871,10 @@
         <v>-0.3934084445240993</v>
       </c>
       <c r="AI348" t="n">
-        <v>7.141397967314151</v>
+        <v>7.141397967314147</v>
       </c>
       <c r="AJ348" t="n">
-        <v>-0.1753978872055084</v>
+        <v>-0.1753978872055049</v>
       </c>
       <c r="AK348" t="n">
         <v>7.12802266215534</v>
@@ -56883,16 +56883,16 @@
         <v>-0.1620225820466974</v>
       </c>
       <c r="AM348" t="n">
-        <v>0.1676675897666616</v>
+        <v>0.1676675897666615</v>
       </c>
       <c r="AN348" t="n">
-        <v>0.005952601612807589</v>
+        <v>0.005952601612807557</v>
       </c>
       <c r="AO348" t="n">
-        <v>0.4322693842687804</v>
+        <v>0.4322693842687806</v>
       </c>
       <c r="AP348" t="n">
-        <v>-2.687935210063377</v>
+        <v>-2.687935210063305</v>
       </c>
       <c r="AQ348" t="n">
         <v>12.76595744680851</v>
@@ -57036,10 +57036,10 @@
         <v>-0.3051124977102484</v>
       </c>
       <c r="AI349" t="n">
-        <v>7.140412492855501</v>
+        <v>7.140412492855504</v>
       </c>
       <c r="AJ349" t="n">
-        <v>-0.1723124219021317</v>
+        <v>-0.1723124219021352</v>
       </c>
       <c r="AK349" t="n">
         <v>7.137738577466652</v>
@@ -57048,16 +57048,16 @@
         <v>-0.1696385065132828</v>
       </c>
       <c r="AM349" t="n">
-        <v>0.1710383543493662</v>
+        <v>0.1710383543493657</v>
       </c>
       <c r="AN349" t="n">
-        <v>0.00606844425683546</v>
+        <v>0.006068444256835448</v>
       </c>
       <c r="AO349" t="n">
-        <v>0.4285062718639572</v>
+        <v>0.4285062718639565</v>
       </c>
       <c r="AP349" t="n">
-        <v>-2.500349987380015</v>
+        <v>-2.500349987380126</v>
       </c>
       <c r="AQ349" t="n">
         <v>20</v>
@@ -57201,10 +57201,10 @@
         <v>-0.3196052296098513</v>
       </c>
       <c r="AI350" t="n">
-        <v>7.138020503721584</v>
+        <v>7.138020503721587</v>
       </c>
       <c r="AJ350" t="n">
-        <v>-0.1699204327682153</v>
+        <v>-0.169920432768218</v>
       </c>
       <c r="AK350" t="n">
         <v>7.13663078035759</v>
@@ -57213,16 +57213,16 @@
         <v>-0.1685307094042212</v>
       </c>
       <c r="AM350" t="n">
-        <v>0.1761956824342154</v>
+        <v>0.176195682434215</v>
       </c>
       <c r="AN350" t="n">
-        <v>0.006402952059750703</v>
+        <v>0.006402952059750722</v>
       </c>
       <c r="AO350" t="n">
-        <v>0.4374093872433956</v>
+        <v>0.4374093872433962</v>
       </c>
       <c r="AP350" t="n">
-        <v>-2.351093557116537</v>
+        <v>-2.351093557116616</v>
       </c>
       <c r="AQ350" t="n">
         <v>19.79166666666666</v>
@@ -57366,28 +57366,28 @@
         <v>-0.3390250647280579</v>
       </c>
       <c r="AI351" t="n">
-        <v>7.136830620687383</v>
+        <v>7.136830620687384</v>
       </c>
       <c r="AJ351" t="n">
-        <v>-0.1769307183436331</v>
+        <v>-0.1769307183436339</v>
       </c>
       <c r="AK351" t="n">
-        <v>7.140049017840021</v>
+        <v>7.14004901784002</v>
       </c>
       <c r="AL351" t="n">
-        <v>-0.1801491154962713</v>
+        <v>-0.1801491154962704</v>
       </c>
       <c r="AM351" t="n">
-        <v>0.1796308914905974</v>
+        <v>0.1796308914905975</v>
       </c>
       <c r="AN351" t="n">
-        <v>0.006948414844703805</v>
+        <v>0.006948414844703821</v>
       </c>
       <c r="AO351" t="n">
-        <v>0.4458727441769483</v>
+        <v>0.4458727441769479</v>
       </c>
       <c r="AP351" t="n">
-        <v>-2.441641144720979</v>
+        <v>-2.441641144721009</v>
       </c>
       <c r="AQ351" t="n">
         <v>18.04123711340206</v>
@@ -57527,10 +57527,10 @@
         <v/>
       </c>
       <c r="AI352" t="n">
-        <v>7.13363857926656</v>
+        <v>7.133638579266565</v>
       </c>
       <c r="AJ352" t="n">
-        <v>-0.1699387616090897</v>
+        <v>-0.1699387616090942</v>
       </c>
       <c r="AK352" t="n">
         <v>7.13798584867198</v>
@@ -57539,16 +57539,16 @@
         <v>-0.1742860310145096</v>
       </c>
       <c r="AM352" t="n">
-        <v>0.1829391475229935</v>
+        <v>0.1829391475229931</v>
       </c>
       <c r="AN352" t="n">
-        <v>0.00760204732154433</v>
+        <v>0.007602047321544403</v>
       </c>
       <c r="AO352" t="n">
-        <v>0.4545618931940826</v>
+        <v>0.4545618931940824</v>
       </c>
       <c r="AP352" t="n">
-        <v>-2.194466762595095</v>
+        <v>-2.194466762595206</v>
       </c>
       <c r="AQ352" t="n">
         <v>27.04081632653061</v>
@@ -57692,10 +57692,10 @@
         <v>-0.3091855344694094</v>
       </c>
       <c r="AI353" t="n">
-        <v>7.126409468908567</v>
+        <v>7.12640946890857</v>
       </c>
       <c r="AJ353" t="n">
-        <v>-0.1538094856932348</v>
+        <v>-0.1538094856932375</v>
       </c>
       <c r="AK353" t="n">
         <v>7.138565167526504</v>
@@ -57704,16 +57704,16 @@
         <v>-0.1659651843111716</v>
       </c>
       <c r="AM353" t="n">
-        <v>0.1834764543657157</v>
+        <v>0.1834764543657148</v>
       </c>
       <c r="AN353" t="n">
-        <v>0.007712839302340297</v>
+        <v>0.007712839302340374</v>
       </c>
       <c r="AO353" t="n">
-        <v>0.4511257152112024</v>
+        <v>0.4511257152112026</v>
       </c>
       <c r="AP353" t="n">
-        <v>-1.753575478488427</v>
+        <v>-1.753575478488488</v>
       </c>
       <c r="AQ353" t="n">
         <v>22.9179550608122</v>
@@ -57857,10 +57857,10 @@
         <v>-0.4171933775451331</v>
       </c>
       <c r="AI354" t="n">
-        <v>7.110999512759042</v>
+        <v>7.110999512759045</v>
       </c>
       <c r="AJ354" t="n">
-        <v>-0.1383995295437099</v>
+        <v>-0.1383995295437126</v>
       </c>
       <c r="AK354" t="n">
         <v>7.137040595974374</v>
@@ -57869,16 +57869,16 @@
         <v>-0.1644406127590416</v>
       </c>
       <c r="AM354" t="n">
-        <v>0.1869739626316108</v>
+        <v>0.1869739626316104</v>
       </c>
       <c r="AN354" t="n">
-        <v>0.008354609519984808</v>
+        <v>0.00835460951998479</v>
       </c>
       <c r="AO354" t="n">
-        <v>0.4618871834350127</v>
+        <v>0.4618871834350119</v>
       </c>
       <c r="AP354" t="n">
-        <v>-1.352715240325543</v>
+        <v>-1.352715240325604</v>
       </c>
       <c r="AQ354" t="n">
         <v>17.08585858585858</v>
@@ -58034,16 +58034,16 @@
         <v>-0.1699559989113286</v>
       </c>
       <c r="AM355" t="n">
-        <v>0.1901371272406383</v>
+        <v>0.1901371272406391</v>
       </c>
       <c r="AN355" t="n">
-        <v>0.008787529863310259</v>
+        <v>0.008787529863310189</v>
       </c>
       <c r="AO355" t="n">
-        <v>0.4631528842621208</v>
+        <v>0.4631528842621211</v>
       </c>
       <c r="AP355" t="n">
-        <v>-1.390419145070144</v>
+        <v>-1.39041914507014</v>
       </c>
       <c r="AQ355" t="n">
         <v>10.43564356435644</v>
@@ -58187,10 +58187,10 @@
         <v>-0.4524735425775077</v>
       </c>
       <c r="AI356" t="n">
-        <v>7.102293381264122</v>
+        <v>7.10229338126412</v>
       </c>
       <c r="AJ356" t="n">
-        <v>-0.1477931828998642</v>
+        <v>-0.1477931828998624</v>
       </c>
       <c r="AK356" t="n">
         <v>7.113436809075056</v>
@@ -58199,16 +58199,16 @@
         <v>-0.1589366107107981</v>
       </c>
       <c r="AM356" t="n">
-        <v>0.193945683545753</v>
+        <v>0.1939456835457532</v>
       </c>
       <c r="AN356" t="n">
-        <v>0.009306466714917755</v>
+        <v>0.009306466714917722</v>
       </c>
       <c r="AO356" t="n">
-        <v>0.4650211967660295</v>
+        <v>0.4650211967660294</v>
       </c>
       <c r="AP356" t="n">
-        <v>-1.536498147639978</v>
+        <v>-1.536498147639932</v>
       </c>
       <c r="AQ356" t="n">
         <v>11.33275092215104</v>
@@ -58364,16 +58364,16 @@
         <v>-0.1683303683513104</v>
       </c>
       <c r="AM357" t="n">
-        <v>0.1968971496416338</v>
+        <v>0.1968971496416331</v>
       </c>
       <c r="AN357" t="n">
-        <v>0.009915270508004639</v>
+        <v>0.009915270508004642</v>
       </c>
       <c r="AO357" t="n">
-        <v>0.4658112293095935</v>
+        <v>0.4658112293095933</v>
       </c>
       <c r="AP357" t="n">
-        <v>-1.307847521398092</v>
+        <v>-1.307847521398089</v>
       </c>
       <c r="AQ357" t="n">
         <v>11.67904054825814</v>
@@ -58529,16 +58529,16 @@
         <v>-0.1677543784610256</v>
       </c>
       <c r="AM358" t="n">
-        <v>0.200157477381068</v>
+        <v>0.2001574773810679</v>
       </c>
       <c r="AN358" t="n">
-        <v>0.01045224758824685</v>
+        <v>0.01045224758824684</v>
       </c>
       <c r="AO358" t="n">
-        <v>0.4652001227613058</v>
+        <v>0.4652001227613064</v>
       </c>
       <c r="AP358" t="n">
-        <v>-1.57610127492425</v>
+        <v>-1.576101274924247</v>
       </c>
       <c r="AQ358" t="n">
         <v>5.293129200896192</v>
@@ -58682,10 +58682,10 @@
         <v>-0.4747535169148094</v>
       </c>
       <c r="AI359" t="n">
-        <v>7.112155432918444</v>
+        <v>7.112155432918446</v>
       </c>
       <c r="AJ359" t="n">
-        <v>-0.1611552192953969</v>
+        <v>-0.1611552192953987</v>
       </c>
       <c r="AK359" t="n">
         <v>7.115439870473561</v>
@@ -58694,16 +58694,16 @@
         <v>-0.1644396568505142</v>
       </c>
       <c r="AM359" t="n">
-        <v>0.2059164257597547</v>
+        <v>0.2059164257597553</v>
       </c>
       <c r="AN359" t="n">
-        <v>0.0109580623600705</v>
+        <v>0.01095806236007055</v>
       </c>
       <c r="AO359" t="n">
-        <v>0.4647071558511972</v>
+        <v>0.4647071558511969</v>
       </c>
       <c r="AP359" t="n">
-        <v>-1.776827470000016</v>
+        <v>-1.776827470000052</v>
       </c>
       <c r="AQ359" t="n">
         <v>6.703296703296703</v>
@@ -58859,16 +58859,16 @@
         <v>-0.179475696197902</v>
       </c>
       <c r="AM360" t="n">
-        <v>0.2103846028094625</v>
+        <v>0.2103846028094628</v>
       </c>
       <c r="AN360" t="n">
-        <v>0.01138655624224671</v>
+        <v>0.01138655624224677</v>
       </c>
       <c r="AO360" t="n">
         <v>0.4605334060319247</v>
       </c>
       <c r="AP360" t="n">
-        <v>-1.805481046668107</v>
+        <v>-1.805481046668102</v>
       </c>
       <c r="AQ360" t="n">
         <v>11.40161725067385</v>
@@ -59012,10 +59012,10 @@
         <v>-0.4110308421391506</v>
       </c>
       <c r="AI361" t="n">
-        <v>7.110775793344654</v>
+        <v>7.110775793344653</v>
       </c>
       <c r="AJ361" t="n">
-        <v>-0.1730759985753672</v>
+        <v>-0.1730759985753663</v>
       </c>
       <c r="AK361" t="n">
         <v>7.127056499711662</v>
@@ -59024,16 +59024,16 @@
         <v>-0.1893567049423748</v>
       </c>
       <c r="AM361" t="n">
-        <v>0.2137349114935566</v>
+        <v>0.2137349114935569</v>
       </c>
       <c r="AN361" t="n">
-        <v>0.0118427752189066</v>
+        <v>0.01184277521890661</v>
       </c>
       <c r="AO361" t="n">
-        <v>0.4573024605378192</v>
+        <v>0.4573024605378193</v>
       </c>
       <c r="AP361" t="n">
-        <v>-1.973713661270174</v>
+        <v>-1.973713661270149</v>
       </c>
       <c r="AQ361" t="n">
         <v>12.72262387585964</v>
@@ -59189,16 +59189,16 @@
         <v>-0.1883703674075337</v>
       </c>
       <c r="AM362" t="n">
-        <v>0.2192999169256231</v>
+        <v>0.2192999169256238</v>
       </c>
       <c r="AN362" t="n">
-        <v>0.01242692746354283</v>
+        <v>0.01242692746354282</v>
       </c>
       <c r="AO362" t="n">
-        <v>0.4593518446085587</v>
+        <v>0.4593518446085588</v>
       </c>
       <c r="AP362" t="n">
-        <v>-1.523267153843557</v>
+        <v>-1.523267153843554</v>
       </c>
       <c r="AQ362" t="n">
         <v>14.43838698511596</v>
@@ -59342,28 +59342,28 @@
         <v>-0.4497684872706866</v>
       </c>
       <c r="AI363" t="n">
-        <v>7.095070446253632</v>
+        <v>7.095070446253633</v>
       </c>
       <c r="AJ363" t="n">
-        <v>-0.1572705156811223</v>
+        <v>-0.1572705156811232</v>
       </c>
       <c r="AK363" t="n">
-        <v>7.099084322920754</v>
+        <v>7.099084322920755</v>
       </c>
       <c r="AL363" t="n">
-        <v>-0.1612843923482439</v>
+        <v>-0.1612843923482448</v>
       </c>
       <c r="AM363" t="n">
-        <v>0.2273791016644665</v>
+        <v>0.2273791016644669</v>
       </c>
       <c r="AN363" t="n">
-        <v>0.01301934706840001</v>
+        <v>0.01301934706839999</v>
       </c>
       <c r="AO363" t="n">
-        <v>0.4655241261491888</v>
+        <v>0.4655241261491886</v>
       </c>
       <c r="AP363" t="n">
-        <v>-1.557058675067582</v>
+        <v>-1.557058675067598</v>
       </c>
       <c r="AQ363" t="n">
         <v>12.45752633367312</v>
@@ -59507,10 +59507,10 @@
         <v>-0.4474892444253866</v>
       </c>
       <c r="AI364" t="n">
-        <v>7.077412848446856</v>
+        <v>7.077412848446851</v>
       </c>
       <c r="AJ364" t="n">
-        <v>-0.138612990353594</v>
+        <v>-0.1386129903535895</v>
       </c>
       <c r="AK364" t="n">
         <v>7.107752072150756</v>
@@ -59519,16 +59519,16 @@
         <v>-0.1689522140574944</v>
       </c>
       <c r="AM364" t="n">
-        <v>0.2346680713248287</v>
+        <v>0.2346680713248289</v>
       </c>
       <c r="AN364" t="n">
-        <v>0.01366280940279221</v>
+        <v>0.01366280940279216</v>
       </c>
       <c r="AO364" t="n">
-        <v>0.4682122340216205</v>
+        <v>0.4682122340216202</v>
       </c>
       <c r="AP364" t="n">
-        <v>-1.117810522367088</v>
+        <v>-1.117810522366985</v>
       </c>
       <c r="AQ364" t="n">
         <v>20.07506255212677</v>
@@ -59672,10 +59672,10 @@
         <v>-0.4209410240232048</v>
       </c>
       <c r="AI365" t="n">
-        <v>7.067855559671529</v>
+        <v>7.067855559671527</v>
       </c>
       <c r="AJ365" t="n">
-        <v>-0.1458556283360801</v>
+        <v>-0.1458556283360775</v>
       </c>
       <c r="AK365" t="n">
         <v>7.100856094477853</v>
@@ -59684,16 +59684,16 @@
         <v>-0.1788561631424042</v>
       </c>
       <c r="AM365" t="n">
-        <v>0.2404731763378833</v>
+        <v>0.2404731763378842</v>
       </c>
       <c r="AN365" t="n">
-        <v>0.01427110593278805</v>
+        <v>0.01427110593278799</v>
       </c>
       <c r="AO365" t="n">
         <v>0.4705695567526583</v>
       </c>
       <c r="AP365" t="n">
-        <v>-1.268402735242881</v>
+        <v>-1.26840273524282</v>
       </c>
       <c r="AQ365" t="n">
         <v>19.46764946764947</v>
@@ -59837,10 +59837,10 @@
         <v>-0.4085339259984559</v>
       </c>
       <c r="AI366" t="n">
-        <v>7.081794385763168</v>
+        <v>7.081794385763164</v>
       </c>
       <c r="AJ366" t="n">
-        <v>-0.1711942003688813</v>
+        <v>-0.1711942003688769</v>
       </c>
       <c r="AK366" t="n">
         <v>7.090764621929079</v>
@@ -59849,16 +59849,16 @@
         <v>-0.1801644365347919</v>
       </c>
       <c r="AM366" t="n">
-        <v>0.2453259423721924</v>
+        <v>0.2453259423721931</v>
       </c>
       <c r="AN366" t="n">
-        <v>0.01502424352484376</v>
+        <v>0.01502424352484369</v>
       </c>
       <c r="AO366" t="n">
-        <v>0.4756424387980304</v>
+        <v>0.4756424387980298</v>
       </c>
       <c r="AP366" t="n">
-        <v>-1.810992524290963</v>
+        <v>-1.810992524290867</v>
       </c>
       <c r="AQ366" t="n">
         <v>15.74565637065637</v>
@@ -60002,10 +60002,10 @@
         <v>-0.406784659944317</v>
       </c>
       <c r="AI367" t="n">
-        <v>7.068234493406101</v>
+        <v>7.068234493406102</v>
       </c>
       <c r="AJ367" t="n">
-        <v>-0.1557345887735329</v>
+        <v>-0.1557345887735337</v>
       </c>
       <c r="AK367" t="n">
         <v>7.110983013755962</v>
@@ -60014,16 +60014,16 @@
         <v>-0.1984831091233934</v>
       </c>
       <c r="AM367" t="n">
-        <v>0.2481172514763511</v>
+        <v>0.2481172514763508</v>
       </c>
       <c r="AN367" t="n">
         <v>0.01591732918741026</v>
       </c>
       <c r="AO367" t="n">
-        <v>0.4781214750573156</v>
+        <v>0.4781214750573159</v>
       </c>
       <c r="AP367" t="n">
-        <v>-1.441711805760835</v>
+        <v>-1.441711805760857</v>
       </c>
       <c r="AQ367" t="n">
         <v>19.59544879898862</v>
@@ -60167,28 +60167,28 @@
         <v>-0.4293296460730334</v>
       </c>
       <c r="AI368" t="n">
-        <v>7.04701169343388</v>
+        <v>7.047011693433886</v>
       </c>
       <c r="AJ368" t="n">
-        <v>-0.1469114622632253</v>
+        <v>-0.1469114622632315</v>
       </c>
       <c r="AK368" t="n">
         <v>7.093736458019618</v>
       </c>
       <c r="AL368" t="n">
-        <v>-0.1936362268489633</v>
+        <v>-0.1936362268489642</v>
       </c>
       <c r="AM368" t="n">
-        <v>0.2517176519946887</v>
+        <v>0.2517176519946896</v>
       </c>
       <c r="AN368" t="n">
-        <v>0.01672959897123727</v>
+        <v>0.01672959897123732</v>
       </c>
       <c r="AO368" t="n">
-        <v>0.4820447952807055</v>
+        <v>0.482044795280705</v>
       </c>
       <c r="AP368" t="n">
-        <v>-1.229621277012902</v>
+        <v>-1.229621277013041</v>
       </c>
       <c r="AQ368" t="n">
         <v>18.94503959012576</v>
@@ -60332,28 +60332,28 @@
         <v>-0.4284740722863445</v>
       </c>
       <c r="AI369" t="n">
-        <v>7.043635211714486</v>
+        <v>7.043635211714482</v>
       </c>
       <c r="AJ369" t="n">
-        <v>-0.1356352193438806</v>
+        <v>-0.135635219343877</v>
       </c>
       <c r="AK369" t="n">
-        <v>7.069112439760901</v>
+        <v>7.069112439760902</v>
       </c>
       <c r="AL369" t="n">
-        <v>-0.1611124473902956</v>
+        <v>-0.1611124473902965</v>
       </c>
       <c r="AM369" t="n">
-        <v>0.2568291528619769</v>
+        <v>0.2568291528619773</v>
       </c>
       <c r="AN369" t="n">
-        <v>0.0175878422274923</v>
+        <v>0.01758784222749221</v>
       </c>
       <c r="AO369" t="n">
-        <v>0.488825658962754</v>
+        <v>0.4888256589627545</v>
       </c>
       <c r="AP369" t="n">
-        <v>-0.9685323988062863</v>
+        <v>-0.968532398806207</v>
       </c>
       <c r="AQ369" t="n">
         <v>24.43554538520213</v>
@@ -60497,10 +60497,10 @@
         <v>-0.4460814008634681</v>
       </c>
       <c r="AI370" t="n">
-        <v>7.04532069676962</v>
+        <v>7.045320696769622</v>
       </c>
       <c r="AJ370" t="n">
-        <v>-0.1373207043990146</v>
+        <v>-0.1373207043990163</v>
       </c>
       <c r="AK370" t="n">
         <v>7.067486653848666</v>
@@ -60509,16 +60509,16 @@
         <v>-0.159486661478061</v>
       </c>
       <c r="AM370" t="n">
-        <v>0.2611441025487396</v>
+        <v>0.2611441025487395</v>
       </c>
       <c r="AN370" t="n">
-        <v>0.01863884916361523</v>
+        <v>0.01863884916361525</v>
       </c>
       <c r="AO370" t="n">
-        <v>0.4958891106408189</v>
+        <v>0.4958891106408185</v>
       </c>
       <c r="AP370" t="n">
-        <v>-0.9976392040422146</v>
+        <v>-0.9976392040422545</v>
       </c>
       <c r="AQ370" t="n">
         <v>22.05397301349325</v>
@@ -60662,10 +60662,10 @@
         <v>-0.4397071044547962</v>
       </c>
       <c r="AI371" t="n">
-        <v>7.052957186540212</v>
+        <v>7.052957186540217</v>
       </c>
       <c r="AJ371" t="n">
-        <v>-0.1449571941696064</v>
+        <v>-0.1449571941696117</v>
       </c>
       <c r="AK371" t="n">
         <v>7.066060765041626</v>
@@ -60674,16 +60674,16 @@
         <v>-0.1580607726710204</v>
       </c>
       <c r="AM371" t="n">
-        <v>0.2646928033319788</v>
+        <v>0.2646928033319798</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.0196144718499898</v>
+        <v>0.01961447184998982</v>
       </c>
       <c r="AO371" t="n">
-        <v>0.4990325267638065</v>
+        <v>0.4990325267638059</v>
       </c>
       <c r="AP371" t="n">
-        <v>-1.157136980079324</v>
+        <v>-1.157136980079441</v>
       </c>
       <c r="AQ371" t="n">
         <v>19.31181844974948</v>
@@ -60827,28 +60827,28 @@
         <v>-0.4380026509862534</v>
       </c>
       <c r="AI372" t="n">
-        <v>7.055218091951103</v>
+        <v>7.055218091951101</v>
       </c>
       <c r="AJ372" t="n">
-        <v>-0.1472180995804973</v>
+        <v>-0.1472180995804955</v>
       </c>
       <c r="AK372" t="n">
-        <v>7.06464674575351</v>
+        <v>7.064646745753511</v>
       </c>
       <c r="AL372" t="n">
-        <v>-0.1566467533829048</v>
+        <v>-0.1566467533829057</v>
       </c>
       <c r="AM372" t="n">
-        <v>0.2692457951306194</v>
+        <v>0.2692457951306195</v>
       </c>
       <c r="AN372" t="n">
-        <v>0.02045122459205891</v>
+        <v>0.02045122459205889</v>
       </c>
       <c r="AO372" t="n">
-        <v>0.5009265659871951</v>
+        <v>0.5009265659871953</v>
       </c>
       <c r="AP372" t="n">
-        <v>-1.19524976703836</v>
+        <v>-1.195249767038319</v>
       </c>
       <c r="AQ372" t="n">
         <v>18.30363610024627</v>
@@ -60992,10 +60992,10 @@
         <v>-0.4222342557606318</v>
       </c>
       <c r="AI373" t="n">
-        <v>7.050463258619345</v>
+        <v>7.050463258619342</v>
       </c>
       <c r="AJ373" t="n">
-        <v>-0.1423631304455171</v>
+        <v>-0.1423631304455135</v>
       </c>
       <c r="AK373" t="n">
         <v>7.063274589921972</v>
@@ -61004,16 +61004,16 @@
         <v>-0.1551744617481443</v>
       </c>
       <c r="AM373" t="n">
-        <v>0.2738618637550991</v>
+        <v>0.2738618637550985</v>
       </c>
       <c r="AN373" t="n">
-        <v>0.02103732430364855</v>
+        <v>0.02103732430364852</v>
       </c>
       <c r="AO373" t="n">
-        <v>0.5007948901071723</v>
+        <v>0.5007948901071727</v>
       </c>
       <c r="AP373" t="n">
-        <v>-1.076832434365783</v>
+        <v>-1.076832434365704</v>
       </c>
       <c r="AQ373" t="n">
         <v>22.79233727389261</v>
@@ -61330,16 +61330,16 @@
         <v/>
       </c>
       <c r="AM375" t="n">
-        <v>0.2803441195876753</v>
+        <v>0.280344119587675</v>
       </c>
       <c r="AN375" t="n">
-        <v>0.02230845224183688</v>
+        <v>0.02230845224183686</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.5036776407221312</v>
+        <v>0.5036776407221306</v>
       </c>
       <c r="AP375" t="n">
-        <v>-1.233165332293827</v>
+        <v>-1.233165332293828</v>
       </c>
       <c r="AQ375" t="n">
         <v>25</v>
@@ -61483,10 +61483,10 @@
         <v>-0.3874832733903126</v>
       </c>
       <c r="AI376" t="n">
-        <v>7.056824809597052</v>
+        <v>7.056824809597053</v>
       </c>
       <c r="AJ376" t="n">
-        <v>-0.1737247767906558</v>
+        <v>-0.1737247767906567</v>
       </c>
       <c r="AK376" t="n">
         <v>7.071238163852278</v>
@@ -61495,16 +61495,16 @@
         <v>-0.1881381310458812</v>
       </c>
       <c r="AM376" t="n">
-        <v>0.2841407798055452</v>
+        <v>0.2841407798055449</v>
       </c>
       <c r="AN376" t="n">
-        <v>0.02276542233315985</v>
+        <v>0.02276542233315987</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.5036956996297983</v>
+        <v>0.5036956996297977</v>
       </c>
       <c r="AP376" t="n">
-        <v>-1.733307247689745</v>
+        <v>-1.733307247689765</v>
       </c>
       <c r="AQ376" t="n">
         <v>21.90082644628099</v>
@@ -61648,10 +61648,10 @@
         <v>-0.4296615554704886</v>
       </c>
       <c r="AI377" t="n">
-        <v>7.047265922594908</v>
+        <v>7.04726592259491</v>
       </c>
       <c r="AJ377" t="n">
-        <v>-0.178065692950133</v>
+        <v>-0.1780656929501347</v>
       </c>
       <c r="AK377" t="n">
         <v>7.075283303194255</v>
@@ -61660,16 +61660,16 @@
         <v>-0.2060830735494799</v>
       </c>
       <c r="AM377" t="n">
-        <v>0.2869603504542598</v>
+        <v>0.2869603504542605</v>
       </c>
       <c r="AN377" t="n">
-        <v>0.02324367830537833</v>
+        <v>0.02324367830537832</v>
       </c>
       <c r="AO377" t="n">
-        <v>0.5029697249741724</v>
+        <v>0.5029697249741727</v>
       </c>
       <c r="AP377" t="n">
-        <v>-1.797075952444542</v>
+        <v>-1.797075952444579</v>
       </c>
       <c r="AQ377" t="n">
         <v>10.65573770491803</v>
@@ -61813,10 +61813,10 @@
         <v>-0.4788983177676771</v>
       </c>
       <c r="AI378" t="n">
-        <v>7.030237372659579</v>
+        <v>7.030237372659574</v>
       </c>
       <c r="AJ378" t="n">
-        <v>-0.1893374283541593</v>
+        <v>-0.189337428354154</v>
       </c>
       <c r="AK378" t="n">
         <v>7.061088020066238</v>
@@ -61825,16 +61825,16 @@
         <v>-0.2201880757608183</v>
       </c>
       <c r="AM378" t="n">
-        <v>0.2909556153842324</v>
+        <v>0.2909556153842325</v>
       </c>
       <c r="AN378" t="n">
-        <v>0.02343150180192457</v>
+        <v>0.02343150180192449</v>
       </c>
       <c r="AO378" t="n">
-        <v>0.5011874977636526</v>
+        <v>0.501187497763653</v>
       </c>
       <c r="AP378" t="n">
-        <v>-2.001502618066459</v>
+        <v>-2.001502618066346</v>
       </c>
       <c r="AQ378" t="n">
         <v>2.439024390243902</v>
@@ -61978,10 +61978,10 @@
         <v>-0.4154300056145983</v>
       </c>
       <c r="AI379" t="n">
-        <v>7.074556523891907</v>
+        <v>7.074556523891909</v>
       </c>
       <c r="AJ379" t="n">
-        <v>-0.2166563812222293</v>
+        <v>-0.2166563812222311</v>
       </c>
       <c r="AK379" t="n">
         <v>7.045371831199247</v>
@@ -61990,16 +61990,16 @@
         <v>-0.1874716885295697</v>
       </c>
       <c r="AM379" t="n">
-        <v>0.2963660759601009</v>
+        <v>0.2963660759601011</v>
       </c>
       <c r="AN379" t="n">
-        <v>0.02388105320115906</v>
+        <v>0.02388105320115907</v>
       </c>
       <c r="AO379" t="n">
-        <v>0.5011837436137511</v>
+        <v>0.5011837436137521</v>
       </c>
       <c r="AP379" t="n">
-        <v>-2.513652032800223</v>
+        <v>-2.513652032800262</v>
       </c>
       <c r="AQ379" t="n">
         <v>14.91935483870968</v>
@@ -62143,10 +62143,10 @@
         <v>-0.3983190184102794</v>
       </c>
       <c r="AI380" t="n">
-        <v>7.103552248295403</v>
+        <v>7.103552248295395</v>
       </c>
       <c r="AJ380" t="n">
-        <v>-0.2215522788129807</v>
+        <v>-0.2215522788129736</v>
       </c>
       <c r="AK380" t="n">
         <v>7.078406423284397</v>
@@ -62155,16 +62155,16 @@
         <v>-0.1964064538019752</v>
       </c>
       <c r="AM380" t="n">
-        <v>0.2998407912997099</v>
+        <v>0.29984079129971</v>
       </c>
       <c r="AN380" t="n">
-        <v>0.02427773372157407</v>
+        <v>0.02427773372157399</v>
       </c>
       <c r="AO380" t="n">
-        <v>0.4964684575356701</v>
+        <v>0.4964684575356704</v>
       </c>
       <c r="AP380" t="n">
-        <v>-2.537533612885238</v>
+        <v>-2.537533612885102</v>
       </c>
       <c r="AQ380" t="n">
         <v>19.6</v>
@@ -62320,16 +62320,16 @@
         <v>-0.1947088368020093</v>
       </c>
       <c r="AM381" t="n">
-        <v>0.3035220749319821</v>
+        <v>0.3035220749319825</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.02465824743687013</v>
+        <v>0.02465824743687012</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.4899948718309223</v>
+        <v>0.4899948718309226</v>
       </c>
       <c r="AP381" t="n">
-        <v>-2.242993256171579</v>
+        <v>-2.242993256171588</v>
       </c>
       <c r="AQ381" t="n">
         <v>23.41269841269841</v>
@@ -62473,10 +62473,10 @@
         <v>-0.3743762766925309</v>
       </c>
       <c r="AI382" t="n">
-        <v>7.127779594400253</v>
+        <v>7.12777959440025</v>
       </c>
       <c r="AJ382" t="n">
-        <v>-0.2307797584322353</v>
+        <v>-0.2307797584322326</v>
       </c>
       <c r="AK382" t="n">
         <v>7.110202206771168</v>
@@ -62485,16 +62485,16 @@
         <v>-0.2132023708031507</v>
       </c>
       <c r="AM382" t="n">
-        <v>0.3056770963992276</v>
+        <v>0.3056770963992281</v>
       </c>
       <c r="AN382" t="n">
-        <v>0.02512392944114575</v>
+        <v>0.02512392944114572</v>
       </c>
       <c r="AO382" t="n">
-        <v>0.48360047858094</v>
+        <v>0.4836004785809395</v>
       </c>
       <c r="AP382" t="n">
-        <v>-2.58274150505997</v>
+        <v>-2.58274150505993</v>
       </c>
       <c r="AQ382" t="n">
         <v>22.83464566929134</v>
@@ -62638,28 +62638,28 @@
         <v>-0.3532653877931793</v>
       </c>
       <c r="AI383" t="n">
-        <v>7.117424820782308</v>
+        <v>7.117424820782309</v>
       </c>
       <c r="AJ383" t="n">
-        <v>-0.2204249848142901</v>
+        <v>-0.2204249848142918</v>
       </c>
       <c r="AK383" t="n">
         <v>7.115220843019268</v>
       </c>
       <c r="AL383" t="n">
-        <v>-0.21822100705125</v>
+        <v>-0.2182210070512509</v>
       </c>
       <c r="AM383" t="n">
-        <v>0.3083414575758079</v>
+        <v>0.3083414575758074</v>
       </c>
       <c r="AN383" t="n">
         <v>0.0254428638817728</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.4749824439402989</v>
+        <v>0.474982443940299</v>
       </c>
       <c r="AP383" t="n">
-        <v>-2.317107881992653</v>
+        <v>-2.317107881992696</v>
       </c>
       <c r="AQ383" t="n">
         <v>25.390625</v>
@@ -62803,10 +62803,10 @@
         <v>-0.3601815164805569</v>
       </c>
       <c r="AI384" t="n">
-        <v>7.116315246651979</v>
+        <v>7.116315246651977</v>
       </c>
       <c r="AJ384" t="n">
-        <v>-0.2198151360257583</v>
+        <v>-0.2198151360257565</v>
       </c>
       <c r="AK384" t="n">
         <v>7.112470209890858</v>
@@ -62815,16 +62815,16 @@
         <v>-0.2159700992646369</v>
       </c>
       <c r="AM384" t="n">
-        <v>0.3094443575020188</v>
+        <v>0.3094443575020182</v>
       </c>
       <c r="AN384" t="n">
-        <v>0.02578750722031873</v>
+        <v>0.0257875072203187</v>
       </c>
       <c r="AO384" t="n">
-        <v>0.467103914503924</v>
+        <v>0.4671039145039241</v>
       </c>
       <c r="AP384" t="n">
-        <v>-2.25010635424544</v>
+        <v>-2.250106354245415</v>
       </c>
       <c r="AQ384" t="n">
         <v>25.1937984496124</v>
@@ -62968,28 +62968,28 @@
         <v>-0.3572511574441446</v>
       </c>
       <c r="AI385" t="n">
-        <v>7.109165799046382</v>
+        <v>7.109165799046384</v>
       </c>
       <c r="AJ385" t="n">
-        <v>-0.1981660241135206</v>
+        <v>-0.1981660241135224</v>
       </c>
       <c r="AK385" t="n">
-        <v>7.105086649080123</v>
+        <v>7.105086649080124</v>
       </c>
       <c r="AL385" t="n">
-        <v>-0.1940868741472617</v>
+        <v>-0.1940868741472626</v>
       </c>
       <c r="AM385" t="n">
-        <v>0.3112159059696449</v>
+        <v>0.3112159059696454</v>
       </c>
       <c r="AN385" t="n">
-        <v>0.02619128791084347</v>
+        <v>0.02619128791084346</v>
       </c>
       <c r="AO385" t="n">
-        <v>0.4597800393113443</v>
+        <v>0.4597800393113445</v>
       </c>
       <c r="AP385" t="n">
-        <v>-1.804694563734907</v>
+        <v>-1.804694563734948</v>
       </c>
       <c r="AQ385" t="n">
         <v>26.53846153846154</v>
@@ -63133,10 +63133,10 @@
         <v>-0.3961107645148783</v>
       </c>
       <c r="AI386" t="n">
-        <v>7.14047665869759</v>
+        <v>7.140476658697598</v>
       </c>
       <c r="AJ386" t="n">
-        <v>-0.2639765289978833</v>
+        <v>-0.2639765289978913</v>
       </c>
       <c r="AK386" t="n">
         <v>7.107009848336411</v>
@@ -63145,16 +63145,16 @@
         <v>-0.2305097186367044</v>
       </c>
       <c r="AM386" t="n">
-        <v>0.3120213667410841</v>
+        <v>0.3120213667410843</v>
       </c>
       <c r="AN386" t="n">
-        <v>0.02660872919284651</v>
+        <v>0.02660872919284657</v>
       </c>
       <c r="AO386" t="n">
-        <v>0.4527828726277021</v>
+        <v>0.4527828726277016</v>
       </c>
       <c r="AP386" t="n">
-        <v>-2.939625212524785</v>
+        <v>-2.939625212524932</v>
       </c>
       <c r="AQ386" t="n">
         <v>19.08396946564886</v>
@@ -63298,10 +63298,10 @@
         <v>-0.3840267967645961</v>
       </c>
       <c r="AI387" t="n">
-        <v>7.192104266103096</v>
+        <v>7.192104266103097</v>
       </c>
       <c r="AJ387" t="n">
-        <v>-0.3266042928059765</v>
+        <v>-0.3266042928059782</v>
       </c>
       <c r="AK387" t="n">
         <v>7.130667004235951</v>
@@ -63310,16 +63310,16 @@
         <v>-0.2651670309388319</v>
       </c>
       <c r="AM387" t="n">
-        <v>0.3119580514589062</v>
+        <v>0.3119580514589064</v>
       </c>
       <c r="AN387" t="n">
-        <v>0.02723917591229311</v>
+        <v>0.02723917591229313</v>
       </c>
       <c r="AO387" t="n">
         <v>0.4402354538323348</v>
       </c>
       <c r="AP387" t="n">
-        <v>-3.839693371807415</v>
+        <v>-3.839693371807441</v>
       </c>
       <c r="AQ387" t="n">
         <v>21.96969696969697</v>
@@ -63475,7 +63475,7 @@
         <v>-0.3034632518909506</v>
       </c>
       <c r="AM388" t="n">
-        <v>0.3060770546706496</v>
+        <v>0.3060770546706492</v>
       </c>
       <c r="AN388" t="n">
         <v>0.02737088803905663</v>
@@ -63484,7 +63484,7 @@
         <v>0.4158878716209133</v>
       </c>
       <c r="AP388" t="n">
-        <v>-3.702123811175266</v>
+        <v>-3.702123811175261</v>
       </c>
       <c r="AQ388" t="n">
         <v>19.54887218045113</v>
@@ -63628,10 +63628,10 @@
         <v>-0.3739557950671877</v>
       </c>
       <c r="AI389" t="n">
-        <v>7.164105908482372</v>
+        <v>7.16410590848237</v>
       </c>
       <c r="AJ389" t="n">
-        <v>-0.2680058642318839</v>
+        <v>-0.2680058642318812</v>
       </c>
       <c r="AK389" t="n">
         <v>7.162206823443969</v>
@@ -63640,16 +63640,16 @@
         <v>-0.266106779193481</v>
       </c>
       <c r="AM389" t="n">
-        <v>0.3021518080029217</v>
+        <v>0.3021518080029227</v>
       </c>
       <c r="AN389" t="n">
-        <v>0.02724691784252936</v>
+        <v>0.02724691784252931</v>
       </c>
       <c r="AO389" t="n">
         <v>0.3910846972576566</v>
       </c>
       <c r="AP389" t="n">
-        <v>-2.573075475175267</v>
+        <v>-2.573075475175223</v>
       </c>
       <c r="AQ389" t="n">
         <v>23.88059701492537</v>
@@ -63793,10 +63793,10 @@
         <v>-0.3098543987164115</v>
       </c>
       <c r="AI390" t="n">
-        <v>7.165713254747862</v>
+        <v>7.165713254747866</v>
       </c>
       <c r="AJ390" t="n">
-        <v>-0.2102131288628524</v>
+        <v>-0.2102131288628559</v>
       </c>
       <c r="AK390" t="n">
         <v>7.141021818380439</v>
@@ -63805,16 +63805,16 @@
         <v>-0.1855216924954295</v>
       </c>
       <c r="AM390" t="n">
-        <v>0.3004913268435102</v>
+        <v>0.3004913268435098</v>
       </c>
       <c r="AN390" t="n">
-        <v>0.02739193077523432</v>
+        <v>0.02739193077523433</v>
       </c>
       <c r="AO390" t="n">
-        <v>0.3752726470948199</v>
+        <v>0.3752726470948202</v>
       </c>
       <c r="AP390" t="n">
-        <v>-1.615899255612474</v>
+        <v>-1.615899255612529</v>
       </c>
       <c r="AQ390" t="n">
         <v>30.74074074074074</v>
@@ -63958,10 +63958,10 @@
         <v>-0.3595117112585564</v>
       </c>
       <c r="AI391" t="n">
-        <v>7.208249532027231</v>
+        <v>7.208249532027229</v>
       </c>
       <c r="AJ391" t="n">
-        <v>-0.321949445052133</v>
+        <v>-0.3219494450521312</v>
       </c>
       <c r="AK391" t="n">
         <v>7.146296571548195</v>
@@ -63970,16 +63970,16 @@
         <v>-0.2599964845730973</v>
       </c>
       <c r="AM391" t="n">
-        <v>0.2982197220770058</v>
+        <v>0.2982197220770054</v>
       </c>
       <c r="AN391" t="n">
-        <v>0.02742417953210373</v>
+        <v>0.02742417953210363</v>
       </c>
       <c r="AO391" t="n">
-        <v>0.3625782951332475</v>
+        <v>0.3625782951332472</v>
       </c>
       <c r="AP391" t="n">
-        <v>-3.262311010331421</v>
+        <v>-3.262311010331393</v>
       </c>
       <c r="AQ391" t="n">
         <v>25.36764705882353</v>
@@ -64123,28 +64123,28 @@
         <v>-0.3569199379835908</v>
       </c>
       <c r="AI392" t="n">
-        <v>7.193412187855726</v>
+        <v>7.193412187855718</v>
       </c>
       <c r="AJ392" t="n">
-        <v>-0.3208121092729623</v>
+        <v>-0.3208121092729543</v>
       </c>
       <c r="AK392" t="n">
-        <v>7.176497065376473</v>
+        <v>7.176497065376474</v>
       </c>
       <c r="AL392" t="n">
-        <v>-0.3038969867937098</v>
+        <v>-0.3038969867937107</v>
       </c>
       <c r="AM392" t="n">
-        <v>0.2910761841041086</v>
+        <v>0.2910761841041076</v>
       </c>
       <c r="AN392" t="n">
-        <v>0.02685747952387156</v>
+        <v>0.02685747952387152</v>
       </c>
       <c r="AO392" t="n">
-        <v>0.3370674577034442</v>
+        <v>0.3370674577034428</v>
       </c>
       <c r="AP392" t="n">
-        <v>-3.114608684051328</v>
+        <v>-3.114608684051217</v>
       </c>
       <c r="AQ392" t="n">
         <v>26.27737226277372</v>
@@ -64288,10 +64288,10 @@
         <v>-0.3379904197184791</v>
       </c>
       <c r="AI393" t="n">
-        <v>7.227115602342041</v>
+        <v>7.227115602342048</v>
       </c>
       <c r="AJ393" t="n">
-        <v>-0.3273157785810543</v>
+        <v>-0.3273157785810614</v>
       </c>
       <c r="AK393" t="n">
         <v>7.185469892270627</v>
@@ -64300,16 +64300,16 @@
         <v>-0.2856700685096403</v>
       </c>
       <c r="AM393" t="n">
-        <v>0.281226998760588</v>
+        <v>0.2812269987605887</v>
       </c>
       <c r="AN393" t="n">
-        <v>0.0269718053742217</v>
+        <v>0.02697180537422167</v>
       </c>
       <c r="AO393" t="n">
-        <v>0.3136210223326474</v>
+        <v>0.3136210223326478</v>
       </c>
       <c r="AP393" t="n">
-        <v>-3.086315120704688</v>
+        <v>-3.086315120704791</v>
       </c>
       <c r="AQ393" t="n">
         <v>27.17391304347826</v>
@@ -64453,10 +64453,10 @@
         <v>-0.3408821770613137</v>
       </c>
       <c r="AI394" t="n">
-        <v>7.187163192389367</v>
+        <v>7.187163192389372</v>
       </c>
       <c r="AJ394" t="n">
-        <v>-0.3014629665592885</v>
+        <v>-0.3014629665592938</v>
       </c>
       <c r="AK394" t="n">
         <v>7.208338760609084</v>
@@ -64465,16 +64465,16 @@
         <v>-0.3226385347790055</v>
       </c>
       <c r="AM394" t="n">
-        <v>0.2681836981576121</v>
+        <v>0.2681836981576122</v>
       </c>
       <c r="AN394" t="n">
-        <v>0.02658698789673927</v>
+        <v>0.02658698789673936</v>
       </c>
       <c r="AO394" t="n">
-        <v>0.2859081509452629</v>
+        <v>0.285908150945263</v>
       </c>
       <c r="AP394" t="n">
-        <v>-2.632696204720034</v>
+        <v>-2.632696204720104</v>
       </c>
       <c r="AQ394" t="n">
         <v>28.05755395683453</v>
@@ -64618,10 +64618,10 @@
         <v>-0.3319473928581012</v>
       </c>
       <c r="AI395" t="n">
-        <v>7.214951953115579</v>
+        <v>7.214951953115591</v>
       </c>
       <c r="AJ395" t="n">
-        <v>-0.3349518386746606</v>
+        <v>-0.334951838674673</v>
       </c>
       <c r="AK395" t="n">
         <v>7.186200492654655</v>
@@ -64630,16 +64630,16 @@
         <v>-0.3062003782137372</v>
       </c>
       <c r="AM395" t="n">
-        <v>0.2591628297636748</v>
+        <v>0.2591628297636744</v>
       </c>
       <c r="AN395" t="n">
-        <v>0.02587977479594331</v>
+        <v>0.02587977479594339</v>
       </c>
       <c r="AO395" t="n">
-        <v>0.2661082014924122</v>
+        <v>0.266108201492412</v>
       </c>
       <c r="AP395" t="n">
-        <v>-2.994052922510445</v>
+        <v>-2.994052922510599</v>
       </c>
       <c r="AQ395" t="n">
         <v>27.5</v>
@@ -64783,10 +64783,10 @@
         <v>-0.3575433349367092</v>
       </c>
       <c r="AI396" t="n">
-        <v>7.197430004066453</v>
+        <v>7.197430004066455</v>
       </c>
       <c r="AJ396" t="n">
-        <v>-0.3056300773086402</v>
+        <v>-0.305630077308642</v>
       </c>
       <c r="AK396" t="n">
         <v>7.201835396295348</v>
@@ -64795,16 +64795,16 @@
         <v>-0.3100354695375351</v>
       </c>
       <c r="AM396" t="n">
-        <v>0.2466333883508324</v>
+        <v>0.2466333883508319</v>
       </c>
       <c r="AN396" t="n">
-        <v>0.02476543449503272</v>
+        <v>0.0247654344950328</v>
       </c>
       <c r="AO396" t="n">
-        <v>0.2401258754735008</v>
+        <v>0.2401258754735003</v>
       </c>
       <c r="AP396" t="n">
-        <v>-2.521856098757829</v>
+        <v>-2.521856098757837</v>
       </c>
       <c r="AQ396" t="n">
         <v>26.24113475177305</v>
@@ -64951,25 +64951,25 @@
         <v>7.230123089945971</v>
       </c>
       <c r="AJ397" t="n">
-        <v>-0.3291230670577878</v>
+        <v>-0.3291230670577869</v>
       </c>
       <c r="AK397" t="n">
-        <v>7.179650721554483</v>
+        <v>7.179650721554484</v>
       </c>
       <c r="AL397" t="n">
-        <v>-0.2786506986662998</v>
+        <v>-0.2786506986663007</v>
       </c>
       <c r="AM397" t="n">
-        <v>0.2377807761788565</v>
+        <v>0.2377807761788571</v>
       </c>
       <c r="AN397" t="n">
-        <v>0.02334020127887796</v>
+        <v>0.02334020127887793</v>
       </c>
       <c r="AO397" t="n">
-        <v>0.2171758918683913</v>
+        <v>0.2171758918683914</v>
       </c>
       <c r="AP397" t="n">
-        <v>-2.751183602296473</v>
+        <v>-2.751183602296446</v>
       </c>
       <c r="AQ397" t="n">
         <v>26.76056338028169</v>
@@ -65113,10 +65113,10 @@
         <v>-0.4126039637192198</v>
       </c>
       <c r="AI398" t="n">
-        <v>7.208528037732954</v>
+        <v>7.20852803773295</v>
       </c>
       <c r="AJ398" t="n">
-        <v>-0.2978281933726024</v>
+        <v>-0.2978281933725988</v>
       </c>
       <c r="AK398" t="n">
         <v>7.206616000051887</v>
@@ -65125,16 +65125,16 @@
         <v>-0.2959161556915353</v>
       </c>
       <c r="AM398" t="n">
-        <v>0.2255544515066683</v>
+        <v>0.2255544515066686</v>
       </c>
       <c r="AN398" t="n">
-        <v>0.0206724522626572</v>
+        <v>0.0206724522626571</v>
       </c>
       <c r="AO398" t="n">
-        <v>0.1898019966940708</v>
+        <v>0.1898019966940717</v>
       </c>
       <c r="AP398" t="n">
-        <v>-2.287488640557831</v>
+        <v>-2.287488640557774</v>
       </c>
       <c r="AQ398" t="n">
         <v>16.43356643356643</v>
@@ -65278,10 +65278,10 @@
         <v>-0.4212184443996074</v>
       </c>
       <c r="AI399" t="n">
-        <v>7.198803092238432</v>
+        <v>7.19880309223843</v>
       </c>
       <c r="AJ399" t="n">
-        <v>-0.2872029793233928</v>
+        <v>-0.287202979323391</v>
       </c>
       <c r="AK399" t="n">
         <v>7.18051307481679</v>
@@ -65290,16 +65290,16 @@
         <v>-0.2689129619017505</v>
       </c>
       <c r="AM399" t="n">
-        <v>0.2150441262650616</v>
+        <v>0.2150441262650612</v>
       </c>
       <c r="AN399" t="n">
-        <v>0.0177489551638892</v>
+        <v>0.01774895516388914</v>
       </c>
       <c r="AO399" t="n">
         <v>0.1629684999540825</v>
       </c>
       <c r="AP399" t="n">
-        <v>-2.108546902541169</v>
+        <v>-2.108546902541137</v>
       </c>
       <c r="AQ399" t="n">
         <v>14.93055555555556</v>
@@ -65443,10 +65443,10 @@
         <v>-0.4085440353357788</v>
       </c>
       <c r="AI400" t="n">
-        <v>7.172424239411002</v>
+        <v>7.172424239411004</v>
       </c>
       <c r="AJ400" t="n">
-        <v>-0.2608241264959634</v>
+        <v>-0.2608241264959652</v>
       </c>
       <c r="AK400" t="n">
         <v>7.16705299197773</v>
@@ -65455,16 +65455,16 @@
         <v>-0.2554528790626911</v>
       </c>
       <c r="AM400" t="n">
-        <v>0.2054336514894463</v>
+        <v>0.205433651489446</v>
       </c>
       <c r="AN400" t="n">
         <v>0.01456465550582345</v>
       </c>
       <c r="AO400" t="n">
-        <v>0.1417286033373033</v>
+        <v>0.1417286033373026</v>
       </c>
       <c r="AP400" t="n">
-        <v>-1.745878920107388</v>
+        <v>-1.745878920107403</v>
       </c>
       <c r="AQ400" t="n">
         <v>18.96551724137931</v>
@@ -65608,10 +65608,10 @@
         <v>-0.3831955966178588</v>
       </c>
       <c r="AI401" t="n">
-        <v>7.163756390646673</v>
+        <v>7.163756390646672</v>
       </c>
       <c r="AJ401" t="n">
-        <v>-0.2695565424716238</v>
+        <v>-0.2695565424716229</v>
       </c>
       <c r="AK401" t="n">
         <v>7.153532751444382</v>
@@ -65620,16 +65620,16 @@
         <v>-0.2593329032693328</v>
       </c>
       <c r="AM401" t="n">
-        <v>0.1941661953581056</v>
+        <v>0.1941661953581061</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.01312004055850015</v>
+        <v>0.01312004055850013</v>
       </c>
       <c r="AO401" t="n">
         <v>0.1245718258151718</v>
       </c>
       <c r="AP401" t="n">
-        <v>-1.828909997258128</v>
+        <v>-1.828909997258109</v>
       </c>
       <c r="AQ401" t="n">
         <v>25.34246575342466</v>
@@ -65773,10 +65773,10 @@
         <v>-0.4292495687682463</v>
       </c>
       <c r="AI402" t="n">
-        <v>7.158063699621736</v>
+        <v>7.158063699621738</v>
       </c>
       <c r="AJ402" t="n">
-        <v>-0.2875636118836988</v>
+        <v>-0.2875636118837006</v>
       </c>
       <c r="AK402" t="n">
         <v>7.150669702211316</v>
@@ -65785,16 +65785,16 @@
         <v>-0.2801696144732793</v>
       </c>
       <c r="AM402" t="n">
-        <v>0.183949493726688</v>
+        <v>0.1839494937266881</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.01194074338472802</v>
+        <v>0.01194074338472806</v>
       </c>
       <c r="AO402" t="n">
-        <v>0.110754980517583</v>
+        <v>0.1107549805175829</v>
       </c>
       <c r="AP402" t="n">
-        <v>-2.019875210260015</v>
+        <v>-2.019875210260029</v>
       </c>
       <c r="AQ402" t="n">
         <v>13.26530612244898</v>
@@ -65938,10 +65938,10 @@
         <v>-0.3992745036704797</v>
       </c>
       <c r="AI403" t="n">
-        <v>7.157435208014565</v>
+        <v>7.157435208014563</v>
       </c>
       <c r="AJ403" t="n">
-        <v>-0.2723353201666647</v>
+        <v>-0.272335320166663</v>
       </c>
       <c r="AK403" t="n">
         <v>7.140926852093823</v>
@@ -65950,16 +65950,16 @@
         <v>-0.255826964245923</v>
       </c>
       <c r="AM403" t="n">
-        <v>0.1753430411611928</v>
+        <v>0.1753430411611933</v>
       </c>
       <c r="AN403" t="n">
-        <v>0.009717654232020439</v>
+        <v>0.00971765423202034</v>
       </c>
       <c r="AO403" t="n">
-        <v>0.09620195025422784</v>
+        <v>0.09620195025422695</v>
       </c>
       <c r="AP403" t="n">
-        <v>-1.803435138632572</v>
+        <v>-1.803435138632542</v>
       </c>
       <c r="AQ403" t="n">
         <v>21.28378378378378</v>
@@ -66103,10 +66103,10 @@
         <v>-0.4054067164299404</v>
       </c>
       <c r="AI404" t="n">
-        <v>7.15038681134007</v>
+        <v>7.150386811340072</v>
       </c>
       <c r="AJ404" t="n">
-        <v>-0.2679867754819156</v>
+        <v>-0.2679867754819174</v>
       </c>
       <c r="AK404" t="n">
         <v>7.142886401315924</v>
@@ -66115,16 +66115,16 @@
         <v>-0.26048636545777</v>
       </c>
       <c r="AM404" t="n">
-        <v>0.1664838398737869</v>
+        <v>0.1664838398737872</v>
       </c>
       <c r="AN404" t="n">
-        <v>0.008089376136153925</v>
+        <v>0.008089376136153875</v>
       </c>
       <c r="AO404" t="n">
-        <v>0.08489626886092971</v>
+        <v>0.0848962688609296</v>
       </c>
       <c r="AP404" t="n">
-        <v>-1.726041303329976</v>
+        <v>-1.72604130332999</v>
       </c>
       <c r="AQ404" t="n">
         <v>20.80536912751678</v>
@@ -66268,10 +66268,10 @@
         <v>-0.4083969632115911</v>
       </c>
       <c r="AI405" t="n">
-        <v>7.137094841694642</v>
+        <v>7.137094841694645</v>
       </c>
       <c r="AJ405" t="n">
-        <v>-0.2547949416397106</v>
+        <v>-0.2547949416397133</v>
       </c>
       <c r="AK405" t="n">
         <v>7.137840883333127</v>
@@ -66280,16 +66280,16 @@
         <v>-0.2555409832781956</v>
       </c>
       <c r="AM405" t="n">
-        <v>0.1571907956492617</v>
+        <v>0.1571907956492611</v>
       </c>
       <c r="AN405" t="n">
-        <v>0.006581947594647856</v>
+        <v>0.006581947594647974</v>
       </c>
       <c r="AO405" t="n">
-        <v>0.07412699588694738</v>
+        <v>0.07412699588694804</v>
       </c>
       <c r="AP405" t="n">
-        <v>-1.546143135458674</v>
+        <v>-1.546143135458699</v>
       </c>
       <c r="AQ405" t="n">
         <v>21</v>
@@ -66433,10 +66433,10 @@
         <v>-0.4293733238353061</v>
       </c>
       <c r="AI406" t="n">
-        <v>7.1233912344352</v>
+        <v>7.123391234435203</v>
       </c>
       <c r="AJ406" t="n">
-        <v>-0.2666912908927195</v>
+        <v>-0.2666912908927221</v>
       </c>
       <c r="AK406" t="n">
         <v>7.12862724785568</v>
@@ -66445,16 +66445,16 @@
         <v>-0.2719273043131993</v>
       </c>
       <c r="AM406" t="n">
-        <v>0.1487097707294973</v>
+        <v>0.1487097707294961</v>
       </c>
       <c r="AN406" t="n">
-        <v>0.005441006961990058</v>
+        <v>0.005441006961990014</v>
       </c>
       <c r="AO406" t="n">
-        <v>0.06531270865715666</v>
+        <v>0.06531270865715677</v>
       </c>
       <c r="AP406" t="n">
-        <v>-1.670173140076241</v>
+        <v>-1.670173140076265</v>
       </c>
       <c r="AQ406" t="n">
         <v>14.56953642384106</v>
@@ -66598,10 +66598,10 @@
         <v>-0.4487866316567706</v>
       </c>
       <c r="AI407" t="n">
-        <v>7.116007318552882</v>
+        <v>7.11600731855288</v>
       </c>
       <c r="AJ407" t="n">
-        <v>-0.2873072529400895</v>
+        <v>-0.2873072529400869</v>
       </c>
       <c r="AK407" t="n">
         <v>7.118961040191934</v>
@@ -66610,16 +66610,16 @@
         <v>-0.2902609745791409</v>
       </c>
       <c r="AM407" t="n">
-        <v>0.1409513724492179</v>
+        <v>0.1409513724492178</v>
       </c>
       <c r="AN407" t="n">
-        <v>0.005644373135176906</v>
+        <v>0.005644373135176822</v>
       </c>
       <c r="AO407" t="n">
-        <v>0.0598657761353214</v>
+        <v>0.05986577613532174</v>
       </c>
       <c r="AP407" t="n">
-        <v>-1.891461410212615</v>
+        <v>-1.891461410212574</v>
       </c>
       <c r="AQ407" t="n">
         <v>10.19736842105263</v>
@@ -66763,10 +66763,10 @@
         <v>-0.4597199693866374</v>
       </c>
       <c r="AI408" t="n">
-        <v>7.11526245458776</v>
+        <v>7.115262454587763</v>
       </c>
       <c r="AJ408" t="n">
-        <v>-0.2838625369852208</v>
+        <v>-0.2838625369852235</v>
       </c>
       <c r="AK408" t="n">
         <v>7.113208458946866</v>
@@ -66778,13 +66778,13 @@
         <v>0.133301314367453</v>
       </c>
       <c r="AN408" t="n">
-        <v>0.005618445165739529</v>
+        <v>0.005618445165739616</v>
       </c>
       <c r="AO408" t="n">
         <v>0.05393458601808487</v>
       </c>
       <c r="AP408" t="n">
-        <v>-1.823531845613265</v>
+        <v>-1.823531845613289</v>
       </c>
       <c r="AQ408" t="n">
         <v>8.823529411764707</v>
@@ -66940,16 +66940,16 @@
         <v>-0.2852148781827166</v>
       </c>
       <c r="AM409" t="n">
-        <v>0.1248427026608145</v>
+        <v>0.1248427026608149</v>
       </c>
       <c r="AN409" t="n">
-        <v>0.005050876420738303</v>
+        <v>0.005050876420738246</v>
       </c>
       <c r="AO409" t="n">
-        <v>0.04692762159457986</v>
+        <v>0.04692762159458042</v>
       </c>
       <c r="AP409" t="n">
-        <v>-1.73798809933283</v>
+        <v>-1.737988099332821</v>
       </c>
       <c r="AQ409" t="n">
         <v>13.96103896103896</v>
@@ -67093,10 +67093,10 @@
         <v>-0.429456816758969</v>
       </c>
       <c r="AI410" t="n">
-        <v>7.100218718661558</v>
+        <v>7.100218718661557</v>
       </c>
       <c r="AJ410" t="n">
-        <v>-0.2699188643829933</v>
+        <v>-0.2699188643829924</v>
       </c>
       <c r="AK410" t="n">
         <v>7.105971078464224</v>
@@ -67108,13 +67108,13 @@
         <v>0.1175739730667294</v>
       </c>
       <c r="AN410" t="n">
-        <v>0.00520957018071537</v>
+        <v>0.005209570180715356</v>
       </c>
       <c r="AO410" t="n">
-        <v>0.04219701739313308</v>
+        <v>0.0421970173931332</v>
       </c>
       <c r="AP410" t="n">
-        <v>-1.615152291713727</v>
+        <v>-1.615152291713709</v>
       </c>
       <c r="AQ410" t="n">
         <v>15.16129032258065</v>
@@ -67258,10 +67258,10 @@
         <v>-0.4334011939243894</v>
       </c>
       <c r="AI411" t="n">
-        <v>7.097935875054439</v>
+        <v>7.097935875054437</v>
       </c>
       <c r="AJ411" t="n">
-        <v>-0.2822358208857381</v>
+        <v>-0.2822358208857363</v>
       </c>
       <c r="AK411" t="n">
         <v>7.101361129315627</v>
@@ -67270,16 +67270,16 @@
         <v>-0.2856610751469262</v>
       </c>
       <c r="AM411" t="n">
-        <v>0.1117472247487876</v>
+        <v>0.1117472247487875</v>
       </c>
       <c r="AN411" t="n">
-        <v>0.005385102682029925</v>
+        <v>0.005385102682029907</v>
       </c>
       <c r="AO411" t="n">
-        <v>0.03866992220359033</v>
+        <v>0.03866992220359</v>
       </c>
       <c r="AP411" t="n">
-        <v>-1.737700494527127</v>
+        <v>-1.737700494527099</v>
       </c>
       <c r="AQ411" t="n">
         <v>14.1025641025641</v>
@@ -67423,10 +67423,10 @@
         <v>-0.4357829635966128</v>
       </c>
       <c r="AI412" t="n">
-        <v>7.097978821692021</v>
+        <v>7.097978821692022</v>
       </c>
       <c r="AJ412" t="n">
-        <v>-0.2799789819093057</v>
+        <v>-0.2799789819093075</v>
       </c>
       <c r="AK412" t="n">
         <v>7.099648834314064</v>
@@ -67435,16 +67435,16 @@
         <v>-0.2816489945313494</v>
       </c>
       <c r="AM412" t="n">
-        <v>0.1065475925362025</v>
+        <v>0.1065475925362033</v>
       </c>
       <c r="AN412" t="n">
-        <v>0.005956926407441003</v>
+        <v>0.005956926407440957</v>
       </c>
       <c r="AO412" t="n">
         <v>0.036279037840516</v>
       </c>
       <c r="AP412" t="n">
-        <v>-1.690013917359392</v>
+        <v>-1.690013917359405</v>
       </c>
       <c r="AQ412" t="n">
         <v>14.01273885350319</v>
@@ -67600,16 +67600,16 @@
         <v>-0.2780302006784368</v>
       </c>
       <c r="AM413" t="n">
-        <v>0.1013724682419976</v>
+        <v>0.1013724682419977</v>
       </c>
       <c r="AN413" t="n">
-        <v>0.006126167203105847</v>
+        <v>0.006126167203105798</v>
       </c>
       <c r="AO413" t="n">
-        <v>0.03348722035246277</v>
+        <v>0.03348722035246332</v>
       </c>
       <c r="AP413" t="n">
-        <v>-1.526737752078196</v>
+        <v>-1.526737752078189</v>
       </c>
       <c r="AQ413" t="n">
         <v>22.78481012658228</v>
@@ -67753,10 +67753,10 @@
         <v>-0.4281188441625243</v>
       </c>
       <c r="AI414" t="n">
-        <v>7.087097940453343</v>
+        <v>7.087097940453345</v>
       </c>
       <c r="AJ414" t="n">
-        <v>-0.2700980281913798</v>
+        <v>-0.2700980281913825</v>
       </c>
       <c r="AK414" t="n">
         <v>7.090805518999606</v>
@@ -67765,16 +67765,16 @@
         <v>-0.2738056067376426</v>
       </c>
       <c r="AM414" t="n">
-        <v>0.09919462776856289</v>
+        <v>0.09919462776856321</v>
       </c>
       <c r="AN414" t="n">
-        <v>0.006113943880485968</v>
+        <v>0.006113943880485972</v>
       </c>
       <c r="AO414" t="n">
-        <v>0.03204155062895098</v>
+        <v>0.03204155062895153</v>
       </c>
       <c r="AP414" t="n">
-        <v>-1.541595404790982</v>
+        <v>-1.541595404791005</v>
       </c>
       <c r="AQ414" t="n">
         <v>17.61006289308176</v>
@@ -67930,16 +67930,16 @@
         <v>-0.2722752351464175</v>
       </c>
       <c r="AM415" t="n">
-        <v>0.09750750254701511</v>
+        <v>0.097507502547015</v>
       </c>
       <c r="AN415" t="n">
-        <v>0.005510714664730422</v>
+        <v>0.005510714664730507</v>
       </c>
       <c r="AO415" t="n">
-        <v>0.03001455024934274</v>
+        <v>0.03001455024934374</v>
       </c>
       <c r="AP415" t="n">
-        <v>-1.600899787479531</v>
+        <v>-1.600899787479524</v>
       </c>
       <c r="AQ415" t="n">
         <v>14.375</v>
@@ -68095,16 +68095,16 @@
         <v>-0.2732956089855723</v>
       </c>
       <c r="AM416" t="n">
-        <v>0.09380549503386949</v>
+        <v>0.09380549503386901</v>
       </c>
       <c r="AN416" t="n">
-        <v>0.004784904607979855</v>
+        <v>0.004784904607979881</v>
       </c>
       <c r="AO416" t="n">
-        <v>0.02699383492044827</v>
+        <v>0.02699383492044782</v>
       </c>
       <c r="AP416" t="n">
-        <v>-1.55794228030282</v>
+        <v>-1.557942280302812</v>
       </c>
       <c r="AQ416" t="n">
         <v>18.01242236024845</v>
@@ -68248,10 +68248,10 @@
         <v>-0.4103351682659895</v>
       </c>
       <c r="AI417" t="n">
-        <v>7.097145375663948</v>
+        <v>7.097145375663951</v>
       </c>
       <c r="AJ417" t="n">
-        <v>-0.2729452223131181</v>
+        <v>-0.2729452223131208</v>
       </c>
       <c r="AK417" t="n">
         <v>7.093828611034739</v>
@@ -68260,16 +68260,16 @@
         <v>-0.2696284576839085</v>
       </c>
       <c r="AM417" t="n">
-        <v>0.08945254406056392</v>
+        <v>0.08945254406056438</v>
       </c>
       <c r="AN417" t="n">
-        <v>0.004001520125414807</v>
+        <v>0.004001520125414798</v>
       </c>
       <c r="AO417" t="n">
-        <v>0.02385555423225172</v>
+        <v>0.02385555423225116</v>
       </c>
       <c r="AP417" t="n">
-        <v>-1.523824448003726</v>
+        <v>-1.523824448003748</v>
       </c>
       <c r="AQ417" t="n">
         <v>22.22222222222222</v>
@@ -68413,10 +68413,10 @@
         <v>-0.3615604420911946</v>
       </c>
       <c r="AI418" t="n">
-        <v>7.088227962421954</v>
+        <v>7.088227962421951</v>
       </c>
       <c r="AJ418" t="n">
-        <v>-0.2622277487989066</v>
+        <v>-0.262227748798904</v>
       </c>
       <c r="AK418" t="n">
         <v>7.092951699003613</v>
@@ -68425,16 +68425,16 @@
         <v>-0.2669514853805666</v>
       </c>
       <c r="AM418" t="n">
-        <v>0.07912491692886864</v>
+        <v>0.07912491692886899</v>
       </c>
       <c r="AN418" t="n">
-        <v>0.003813743757049957</v>
+        <v>0.003813743757049903</v>
       </c>
       <c r="AO418" t="n">
-        <v>0.01902803623666371</v>
+        <v>0.01902803623666316</v>
       </c>
       <c r="AP418" t="n">
-        <v>-1.388972796501224</v>
+        <v>-1.388972796501187</v>
       </c>
       <c r="AQ418" t="n">
         <v>35.2760736196319</v>
@@ -68578,10 +68578,10 @@
         <v>-0.384938382057288</v>
       </c>
       <c r="AI419" t="n">
-        <v>7.082675656384675</v>
+        <v>7.082675656384673</v>
       </c>
       <c r="AJ419" t="n">
-        <v>-0.2467758265201727</v>
+        <v>-0.2467758265201709</v>
       </c>
       <c r="AK419" t="n">
         <v>7.085940899278786</v>
@@ -68590,16 +68590,16 @@
         <v>-0.2500410694142845</v>
       </c>
       <c r="AM419" t="n">
-        <v>0.07019093860911679</v>
+        <v>0.07019093860911668</v>
       </c>
       <c r="AN419" t="n">
-        <v>0.003788844982403293</v>
+        <v>0.003788844982403339</v>
       </c>
       <c r="AO419" t="n">
-        <v>0.0153072785246503</v>
+        <v>0.01530727852465064</v>
       </c>
       <c r="AP419" t="n">
-        <v>-1.204234266049846</v>
+        <v>-1.204234266049821</v>
       </c>
       <c r="AQ419" t="n">
         <v>33.23170731707317</v>
@@ -68743,10 +68743,10 @@
         <v>-0.3843760100465339</v>
       </c>
       <c r="AI420" t="n">
-        <v>7.082585232341569</v>
+        <v>7.082585232341567</v>
       </c>
       <c r="AJ420" t="n">
-        <v>-0.2597850728872233</v>
+        <v>-0.2597850728872215</v>
       </c>
       <c r="AK420" t="n">
         <v>7.080231185021037</v>
@@ -68755,16 +68755,16 @@
         <v>-0.2574310255666914</v>
       </c>
       <c r="AM420" t="n">
-        <v>0.06072301451314636</v>
+        <v>0.0607230145131474</v>
       </c>
       <c r="AN420" t="n">
-        <v>0.003218097337044184</v>
+        <v>0.003218097337044118</v>
       </c>
       <c r="AO420" t="n">
-        <v>0.01127031184523331</v>
+        <v>0.01127031184523342</v>
       </c>
       <c r="AP420" t="n">
-        <v>-1.340364881437342</v>
+        <v>-1.340364881437316</v>
       </c>
       <c r="AQ420" t="n">
         <v>33.33333333333334</v>
@@ -68908,10 +68908,10 @@
         <v>-0.3814275031811007</v>
       </c>
       <c r="AI421" t="n">
-        <v>7.082752176397554</v>
+        <v>7.082752176397555</v>
       </c>
       <c r="AJ421" t="n">
-        <v>-0.2453522168333455</v>
+        <v>-0.2453522168333464</v>
       </c>
       <c r="AK421" t="n">
         <v>7.078545045220129</v>
@@ -68920,16 +68920,16 @@
         <v>-0.2411450856559201</v>
       </c>
       <c r="AM421" t="n">
-        <v>0.04987769893955601</v>
+        <v>0.04987769893955558</v>
       </c>
       <c r="AN421" t="n">
-        <v>0.002647769861786034</v>
+        <v>0.002647769861786137</v>
       </c>
       <c r="AO421" t="n">
-        <v>0.007555907385723093</v>
+        <v>0.00755590738572276</v>
       </c>
       <c r="AP421" t="n">
-        <v>-1.168532659260674</v>
+        <v>-1.168532659260679</v>
       </c>
       <c r="AQ421" t="n">
         <v>34.93975903614458</v>
@@ -69073,10 +69073,10 @@
         <v>-0.3607442933905176</v>
       </c>
       <c r="AI422" t="n">
-        <v>7.073418742129173</v>
+        <v>7.073418742129174</v>
       </c>
       <c r="AJ422" t="n">
-        <v>-0.2359186467617418</v>
+        <v>-0.2359186467617427</v>
       </c>
       <c r="AK422" t="n">
         <v>7.075576762908686</v>
@@ -69085,16 +69085,16 @@
         <v>-0.2380766675412547</v>
       </c>
       <c r="AM422" t="n">
-        <v>0.03723342047483347</v>
+        <v>0.03723342047483359</v>
       </c>
       <c r="AN422" t="n">
-        <v>0.0007434096776329864</v>
+        <v>0.0007434096776329363</v>
       </c>
       <c r="AO422" t="n">
-        <v>0.003691827899840794</v>
+        <v>0.003691827899839573</v>
       </c>
       <c r="AP422" t="n">
-        <v>-1.05510573895228</v>
+        <v>-1.055105738952285</v>
       </c>
       <c r="AQ422" t="n">
         <v>37.4251497005988</v>
@@ -69250,16 +69250,16 @@
         <v>-0.2404456852747119</v>
       </c>
       <c r="AM423" t="n">
-        <v>0.02391394499985489</v>
+        <v>0.02391394499985428</v>
       </c>
       <c r="AN423" t="n">
-        <v>0.0004638728584110585</v>
+        <v>0.0004638728584110997</v>
       </c>
       <c r="AO423" t="n">
-        <v>0.001504277651263042</v>
+        <v>0.00150427765126282</v>
       </c>
       <c r="AP423" t="n">
-        <v>-1.095172559240736</v>
+        <v>-1.095172559240732</v>
       </c>
       <c r="AQ423" t="n">
         <v>35.11904761904762</v>
@@ -69403,10 +69403,10 @@
         <v>-0.3513694742831692</v>
       </c>
       <c r="AI424" t="n">
-        <v>7.06117555197594</v>
+        <v>7.061175551975939</v>
       </c>
       <c r="AJ424" t="n">
-        <v>-0.2336756854903443</v>
+        <v>-0.2336756854903435</v>
       </c>
       <c r="AK424" t="n">
         <v>7.061105294515807</v>
@@ -69415,16 +69415,16 @@
         <v>-0.2336054280302111</v>
       </c>
       <c r="AM424" t="n">
-        <v>0.01023096587809607</v>
+        <v>0.01023096587809661</v>
       </c>
       <c r="AN424" t="n">
-        <v>-0.0001641525470544615</v>
+        <v>-0.0001641525470544823</v>
       </c>
       <c r="AO424" t="n">
-        <v>0.000253092979595082</v>
+        <v>0.0002530929795961923</v>
       </c>
       <c r="AP424" t="n">
-        <v>-1.016380466853314</v>
+        <v>-1.0163804668533</v>
       </c>
       <c r="AQ424" t="n">
         <v>40.23668639053254</v>
@@ -69580,16 +69580,16 @@
         <v>-0.2251073081074608</v>
       </c>
       <c r="AM425" t="n">
-        <v>-0.001349940557734529</v>
+        <v>-0.001349940557734956</v>
       </c>
       <c r="AN425" t="n">
-        <v>-0.001242569541730301</v>
+        <v>-0.001242569541730382</v>
       </c>
       <c r="AO425" t="n">
-        <v>9.828375502973774e-05</v>
+        <v>9.828375502929365e-05</v>
       </c>
       <c r="AP425" t="n">
-        <v>-0.9199308462067914</v>
+        <v>-0.9199308462067871</v>
       </c>
       <c r="AQ425" t="n">
         <v>40.58823529411764</v>
@@ -69733,10 +69733,10 @@
         <v>-0.3665720868906721</v>
       </c>
       <c r="AI426" t="n">
-        <v>7.051845784111937</v>
+        <v>7.051845784111939</v>
       </c>
       <c r="AJ426" t="n">
-        <v>-0.22174572460266</v>
+        <v>-0.2217457246026617</v>
       </c>
       <c r="AK426" t="n">
         <v>7.04924004450221</v>
@@ -69745,16 +69745,16 @@
         <v>-0.2191399849929327</v>
       </c>
       <c r="AM426" t="n">
-        <v>-0.0124592779456514</v>
+        <v>-0.01245927794565087</v>
       </c>
       <c r="AN426" t="n">
-        <v>-0.002690846636687166</v>
+        <v>-0.002690846636687106</v>
       </c>
       <c r="AO426" t="n">
-        <v>0.000914944322433886</v>
+        <v>0.0009149443224345521</v>
       </c>
       <c r="AP426" t="n">
-        <v>-0.8720391648380724</v>
+        <v>-0.872039164838088</v>
       </c>
       <c r="AQ426" t="n">
         <v>37.42690058479532</v>
@@ -69898,10 +69898,10 @@
         <v>-0.3749214453147598</v>
       </c>
       <c r="AI427" t="n">
-        <v>7.044932512363692</v>
+        <v>7.044932512363691</v>
       </c>
       <c r="AJ427" t="n">
-        <v>-0.2339326420633991</v>
+        <v>-0.2339326420633983</v>
       </c>
       <c r="AK427" t="n">
         <v>7.044607485549974</v>
@@ -69910,16 +69910,16 @@
         <v>-0.2336076152496807</v>
       </c>
       <c r="AM427" t="n">
-        <v>-0.0235197471891116</v>
+        <v>-0.02351974718911197</v>
       </c>
       <c r="AN427" t="n">
-        <v>-0.003286981705062081</v>
+        <v>-0.003286981705062079</v>
       </c>
       <c r="AO427" t="n">
-        <v>0.002235402288773058</v>
+        <v>0.002235402288773947</v>
       </c>
       <c r="AP427" t="n">
-        <v>-1.003954290846183</v>
+        <v>-1.003954290846168</v>
       </c>
       <c r="AQ427" t="n">
         <v>35.46511627906976</v>
@@ -70063,10 +70063,10 @@
         <v>-0.4038889304824842</v>
       </c>
       <c r="AI428" t="n">
-        <v>7.04138072456642</v>
+        <v>7.041380724566422</v>
       </c>
       <c r="AJ428" t="n">
-        <v>-0.2399805399350727</v>
+        <v>-0.2399805399350745</v>
       </c>
       <c r="AK428" t="n">
         <v>7.036677431055121</v>
@@ -70075,16 +70075,16 @@
         <v>-0.2352772464237729</v>
       </c>
       <c r="AM428" t="n">
-        <v>-0.03604973348542571</v>
+        <v>-0.03604973348542533</v>
       </c>
       <c r="AN428" t="n">
-        <v>-0.003896888881646666</v>
+        <v>-0.003896888881646653</v>
       </c>
       <c r="AO428" t="n">
-        <v>0.004508577134016423</v>
+        <v>0.004508577134016534</v>
       </c>
       <c r="AP428" t="n">
-        <v>-1.06570750342158</v>
+        <v>-1.065707503421595</v>
       </c>
       <c r="AQ428" t="n">
         <v>28.03468208092486</v>
@@ -70228,10 +70228,10 @@
         <v>-0.379631294805006</v>
       </c>
       <c r="AI429" t="n">
-        <v>7.031781164871438</v>
+        <v>7.031781164871437</v>
       </c>
       <c r="AJ429" t="n">
-        <v>-0.2312812487947777</v>
+        <v>-0.2312812487947769</v>
       </c>
       <c r="AK429" t="n">
         <v>7.031531243279009</v>
@@ -70240,16 +70240,16 @@
         <v>-0.2310313272023485</v>
       </c>
       <c r="AM429" t="n">
-        <v>-0.04964211158845258</v>
+        <v>-0.0496421115884523</v>
       </c>
       <c r="AN429" t="n">
-        <v>-0.003622848094475877</v>
+        <v>-0.003622848094475932</v>
       </c>
       <c r="AO429" t="n">
-        <v>0.007358432861333086</v>
+        <v>0.007358432861332531</v>
       </c>
       <c r="AP429" t="n">
-        <v>-0.9620021970824821</v>
+        <v>-0.9620021970824676</v>
       </c>
       <c r="AQ429" t="n">
         <v>35.63218390804597</v>
@@ -70405,16 +70405,16 @@
         <v>-0.226940421596697</v>
       </c>
       <c r="AM430" t="n">
-        <v>-0.06336633742876532</v>
+        <v>-0.06336633742876464</v>
       </c>
       <c r="AN430" t="n">
-        <v>-0.003832222031667326</v>
+        <v>-0.00383222203166729</v>
       </c>
       <c r="AO430" t="n">
-        <v>0.01139353356262962</v>
+        <v>0.0113935335626284</v>
       </c>
       <c r="AP430" t="n">
-        <v>-0.8915152845393419</v>
+        <v>-0.8915152845393376</v>
       </c>
       <c r="AQ430" t="n">
         <v>36.28571428571429</v>
@@ -70558,10 +70558,10 @@
         <v>-0.3866719912931416</v>
       </c>
       <c r="AI431" t="n">
-        <v>7.012358254068221</v>
+        <v>7.012358254068223</v>
       </c>
       <c r="AJ431" t="n">
-        <v>-0.2203584371736902</v>
+        <v>-0.220358437173692</v>
       </c>
       <c r="AK431" t="n">
         <v>7.010266108789461</v>
@@ -70570,16 +70570,16 @@
         <v>-0.2182662918949294</v>
       </c>
       <c r="AM431" t="n">
-        <v>-0.07815930192347212</v>
+        <v>-0.07815930192347351</v>
       </c>
       <c r="AN431" t="n">
-        <v>-0.003730201847889384</v>
+        <v>-0.0037302018478894</v>
       </c>
       <c r="AO431" t="n">
-        <v>0.01669360800688602</v>
+        <v>0.01669360800688513</v>
       </c>
       <c r="AP431" t="n">
-        <v>-0.8298595079411745</v>
+        <v>-0.8298595079411905</v>
       </c>
       <c r="AQ431" t="n">
         <v>35.51136363636363</v>
@@ -70723,10 +70723,10 @@
         <v>-0.3737794891681316</v>
       </c>
       <c r="AI432" t="n">
-        <v>7.001516536947591</v>
+        <v>7.001516536947593</v>
       </c>
       <c r="AJ432" t="n">
-        <v>-0.2107164423430987</v>
+        <v>-0.2107164423431005</v>
       </c>
       <c r="AK432" t="n">
         <v>7.003692382618654</v>
@@ -70735,16 +70735,16 @@
         <v>-0.2128922880141619</v>
       </c>
       <c r="AM432" t="n">
-        <v>-0.09225745624393285</v>
+        <v>-0.09225745624393369</v>
       </c>
       <c r="AN432" t="n">
-        <v>-0.003729646461095566</v>
+        <v>-0.003729646461095512</v>
       </c>
       <c r="AO432" t="n">
-        <v>0.02283737241168682</v>
+        <v>0.02283737241168637</v>
       </c>
       <c r="AP432" t="n">
-        <v>-0.7175971148724744</v>
+        <v>-0.7175971148724907</v>
       </c>
       <c r="AQ432" t="n">
         <v>40.11299435028249</v>
@@ -70888,10 +70888,10 @@
         <v>-0.3720096601974126</v>
       </c>
       <c r="AI433" t="n">
-        <v>6.982853032266831</v>
+        <v>6.98285303226683</v>
       </c>
       <c r="AJ433" t="n">
-        <v>-0.1977530490514985</v>
+        <v>-0.1977530490514976</v>
       </c>
       <c r="AK433" t="n">
         <v>6.994908837140057</v>
@@ -70900,16 +70900,16 @@
         <v>-0.2098088539247245</v>
       </c>
       <c r="AM433" t="n">
-        <v>-0.1040956648961739</v>
+        <v>-0.1040956648961724</v>
       </c>
       <c r="AN433" t="n">
-        <v>-0.004775368000139281</v>
+        <v>-0.004775368000139335</v>
       </c>
       <c r="AO433" t="n">
         <v>0.0296640458840205</v>
       </c>
       <c r="AP433" t="n">
-        <v>-0.5684906885651003</v>
+        <v>-0.5684906885650866</v>
       </c>
       <c r="AQ433" t="n">
         <v>41.29213483146067</v>
@@ -71053,10 +71053,10 @@
         <v>-0.3427684275988581</v>
       </c>
       <c r="AI434" t="n">
-        <v>6.976537964100195</v>
+        <v>6.976537964100197</v>
       </c>
       <c r="AJ434" t="n">
-        <v>-0.1673381540721186</v>
+        <v>-0.1673381540721204</v>
       </c>
       <c r="AK434" t="n">
         <v>6.976048621620001</v>
@@ -71065,16 +71065,16 @@
         <v>-0.1668488115919251</v>
       </c>
       <c r="AM434" t="n">
-        <v>-0.1171809788132892</v>
+        <v>-0.1171809788132883</v>
       </c>
       <c r="AN434" t="n">
-        <v>-0.006568629287185491</v>
+        <v>-0.006568629287185546</v>
       </c>
       <c r="AO434" t="n">
-        <v>0.03914952746580436</v>
+        <v>0.03914952746580425</v>
       </c>
       <c r="AP434" t="n">
-        <v>-0.2223140460906146</v>
+        <v>-0.2223140460906322</v>
       </c>
       <c r="AQ434" t="n">
         <v>49.16201117318435</v>
@@ -71221,7 +71221,7 @@
         <v>6.958225902093973</v>
       </c>
       <c r="AJ435" t="n">
-        <v>-0.1582257113591092</v>
+        <v>-0.1582257113591101</v>
       </c>
       <c r="AK435" t="n">
         <v>6.970728111892008</v>
@@ -71230,16 +71230,16 @@
         <v>-0.1707279211571446</v>
       </c>
       <c r="AM435" t="n">
-        <v>-0.127636816539943</v>
+        <v>-0.127636816539944</v>
       </c>
       <c r="AN435" t="n">
-        <v>-0.00745101973257774</v>
+        <v>-0.007451019732577668</v>
       </c>
       <c r="AO435" t="n">
-        <v>0.04750067483060572</v>
+        <v>0.04750067483060583</v>
       </c>
       <c r="AP435" t="n">
-        <v>-0.1181830488027779</v>
+        <v>-0.1181830488027858</v>
       </c>
       <c r="AQ435" t="n">
         <v>50.27777777777779</v>
@@ -71398,13 +71398,13 @@
         <v>-0.138035958368065</v>
       </c>
       <c r="AN436" t="n">
-        <v>-0.008628156625160163</v>
+        <v>-0.008628156625160088</v>
       </c>
       <c r="AO436" t="n">
-        <v>0.05751510742764121</v>
+        <v>0.05751510742764043</v>
       </c>
       <c r="AP436" t="n">
-        <v>-0.005878665741873697</v>
+        <v>-0.005878665741872089</v>
       </c>
       <c r="AQ436" t="n">
         <v>52.48618784530387</v>
@@ -71548,10 +71548,10 @@
         <v>-0.3547928847683641</v>
       </c>
       <c r="AI437" t="n">
-        <v>6.950644730799363</v>
+        <v>6.950644730799358</v>
       </c>
       <c r="AJ437" t="n">
-        <v>-0.1501448147227027</v>
+        <v>-0.1501448147226974</v>
       </c>
       <c r="AK437" t="n">
         <v>6.959853578800648</v>
@@ -71560,16 +71560,16 @@
         <v>-0.159353662723988</v>
       </c>
       <c r="AM437" t="n">
-        <v>-0.1469566450661556</v>
+        <v>-0.1469566450661546</v>
       </c>
       <c r="AN437" t="n">
-        <v>-0.009026348114251901</v>
+        <v>-0.009026348114251986</v>
       </c>
       <c r="AO437" t="n">
-        <v>0.06603756167960351</v>
+        <v>0.06603756167960417</v>
       </c>
       <c r="AP437" t="n">
-        <v>-0.02584869659759381</v>
+        <v>-0.02584869659753125</v>
       </c>
       <c r="AQ437" t="n">
         <v>50.27472527472527</v>
@@ -71713,28 +71713,28 @@
         <v>-0.3370838716023448</v>
       </c>
       <c r="AI438" t="n">
-        <v>6.934622414140152</v>
+        <v>6.934622414140156</v>
       </c>
       <c r="AJ438" t="n">
-        <v>-0.1321226430219875</v>
+        <v>-0.1321226430219919</v>
       </c>
       <c r="AK438" t="n">
-        <v>6.947114416435721</v>
+        <v>6.94711441643572</v>
       </c>
       <c r="AL438" t="n">
-        <v>-0.1446146453175565</v>
+        <v>-0.1446146453175556</v>
       </c>
       <c r="AM438" t="n">
-        <v>-0.1568781652619921</v>
+        <v>-0.1568781652619925</v>
       </c>
       <c r="AN438" t="n">
-        <v>-0.01004287133747513</v>
+        <v>-0.010042871337475</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.07699206242755419</v>
+        <v>0.07699206242755485</v>
       </c>
       <c r="AP438" t="n">
-        <v>0.1806443022076749</v>
+        <v>0.1806443022076252</v>
       </c>
       <c r="AQ438" t="n">
         <v>59.56284153005465</v>
@@ -71878,10 +71878,10 @@
         <v>-0.3543105242733491</v>
       </c>
       <c r="AI439" t="n">
-        <v>6.928042396530073</v>
+        <v>6.928042396530076</v>
       </c>
       <c r="AJ439" t="n">
-        <v>-0.133542522415083</v>
+        <v>-0.1335425224150857</v>
       </c>
       <c r="AK439" t="n">
         <v>6.933186989735641</v>
@@ -71890,16 +71890,16 @@
         <v>-0.1386871156206508</v>
       </c>
       <c r="AM439" t="n">
-        <v>-0.1650917115670582</v>
+        <v>-0.1650917115670576</v>
       </c>
       <c r="AN439" t="n">
-        <v>-0.01061494647532512</v>
+        <v>-0.0106149464753251</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.08732871254562202</v>
+        <v>0.08732871254562191</v>
       </c>
       <c r="AP439" t="n">
-        <v>0.1638353991091144</v>
+        <v>0.1638353991090848</v>
       </c>
       <c r="AQ439" t="n">
         <v>56.25</v>
@@ -72043,10 +72043,10 @@
         <v>-0.3599723140764661</v>
       </c>
       <c r="AI440" t="n">
-        <v>6.941461393298106</v>
+        <v>6.941461393298105</v>
       </c>
       <c r="AJ440" t="n">
-        <v>-0.1469615191831153</v>
+        <v>-0.1469615191831144</v>
       </c>
       <c r="AK440" t="n">
         <v>6.925995477801935</v>
@@ -72055,16 +72055,16 @@
         <v>-0.131495603686945</v>
       </c>
       <c r="AM440" t="n">
-        <v>-0.1745447047691478</v>
+        <v>-0.1745447047691483</v>
       </c>
       <c r="AN440" t="n">
-        <v>-0.01108963812755724</v>
+        <v>-0.01108963812755723</v>
       </c>
       <c r="AO440" t="n">
-        <v>0.09935205695041927</v>
+        <v>0.09935205695041804</v>
       </c>
       <c r="AP440" t="n">
-        <v>0.008857437085353572</v>
+        <v>0.008857437085365438</v>
       </c>
       <c r="AQ440" t="n">
         <v>49.72972972972973</v>
@@ -72208,10 +72208,10 @@
         <v>-0.376957691116683</v>
       </c>
       <c r="AI441" t="n">
-        <v>6.933232103976423</v>
+        <v>6.93323210397643</v>
       </c>
       <c r="AJ441" t="n">
-        <v>-0.147232329043562</v>
+        <v>-0.1472323290435682</v>
       </c>
       <c r="AK441" t="n">
         <v>6.938996539173566</v>
@@ -72220,16 +72220,16 @@
         <v>-0.1529967642407044</v>
       </c>
       <c r="AM441" t="n">
-        <v>-0.1853013335308053</v>
+        <v>-0.1853013335308036</v>
       </c>
       <c r="AN441" t="n">
-        <v>-0.01193987645426136</v>
+        <v>-0.01193987645426134</v>
       </c>
       <c r="AO441" t="n">
-        <v>0.1123648810347067</v>
+        <v>0.1123648810347069</v>
       </c>
       <c r="AP441" t="n">
-        <v>0.005706446015462478</v>
+        <v>0.005706446015392532</v>
       </c>
       <c r="AQ441" t="n">
         <v>45.43010752688172</v>
@@ -72373,10 +72373,10 @@
         <v>-0.3749172355506429</v>
       </c>
       <c r="AI442" t="n">
-        <v>6.928429644379658</v>
+        <v>6.928429644379657</v>
       </c>
       <c r="AJ442" t="n">
-        <v>-0.1496296336985061</v>
+        <v>-0.1496296336985043</v>
       </c>
       <c r="AK442" t="n">
         <v>6.93160690101155</v>
@@ -72388,13 +72388,13 @@
         <v>-0.195778453092554</v>
       </c>
       <c r="AN442" t="n">
-        <v>-0.01257308415669775</v>
+        <v>-0.01257308415669778</v>
       </c>
       <c r="AO442" t="n">
-        <v>0.1258578984724115</v>
+        <v>0.125857898472412</v>
       </c>
       <c r="AP442" t="n">
-        <v>-0.02206800494325076</v>
+        <v>-0.02206800494322776</v>
       </c>
       <c r="AQ442" t="n">
         <v>45.72192513368984</v>
@@ -72538,10 +72538,10 @@
         <v>-0.367895966868744</v>
       </c>
       <c r="AI443" t="n">
-        <v>6.925068850639512</v>
+        <v>6.925068850639515</v>
       </c>
       <c r="AJ443" t="n">
-        <v>-0.1455688430101176</v>
+        <v>-0.1455688430101203</v>
       </c>
       <c r="AK443" t="n">
         <v>6.924763510572069</v>
@@ -72550,16 +72550,16 @@
         <v>-0.1452635029426741</v>
       </c>
       <c r="AM443" t="n">
-        <v>-0.2060805417157789</v>
+        <v>-0.2060805417157788</v>
       </c>
       <c r="AN443" t="n">
-        <v>-0.01318646791849928</v>
+        <v>-0.01318646791849926</v>
       </c>
       <c r="AO443" t="n">
-        <v>0.1396251026736647</v>
+        <v>0.1396251026736655</v>
       </c>
       <c r="AP443" t="n">
-        <v>0.02513933444019229</v>
+        <v>0.02513933444016338</v>
       </c>
       <c r="AQ443" t="n">
         <v>49.46808510638298</v>
@@ -72703,10 +72703,10 @@
         <v>-0.3778029353163523</v>
       </c>
       <c r="AI444" t="n">
-        <v>6.900929863197373</v>
+        <v>6.900929863197374</v>
       </c>
       <c r="AJ444" t="n">
-        <v>-0.1347297975845798</v>
+        <v>-0.1347297975845807</v>
       </c>
       <c r="AK444" t="n">
         <v>6.921049732547429</v>
@@ -72715,16 +72715,16 @@
         <v>-0.154849666934636</v>
       </c>
       <c r="AM444" t="n">
-        <v>-0.2151279705591481</v>
+        <v>-0.2151279705591488</v>
       </c>
       <c r="AN444" t="n">
         <v>-0.01327344636859884</v>
       </c>
       <c r="AO444" t="n">
-        <v>0.1518365696223549</v>
+        <v>0.1518365696223548</v>
       </c>
       <c r="AP444" t="n">
-        <v>0.151252963667153</v>
+        <v>0.1512529636671445</v>
       </c>
       <c r="AQ444" t="n">
         <v>50.52910052910053</v>
@@ -72868,10 +72868,10 @@
         <v>-0.389231641388263</v>
       </c>
       <c r="AI445" t="n">
-        <v>6.89521901018146</v>
+        <v>6.895219010181459</v>
       </c>
       <c r="AJ445" t="n">
-        <v>-0.1302191436958644</v>
+        <v>-0.1302191436958635</v>
       </c>
       <c r="AK445" t="n">
         <v>6.89978353884127</v>
@@ -72883,13 +72883,13 @@
         <v>-0.2238560204067715</v>
       </c>
       <c r="AN445" t="n">
-        <v>-0.01278923357027006</v>
+        <v>-0.01278923357027009</v>
       </c>
       <c r="AO445" t="n">
-        <v>0.1644177475946105</v>
+        <v>0.1644177475946104</v>
       </c>
       <c r="AP445" t="n">
-        <v>0.2034852657845942</v>
+        <v>0.2034852657846063</v>
       </c>
       <c r="AQ445" t="n">
         <v>48.1578947368421</v>
@@ -73033,10 +73033,10 @@
         <v>-0.3799051321072451</v>
       </c>
       <c r="AI446" t="n">
-        <v>6.87951223984858</v>
+        <v>6.879512239848579</v>
       </c>
       <c r="AJ446" t="n">
-        <v>-0.1173123611559532</v>
+        <v>-0.1173123611559523</v>
       </c>
       <c r="AK446" t="n">
         <v>6.893260360395011</v>
@@ -73045,16 +73045,16 @@
         <v>-0.1310604817023844</v>
       </c>
       <c r="AM446" t="n">
-        <v>-0.233692768734328</v>
+        <v>-0.233692768734329</v>
       </c>
       <c r="AN446" t="n">
-        <v>-0.01245257184765156</v>
+        <v>-0.01245257184765153</v>
       </c>
       <c r="AO446" t="n">
-        <v>0.1791295233320875</v>
+        <v>0.179129523332087</v>
       </c>
       <c r="AP446" t="n">
-        <v>0.3538789872686283</v>
+        <v>0.35387898726864</v>
       </c>
       <c r="AQ446" t="n">
         <v>51.57068062827225</v>
@@ -73198,10 +73198,10 @@
         <v>-0.3756598353052443</v>
       </c>
       <c r="AI447" t="n">
-        <v>6.882426232260437</v>
+        <v>6.882426232260446</v>
       </c>
       <c r="AJ447" t="n">
-        <v>-0.1132263840853884</v>
+        <v>-0.1132263840853973</v>
       </c>
       <c r="AK447" t="n">
         <v>6.880758546638964</v>
@@ -73210,16 +73210,16 @@
         <v>-0.1115586984639148</v>
       </c>
       <c r="AM447" t="n">
-        <v>-0.2433281856134888</v>
+        <v>-0.2433281856134891</v>
       </c>
       <c r="AN447" t="n">
-        <v>-0.01202813951384067</v>
+        <v>-0.01202813951384066</v>
       </c>
       <c r="AO447" t="n">
-        <v>0.1944608722019407</v>
+        <v>0.1944608722019401</v>
       </c>
       <c r="AP447" t="n">
-        <v>0.4007188594352498</v>
+        <v>0.400718859435147</v>
       </c>
       <c r="AQ447" t="n">
         <v>53.125</v>
@@ -73375,16 +73375,16 @@
         <v>-0.1090386648503241</v>
       </c>
       <c r="AM448" t="n">
-        <v>-0.25202644278106</v>
+        <v>-0.2520264427810588</v>
       </c>
       <c r="AN448" t="n">
-        <v>-0.01246671652825434</v>
+        <v>-0.01246671652825437</v>
       </c>
       <c r="AO448" t="n">
-        <v>0.2101991144027905</v>
+        <v>0.2101991144027906</v>
       </c>
       <c r="AP448" t="n">
-        <v>0.9721302198060142</v>
+        <v>0.9721302198060143</v>
       </c>
       <c r="AQ448" t="n">
         <v>66.06217616580309</v>
@@ -73528,10 +73528,10 @@
         <v>-0.3786112675178819</v>
       </c>
       <c r="AI449" t="n">
-        <v>6.841963898035326</v>
+        <v>6.841963898035317</v>
       </c>
       <c r="AJ449" t="n">
-        <v>-0.07646382937077512</v>
+        <v>-0.07646382937076623</v>
       </c>
       <c r="AK449" t="n">
         <v>6.844785316397215</v>
@@ -73540,16 +73540,16 @@
         <v>-0.07928524773266421</v>
       </c>
       <c r="AM449" t="n">
-        <v>-0.2592973891940566</v>
+        <v>-0.2592973891940562</v>
       </c>
       <c r="AN449" t="n">
-        <v>-0.01305068899435077</v>
+        <v>-0.01305068899435097</v>
       </c>
       <c r="AO449" t="n">
-        <v>0.2277185089957524</v>
+        <v>0.2277185089957531</v>
       </c>
       <c r="AP449" t="n">
-        <v>0.8254556631440507</v>
+        <v>0.8254556631441549</v>
       </c>
       <c r="AQ449" t="n">
         <v>59.27835051546391</v>
@@ -73693,28 +73693,28 @@
         <v>-0.3772897849047219</v>
       </c>
       <c r="AI450" t="n">
-        <v>6.845644916883079</v>
+        <v>6.845644916883085</v>
       </c>
       <c r="AJ450" t="n">
-        <v>-0.08014484821852808</v>
+        <v>-0.08014484821853429</v>
       </c>
       <c r="AK450" t="n">
-        <v>6.849407886968132</v>
+        <v>6.849407886968131</v>
       </c>
       <c r="AL450" t="n">
-        <v>-0.08390781830358129</v>
+        <v>-0.08390781830358041</v>
       </c>
       <c r="AM450" t="n">
-        <v>-0.2668003223256254</v>
+        <v>-0.2668003223256257</v>
       </c>
       <c r="AN450" t="n">
-        <v>-0.0136798902005495</v>
+        <v>-0.01367989020054944</v>
       </c>
       <c r="AO450" t="n">
-        <v>0.2456601220977566</v>
+        <v>0.2456601220977563</v>
       </c>
       <c r="AP450" t="n">
-        <v>0.7788054311405997</v>
+        <v>0.7788054311405267</v>
       </c>
       <c r="AQ450" t="n">
         <v>58.97435897435898</v>
@@ -73858,10 +73858,10 @@
         <v>-0.363071453483653</v>
       </c>
       <c r="AI451" t="n">
-        <v>6.842084108625038</v>
+        <v>6.842084108625032</v>
       </c>
       <c r="AJ451" t="n">
-        <v>-0.06958407047806503</v>
+        <v>-0.0695840704780597</v>
       </c>
       <c r="AK451" t="n">
         <v>6.852702018840203</v>
@@ -73870,16 +73870,16 @@
         <v>-0.08020198069323037</v>
       </c>
       <c r="AM451" t="n">
-        <v>-0.273543646731814</v>
+        <v>-0.2735436467318143</v>
       </c>
       <c r="AN451" t="n">
-        <v>-0.01403412282467991</v>
+        <v>-0.01403412282467997</v>
       </c>
       <c r="AO451" t="n">
-        <v>0.261983510217226</v>
+        <v>0.2619835102172253</v>
       </c>
       <c r="AP451" t="n">
-        <v>0.8993437222325723</v>
+        <v>0.8993437222326349</v>
       </c>
       <c r="AQ451" t="n">
         <v>64.28571428571428</v>
@@ -74023,10 +74023,10 @@
         <v>-0.3531693686636164</v>
       </c>
       <c r="AI452" t="n">
-        <v>6.863831060847785</v>
+        <v>6.863831060847773</v>
       </c>
       <c r="AJ452" t="n">
-        <v>-0.09133102270081217</v>
+        <v>-0.09133102270080062</v>
       </c>
       <c r="AK452" t="n">
         <v>6.850973969550408</v>
@@ -74035,16 +74035,16 @@
         <v>-0.07847393140343506</v>
       </c>
       <c r="AM452" t="n">
-        <v>-0.2787367835501617</v>
+        <v>-0.2787367835501612</v>
       </c>
       <c r="AN452" t="n">
-        <v>-0.01406387644726588</v>
+        <v>-0.01406387644726603</v>
       </c>
       <c r="AO452" t="n">
-        <v>0.2758112468611976</v>
+        <v>0.2758112468611987</v>
       </c>
       <c r="AP452" t="n">
-        <v>0.6401069829083486</v>
+        <v>0.6401069829084844</v>
       </c>
       <c r="AQ452" t="n">
         <v>63.19796954314721</v>
@@ -74188,10 +74188,10 @@
         <v>-0.3365426739870401</v>
       </c>
       <c r="AI453" t="n">
-        <v>6.853037915615573</v>
+        <v>6.853037915615571</v>
       </c>
       <c r="AJ453" t="n">
-        <v>-0.07753809490634467</v>
+        <v>-0.07753809490634289</v>
       </c>
       <c r="AK453" t="n">
         <v>6.873527983489108</v>
@@ -74203,13 +74203,13 @@
         <v>-0.2827572515625069</v>
       </c>
       <c r="AN453" t="n">
-        <v>-0.01379017718565697</v>
+        <v>-0.013790177185657</v>
       </c>
       <c r="AO453" t="n">
-        <v>0.2854425463774817</v>
+        <v>0.285442546377481</v>
       </c>
       <c r="AP453" t="n">
-        <v>0.7999851756792175</v>
+        <v>0.7999851756792368</v>
       </c>
       <c r="AQ453" t="n">
         <v>69.44444444444443</v>
@@ -74365,7 +74365,7 @@
         <v>-0.09446478821400195</v>
       </c>
       <c r="AM454" t="n">
-        <v>-0.2865252693972545</v>
+        <v>-0.2865252693972544</v>
       </c>
       <c r="AN454" t="n">
         <v>-0.01327380582108439</v>
@@ -74374,7 +74374,7 @@
         <v>0.2945802259112972</v>
       </c>
       <c r="AP454" t="n">
-        <v>0.5996233412815121</v>
+        <v>0.5996233412815115</v>
       </c>
       <c r="AQ454" t="n">
         <v>62.56281407035176</v>
@@ -74518,10 +74518,10 @@
         <v>-0.3556204057104786</v>
       </c>
       <c r="AI455" t="n">
-        <v>6.860047631936787</v>
+        <v>6.860047631936786</v>
       </c>
       <c r="AJ455" t="n">
-        <v>-0.1030476624543653</v>
+        <v>-0.1030476624543644</v>
       </c>
       <c r="AK455" t="n">
         <v>6.865985861260643</v>
@@ -74530,16 +74530,16 @@
         <v>-0.1089858917782207</v>
       </c>
       <c r="AM455" t="n">
-        <v>-0.2905223093479492</v>
+        <v>-0.290522309347949</v>
       </c>
       <c r="AN455" t="n">
-        <v>-0.01240158194086378</v>
+        <v>-0.01240158194086383</v>
       </c>
       <c r="AO455" t="n">
-        <v>0.3024992257449914</v>
+        <v>0.3024992257449916</v>
       </c>
       <c r="AP455" t="n">
-        <v>0.4941009333209234</v>
+        <v>0.4941009333209337</v>
       </c>
       <c r="AQ455" t="n">
         <v>58.75</v>
@@ -74683,10 +74683,10 @@
         <v>-0.3353395133383152</v>
       </c>
       <c r="AI456" t="n">
-        <v>6.801980414635016</v>
+        <v>6.801980414635013</v>
       </c>
       <c r="AJ456" t="n">
-        <v>-0.04478065038330659</v>
+        <v>-0.04478065038330392</v>
       </c>
       <c r="AK456" t="n">
         <v>6.863576603094304</v>
@@ -74695,16 +74695,16 @@
         <v>-0.1063768388425945</v>
       </c>
       <c r="AM456" t="n">
-        <v>-0.2950697019949104</v>
+        <v>-0.2950697019949103</v>
       </c>
       <c r="AN456" t="n">
-        <v>-0.01161053315968381</v>
+        <v>-0.0116105331596838</v>
       </c>
       <c r="AO456" t="n">
-        <v>0.3113800696686918</v>
+        <v>0.3113800696686924</v>
       </c>
       <c r="AP456" t="n">
-        <v>1.179534937195594</v>
+        <v>1.179534937195622</v>
       </c>
       <c r="AQ456" t="n">
         <v>80.09950248756219</v>
@@ -74848,10 +74848,10 @@
         <v>-0.3329500208577869</v>
       </c>
       <c r="AI457" t="n">
-        <v>6.789283666813422</v>
+        <v>6.789283666813423</v>
       </c>
       <c r="AJ457" t="n">
-        <v>-0.03208390256171256</v>
+        <v>-0.03208390256171434</v>
       </c>
       <c r="AK457" t="n">
         <v>6.809671190627447</v>
@@ -74860,16 +74860,16 @@
         <v>-0.05247142637573798</v>
       </c>
       <c r="AM457" t="n">
-        <v>-0.2987092362344108</v>
+        <v>-0.2987092362344105</v>
       </c>
       <c r="AN457" t="n">
-        <v>-0.01030385953714808</v>
+        <v>-0.01030385953714813</v>
       </c>
       <c r="AO457" t="n">
         <v>0.3212764901162176</v>
       </c>
       <c r="AP457" t="n">
-        <v>1.321204242911509</v>
+        <v>1.321204242911485</v>
       </c>
       <c r="AQ457" t="n">
         <v>82.92079207920793</v>
@@ -75013,10 +75013,10 @@
         <v>-0.3235182598404904</v>
       </c>
       <c r="AI458" t="n">
-        <v>6.789252537988933</v>
+        <v>6.789252537988938</v>
       </c>
       <c r="AJ458" t="n">
-        <v>-0.0206525509589035</v>
+        <v>-0.02065255095890883</v>
       </c>
       <c r="AK458" t="n">
         <v>6.802840448144932</v>
@@ -75025,16 +75025,16 @@
         <v>-0.03424046111490231</v>
       </c>
       <c r="AM458" t="n">
-        <v>-0.3027504956929284</v>
+        <v>-0.3027504956929287</v>
       </c>
       <c r="AN458" t="n">
-        <v>-0.008812786025409641</v>
+        <v>-0.00881278602540958</v>
       </c>
       <c r="AO458" t="n">
-        <v>0.3322271170679635</v>
+        <v>0.332227117067963</v>
       </c>
       <c r="AP458" t="n">
-        <v>1.445529712541155</v>
+        <v>1.445529712541089</v>
       </c>
       <c r="AQ458" t="n">
         <v>83.74384236453203</v>
@@ -75178,10 +75178,10 @@
         <v>-0.3307736515702473</v>
       </c>
       <c r="AI459" t="n">
-        <v>6.774001672255932</v>
+        <v>6.774001672255927</v>
       </c>
       <c r="AJ459" t="n">
-        <v>-0.005401685225902675</v>
+        <v>-0.005401685225897346</v>
       </c>
       <c r="AK459" t="n">
         <v>6.800260207803535</v>
@@ -75190,16 +75190,16 @@
         <v>-0.03166022077350572</v>
       </c>
       <c r="AM459" t="n">
-        <v>-0.3068099364477367</v>
+        <v>-0.3068099364477369</v>
       </c>
       <c r="AN459" t="n">
-        <v>-0.007070247176567688</v>
+        <v>-0.007070247176567734</v>
       </c>
       <c r="AO459" t="n">
-        <v>0.3427146952658534</v>
+        <v>0.3427146952658529</v>
       </c>
       <c r="AP459" t="n">
-        <v>1.611345626774689</v>
+        <v>1.611345626774747</v>
       </c>
       <c r="AQ459" t="n">
         <v>84.06862745098039</v>
@@ -75343,10 +75343,10 @@
         <v>-0.3393222260601885</v>
       </c>
       <c r="AI460" t="n">
-        <v>6.802628307046303</v>
+        <v>6.802628307046305</v>
       </c>
       <c r="AJ460" t="n">
-        <v>-0.02812841385782594</v>
+        <v>-0.0281284138578286</v>
       </c>
       <c r="AK460" t="n">
         <v>6.781970485204615</v>
@@ -75355,16 +75355,16 @@
         <v>-0.007470592016137978</v>
       </c>
       <c r="AM460" t="n">
-        <v>-0.3121566752204101</v>
+        <v>-0.3121566752204096</v>
       </c>
       <c r="AN460" t="n">
-        <v>-0.005102880740085154</v>
+        <v>-0.005102880740085192</v>
       </c>
       <c r="AO460" t="n">
-        <v>0.3560731605465757</v>
+        <v>0.3560731605465752</v>
       </c>
       <c r="AP460" t="n">
-        <v>1.33466179751765</v>
+        <v>1.334661797517615</v>
       </c>
       <c r="AQ460" t="n">
         <v>80.73170731707317</v>
@@ -75508,28 +75508,28 @@
         <v>-0.3327092202568753</v>
       </c>
       <c r="AI461" t="n">
-        <v>6.815944895083632</v>
+        <v>6.815944895083629</v>
       </c>
       <c r="AJ461" t="n">
-        <v>-0.02594493323060476</v>
+        <v>-0.0259449332306021</v>
       </c>
       <c r="AK461" t="n">
-        <v>6.809638458820508</v>
+        <v>6.809638458820509</v>
       </c>
       <c r="AL461" t="n">
-        <v>-0.01963849696748099</v>
+        <v>-0.01963849696748188</v>
       </c>
       <c r="AM461" t="n">
-        <v>-0.3181413841564619</v>
+        <v>-0.3181413841564625</v>
       </c>
       <c r="AN461" t="n">
-        <v>-0.003317316385138562</v>
+        <v>-0.003317316385138602</v>
       </c>
       <c r="AO461" t="n">
-        <v>0.3690689225934922</v>
+        <v>0.3690689225934927</v>
       </c>
       <c r="AP461" t="n">
-        <v>1.35094094440808</v>
+        <v>1.350940944408107</v>
       </c>
       <c r="AQ461" t="n">
         <v>82.52427184466021</v>
@@ -75673,10 +75673,10 @@
         <v>-0.3426415923441448</v>
       </c>
       <c r="AI462" t="n">
-        <v>6.821941449304753</v>
+        <v>6.821941449304759</v>
       </c>
       <c r="AJ462" t="n">
-        <v>-0.03194148745172587</v>
+        <v>-0.0319414874517312</v>
       </c>
       <c r="AK462" t="n">
         <v>6.819973703544699</v>
@@ -75685,16 +75685,16 @@
         <v>-0.02997374169167166</v>
       </c>
       <c r="AM462" t="n">
-        <v>-0.3244228225822198</v>
+        <v>-0.3244228225822193</v>
       </c>
       <c r="AN462" t="n">
-        <v>-0.001700148658338742</v>
+        <v>-0.001700148658338674</v>
       </c>
       <c r="AO462" t="n">
         <v>0.3824275372863725</v>
       </c>
       <c r="AP462" t="n">
-        <v>1.272497711914839</v>
+        <v>1.272497711914774</v>
       </c>
       <c r="AQ462" t="n">
         <v>79.22705314009661</v>
@@ -75838,10 +75838,10 @@
         <v>-0.3364383256526304</v>
       </c>
       <c r="AI463" t="n">
-        <v>6.826413262727749</v>
+        <v>6.826413262727742</v>
       </c>
       <c r="AJ463" t="n">
-        <v>-0.03641330087472205</v>
+        <v>-0.03641330087471495</v>
       </c>
       <c r="AK463" t="n">
         <v>6.822087900644207</v>
@@ -75850,16 +75850,16 @@
         <v>-0.03208793879117966</v>
       </c>
       <c r="AM463" t="n">
-        <v>-0.3308797299382495</v>
+        <v>-0.3308797299382499</v>
       </c>
       <c r="AN463" t="n">
-        <v>-7.481797733213274e-05</v>
+        <v>-7.481797733216444e-05</v>
       </c>
       <c r="AO463" t="n">
-        <v>0.396078871041881</v>
+        <v>0.3960788710418811</v>
       </c>
       <c r="AP463" t="n">
-        <v>1.212872589244813</v>
+        <v>1.212872589244893</v>
       </c>
       <c r="AQ463" t="n">
         <v>79.80769230769231</v>
@@ -76003,10 +76003,10 @@
         <v>-0.3263518796958209</v>
       </c>
       <c r="AI464" t="n">
-        <v>6.81265664767955</v>
+        <v>6.812656647679548</v>
       </c>
       <c r="AJ464" t="n">
-        <v>-0.01465678882334931</v>
+        <v>-0.01465678882334664</v>
       </c>
       <c r="AK464" t="n">
         <v>6.823881638371397</v>
@@ -76015,16 +76015,16 @@
         <v>-0.02588177951519555</v>
       </c>
       <c r="AM464" t="n">
-        <v>-0.3363418922753058</v>
+        <v>-0.3363418922753055</v>
       </c>
       <c r="AN464" t="n">
-        <v>0.001379920606120097</v>
+        <v>0.001379920606120022</v>
       </c>
       <c r="AO464" t="n">
-        <v>0.4081029523904167</v>
+        <v>0.4081029523904164</v>
       </c>
       <c r="AP464" t="n">
-        <v>1.456252967655684</v>
+        <v>1.45625296765571</v>
       </c>
       <c r="AQ464" t="n">
         <v>83.97129186602871</v>
@@ -76168,10 +76168,10 @@
         <v>-0.3266602018416904</v>
       </c>
       <c r="AI465" t="n">
-        <v>6.802797817425505</v>
+        <v>6.802797817425507</v>
       </c>
       <c r="AJ465" t="n">
-        <v>-0.009197735028044107</v>
+        <v>-0.009197735028045884</v>
       </c>
       <c r="AK465" t="n">
         <v>6.808320681191073</v>
@@ -76180,16 +76180,16 @@
         <v>-0.01472059879361254</v>
       </c>
       <c r="AM465" t="n">
-        <v>-0.3410659803634682</v>
+        <v>-0.3410659803634685</v>
       </c>
       <c r="AN465" t="n">
         <v>0.002855151959729019</v>
       </c>
       <c r="AO465" t="n">
-        <v>0.4198133218741357</v>
+        <v>0.4198133218741356</v>
       </c>
       <c r="AP465" t="n">
-        <v>1.507992928081032</v>
+        <v>1.507992928081006</v>
       </c>
       <c r="AQ465" t="n">
         <v>84.04761904761904</v>
@@ -76339,22 +76339,22 @@
         <v>-0.002828874871806164</v>
       </c>
       <c r="AK466" t="n">
-        <v>6.795980661778266</v>
+        <v>6.795980661778267</v>
       </c>
       <c r="AL466" t="n">
-        <v>-0.002380579380805159</v>
+        <v>-0.002380579380806047</v>
       </c>
       <c r="AM466" t="n">
-        <v>-0.3461577281601509</v>
+        <v>-0.3461577281601511</v>
       </c>
       <c r="AN466" t="n">
-        <v>0.00428288788357468</v>
+        <v>0.004282887883574671</v>
       </c>
       <c r="AO466" t="n">
-        <v>0.4328049372030969</v>
+        <v>0.4328049372030962</v>
       </c>
       <c r="AP466" t="n">
-        <v>1.568971829556587</v>
+        <v>1.568971829556582</v>
       </c>
       <c r="AQ466" t="n">
         <v>85.07109004739337</v>
@@ -76498,10 +76498,10 @@
         <v>-0.3262622212351571</v>
       </c>
       <c r="AI467" t="n">
-        <v>6.800189882196236</v>
+        <v>6.800189882196235</v>
       </c>
       <c r="AJ467" t="n">
-        <v>-0.005989938653755189</v>
+        <v>-0.005989938653754301</v>
       </c>
       <c r="AK467" t="n">
         <v>6.78726841810145</v>
@@ -76510,16 +76510,16 @@
         <v>0.00693152544103004</v>
       </c>
       <c r="AM467" t="n">
-        <v>-0.3502903933401418</v>
+        <v>-0.3502903933401412</v>
       </c>
       <c r="AN467" t="n">
-        <v>0.005405808652032067</v>
+        <v>0.005405808652032051</v>
       </c>
       <c r="AO467" t="n">
-        <v>0.4450018361960534</v>
+        <v>0.4450018361960529</v>
       </c>
       <c r="AP467" t="n">
-        <v>1.520317609051729</v>
+        <v>1.520317609051734</v>
       </c>
       <c r="AQ467" t="n">
         <v>83.9622641509434</v>
@@ -76663,10 +76663,10 @@
         <v>-0.3288036676654578</v>
       </c>
       <c r="AI468" t="n">
-        <v>6.797972083642554</v>
+        <v>6.79797208364255</v>
       </c>
       <c r="AJ468" t="n">
-        <v>-0.009372115686010929</v>
+        <v>-0.009372115686007376</v>
       </c>
       <c r="AK468" t="n">
         <v>6.791305278184372</v>
@@ -76675,16 +76675,16 @@
         <v>-0.002705310227828939</v>
       </c>
       <c r="AM468" t="n">
-        <v>-0.3548656112706071</v>
+        <v>-0.3548656112706069</v>
       </c>
       <c r="AN468" t="n">
-        <v>0.006091291211178139</v>
+        <v>0.006091291211178074</v>
       </c>
       <c r="AO468" t="n">
-        <v>0.4593697101544705</v>
+        <v>0.4593697101544711</v>
       </c>
       <c r="AP468" t="n">
-        <v>1.470209466853828</v>
+        <v>1.470209466853863</v>
       </c>
       <c r="AQ468" t="n">
         <v>82.86384976525821</v>
@@ -76828,10 +76828,10 @@
         <v>-0.3403504824304679</v>
       </c>
       <c r="AI469" t="n">
-        <v>6.800452644405178</v>
+        <v>6.800452644405181</v>
       </c>
       <c r="AJ469" t="n">
-        <v>-0.01185267644863508</v>
+        <v>-0.01185267644863774</v>
       </c>
       <c r="AK469" t="n">
         <v>6.789098969069376</v>
@@ -76846,10 +76846,10 @@
         <v>0.006876393748008469</v>
       </c>
       <c r="AO469" t="n">
-        <v>0.4721687943484545</v>
+        <v>0.4721687943484544</v>
       </c>
       <c r="AP469" t="n">
-        <v>1.431322929350439</v>
+        <v>1.431322929350403</v>
       </c>
       <c r="AQ469" t="n">
         <v>79.67289719626169</v>
@@ -76993,10 +76993,10 @@
         <v>-0.3262206357021356</v>
       </c>
       <c r="AI470" t="n">
-        <v>6.778720347685814</v>
+        <v>6.778720347685821</v>
       </c>
       <c r="AJ470" t="n">
-        <v>0.01707986135959594</v>
+        <v>0.01707986135958883</v>
       </c>
       <c r="AK470" t="n">
         <v>6.790465135395929</v>
@@ -77005,16 +77005,16 @@
         <v>0.005335073649480826</v>
       </c>
       <c r="AM470" t="n">
-        <v>-0.3625273381377933</v>
+        <v>-0.3625273381377937</v>
       </c>
       <c r="AN470" t="n">
-        <v>0.007343464385960585</v>
+        <v>0.007343464385960674</v>
       </c>
       <c r="AO470" t="n">
-        <v>0.4863203622043382</v>
+        <v>0.4863203622043377</v>
       </c>
       <c r="AP470" t="n">
-        <v>1.746913751099204</v>
+        <v>1.746913751099119</v>
       </c>
       <c r="AQ470" t="n">
         <v>84.65116279069767</v>
@@ -77158,10 +77158,10 @@
         <v>-0.3148699432795414</v>
       </c>
       <c r="AI471" t="n">
-        <v>6.769755998762545</v>
+        <v>6.769755998762547</v>
       </c>
       <c r="AJ471" t="n">
-        <v>0.02364381202847099</v>
+        <v>0.02364381202846833</v>
       </c>
       <c r="AK471" t="n">
         <v>6.767889899932765</v>
@@ -77170,16 +77170,16 @@
         <v>0.02550991085825061</v>
       </c>
       <c r="AM471" t="n">
-        <v>-0.3660007866474813</v>
+        <v>-0.3660007866474812</v>
       </c>
       <c r="AN471" t="n">
-        <v>0.008260137822954145</v>
+        <v>0.00826013782295415</v>
       </c>
       <c r="AO471" t="n">
-        <v>0.4997690914082401</v>
+        <v>0.4997690914082398</v>
       </c>
       <c r="AP471" t="n">
-        <v>1.803867771120674</v>
+        <v>1.803867771120641</v>
       </c>
       <c r="AQ471" t="n">
         <v>85.41666666666667</v>
@@ -77323,10 +77323,10 @@
         <v>-0.3079851300578911</v>
       </c>
       <c r="AI472" t="n">
-        <v>6.789177604754244</v>
+        <v>6.789177604754239</v>
       </c>
       <c r="AJ472" t="n">
-        <v>0.01332216636391959</v>
+        <v>0.01332216636392491</v>
       </c>
       <c r="AK472" t="n">
         <v>6.759766754404358</v>
@@ -77335,16 +77335,16 @@
         <v>0.04273301671380558</v>
       </c>
       <c r="AM472" t="n">
-        <v>-0.3700034659576351</v>
+        <v>-0.3700034659576358</v>
       </c>
       <c r="AN472" t="n">
-        <v>0.009871715534546958</v>
+        <v>0.00987171553454691</v>
       </c>
       <c r="AO472" t="n">
-        <v>0.5120623436103324</v>
+        <v>0.5120623436103316</v>
       </c>
       <c r="AP472" t="n">
-        <v>1.671670611528598</v>
+        <v>1.671670611528654</v>
       </c>
       <c r="AQ472" t="n">
         <v>85.48387096774194</v>
@@ -77488,10 +77488,10 @@
         <v>-0.3161537021676821</v>
       </c>
       <c r="AI473" t="n">
-        <v>6.774331376960425</v>
+        <v>6.774331376960423</v>
       </c>
       <c r="AJ473" t="n">
-        <v>0.01776857573732915</v>
+        <v>0.01776857573733093</v>
       </c>
       <c r="AK473" t="n">
         <v>6.777856240868369</v>
@@ -77500,16 +77500,16 @@
         <v>0.01424371182938522</v>
       </c>
       <c r="AM473" t="n">
-        <v>-0.3750442390024147</v>
+        <v>-0.3750442390024145</v>
       </c>
       <c r="AN473" t="n">
-        <v>0.01196068662558781</v>
+        <v>0.01196068662558775</v>
       </c>
       <c r="AO473" t="n">
-        <v>0.5238651846176463</v>
+        <v>0.5238651846176465</v>
       </c>
       <c r="AP473" t="n">
-        <v>1.706456035136504</v>
+        <v>1.70645603513652</v>
       </c>
       <c r="AQ473" t="n">
         <v>84.63302752293578</v>
@@ -77665,16 +77665,16 @@
         <v>0.01490118062612744</v>
       </c>
       <c r="AM474" t="n">
-        <v>-0.3816350905604307</v>
+        <v>-0.3816350905604304</v>
       </c>
       <c r="AN474" t="n">
-        <v>0.01460798460929556</v>
+        <v>0.01460798460929558</v>
       </c>
       <c r="AO474" t="n">
-        <v>0.5379583104732891</v>
+        <v>0.537958310473289</v>
       </c>
       <c r="AP474" t="n">
-        <v>1.651824891106279</v>
+        <v>1.651824891106274</v>
       </c>
       <c r="AQ474" t="n">
         <v>85.15981735159818</v>
@@ -77818,10 +77818,10 @@
         <v>-0.3137378908481967</v>
       </c>
       <c r="AI475" t="n">
-        <v>6.789815280543245</v>
+        <v>6.789815280543246</v>
       </c>
       <c r="AJ475" t="n">
-        <v>-0.01031527291385093</v>
+        <v>-0.01031527291385181</v>
       </c>
       <c r="AK475" t="n">
         <v>6.744939020214936</v>
@@ -77830,16 +77830,16 @@
         <v>0.03456098741445857</v>
       </c>
       <c r="AM475" t="n">
-        <v>-0.3872393091179339</v>
+        <v>-0.3872393091179336</v>
       </c>
       <c r="AN475" t="n">
-        <v>0.01685992867552231</v>
+        <v>0.01685992867552227</v>
       </c>
       <c r="AO475" t="n">
-        <v>0.5511317941481415</v>
+        <v>0.5511317941481411</v>
       </c>
       <c r="AP475" t="n">
-        <v>1.367727610243447</v>
+        <v>1.367727610243434</v>
       </c>
       <c r="AQ475" t="n">
         <v>82.95454545454545</v>
@@ -77983,10 +77983,10 @@
         <v>-0.3330204484485053</v>
       </c>
       <c r="AI476" t="n">
-        <v>6.801295181477309</v>
+        <v>6.801295181477315</v>
       </c>
       <c r="AJ476" t="n">
-        <v>-0.0312952005507956</v>
+        <v>-0.03129520055080093</v>
       </c>
       <c r="AK476" t="n">
         <v>6.772636231606738</v>
@@ -77995,16 +77995,16 @@
         <v>-0.002636250680223995</v>
       </c>
       <c r="AM476" t="n">
-        <v>-0.3930200198603389</v>
+        <v>-0.393020019860339</v>
       </c>
       <c r="AN476" t="n">
-        <v>0.01873686412955481</v>
+        <v>0.01873686412955489</v>
       </c>
       <c r="AO476" t="n">
-        <v>0.5644439393662187</v>
+        <v>0.5644439393662184</v>
       </c>
       <c r="AP476" t="n">
-        <v>1.126848917540677</v>
+        <v>1.126848917540616</v>
       </c>
       <c r="AQ476" t="n">
         <v>77.60180995475113</v>
@@ -78148,10 +78148,10 @@
         <v>-0.3438666362584355</v>
       </c>
       <c r="AI477" t="n">
-        <v>6.791632066062364</v>
+        <v>6.791632066062363</v>
       </c>
       <c r="AJ477" t="n">
-        <v>-0.02343214540806748</v>
+        <v>-0.0234321454080666</v>
       </c>
       <c r="AK477" t="n">
         <v>6.788619247652995</v>
@@ -78160,16 +78160,16 @@
         <v>-0.02041932699869786</v>
       </c>
       <c r="AM477" t="n">
-        <v>-0.3966294116439323</v>
+        <v>-0.3966294116439325</v>
       </c>
       <c r="AN477" t="n">
         <v>0.01929745523377641</v>
       </c>
       <c r="AO477" t="n">
-        <v>0.5769744719733717</v>
+        <v>0.576974471973372</v>
       </c>
       <c r="AP477" t="n">
-        <v>1.208130895477032</v>
+        <v>1.20813089547704</v>
       </c>
       <c r="AQ477" t="n">
         <v>75.22522522522523</v>
@@ -78313,10 +78313,10 @@
         <v>-0.3477358498632128</v>
       </c>
       <c r="AI478" t="n">
-        <v>6.779898505875918</v>
+        <v>6.779898505875916</v>
       </c>
       <c r="AJ478" t="n">
-        <v>-0.00739846772894559</v>
+        <v>-0.007398467728943814</v>
       </c>
       <c r="AK478" t="n">
         <v>6.776305653888958</v>
@@ -78325,16 +78325,16 @@
         <v>-0.003805615741985235</v>
       </c>
       <c r="AM478" t="n">
-        <v>-0.3980313152890724</v>
+        <v>-0.3980313152890726</v>
       </c>
       <c r="AN478" t="n">
-        <v>0.0193312470422838</v>
+        <v>0.01933124704228378</v>
       </c>
       <c r="AO478" t="n">
-        <v>0.5877384296086161</v>
+        <v>0.5877384296086169</v>
       </c>
       <c r="AP478" t="n">
-        <v>1.378393366854553</v>
+        <v>1.37839336685457</v>
       </c>
       <c r="AQ478" t="n">
         <v>76.68161434977578</v>
@@ -78478,10 +78478,10 @@
         <v>-0.3456027036349925</v>
       </c>
       <c r="AI479" t="n">
-        <v>6.771360892616116</v>
+        <v>6.771360892616113</v>
       </c>
       <c r="AJ479" t="n">
-        <v>0.001139145530856922</v>
+        <v>0.001139145530859587</v>
       </c>
       <c r="AK479" t="n">
         <v>6.76492936370744</v>
@@ -78490,16 +78490,16 @@
         <v>0.007570674439532965</v>
       </c>
       <c r="AM479" t="n">
-        <v>-0.3979537985659302</v>
+        <v>-0.3979537985659305</v>
       </c>
       <c r="AN479" t="n">
-        <v>0.01835844536093246</v>
+        <v>0.0183584453609324</v>
       </c>
       <c r="AO479" t="n">
-        <v>0.6001791687136286</v>
+        <v>0.6001791687136281</v>
       </c>
       <c r="AP479" t="n">
-        <v>1.463297950386995</v>
+        <v>1.46329795038702</v>
       </c>
       <c r="AQ479" t="n">
         <v>77.67857142857142</v>
@@ -78643,10 +78643,10 @@
         <v>-0.3271701475293147</v>
       </c>
       <c r="AI480" t="n">
-        <v>6.751667781721842</v>
+        <v>6.751667781721844</v>
       </c>
       <c r="AJ480" t="n">
-        <v>0.02083225642513042</v>
+        <v>0.02083225642512865</v>
       </c>
       <c r="AK480" t="n">
         <v>6.753855191419989</v>
@@ -78655,16 +78655,16 @@
         <v>0.01864484672698374</v>
       </c>
       <c r="AM480" t="n">
-        <v>-0.3975762425746347</v>
+        <v>-0.3975762425746344</v>
       </c>
       <c r="AN480" t="n">
-        <v>0.01731206726614282</v>
+        <v>0.01731206726614276</v>
       </c>
       <c r="AO480" t="n">
-        <v>0.6129676701055397</v>
+        <v>0.6129676701055393</v>
       </c>
       <c r="AP480" t="n">
-        <v>1.668293556056633</v>
+        <v>1.668293556056609</v>
       </c>
       <c r="AQ480" t="n">
         <v>83.11111111111111</v>
@@ -78808,10 +78808,10 @@
         <v>-0.3380039445079355</v>
       </c>
       <c r="AI481" t="n">
-        <v>6.72973866986929</v>
+        <v>6.729738669869288</v>
       </c>
       <c r="AJ481" t="n">
-        <v>0.0358615345984834</v>
+        <v>0.03586153459848518</v>
       </c>
       <c r="AK481" t="n">
         <v>6.736226026398153</v>
@@ -78820,16 +78820,16 @@
         <v>0.02937417806962017</v>
       </c>
       <c r="AM481" t="n">
-        <v>-0.3964908591695858</v>
+        <v>-0.3964908591695859</v>
       </c>
       <c r="AN481" t="n">
-        <v>0.01740130648959375</v>
+        <v>0.01740130648959376</v>
       </c>
       <c r="AO481" t="n">
-        <v>0.6198907013195265</v>
+        <v>0.6198907013195262</v>
       </c>
       <c r="AP481" t="n">
-        <v>1.817336727992009</v>
+        <v>1.817336727992024</v>
       </c>
       <c r="AQ481" t="n">
         <v>80.53097345132743</v>
@@ -78973,10 +78973,10 @@
         <v>-0.2945538086312354</v>
       </c>
       <c r="AI482" t="n">
-        <v>6.713320364291505</v>
+        <v>6.713320364291503</v>
       </c>
       <c r="AJ482" t="n">
-        <v>0.05917967385546774</v>
+        <v>0.05917967385546952</v>
       </c>
       <c r="AK482" t="n">
         <v>6.717723214958548</v>
@@ -78985,16 +78985,16 @@
         <v>0.05477682318842447</v>
       </c>
       <c r="AM482" t="n">
-        <v>-0.3947605344816719</v>
+        <v>-0.394760534481672</v>
       </c>
       <c r="AN482" t="n">
-        <v>0.01742962324324019</v>
+        <v>0.01742962324324016</v>
       </c>
       <c r="AO482" t="n">
-        <v>0.6272835381163618</v>
+        <v>0.6272835381163622</v>
       </c>
       <c r="AP482" t="n">
-        <v>2.050548117521357</v>
+        <v>2.050548117521371</v>
       </c>
       <c r="AQ482" t="n">
         <v>87.44493392070484</v>
@@ -79138,10 +79138,10 @@
         <v>-0.3026099231499435</v>
       </c>
       <c r="AI483" t="n">
-        <v>6.731179671396997</v>
+        <v>6.731179671396989</v>
       </c>
       <c r="AJ483" t="n">
-        <v>0.04132036674997597</v>
+        <v>0.04132036674998396</v>
       </c>
       <c r="AK483" t="n">
         <v>6.699415101064979</v>
@@ -79153,13 +79153,13 @@
         <v>-0.3930396958464927</v>
       </c>
       <c r="AN483" t="n">
-        <v>0.0176659673264611</v>
+        <v>0.01766596732646103</v>
       </c>
       <c r="AO483" t="n">
         <v>0.6334129699358579</v>
       </c>
       <c r="AP483" t="n">
-        <v>1.837051154471533</v>
+        <v>1.837051154471614</v>
       </c>
       <c r="AQ483" t="n">
         <v>86.84210526315789</v>
@@ -79303,10 +79303,10 @@
         <v>-0.3108543589941197</v>
       </c>
       <c r="AI484" t="n">
-        <v>6.740946959621005</v>
+        <v>6.740946959621007</v>
       </c>
       <c r="AJ484" t="n">
-        <v>0.03085308157772548</v>
+        <v>0.03085308157772371</v>
       </c>
       <c r="AK484" t="n">
         <v>6.714685154719483</v>
@@ -79315,16 +79315,16 @@
         <v>0.05711488647924767</v>
       </c>
       <c r="AM484" t="n">
-        <v>-0.392942339423851</v>
+        <v>-0.3929423394238508</v>
       </c>
       <c r="AN484" t="n">
-        <v>0.0184207037809263</v>
+        <v>0.01842070378092631</v>
       </c>
       <c r="AO484" t="n">
-        <v>0.6403745111659787</v>
+        <v>0.640374511165978</v>
       </c>
       <c r="AP484" t="n">
-        <v>1.708199635372456</v>
+        <v>1.708199635372431</v>
       </c>
       <c r="AQ484" t="n">
         <v>84.71615720524017</v>
@@ -79468,10 +79468,10 @@
         <v>-0.3288542807561932</v>
       </c>
       <c r="AI485" t="n">
-        <v>6.758957757771704</v>
+        <v>6.7589577577717</v>
       </c>
       <c r="AJ485" t="n">
-        <v>0.006742105662134179</v>
+        <v>0.006742105662137732</v>
       </c>
       <c r="AK485" t="n">
         <v>6.722064699270507</v>
@@ -79480,16 +79480,16 @@
         <v>0.04363516416333102</v>
       </c>
       <c r="AM485" t="n">
-        <v>-0.3931401656438955</v>
+        <v>-0.3931401656438959</v>
       </c>
       <c r="AN485" t="n">
-        <v>0.01902711841846487</v>
+        <v>0.01902711841846483</v>
       </c>
       <c r="AO485" t="n">
         <v>0.648485714148394</v>
       </c>
       <c r="AP485" t="n">
-        <v>1.437000826386048</v>
+        <v>1.437000826386082</v>
       </c>
       <c r="AQ485" t="n">
         <v>80.43478260869566</v>
@@ -79633,10 +79633,10 @@
         <v>-0.3275028220247851</v>
       </c>
       <c r="AI486" t="n">
-        <v>6.763209774497788</v>
+        <v>6.763209774497792</v>
       </c>
       <c r="AJ486" t="n">
-        <v>0.007790133949477251</v>
+        <v>0.007790133949473699</v>
       </c>
       <c r="AK486" t="n">
         <v>6.739235851443908</v>
@@ -79645,16 +79645,16 @@
         <v>0.03176405700335749</v>
       </c>
       <c r="AM486" t="n">
-        <v>-0.3951733572725246</v>
+        <v>-0.3951733572725242</v>
       </c>
       <c r="AN486" t="n">
         <v>0.019963995720711</v>
       </c>
       <c r="AO486" t="n">
-        <v>0.6590798145480942</v>
+        <v>0.6590798145480943</v>
       </c>
       <c r="AP486" t="n">
-        <v>1.438670607116224</v>
+        <v>1.438670607116181</v>
       </c>
       <c r="AQ486" t="n">
         <v>80.73593073593074</v>
@@ -79810,16 +79810,16 @@
         <v>0.01350499198054056</v>
       </c>
       <c r="AM487" t="n">
-        <v>-0.396000186332361</v>
+        <v>-0.3960001863323608</v>
       </c>
       <c r="AN487" t="n">
-        <v>0.02043272610569401</v>
+        <v>0.02043272610569408</v>
       </c>
       <c r="AO487" t="n">
-        <v>0.6685846444009627</v>
+        <v>0.6685846444009622</v>
       </c>
       <c r="AP487" t="n">
-        <v>1.620848360850708</v>
+        <v>1.620848360850703</v>
       </c>
       <c r="AQ487" t="n">
         <v>81.25</v>
@@ -79963,10 +79963,10 @@
         <v>-0.3203246073380841</v>
       </c>
       <c r="AI488" t="n">
-        <v>6.714622134232888</v>
+        <v>6.714622134232894</v>
       </c>
       <c r="AJ488" t="n">
-        <v>0.04037798020802974</v>
+        <v>0.04037798020802441</v>
       </c>
       <c r="AK488" t="n">
         <v>6.746779913842831</v>
@@ -79975,16 +79975,16 @@
         <v>0.008220200598087146</v>
       </c>
       <c r="AM488" t="n">
-        <v>-0.3967409053619114</v>
+        <v>-0.396740905361911</v>
       </c>
       <c r="AN488" t="n">
-        <v>0.02120763540003743</v>
+        <v>0.02120763540003751</v>
       </c>
       <c r="AO488" t="n">
-        <v>0.6777865296786978</v>
+        <v>0.6777865296786982</v>
       </c>
       <c r="AP488" t="n">
-        <v>1.761306144067141</v>
+        <v>1.761306144067079</v>
       </c>
       <c r="AQ488" t="n">
         <v>83.90557939914163</v>
@@ -80128,28 +80128,28 @@
         <v>-0.3340959985244947</v>
       </c>
       <c r="AI489" t="n">
-        <v>6.73157005939442</v>
+        <v>6.731570059394423</v>
       </c>
       <c r="AJ489" t="n">
-        <v>0.01932973232310964</v>
+        <v>0.01932973232310609</v>
       </c>
       <c r="AK489" t="n">
-        <v>6.728823425344639</v>
+        <v>6.728823425344638</v>
       </c>
       <c r="AL489" t="n">
-        <v>0.02207636637289045</v>
+        <v>0.02207636637289134</v>
       </c>
       <c r="AM489" t="n">
         <v>-0.3968575339788111</v>
       </c>
       <c r="AN489" t="n">
-        <v>0.02200829621703764</v>
+        <v>0.0220082962170377</v>
       </c>
       <c r="AO489" t="n">
         <v>0.6856993240123035</v>
       </c>
       <c r="AP489" t="n">
-        <v>1.524965965273247</v>
+        <v>1.524965965273205</v>
       </c>
       <c r="AQ489" t="n">
         <v>79.27350427350427</v>
@@ -80293,10 +80293,10 @@
         <v>-0.3456268937433125</v>
       </c>
       <c r="AI490" t="n">
-        <v>6.748064561399863</v>
+        <v>6.748064561399866</v>
       </c>
       <c r="AJ490" t="n">
-        <v>0.00423522421415079</v>
+        <v>0.004235224214148126</v>
       </c>
       <c r="AK490" t="n">
         <v>6.740096815166266</v>
@@ -80305,16 +80305,16 @@
         <v>0.01220297044774732</v>
       </c>
       <c r="AM490" t="n">
-        <v>-0.3976889317784196</v>
+        <v>-0.3976889317784199</v>
       </c>
       <c r="AN490" t="n">
-        <v>0.02268190844878653</v>
+        <v>0.02268190844878654</v>
       </c>
       <c r="AO490" t="n">
-        <v>0.6953567146475526</v>
+        <v>0.6953567146475523</v>
       </c>
       <c r="AP490" t="n">
-        <v>1.355542505445825</v>
+        <v>1.355542505445795</v>
       </c>
       <c r="AQ490" t="n">
         <v>74.25531914893617</v>
@@ -80458,10 +80458,10 @@
         <v>-0.3468885181379404</v>
       </c>
       <c r="AI491" t="n">
-        <v>6.747226278872151</v>
+        <v>6.747226278872152</v>
       </c>
       <c r="AJ491" t="n">
-        <v>0.005973775296550521</v>
+        <v>0.005973775296548745</v>
       </c>
       <c r="AK491" t="n">
         <v>6.755554272205931</v>
@@ -80470,16 +80470,16 @@
         <v>-0.002354218037229572</v>
       </c>
       <c r="AM491" t="n">
-        <v>-0.400351527586135</v>
+        <v>-0.4003515275861345</v>
       </c>
       <c r="AN491" t="n">
-        <v>0.02398656672240616</v>
+        <v>0.02398656672240618</v>
       </c>
       <c r="AO491" t="n">
-        <v>0.7067969646460924</v>
+        <v>0.7067969646460921</v>
       </c>
       <c r="AP491" t="n">
-        <v>1.365693002475604</v>
+        <v>1.365693002475583</v>
       </c>
       <c r="AQ491" t="n">
         <v>73.94067796610169</v>
@@ -80623,10 +80623,10 @@
         <v>-0.3419644234534092</v>
       </c>
       <c r="AI492" t="n">
-        <v>6.724989986752573</v>
+        <v>6.724989986752571</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0.02471008267491737</v>
+        <v>0.02471008267491914</v>
       </c>
       <c r="AK492" t="n">
         <v>6.75925064743029</v>
@@ -80635,7 +80635,7 @@
         <v>-0.009550578002800236</v>
       </c>
       <c r="AM492" t="n">
-        <v>-0.4017887258056131</v>
+        <v>-0.4017887258056133</v>
       </c>
       <c r="AN492" t="n">
         <v>0.02482212216928553</v>
@@ -80644,7 +80644,7 @@
         <v>0.7172988664983253</v>
       </c>
       <c r="AP492" t="n">
-        <v>1.553659964165089</v>
+        <v>1.553659964165104</v>
       </c>
       <c r="AQ492" t="n">
         <v>77.42616033755274</v>
@@ -80788,28 +80788,28 @@
         <v>-0.3448997849091837</v>
       </c>
       <c r="AI493" t="n">
-        <v>6.738231277482303</v>
+        <v>6.738231277482312</v>
       </c>
       <c r="AJ493" t="n">
-        <v>0.01056852339049996</v>
+        <v>0.01056852339049108</v>
       </c>
       <c r="AK493" t="n">
-        <v>6.734775445902896</v>
+        <v>6.734775445902895</v>
       </c>
       <c r="AL493" t="n">
-        <v>0.01402435496990684</v>
+        <v>0.01402435496990773</v>
       </c>
       <c r="AM493" t="n">
-        <v>-0.402229404255429</v>
+        <v>-0.4022294042554291</v>
       </c>
       <c r="AN493" t="n">
-        <v>0.02545790195722734</v>
+        <v>0.02545790195722747</v>
       </c>
       <c r="AO493" t="n">
-        <v>0.7273309315128232</v>
+        <v>0.7273309315128231</v>
       </c>
       <c r="AP493" t="n">
-        <v>1.394965385482637</v>
+        <v>1.394965385482541</v>
       </c>
       <c r="AQ493" t="n">
         <v>74.78991596638656</v>
@@ -80953,10 +80953,10 @@
         <v>-0.3389992354304407</v>
       </c>
       <c r="AI494" t="n">
-        <v>6.718201282169575</v>
+        <v>6.718201282169581</v>
       </c>
       <c r="AJ494" t="n">
-        <v>0.02919852480674301</v>
+        <v>0.02919852480673768</v>
       </c>
       <c r="AK494" t="n">
         <v>6.753996132599221</v>
@@ -80965,16 +80965,16 @@
         <v>-0.00659632562290291</v>
       </c>
       <c r="AM494" t="n">
-        <v>-0.4027953816469059</v>
+        <v>-0.4027953816469058</v>
       </c>
       <c r="AN494" t="n">
-        <v>0.02608258444417639</v>
+        <v>0.02608258444417638</v>
       </c>
       <c r="AO494" t="n">
         <v>0.736674421029931</v>
       </c>
       <c r="AP494" t="n">
-        <v>1.58041832563928</v>
+        <v>1.580418325639223</v>
       </c>
       <c r="AQ494" t="n">
         <v>78.66108786610879</v>
@@ -81118,10 +81118,10 @@
         <v>-0.3329117502755388</v>
       </c>
       <c r="AI495" t="n">
-        <v>6.730898772467415</v>
+        <v>6.730898772467414</v>
       </c>
       <c r="AJ495" t="n">
-        <v>0.01650103450890317</v>
+        <v>0.01650103450890406</v>
       </c>
       <c r="AK495" t="n">
         <v>6.732394407262716</v>
@@ -81130,16 +81130,16 @@
         <v>0.01500539971360215</v>
       </c>
       <c r="AM495" t="n">
-        <v>-0.402509900769414</v>
+        <v>-0.4025099007694142</v>
       </c>
       <c r="AN495" t="n">
-        <v>0.02634377330607648</v>
+        <v>0.02634377330607651</v>
       </c>
       <c r="AO495" t="n">
-        <v>0.7465615195282662</v>
+        <v>0.746561519528266</v>
       </c>
       <c r="AP495" t="n">
-        <v>1.437183781016368</v>
+        <v>1.437183781016376</v>
       </c>
       <c r="AQ495" t="n">
         <v>79.16666666666666</v>
@@ -81295,13 +81295,13 @@
         <v>0.001816379339821594</v>
       </c>
       <c r="AM496" t="n">
-        <v>-0.4034224290251453</v>
+        <v>-0.4034224290251451</v>
       </c>
       <c r="AN496" t="n">
-        <v>0.02736182786837866</v>
+        <v>0.02736182786837871</v>
       </c>
       <c r="AO496" t="n">
-        <v>0.7551898634710656</v>
+        <v>0.755189863471066</v>
       </c>
       <c r="AP496" t="n">
         <v>1.302657079643351</v>
@@ -81448,10 +81448,10 @@
         <v>-0.3086955151355042</v>
       </c>
       <c r="AI497" t="n">
-        <v>6.75570846679488</v>
+        <v>6.755708466794879</v>
       </c>
       <c r="AJ497" t="n">
-        <v>-0.01240850570479246</v>
+        <v>-0.01240850570479068</v>
       </c>
       <c r="AK497" t="n">
         <v>6.746865899087779</v>
@@ -81460,16 +81460,16 @@
         <v>-0.003565937997691115</v>
       </c>
       <c r="AM497" t="n">
-        <v>-0.4037073020769305</v>
+        <v>-0.4037073020769307</v>
       </c>
       <c r="AN497" t="n">
-        <v>0.02778289906564353</v>
+        <v>0.02778289906564352</v>
       </c>
       <c r="AO497" t="n">
-        <v>0.7638221248099444</v>
+        <v>0.7638221248099442</v>
       </c>
       <c r="AP497" t="n">
-        <v>1.120529895849317</v>
+        <v>1.120529895849335</v>
       </c>
       <c r="AQ497" t="n">
         <v>80.16528925619835</v>
@@ -81613,10 +81613,10 @@
         <v>-0.3044857117372084</v>
       </c>
       <c r="AI498" t="n">
-        <v>6.73601646973097</v>
+        <v>6.73601646973098</v>
       </c>
       <c r="AJ498" t="n">
-        <v>0.006783766017321113</v>
+        <v>0.006783766017311343</v>
       </c>
       <c r="AK498" t="n">
         <v>6.761018647414997</v>
@@ -81625,16 +81625,16 @@
         <v>-0.01821841166670612</v>
       </c>
       <c r="AM498" t="n">
-        <v>-0.4035108188951355</v>
+        <v>-0.403510818895136</v>
       </c>
       <c r="AN498" t="n">
-        <v>0.02805871830419202</v>
+        <v>0.02805871830419215</v>
       </c>
       <c r="AO498" t="n">
         <v>0.7683919203573231</v>
       </c>
       <c r="AP498" t="n">
-        <v>1.314684197600949</v>
+        <v>1.314684197600847</v>
       </c>
       <c r="AQ498" t="n">
         <v>83.74485596707819</v>
@@ -81793,7 +81793,7 @@
         <v>-0.4027898636641267</v>
       </c>
       <c r="AN499" t="n">
-        <v>0.02827333203020884</v>
+        <v>0.02827333203020888</v>
       </c>
       <c r="AO499" t="n">
         <v>0.7726830480787004</v>
@@ -81943,10 +81943,10 @@
         <v>-0.3061509986743562</v>
       </c>
       <c r="AI500" t="n">
-        <v>6.725806144687716</v>
+        <v>6.725806144687715</v>
       </c>
       <c r="AJ500" t="n">
-        <v>0.01409396746438318</v>
+        <v>0.01409396746438496</v>
       </c>
       <c r="AK500" t="n">
         <v>6.744478107428201</v>
@@ -81955,16 +81955,16 @@
         <v>-0.004577995276100921</v>
       </c>
       <c r="AM500" t="n">
-        <v>-0.4027900432658339</v>
+        <v>-0.4027900432658338</v>
       </c>
       <c r="AN500" t="n">
-        <v>0.0289145361322863</v>
+        <v>0.02891453613228628</v>
       </c>
       <c r="AO500" t="n">
-        <v>0.7784357006627718</v>
+        <v>0.7784357006627721</v>
       </c>
       <c r="AP500" t="n">
-        <v>1.374622432787269</v>
+        <v>1.374622432787288</v>
       </c>
       <c r="AQ500" t="n">
         <v>83.67346938775509</v>
@@ -82108,10 +82108,10 @@
         <v>-0.2816739226305129</v>
       </c>
       <c r="AI501" t="n">
-        <v>6.700854569500285</v>
+        <v>6.700854569500288</v>
       </c>
       <c r="AJ501" t="n">
-        <v>0.04174539464156091</v>
+        <v>0.04174539464155735</v>
       </c>
       <c r="AK501" t="n">
         <v>6.743301592583855</v>
@@ -82120,16 +82120,16 @@
         <v>-0.0007016284420089391</v>
       </c>
       <c r="AM501" t="n">
-        <v>-0.4027426974585472</v>
+        <v>-0.402742697458547</v>
       </c>
       <c r="AN501" t="n">
-        <v>0.0295556803648227</v>
+        <v>0.02955568036482276</v>
       </c>
       <c r="AO501" t="n">
-        <v>0.7839391318357879</v>
+        <v>0.7839391318357882</v>
       </c>
       <c r="AP501" t="n">
-        <v>1.650860867528334</v>
+        <v>1.650860867528298</v>
       </c>
       <c r="AQ501" t="n">
         <v>88.6178861788618</v>
@@ -82273,10 +82273,10 @@
         <v>-0.3051321154354865</v>
       </c>
       <c r="AI502" t="n">
-        <v>6.705597066237454</v>
+        <v>6.705597066237452</v>
       </c>
       <c r="AJ502" t="n">
-        <v>0.02390275065707748</v>
+        <v>0.02390275065707925</v>
       </c>
       <c r="AK502" t="n">
         <v>6.74285285202661</v>
@@ -82285,16 +82285,16 @@
         <v>-0.01335303513207897</v>
       </c>
       <c r="AM502" t="n">
-        <v>-0.4015885003200582</v>
+        <v>-0.401588500320058</v>
       </c>
       <c r="AN502" t="n">
-        <v>0.02985284499018428</v>
+        <v>0.02985284499018426</v>
       </c>
       <c r="AO502" t="n">
         <v>0.7880284607160943</v>
       </c>
       <c r="AP502" t="n">
-        <v>1.455808053167857</v>
+        <v>1.455808053167875</v>
       </c>
       <c r="AQ502" t="n">
         <v>85.22267206477733</v>
@@ -82438,28 +82438,28 @@
         <v>-0.3102807084114545</v>
       </c>
       <c r="AI503" t="n">
-        <v>6.686024746022948</v>
+        <v>6.686024746022946</v>
       </c>
       <c r="AJ503" t="n">
-        <v>0.03647510138916132</v>
+        <v>0.0364751013891631</v>
       </c>
       <c r="AK503" t="n">
-        <v>6.744526329542679</v>
+        <v>6.744526329542678</v>
       </c>
       <c r="AL503" t="n">
-        <v>-0.02202648213056957</v>
+        <v>-0.02202648213056868</v>
       </c>
       <c r="AM503" t="n">
         <v>-0.4006335261718523</v>
       </c>
       <c r="AN503" t="n">
-        <v>0.02995529076246446</v>
+        <v>0.02995529076246445</v>
       </c>
       <c r="AO503" t="n">
-        <v>0.7933293013213371</v>
+        <v>0.7933293013213367</v>
       </c>
       <c r="AP503" t="n">
-        <v>1.575202902620198</v>
+        <v>1.575202902620216</v>
       </c>
       <c r="AQ503" t="n">
         <v>84.4758064516129</v>
@@ -82603,10 +82603,10 @@
         <v>-0.3079326643460796</v>
       </c>
       <c r="AI504" t="n">
-        <v>6.689653251437547</v>
+        <v>6.689653251437546</v>
       </c>
       <c r="AJ504" t="n">
-        <v>0.03134694311201347</v>
+        <v>0.03134694311201436</v>
       </c>
       <c r="AK504" t="n">
         <v>6.730402461316146</v>
@@ -82615,16 +82615,16 @@
         <v>-0.009402266766585399</v>
       </c>
       <c r="AM504" t="n">
-        <v>-0.3993041981056886</v>
+        <v>-0.3993041981056888</v>
       </c>
       <c r="AN504" t="n">
-        <v>0.03010093147709737</v>
+        <v>0.03010093147709741</v>
       </c>
       <c r="AO504" t="n">
-        <v>0.7985853639949436</v>
+        <v>0.7985853639949437</v>
       </c>
       <c r="AP504" t="n">
-        <v>1.51200548439217</v>
+        <v>1.512005484392179</v>
       </c>
       <c r="AQ504" t="n">
         <v>85.14056224899599</v>
@@ -82768,10 +82768,10 @@
         <v>-0.3053946098528053</v>
       </c>
       <c r="AI505" t="n">
-        <v>6.716786041117424</v>
+        <v>6.716786041117415</v>
       </c>
       <c r="AJ505" t="n">
-        <v>0.005113945149665788</v>
+        <v>0.00511394514967467</v>
       </c>
       <c r="AK505" t="n">
         <v>6.728106442363027</v>
@@ -82780,16 +82780,16 @@
         <v>-0.00620645609593673</v>
       </c>
       <c r="AM505" t="n">
-        <v>-0.3976134529492094</v>
+        <v>-0.3976134529492091</v>
       </c>
       <c r="AN505" t="n">
-        <v>0.03006044259180338</v>
+        <v>0.03006044259180324</v>
       </c>
       <c r="AO505" t="n">
-        <v>0.8026437279892848</v>
+        <v>0.8026437279892851</v>
       </c>
       <c r="AP505" t="n">
-        <v>1.234777974751887</v>
+        <v>1.234777974751978</v>
       </c>
       <c r="AQ505" t="n">
         <v>81.59999999999999</v>
@@ -82933,10 +82933,10 @@
         <v>-0.2950483744078509</v>
       </c>
       <c r="AI506" t="n">
-        <v>6.72193279551444</v>
+        <v>6.721932795514441</v>
       </c>
       <c r="AJ506" t="n">
-        <v>-0.001632597913121536</v>
+        <v>-0.001632597913122424</v>
       </c>
       <c r="AK506" t="n">
         <v>6.752314636061016</v>
@@ -82948,13 +82948,13 @@
         <v>-0.3970272765443574</v>
       </c>
       <c r="AN506" t="n">
-        <v>0.03043336917902487</v>
+        <v>0.03043336917902489</v>
       </c>
       <c r="AO506" t="n">
         <v>0.8059543095734281</v>
       </c>
       <c r="AP506" t="n">
-        <v>1.163823515923099</v>
+        <v>1.163823515923089</v>
       </c>
       <c r="AQ506" t="n">
         <v>82.19999999999999</v>
@@ -83098,28 +83098,28 @@
         <v>-0.2936792078827581</v>
       </c>
       <c r="AI507" t="n">
-        <v>6.718669003366529</v>
+        <v>6.718669003366535</v>
       </c>
       <c r="AJ507" t="n">
-        <v>0.003830844045580761</v>
+        <v>0.003830844045574544</v>
       </c>
       <c r="AK507" t="n">
-        <v>6.750203856204786</v>
+        <v>6.750203856204787</v>
       </c>
       <c r="AL507" t="n">
-        <v>-0.02770400879267676</v>
+        <v>-0.02770400879267765</v>
       </c>
       <c r="AM507" t="n">
-        <v>-0.3969152632178359</v>
+        <v>-0.3969152632178358</v>
       </c>
       <c r="AN507" t="n">
-        <v>0.03100517332816427</v>
+        <v>0.03100517332816438</v>
       </c>
       <c r="AO507" t="n">
-        <v>0.8091236362457366</v>
+        <v>0.8091236362457368</v>
       </c>
       <c r="AP507" t="n">
-        <v>1.217453571381111</v>
+        <v>1.217453571381047</v>
       </c>
       <c r="AQ507" t="n">
         <v>82.80000000000001</v>
@@ -83263,10 +83263,10 @@
         <v>-0.2654341946961871</v>
       </c>
       <c r="AI508" t="n">
-        <v>6.680190080689519</v>
+        <v>6.680190080689523</v>
       </c>
       <c r="AJ508" t="n">
-        <v>0.04230976672259068</v>
+        <v>0.04230976672258624</v>
       </c>
       <c r="AK508" t="n">
         <v>6.74780904069481</v>
@@ -83275,16 +83275,16 @@
         <v>-0.02530919328270098</v>
       </c>
       <c r="AM508" t="n">
-        <v>-0.3964565291282773</v>
+        <v>-0.3964565291282772</v>
       </c>
       <c r="AN508" t="n">
-        <v>0.03139664408873165</v>
+        <v>0.03139664408873172</v>
       </c>
       <c r="AO508" t="n">
-        <v>0.8123541153569371</v>
+        <v>0.8123541153569376</v>
       </c>
       <c r="AP508" t="n">
-        <v>1.60449324842414</v>
+        <v>1.604493248424094</v>
       </c>
       <c r="AQ508" t="n">
         <v>89.8</v>
@@ -83428,10 +83428,10 @@
         <v>-0.2603878539235573</v>
       </c>
       <c r="AI509" t="n">
-        <v>6.671580974366949</v>
+        <v>6.671580974366952</v>
       </c>
       <c r="AJ509" t="n">
-        <v>0.05441885778637179</v>
+        <v>0.05441885778636824</v>
       </c>
       <c r="AK509" t="n">
         <v>6.701878095437348</v>
@@ -83443,13 +83443,13 @@
         <v>-0.3949628888934956</v>
       </c>
       <c r="AN509" t="n">
-        <v>0.03163116863423025</v>
+        <v>0.03163116863423027</v>
       </c>
       <c r="AO509" t="n">
-        <v>0.8147568654710426</v>
+        <v>0.8147568654710424</v>
       </c>
       <c r="AP509" t="n">
-        <v>1.717274375116493</v>
+        <v>1.717274375116458</v>
       </c>
       <c r="AQ509" t="n">
         <v>90.2</v>
@@ -83593,28 +83593,28 @@
         <v>-0.2536944038688542</v>
       </c>
       <c r="AI510" t="n">
-        <v>6.656216276126093</v>
+        <v>6.656216276126097</v>
       </c>
       <c r="AJ510" t="n">
-        <v>0.06978355602722708</v>
+        <v>0.06978355602722353</v>
       </c>
       <c r="AK510" t="n">
-        <v>6.701765808189925</v>
+        <v>6.701765808189924</v>
       </c>
       <c r="AL510" t="n">
-        <v>0.02423402396339558</v>
+        <v>0.02423402396339647</v>
       </c>
       <c r="AM510" t="n">
-        <v>-0.3932426568003567</v>
+        <v>-0.3932426568003564</v>
       </c>
       <c r="AN510" t="n">
-        <v>0.03191273276172183</v>
+        <v>0.0319127327617218</v>
       </c>
       <c r="AO510" t="n">
-        <v>0.8170879052811416</v>
+        <v>0.8170879052811413</v>
       </c>
       <c r="AP510" t="n">
-        <v>1.858889534485378</v>
+        <v>1.858889534485343</v>
       </c>
       <c r="AQ510" t="n">
         <v>90.59999999999999</v>
@@ -83764,19 +83764,19 @@
         <v>0.06711910062773718</v>
       </c>
       <c r="AK511" t="n">
-        <v>6.682658801267994</v>
+        <v>6.682658801267993</v>
       </c>
       <c r="AL511" t="n">
-        <v>0.03754126053010154</v>
+        <v>0.03754126053010243</v>
       </c>
       <c r="AM511" t="n">
         <v>-0.3912302977255052</v>
       </c>
       <c r="AN511" t="n">
-        <v>0.03225018457163047</v>
+        <v>0.03225018457163042</v>
       </c>
       <c r="AO511" t="n">
-        <v>0.8195353634242113</v>
+        <v>0.8195353634242114</v>
       </c>
       <c r="AP511" t="n">
         <v>1.818117584748586</v>
@@ -83923,10 +83923,10 @@
         <v>-0.2627336707354031</v>
       </c>
       <c r="AI512" t="n">
-        <v>6.654231073451242</v>
+        <v>6.654231073451243</v>
       </c>
       <c r="AJ512" t="n">
-        <v>0.06476878921965668</v>
+        <v>0.06476878921965579</v>
       </c>
       <c r="AK512" t="n">
         <v>6.682840937292736</v>
@@ -83935,16 +83935,16 @@
         <v>0.0361589253781629</v>
       </c>
       <c r="AM512" t="n">
-        <v>-0.3894836768645476</v>
+        <v>-0.3894836768645471</v>
       </c>
       <c r="AN512" t="n">
-        <v>0.03277193700354209</v>
+        <v>0.03277193700354208</v>
       </c>
       <c r="AO512" t="n">
         <v>0.8225580809638018</v>
       </c>
       <c r="AP512" t="n">
-        <v>1.781104797300574</v>
+        <v>1.781104797300566</v>
       </c>
       <c r="AQ512" t="n">
         <v>90.2</v>
@@ -84088,10 +84088,10 @@
         <v>-0.253393206922583</v>
       </c>
       <c r="AI513" t="n">
-        <v>6.650937329061552</v>
+        <v>6.650937329061554</v>
       </c>
       <c r="AJ513" t="n">
-        <v>0.06806253360934633</v>
+        <v>0.06806253360934456</v>
       </c>
       <c r="AK513" t="n">
         <v>6.698821600583909</v>
@@ -84100,16 +84100,16 @@
         <v>0.02017826208698903</v>
       </c>
       <c r="AM513" t="n">
-        <v>-0.3885003849593203</v>
+        <v>-0.3885003849593205</v>
       </c>
       <c r="AN513" t="n">
         <v>0.03373576842400933</v>
       </c>
       <c r="AO513" t="n">
-        <v>0.8264954348925952</v>
+        <v>0.8264954348925954</v>
       </c>
       <c r="AP513" t="n">
-        <v>1.799874833536367</v>
+        <v>1.79987483353635</v>
       </c>
       <c r="AQ513" t="n">
         <v>91</v>
@@ -84253,10 +84253,10 @@
         <v>-0.2506331473053347</v>
       </c>
       <c r="AI514" t="n">
-        <v>6.651733245487366</v>
+        <v>6.651733245487365</v>
       </c>
       <c r="AJ514" t="n">
-        <v>0.05906692541107184</v>
+        <v>0.05906692541107272</v>
       </c>
       <c r="AK514" t="n">
         <v>6.69208631505748</v>
@@ -84265,16 +84265,16 @@
         <v>0.01871385584095719</v>
       </c>
       <c r="AM514" t="n">
-        <v>-0.3869746098498528</v>
+        <v>-0.3869746098498524</v>
       </c>
       <c r="AN514" t="n">
-        <v>0.03441888977522091</v>
+        <v>0.0344188897752209</v>
       </c>
       <c r="AO514" t="n">
-        <v>0.8294137131605726</v>
+        <v>0.8294137131605728</v>
       </c>
       <c r="AP514" t="n">
-        <v>1.696616308981445</v>
+        <v>1.696616308981454</v>
       </c>
       <c r="AQ514" t="n">
         <v>90.40000000000001</v>
@@ -84418,10 +84418,10 @@
         <v>-0.2566424956004925</v>
       </c>
       <c r="AI515" t="n">
-        <v>6.632036771677475</v>
+        <v>6.632036771677474</v>
       </c>
       <c r="AJ515" t="n">
-        <v>0.07876339922096243</v>
+        <v>0.07876339922096331</v>
       </c>
       <c r="AK515" t="n">
         <v>6.692627206904497</v>
@@ -84439,7 +84439,7 @@
         <v>0.8315239871298428</v>
       </c>
       <c r="AP515" t="n">
-        <v>1.875440190456845</v>
+        <v>1.875440190456854</v>
       </c>
       <c r="AQ515" t="n">
         <v>91</v>
@@ -84583,10 +84583,10 @@
         <v>-0.2566702428956829</v>
       </c>
       <c r="AI516" t="n">
-        <v>6.617259294346145</v>
+        <v>6.617259294346139</v>
       </c>
       <c r="AJ516" t="n">
-        <v>0.09324046914262496</v>
+        <v>0.09324046914263029</v>
       </c>
       <c r="AK516" t="n">
         <v>6.685306332307247</v>
@@ -84598,13 +84598,13 @@
         <v>-0.3822510793158705</v>
       </c>
       <c r="AN516" t="n">
-        <v>0.03459091746240425</v>
+        <v>0.03459091746240417</v>
       </c>
       <c r="AO516" t="n">
-        <v>0.8328314813119078</v>
+        <v>0.8328314813119074</v>
       </c>
       <c r="AP516" t="n">
-        <v>1.998006000856694</v>
+        <v>1.998006000856745</v>
       </c>
       <c r="AQ516" t="n">
         <v>91</v>
@@ -84760,16 +84760,16 @@
         <v>0.03626545537058501</v>
       </c>
       <c r="AM517" t="n">
-        <v>-0.3791985032227784</v>
+        <v>-0.379198503222778</v>
       </c>
       <c r="AN517" t="n">
-        <v>0.03468237364461172</v>
+        <v>0.03468237364461174</v>
       </c>
       <c r="AO517" t="n">
-        <v>0.8349203610870052</v>
+        <v>0.8349203610870053</v>
       </c>
       <c r="AP517" t="n">
-        <v>2.317228225252932</v>
+        <v>2.317228225252931</v>
       </c>
       <c r="AQ517" t="n">
         <v>93</v>
@@ -84928,13 +84928,13 @@
         <v>-0.374377214117826</v>
       </c>
       <c r="AN518" t="n">
-        <v>0.0343742787852416</v>
+        <v>0.03437427878524163</v>
       </c>
       <c r="AO518" t="n">
-        <v>0.8337972329517072</v>
+        <v>0.8337972329517069</v>
       </c>
       <c r="AP518" t="n">
-        <v>2.426255822246375</v>
+        <v>2.426255822246373</v>
       </c>
       <c r="AQ518" t="n">
         <v>93.40000000000001</v>
@@ -85078,10 +85078,10 @@
         <v>-0.2483229054629721</v>
       </c>
       <c r="AI519" t="n">
-        <v>6.57078983057249</v>
+        <v>6.570789830572489</v>
       </c>
       <c r="AJ519" t="n">
-        <v>0.1372103525329784</v>
+        <v>0.1372103525329802</v>
       </c>
       <c r="AK519" t="n">
         <v>6.617345065810827</v>
@@ -85090,16 +85090,16 @@
         <v>0.09065511729464149</v>
       </c>
       <c r="AM519" t="n">
-        <v>-0.3685435183382902</v>
+        <v>-0.3685435183382903</v>
       </c>
       <c r="AN519" t="n">
-        <v>0.03361173230743112</v>
+        <v>0.03361173230743109</v>
       </c>
       <c r="AO519" t="n">
-        <v>0.8313650598704546</v>
+        <v>0.8313650598704547</v>
       </c>
       <c r="AP519" t="n">
-        <v>2.33221640036803</v>
+        <v>2.332216400368044</v>
       </c>
       <c r="AQ519" t="n">
         <v>91.8</v>
@@ -85243,10 +85243,10 @@
         <v>-0.2475852618441712</v>
       </c>
       <c r="AI520" t="n">
-        <v>6.574987720536736</v>
+        <v>6.574987720536733</v>
       </c>
       <c r="AJ520" t="n">
-        <v>0.1332122573380197</v>
+        <v>0.1332122573380232</v>
       </c>
       <c r="AK520" t="n">
         <v>6.613295682645951</v>
@@ -85255,16 +85255,16 @@
         <v>0.09490429522880461</v>
       </c>
       <c r="AM520" t="n">
-        <v>-0.3628803332699742</v>
+        <v>-0.362880333269974</v>
       </c>
       <c r="AN520" t="n">
-        <v>0.03286620172062364</v>
+        <v>0.0328662017206236</v>
       </c>
       <c r="AO520" t="n">
-        <v>0.8299335523861298</v>
+        <v>0.82993355238613</v>
       </c>
       <c r="AP520" t="n">
-        <v>2.265952574875376</v>
+        <v>2.265952574875406</v>
       </c>
       <c r="AQ520" t="n">
         <v>91.8</v>
@@ -85420,16 +85420,16 @@
         <v>0.1007055635562768</v>
       </c>
       <c r="AM521" t="n">
-        <v>-0.3578313453157059</v>
+        <v>-0.3578313453157061</v>
       </c>
       <c r="AN521" t="n">
-        <v>0.03253304912369535</v>
+        <v>0.03253304912369537</v>
       </c>
       <c r="AO521" t="n">
-        <v>0.829501685468071</v>
+        <v>0.8295016854680709</v>
       <